--- a/data/OVS.MI.xlsx
+++ b/data/OVS.MI.xlsx
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03756380081177</t>
+    <t xml:space="preserve">5.03756427764893</t>
   </si>
   <si>
     <t xml:space="preserve">OVS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89862394332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76365327835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64456272125244</t>
+    <t xml:space="preserve">4.89862489700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76365375518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64456224441528</t>
   </si>
   <si>
     <t xml:space="preserve">4.71998691558838</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65647125244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78747224807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94229030609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69219827651978</t>
+    <t xml:space="preserve">4.65647077560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78747129440308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94229078292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69219923019409</t>
   </si>
   <si>
     <t xml:space="preserve">4.60486507415771</t>
@@ -74,13 +74,13 @@
     <t xml:space="preserve">4.63662338256836</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61677408218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25156021118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22774219512939</t>
+    <t xml:space="preserve">4.616774559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2515606880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22774267196655</t>
   </si>
   <si>
     <t xml:space="preserve">4.53341007232666</t>
@@ -92,10 +92,10 @@
     <t xml:space="preserve">4.47783422470093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49768304824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51356172561646</t>
+    <t xml:space="preserve">4.49768257141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51356220245361</t>
   </si>
   <si>
     <t xml:space="preserve">4.4460768699646</t>
@@ -113,25 +113,25 @@
     <t xml:space="preserve">4.5453200340271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32698535919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03322649002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02925729751587</t>
+    <t xml:space="preserve">4.32698583602905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03322601318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02925682067871</t>
   </si>
   <si>
     <t xml:space="preserve">4.27934885025024</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2237720489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38256168365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30316734313965</t>
+    <t xml:space="preserve">4.22377252578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38256120681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30316781997681</t>
   </si>
   <si>
     <t xml:space="preserve">4.469895362854</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">4.48974323272705</t>
   </si>
   <si>
-    <t xml:space="preserve">4.271409034729</t>
+    <t xml:space="preserve">4.27140855789185</t>
   </si>
   <si>
     <t xml:space="preserve">4.23965167999268</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">4.43813705444336</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5651683807373</t>
+    <t xml:space="preserve">4.56516885757446</t>
   </si>
   <si>
     <t xml:space="preserve">4.67234992980957</t>
@@ -173,10 +173,10 @@
     <t xml:space="preserve">4.52547121047974</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38653039932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43019771575928</t>
+    <t xml:space="preserve">4.38653135299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43019819259644</t>
   </si>
   <si>
     <t xml:space="preserve">4.40240955352783</t>
@@ -185,13 +185,13 @@
     <t xml:space="preserve">4.29125833511353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12055969238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09674119949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06498432159424</t>
+    <t xml:space="preserve">4.12056064605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09674167633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0649847984314</t>
   </si>
   <si>
     <t xml:space="preserve">4.08880281448364</t>
@@ -203,13 +203,13 @@
     <t xml:space="preserve">4.21186399459839</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04910564422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02131748199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31110572814941</t>
+    <t xml:space="preserve">4.04910516738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02131795883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31110620498657</t>
   </si>
   <si>
     <t xml:space="preserve">4.16422748565674</t>
@@ -218,13 +218,13 @@
     <t xml:space="preserve">4.23568201065063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50959157943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73586654663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54928970336914</t>
+    <t xml:space="preserve">4.50959205627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7358660697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54928922653198</t>
   </si>
   <si>
     <t xml:space="preserve">4.50165271759033</t>
@@ -236,10 +236,10 @@
     <t xml:space="preserve">4.48180389404297</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52150106430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55325841903687</t>
+    <t xml:space="preserve">4.5215015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55325889587402</t>
   </si>
   <si>
     <t xml:space="preserve">4.5413498878479</t>
@@ -248,49 +248,49 @@
     <t xml:space="preserve">4.56913709640503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53737926483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64853191375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70410776138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84304809570312</t>
+    <t xml:space="preserve">4.53737878799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64853239059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7041072845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84304761886597</t>
   </si>
   <si>
     <t xml:space="preserve">4.89068460464478</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81525945663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87877511978149</t>
+    <t xml:space="preserve">4.81525993347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87877559661865</t>
   </si>
   <si>
     <t xml:space="preserve">4.91053295135498</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75968408584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73826885223389</t>
+    <t xml:space="preserve">4.75968360900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73826837539673</t>
   </si>
   <si>
     <t xml:space="preserve">4.7667875289917</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90123510360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73419427871704</t>
+    <t xml:space="preserve">4.90123558044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73419380187988</t>
   </si>
   <si>
     <t xml:space="preserve">4.5671534538269</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51826238632202</t>
+    <t xml:space="preserve">4.51826333999634</t>
   </si>
   <si>
     <t xml:space="preserve">4.47344636917114</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">4.48974418640137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6323390007019</t>
+    <t xml:space="preserve">4.63233947753906</t>
   </si>
   <si>
     <t xml:space="preserve">4.61196899414062</t>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">4.55085611343384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51418924331665</t>
+    <t xml:space="preserve">4.51418876647949</t>
   </si>
   <si>
     <t xml:space="preserve">4.33085012435913</t>
@@ -320,37 +320,37 @@
     <t xml:space="preserve">3.94706296920776</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13528966903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24529361724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26566314697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30233144760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2575159072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11084461212158</t>
+    <t xml:space="preserve">4.13529014587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24529314041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26566362380981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30233097076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25751543045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11084508895874</t>
   </si>
   <si>
     <t xml:space="preserve">4.09047365188599</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05299186706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18825387954712</t>
+    <t xml:space="preserve">4.05299139022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18825340270996</t>
   </si>
   <si>
     <t xml:space="preserve">4.16380929946899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15566062927246</t>
+    <t xml:space="preserve">4.15566110610962</t>
   </si>
   <si>
     <t xml:space="preserve">4.15973472595215</t>
@@ -359,13 +359,13 @@
     <t xml:space="preserve">4.10677099227905</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04321432113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11899328231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16788291931152</t>
+    <t xml:space="preserve">4.04321384429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11899280548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16788244247437</t>
   </si>
   <si>
     <t xml:space="preserve">4.26158952713013</t>
@@ -374,7 +374,7 @@
     <t xml:space="preserve">4.20047760009766</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20862483978271</t>
+    <t xml:space="preserve">4.20862531661987</t>
   </si>
   <si>
     <t xml:space="preserve">4.233069896698</t>
@@ -383,40 +383,40 @@
     <t xml:space="preserve">4.37159299850464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36751794815063</t>
+    <t xml:space="preserve">4.36751842498779</t>
   </si>
   <si>
     <t xml:space="preserve">4.28603410720825</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27788591384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24121856689453</t>
+    <t xml:space="preserve">4.27788639068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24121809005737</t>
   </si>
   <si>
     <t xml:space="preserve">4.25344133377075</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29825782775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22899580001831</t>
+    <t xml:space="preserve">4.29825735092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22899627685547</t>
   </si>
   <si>
     <t xml:space="preserve">4.0725474357605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17195796966553</t>
+    <t xml:space="preserve">4.17195749282837</t>
   </si>
   <si>
     <t xml:space="preserve">4.19232797622681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10269737243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04158353805542</t>
+    <t xml:space="preserve">4.10269689559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04158306121826</t>
   </si>
   <si>
     <t xml:space="preserve">4.13936376571655</t>
@@ -431,10 +431,10 @@
     <t xml:space="preserve">3.99269413948059</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0334358215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19640254974365</t>
+    <t xml:space="preserve">4.03343534469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19640207290649</t>
   </si>
   <si>
     <t xml:space="preserve">4.15158700942993</t>
@@ -443,13 +443,13 @@
     <t xml:space="preserve">4.08640003204346</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06114053726196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35937023162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37566614151001</t>
+    <t xml:space="preserve">4.06114101409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35936975479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37566661834717</t>
   </si>
   <si>
     <t xml:space="preserve">4.4408540725708</t>
@@ -458,16 +458,16 @@
     <t xml:space="preserve">4.41233444213867</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31862831115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31047964096069</t>
+    <t xml:space="preserve">4.31862783432007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31047916412354</t>
   </si>
   <si>
     <t xml:space="preserve">4.31455326080322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2697377204895</t>
+    <t xml:space="preserve">4.26973819732666</t>
   </si>
   <si>
     <t xml:space="preserve">4.21677350997925</t>
@@ -476,40 +476,40 @@
     <t xml:space="preserve">4.18010568618774</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14343786239624</t>
+    <t xml:space="preserve">4.1434383392334</t>
   </si>
   <si>
     <t xml:space="preserve">4.11491870880127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07417774200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06928825378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08232498168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06440019607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00573110580444</t>
+    <t xml:space="preserve">4.07417726516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06928873062134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08232545852661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06439971923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00573062896729</t>
   </si>
   <si>
     <t xml:space="preserve">3.96010041236877</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05462121963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13121604919434</t>
+    <t xml:space="preserve">4.05462169647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13121557235718</t>
   </si>
   <si>
     <t xml:space="preserve">4.04647302627563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98128533363342</t>
+    <t xml:space="preserve">3.98128485679626</t>
   </si>
   <si>
     <t xml:space="preserve">4.00410175323486</t>
@@ -518,19 +518,19 @@
     <t xml:space="preserve">3.98617577552795</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02528762817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97476744651794</t>
+    <t xml:space="preserve">4.02528715133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97476696968079</t>
   </si>
   <si>
     <t xml:space="preserve">4.02365732192993</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05951023101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04810237884521</t>
+    <t xml:space="preserve">4.05950975418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04810285568237</t>
   </si>
   <si>
     <t xml:space="preserve">4.05136203765869</t>
@@ -539,61 +539,61 @@
     <t xml:space="preserve">3.97965598106384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03017568588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02039861679077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99921154975891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07825136184692</t>
+    <t xml:space="preserve">4.03017616271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02039813995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99921226501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07825183868408</t>
   </si>
   <si>
     <t xml:space="preserve">4.1475133895874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23714399337769</t>
+    <t xml:space="preserve">4.23714447021484</t>
   </si>
   <si>
     <t xml:space="preserve">4.20455121994019</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22492170333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01713848114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02202749252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93076610565186</t>
+    <t xml:space="preserve">4.22492218017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01713895797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02202796936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93076658248901</t>
   </si>
   <si>
     <t xml:space="preserve">3.91283941268921</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8949134349823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87535691261292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94054508209229</t>
+    <t xml:space="preserve">3.89491295814514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87535715103149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94054460525513</t>
   </si>
   <si>
     <t xml:space="preserve">3.93402576446533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89654350280762</t>
+    <t xml:space="preserve">3.89654302597046</t>
   </si>
   <si>
     <t xml:space="preserve">3.95521140098572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00247240066528</t>
+    <t xml:space="preserve">4.00247144699097</t>
   </si>
   <si>
     <t xml:space="preserve">4.3797402381897</t>
@@ -608,22 +608,22 @@
     <t xml:space="preserve">4.35529565811157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29010915756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28195953369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32677698135376</t>
+    <t xml:space="preserve">4.2901086807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28196048736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32677602767944</t>
   </si>
   <si>
     <t xml:space="preserve">4.29418325424194</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33899879455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33492422103882</t>
+    <t xml:space="preserve">4.33899831771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33492469787598</t>
   </si>
   <si>
     <t xml:space="preserve">4.34307384490967</t>
@@ -632,25 +632,25 @@
     <t xml:space="preserve">4.46529817581177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48159503936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40825939178467</t>
+    <t xml:space="preserve">4.48159456253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40825986862183</t>
   </si>
   <si>
     <t xml:space="preserve">4.53863382339478</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55493021011353</t>
+    <t xml:space="preserve">4.55493068695068</t>
   </si>
   <si>
     <t xml:space="preserve">4.52641105651855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5060396194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43270444869995</t>
+    <t xml:space="preserve">4.50604057312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43270492553711</t>
   </si>
   <si>
     <t xml:space="preserve">4.59567213058472</t>
@@ -659,34 +659,34 @@
     <t xml:space="preserve">4.68530464172363</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6730809211731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60382032394409</t>
+    <t xml:space="preserve">4.67308187484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60381984710693</t>
   </si>
   <si>
     <t xml:space="preserve">4.70160055160522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85642004013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8238263130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77493524551392</t>
+    <t xml:space="preserve">4.8564190864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82382583618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77493572235107</t>
   </si>
   <si>
     <t xml:space="preserve">4.7993803024292</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74234294891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78308439254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72604513168335</t>
+    <t xml:space="preserve">4.74234247207642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78308486938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72604560852051</t>
   </si>
   <si>
     <t xml:space="preserve">4.77900981903076</t>
@@ -695,28 +695,28 @@
     <t xml:space="preserve">4.80752992630005</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86456775665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04790639877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01531267166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89716100692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91753149032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88901329040527</t>
+    <t xml:space="preserve">4.86456727981567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04790496826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01531219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89716053009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91753196716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88901281356812</t>
   </si>
   <si>
     <t xml:space="preserve">5.04383182525635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90531015396118</t>
+    <t xml:space="preserve">4.90530967712402</t>
   </si>
   <si>
     <t xml:space="preserve">4.9501256942749</t>
@@ -731,13 +731,13 @@
     <t xml:space="preserve">5.03160905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08457326889038</t>
+    <t xml:space="preserve">5.08457374572754</t>
   </si>
   <si>
     <t xml:space="preserve">5.23939228057861</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19864988327026</t>
+    <t xml:space="preserve">5.19865036010742</t>
   </si>
   <si>
     <t xml:space="preserve">5.14568519592285</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">5.19457626342773</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05605459213257</t>
+    <t xml:space="preserve">5.05605506896973</t>
   </si>
   <si>
     <t xml:space="preserve">5.06420278549194</t>
@@ -758,13 +758,13 @@
     <t xml:space="preserve">5.11716651916504</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25161552429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18235397338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17827987670898</t>
+    <t xml:space="preserve">5.25161457061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18235349655151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17828035354614</t>
   </si>
   <si>
     <t xml:space="preserve">5.25568914413452</t>
@@ -785,13 +785,13 @@
     <t xml:space="preserve">5.10494470596313</t>
   </si>
   <si>
-    <t xml:space="preserve">5.072350025177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94605159759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06827592849731</t>
+    <t xml:space="preserve">5.07235097885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94605207443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06827640533447</t>
   </si>
   <si>
     <t xml:space="preserve">4.98679304122925</t>
@@ -800,7 +800,7 @@
     <t xml:space="preserve">5.03691244125366</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36268186569214</t>
+    <t xml:space="preserve">5.3626823425293</t>
   </si>
   <si>
     <t xml:space="preserve">5.39191770553589</t>
@@ -809,7 +809,7 @@
     <t xml:space="preserve">5.31256341934204</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27915000915527</t>
+    <t xml:space="preserve">5.27915048599243</t>
   </si>
   <si>
     <t xml:space="preserve">5.34597587585449</t>
@@ -818,22 +818,22 @@
     <t xml:space="preserve">5.35432863235474</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32091569900513</t>
+    <t xml:space="preserve">5.32091617584229</t>
   </si>
   <si>
     <t xml:space="preserve">5.33762311935425</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27079820632935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27497434616089</t>
+    <t xml:space="preserve">5.27079772949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27497386932373</t>
   </si>
   <si>
     <t xml:space="preserve">5.18726778030396</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13297176361084</t>
+    <t xml:space="preserve">5.132972240448</t>
   </si>
   <si>
     <t xml:space="preserve">5.2039737701416</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">5.22903347015381</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25409173965454</t>
+    <t xml:space="preserve">5.25409126281738</t>
   </si>
   <si>
     <t xml:space="preserve">5.2624454498291</t>
@@ -857,7 +857,7 @@
     <t xml:space="preserve">5.17891454696655</t>
   </si>
   <si>
-    <t xml:space="preserve">5.249915599823</t>
+    <t xml:space="preserve">5.24991512298584</t>
   </si>
   <si>
     <t xml:space="preserve">5.24573850631714</t>
@@ -878,10 +878,10 @@
     <t xml:space="preserve">5.40444660186768</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37521123886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40027093887329</t>
+    <t xml:space="preserve">5.37521171569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40027046203613</t>
   </si>
   <si>
     <t xml:space="preserve">5.38356494903564</t>
@@ -893,22 +893,22 @@
     <t xml:space="preserve">5.23320960998535</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30838680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2582688331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20814990997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13714838027954</t>
+    <t xml:space="preserve">5.3083872795105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25826835632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2081503868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1371488571167</t>
   </si>
   <si>
     <t xml:space="preserve">5.11208963394165</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15385484695435</t>
+    <t xml:space="preserve">5.1538553237915</t>
   </si>
   <si>
     <t xml:space="preserve">5.23738527297974</t>
@@ -920,13 +920,13 @@
     <t xml:space="preserve">5.30420970916748</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29585742950439</t>
+    <t xml:space="preserve">5.29585695266724</t>
   </si>
   <si>
     <t xml:space="preserve">5.32926940917969</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48797798156738</t>
+    <t xml:space="preserve">5.48797845840454</t>
   </si>
   <si>
     <t xml:space="preserve">5.5380973815918</t>
@@ -938,22 +938,22 @@
     <t xml:space="preserve">5.62580394744873</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68845272064209</t>
+    <t xml:space="preserve">5.68845319747925</t>
   </si>
   <si>
     <t xml:space="preserve">5.61327505111694</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57568550109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44203662872314</t>
+    <t xml:space="preserve">5.57568597793579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44203615188599</t>
   </si>
   <si>
     <t xml:space="preserve">5.62162828445435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68009853363037</t>
+    <t xml:space="preserve">5.68009901046753</t>
   </si>
   <si>
     <t xml:space="preserve">5.64251041412354</t>
@@ -968,19 +968,19 @@
     <t xml:space="preserve">5.38774156570435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24156188964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29168081283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19561958312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08285427093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88655614852905</t>
+    <t xml:space="preserve">5.2415623664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29168033599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19562005996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0828537940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88655567169189</t>
   </si>
   <si>
     <t xml:space="preserve">4.90743923187256</t>
@@ -995,25 +995,25 @@
     <t xml:space="preserve">4.84478998184204</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8364372253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94502782821655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90326309204102</t>
+    <t xml:space="preserve">4.83643770217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94502735137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90326261520386</t>
   </si>
   <si>
     <t xml:space="preserve">4.86567306518555</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87820291519165</t>
+    <t xml:space="preserve">4.87820339202881</t>
   </si>
   <si>
     <t xml:space="preserve">4.8531436920166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81137752532959</t>
+    <t xml:space="preserve">4.81137800216675</t>
   </si>
   <si>
     <t xml:space="preserve">4.95755767822266</t>
@@ -1052,10 +1052,10 @@
     <t xml:space="preserve">4.67355155944824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64014005661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71949434280396</t>
+    <t xml:space="preserve">4.64013957977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7194938659668</t>
   </si>
   <si>
     <t xml:space="preserve">4.79049587249756</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">4.67772912979126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91579246520996</t>
+    <t xml:space="preserve">4.9157919883728</t>
   </si>
   <si>
     <t xml:space="preserve">4.92414426803589</t>
@@ -1094,31 +1094,31 @@
     <t xml:space="preserve">5.02020502090454</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17056035995483</t>
+    <t xml:space="preserve">5.17056083679199</t>
   </si>
   <si>
     <t xml:space="preserve">5.09955930709839</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95338153839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78631925582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68608140945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60672807693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59419822692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61508131027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63178682327271</t>
+    <t xml:space="preserve">4.95338106155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7863187789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6860818862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60672760009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59419775009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61508083343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63178730010986</t>
   </si>
   <si>
     <t xml:space="preserve">4.70696449279785</t>
@@ -1139,46 +1139,46 @@
     <t xml:space="preserve">4.48978424072266</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41042995452881</t>
+    <t xml:space="preserve">4.41043043136597</t>
   </si>
   <si>
     <t xml:space="preserve">4.44384241104126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4939603805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47307777404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51901960372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56913805007935</t>
+    <t xml:space="preserve">4.49395990371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47307825088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51902055740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56913757324219</t>
   </si>
   <si>
     <t xml:space="preserve">4.59002113342285</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65684604644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64849233627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59837484359741</t>
+    <t xml:space="preserve">4.65684652328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64849281311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59837436676025</t>
   </si>
   <si>
     <t xml:space="preserve">4.5607852935791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48560810089111</t>
+    <t xml:space="preserve">4.48560857772827</t>
   </si>
   <si>
     <t xml:space="preserve">4.43966579437256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36031150817871</t>
+    <t xml:space="preserve">4.36031103134155</t>
   </si>
   <si>
     <t xml:space="preserve">4.38537073135376</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">4.19324970245361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09802484512329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15315437316895</t>
+    <t xml:space="preserve">4.09802436828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1531548500061</t>
   </si>
   <si>
     <t xml:space="preserve">4.10303688049316</t>
@@ -1214,7 +1214,7 @@
     <t xml:space="preserve">4.16986131668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17654371261597</t>
+    <t xml:space="preserve">4.17654418945312</t>
   </si>
   <si>
     <t xml:space="preserve">4.1431303024292</t>
@@ -1223,22 +1223,22 @@
     <t xml:space="preserve">4.16819047927856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83002591133118</t>
+    <t xml:space="preserve">2.8300256729126</t>
   </si>
   <si>
     <t xml:space="preserve">2.90687417984009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84339046478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87179160118103</t>
+    <t xml:space="preserve">2.84339070320129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87179183959961</t>
   </si>
   <si>
     <t xml:space="preserve">2.89350938796997</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80162501335144</t>
+    <t xml:space="preserve">2.80162525177002</t>
   </si>
   <si>
     <t xml:space="preserve">2.92358064651489</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">3.01713514328003</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08061838150024</t>
+    <t xml:space="preserve">3.08061861991882</t>
   </si>
   <si>
     <t xml:space="preserve">3.17083120346069</t>
@@ -1259,13 +1259,13 @@
     <t xml:space="preserve">3.14911389350891</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15746641159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14410185813904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17918515205383</t>
+    <t xml:space="preserve">3.15746665000916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14410161972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17918491363525</t>
   </si>
   <si>
     <t xml:space="preserve">3.17417335510254</t>
@@ -1283,13 +1283,13 @@
     <t xml:space="preserve">2.94529819488525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95699238777161</t>
+    <t xml:space="preserve">2.95699262619019</t>
   </si>
   <si>
     <t xml:space="preserve">2.89852142333984</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84004878997803</t>
+    <t xml:space="preserve">2.84004902839661</t>
   </si>
   <si>
     <t xml:space="preserve">2.82501363754272</t>
@@ -1298,10 +1298,10 @@
     <t xml:space="preserve">2.85007309913635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74649548530579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55771493911743</t>
+    <t xml:space="preserve">2.74649524688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55771470069885</t>
   </si>
   <si>
     <t xml:space="preserve">2.54769158363342</t>
@@ -1316,19 +1316,19 @@
     <t xml:space="preserve">2.5009138584137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51594996452332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50592565536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47919607162476</t>
+    <t xml:space="preserve">2.51594972610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50592541694641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47919631004333</t>
   </si>
   <si>
     <t xml:space="preserve">2.41905355453491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39566540718079</t>
+    <t xml:space="preserve">2.39566516876221</t>
   </si>
   <si>
     <t xml:space="preserve">2.36058211326599</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">2.31380534172058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26201558113098</t>
+    <t xml:space="preserve">2.2620153427124</t>
   </si>
   <si>
     <t xml:space="preserve">2.27203965187073</t>
@@ -1364,7 +1364,7 @@
     <t xml:space="preserve">2.30211091041565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29709911346436</t>
+    <t xml:space="preserve">2.29709887504578</t>
   </si>
   <si>
     <t xml:space="preserve">2.32382822036743</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">2.36559438705444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35055804252625</t>
+    <t xml:space="preserve">2.35055780410767</t>
   </si>
   <si>
     <t xml:space="preserve">2.35222935676575</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">2.25533318519592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22025060653687</t>
+    <t xml:space="preserve">2.22025084495544</t>
   </si>
   <si>
     <t xml:space="preserve">2.28039240837097</t>
@@ -1400,19 +1400,19 @@
     <t xml:space="preserve">2.225261926651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23027396202087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40067672729492</t>
+    <t xml:space="preserve">2.23027372360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40067648887634</t>
   </si>
   <si>
     <t xml:space="preserve">2.44912457466125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42406558990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31881666183472</t>
+    <t xml:space="preserve">2.42406582832336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31881642341614</t>
   </si>
   <si>
     <t xml:space="preserve">2.30879354476929</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">2.33218121528625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27371001243591</t>
+    <t xml:space="preserve">2.27370977401733</t>
   </si>
   <si>
     <t xml:space="preserve">2.18850898742676</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">2.17681455612183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15342569351196</t>
+    <t xml:space="preserve">2.15342545509338</t>
   </si>
   <si>
     <t xml:space="preserve">2.21022653579712</t>
@@ -1445,13 +1445,13 @@
     <t xml:space="preserve">2.05485892295837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01142263412476</t>
+    <t xml:space="preserve">2.01142287254333</t>
   </si>
   <si>
     <t xml:space="preserve">1.97466921806335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00474047660828</t>
+    <t xml:space="preserve">2.00474071502686</t>
   </si>
   <si>
     <t xml:space="preserve">2.03815340995789</t>
@@ -1463,10 +1463,10 @@
     <t xml:space="preserve">2.17180252075195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18182563781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1667902469635</t>
+    <t xml:space="preserve">2.18182587623596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16679048538208</t>
   </si>
   <si>
     <t xml:space="preserve">2.16846084594727</t>
@@ -1475,22 +1475,22 @@
     <t xml:space="preserve">2.15509605407715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15676641464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1150016784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07657718658447</t>
+    <t xml:space="preserve">2.15676617622375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11500144004822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07657742500305</t>
   </si>
   <si>
     <t xml:space="preserve">2.08994221687317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09829473495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16010808944702</t>
+    <t xml:space="preserve">2.09829497337341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16010785102844</t>
   </si>
   <si>
     <t xml:space="preserve">2.09662485122681</t>
@@ -1514,10 +1514,10 @@
     <t xml:space="preserve">2.18683767318726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11834263801575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06989526748657</t>
+    <t xml:space="preserve">2.11834239959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06989502906799</t>
   </si>
   <si>
     <t xml:space="preserve">2.06321263313293</t>
@@ -1535,13 +1535,13 @@
     <t xml:space="preserve">1.94626927375793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87610340118408</t>
+    <t xml:space="preserve">1.87610328197479</t>
   </si>
   <si>
     <t xml:space="preserve">1.75748932361603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.695676445961</t>
+    <t xml:space="preserve">1.69567656517029</t>
   </si>
   <si>
     <t xml:space="preserve">1.65391063690186</t>
@@ -1553,10 +1553,10 @@
     <t xml:space="preserve">1.62968695163727</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50439071655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48601388931274</t>
+    <t xml:space="preserve">1.50439083576202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48601400852203</t>
   </si>
   <si>
     <t xml:space="preserve">1.39663565158844</t>
@@ -1589,13 +1589,13 @@
     <t xml:space="preserve">1.3156111240387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31310510635376</t>
+    <t xml:space="preserve">1.31310498714447</t>
   </si>
   <si>
     <t xml:space="preserve">1.2838693857193</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27969288825989</t>
+    <t xml:space="preserve">1.27969300746918</t>
   </si>
   <si>
     <t xml:space="preserve">1.33899998664856</t>
@@ -1613,22 +1613,22 @@
     <t xml:space="preserve">1.24293923377991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25212776660919</t>
+    <t xml:space="preserve">1.2521276473999</t>
   </si>
   <si>
     <t xml:space="preserve">1.26799857616425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25296235084534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2337509393692</t>
+    <t xml:space="preserve">1.25296247005463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23375082015991</t>
   </si>
   <si>
     <t xml:space="preserve">1.25630414485931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2579745054245</t>
+    <t xml:space="preserve">1.25797438621521</t>
   </si>
   <si>
     <t xml:space="preserve">1.26048040390015</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">1.23876285552979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06835913658142</t>
+    <t xml:space="preserve">1.06835925579071</t>
   </si>
   <si>
     <t xml:space="preserve">0.962275266647339</t>
@@ -1679,7 +1679,7 @@
     <t xml:space="preserve">0.862038195133209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958098888397217</t>
+    <t xml:space="preserve">0.958098828792572</t>
   </si>
   <si>
     <t xml:space="preserve">0.948074817657471</t>
@@ -1691,28 +1691,28 @@
     <t xml:space="preserve">0.913827180862427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9447340965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91883909702301</t>
+    <t xml:space="preserve">0.944734156131744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918839156627655</t>
   </si>
   <si>
     <t xml:space="preserve">0.917168796062469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00487565994263</t>
+    <t xml:space="preserve">1.00487577915192</t>
   </si>
   <si>
     <t xml:space="preserve">1.1477142572403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11430144309998</t>
+    <t xml:space="preserve">1.11430132389069</t>
   </si>
   <si>
     <t xml:space="preserve">1.09926617145538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13184344768524</t>
+    <t xml:space="preserve">1.13184332847595</t>
   </si>
   <si>
     <t xml:space="preserve">1.10344254970551</t>
@@ -1721,13 +1721,13 @@
     <t xml:space="preserve">1.0357825756073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01155805587769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01824057102203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999029040336609</t>
+    <t xml:space="preserve">1.01155817508698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01824045181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999028921127319</t>
   </si>
   <si>
     <t xml:space="preserve">1.01573550701141</t>
@@ -1736,10 +1736,10 @@
     <t xml:space="preserve">1.01322960853577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.082559466362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10177206993103</t>
+    <t xml:space="preserve">1.08255958557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10177218914032</t>
   </si>
   <si>
     <t xml:space="preserve">1.1276661157608</t>
@@ -1751,22 +1751,22 @@
     <t xml:space="preserve">1.13017213344574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1368545293808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11346662044525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10260689258575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06585299968719</t>
+    <t xml:space="preserve">1.13685441017151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11346650123596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10260677337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06585311889648</t>
   </si>
   <si>
     <t xml:space="preserve">1.03244113922119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07086527347565</t>
+    <t xml:space="preserve">1.07086515426636</t>
   </si>
   <si>
     <t xml:space="preserve">1.06334805488586</t>
@@ -1775,7 +1775,7 @@
     <t xml:space="preserve">1.01907622814178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03494715690613</t>
+    <t xml:space="preserve">1.03494703769684</t>
   </si>
   <si>
     <t xml:space="preserve">1.06501841545105</t>
@@ -1784,13 +1784,13 @@
     <t xml:space="preserve">1.12850165367126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08506548404694</t>
+    <t xml:space="preserve">1.08506560325623</t>
   </si>
   <si>
     <t xml:space="preserve">1.08673584461212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07253646850586</t>
+    <t xml:space="preserve">1.07253634929657</t>
   </si>
   <si>
     <t xml:space="preserve">1.0808892250061</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">1.1051127910614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07838320732117</t>
+    <t xml:space="preserve">1.07838308811188</t>
   </si>
   <si>
     <t xml:space="preserve">1.10010075569153</t>
@@ -1817,7 +1817,7 @@
     <t xml:space="preserve">1.46179032325745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41584801673889</t>
+    <t xml:space="preserve">1.4158478975296</t>
   </si>
   <si>
     <t xml:space="preserve">1.414177775383</t>
@@ -1826,25 +1826,25 @@
     <t xml:space="preserve">1.36071765422821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33064615726471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29806971549988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37324774265289</t>
+    <t xml:space="preserve">1.330646276474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29806983470917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3732476234436</t>
   </si>
   <si>
     <t xml:space="preserve">1.38744723796844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32981157302856</t>
+    <t xml:space="preserve">1.32981145381927</t>
   </si>
   <si>
     <t xml:space="preserve">1.35069346427917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3548709154129</t>
+    <t xml:space="preserve">1.35487079620361</t>
   </si>
   <si>
     <t xml:space="preserve">1.32897579669952</t>
@@ -1856,13 +1856,13 @@
     <t xml:space="preserve">1.37157642841339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40248322486877</t>
+    <t xml:space="preserve">1.40248334407806</t>
   </si>
   <si>
     <t xml:space="preserve">1.41918885707855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4216947555542</t>
+    <t xml:space="preserve">1.42169487476349</t>
   </si>
   <si>
     <t xml:space="preserve">1.42253053188324</t>
@@ -1889,10 +1889,10 @@
     <t xml:space="preserve">1.52861440181732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61131036281586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5971097946167</t>
+    <t xml:space="preserve">1.61131024360657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59710967540741</t>
   </si>
   <si>
     <t xml:space="preserve">1.59376907348633</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">1.5745564699173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55283892154694</t>
+    <t xml:space="preserve">1.55283880233765</t>
   </si>
   <si>
     <t xml:space="preserve">1.55116760730743</t>
@@ -1916,13 +1916,13 @@
     <t xml:space="preserve">1.41751849651337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43422508239746</t>
+    <t xml:space="preserve">1.43422496318817</t>
   </si>
   <si>
     <t xml:space="preserve">1.38828277587891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38327074050903</t>
+    <t xml:space="preserve">1.38327085971832</t>
   </si>
   <si>
     <t xml:space="preserve">1.33231663703918</t>
@@ -1931,13 +1931,13 @@
     <t xml:space="preserve">1.36740005016327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34985876083374</t>
+    <t xml:space="preserve">1.34985888004303</t>
   </si>
   <si>
     <t xml:space="preserve">1.30308103561401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32229351997375</t>
+    <t xml:space="preserve">1.32229363918304</t>
   </si>
   <si>
     <t xml:space="preserve">1.31644594669342</t>
@@ -1949,16 +1949,16 @@
     <t xml:space="preserve">1.30892860889435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31059908866882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31895196437836</t>
+    <t xml:space="preserve">1.31059896945953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31895184516907</t>
   </si>
   <si>
     <t xml:space="preserve">1.29222226142883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28721010684967</t>
+    <t xml:space="preserve">1.28721022605896</t>
   </si>
   <si>
     <t xml:space="preserve">1.25045645236969</t>
@@ -1970,34 +1970,34 @@
     <t xml:space="preserve">1.31143462657928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31978738307953</t>
+    <t xml:space="preserve">1.31978750228882</t>
   </si>
   <si>
     <t xml:space="preserve">1.34902310371399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34651708602905</t>
+    <t xml:space="preserve">1.34651696681976</t>
   </si>
   <si>
     <t xml:space="preserve">1.30725836753845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26215076446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26883327960968</t>
+    <t xml:space="preserve">1.26215088367462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26883316040039</t>
   </si>
   <si>
     <t xml:space="preserve">1.22205626964569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19198513031006</t>
+    <t xml:space="preserve">1.19198501110077</t>
   </si>
   <si>
     <t xml:space="preserve">1.35821163654327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32312905788422</t>
+    <t xml:space="preserve">1.32312917709351</t>
   </si>
   <si>
     <t xml:space="preserve">1.28219890594482</t>
@@ -2015,7 +2015,7 @@
     <t xml:space="preserve">1.32646989822388</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33816432952881</t>
+    <t xml:space="preserve">1.33816421031952</t>
   </si>
   <si>
     <t xml:space="preserve">1.42503654956818</t>
@@ -2036,16 +2036,16 @@
     <t xml:space="preserve">1.54448509216309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56369757652283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53863823413849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54866254329681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49186086654663</t>
+    <t xml:space="preserve">1.56369769573212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53863835334778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5486626625061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49186074733734</t>
   </si>
   <si>
     <t xml:space="preserve">1.41668295860291</t>
@@ -2054,10 +2054,10 @@
     <t xml:space="preserve">1.39329493045807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39078891277313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42002439498901</t>
+    <t xml:space="preserve">1.39078879356384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4200245141983</t>
   </si>
   <si>
     <t xml:space="preserve">1.37491798400879</t>
@@ -2087,10 +2087,10 @@
     <t xml:space="preserve">1.26549255847931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24210357666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38995337486267</t>
+    <t xml:space="preserve">1.24210369586945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38995325565338</t>
   </si>
   <si>
     <t xml:space="preserve">1.37074160575867</t>
@@ -2114,19 +2114,19 @@
     <t xml:space="preserve">1.49687278270721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50104880332947</t>
+    <t xml:space="preserve">1.50104892253876</t>
   </si>
   <si>
     <t xml:space="preserve">1.44758987426758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39914166927338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5428147315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46095454692841</t>
+    <t xml:space="preserve">1.39914155006409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54281485080719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4609546661377</t>
   </si>
   <si>
     <t xml:space="preserve">1.39162361621857</t>
@@ -2135,7 +2135,7 @@
     <t xml:space="preserve">1.41000056266785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40833008289337</t>
+    <t xml:space="preserve">1.40833020210266</t>
   </si>
   <si>
     <t xml:space="preserve">1.4292129278183</t>
@@ -2150,10 +2150,10 @@
     <t xml:space="preserve">1.32563424110413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33732867240906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36155307292938</t>
+    <t xml:space="preserve">1.33732855319977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36155319213867</t>
   </si>
   <si>
     <t xml:space="preserve">1.36907052993774</t>
@@ -2177,28 +2177,28 @@
     <t xml:space="preserve">1.47264909744263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51190876960754</t>
+    <t xml:space="preserve">1.51190865039825</t>
   </si>
   <si>
     <t xml:space="preserve">1.47014307975769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4926962852478</t>
+    <t xml:space="preserve">1.49269616603851</t>
   </si>
   <si>
     <t xml:space="preserve">1.52276766300201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54030871391296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53529691696167</t>
+    <t xml:space="preserve">1.54030883312225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53529679775238</t>
   </si>
   <si>
     <t xml:space="preserve">1.59794545173645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60629820823669</t>
+    <t xml:space="preserve">1.60629832744598</t>
   </si>
   <si>
     <t xml:space="preserve">1.58625090122223</t>
@@ -2210,10 +2210,10 @@
     <t xml:space="preserve">1.59293341636658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63219308853149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58458054065704</t>
+    <t xml:space="preserve">1.6321929693222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58458065986633</t>
   </si>
   <si>
     <t xml:space="preserve">1.56035614013672</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">1.70737075805664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71906530857086</t>
+    <t xml:space="preserve">1.71906518936157</t>
   </si>
   <si>
     <t xml:space="preserve">1.72908842563629</t>
@@ -2252,7 +2252,7 @@
     <t xml:space="preserve">1.7123829126358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73243033885956</t>
+    <t xml:space="preserve">1.73243021965027</t>
   </si>
   <si>
     <t xml:space="preserve">1.69233477115631</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">1.76584208011627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74913585186005</t>
+    <t xml:space="preserve">1.74913573265076</t>
   </si>
   <si>
     <t xml:space="preserve">1.72073566913605</t>
@@ -2300,10 +2300,10 @@
     <t xml:space="preserve">1.61047458648682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64054572582245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62383937835693</t>
+    <t xml:space="preserve">1.64054584503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62383949756622</t>
   </si>
   <si>
     <t xml:space="preserve">1.60963988304138</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">1.59126305580139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56202745437622</t>
+    <t xml:space="preserve">1.56202733516693</t>
   </si>
   <si>
     <t xml:space="preserve">1.59209775924683</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">1.59543943405151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58290922641754</t>
+    <t xml:space="preserve">1.58290934562683</t>
   </si>
   <si>
     <t xml:space="preserve">1.60379219055176</t>
@@ -2336,7 +2336,7 @@
     <t xml:space="preserve">1.58541512489319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54532074928284</t>
+    <t xml:space="preserve">1.54532063007355</t>
   </si>
   <si>
     <t xml:space="preserve">1.54699122905731</t>
@@ -2354,7 +2354,7 @@
     <t xml:space="preserve">1.48935556411743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46763694286346</t>
+    <t xml:space="preserve">1.46763682365417</t>
   </si>
   <si>
     <t xml:space="preserve">1.51274359226227</t>
@@ -2369,22 +2369,22 @@
     <t xml:space="preserve">1.54782676696777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51691997051239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5094028711319</t>
+    <t xml:space="preserve">1.5169198513031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50940275192261</t>
   </si>
   <si>
     <t xml:space="preserve">1.48267221450806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26465678215027</t>
+    <t xml:space="preserve">1.26465690135956</t>
   </si>
   <si>
     <t xml:space="preserve">1.23208045959473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18029081821442</t>
+    <t xml:space="preserve">1.18029069900513</t>
   </si>
   <si>
     <t xml:space="preserve">1.16692578792572</t>
@@ -2399,10 +2399,10 @@
     <t xml:space="preserve">0.933039724826813</t>
   </si>
   <si>
-    <t xml:space="preserve">0.776836335659027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.719200670719147</t>
+    <t xml:space="preserve">0.776836395263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.719200730323792</t>
   </si>
   <si>
     <t xml:space="preserve">0.695811808109283</t>
@@ -2426,13 +2426,13 @@
     <t xml:space="preserve">0.725047469139099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.701658606529236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.637340545654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.682446956634521</t>
+    <t xml:space="preserve">0.701658546924591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.637340486049652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.682447016239166</t>
   </si>
   <si>
     <t xml:space="preserve">0.680358350276947</t>
@@ -2441,16 +2441,16 @@
     <t xml:space="preserve">0.687876343727112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.659893691539764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643604576587677</t>
+    <t xml:space="preserve">0.659893751144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.643604636192322</t>
   </si>
   <si>
     <t xml:space="preserve">0.659475445747375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.64318722486496</t>
+    <t xml:space="preserve">0.643187284469604</t>
   </si>
   <si>
     <t xml:space="preserve">0.627316355705261</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">0.576780498027802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618127942085266</t>
+    <t xml:space="preserve">0.618128001689911</t>
   </si>
   <si>
     <t xml:space="preserve">0.660728514194489</t>
@@ -2471,13 +2471,13 @@
     <t xml:space="preserve">0.650705277919769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.638175249099731</t>
+    <t xml:space="preserve">0.638175189495087</t>
   </si>
   <si>
     <t xml:space="preserve">0.649869620800018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.640263915061951</t>
+    <t xml:space="preserve">0.640263855457306</t>
   </si>
   <si>
     <t xml:space="preserve">0.612281143665314</t>
@@ -2504,7 +2504,7 @@
     <t xml:space="preserve">0.654881656169891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.642351627349854</t>
+    <t xml:space="preserve">0.642351567745209</t>
   </si>
   <si>
     <t xml:space="preserve">0.641516864299774</t>
@@ -2513,10 +2513,10 @@
     <t xml:space="preserve">0.655717313289642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639846444129944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.649034857749939</t>
+    <t xml:space="preserve">0.639846503734589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.649034917354584</t>
   </si>
   <si>
     <t xml:space="preserve">0.668246507644653</t>
@@ -2525,22 +2525,22 @@
     <t xml:space="preserve">0.65028703212738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.6264808177948</t>
+    <t xml:space="preserve">0.626480877399445</t>
   </si>
   <si>
     <t xml:space="preserve">0.609775125980377</t>
   </si>
   <si>
-    <t xml:space="preserve">0.606016099452972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.629822432994843</t>
+    <t xml:space="preserve">0.606016159057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.629822373390198</t>
   </si>
   <si>
     <t xml:space="preserve">0.596827805042267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.574691832065582</t>
+    <t xml:space="preserve">0.574691891670227</t>
   </si>
   <si>
     <t xml:space="preserve">0.581792593002319</t>
@@ -2549,7 +2549,7 @@
     <t xml:space="preserve">0.57427453994751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.60183972120285</t>
+    <t xml:space="preserve">0.601839780807495</t>
   </si>
   <si>
     <t xml:space="preserve">0.630658030509949</t>
@@ -2564,7 +2564,7 @@
     <t xml:space="preserve">0.763054192066193</t>
   </si>
   <si>
-    <t xml:space="preserve">0.768483579158783</t>
+    <t xml:space="preserve">0.768483638763428</t>
   </si>
   <si>
     <t xml:space="preserve">0.82779061794281</t>
@@ -2576,28 +2576,28 @@
     <t xml:space="preserve">0.901297986507416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.910486400127411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00571131706238</t>
+    <t xml:space="preserve">0.910486340522766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00571143627167</t>
   </si>
   <si>
     <t xml:space="preserve">1.01072347164154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968957781791687</t>
+    <t xml:space="preserve">0.968957841396332</t>
   </si>
   <si>
     <t xml:space="preserve">0.877909004688263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.924685955047607</t>
+    <t xml:space="preserve">0.924685895442963</t>
   </si>
   <si>
     <t xml:space="preserve">0.925521612167358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938051700592041</t>
+    <t xml:space="preserve">0.938051640987396</t>
   </si>
   <si>
     <t xml:space="preserve">0.922180950641632</t>
@@ -2612,10 +2612,10 @@
     <t xml:space="preserve">0.895450294017792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.823614180088043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78101372718811</t>
+    <t xml:space="preserve">0.823614120483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781013667583466</t>
   </si>
   <si>
     <t xml:space="preserve">0.824867188930511</t>
@@ -2636,10 +2636,10 @@
     <t xml:space="preserve">0.801895618438721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.79855489730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77641898393631</t>
+    <t xml:space="preserve">0.798554837703705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776418924331665</t>
   </si>
   <si>
     <t xml:space="preserve">0.782266736030579</t>
@@ -2654,16 +2654,16 @@
     <t xml:space="preserve">0.795631527900696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.863708555698395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855355799198151</t>
+    <t xml:space="preserve">0.86370861530304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855355858802795</t>
   </si>
   <si>
     <t xml:space="preserve">0.84449702501297</t>
   </si>
   <si>
-    <t xml:space="preserve">0.857861876487732</t>
+    <t xml:space="preserve">0.857861816883087</t>
   </si>
   <si>
     <t xml:space="preserve">0.836143374443054</t>
@@ -2675,10 +2675,10 @@
     <t xml:space="preserve">0.838649392127991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.800225257873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.773912906646729</t>
+    <t xml:space="preserve">0.80022531747818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.773912966251373</t>
   </si>
   <si>
     <t xml:space="preserve">0.789783895015717</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">0.767230570316315</t>
   </si>
   <si>
-    <t xml:space="preserve">0.775583326816559</t>
+    <t xml:space="preserve">0.775583386421204</t>
   </si>
   <si>
     <t xml:space="preserve">0.786860525608063</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">0.765977621078491</t>
   </si>
   <si>
-    <t xml:space="preserve">0.800642669200897</t>
+    <t xml:space="preserve">0.800642609596252</t>
   </si>
   <si>
     <t xml:space="preserve">0.809831082820892</t>
@@ -2735,10 +2735,10 @@
     <t xml:space="preserve">0.690799713134766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.69288831949234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.685787737369537</t>
+    <t xml:space="preserve">0.692888379096985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.685787796974182</t>
   </si>
   <si>
     <t xml:space="preserve">0.674094140529633</t>
@@ -2753,7 +2753,7 @@
     <t xml:space="preserve">0.687458992004395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.68537038564682</t>
+    <t xml:space="preserve">0.685370326042175</t>
   </si>
   <si>
     <t xml:space="preserve">0.67785233259201</t>
@@ -2771,13 +2771,13 @@
     <t xml:space="preserve">0.69831782579422</t>
   </si>
   <si>
-    <t xml:space="preserve">0.721288502216339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.720453679561615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.742588639259338</t>
+    <t xml:space="preserve">0.721288442611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.72045373916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.742588698863983</t>
   </si>
   <si>
     <t xml:space="preserve">0.767647981643677</t>
@@ -2804,7 +2804,7 @@
     <t xml:space="preserve">0.825284600257874</t>
   </si>
   <si>
-    <t xml:space="preserve">0.850343704223633</t>
+    <t xml:space="preserve">0.850343763828278</t>
   </si>
   <si>
     <t xml:space="preserve">0.860367834568024</t>
@@ -2813,13 +2813,13 @@
     <t xml:space="preserve">0.847003042697906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.858696579933167</t>
+    <t xml:space="preserve">0.858696639537811</t>
   </si>
   <si>
     <t xml:space="preserve">0.843661308288574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.8720623254776</t>
+    <t xml:space="preserve">0.872062206268311</t>
   </si>
   <si>
     <t xml:space="preserve">0.852014183998108</t>
@@ -2861,7 +2861,7 @@
     <t xml:space="preserve">0.645275831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.660311102867126</t>
+    <t xml:space="preserve">0.660311043262482</t>
   </si>
   <si>
     <t xml:space="preserve">0.684534728527069</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">0.68912935256958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.753030061721802</t>
+    <t xml:space="preserve">0.753030121326447</t>
   </si>
   <si>
     <t xml:space="preserve">0.784354448318481</t>
@@ -2879,16 +2879,16 @@
     <t xml:space="preserve">0.787696123123169</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803148627281189</t>
+    <t xml:space="preserve">0.803148686885834</t>
   </si>
   <si>
     <t xml:space="preserve">0.856191456317902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.845331788063049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877073466777802</t>
+    <t xml:space="preserve">0.845331728458405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877073407173157</t>
   </si>
   <si>
     <t xml:space="preserve">0.900462329387665</t>
@@ -2900,19 +2900,19 @@
     <t xml:space="preserve">0.887097477912903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.890439212322235</t>
+    <t xml:space="preserve">0.89043927192688</t>
   </si>
   <si>
     <t xml:space="preserve">0.881250739097595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.904638826847076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89294421672821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902132749557495</t>
+    <t xml:space="preserve">0.904638767242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892944276332855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.90213280916214</t>
   </si>
   <si>
     <t xml:space="preserve">0.88208544254303</t>
@@ -2927,13 +2927,13 @@
     <t xml:space="preserve">0.839484930038452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.841990947723389</t>
+    <t xml:space="preserve">0.841991007328033</t>
   </si>
   <si>
     <t xml:space="preserve">0.840320587158203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.859532177448273</t>
+    <t xml:space="preserve">0.859532237052917</t>
   </si>
   <si>
     <t xml:space="preserve">0.905474305152893</t>
@@ -2948,13 +2948,13 @@
     <t xml:space="preserve">0.906310021877289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.943898439407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95392245054245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9572634100914</t>
+    <t xml:space="preserve">0.943898558616638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953922390937805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957263290882111</t>
   </si>
   <si>
     <t xml:space="preserve">0.965616941452026</t>
@@ -2963,10 +2963,10 @@
     <t xml:space="preserve">0.978146135807037</t>
   </si>
   <si>
-    <t xml:space="preserve">0.961439728736877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934710025787354</t>
+    <t xml:space="preserve">0.961439669132233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934710085391998</t>
   </si>
   <si>
     <t xml:space="preserve">0.902968287467957</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">0.852849841117859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.867050290107727</t>
+    <t xml:space="preserve">0.867050230503082</t>
   </si>
   <si>
     <t xml:space="preserve">0.878744661808014</t>
@@ -2987,28 +2987,28 @@
     <t xml:space="preserve">0.907144844532013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.931369364261627</t>
+    <t xml:space="preserve">0.931369304656982</t>
   </si>
   <si>
     <t xml:space="preserve">0.921345114707947</t>
   </si>
   <si>
-    <t xml:space="preserve">0.927191972732544</t>
+    <t xml:space="preserve">0.927192032337189</t>
   </si>
   <si>
     <t xml:space="preserve">0.912992417812347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947239995002747</t>
+    <t xml:space="preserve">0.947240054607391</t>
   </si>
   <si>
     <t xml:space="preserve">0.899626731872559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.929697871208191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938886523246765</t>
+    <t xml:space="preserve">0.929697930812836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93888646364212</t>
   </si>
   <si>
     <t xml:space="preserve">0.937216103076935</t>
@@ -3017,13 +3017,13 @@
     <t xml:space="preserve">0.942228019237518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941392481327057</t>
+    <t xml:space="preserve">0.941392421722412</t>
   </si>
   <si>
     <t xml:space="preserve">0.94640451669693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.935545742511749</t>
+    <t xml:space="preserve">0.935545802116394</t>
   </si>
   <si>
     <t xml:space="preserve">0.975640118122101</t>
@@ -3032,7 +3032,7 @@
     <t xml:space="preserve">1.14687860012054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18947911262512</t>
+    <t xml:space="preserve">1.18947899341583</t>
   </si>
   <si>
     <t xml:space="preserve">1.17360818386078</t>
@@ -3041,7 +3041,7 @@
     <t xml:space="preserve">1.16024339199066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15773749351501</t>
+    <t xml:space="preserve">1.15773737430573</t>
   </si>
   <si>
     <t xml:space="preserve">1.17193794250488</t>
@@ -3056,16 +3056,16 @@
     <t xml:space="preserve">1.11096060276031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1067841053009</t>
+    <t xml:space="preserve">1.10678398609161</t>
   </si>
   <si>
     <t xml:space="preserve">1.11179530620575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13100779056549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12098360061646</t>
+    <t xml:space="preserve">1.1310076713562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12098371982574</t>
   </si>
   <si>
     <t xml:space="preserve">1.16358518600464</t>
@@ -3074,13 +3074,13 @@
     <t xml:space="preserve">1.14520823955536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11513698101044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10761880874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37742388248444</t>
+    <t xml:space="preserve">1.11513686180115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10761892795563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37742400169373</t>
   </si>
   <si>
     <t xml:space="preserve">1.37241184711456</t>
@@ -3101,22 +3101,22 @@
     <t xml:space="preserve">1.41167175769806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39747142791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43840134143829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47682547569275</t>
+    <t xml:space="preserve">1.39747130870819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43840146064758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47682535648346</t>
   </si>
   <si>
     <t xml:space="preserve">1.45928406715393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44090735912323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43338942527771</t>
+    <t xml:space="preserve">1.44090747833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43338930606842</t>
   </si>
   <si>
     <t xml:space="preserve">1.48100185394287</t>
@@ -3149,10 +3149,10 @@
     <t xml:space="preserve">1.62718093395233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6138162612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45677816867828</t>
+    <t xml:space="preserve">1.61381614208221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45677804946899</t>
   </si>
   <si>
     <t xml:space="preserve">1.39830696582794</t>
@@ -3161,13 +3161,13 @@
     <t xml:space="preserve">1.34317636489868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35654127597809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35904705524445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36489391326904</t>
+    <t xml:space="preserve">1.3565411567688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35904717445374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36489403247833</t>
   </si>
   <si>
     <t xml:space="preserve">1.4027658700943</t>
@@ -3179,7 +3179,7 @@
     <t xml:space="preserve">1.41251361370087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39390444755554</t>
+    <t xml:space="preserve">1.39390432834625</t>
   </si>
   <si>
     <t xml:space="preserve">1.39213216304779</t>
@@ -3188,10 +3188,10 @@
     <t xml:space="preserve">1.33364653587341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44795918464661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49049437046051</t>
+    <t xml:space="preserve">1.4479593038559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49049425125122</t>
   </si>
   <si>
     <t xml:space="preserve">1.51796472072601</t>
@@ -3203,13 +3203,13 @@
     <t xml:space="preserve">1.58442544937134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52859854698181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54897975921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54454910755157</t>
+    <t xml:space="preserve">1.52859842777252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5489798784256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54454898834229</t>
   </si>
   <si>
     <t xml:space="preserve">1.53834593296051</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">1.5587272644043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57645010948181</t>
+    <t xml:space="preserve">1.5764502286911</t>
   </si>
   <si>
     <t xml:space="preserve">1.6145544052124</t>
@@ -3236,19 +3236,19 @@
     <t xml:space="preserve">1.60392069816589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63582193851471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62518799304962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61278212070465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58353936672211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51885080337524</t>
+    <t xml:space="preserve">1.63582181930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62518811225891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61278223991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58353924751282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51885092258453</t>
   </si>
   <si>
     <t xml:space="preserve">1.520623087883</t>
@@ -3257,10 +3257,10 @@
     <t xml:space="preserve">1.4931526184082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49758338928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52505362033844</t>
+    <t xml:space="preserve">1.49758350849152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52505373954773</t>
   </si>
   <si>
     <t xml:space="preserve">1.50733089447021</t>
@@ -3272,10 +3272,10 @@
     <t xml:space="preserve">1.54011833667755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53037071228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55341053009033</t>
+    <t xml:space="preserve">1.53037083148956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55341041088104</t>
   </si>
   <si>
     <t xml:space="preserve">1.6384801864624</t>
@@ -3284,10 +3284,10 @@
     <t xml:space="preserve">1.66329228878021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56404423713684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51707851886749</t>
+    <t xml:space="preserve">1.56404411792755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5170783996582</t>
   </si>
   <si>
     <t xml:space="preserve">1.48872196674347</t>
@@ -3296,34 +3296,34 @@
     <t xml:space="preserve">1.46568214893341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42403340339661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44707310199738</t>
+    <t xml:space="preserve">1.42403328418732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44707322120667</t>
   </si>
   <si>
     <t xml:space="preserve">1.46656835079193</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61809885501862</t>
+    <t xml:space="preserve">1.61809897422791</t>
   </si>
   <si>
     <t xml:space="preserve">1.8290011882782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84672427177429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90520966053009</t>
+    <t xml:space="preserve">1.84672403335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9052095413208</t>
   </si>
   <si>
     <t xml:space="preserve">1.89634823799133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98319029808044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03635883331299</t>
+    <t xml:space="preserve">1.98319053649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03635907173157</t>
   </si>
   <si>
     <t xml:space="preserve">2.09129977226257</t>
@@ -3335,7 +3335,7 @@
     <t xml:space="preserve">1.96015048027039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88925921916962</t>
+    <t xml:space="preserve">1.88925909996033</t>
   </si>
   <si>
     <t xml:space="preserve">1.96192288398743</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">1.94597256183624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01863646507263</t>
+    <t xml:space="preserve">2.01863622665405</t>
   </si>
   <si>
     <t xml:space="preserve">2.10902261734009</t>
@@ -3356,13 +3356,13 @@
     <t xml:space="preserve">2.10547828674316</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13737940788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12674570083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17814207077026</t>
+    <t xml:space="preserve">2.13737964630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12674593925476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17814183235168</t>
   </si>
   <si>
     <t xml:space="preserve">2.16396379470825</t>
@@ -3374,16 +3374,16 @@
     <t xml:space="preserve">2.18168640136719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24371695518494</t>
+    <t xml:space="preserve">2.24371671676636</t>
   </si>
   <si>
     <t xml:space="preserve">2.1799144744873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12320137023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14624071121216</t>
+    <t xml:space="preserve">2.1232008934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14624047279358</t>
   </si>
   <si>
     <t xml:space="preserve">2.19763708114624</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">2.28625154495239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31992483139038</t>
+    <t xml:space="preserve">2.31992506980896</t>
   </si>
   <si>
     <t xml:space="preserve">2.34828162193298</t>
@@ -3407,28 +3407,28 @@
     <t xml:space="preserve">2.44575762748718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38372731208801</t>
+    <t xml:space="preserve">2.38372755050659</t>
   </si>
   <si>
     <t xml:space="preserve">2.46348023414612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42449021339417</t>
+    <t xml:space="preserve">2.42448997497559</t>
   </si>
   <si>
     <t xml:space="preserve">2.47411417961121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51310443878174</t>
+    <t xml:space="preserve">2.51310420036316</t>
   </si>
   <si>
     <t xml:space="preserve">2.50955986976624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43157911300659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47056984901428</t>
+    <t xml:space="preserve">2.43157887458801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4705696105957</t>
   </si>
   <si>
     <t xml:space="preserve">2.39613318443298</t>
@@ -3437,19 +3437,19 @@
     <t xml:space="preserve">2.33942031860352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37841033935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21004319190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38904452323914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47943115234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49183702468872</t>
+    <t xml:space="preserve">2.37841057777405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21004343032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38904428482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47943067550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49183678627014</t>
   </si>
   <si>
     <t xml:space="preserve">2.56095623970032</t>
@@ -3461,7 +3461,7 @@
     <t xml:space="preserve">2.64070916175842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63184762001038</t>
+    <t xml:space="preserve">2.63184785842896</t>
   </si>
   <si>
     <t xml:space="preserve">2.65311527252197</t>
@@ -3470,10 +3470,10 @@
     <t xml:space="preserve">2.59640192985535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52373814582825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33233118057251</t>
+    <t xml:space="preserve">2.52373790740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33233094215393</t>
   </si>
   <si>
     <t xml:space="preserve">2.31815266609192</t>
@@ -3482,16 +3482,16 @@
     <t xml:space="preserve">2.2968852519989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28270721435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2756175994873</t>
+    <t xml:space="preserve">2.28270697593689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27561783790588</t>
   </si>
   <si>
     <t xml:space="preserve">2.25966739654541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30929136276245</t>
+    <t xml:space="preserve">2.30929112434387</t>
   </si>
   <si>
     <t xml:space="preserve">2.27916240692139</t>
@@ -3503,7 +3503,7 @@
     <t xml:space="preserve">2.26852869987488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36600470542908</t>
+    <t xml:space="preserve">2.3660044670105</t>
   </si>
   <si>
     <t xml:space="preserve">2.30751919746399</t>
@@ -3521,40 +3521,40 @@
     <t xml:space="preserve">2.17459726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13915181159973</t>
+    <t xml:space="preserve">2.13915157318115</t>
   </si>
   <si>
     <t xml:space="preserve">2.15687441825867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05762648582458</t>
+    <t xml:space="preserve">2.05762624740601</t>
   </si>
   <si>
     <t xml:space="preserve">2.16928029060364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1958646774292</t>
+    <t xml:space="preserve">2.19586491584778</t>
   </si>
   <si>
     <t xml:space="preserve">2.13560724258423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39258861541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39436101913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06648778915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99382436275482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12142872810364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1196563243866</t>
+    <t xml:space="preserve">2.39258885383606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39436078071594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06648802757263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99382412433624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12142896652222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11965656280518</t>
   </si>
   <si>
     <t xml:space="preserve">2.09484434127808</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">2.01331901550293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08066630363464</t>
+    <t xml:space="preserve">2.08066606521606</t>
   </si>
   <si>
     <t xml:space="preserve">1.99205148220062</t>
@@ -3581,16 +3581,16 @@
     <t xml:space="preserve">2.01509141921997</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00445771217346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86799156665802</t>
+    <t xml:space="preserve">2.00445795059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86799168586731</t>
   </si>
   <si>
     <t xml:space="preserve">1.90166509151459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80596172809601</t>
+    <t xml:space="preserve">1.80596160888672</t>
   </si>
   <si>
     <t xml:space="preserve">1.6455694437027</t>
@@ -3614,10 +3614,10 @@
     <t xml:space="preserve">1.65974771976471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78646647930145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75545120239258</t>
+    <t xml:space="preserve">1.78646636009216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75545132160187</t>
   </si>
   <si>
     <t xml:space="preserve">1.73684227466583</t>
@@ -3626,37 +3626,37 @@
     <t xml:space="preserve">1.73418390750885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70671343803406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65088629722595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66595065593719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67924284934998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72798085212708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86444699764252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83431792259216</t>
+    <t xml:space="preserve">1.70671331882477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65088641643524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66595077514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67924273014069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72798097133636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86444711685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83431804180145</t>
   </si>
   <si>
     <t xml:space="preserve">1.74570381641388</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78469407558441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76254034042358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7288670539856</t>
+    <t xml:space="preserve">1.78469395637512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76254022121429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72886681556702</t>
   </si>
   <si>
     <t xml:space="preserve">1.67038142681122</t>
@@ -3665,22 +3665,22 @@
     <t xml:space="preserve">1.64113867282867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60126221179962</t>
+    <t xml:space="preserve">1.60126233100891</t>
   </si>
   <si>
     <t xml:space="preserve">1.61987113952637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71025788784027</t>
+    <t xml:space="preserve">1.71025800704956</t>
   </si>
   <si>
     <t xml:space="preserve">1.70051038265228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67835664749146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62961864471436</t>
+    <t xml:space="preserve">1.67835676670074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62961876392365</t>
   </si>
   <si>
     <t xml:space="preserve">1.63936650753021</t>
@@ -3689,34 +3689,34 @@
     <t xml:space="preserve">1.63050496578217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60923743247986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62075746059418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55075216293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46302366256714</t>
+    <t xml:space="preserve">1.60923755168915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62075757980347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55075204372406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46302378177643</t>
   </si>
   <si>
     <t xml:space="preserve">1.47897446155548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5418906211853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60835146903992</t>
+    <t xml:space="preserve">1.54189050197601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60835123062134</t>
   </si>
   <si>
     <t xml:space="preserve">1.58974242210388</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64468336105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60746514797211</t>
+    <t xml:space="preserve">1.64468324184418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6074652671814</t>
   </si>
   <si>
     <t xml:space="preserve">1.60037612915039</t>
@@ -3731,10 +3731,10 @@
     <t xml:space="preserve">1.63139116764069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64734160900116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72266399860382</t>
+    <t xml:space="preserve">1.64734172821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72266411781311</t>
   </si>
   <si>
     <t xml:space="preserve">1.69076263904572</t>
@@ -3743,16 +3743,16 @@
     <t xml:space="preserve">1.71646106243134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78114938735962</t>
+    <t xml:space="preserve">1.78114926815033</t>
   </si>
   <si>
     <t xml:space="preserve">1.84495174884796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80773365497589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79887235164642</t>
+    <t xml:space="preserve">1.80773377418518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79887223243713</t>
   </si>
   <si>
     <t xml:space="preserve">1.79532778263092</t>
@@ -3761,7 +3761,7 @@
     <t xml:space="preserve">1.65797555446625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45593452453613</t>
+    <t xml:space="preserve">1.45593464374542</t>
   </si>
   <si>
     <t xml:space="preserve">1.41871654987335</t>
@@ -70880,7 +70880,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6495023148</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>406858</v>
@@ -70901,6 +70901,32 @@
         <v>1955</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6496064815</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>425500</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>4.21799993515015</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>4.11800003051758</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>4.21199989318848</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>4.19000005722046</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>1947</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/OVS.MI.xlsx
+++ b/data/OVS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1957" uniqueCount="1957">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1958" uniqueCount="1958">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03756380081177</t>
+    <t xml:space="preserve">5.03756332397461</t>
   </si>
   <si>
     <t xml:space="preserve">OVS.MI</t>
@@ -50,55 +50,55 @@
     <t xml:space="preserve">4.76365375518799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64456224441528</t>
+    <t xml:space="preserve">4.64456176757812</t>
   </si>
   <si>
     <t xml:space="preserve">4.71998596191406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65647125244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78747224807739</t>
+    <t xml:space="preserve">4.65647077560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78747177124023</t>
   </si>
   <si>
     <t xml:space="preserve">4.94228982925415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69219923019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60486459732056</t>
+    <t xml:space="preserve">4.69219875335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60486507415771</t>
   </si>
   <si>
     <t xml:space="preserve">4.63662338256836</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61677408218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25155973434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22774219512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53341007232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45798587799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47783422470093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49768257141113</t>
+    <t xml:space="preserve">4.616774559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25156021118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22774267196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5334095954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45798540115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47783374786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49768352508545</t>
   </si>
   <si>
     <t xml:space="preserve">4.51356172561646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44607782363892</t>
+    <t xml:space="preserve">4.44607734680176</t>
   </si>
   <si>
     <t xml:space="preserve">4.62868309020996</t>
@@ -110,31 +110,31 @@
     <t xml:space="preserve">4.51753234863281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54531908035278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32698535919189</t>
+    <t xml:space="preserve">4.54531955718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32698583602905</t>
   </si>
   <si>
     <t xml:space="preserve">4.03322649002075</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02925634384155</t>
+    <t xml:space="preserve">4.02925777435303</t>
   </si>
   <si>
     <t xml:space="preserve">4.27934885025024</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22377252578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38256168365479</t>
+    <t xml:space="preserve">4.22377300262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38256072998047</t>
   </si>
   <si>
     <t xml:space="preserve">4.30316781997681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46989488601685</t>
+    <t xml:space="preserve">4.469895362854</t>
   </si>
   <si>
     <t xml:space="preserve">4.46592473983765</t>
@@ -143,16 +143,16 @@
     <t xml:space="preserve">4.48577356338501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48974227905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.271409034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23965120315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43813753128052</t>
+    <t xml:space="preserve">4.48974323272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27140951156616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23965167999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4381365776062</t>
   </si>
   <si>
     <t xml:space="preserve">4.5651683807373</t>
@@ -161,64 +161,64 @@
     <t xml:space="preserve">4.67235040664673</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71601629257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58898735046387</t>
+    <t xml:space="preserve">4.71601676940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58898687362671</t>
   </si>
   <si>
     <t xml:space="preserve">4.50562238693237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52547073364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38653087615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43019819259644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40241003036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29125833511353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12056064605713</t>
+    <t xml:space="preserve">4.52547025680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38653039932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43019771575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40241050720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29125738143921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12056016921997</t>
   </si>
   <si>
     <t xml:space="preserve">4.09674215316772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06498432159424</t>
+    <t xml:space="preserve">4.0649847984314</t>
   </si>
   <si>
     <t xml:space="preserve">4.08880233764648</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1562876701355</t>
+    <t xml:space="preserve">4.15628671646118</t>
   </si>
   <si>
     <t xml:space="preserve">4.21186399459839</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04910564422607</t>
+    <t xml:space="preserve">4.04910516738892</t>
   </si>
   <si>
     <t xml:space="preserve">4.02131748199463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31110620498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16422653198242</t>
+    <t xml:space="preserve">4.31110715866089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16422748565674</t>
   </si>
   <si>
     <t xml:space="preserve">4.23568201065063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50959157943726</t>
+    <t xml:space="preserve">4.50959205627441</t>
   </si>
   <si>
     <t xml:space="preserve">4.73586559295654</t>
@@ -233,46 +233,46 @@
     <t xml:space="preserve">4.56119775772095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48180437088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52150201797485</t>
+    <t xml:space="preserve">4.48180341720581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5215015411377</t>
   </si>
   <si>
     <t xml:space="preserve">4.55325889587402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5413498878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56913709640503</t>
+    <t xml:space="preserve">4.54134941101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56913757324219</t>
   </si>
   <si>
     <t xml:space="preserve">4.5373797416687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64853191375732</t>
+    <t xml:space="preserve">4.64853143692017</t>
   </si>
   <si>
     <t xml:space="preserve">4.70410776138306</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84304761886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89068412780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81525945663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87877559661865</t>
+    <t xml:space="preserve">4.84304714202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89068460464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81525993347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87877511978149</t>
   </si>
   <si>
     <t xml:space="preserve">4.91053247451782</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75968360900879</t>
+    <t xml:space="preserve">4.75968408584595</t>
   </si>
   <si>
     <t xml:space="preserve">4.73826837539673</t>
@@ -287,16 +287,16 @@
     <t xml:space="preserve">4.73419427871704</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56715297698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51826286315918</t>
+    <t xml:space="preserve">4.5671534538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51826333999634</t>
   </si>
   <si>
     <t xml:space="preserve">4.4734468460083</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47752046585083</t>
+    <t xml:space="preserve">4.47752094268799</t>
   </si>
   <si>
     <t xml:space="preserve">4.48974370956421</t>
@@ -305,22 +305,22 @@
     <t xml:space="preserve">4.63233947753906</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61196851730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55085563659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51418876647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33085060119629</t>
+    <t xml:space="preserve">4.61196899414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55085611343384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51418924331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33085107803345</t>
   </si>
   <si>
     <t xml:space="preserve">3.94706296920776</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13528966903687</t>
+    <t xml:space="preserve">4.13529062271118</t>
   </si>
   <si>
     <t xml:space="preserve">4.24529314041138</t>
@@ -329,19 +329,19 @@
     <t xml:space="preserve">4.2656626701355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30233192443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25751495361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11084461212158</t>
+    <t xml:space="preserve">4.30233144760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25751543045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11084413528442</t>
   </si>
   <si>
     <t xml:space="preserve">4.09047412872314</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05299139022827</t>
+    <t xml:space="preserve">4.05299091339111</t>
   </si>
   <si>
     <t xml:space="preserve">4.18825340270996</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">4.15973472595215</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10677146911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04321479797363</t>
+    <t xml:space="preserve">4.10677051544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04321432113647</t>
   </si>
   <si>
     <t xml:space="preserve">4.11899280548096</t>
@@ -368,7 +368,7 @@
     <t xml:space="preserve">4.16788339614868</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26158952713013</t>
+    <t xml:space="preserve">4.26159000396729</t>
   </si>
   <si>
     <t xml:space="preserve">4.20047664642334</t>
@@ -380,40 +380,40 @@
     <t xml:space="preserve">4.233069896698</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37159252166748</t>
+    <t xml:space="preserve">4.37159204483032</t>
   </si>
   <si>
     <t xml:space="preserve">4.36751842498779</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28603458404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27788591384888</t>
+    <t xml:space="preserve">4.28603363037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27788639068604</t>
   </si>
   <si>
     <t xml:space="preserve">4.24121809005737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25344133377075</t>
+    <t xml:space="preserve">4.25344181060791</t>
   </si>
   <si>
     <t xml:space="preserve">4.29825782775879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22899627685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0725474357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17195749282837</t>
+    <t xml:space="preserve">4.22899580001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07254695892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17195796966553</t>
   </si>
   <si>
     <t xml:space="preserve">4.19232749938965</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10269641876221</t>
+    <t xml:space="preserve">4.10269594192505</t>
   </si>
   <si>
     <t xml:space="preserve">4.04158353805542</t>
@@ -446,19 +446,19 @@
     <t xml:space="preserve">4.0611400604248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35936975479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37566709518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44085311889648</t>
+    <t xml:space="preserve">4.3593692779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37566661834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4408540725708</t>
   </si>
   <si>
     <t xml:space="preserve">4.41233348846436</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31862831115723</t>
+    <t xml:space="preserve">4.31862783432007</t>
   </si>
   <si>
     <t xml:space="preserve">4.31047916412354</t>
@@ -479,25 +479,25 @@
     <t xml:space="preserve">4.1434383392334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11491823196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07417774200439</t>
+    <t xml:space="preserve">4.11491870880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07417821884155</t>
   </si>
   <si>
     <t xml:space="preserve">4.06928825378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08232545852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06439971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00573062896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96010065078735</t>
+    <t xml:space="preserve">4.08232593536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06439924240112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00573110580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9601001739502</t>
   </si>
   <si>
     <t xml:space="preserve">4.05462121963501</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">4.00410127639771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98617482185364</t>
+    <t xml:space="preserve">3.9861752986908</t>
   </si>
   <si>
     <t xml:space="preserve">4.02528715133667</t>
@@ -527,28 +527,28 @@
     <t xml:space="preserve">4.02365732192993</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05951023101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04810190200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05136203765869</t>
+    <t xml:space="preserve">4.05950975418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04810237884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05136156082153</t>
   </si>
   <si>
     <t xml:space="preserve">3.979656457901</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03017568588257</t>
+    <t xml:space="preserve">4.03017520904541</t>
   </si>
   <si>
     <t xml:space="preserve">4.02039813995361</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99921274185181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07825136184692</t>
+    <t xml:space="preserve">3.99921226501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07825183868408</t>
   </si>
   <si>
     <t xml:space="preserve">4.1475133895874</t>
@@ -560,7 +560,7 @@
     <t xml:space="preserve">4.20455121994019</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22492265701294</t>
+    <t xml:space="preserve">4.22492218017578</t>
   </si>
   <si>
     <t xml:space="preserve">4.01713800430298</t>
@@ -575,25 +575,25 @@
     <t xml:space="preserve">3.91283941268921</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89491319656372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87535691261292</t>
+    <t xml:space="preserve">3.89491367340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87535738945007</t>
   </si>
   <si>
     <t xml:space="preserve">3.94054436683655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93402552604675</t>
+    <t xml:space="preserve">3.93402600288391</t>
   </si>
   <si>
     <t xml:space="preserve">3.89654350280762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95521116256714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00247192382812</t>
+    <t xml:space="preserve">3.9552116394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00247240066528</t>
   </si>
   <si>
     <t xml:space="preserve">4.37974071502686</t>
@@ -608,10 +608,10 @@
     <t xml:space="preserve">4.35529518127441</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2901086807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28196001052856</t>
+    <t xml:space="preserve">4.29010820388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28195953369141</t>
   </si>
   <si>
     <t xml:space="preserve">4.3267765045166</t>
@@ -620,52 +620,52 @@
     <t xml:space="preserve">4.29418325424194</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33899879455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33492422103882</t>
+    <t xml:space="preserve">4.33899927139282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33492469787598</t>
   </si>
   <si>
     <t xml:space="preserve">4.34307289123535</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46529912948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48159503936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40825986862183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53863430023193</t>
+    <t xml:space="preserve">4.46529817581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48159456253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40825939178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53863382339478</t>
   </si>
   <si>
     <t xml:space="preserve">4.55492973327637</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5264105796814</t>
+    <t xml:space="preserve">4.52641105651855</t>
   </si>
   <si>
     <t xml:space="preserve">4.5060396194458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43270444869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59567213058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68530464172363</t>
+    <t xml:space="preserve">4.43270492553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59567165374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68530416488647</t>
   </si>
   <si>
     <t xml:space="preserve">4.67308139801025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60381984710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70160055160522</t>
+    <t xml:space="preserve">4.60382032394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70160102844238</t>
   </si>
   <si>
     <t xml:space="preserve">4.85642004013062</t>
@@ -677,13 +677,13 @@
     <t xml:space="preserve">4.77493524551392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79938125610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74234199523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78308439254761</t>
+    <t xml:space="preserve">4.79938077926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74234294891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78308486938477</t>
   </si>
   <si>
     <t xml:space="preserve">4.72604560852051</t>
@@ -698,43 +698,43 @@
     <t xml:space="preserve">4.86456775665283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04790592193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01531314849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89716148376465</t>
+    <t xml:space="preserve">5.04790544509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01531267166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89716100692749</t>
   </si>
   <si>
     <t xml:space="preserve">4.91753196716309</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88901281356812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04383182525635</t>
+    <t xml:space="preserve">4.88901329040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04383134841919</t>
   </si>
   <si>
     <t xml:space="preserve">4.90531015396118</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95012521743774</t>
+    <t xml:space="preserve">4.95012474060059</t>
   </si>
   <si>
     <t xml:space="preserve">5.05198097229004</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97864532470703</t>
+    <t xml:space="preserve">4.97864484786987</t>
   </si>
   <si>
     <t xml:space="preserve">5.03160905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08457374572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23939228057861</t>
+    <t xml:space="preserve">5.08457326889038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23939180374146</t>
   </si>
   <si>
     <t xml:space="preserve">5.19865036010742</t>
@@ -752,46 +752,46 @@
     <t xml:space="preserve">5.06420278549194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13346338272095</t>
+    <t xml:space="preserve">5.13346290588379</t>
   </si>
   <si>
     <t xml:space="preserve">5.11716651916504</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25161457061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18235349655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17827987670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25568914413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27198505401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17420434951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16605710983276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1864275932312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10494422912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07235050201416</t>
+    <t xml:space="preserve">5.25161504745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18235445022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17828035354614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25568866729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27198553085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17420530319214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16605663299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18642807006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10494518280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.072350025177</t>
   </si>
   <si>
     <t xml:space="preserve">4.94605159759521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06827592849731</t>
+    <t xml:space="preserve">5.06827640533447</t>
   </si>
   <si>
     <t xml:space="preserve">4.98679351806641</t>
@@ -800,13 +800,13 @@
     <t xml:space="preserve">5.03691148757935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36268186569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39191770553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3125638961792</t>
+    <t xml:space="preserve">5.3626823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39191722869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31256437301636</t>
   </si>
   <si>
     <t xml:space="preserve">5.27915048599243</t>
@@ -815,40 +815,40 @@
     <t xml:space="preserve">5.34597587585449</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35432863235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32091617584229</t>
+    <t xml:space="preserve">5.35432815551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32091665267944</t>
   </si>
   <si>
     <t xml:space="preserve">5.33762311935425</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27079772949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27497434616089</t>
+    <t xml:space="preserve">5.27079820632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27497386932373</t>
   </si>
   <si>
     <t xml:space="preserve">5.18726778030396</t>
   </si>
   <si>
-    <t xml:space="preserve">5.132972240448</t>
+    <t xml:space="preserve">5.13297271728516</t>
   </si>
   <si>
     <t xml:space="preserve">5.2039737701416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22903299331665</t>
+    <t xml:space="preserve">5.22903347015381</t>
   </si>
   <si>
     <t xml:space="preserve">5.25409126281738</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2624454498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1830906867981</t>
+    <t xml:space="preserve">5.26244497299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18309116363525</t>
   </si>
   <si>
     <t xml:space="preserve">5.21232652664185</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">5.24991512298584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2457389831543</t>
+    <t xml:space="preserve">5.24573850631714</t>
   </si>
   <si>
     <t xml:space="preserve">5.28332805633545</t>
@@ -875,10 +875,10 @@
     <t xml:space="preserve">5.33344650268555</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40444707870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37521171569824</t>
+    <t xml:space="preserve">5.40444755554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37521123886108</t>
   </si>
   <si>
     <t xml:space="preserve">5.40027046203613</t>
@@ -890,13 +890,13 @@
     <t xml:space="preserve">5.37938737869263</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23320960998535</t>
+    <t xml:space="preserve">5.23321008682251</t>
   </si>
   <si>
     <t xml:space="preserve">5.3083872795105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25826930999756</t>
+    <t xml:space="preserve">5.25826835632324</t>
   </si>
   <si>
     <t xml:space="preserve">5.20814990997314</t>
@@ -905,25 +905,25 @@
     <t xml:space="preserve">5.1371488571167</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11208963394165</t>
+    <t xml:space="preserve">5.11209011077881</t>
   </si>
   <si>
     <t xml:space="preserve">5.1538553237915</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23738527297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32509231567383</t>
+    <t xml:space="preserve">5.23738622665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32509279251099</t>
   </si>
   <si>
     <t xml:space="preserve">5.30421018600464</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29585742950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32926988601685</t>
+    <t xml:space="preserve">5.29585695266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32926940917969</t>
   </si>
   <si>
     <t xml:space="preserve">5.48797798156738</t>
@@ -941,22 +941,22 @@
     <t xml:space="preserve">5.68845272064209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61327505111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57568502426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44203615188599</t>
+    <t xml:space="preserve">5.61327457427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57568550109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44203567504883</t>
   </si>
   <si>
     <t xml:space="preserve">5.62162780761719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68009901046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64251041412354</t>
+    <t xml:space="preserve">5.68009853363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64251089096069</t>
   </si>
   <si>
     <t xml:space="preserve">5.37103509902954</t>
@@ -965,19 +965,19 @@
     <t xml:space="preserve">5.39609336853027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3877420425415</t>
+    <t xml:space="preserve">5.38774156570435</t>
   </si>
   <si>
     <t xml:space="preserve">5.24156188964844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29168081283569</t>
+    <t xml:space="preserve">5.29168033599854</t>
   </si>
   <si>
     <t xml:space="preserve">5.19561958312988</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0828537940979</t>
+    <t xml:space="preserve">5.08285331726074</t>
   </si>
   <si>
     <t xml:space="preserve">4.88655567169189</t>
@@ -998,7 +998,7 @@
     <t xml:space="preserve">4.83643770217896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94502687454224</t>
+    <t xml:space="preserve">4.94502735137939</t>
   </si>
   <si>
     <t xml:space="preserve">4.90326261520386</t>
@@ -1007,31 +1007,31 @@
     <t xml:space="preserve">4.86567354202271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87820339202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85314416885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81137800216675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9575572013855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92832136154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77796602249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.861496925354</t>
+    <t xml:space="preserve">4.87820386886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8531436920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81137847900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95755767822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92832183837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77796649932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86149740219116</t>
   </si>
   <si>
     <t xml:space="preserve">4.83226108551025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72367000579834</t>
+    <t xml:space="preserve">4.7236704826355</t>
   </si>
   <si>
     <t xml:space="preserve">4.66102266311646</t>
@@ -1043,16 +1043,16 @@
     <t xml:space="preserve">4.6693754196167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63596296310425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70278882980347</t>
+    <t xml:space="preserve">4.63596391677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70278835296631</t>
   </si>
   <si>
     <t xml:space="preserve">4.67355251312256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64014005661011</t>
+    <t xml:space="preserve">4.64014053344727</t>
   </si>
   <si>
     <t xml:space="preserve">4.71949434280396</t>
@@ -1064,13 +1064,13 @@
     <t xml:space="preserve">4.74872970581055</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7320237159729</t>
+    <t xml:space="preserve">4.73202419281006</t>
   </si>
   <si>
     <t xml:space="preserve">4.71114110946655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67772912979126</t>
+    <t xml:space="preserve">4.67772960662842</t>
   </si>
   <si>
     <t xml:space="preserve">4.91579246520996</t>
@@ -1079,13 +1079,13 @@
     <t xml:space="preserve">4.92414474487305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89490842819214</t>
+    <t xml:space="preserve">4.8949089050293</t>
   </si>
   <si>
     <t xml:space="preserve">4.84061431884766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16220808029175</t>
+    <t xml:space="preserve">5.16220760345459</t>
   </si>
   <si>
     <t xml:space="preserve">4.99932241439819</t>
@@ -1118,28 +1118,28 @@
     <t xml:space="preserve">4.59419822692871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6150803565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63178682327271</t>
+    <t xml:space="preserve">4.61507987976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63178730010986</t>
   </si>
   <si>
     <t xml:space="preserve">4.70696496963501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58584451675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5524320602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53990268707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57749271392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4897837638855</t>
+    <t xml:space="preserve">4.58584499359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55243301391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53990316390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57749223709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48978424072266</t>
   </si>
   <si>
     <t xml:space="preserve">4.41043043136597</t>
@@ -1148,10 +1148,10 @@
     <t xml:space="preserve">4.4438419342041</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49396085739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47307777404785</t>
+    <t xml:space="preserve">4.4939603805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47307825088501</t>
   </si>
   <si>
     <t xml:space="preserve">4.51902008056641</t>
@@ -1172,52 +1172,52 @@
     <t xml:space="preserve">4.5983738899231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56078577041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48560857772827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43966579437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36031150817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3853702545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18907308578491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16150808334351</t>
+    <t xml:space="preserve">4.56078624725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48560810089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43966627120972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36031198501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38537073135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18907356262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16150760650635</t>
   </si>
   <si>
     <t xml:space="preserve">4.15148496627808</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15649557113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1932487487793</t>
+    <t xml:space="preserve">4.15649604797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19324922561646</t>
   </si>
   <si>
     <t xml:space="preserve">4.09802436828613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1531548500061</t>
+    <t xml:space="preserve">4.15315437316895</t>
   </si>
   <si>
     <t xml:space="preserve">4.10303688049316</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12642574310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16986131668091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17654371261597</t>
+    <t xml:space="preserve">4.12642526626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16986083984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17654418945312</t>
   </si>
   <si>
     <t xml:space="preserve">4.14313125610352</t>
@@ -1229,40 +1229,40 @@
     <t xml:space="preserve">2.83002591133118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90687417984009</t>
+    <t xml:space="preserve">2.90687441825867</t>
   </si>
   <si>
     <t xml:space="preserve">2.84339070320129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87179136276245</t>
+    <t xml:space="preserve">2.87179160118103</t>
   </si>
   <si>
     <t xml:space="preserve">2.89350914955139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80162525177002</t>
+    <t xml:space="preserve">2.80162501335144</t>
   </si>
   <si>
     <t xml:space="preserve">2.92358040809631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94863963127136</t>
+    <t xml:space="preserve">2.94863986968994</t>
   </si>
   <si>
     <t xml:space="preserve">3.01713514328003</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0806188583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17083168029785</t>
+    <t xml:space="preserve">3.08061838150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17083144187927</t>
   </si>
   <si>
     <t xml:space="preserve">3.14911389350891</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15746665000916</t>
+    <t xml:space="preserve">3.15746688842773</t>
   </si>
   <si>
     <t xml:space="preserve">3.14410185813904</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">3.17417287826538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10400748252869</t>
+    <t xml:space="preserve">3.10400724411011</t>
   </si>
   <si>
     <t xml:space="preserve">3.01212334632874</t>
@@ -1286,31 +1286,31 @@
     <t xml:space="preserve">2.94529795646667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95699238777161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89852142333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84004902839661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82501411437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85007309913635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74649500846863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55771470069885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.547691822052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51093792915344</t>
+    <t xml:space="preserve">2.95699262619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89852118492126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84004878997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8250138759613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85007333755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74649524688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55771446228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54769158363342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51093769073486</t>
   </si>
   <si>
     <t xml:space="preserve">2.58945727348328</t>
@@ -1319,13 +1319,13 @@
     <t xml:space="preserve">2.5009138584137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51594996452332</t>
+    <t xml:space="preserve">2.51594972610474</t>
   </si>
   <si>
     <t xml:space="preserve">2.50592589378357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47919631004333</t>
+    <t xml:space="preserve">2.47919607162476</t>
   </si>
   <si>
     <t xml:space="preserve">2.41905355453491</t>
@@ -1346,19 +1346,19 @@
     <t xml:space="preserve">2.2753803730011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31380534172058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26201558113098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27203965187073</t>
+    <t xml:space="preserve">2.31380558013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2620153427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27203989028931</t>
   </si>
   <si>
     <t xml:space="preserve">2.41404271125793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38062930107117</t>
+    <t xml:space="preserve">2.38062953948975</t>
   </si>
   <si>
     <t xml:space="preserve">2.30043959617615</t>
@@ -1376,16 +1376,16 @@
     <t xml:space="preserve">2.33552289009094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35389971733093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36559414863586</t>
+    <t xml:space="preserve">2.35389947891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36559438705444</t>
   </si>
   <si>
     <t xml:space="preserve">2.35055828094482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35222911834717</t>
+    <t xml:space="preserve">2.35222935676575</t>
   </si>
   <si>
     <t xml:space="preserve">2.35557007789612</t>
@@ -1394,7 +1394,7 @@
     <t xml:space="preserve">2.25533318519592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22025084495544</t>
+    <t xml:space="preserve">2.22025036811829</t>
   </si>
   <si>
     <t xml:space="preserve">2.28039264678955</t>
@@ -1406,7 +1406,7 @@
     <t xml:space="preserve">2.23027372360229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40067648887634</t>
+    <t xml:space="preserve">2.40067672729492</t>
   </si>
   <si>
     <t xml:space="preserve">2.44912457466125</t>
@@ -1415,16 +1415,16 @@
     <t xml:space="preserve">2.42406535148621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31881666183472</t>
+    <t xml:space="preserve">2.31881642341614</t>
   </si>
   <si>
     <t xml:space="preserve">2.30879330635071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387564659119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33218121528625</t>
+    <t xml:space="preserve">2.34387588500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33218097686768</t>
   </si>
   <si>
     <t xml:space="preserve">2.27371001243591</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">2.18850898742676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17681455612183</t>
+    <t xml:space="preserve">2.17681479454041</t>
   </si>
   <si>
     <t xml:space="preserve">2.15342545509338</t>
@@ -1442,13 +1442,13 @@
     <t xml:space="preserve">2.21022653579712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21189737319946</t>
+    <t xml:space="preserve">2.2118968963623</t>
   </si>
   <si>
     <t xml:space="preserve">2.05485892295837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01142311096191</t>
+    <t xml:space="preserve">2.01142287254333</t>
   </si>
   <si>
     <t xml:space="preserve">1.97466909885406</t>
@@ -1466,37 +1466,37 @@
     <t xml:space="preserve">2.17180252075195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18182587623596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16679048538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16846060752869</t>
+    <t xml:space="preserve">2.18182563781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1667902469635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16846084594727</t>
   </si>
   <si>
     <t xml:space="preserve">2.15509605407715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15676617622375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11500144004822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07657742500305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08994221687317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09829521179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16010808944702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09662437438965</t>
+    <t xml:space="preserve">2.15676665306091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1150016784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07657718658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08994245529175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09829497337341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1601083278656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09662461280823</t>
   </si>
   <si>
     <t xml:space="preserve">2.09161257743835</t>
@@ -1511,22 +1511,22 @@
     <t xml:space="preserve">2.12502455711365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23695635795593</t>
+    <t xml:space="preserve">2.23695611953735</t>
   </si>
   <si>
     <t xml:space="preserve">2.18683767318726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11834216117859</t>
+    <t xml:space="preserve">2.11834239959717</t>
   </si>
   <si>
     <t xml:space="preserve">2.06989502906799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06321287155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00139951705933</t>
+    <t xml:space="preserve">2.06321263313293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00139975547791</t>
   </si>
   <si>
     <t xml:space="preserve">1.99972856044769</t>
@@ -1535,13 +1535,13 @@
     <t xml:space="preserve">1.98302280902863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94626939296722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8761031627655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75748944282532</t>
+    <t xml:space="preserve">1.94626891613007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87610304355621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75748932361603</t>
   </si>
   <si>
     <t xml:space="preserve">1.69567656517029</t>
@@ -1553,7 +1553,7 @@
     <t xml:space="preserve">1.6288515329361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62968707084656</t>
+    <t xml:space="preserve">1.62968695163727</t>
   </si>
   <si>
     <t xml:space="preserve">1.50439071655273</t>
@@ -1562,16 +1562,16 @@
     <t xml:space="preserve">1.48601388931274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39663553237915</t>
+    <t xml:space="preserve">1.39663565158844</t>
   </si>
   <si>
     <t xml:space="preserve">1.31728148460388</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28553974628448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27133929729462</t>
+    <t xml:space="preserve">1.28553986549377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27133941650391</t>
   </si>
   <si>
     <t xml:space="preserve">1.24962174892426</t>
@@ -1580,31 +1580,31 @@
     <t xml:space="preserve">1.24460959434509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28971612453461</t>
+    <t xml:space="preserve">1.2897162437439</t>
   </si>
   <si>
     <t xml:space="preserve">1.27635133266449</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30391657352448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3156111240387</t>
+    <t xml:space="preserve">1.30391645431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31561100482941</t>
   </si>
   <si>
     <t xml:space="preserve">1.31310498714447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2838693857193</t>
+    <t xml:space="preserve">1.28386950492859</t>
   </si>
   <si>
     <t xml:space="preserve">1.27969300746918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33899998664856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35152912139893</t>
+    <t xml:space="preserve">1.33899986743927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35152900218964</t>
   </si>
   <si>
     <t xml:space="preserve">1.29472815990448</t>
@@ -1613,13 +1613,13 @@
     <t xml:space="preserve">1.29639863967896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2429393529892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25212776660919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26799869537354</t>
+    <t xml:space="preserve">1.24293923377991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2521276473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26799857616425</t>
   </si>
   <si>
     <t xml:space="preserve">1.25296247005463</t>
@@ -1628,13 +1628,13 @@
     <t xml:space="preserve">1.2337509393692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25630402565002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25797462463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26048052310944</t>
+    <t xml:space="preserve">1.25630414485931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25797438621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26048064231873</t>
   </si>
   <si>
     <t xml:space="preserve">1.36823558807373</t>
@@ -1643,7 +1643,7 @@
     <t xml:space="preserve">1.36990582942963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36405909061432</t>
+    <t xml:space="preserve">1.36405920982361</t>
   </si>
   <si>
     <t xml:space="preserve">1.34568238258362</t>
@@ -1658,49 +1658,49 @@
     <t xml:space="preserve">1.25129199028015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2387627363205</t>
+    <t xml:space="preserve">1.23876297473907</t>
   </si>
   <si>
     <t xml:space="preserve">1.06835913658142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962275207042694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989840567111969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.633163154125214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.703329920768738</t>
+    <t xml:space="preserve">0.962275266647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989840686321259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.633163273334503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.703329861164093</t>
   </si>
   <si>
     <t xml:space="preserve">0.705000221729279</t>
   </si>
   <si>
-    <t xml:space="preserve">0.862038254737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958098948001862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948074877262115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848673403263092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913827180862427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944734036922455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918839156627655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917168855667114</t>
+    <t xml:space="preserve">0.862038195133209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958098888397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948074817657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848673343658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913827061653137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944734156131744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9188392162323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917168915271759</t>
   </si>
   <si>
     <t xml:space="preserve">1.00487565994263</t>
@@ -1724,7 +1724,7 @@
     <t xml:space="preserve">1.03578281402588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01155817508698</t>
+    <t xml:space="preserve">1.01155829429626</t>
   </si>
   <si>
     <t xml:space="preserve">1.01824069023132</t>
@@ -1733,7 +1733,7 @@
     <t xml:space="preserve">0.999029040336609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01573550701141</t>
+    <t xml:space="preserve">1.0157356262207</t>
   </si>
   <si>
     <t xml:space="preserve">1.01322948932648</t>
@@ -1745,10 +1745,10 @@
     <t xml:space="preserve">1.10177206993103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1276661157608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12933743000031</t>
+    <t xml:space="preserve">1.12766623497009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12933731079102</t>
   </si>
   <si>
     <t xml:space="preserve">1.13017213344574</t>
@@ -1757,34 +1757,34 @@
     <t xml:space="preserve">1.1368545293808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11346650123596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10260701179504</t>
+    <t xml:space="preserve">1.11346662044525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10260689258575</t>
   </si>
   <si>
     <t xml:space="preserve">1.06585311889648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0324410200119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07086503505707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06334793567657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01907622814178</t>
+    <t xml:space="preserve">1.03244113922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07086515426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06334805488586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01907634735107</t>
   </si>
   <si>
     <t xml:space="preserve">1.03494703769684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06501829624176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12850165367126</t>
+    <t xml:space="preserve">1.06501841545105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12850177288055</t>
   </si>
   <si>
     <t xml:space="preserve">1.08506560325623</t>
@@ -1796,13 +1796,13 @@
     <t xml:space="preserve">1.07253634929657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08088898658752</t>
+    <t xml:space="preserve">1.08088910579681</t>
   </si>
   <si>
     <t xml:space="preserve">1.1051127910614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07838308811188</t>
+    <t xml:space="preserve">1.07838332653046</t>
   </si>
   <si>
     <t xml:space="preserve">1.10010087490082</t>
@@ -1820,34 +1820,34 @@
     <t xml:space="preserve">1.46179020404816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41584801673889</t>
+    <t xml:space="preserve">1.4158478975296</t>
   </si>
   <si>
     <t xml:space="preserve">1.414177775383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36071753501892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.330646276474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29806983470917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37324750423431</t>
+    <t xml:space="preserve">1.36071765422821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33064615726471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29806995391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3732476234436</t>
   </si>
   <si>
     <t xml:space="preserve">1.38744723796844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32981145381927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35069346427917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35487067699432</t>
+    <t xml:space="preserve">1.32981157302856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35069358348846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35487079620361</t>
   </si>
   <si>
     <t xml:space="preserve">1.32897591590881</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">1.41918897628784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42169499397278</t>
+    <t xml:space="preserve">1.42169487476349</t>
   </si>
   <si>
     <t xml:space="preserve">1.42253053188324</t>
@@ -1880,10 +1880,10 @@
     <t xml:space="preserve">1.37575268745422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3941296339035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4534364938736</t>
+    <t xml:space="preserve">1.39412951469421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45343661308289</t>
   </si>
   <si>
     <t xml:space="preserve">1.43589532375336</t>
@@ -1895,31 +1895,31 @@
     <t xml:space="preserve">1.61131012439728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59710991382599</t>
+    <t xml:space="preserve">1.5971097946167</t>
   </si>
   <si>
     <t xml:space="preserve">1.59376907348633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57455658912659</t>
+    <t xml:space="preserve">1.5745564699173</t>
   </si>
   <si>
     <t xml:space="preserve">1.55283880233765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55116760730743</t>
+    <t xml:space="preserve">1.55116748809814</t>
   </si>
   <si>
     <t xml:space="preserve">1.51441478729248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47097861766815</t>
+    <t xml:space="preserve">1.47097873687744</t>
   </si>
   <si>
     <t xml:space="preserve">1.41751849651337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43422496318817</t>
+    <t xml:space="preserve">1.43422484397888</t>
   </si>
   <si>
     <t xml:space="preserve">1.3882828950882</t>
@@ -1928,13 +1928,13 @@
     <t xml:space="preserve">1.38327085971832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33231675624847</t>
+    <t xml:space="preserve">1.33231663703918</t>
   </si>
   <si>
     <t xml:space="preserve">1.36739993095398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34985888004303</t>
+    <t xml:space="preserve">1.34985876083374</t>
   </si>
   <si>
     <t xml:space="preserve">1.30308091640472</t>
@@ -1943,7 +1943,7 @@
     <t xml:space="preserve">1.32229340076447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31644570827484</t>
+    <t xml:space="preserve">1.31644594669342</t>
   </si>
   <si>
     <t xml:space="preserve">1.2989045381546</t>
@@ -1958,10 +1958,10 @@
     <t xml:space="preserve">1.31895184516907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29222214221954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28721022605896</t>
+    <t xml:space="preserve">1.29222226142883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28720998764038</t>
   </si>
   <si>
     <t xml:space="preserve">1.25045645236969</t>
@@ -1970,34 +1970,34 @@
     <t xml:space="preserve">1.32730543613434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31143474578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31978750228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3490229845047</t>
+    <t xml:space="preserve">1.31143462657928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31978738307953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34902310371399</t>
   </si>
   <si>
     <t xml:space="preserve">1.34651708602905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30725824832916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26215088367462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26883316040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22205638885498</t>
+    <t xml:space="preserve">1.30725836753845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26215076446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26883327960968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22205626964569</t>
   </si>
   <si>
     <t xml:space="preserve">1.19198513031006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35821151733398</t>
+    <t xml:space="preserve">1.35821163654327</t>
   </si>
   <si>
     <t xml:space="preserve">1.32312917709351</t>
@@ -2009,19 +2009,19 @@
     <t xml:space="preserve">1.24043321609497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27384543418884</t>
+    <t xml:space="preserve">1.27384531497955</t>
   </si>
   <si>
     <t xml:space="preserve">1.26131618022919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32646989822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33816432952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42503654956818</t>
+    <t xml:space="preserve">1.32646977901459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33816421031952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42503666877747</t>
   </si>
   <si>
     <t xml:space="preserve">1.48183751106262</t>
@@ -2030,13 +2030,13 @@
     <t xml:space="preserve">1.49603796005249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50272023677826</t>
+    <t xml:space="preserve">1.50272035598755</t>
   </si>
   <si>
     <t xml:space="preserve">1.50355505943298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54448533058167</t>
+    <t xml:space="preserve">1.54448521137238</t>
   </si>
   <si>
     <t xml:space="preserve">1.56369769573212</t>
@@ -2048,40 +2048,40 @@
     <t xml:space="preserve">1.54866242408752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49186062812805</t>
+    <t xml:space="preserve">1.49186074733734</t>
   </si>
   <si>
     <t xml:space="preserve">1.41668295860291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39329493045807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39078891277313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4200245141983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37491798400879</t>
+    <t xml:space="preserve">1.39329481124878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39078879356384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42002439498901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37491810321808</t>
   </si>
   <si>
     <t xml:space="preserve">1.34818840026855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33148181438446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32814013957977</t>
+    <t xml:space="preserve">1.33148205280304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32814025878906</t>
   </si>
   <si>
     <t xml:space="preserve">1.29723417758942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29974031448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30224645137787</t>
+    <t xml:space="preserve">1.29974019527435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30224633216858</t>
   </si>
   <si>
     <t xml:space="preserve">1.33315217494965</t>
@@ -2090,7 +2090,7 @@
     <t xml:space="preserve">1.26549255847931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24210357666016</t>
+    <t xml:space="preserve">1.24210369586945</t>
   </si>
   <si>
     <t xml:space="preserve">1.38995325565338</t>
@@ -2099,13 +2099,13 @@
     <t xml:space="preserve">1.37074172496796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38494122028351</t>
+    <t xml:space="preserve">1.3849413394928</t>
   </si>
   <si>
     <t xml:space="preserve">1.38911843299866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37993013858795</t>
+    <t xml:space="preserve">1.37993001937866</t>
   </si>
   <si>
     <t xml:space="preserve">1.45260179042816</t>
@@ -2117,13 +2117,13 @@
     <t xml:space="preserve">1.49687266349792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50104892253876</t>
+    <t xml:space="preserve">1.50104904174805</t>
   </si>
   <si>
     <t xml:space="preserve">1.44758975505829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39914178848267</t>
+    <t xml:space="preserve">1.39914166927338</t>
   </si>
   <si>
     <t xml:space="preserve">1.5428147315979</t>
@@ -2147,13 +2147,13 @@
     <t xml:space="preserve">1.40749442577362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3339878320694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32563424110413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33732855319977</t>
+    <t xml:space="preserve">1.33398795127869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32563412189484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33732867240906</t>
   </si>
   <si>
     <t xml:space="preserve">1.36155307292938</t>
@@ -2162,7 +2162,7 @@
     <t xml:space="preserve">1.36907041072845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44508385658264</t>
+    <t xml:space="preserve">1.44508373737335</t>
   </si>
   <si>
     <t xml:space="preserve">1.4350597858429</t>
@@ -2171,10 +2171,10 @@
     <t xml:space="preserve">1.46596658229828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47181344032288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46513092517853</t>
+    <t xml:space="preserve">1.47181332111359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46513104438782</t>
   </si>
   <si>
     <t xml:space="preserve">1.47264897823334</t>
@@ -2183,19 +2183,19 @@
     <t xml:space="preserve">1.51190888881683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4701429605484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4926962852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52276766300201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54030895233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53529667854309</t>
+    <t xml:space="preserve">1.47014307975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49269616603851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52276754379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54030871391296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53529679775238</t>
   </si>
   <si>
     <t xml:space="preserve">1.59794533252716</t>
@@ -2213,22 +2213,22 @@
     <t xml:space="preserve">1.59293341636658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6321929693222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58458054065704</t>
+    <t xml:space="preserve">1.63219308853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58458065986633</t>
   </si>
   <si>
     <t xml:space="preserve">1.56035614013672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54197931289673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55868577957153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56620371341705</t>
+    <t xml:space="preserve">1.54197919368744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55868566036224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56620359420776</t>
   </si>
   <si>
     <t xml:space="preserve">1.56703853607178</t>
@@ -2237,13 +2237,13 @@
     <t xml:space="preserve">1.58708643913269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64973413944244</t>
+    <t xml:space="preserve">1.64973437786102</t>
   </si>
   <si>
     <t xml:space="preserve">1.74078285694122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70737099647522</t>
+    <t xml:space="preserve">1.70737087726593</t>
   </si>
   <si>
     <t xml:space="preserve">1.71906542778015</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">1.69233477115631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76584219932556</t>
+    <t xml:space="preserve">1.76584208011627</t>
   </si>
   <si>
     <t xml:space="preserve">1.74913573265076</t>
@@ -2273,28 +2273,28 @@
     <t xml:space="preserve">1.63887560367584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60880422592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68565237522125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67061698436737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68732368946075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67562913894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68064117431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61715686321259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6154865026474</t>
+    <t xml:space="preserve">1.60880410671234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68565249443054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67061722278595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68732357025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67562925815582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68064105510712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61715698242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61548662185669</t>
   </si>
   <si>
     <t xml:space="preserve">1.62467503547668</t>
@@ -2306,19 +2306,19 @@
     <t xml:space="preserve">1.64054584503174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62383937835693</t>
+    <t xml:space="preserve">1.62383949756622</t>
   </si>
   <si>
     <t xml:space="preserve">1.60963988304138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57789826393127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59126305580139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56202745437622</t>
+    <t xml:space="preserve">1.57789814472198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5912629365921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56202733516693</t>
   </si>
   <si>
     <t xml:space="preserve">1.59209775924683</t>
@@ -2327,16 +2327,16 @@
     <t xml:space="preserve">1.59543931484222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58290922641754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60379207134247</t>
+    <t xml:space="preserve">1.58290934562683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60379219055176</t>
   </si>
   <si>
     <t xml:space="preserve">1.6004513502121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58541536331177</t>
+    <t xml:space="preserve">1.58541524410248</t>
   </si>
   <si>
     <t xml:space="preserve">1.54532086849213</t>
@@ -2354,25 +2354,25 @@
     <t xml:space="preserve">1.49436664581299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48935544490814</t>
+    <t xml:space="preserve">1.48935556411743</t>
   </si>
   <si>
     <t xml:space="preserve">1.46763706207275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51274335384369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52610850334167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53195607662201</t>
+    <t xml:space="preserve">1.51274359226227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52610838413239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53195595741272</t>
   </si>
   <si>
     <t xml:space="preserve">1.54782688617706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51691997051239</t>
+    <t xml:space="preserve">1.5169198513031</t>
   </si>
   <si>
     <t xml:space="preserve">1.50940275192261</t>
@@ -2381,28 +2381,28 @@
     <t xml:space="preserve">1.48267209529877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26465678215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23208034038544</t>
+    <t xml:space="preserve">1.26465690135956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23208045959473</t>
   </si>
   <si>
     <t xml:space="preserve">1.18029069900513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16692590713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13601982593536</t>
+    <t xml:space="preserve">1.16692578792572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13601994514465</t>
   </si>
   <si>
     <t xml:space="preserve">1.02742898464203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.933039784431458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776836335659027</t>
+    <t xml:space="preserve">0.933039665222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776836395263672</t>
   </si>
   <si>
     <t xml:space="preserve">0.719200670719147</t>
@@ -2417,19 +2417,19 @@
     <t xml:space="preserve">0.613534152507782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519561231136322</t>
+    <t xml:space="preserve">0.519561290740967</t>
   </si>
   <si>
     <t xml:space="preserve">0.599333703517914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674928903579712</t>
+    <t xml:space="preserve">0.674928963184357</t>
   </si>
   <si>
     <t xml:space="preserve">0.725047469139099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.701658606529236</t>
+    <t xml:space="preserve">0.701658546924591</t>
   </si>
   <si>
     <t xml:space="preserve">0.637340426445007</t>
@@ -2444,7 +2444,7 @@
     <t xml:space="preserve">0.687876343727112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.659893751144409</t>
+    <t xml:space="preserve">0.659893691539764</t>
   </si>
   <si>
     <t xml:space="preserve">0.643604576587677</t>
@@ -2453,13 +2453,13 @@
     <t xml:space="preserve">0.659475445747375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643187284469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627316415309906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.576780557632446</t>
+    <t xml:space="preserve">0.64318722486496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627316355705261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.576780498027802</t>
   </si>
   <si>
     <t xml:space="preserve">0.618128001689911</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">0.650705218315125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.638175189495087</t>
+    <t xml:space="preserve">0.638175129890442</t>
   </si>
   <si>
     <t xml:space="preserve">0.649869680404663</t>
@@ -2489,40 +2489,40 @@
     <t xml:space="preserve">0.615621984004974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610192537307739</t>
+    <t xml:space="preserve">0.610192477703094</t>
   </si>
   <si>
     <t xml:space="preserve">0.6055988073349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61102819442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.651539981365204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.676599383354187</t>
+    <t xml:space="preserve">0.611028134822845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.651540040969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.676599264144897</t>
   </si>
   <si>
     <t xml:space="preserve">0.654881656169891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.642351627349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.641516864299774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.655717372894287</t>
+    <t xml:space="preserve">0.642351567745209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.641516804695129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.655717313289642</t>
   </si>
   <si>
     <t xml:space="preserve">0.639846503734589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649034917354584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.668246507644653</t>
+    <t xml:space="preserve">0.649034976959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.668246448040009</t>
   </si>
   <si>
     <t xml:space="preserve">0.650286972522736</t>
@@ -2534,10 +2534,10 @@
     <t xml:space="preserve">0.609775185585022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.606016039848328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.629822373390198</t>
+    <t xml:space="preserve">0.606016099452972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.629822432994843</t>
   </si>
   <si>
     <t xml:space="preserve">0.596827805042267</t>
@@ -2546,85 +2546,85 @@
     <t xml:space="preserve">0.574691891670227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581792593002319</t>
+    <t xml:space="preserve">0.581792533397675</t>
   </si>
   <si>
     <t xml:space="preserve">0.57427453994751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.60183972120285</t>
+    <t xml:space="preserve">0.601839780807495</t>
   </si>
   <si>
     <t xml:space="preserve">0.630658090114594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.726300418376923</t>
+    <t xml:space="preserve">0.726300477981567</t>
   </si>
   <si>
     <t xml:space="preserve">0.789366483688354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.763054251670837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768483579158783</t>
+    <t xml:space="preserve">0.763054192066193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.768483519554138</t>
   </si>
   <si>
     <t xml:space="preserve">0.827790558338165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.835308492183685</t>
+    <t xml:space="preserve">0.835308611392975</t>
   </si>
   <si>
     <t xml:space="preserve">0.901298046112061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.910486400127411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00571155548096</t>
+    <t xml:space="preserve">0.910486459732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00571143627167</t>
   </si>
   <si>
     <t xml:space="preserve">1.01072347164154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968957841396332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877909004688263</t>
+    <t xml:space="preserve">0.968957781791687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877909064292908</t>
   </si>
   <si>
     <t xml:space="preserve">0.924685955047607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.925521671772003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938051581382751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922180950641632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892109513282776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.893779933452606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895450353622437</t>
+    <t xml:space="preserve">0.925521612167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938051521778107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922180891036987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892109572887421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.893779993057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895450294017792</t>
   </si>
   <si>
     <t xml:space="preserve">0.823614180088043</t>
   </si>
   <si>
-    <t xml:space="preserve">0.78101372718811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824867069721222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806073009967804</t>
+    <t xml:space="preserve">0.781013667583466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.824867188930511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806072890758514</t>
   </si>
   <si>
     <t xml:space="preserve">0.785607397556305</t>
@@ -2633,19 +2633,19 @@
     <t xml:space="preserve">0.802313923835754</t>
   </si>
   <si>
-    <t xml:space="preserve">0.797719240188599</t>
+    <t xml:space="preserve">0.797719299793243</t>
   </si>
   <si>
     <t xml:space="preserve">0.801895618438721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.798554956912994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776419103145599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.782266736030579</t>
+    <t xml:space="preserve">0.79855489730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776419043540955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.782266676425934</t>
   </si>
   <si>
     <t xml:space="preserve">0.766394972801208</t>
@@ -2654,7 +2654,7 @@
     <t xml:space="preserve">0.821525514125824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.795631527900696</t>
+    <t xml:space="preserve">0.795631468296051</t>
   </si>
   <si>
     <t xml:space="preserve">0.86370861530304</t>
@@ -2663,10 +2663,10 @@
     <t xml:space="preserve">0.855355799198151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.84449702501297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857861876487732</t>
+    <t xml:space="preserve">0.844496965408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857861816883087</t>
   </si>
   <si>
     <t xml:space="preserve">0.836143374443054</t>
@@ -2678,16 +2678,16 @@
     <t xml:space="preserve">0.838649392127991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.80022531747818</t>
+    <t xml:space="preserve">0.800225257873535</t>
   </si>
   <si>
     <t xml:space="preserve">0.773912966251373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.789783835411072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.771825313568115</t>
+    <t xml:space="preserve">0.789783775806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77182525396347</t>
   </si>
   <si>
     <t xml:space="preserve">0.767230629920959</t>
@@ -2699,28 +2699,28 @@
     <t xml:space="preserve">0.786860466003418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.79270726442337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.758877754211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.765977621078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.800642609596252</t>
+    <t xml:space="preserve">0.792707204818726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.758877813816071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.765977561473846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800642728805542</t>
   </si>
   <si>
     <t xml:space="preserve">0.809831082820892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.799807906150818</t>
+    <t xml:space="preserve">0.799807846546173</t>
   </si>
   <si>
     <t xml:space="preserve">0.780178070068359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.770989656448364</t>
+    <t xml:space="preserve">0.770989596843719</t>
   </si>
   <si>
     <t xml:space="preserve">0.740918278694153</t>
@@ -2732,10 +2732,10 @@
     <t xml:space="preserve">0.712099969387054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.684117376804352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.690799832344055</t>
+    <t xml:space="preserve">0.684117317199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69079977273941</t>
   </si>
   <si>
     <t xml:space="preserve">0.69288843870163</t>
@@ -2750,10 +2750,10 @@
     <t xml:space="preserve">0.666576087474823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.682029545307159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.687458992004395</t>
+    <t xml:space="preserve">0.682029604911804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.687459051609039</t>
   </si>
   <si>
     <t xml:space="preserve">0.68537038564682</t>
@@ -2762,43 +2762,43 @@
     <t xml:space="preserve">0.67785233259201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.69455885887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.697482228279114</t>
+    <t xml:space="preserve">0.694558799266815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.697482168674469</t>
   </si>
   <si>
     <t xml:space="preserve">0.70374721288681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.698317766189575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.721288442611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.72045373916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.742588639259338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.767647981643677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.718365073204041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.715024292469025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781848430633545</t>
+    <t xml:space="preserve">0.69831782579422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.72128838300705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.720453679561615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.742588698863983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767647922039032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.718365013599396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.71502423286438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7818483710289</t>
   </si>
   <si>
     <t xml:space="preserve">0.75720739364624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778925061225891</t>
+    <t xml:space="preserve">0.778925001621246</t>
   </si>
   <si>
     <t xml:space="preserve">0.79646623134613</t>
@@ -2807,13 +2807,13 @@
     <t xml:space="preserve">0.825284540653229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.850343763828278</t>
+    <t xml:space="preserve">0.850343704223633</t>
   </si>
   <si>
     <t xml:space="preserve">0.860367834568024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.847003042697906</t>
+    <t xml:space="preserve">0.847002983093262</t>
   </si>
   <si>
     <t xml:space="preserve">0.858696579933167</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">0.8720623254776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.852014243602753</t>
+    <t xml:space="preserve">0.852014183998108</t>
   </si>
   <si>
     <t xml:space="preserve">0.8545201420784</t>
@@ -2834,43 +2834,43 @@
     <t xml:space="preserve">0.812755346298218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.8077432513237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81317275762558</t>
+    <t xml:space="preserve">0.807743310928345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.813172698020935</t>
   </si>
   <si>
     <t xml:space="preserve">0.828626155853271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.832802593708038</t>
+    <t xml:space="preserve">0.832802534103394</t>
   </si>
   <si>
     <t xml:space="preserve">0.820690751075745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.749689340591431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.710847020149231</t>
+    <t xml:space="preserve">0.749689400196075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.710846960544586</t>
   </si>
   <si>
     <t xml:space="preserve">0.654464304447174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.633998811244965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.645275890827179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.660311102867126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.684534728527069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.689129412174225</t>
+    <t xml:space="preserve">0.63399875164032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.645275831222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.660311162471771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.684534668922424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.68912935256958</t>
   </si>
   <si>
     <t xml:space="preserve">0.753030121326447</t>
@@ -2888,13 +2888,13 @@
     <t xml:space="preserve">0.856191396713257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.845331728458405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877073466777802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900462329387665</t>
+    <t xml:space="preserve">0.845331788063049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877073407173157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.90046226978302</t>
   </si>
   <si>
     <t xml:space="preserve">0.889603495597839</t>
@@ -2909,7 +2909,7 @@
     <t xml:space="preserve">0.88125067949295</t>
   </si>
   <si>
-    <t xml:space="preserve">0.904638826847076</t>
+    <t xml:space="preserve">0.904638767242432</t>
   </si>
   <si>
     <t xml:space="preserve">0.89294421672821</t>
@@ -2921,19 +2921,19 @@
     <t xml:space="preserve">0.88208544254303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.867884933948517</t>
+    <t xml:space="preserve">0.867884993553162</t>
   </si>
   <si>
     <t xml:space="preserve">0.841155350208282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.839484989643097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841990947723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840320587158203</t>
+    <t xml:space="preserve">0.839484930038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841991007328033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840320527553558</t>
   </si>
   <si>
     <t xml:space="preserve">0.859532177448273</t>
@@ -2942,49 +2942,49 @@
     <t xml:space="preserve">0.905474364757538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.849508166313171</t>
+    <t xml:space="preserve">0.849508106708527</t>
   </si>
   <si>
     <t xml:space="preserve">0.872897028923035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.906310021877289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943898439407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95392256975174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957263231277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965616941452026</t>
+    <t xml:space="preserve">0.906310081481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943898558616638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953922510147095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957263350486755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965617060661316</t>
   </si>
   <si>
     <t xml:space="preserve">0.978146135807037</t>
   </si>
   <si>
-    <t xml:space="preserve">0.961439609527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934710085391998</t>
+    <t xml:space="preserve">0.961439728736877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934709966182709</t>
   </si>
   <si>
     <t xml:space="preserve">0.902968347072601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.87456738948822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852849781513214</t>
+    <t xml:space="preserve">0.874567449092865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852849841117859</t>
   </si>
   <si>
     <t xml:space="preserve">0.867050290107727</t>
   </si>
   <si>
-    <t xml:space="preserve">0.878744721412659</t>
+    <t xml:space="preserve">0.878744661808014</t>
   </si>
   <si>
     <t xml:space="preserve">0.907144784927368</t>
@@ -2999,16 +2999,16 @@
     <t xml:space="preserve">0.927192032337189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.912992417812347</t>
+    <t xml:space="preserve">0.912992358207703</t>
   </si>
   <si>
     <t xml:space="preserve">0.947240114212036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.899626791477203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929697930812836</t>
+    <t xml:space="preserve">0.899626731872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92969799041748</t>
   </si>
   <si>
     <t xml:space="preserve">0.93888658285141</t>
@@ -3017,10 +3017,10 @@
     <t xml:space="preserve">0.93721604347229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.942228078842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941392421722412</t>
+    <t xml:space="preserve">0.942228019237518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941392540931702</t>
   </si>
   <si>
     <t xml:space="preserve">0.94640451669693</t>
@@ -3032,13 +3032,13 @@
     <t xml:space="preserve">0.975640118122101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14687860012054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18947923183441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17360806465149</t>
+    <t xml:space="preserve">1.14687871932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18947899341583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17360818386078</t>
   </si>
   <si>
     <t xml:space="preserve">1.16024339199066</t>
@@ -3047,34 +3047,34 @@
     <t xml:space="preserve">1.15773737430573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17193782329559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13852596282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10928928852081</t>
+    <t xml:space="preserve">1.17193794250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1385258436203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10928916931152</t>
   </si>
   <si>
     <t xml:space="preserve">1.11096048355103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1067841053009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11179542541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13100779056549</t>
+    <t xml:space="preserve">1.10678398609161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11179530620575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1310076713562</t>
   </si>
   <si>
     <t xml:space="preserve">1.12098383903503</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16358518600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14520823955536</t>
+    <t xml:space="preserve">1.16358506679535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14520812034607</t>
   </si>
   <si>
     <t xml:space="preserve">1.11513686180115</t>
@@ -3083,28 +3083,28 @@
     <t xml:space="preserve">1.10761880874634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37742388248444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37241196632385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43923711776733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43673098087311</t>
+    <t xml:space="preserve">1.37742400169373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37241184711456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43923699855804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43673086166382</t>
   </si>
   <si>
     <t xml:space="preserve">1.44007158279419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40665984153748</t>
+    <t xml:space="preserve">1.40665972232819</t>
   </si>
   <si>
     <t xml:space="preserve">1.41167163848877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39747142791748</t>
+    <t xml:space="preserve">1.39747130870819</t>
   </si>
   <si>
     <t xml:space="preserve">1.43840134143829</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">1.45928418636322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44090747833252</t>
+    <t xml:space="preserve">1.44090735912323</t>
   </si>
   <si>
     <t xml:space="preserve">1.43338942527771</t>
@@ -3131,22 +3131,22 @@
     <t xml:space="preserve">1.42587125301361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5879213809967</t>
+    <t xml:space="preserve">1.58792126178741</t>
   </si>
   <si>
     <t xml:space="preserve">1.550332903862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62634551525116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61214601993561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62049877643585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61966288089752</t>
+    <t xml:space="preserve">1.62634539604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61214578151703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62049865722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61966300010681</t>
   </si>
   <si>
     <t xml:space="preserve">1.62718117237091</t>
@@ -3164,10 +3164,10 @@
     <t xml:space="preserve">1.34317624568939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3565411567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35904717445374</t>
+    <t xml:space="preserve">1.35654127597809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35904705524445</t>
   </si>
   <si>
     <t xml:space="preserve">1.36489403247833</t>
@@ -3176,31 +3176,31 @@
     <t xml:space="preserve">1.4027658700943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4346672296524</t>
+    <t xml:space="preserve">1.43466699123383</t>
   </si>
   <si>
     <t xml:space="preserve">1.41251349449158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39390432834625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39213228225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33364677429199</t>
+    <t xml:space="preserve">1.39390444755554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39213216304779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3336466550827</t>
   </si>
   <si>
     <t xml:space="preserve">1.4479593038559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49049425125122</t>
+    <t xml:space="preserve">1.49049413204193</t>
   </si>
   <si>
     <t xml:space="preserve">1.5179648399353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53214299678802</t>
+    <t xml:space="preserve">1.53214311599731</t>
   </si>
   <si>
     <t xml:space="preserve">1.58442544937134</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">1.53834593296051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5587272644043</t>
+    <t xml:space="preserve">1.55872714519501</t>
   </si>
   <si>
     <t xml:space="preserve">1.5764502286911</t>
@@ -3227,7 +3227,7 @@
     <t xml:space="preserve">1.6145544052124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60657906532288</t>
+    <t xml:space="preserve">1.60657918453217</t>
   </si>
   <si>
     <t xml:space="preserve">1.5693610906601</t>
@@ -3236,31 +3236,31 @@
     <t xml:space="preserve">1.58885622024536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60392069816589</t>
+    <t xml:space="preserve">1.6039205789566</t>
   </si>
   <si>
     <t xml:space="preserve">1.63582181930542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62518811225891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61278223991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58353924751282</t>
+    <t xml:space="preserve">1.6251882314682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61278212070465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58353936672211</t>
   </si>
   <si>
     <t xml:space="preserve">1.51885080337524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52062320709229</t>
+    <t xml:space="preserve">1.520623087883</t>
   </si>
   <si>
     <t xml:space="preserve">1.4931526184082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49758350849152</t>
+    <t xml:space="preserve">1.49758338928223</t>
   </si>
   <si>
     <t xml:space="preserve">1.52505385875702</t>
@@ -3287,7 +3287,7 @@
     <t xml:space="preserve">1.66329228878021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56404411792755</t>
+    <t xml:space="preserve">1.56404423713684</t>
   </si>
   <si>
     <t xml:space="preserve">1.51707851886749</t>
@@ -3305,13 +3305,13 @@
     <t xml:space="preserve">1.44707322120667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46656823158264</t>
+    <t xml:space="preserve">1.46656835079193</t>
   </si>
   <si>
     <t xml:space="preserve">1.61809897422791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82900106906891</t>
+    <t xml:space="preserve">1.8290011882782</t>
   </si>
   <si>
     <t xml:space="preserve">1.84672403335571</t>
@@ -3323,13 +3323,13 @@
     <t xml:space="preserve">1.89634811878204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98319053649902</t>
+    <t xml:space="preserve">1.98319029808044</t>
   </si>
   <si>
     <t xml:space="preserve">2.03635907173157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09130001068115</t>
+    <t xml:space="preserve">2.09130024909973</t>
   </si>
   <si>
     <t xml:space="preserve">2.17105293273926</t>
@@ -3341,49 +3341,49 @@
     <t xml:space="preserve">1.88925898075104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96192300319672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94597232341766</t>
+    <t xml:space="preserve">1.96192276477814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94597256183624</t>
   </si>
   <si>
     <t xml:space="preserve">2.01863622665405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10902285575867</t>
+    <t xml:space="preserve">2.10902309417725</t>
   </si>
   <si>
     <t xml:space="preserve">2.0753493309021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10547804832458</t>
+    <t xml:space="preserve">2.10547828674316</t>
   </si>
   <si>
     <t xml:space="preserve">2.13737940788269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12674570083618</t>
+    <t xml:space="preserve">2.12674593925476</t>
   </si>
   <si>
     <t xml:space="preserve">2.17814183235168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16396379470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17636966705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18168616294861</t>
+    <t xml:space="preserve">2.16396355628967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1763699054718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18168640136719</t>
   </si>
   <si>
     <t xml:space="preserve">2.24371695518494</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17991423606873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1232008934021</t>
+    <t xml:space="preserve">2.1799144744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12320113182068</t>
   </si>
   <si>
     <t xml:space="preserve">2.14624071121216</t>
@@ -3395,25 +3395,25 @@
     <t xml:space="preserve">2.30574655532837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28625130653381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31992506980896</t>
+    <t xml:space="preserve">2.28625154495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31992483139038</t>
   </si>
   <si>
     <t xml:space="preserve">2.34828162193298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41740083694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4457573890686</t>
+    <t xml:space="preserve">2.41740107536316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44575715065002</t>
   </si>
   <si>
     <t xml:space="preserve">2.38372778892517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46347999572754</t>
+    <t xml:space="preserve">2.46348023414612</t>
   </si>
   <si>
     <t xml:space="preserve">2.42449021339417</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">2.47411394119263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51310443878174</t>
+    <t xml:space="preserve">2.51310420036316</t>
   </si>
   <si>
     <t xml:space="preserve">2.50955963134766</t>
@@ -3437,13 +3437,13 @@
     <t xml:space="preserve">2.39613342285156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33942008018494</t>
+    <t xml:space="preserve">2.33942031860352</t>
   </si>
   <si>
     <t xml:space="preserve">2.37841057777405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21004343032837</t>
+    <t xml:space="preserve">2.21004295349121</t>
   </si>
   <si>
     <t xml:space="preserve">2.38904452323914</t>
@@ -3455,25 +3455,25 @@
     <t xml:space="preserve">2.49183702468872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56095623970032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65665984153748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64070892333984</t>
+    <t xml:space="preserve">2.5609564781189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6566596031189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64070916175842</t>
   </si>
   <si>
     <t xml:space="preserve">2.63184762001038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65311527252197</t>
+    <t xml:space="preserve">2.65311503410339</t>
   </si>
   <si>
     <t xml:space="preserve">2.59640216827393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52373814582825</t>
+    <t xml:space="preserve">2.52373838424683</t>
   </si>
   <si>
     <t xml:space="preserve">2.33233094215393</t>
@@ -3485,7 +3485,7 @@
     <t xml:space="preserve">2.29688501358032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28270673751831</t>
+    <t xml:space="preserve">2.28270697593689</t>
   </si>
   <si>
     <t xml:space="preserve">2.27561783790588</t>
@@ -3497,34 +3497,34 @@
     <t xml:space="preserve">2.30929112434387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27916240692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28802371025085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2685284614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3660044670105</t>
+    <t xml:space="preserve">2.27916216850281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28802347183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26852869987488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36600470542908</t>
   </si>
   <si>
     <t xml:space="preserve">2.30751919746399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24017214775085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14978575706482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16041922569275</t>
+    <t xml:space="preserve">2.24017238616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14978551864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16041898727417</t>
   </si>
   <si>
     <t xml:space="preserve">2.17459726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13915157318115</t>
+    <t xml:space="preserve">2.13915133476257</t>
   </si>
   <si>
     <t xml:space="preserve">2.15687441825867</t>
@@ -3533,22 +3533,22 @@
     <t xml:space="preserve">2.05762648582458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16928029060364</t>
+    <t xml:space="preserve">2.16928052902222</t>
   </si>
   <si>
     <t xml:space="preserve">2.1958646774292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13560700416565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39258885383606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39436101913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06648802757263</t>
+    <t xml:space="preserve">2.13560724258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39258909225464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3943612575531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06648778915405</t>
   </si>
   <si>
     <t xml:space="preserve">1.99382400512695</t>
@@ -3557,25 +3557,25 @@
     <t xml:space="preserve">2.12142848968506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1196563243866</t>
+    <t xml:space="preserve">2.11965656280518</t>
   </si>
   <si>
     <t xml:space="preserve">2.09484457969666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01331925392151</t>
+    <t xml:space="preserve">2.01331901550293</t>
   </si>
   <si>
     <t xml:space="preserve">2.08066630363464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99205183982849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03458690643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02926993370056</t>
+    <t xml:space="preserve">1.99205160140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03458666801453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02926969528198</t>
   </si>
   <si>
     <t xml:space="preserve">1.93179392814636</t>
@@ -3584,28 +3584,28 @@
     <t xml:space="preserve">2.01509141921997</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00445747375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86799168586731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90166485309601</t>
+    <t xml:space="preserve">2.00445771217346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86799156665802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90166509151459</t>
   </si>
   <si>
     <t xml:space="preserve">1.80596160888672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64556956291199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56315803527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56847476959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68012917041779</t>
+    <t xml:space="preserve">1.6455694437027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56315791606903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56847488880157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6801290512085</t>
   </si>
   <si>
     <t xml:space="preserve">1.5799947977066</t>
@@ -3617,55 +3617,55 @@
     <t xml:space="preserve">1.65974771976471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78646647930145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75545120239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73684215545654</t>
+    <t xml:space="preserve">1.78646636009216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75545132160187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73684227466583</t>
   </si>
   <si>
     <t xml:space="preserve">1.73418378829956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70671331882477</t>
+    <t xml:space="preserve">1.70671355724335</t>
   </si>
   <si>
     <t xml:space="preserve">1.65088629722595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66595065593719</t>
+    <t xml:space="preserve">1.66595077514648</t>
   </si>
   <si>
     <t xml:space="preserve">1.67924284934998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72798085212708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8644472360611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83431816101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74570381641388</t>
+    <t xml:space="preserve">1.72798073291779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86444699764252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83431804180145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74570369720459</t>
   </si>
   <si>
     <t xml:space="preserve">1.78469407558441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76254034042358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7288670539856</t>
+    <t xml:space="preserve">1.76254045963287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72886693477631</t>
   </si>
   <si>
     <t xml:space="preserve">1.67038142681122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64113867282867</t>
+    <t xml:space="preserve">1.64113879203796</t>
   </si>
   <si>
     <t xml:space="preserve">1.60126233100891</t>
@@ -3680,19 +3680,19 @@
     <t xml:space="preserve">1.70051038265228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67835676670074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62961888313293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63936650753021</t>
+    <t xml:space="preserve">1.67835688591003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62961900234222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63936638832092</t>
   </si>
   <si>
     <t xml:space="preserve">1.63050496578217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60923755168915</t>
+    <t xml:space="preserve">1.60923743247986</t>
   </si>
   <si>
     <t xml:space="preserve">1.62075746059418</t>
@@ -3701,7 +3701,7 @@
     <t xml:space="preserve">1.55075216293335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46302390098572</t>
+    <t xml:space="preserve">1.46302378177643</t>
   </si>
   <si>
     <t xml:space="preserve">1.4789742231369</t>
@@ -3713,13 +3713,13 @@
     <t xml:space="preserve">1.60835146903992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58974242210388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64468324184418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6074652671814</t>
+    <t xml:space="preserve">1.58974230289459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64468312263489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60746514797211</t>
   </si>
   <si>
     <t xml:space="preserve">1.6003760099411</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">1.63139116764069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64734148979187</t>
+    <t xml:space="preserve">1.64734172821045</t>
   </si>
   <si>
     <t xml:space="preserve">1.72266399860382</t>
@@ -3743,16 +3743,16 @@
     <t xml:space="preserve">1.690762758255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71646106243134</t>
+    <t xml:space="preserve">1.71646094322205</t>
   </si>
   <si>
     <t xml:space="preserve">1.78114950656891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84495186805725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80773377418518</t>
+    <t xml:space="preserve">1.84495174884796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80773365497589</t>
   </si>
   <si>
     <t xml:space="preserve">1.79887235164642</t>
@@ -3761,13 +3761,13 @@
     <t xml:space="preserve">1.79532778263092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65797543525696</t>
+    <t xml:space="preserve">1.65797531604767</t>
   </si>
   <si>
     <t xml:space="preserve">1.45593464374542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41871654987335</t>
+    <t xml:space="preserve">1.41871643066406</t>
   </si>
   <si>
     <t xml:space="preserve">1.46506798267365</t>
@@ -3776,22 +3776,22 @@
     <t xml:space="preserve">1.4768830537796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48960709571838</t>
+    <t xml:space="preserve">1.48960697650909</t>
   </si>
   <si>
     <t xml:space="preserve">1.45779716968536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47597420215607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43689358234406</t>
+    <t xml:space="preserve">1.47597408294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43689334392548</t>
   </si>
   <si>
     <t xml:space="preserve">1.47415637969971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48142719268799</t>
+    <t xml:space="preserve">1.48142731189728</t>
   </si>
   <si>
     <t xml:space="preserve">1.41417241096497</t>
@@ -3800,37 +3800,37 @@
     <t xml:space="preserve">1.37236499786377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37872695922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30147469043732</t>
+    <t xml:space="preserve">1.37872707843781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30147480964661</t>
   </si>
   <si>
     <t xml:space="preserve">1.32783138751984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37418282032013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40781044960022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3859977722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31510758399963</t>
+    <t xml:space="preserve">1.37418270111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40781033039093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38599789142609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31510770320892</t>
   </si>
   <si>
     <t xml:space="preserve">1.28420662879944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27966237068176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30874562263489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32692277431488</t>
+    <t xml:space="preserve">1.27966225147247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3087455034256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32692265510559</t>
   </si>
   <si>
     <t xml:space="preserve">1.39781284332275</t>
@@ -3839,13 +3839,13 @@
     <t xml:space="preserve">1.37145614624023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3578234910965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35691463947296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29693043231964</t>
+    <t xml:space="preserve">1.35782337188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35691475868225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29693055152893</t>
   </si>
   <si>
     <t xml:space="preserve">1.31328988075256</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">1.33328461647034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41962540149689</t>
+    <t xml:space="preserve">1.41962552070618</t>
   </si>
   <si>
     <t xml:space="preserve">1.42689621448517</t>
@@ -3863,10 +3863,10 @@
     <t xml:space="preserve">1.40144848823547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44416439533234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46961212158203</t>
+    <t xml:space="preserve">1.44416427612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46961200237274</t>
   </si>
   <si>
     <t xml:space="preserve">1.45961463451385</t>
@@ -3875,16 +3875,16 @@
     <t xml:space="preserve">1.48778915405273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49505996704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48869800567627</t>
+    <t xml:space="preserve">1.49505984783173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48869812488556</t>
   </si>
   <si>
     <t xml:space="preserve">1.51596355438232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50505745410919</t>
+    <t xml:space="preserve">1.5050573348999</t>
   </si>
   <si>
     <t xml:space="preserve">1.50051319599152</t>
@@ -3902,10 +3902,10 @@
     <t xml:space="preserve">1.41144561767578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34691739082336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34328186511993</t>
+    <t xml:space="preserve">1.34691727161407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34328198432922</t>
   </si>
   <si>
     <t xml:space="preserve">1.37327396869659</t>
@@ -3917,16 +3917,16 @@
     <t xml:space="preserve">1.36236763000488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39235973358154</t>
+    <t xml:space="preserve">1.39235985279083</t>
   </si>
   <si>
     <t xml:space="preserve">1.33601117134094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35237050056458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36963868141174</t>
+    <t xml:space="preserve">1.35237038135529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36963856220245</t>
   </si>
   <si>
     <t xml:space="preserve">1.35964131355286</t>
@@ -3935,16 +3935,16 @@
     <t xml:space="preserve">1.41326344013214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43507587909698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41689872741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4687032699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41235458850861</t>
+    <t xml:space="preserve">1.43507599830627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41689884662628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46870338916779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4123547077179</t>
   </si>
   <si>
     <t xml:space="preserve">1.39872181415558</t>
@@ -3959,19 +3959,19 @@
     <t xml:space="preserve">1.58412742614746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57867419719696</t>
+    <t xml:space="preserve">1.57867431640625</t>
   </si>
   <si>
     <t xml:space="preserve">1.59139823913574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56322383880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49960434436798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55777060985565</t>
+    <t xml:space="preserve">1.56322395801544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49960422515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55777072906494</t>
   </si>
   <si>
     <t xml:space="preserve">1.55231761932373</t>
@@ -3983,7 +3983,7 @@
     <t xml:space="preserve">1.58140087127686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53777611255646</t>
+    <t xml:space="preserve">1.53777599334717</t>
   </si>
   <si>
     <t xml:space="preserve">1.52323436737061</t>
@@ -3998,7 +3998,7 @@
     <t xml:space="preserve">1.59503364562988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59412479400635</t>
+    <t xml:space="preserve">1.59412467479706</t>
   </si>
   <si>
     <t xml:space="preserve">1.64047610759735</t>
@@ -4007,16 +4007,16 @@
     <t xml:space="preserve">1.65774440765381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65865325927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65956199169159</t>
+    <t xml:space="preserve">1.65865314006805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65956211090088</t>
   </si>
   <si>
     <t xml:space="preserve">1.6704683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7631710767746</t>
+    <t xml:space="preserve">1.76317095756531</t>
   </si>
   <si>
     <t xml:space="preserve">1.79225444793701</t>
@@ -4025,16 +4025,16 @@
     <t xml:space="preserve">1.78861892223358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73045253753662</t>
+    <t xml:space="preserve">1.73045241832733</t>
   </si>
   <si>
     <t xml:space="preserve">1.71772861480713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72681701183319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77135074138641</t>
+    <t xml:space="preserve">1.72681713104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7713508605957</t>
   </si>
   <si>
     <t xml:space="preserve">1.73136126995087</t>
@@ -4046,25 +4046,25 @@
     <t xml:space="preserve">1.78771007061005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8486031293869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86678004264832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87223303318024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89949870109558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9340353012085</t>
+    <t xml:space="preserve">1.84860289096832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8667801618576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87223315238953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89949882030487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93403506278992</t>
   </si>
   <si>
     <t xml:space="preserve">1.94494116306305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90676963329315</t>
+    <t xml:space="preserve">1.90676951408386</t>
   </si>
   <si>
     <t xml:space="preserve">1.95402979850769</t>
@@ -4085,16 +4085,16 @@
     <t xml:space="preserve">1.97402453422546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9903838634491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04491519927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13398241996765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15397715568542</t>
+    <t xml:space="preserve">1.99038362503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04491496086121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13398218154907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15397691726685</t>
   </si>
   <si>
     <t xml:space="preserve">2.12307596206665</t>
@@ -4106,7 +4106,7 @@
     <t xml:space="preserve">2.13761758804321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16851878166199</t>
+    <t xml:space="preserve">2.16851854324341</t>
   </si>
   <si>
     <t xml:space="preserve">2.11035227775574</t>
@@ -4115,31 +4115,31 @@
     <t xml:space="preserve">2.10308122634888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10126376152039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97584247589111</t>
+    <t xml:space="preserve">2.10126352310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97584223747253</t>
   </si>
   <si>
     <t xml:space="preserve">2.02128481864929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85223865509033</t>
+    <t xml:space="preserve">1.85223853588104</t>
   </si>
   <si>
     <t xml:space="preserve">1.89041018486023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91222286224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92676413059235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93585300445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93948829174042</t>
+    <t xml:space="preserve">1.91222274303436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92676424980164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93585312366486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93948805332184</t>
   </si>
   <si>
     <t xml:space="preserve">1.90131652355194</t>
@@ -4151,10 +4151,10 @@
     <t xml:space="preserve">1.96311843395233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96857118606567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03219127655029</t>
+    <t xml:space="preserve">1.96857142448425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03219079971313</t>
   </si>
   <si>
     <t xml:space="preserve">2.05945658683777</t>
@@ -4163,10 +4163,10 @@
     <t xml:space="preserve">2.10489916801453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12852931022644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12671136856079</t>
+    <t xml:space="preserve">2.12852907180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12671160697937</t>
   </si>
   <si>
     <t xml:space="preserve">2.09944605827332</t>
@@ -4175,7 +4175,7 @@
     <t xml:space="preserve">2.01946711540222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07218050956726</t>
+    <t xml:space="preserve">2.07218027114868</t>
   </si>
   <si>
     <t xml:space="preserve">2.06309199333191</t>
@@ -4184,7 +4184,7 @@
     <t xml:space="preserve">2.03764414787292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00310802459717</t>
+    <t xml:space="preserve">2.00310778617859</t>
   </si>
   <si>
     <t xml:space="preserve">2.01219630241394</t>
@@ -4193,13 +4193,13 @@
     <t xml:space="preserve">2.01764941215515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00128984451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27394533157349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24849724769592</t>
+    <t xml:space="preserve">2.00129008293152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27394556999207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2484974861145</t>
   </si>
   <si>
     <t xml:space="preserve">2.31756997108459</t>
@@ -4211,22 +4211,22 @@
     <t xml:space="preserve">2.33211159706116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3721010684967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41572642326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.375736951828</t>
+    <t xml:space="preserve">2.37210130691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41572618484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37573671340942</t>
   </si>
   <si>
     <t xml:space="preserve">2.40845537185669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39754915237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3884608745575</t>
+    <t xml:space="preserve">2.39754891395569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38846063613892</t>
   </si>
   <si>
     <t xml:space="preserve">2.39209604263306</t>
@@ -4235,22 +4235,22 @@
     <t xml:space="preserve">2.35755968093872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34483551979065</t>
+    <t xml:space="preserve">2.34483575820923</t>
   </si>
   <si>
     <t xml:space="preserve">2.30666422843933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3157525062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3357470035553</t>
+    <t xml:space="preserve">2.31575274467468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33574724197388</t>
   </si>
   <si>
     <t xml:space="preserve">2.33938264846802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38118958473206</t>
+    <t xml:space="preserve">2.38118982315063</t>
   </si>
   <si>
     <t xml:space="preserve">2.40663766860962</t>
@@ -4271,7 +4271,7 @@
     <t xml:space="preserve">2.28666925430298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18487811088562</t>
+    <t xml:space="preserve">2.18487787246704</t>
   </si>
   <si>
     <t xml:space="preserve">2.23213839530945</t>
@@ -4280,7 +4280,7 @@
     <t xml:space="preserve">2.18306016921997</t>
   </si>
   <si>
-    <t xml:space="preserve">2.143070936203</t>
+    <t xml:space="preserve">2.14307069778442</t>
   </si>
   <si>
     <t xml:space="preserve">2.20487284660339</t>
@@ -4292,7 +4292,7 @@
     <t xml:space="preserve">2.17033648490906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13943529129028</t>
+    <t xml:space="preserve">2.13943552970886</t>
   </si>
   <si>
     <t xml:space="preserve">2.14670634269714</t>
@@ -4310,37 +4310,37 @@
     <t xml:space="preserve">2.26849222183228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24667954444885</t>
+    <t xml:space="preserve">2.24667978286743</t>
   </si>
   <si>
     <t xml:space="preserve">2.24304461479187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25213313102722</t>
+    <t xml:space="preserve">2.25213289260864</t>
   </si>
   <si>
     <t xml:space="preserve">2.30121111869812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28303408622742</t>
+    <t xml:space="preserve">2.283034324646</t>
   </si>
   <si>
     <t xml:space="preserve">2.34120035171509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47934556007385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44844484329224</t>
+    <t xml:space="preserve">2.47934579849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44844460487366</t>
   </si>
   <si>
     <t xml:space="preserve">2.4884340763092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46843934059143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47207522392273</t>
+    <t xml:space="preserve">2.46843957901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47207498550415</t>
   </si>
   <si>
     <t xml:space="preserve">2.45935130119324</t>
@@ -4349,7 +4349,7 @@
     <t xml:space="preserve">2.45753335952759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43390345573425</t>
+    <t xml:space="preserve">2.43390321731567</t>
   </si>
   <si>
     <t xml:space="preserve">2.51388216018677</t>
@@ -4379,16 +4379,16 @@
     <t xml:space="preserve">2.28485155105591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29212260246277</t>
+    <t xml:space="preserve">2.29212236404419</t>
   </si>
   <si>
     <t xml:space="preserve">2.27030992507935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22668528556824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30302858352661</t>
+    <t xml:space="preserve">2.22668504714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30302882194519</t>
   </si>
   <si>
     <t xml:space="preserve">2.32484126091003</t>
@@ -4403,10 +4403,10 @@
     <t xml:space="preserve">2.41936135292053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4320855140686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4211790561676</t>
+    <t xml:space="preserve">2.43208575248718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42117929458618</t>
   </si>
   <si>
     <t xml:space="preserve">2.43935608863831</t>
@@ -4433,19 +4433,19 @@
     <t xml:space="preserve">2.31188225746155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36590647697449</t>
+    <t xml:space="preserve">2.36590671539307</t>
   </si>
   <si>
     <t xml:space="preserve">2.40130209922791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36404371261597</t>
+    <t xml:space="preserve">2.36404395103455</t>
   </si>
   <si>
     <t xml:space="preserve">2.29697895050049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32678532600403</t>
+    <t xml:space="preserve">2.32678556442261</t>
   </si>
   <si>
     <t xml:space="preserve">2.34168863296509</t>
@@ -4457,10 +4457,10 @@
     <t xml:space="preserve">2.36963248252869</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36776947975159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32864832878113</t>
+    <t xml:space="preserve">2.36776971817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32864856719971</t>
   </si>
   <si>
     <t xml:space="preserve">2.29884171485901</t>
@@ -4469,7 +4469,7 @@
     <t xml:space="preserve">2.28580117225647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28021216392517</t>
+    <t xml:space="preserve">2.28021240234375</t>
   </si>
   <si>
     <t xml:space="preserve">2.29511594772339</t>
@@ -4481,13 +4481,13 @@
     <t xml:space="preserve">2.29325270652771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33051109313965</t>
+    <t xml:space="preserve">2.33051133155823</t>
   </si>
   <si>
     <t xml:space="preserve">2.31374502182007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28952693939209</t>
+    <t xml:space="preserve">2.28952670097351</t>
   </si>
   <si>
     <t xml:space="preserve">2.22432494163513</t>
@@ -4514,7 +4514,7 @@
     <t xml:space="preserve">2.10882377624512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09019446372986</t>
+    <t xml:space="preserve">2.09019470214844</t>
   </si>
   <si>
     <t xml:space="preserve">2.0585253238678</t>
@@ -4538,13 +4538,13 @@
     <t xml:space="preserve">2.04175877571106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09205746650696</t>
+    <t xml:space="preserve">2.09205770492554</t>
   </si>
   <si>
     <t xml:space="preserve">2.15912270545959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15353393554688</t>
+    <t xml:space="preserve">2.15353417396545</t>
   </si>
   <si>
     <t xml:space="preserve">2.13863062858582</t>
@@ -4553,7 +4553,7 @@
     <t xml:space="preserve">2.12186455726624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06970262527466</t>
+    <t xml:space="preserve">2.06970238685608</t>
   </si>
   <si>
     <t xml:space="preserve">2.02312970161438</t>
@@ -4565,13 +4565,13 @@
     <t xml:space="preserve">1.9989116191864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01195216178894</t>
+    <t xml:space="preserve">2.01195240020752</t>
   </si>
   <si>
     <t xml:space="preserve">2.0007746219635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99332284927368</t>
+    <t xml:space="preserve">1.99332308769226</t>
   </si>
   <si>
     <t xml:space="preserve">1.97469365596771</t>
@@ -4580,13 +4580,13 @@
     <t xml:space="preserve">1.95606446266174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92625796794891</t>
+    <t xml:space="preserve">1.92625784873962</t>
   </si>
   <si>
     <t xml:space="preserve">1.86478161811829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77349865436554</t>
+    <t xml:space="preserve">1.77349853515625</t>
   </si>
   <si>
     <t xml:space="preserve">1.78095018863678</t>
@@ -4595,7 +4595,7 @@
     <t xml:space="preserve">1.78467607498169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80330514907837</t>
+    <t xml:space="preserve">1.80330526828766</t>
   </si>
   <si>
     <t xml:space="preserve">1.83311200141907</t>
@@ -4610,22 +4610,22 @@
     <t xml:space="preserve">1.71109080314636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70829629898071</t>
+    <t xml:space="preserve">1.70829641819</t>
   </si>
   <si>
     <t xml:space="preserve">1.71947383880615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67196929454803</t>
+    <t xml:space="preserve">1.67196941375732</t>
   </si>
   <si>
     <t xml:space="preserve">1.69991326332092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66638076305389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61608195304871</t>
+    <t xml:space="preserve">1.6663806438446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61608183383942</t>
   </si>
   <si>
     <t xml:space="preserve">1.63005375862122</t>
@@ -4634,16 +4634,16 @@
     <t xml:space="preserve">1.63377952575684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63564252853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64775168895721</t>
+    <t xml:space="preserve">1.63564264774323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64775156974792</t>
   </si>
   <si>
     <t xml:space="preserve">1.64682006835938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53131914138794</t>
+    <t xml:space="preserve">1.53131926059723</t>
   </si>
   <si>
     <t xml:space="preserve">1.54994833469391</t>
@@ -4679,25 +4679,25 @@
     <t xml:space="preserve">1.60956168174744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61980772018433</t>
+    <t xml:space="preserve">1.61980783939362</t>
   </si>
   <si>
     <t xml:space="preserve">1.62819087505341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59745287895203</t>
+    <t xml:space="preserve">1.59745275974274</t>
   </si>
   <si>
     <t xml:space="preserve">1.6123560667038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62073922157288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67755818367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64123141765594</t>
+    <t xml:space="preserve">1.62073934078217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67755830287933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64123129844666</t>
   </si>
   <si>
     <t xml:space="preserve">1.65706610679626</t>
@@ -4715,7 +4715,7 @@
     <t xml:space="preserve">1.6682436466217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67662668228149</t>
+    <t xml:space="preserve">1.67662680149078</t>
   </si>
   <si>
     <t xml:space="preserve">1.69059872627258</t>
@@ -4724,19 +4724,19 @@
     <t xml:space="preserve">1.72785711288452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84242653846741</t>
+    <t xml:space="preserve">1.84242641925812</t>
   </si>
   <si>
     <t xml:space="preserve">1.84801530838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90390264987946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92998361587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97655665874481</t>
+    <t xml:space="preserve">1.90390276908875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92998373508453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97655689716339</t>
   </si>
   <si>
     <t xml:space="preserve">1.96165335178375</t>
@@ -4748,10 +4748,10 @@
     <t xml:space="preserve">1.93557250499725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90949165821075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91135466098785</t>
+    <t xml:space="preserve">1.90949153900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91135454177856</t>
   </si>
   <si>
     <t xml:space="preserve">1.88899958133698</t>
@@ -4763,10 +4763,10 @@
     <t xml:space="preserve">2.09764647483826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09392023086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1106870174408</t>
+    <t xml:space="preserve">2.09392046928406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11068677902222</t>
   </si>
   <si>
     <t xml:space="preserve">2.08646893501282</t>
@@ -4775,40 +4775,40 @@
     <t xml:space="preserve">2.12000155448914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11441278457642</t>
+    <t xml:space="preserve">2.11441254615784</t>
   </si>
   <si>
     <t xml:space="preserve">2.10137224197388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03617024421692</t>
+    <t xml:space="preserve">2.03617000579834</t>
   </si>
   <si>
     <t xml:space="preserve">2.00263738632202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98028230667114</t>
+    <t xml:space="preserve">1.98028254508972</t>
   </si>
   <si>
     <t xml:space="preserve">2.01008915901184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01567792892456</t>
+    <t xml:space="preserve">2.01567816734314</t>
   </si>
   <si>
     <t xml:space="preserve">1.98214554786682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90017688274384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91694331169128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89272522926331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92812061309814</t>
+    <t xml:space="preserve">1.90017700195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91694343090057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8927253484726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92812073230743</t>
   </si>
   <si>
     <t xml:space="preserve">1.95420169830322</t>
@@ -5883,6 +5883,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19999980926514</t>
   </si>
 </sst>
 </file>
@@ -70935,7 +70938,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.649537037</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>472897</v>
@@ -70956,6 +70959,32 @@
         <v>1948</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.6494097222</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>299430</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>4.2020001411438</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>4.14400005340576</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>4.17399978637695</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>4.19999980926514</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>1957</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/OVS.MI.xlsx
+++ b/data/OVS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1966" uniqueCount="1966">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1967" uniqueCount="1967">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03756332397461</t>
+    <t xml:space="preserve">5.03756427764893</t>
   </si>
   <si>
     <t xml:space="preserve">OVS.MI</t>
@@ -56,22 +56,22 @@
     <t xml:space="preserve">4.71998643875122</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65647125244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78747224807739</t>
+    <t xml:space="preserve">4.65647077560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78747177124023</t>
   </si>
   <si>
     <t xml:space="preserve">4.94229030609131</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69219875335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60486459732056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63662338256836</t>
+    <t xml:space="preserve">4.69219923019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60486507415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6366229057312</t>
   </si>
   <si>
     <t xml:space="preserve">4.616774559021</t>
@@ -83,25 +83,25 @@
     <t xml:space="preserve">4.22774219512939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5334095954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45798540115356</t>
+    <t xml:space="preserve">4.53341007232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45798587799072</t>
   </si>
   <si>
     <t xml:space="preserve">4.47783422470093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49768257141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51356220245361</t>
+    <t xml:space="preserve">4.49768304824829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5135612487793</t>
   </si>
   <si>
     <t xml:space="preserve">4.4460768699646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6286826133728</t>
+    <t xml:space="preserve">4.62868309020996</t>
   </si>
   <si>
     <t xml:space="preserve">4.59295654296875</t>
@@ -110,85 +110,85 @@
     <t xml:space="preserve">4.51753187179565</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54531955718994</t>
+    <t xml:space="preserve">4.54531908035278</t>
   </si>
   <si>
     <t xml:space="preserve">4.32698583602905</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03322649002075</t>
+    <t xml:space="preserve">4.03322601318359</t>
   </si>
   <si>
     <t xml:space="preserve">4.02925682067871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27934885025024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22377300262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38256120681763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30316781997681</t>
+    <t xml:space="preserve">4.2793493270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22377252578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38256072998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30316734313965</t>
   </si>
   <si>
     <t xml:space="preserve">4.469895362854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46592426300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48577308654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48974323272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27140855789185</t>
+    <t xml:space="preserve">4.46592473983765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48577451705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48974275588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.271409034729</t>
   </si>
   <si>
     <t xml:space="preserve">4.23965167999268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43813753128052</t>
+    <t xml:space="preserve">4.43813705444336</t>
   </si>
   <si>
     <t xml:space="preserve">4.5651683807373</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67235040664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71601676940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58898639678955</t>
+    <t xml:space="preserve">4.67234992980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71601724624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58898687362671</t>
   </si>
   <si>
     <t xml:space="preserve">4.50562238693237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52547168731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38653039932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43019771575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40241050720215</t>
+    <t xml:space="preserve">4.52547216415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38653087615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43019819259644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40241003036499</t>
   </si>
   <si>
     <t xml:space="preserve">4.29125785827637</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12056016921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09674119949341</t>
+    <t xml:space="preserve">4.12056064605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09674167633057</t>
   </si>
   <si>
     <t xml:space="preserve">4.0649847984314</t>
@@ -203,10 +203,10 @@
     <t xml:space="preserve">4.21186447143555</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04910516738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02131748199463</t>
+    <t xml:space="preserve">4.04910612106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02131843566895</t>
   </si>
   <si>
     <t xml:space="preserve">4.31110668182373</t>
@@ -215,49 +215,49 @@
     <t xml:space="preserve">4.16422700881958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23568153381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50959157943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7358660697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5492901802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50165319442749</t>
+    <t xml:space="preserve">4.23568201065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50959205627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73586559295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54928922653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50165271759033</t>
   </si>
   <si>
     <t xml:space="preserve">4.56119823455811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48180437088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52150058746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55325841903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54134941101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56913805007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53738021850586</t>
+    <t xml:space="preserve">4.48180389404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5215015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55325937271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5413498878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56913757324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53737926483154</t>
   </si>
   <si>
     <t xml:space="preserve">4.64853191375732</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70410776138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84304761886597</t>
+    <t xml:space="preserve">4.7041072845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84304714202881</t>
   </si>
   <si>
     <t xml:space="preserve">4.89068412780762</t>
@@ -272,19 +272,19 @@
     <t xml:space="preserve">4.91053295135498</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75968456268311</t>
+    <t xml:space="preserve">4.75968360900879</t>
   </si>
   <si>
     <t xml:space="preserve">4.73826837539673</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76678800582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90123510360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73419523239136</t>
+    <t xml:space="preserve">4.76678705215454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90123462677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7341947555542</t>
   </si>
   <si>
     <t xml:space="preserve">4.56715393066406</t>
@@ -293,22 +293,22 @@
     <t xml:space="preserve">4.51826333999634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47344636917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47752094268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48974418640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63233995437622</t>
+    <t xml:space="preserve">4.47344732284546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47752046585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48974370956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6323390007019</t>
   </si>
   <si>
     <t xml:space="preserve">4.61196899414062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55085611343384</t>
+    <t xml:space="preserve">4.55085563659668</t>
   </si>
   <si>
     <t xml:space="preserve">4.51418828964233</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">4.33085060119629</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94706273078918</t>
+    <t xml:space="preserve">3.94706320762634</t>
   </si>
   <si>
     <t xml:space="preserve">4.13528966903687</t>
@@ -332,16 +332,16 @@
     <t xml:space="preserve">4.30233192443848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25751543045044</t>
+    <t xml:space="preserve">4.2575159072876</t>
   </si>
   <si>
     <t xml:space="preserve">4.11084461212158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09047365188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05299139022827</t>
+    <t xml:space="preserve">4.0904746055603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05299091339111</t>
   </si>
   <si>
     <t xml:space="preserve">4.18825435638428</t>
@@ -350,22 +350,22 @@
     <t xml:space="preserve">4.16380929946899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15566062927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15973424911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10677099227905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04321384429932</t>
+    <t xml:space="preserve">4.15566110610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15973472595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10677051544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04321432113647</t>
   </si>
   <si>
     <t xml:space="preserve">4.11899280548096</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16788291931152</t>
+    <t xml:space="preserve">4.16788339614868</t>
   </si>
   <si>
     <t xml:space="preserve">4.26158952713013</t>
@@ -374,19 +374,19 @@
     <t xml:space="preserve">4.20047760009766</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20862531661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23307037353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37159252166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36751890182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28603410720825</t>
+    <t xml:space="preserve">4.20862483978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.233069896698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37159299850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36751842498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28603363037109</t>
   </si>
   <si>
     <t xml:space="preserve">4.27788639068604</t>
@@ -395,7 +395,7 @@
     <t xml:space="preserve">4.24121809005737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25344181060791</t>
+    <t xml:space="preserve">4.25344133377075</t>
   </si>
   <si>
     <t xml:space="preserve">4.29825735092163</t>
@@ -407,22 +407,22 @@
     <t xml:space="preserve">4.07254695892334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17195796966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19232749938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10269641876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04158353805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13936424255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09862279891968</t>
+    <t xml:space="preserve">4.17195749282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19232845306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10269737243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04158306121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13936376571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09862232208252</t>
   </si>
   <si>
     <t xml:space="preserve">4.00084209442139</t>
@@ -434,10 +434,10 @@
     <t xml:space="preserve">4.0334358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19640302658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15158700942993</t>
+    <t xml:space="preserve">4.19640254974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15158653259277</t>
   </si>
   <si>
     <t xml:space="preserve">4.08640003204346</t>
@@ -446,7 +446,7 @@
     <t xml:space="preserve">4.0611400604248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3593692779541</t>
+    <t xml:space="preserve">4.35936975479126</t>
   </si>
   <si>
     <t xml:space="preserve">4.37566661834717</t>
@@ -455,13 +455,13 @@
     <t xml:space="preserve">4.4408540725708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41233396530151</t>
+    <t xml:space="preserve">4.41233348846436</t>
   </si>
   <si>
     <t xml:space="preserve">4.31862831115723</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31047964096069</t>
+    <t xml:space="preserve">4.31047916412354</t>
   </si>
   <si>
     <t xml:space="preserve">4.31455326080322</t>
@@ -476,10 +476,10 @@
     <t xml:space="preserve">4.1801061630249</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1434383392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11491870880127</t>
+    <t xml:space="preserve">4.14343786239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11491823196411</t>
   </si>
   <si>
     <t xml:space="preserve">4.07417774200439</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">4.06928873062134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08232593536377</t>
+    <t xml:space="preserve">4.08232545852661</t>
   </si>
   <si>
     <t xml:space="preserve">4.06439971923828</t>
@@ -497,25 +497,25 @@
     <t xml:space="preserve">4.00573110580444</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96009993553162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05462121963501</t>
+    <t xml:space="preserve">3.96010041236877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05462074279785</t>
   </si>
   <si>
     <t xml:space="preserve">4.13121604919434</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04647254943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.981285572052</t>
+    <t xml:space="preserve">4.04647302627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98128509521484</t>
   </si>
   <si>
     <t xml:space="preserve">4.00410175323486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9861752986908</t>
+    <t xml:space="preserve">3.98617482185364</t>
   </si>
   <si>
     <t xml:space="preserve">4.02528762817383</t>
@@ -527,46 +527,46 @@
     <t xml:space="preserve">4.02365779876709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05950975418091</t>
+    <t xml:space="preserve">4.05951023101807</t>
   </si>
   <si>
     <t xml:space="preserve">4.04810190200806</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05136203765869</t>
+    <t xml:space="preserve">4.05136156082153</t>
   </si>
   <si>
     <t xml:space="preserve">3.97965621948242</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03017568588257</t>
+    <t xml:space="preserve">4.03017616271973</t>
   </si>
   <si>
     <t xml:space="preserve">4.02039813995361</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99921202659607</t>
+    <t xml:space="preserve">3.99921154975891</t>
   </si>
   <si>
     <t xml:space="preserve">4.07825136184692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14751243591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23714351654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20455026626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22492170333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01713848114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02202749252319</t>
+    <t xml:space="preserve">4.1475133895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23714399337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20455121994019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22492218017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01713895797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02202701568604</t>
   </si>
   <si>
     <t xml:space="preserve">3.93076610565186</t>
@@ -578,46 +578,46 @@
     <t xml:space="preserve">3.8949134349823</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87535691261292</t>
+    <t xml:space="preserve">3.87535762786865</t>
   </si>
   <si>
     <t xml:space="preserve">3.94054460525513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93402600288391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89654350280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9552116394043</t>
+    <t xml:space="preserve">3.93402552604675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89654326438904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95521116256714</t>
   </si>
   <si>
     <t xml:space="preserve">4.00247240066528</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37974071502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38381385803223</t>
+    <t xml:space="preserve">4.3797402381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38381433486938</t>
   </si>
   <si>
     <t xml:space="preserve">4.39196348190308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35529518127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29010915756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28196001052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3267765045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29418277740479</t>
+    <t xml:space="preserve">4.35529565811157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2901086807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28196048736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32677698135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2941837310791</t>
   </si>
   <si>
     <t xml:space="preserve">4.33899879455566</t>
@@ -635,16 +635,16 @@
     <t xml:space="preserve">4.48159503936768</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40825986862183</t>
+    <t xml:space="preserve">4.40826034545898</t>
   </si>
   <si>
     <t xml:space="preserve">4.53863382339478</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55493068695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5264105796814</t>
+    <t xml:space="preserve">4.55493021011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52641105651855</t>
   </si>
   <si>
     <t xml:space="preserve">4.50604009628296</t>
@@ -653,40 +653,40 @@
     <t xml:space="preserve">4.43270444869995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59567213058472</t>
+    <t xml:space="preserve">4.59567165374756</t>
   </si>
   <si>
     <t xml:space="preserve">4.68530416488647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6730809211731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60381984710693</t>
+    <t xml:space="preserve">4.67308139801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60382032394409</t>
   </si>
   <si>
     <t xml:space="preserve">4.70160055160522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85642004013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82382678985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77493524551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79937982559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74234199523926</t>
+    <t xml:space="preserve">4.85641956329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8238263130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77493572235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7993803024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74234247207642</t>
   </si>
   <si>
     <t xml:space="preserve">4.78308486938477</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72604513168335</t>
+    <t xml:space="preserve">4.72604560852051</t>
   </si>
   <si>
     <t xml:space="preserve">4.77900981903076</t>
@@ -698,19 +698,19 @@
     <t xml:space="preserve">4.86456775665283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04790592193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01531219482422</t>
+    <t xml:space="preserve">5.04790544509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01531267166138</t>
   </si>
   <si>
     <t xml:space="preserve">4.89716148376465</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91753149032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88901233673096</t>
+    <t xml:space="preserve">4.91753196716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88901329040527</t>
   </si>
   <si>
     <t xml:space="preserve">5.04383134841919</t>
@@ -722,19 +722,19 @@
     <t xml:space="preserve">4.9501256942749</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05198049545288</t>
+    <t xml:space="preserve">5.05198097229004</t>
   </si>
   <si>
     <t xml:space="preserve">4.97864484786987</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03160905838013</t>
+    <t xml:space="preserve">5.03160953521729</t>
   </si>
   <si>
     <t xml:space="preserve">5.08457374572754</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23939228057861</t>
+    <t xml:space="preserve">5.23939180374146</t>
   </si>
   <si>
     <t xml:space="preserve">5.19864988327026</t>
@@ -743,28 +743,28 @@
     <t xml:space="preserve">5.14568519592285</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19457578659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05605411529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0642032623291</t>
+    <t xml:space="preserve">5.19457626342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05605459213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06420278549194</t>
   </si>
   <si>
     <t xml:space="preserve">5.13346385955811</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11716604232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25161552429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18235397338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17828035354614</t>
+    <t xml:space="preserve">5.11716651916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25161504745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18235349655151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17827987670898</t>
   </si>
   <si>
     <t xml:space="preserve">5.25568914413452</t>
@@ -773,13 +773,13 @@
     <t xml:space="preserve">5.27198505401611</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17420530319214</t>
+    <t xml:space="preserve">5.17420482635498</t>
   </si>
   <si>
     <t xml:space="preserve">5.16605663299561</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1864275932312</t>
+    <t xml:space="preserve">5.18642807006836</t>
   </si>
   <si>
     <t xml:space="preserve">5.10494470596313</t>
@@ -788,25 +788,25 @@
     <t xml:space="preserve">5.07235050201416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94605207443237</t>
+    <t xml:space="preserve">4.94605159759521</t>
   </si>
   <si>
     <t xml:space="preserve">5.06827592849731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98679351806641</t>
+    <t xml:space="preserve">4.98679399490356</t>
   </si>
   <si>
     <t xml:space="preserve">5.0369119644165</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36268186569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39191770553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3125638961792</t>
+    <t xml:space="preserve">5.3626823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39191818237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31256341934204</t>
   </si>
   <si>
     <t xml:space="preserve">5.27915048599243</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">5.34597587585449</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35432815551758</t>
+    <t xml:space="preserve">5.35432863235474</t>
   </si>
   <si>
     <t xml:space="preserve">5.32091665267944</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">5.27497386932373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1872673034668</t>
+    <t xml:space="preserve">5.18726778030396</t>
   </si>
   <si>
     <t xml:space="preserve">5.132972240448</t>
@@ -839,34 +839,34 @@
     <t xml:space="preserve">5.2039737701416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22903347015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25409173965454</t>
+    <t xml:space="preserve">5.22903299331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25409126281738</t>
   </si>
   <si>
     <t xml:space="preserve">5.2624454498291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1830906867981</t>
+    <t xml:space="preserve">5.18309116363525</t>
   </si>
   <si>
     <t xml:space="preserve">5.21232652664185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17891454696655</t>
+    <t xml:space="preserve">5.17891502380371</t>
   </si>
   <si>
     <t xml:space="preserve">5.24991512298584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24573802947998</t>
+    <t xml:space="preserve">5.24573850631714</t>
   </si>
   <si>
     <t xml:space="preserve">5.28332805633545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22485542297363</t>
+    <t xml:space="preserve">5.22485637664795</t>
   </si>
   <si>
     <t xml:space="preserve">5.30003356933594</t>
@@ -881,10 +881,10 @@
     <t xml:space="preserve">5.37521123886108</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40027046203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3835654258728</t>
+    <t xml:space="preserve">5.40027093887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38356494903564</t>
   </si>
   <si>
     <t xml:space="preserve">5.37938785552979</t>
@@ -893,31 +893,31 @@
     <t xml:space="preserve">5.23320960998535</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30838775634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25826835632324</t>
+    <t xml:space="preserve">5.3083872795105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2582688331604</t>
   </si>
   <si>
     <t xml:space="preserve">5.20814990997314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1371488571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11208963394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15385484695435</t>
+    <t xml:space="preserve">5.13714790344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11209011077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1538553237915</t>
   </si>
   <si>
     <t xml:space="preserve">5.23738527297974</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32509279251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30421018600464</t>
+    <t xml:space="preserve">5.32509326934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30420970916748</t>
   </si>
   <si>
     <t xml:space="preserve">5.29585695266724</t>
@@ -926,31 +926,31 @@
     <t xml:space="preserve">5.32926893234253</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48797845840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53809690475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59656858444214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62580394744873</t>
+    <t xml:space="preserve">5.48797798156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5380973815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59656810760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62580347061157</t>
   </si>
   <si>
     <t xml:space="preserve">5.68845272064209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61327505111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57568502426147</t>
+    <t xml:space="preserve">5.6132755279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57568597793579</t>
   </si>
   <si>
     <t xml:space="preserve">5.44203615188599</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62162733078003</t>
+    <t xml:space="preserve">5.62162780761719</t>
   </si>
   <si>
     <t xml:space="preserve">5.68009901046753</t>
@@ -959,10 +959,10 @@
     <t xml:space="preserve">5.64251041412354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37103509902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39609432220459</t>
+    <t xml:space="preserve">5.37103462219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39609384536743</t>
   </si>
   <si>
     <t xml:space="preserve">5.38774156570435</t>
@@ -977,13 +977,13 @@
     <t xml:space="preserve">5.19561958312988</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0828537940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88655662536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9074387550354</t>
+    <t xml:space="preserve">5.08285331726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88655567169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90743923187256</t>
   </si>
   <si>
     <t xml:space="preserve">4.81973123550415</t>
@@ -992,82 +992,82 @@
     <t xml:space="preserve">4.8030252456665</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84478998184204</t>
+    <t xml:space="preserve">4.8447904586792</t>
   </si>
   <si>
     <t xml:space="preserve">4.83643770217896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94502830505371</t>
+    <t xml:space="preserve">4.94502782821655</t>
   </si>
   <si>
     <t xml:space="preserve">4.90326261520386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86567401885986</t>
+    <t xml:space="preserve">4.86567354202271</t>
   </si>
   <si>
     <t xml:space="preserve">4.87820339202881</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85314464569092</t>
+    <t xml:space="preserve">4.85314416885376</t>
   </si>
   <si>
     <t xml:space="preserve">4.81137800216675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95755863189697</t>
+    <t xml:space="preserve">4.9575572013855</t>
   </si>
   <si>
     <t xml:space="preserve">4.92832183837891</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7779655456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86149644851685</t>
+    <t xml:space="preserve">4.77796602249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.861496925354</t>
   </si>
   <si>
     <t xml:space="preserve">4.83226156234741</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7236704826355</t>
+    <t xml:space="preserve">4.72367000579834</t>
   </si>
   <si>
     <t xml:space="preserve">4.66102266311646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69861030578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66937589645386</t>
+    <t xml:space="preserve">4.69861125946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6693754196167</t>
   </si>
   <si>
     <t xml:space="preserve">4.63596343994141</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70278882980347</t>
+    <t xml:space="preserve">4.70278835296631</t>
   </si>
   <si>
     <t xml:space="preserve">4.67355155944824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64013957977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7194938659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79049491882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74873018264771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7320237159729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71114110946655</t>
+    <t xml:space="preserve">4.64014005661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71949434280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7904953956604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74872922897339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73202419281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71114063262939</t>
   </si>
   <si>
     <t xml:space="preserve">4.67772912979126</t>
@@ -1076,16 +1076,16 @@
     <t xml:space="preserve">4.9157919883728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92414474487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89490842819214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84061479568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16220808029175</t>
+    <t xml:space="preserve">4.92414379119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8949089050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8406138420105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16220760345459</t>
   </si>
   <si>
     <t xml:space="preserve">4.99932193756104</t>
@@ -1097,19 +1097,19 @@
     <t xml:space="preserve">5.17056083679199</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09955978393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95338106155396</t>
+    <t xml:space="preserve">5.09955930709839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95338153839111</t>
   </si>
   <si>
     <t xml:space="preserve">4.98679304122925</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78631973266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68608093261719</t>
+    <t xml:space="preserve">4.7863187789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6860818862915</t>
   </si>
   <si>
     <t xml:space="preserve">4.60672760009766</t>
@@ -1124,22 +1124,22 @@
     <t xml:space="preserve">4.63178730010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70696496963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58584451675415</t>
+    <t xml:space="preserve">4.70696449279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58584547042847</t>
   </si>
   <si>
     <t xml:space="preserve">4.55243301391602</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53990268707275</t>
+    <t xml:space="preserve">4.53990316390991</t>
   </si>
   <si>
     <t xml:space="preserve">4.57749223709106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48978424072266</t>
+    <t xml:space="preserve">4.4897837638855</t>
   </si>
   <si>
     <t xml:space="preserve">4.41043043136597</t>
@@ -1148,22 +1148,22 @@
     <t xml:space="preserve">4.44384241104126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49395990371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47307777404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51902008056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59002161026001</t>
+    <t xml:space="preserve">4.4939603805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47307825088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51902055740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59002113342285</t>
   </si>
   <si>
     <t xml:space="preserve">4.65684652328491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64849233627319</t>
+    <t xml:space="preserve">4.64849281311035</t>
   </si>
   <si>
     <t xml:space="preserve">4.59837436676025</t>
@@ -1178,7 +1178,7 @@
     <t xml:space="preserve">4.43966579437256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36031198501587</t>
+    <t xml:space="preserve">4.36031150817871</t>
   </si>
   <si>
     <t xml:space="preserve">4.38537073135376</t>
@@ -1187,22 +1187,22 @@
     <t xml:space="preserve">4.18907308578491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16150760650635</t>
+    <t xml:space="preserve">4.16150808334351</t>
   </si>
   <si>
     <t xml:space="preserve">4.15148448944092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15649604797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19324922561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09802436828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1531548500061</t>
+    <t xml:space="preserve">4.15649557113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19325017929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09802389144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15315437316895</t>
   </si>
   <si>
     <t xml:space="preserve">4.10303688049316</t>
@@ -1217,10 +1217,10 @@
     <t xml:space="preserve">4.17654418945312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14313077926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16819000244141</t>
+    <t xml:space="preserve">4.1431303024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16819047927856</t>
   </si>
   <si>
     <t xml:space="preserve">2.83002591133118</t>
@@ -1232,13 +1232,13 @@
     <t xml:space="preserve">2.84339070320129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87179136276245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89350914955139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80162477493286</t>
+    <t xml:space="preserve">2.87179160118103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89350891113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80162501335144</t>
   </si>
   <si>
     <t xml:space="preserve">2.92358064651489</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">2.94863963127136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01713538169861</t>
+    <t xml:space="preserve">3.01713514328003</t>
   </si>
   <si>
     <t xml:space="preserve">3.08061838150024</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">3.14911389350891</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15746688842773</t>
+    <t xml:space="preserve">3.15746665000916</t>
   </si>
   <si>
     <t xml:space="preserve">3.14410185813904</t>
@@ -1268,22 +1268,22 @@
     <t xml:space="preserve">3.17918515205383</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17417335510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10400772094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01212334632874</t>
+    <t xml:space="preserve">3.17417311668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10400748252869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01212286949158</t>
   </si>
   <si>
     <t xml:space="preserve">3.02882957458496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94529795646667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95699262619019</t>
+    <t xml:space="preserve">2.94529819488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95699238777161</t>
   </si>
   <si>
     <t xml:space="preserve">2.89852118492126</t>
@@ -1295,64 +1295,64 @@
     <t xml:space="preserve">2.8250138759613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85007309913635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74649524688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55771446228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54769158363342</t>
+    <t xml:space="preserve">2.85007333755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74649548530579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55771470069885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54769134521484</t>
   </si>
   <si>
     <t xml:space="preserve">2.51093792915344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58945727348328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50091361999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51594972610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50592541694641</t>
+    <t xml:space="preserve">2.58945751190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5009138584137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51594996452332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50592589378357</t>
   </si>
   <si>
     <t xml:space="preserve">2.47919607162476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41905379295349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39566516876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36058235168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36726474761963</t>
+    <t xml:space="preserve">2.41905355453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39566564559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36058187484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36726450920105</t>
   </si>
   <si>
     <t xml:space="preserve">2.3772885799408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2753803730011</t>
+    <t xml:space="preserve">2.27538061141968</t>
   </si>
   <si>
     <t xml:space="preserve">2.313805103302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26201510429382</t>
+    <t xml:space="preserve">2.26201558113098</t>
   </si>
   <si>
     <t xml:space="preserve">2.27203941345215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41404223442078</t>
+    <t xml:space="preserve">2.41404247283936</t>
   </si>
   <si>
     <t xml:space="preserve">2.38062953948975</t>
@@ -1367,19 +1367,19 @@
     <t xml:space="preserve">2.29709887504578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32382845878601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33552289009094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35389947891235</t>
+    <t xml:space="preserve">2.32382869720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33552312850952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35389971733093</t>
   </si>
   <si>
     <t xml:space="preserve">2.36559438705444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35055828094482</t>
+    <t xml:space="preserve">2.35055804252625</t>
   </si>
   <si>
     <t xml:space="preserve">2.35222935676575</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">2.35557007789612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25533318519592</t>
+    <t xml:space="preserve">2.25533294677734</t>
   </si>
   <si>
     <t xml:space="preserve">2.22025060653687</t>
@@ -1397,13 +1397,13 @@
     <t xml:space="preserve">2.28039240837097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22526168823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23027396202087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40067672729492</t>
+    <t xml:space="preserve">2.22526144981384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23027372360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40067648887634</t>
   </si>
   <si>
     <t xml:space="preserve">2.44912481307983</t>
@@ -1412,10 +1412,10 @@
     <t xml:space="preserve">2.42406558990479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31881642341614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30879330635071</t>
+    <t xml:space="preserve">2.31881666183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30879306793213</t>
   </si>
   <si>
     <t xml:space="preserve">2.34387588500977</t>
@@ -1436,34 +1436,34 @@
     <t xml:space="preserve">2.15342569351196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21022629737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21189713478088</t>
+    <t xml:space="preserve">2.21022653579712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2118968963623</t>
   </si>
   <si>
     <t xml:space="preserve">2.05485892295837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01142311096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97466933727264</t>
+    <t xml:space="preserve">2.01142263412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97466897964478</t>
   </si>
   <si>
     <t xml:space="preserve">2.00474047660828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03815317153931</t>
+    <t xml:space="preserve">2.03815340995789</t>
   </si>
   <si>
     <t xml:space="preserve">2.1517550945282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17180228233337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18182563781738</t>
+    <t xml:space="preserve">2.17180252075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1818253993988</t>
   </si>
   <si>
     <t xml:space="preserve">2.16679048538208</t>
@@ -1475,28 +1475,28 @@
     <t xml:space="preserve">2.15509605407715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15676641464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11500144004822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07657742500305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08994221687317</t>
+    <t xml:space="preserve">2.15676665306091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11500120162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07657718658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08994245529175</t>
   </si>
   <si>
     <t xml:space="preserve">2.09829497337341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1601083278656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09662461280823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09161281585693</t>
+    <t xml:space="preserve">2.16010808944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09662508964539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09161257743835</t>
   </si>
   <si>
     <t xml:space="preserve">2.02478766441345</t>
@@ -1511,52 +1511,52 @@
     <t xml:space="preserve">2.23695611953735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18683791160583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11834239959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06989502906799</t>
+    <t xml:space="preserve">2.18683767318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11834216117859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06989526748657</t>
   </si>
   <si>
     <t xml:space="preserve">2.06321263313293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00139975547791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9997284412384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98302268981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94626927375793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87610304355621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75748944282532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69567656517029</t>
+    <t xml:space="preserve">2.00139951705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99972856044769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9830230474472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94626903533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87610328197479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75748932361603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.695676445961</t>
   </si>
   <si>
     <t xml:space="preserve">1.65391063690186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62885141372681</t>
+    <t xml:space="preserve">1.6288515329361</t>
   </si>
   <si>
     <t xml:space="preserve">1.62968707084656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50439071655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48601400852203</t>
+    <t xml:space="preserve">1.50439059734344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48601388931274</t>
   </si>
   <si>
     <t xml:space="preserve">1.39663565158844</t>
@@ -1571,10 +1571,10 @@
     <t xml:space="preserve">1.27133929729462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24962162971497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24460971355438</t>
+    <t xml:space="preserve">1.24962174892426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24460959434509</t>
   </si>
   <si>
     <t xml:space="preserve">1.2897162437439</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">1.27635133266449</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30391657352448</t>
+    <t xml:space="preserve">1.30391645431519</t>
   </si>
   <si>
     <t xml:space="preserve">1.3156111240387</t>
@@ -1598,10 +1598,10 @@
     <t xml:space="preserve">1.27969300746918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33899986743927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35152924060822</t>
+    <t xml:space="preserve">1.33899998664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35152912139893</t>
   </si>
   <si>
     <t xml:space="preserve">1.29472827911377</t>
@@ -1610,22 +1610,22 @@
     <t xml:space="preserve">1.29639852046967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24293911457062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25212776660919</t>
+    <t xml:space="preserve">1.2429393529892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2521276473999</t>
   </si>
   <si>
     <t xml:space="preserve">1.26799845695496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25296258926392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23375082015991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25630402565002</t>
+    <t xml:space="preserve">1.25296247005463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2337509393692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25630414485931</t>
   </si>
   <si>
     <t xml:space="preserve">1.2579745054245</t>
@@ -1634,37 +1634,37 @@
     <t xml:space="preserve">1.26048040390015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36823558807373</t>
+    <t xml:space="preserve">1.36823582649231</t>
   </si>
   <si>
     <t xml:space="preserve">1.36990594863892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36405920982361</t>
+    <t xml:space="preserve">1.36405909061432</t>
   </si>
   <si>
     <t xml:space="preserve">1.34568238258362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31477534770966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34484672546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25129187107086</t>
+    <t xml:space="preserve">1.31477546691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34484684467316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25129210948944</t>
   </si>
   <si>
     <t xml:space="preserve">1.23876285552979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06835901737213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962275147438049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989840507507324</t>
+    <t xml:space="preserve">1.06835913658142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962275207042694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989840626716614</t>
   </si>
   <si>
     <t xml:space="preserve">0.633163154125214</t>
@@ -1676,16 +1676,16 @@
     <t xml:space="preserve">0.705000281333923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.862038254737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958099007606506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948074877262115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848673462867737</t>
+    <t xml:space="preserve">0.862038195133209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958098888397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948074817657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848673403263092</t>
   </si>
   <si>
     <t xml:space="preserve">0.913827121257782</t>
@@ -1694,7 +1694,7 @@
     <t xml:space="preserve">0.9447340965271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.918839156627655</t>
+    <t xml:space="preserve">0.91883909702301</t>
   </si>
   <si>
     <t xml:space="preserve">0.917168855667114</t>
@@ -1703,10 +1703,10 @@
     <t xml:space="preserve">1.00487577915192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1477142572403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11430132389069</t>
+    <t xml:space="preserve">1.14771413803101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11430144309998</t>
   </si>
   <si>
     <t xml:space="preserve">1.09926605224609</t>
@@ -1715,16 +1715,16 @@
     <t xml:space="preserve">1.13184344768524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10344243049622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03578269481659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01155817508698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01824057102203</t>
+    <t xml:space="preserve">1.10344254970551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0357825756073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01155829429626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01824069023132</t>
   </si>
   <si>
     <t xml:space="preserve">0.999028921127319</t>
@@ -1736,16 +1736,16 @@
     <t xml:space="preserve">1.01322948932648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08255970478058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10177206993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1276661157608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12933743000031</t>
+    <t xml:space="preserve">1.082559466362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10177218914032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12766623497009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12933731079102</t>
   </si>
   <si>
     <t xml:space="preserve">1.13017225265503</t>
@@ -1754,19 +1754,19 @@
     <t xml:space="preserve">1.1368545293808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11346650123596</t>
+    <t xml:space="preserve">1.11346662044525</t>
   </si>
   <si>
     <t xml:space="preserve">1.10260689258575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06585311889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0324410200119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07086503505707</t>
+    <t xml:space="preserve">1.06585299968719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03244113922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07086527347565</t>
   </si>
   <si>
     <t xml:space="preserve">1.06334805488586</t>
@@ -1778,37 +1778,37 @@
     <t xml:space="preserve">1.03494715690613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06501829624176</t>
+    <t xml:space="preserve">1.06501841545105</t>
   </si>
   <si>
     <t xml:space="preserve">1.12850165367126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08506572246552</t>
+    <t xml:space="preserve">1.08506560325623</t>
   </si>
   <si>
     <t xml:space="preserve">1.08673596382141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07253634929657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08088910579681</t>
+    <t xml:space="preserve">1.07253646850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0808892250061</t>
   </si>
   <si>
     <t xml:space="preserve">1.1051127910614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07838320732117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10010075569153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11263084411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11012494564056</t>
+    <t xml:space="preserve">1.07838332653046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10010087490082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11263072490692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11012482643127</t>
   </si>
   <si>
     <t xml:space="preserve">1.22623288631439</t>
@@ -1817,37 +1817,37 @@
     <t xml:space="preserve">1.46179032325745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41584801673889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.414177775383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36071765422821</t>
+    <t xml:space="preserve">1.4158478975296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41417765617371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36071753501892</t>
   </si>
   <si>
     <t xml:space="preserve">1.33064615726471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29806983470917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3732476234436</t>
+    <t xml:space="preserve">1.29806971549988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37324774265289</t>
   </si>
   <si>
     <t xml:space="preserve">1.38744723796844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32981145381927</t>
+    <t xml:space="preserve">1.32981157302856</t>
   </si>
   <si>
     <t xml:space="preserve">1.35069346427917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35487067699432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32897579669952</t>
+    <t xml:space="preserve">1.3548709154129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32897591590881</t>
   </si>
   <si>
     <t xml:space="preserve">1.36572968959808</t>
@@ -1856,19 +1856,19 @@
     <t xml:space="preserve">1.37157642841339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40248322486877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41918897628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42169487476349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42253065109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42837727069855</t>
+    <t xml:space="preserve">1.40248310565948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41918885707855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42169499397278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42253041267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42837738990784</t>
   </si>
   <si>
     <t xml:space="preserve">1.39997732639313</t>
@@ -1880,16 +1880,16 @@
     <t xml:space="preserve">1.39412951469421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45343661308289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43589544296265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52861428260803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61131024360657</t>
+    <t xml:space="preserve">1.4534364938736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43589532375336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52861440181732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61131036281586</t>
   </si>
   <si>
     <t xml:space="preserve">1.5971097946167</t>
@@ -1898,10 +1898,10 @@
     <t xml:space="preserve">1.59376895427704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5745564699173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55283892154694</t>
+    <t xml:space="preserve">1.57455658912659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55283880233765</t>
   </si>
   <si>
     <t xml:space="preserve">1.55116772651672</t>
@@ -1913,7 +1913,7 @@
     <t xml:space="preserve">1.47097861766815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41751861572266</t>
+    <t xml:space="preserve">1.41751849651337</t>
   </si>
   <si>
     <t xml:space="preserve">1.43422496318817</t>
@@ -1925,7 +1925,7 @@
     <t xml:space="preserve">1.38327074050903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3323165178299</t>
+    <t xml:space="preserve">1.33231663703918</t>
   </si>
   <si>
     <t xml:space="preserve">1.36739993095398</t>
@@ -1934,7 +1934,7 @@
     <t xml:space="preserve">1.34985876083374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30308091640472</t>
+    <t xml:space="preserve">1.3030811548233</t>
   </si>
   <si>
     <t xml:space="preserve">1.32229351997375</t>
@@ -1946,13 +1946,13 @@
     <t xml:space="preserve">1.2989045381546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30892872810364</t>
+    <t xml:space="preserve">1.30892860889435</t>
   </si>
   <si>
     <t xml:space="preserve">1.31059908866882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31895196437836</t>
+    <t xml:space="preserve">1.31895172595978</t>
   </si>
   <si>
     <t xml:space="preserve">1.29222226142883</t>
@@ -1967,19 +1967,19 @@
     <t xml:space="preserve">1.32730543613434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31143450737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31978738307953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34902310371399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34651720523834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30725836753845</t>
+    <t xml:space="preserve">1.31143462657928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31978750228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3490229845047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34651708602905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30725824832916</t>
   </si>
   <si>
     <t xml:space="preserve">1.26215088367462</t>
@@ -1988,10 +1988,10 @@
     <t xml:space="preserve">1.26883327960968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22205626964569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19198524951935</t>
+    <t xml:space="preserve">1.22205638885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19198513031006</t>
   </si>
   <si>
     <t xml:space="preserve">1.35821151733398</t>
@@ -2000,43 +2000,43 @@
     <t xml:space="preserve">1.32312917709351</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28219902515411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24043309688568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27384531497955</t>
+    <t xml:space="preserve">1.28219890594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24043321609497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27384519577026</t>
   </si>
   <si>
     <t xml:space="preserve">1.2613160610199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32646977901459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33816432952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42503654956818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48183727264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49603807926178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50272023677826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50355517864227</t>
+    <t xml:space="preserve">1.32646989822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3381644487381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42503666877747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48183739185333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49603796005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50272035598755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50355494022369</t>
   </si>
   <si>
     <t xml:space="preserve">1.54448533058167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56369769573212</t>
+    <t xml:space="preserve">1.56369757652283</t>
   </si>
   <si>
     <t xml:space="preserve">1.53863835334778</t>
@@ -2045,13 +2045,13 @@
     <t xml:space="preserve">1.54866254329681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49186050891876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41668283939362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39329493045807</t>
+    <t xml:space="preserve">1.49186074733734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41668295860291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39329481124878</t>
   </si>
   <si>
     <t xml:space="preserve">1.39078879356384</t>
@@ -2084,13 +2084,13 @@
     <t xml:space="preserve">1.33315229415894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26549255847931</t>
+    <t xml:space="preserve">1.26549243927002</t>
   </si>
   <si>
     <t xml:space="preserve">1.24210357666016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38995337486267</t>
+    <t xml:space="preserve">1.38995325565338</t>
   </si>
   <si>
     <t xml:space="preserve">1.37074172496796</t>
@@ -2105,7 +2105,7 @@
     <t xml:space="preserve">1.37993001937866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45260179042816</t>
+    <t xml:space="preserve">1.45260167121887</t>
   </si>
   <si>
     <t xml:space="preserve">1.48852002620697</t>
@@ -2114,7 +2114,7 @@
     <t xml:space="preserve">1.49687266349792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50104892253876</t>
+    <t xml:space="preserve">1.50104904174805</t>
   </si>
   <si>
     <t xml:space="preserve">1.44758975505829</t>
@@ -2126,16 +2126,16 @@
     <t xml:space="preserve">1.54281485080719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4609546661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39162373542786</t>
+    <t xml:space="preserve">1.46095454692841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39162361621857</t>
   </si>
   <si>
     <t xml:space="preserve">1.41000056266785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40833020210266</t>
+    <t xml:space="preserve">1.40833008289337</t>
   </si>
   <si>
     <t xml:space="preserve">1.4292129278183</t>
@@ -2147,7 +2147,7 @@
     <t xml:space="preserve">1.3339878320694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32563424110413</t>
+    <t xml:space="preserve">1.32563400268555</t>
   </si>
   <si>
     <t xml:space="preserve">1.33732867240906</t>
@@ -2171,28 +2171,28 @@
     <t xml:space="preserve">1.47181332111359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46513104438782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47264897823334</t>
+    <t xml:space="preserve">1.46513092517853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47264909744263</t>
   </si>
   <si>
     <t xml:space="preserve">1.51190876960754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47014307975769</t>
+    <t xml:space="preserve">1.47014319896698</t>
   </si>
   <si>
     <t xml:space="preserve">1.49269616603851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52276766300201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54030871391296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53529667854309</t>
+    <t xml:space="preserve">1.52276754379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54030883312225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53529679775238</t>
   </si>
   <si>
     <t xml:space="preserve">1.59794545173645</t>
@@ -2204,7 +2204,7 @@
     <t xml:space="preserve">1.58625102043152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64555788040161</t>
+    <t xml:space="preserve">1.64555776119232</t>
   </si>
   <si>
     <t xml:space="preserve">1.59293341636658</t>
@@ -2213,37 +2213,37 @@
     <t xml:space="preserve">1.63219308853149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58458054065704</t>
+    <t xml:space="preserve">1.58458065986633</t>
   </si>
   <si>
     <t xml:space="preserve">1.56035614013672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54197931289673</t>
+    <t xml:space="preserve">1.54197919368744</t>
   </si>
   <si>
     <t xml:space="preserve">1.55868566036224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56620359420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56703853607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58708667755127</t>
+    <t xml:space="preserve">1.56620371341705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56703841686249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58708655834198</t>
   </si>
   <si>
     <t xml:space="preserve">1.64973437786102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74078297615051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70737075805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71906542778015</t>
+    <t xml:space="preserve">1.74078285694122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70737087726593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71906530857086</t>
   </si>
   <si>
     <t xml:space="preserve">1.72908842563629</t>
@@ -2252,10 +2252,10 @@
     <t xml:space="preserve">1.71238279342651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73243010044098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69233465194702</t>
+    <t xml:space="preserve">1.73243021965027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69233477115631</t>
   </si>
   <si>
     <t xml:space="preserve">1.76584208011627</t>
@@ -2267,31 +2267,31 @@
     <t xml:space="preserve">1.72073566913605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63887560367584</t>
+    <t xml:space="preserve">1.63887548446655</t>
   </si>
   <si>
     <t xml:space="preserve">1.60880410671234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68565237522125</t>
+    <t xml:space="preserve">1.68565249443054</t>
   </si>
   <si>
     <t xml:space="preserve">1.67061710357666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68732368946075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67562913894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6806412935257</t>
+    <t xml:space="preserve">1.68732357025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67562901973724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68064117431641</t>
   </si>
   <si>
     <t xml:space="preserve">1.61715698242188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61548674106598</t>
+    <t xml:space="preserve">1.6154865026474</t>
   </si>
   <si>
     <t xml:space="preserve">1.62467503547668</t>
@@ -2300,16 +2300,16 @@
     <t xml:space="preserve">1.61047458648682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64054596424103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62383949756622</t>
+    <t xml:space="preserve">1.64054584503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62383937835693</t>
   </si>
   <si>
     <t xml:space="preserve">1.60963988304138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57789826393127</t>
+    <t xml:space="preserve">1.57789814472198</t>
   </si>
   <si>
     <t xml:space="preserve">1.59126305580139</t>
@@ -2327,22 +2327,22 @@
     <t xml:space="preserve">1.58290922641754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60379207134247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6004513502121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58541536331177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54532074928284</t>
+    <t xml:space="preserve">1.60379219055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60045146942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58541512489319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54532086849213</t>
   </si>
   <si>
     <t xml:space="preserve">1.54699122905731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57706260681152</t>
+    <t xml:space="preserve">1.57706248760223</t>
   </si>
   <si>
     <t xml:space="preserve">1.43756568431854</t>
@@ -2351,10 +2351,10 @@
     <t xml:space="preserve">1.49436676502228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48935556411743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46763706207275</t>
+    <t xml:space="preserve">1.48935544490814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46763694286346</t>
   </si>
   <si>
     <t xml:space="preserve">1.51274359226227</t>
@@ -2366,16 +2366,16 @@
     <t xml:space="preserve">1.53195595741272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54782676696777</t>
+    <t xml:space="preserve">1.54782688617706</t>
   </si>
   <si>
     <t xml:space="preserve">1.51691997051239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50940263271332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48267209529877</t>
+    <t xml:space="preserve">1.50940275192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48267221450806</t>
   </si>
   <si>
     <t xml:space="preserve">1.26465690135956</t>
@@ -2384,10 +2384,10 @@
     <t xml:space="preserve">1.23208045959473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18029069900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16692566871643</t>
+    <t xml:space="preserve">1.18029081821442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16692590713501</t>
   </si>
   <si>
     <t xml:space="preserve">1.13601970672607</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">1.02742898464203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.933039665222168</t>
+    <t xml:space="preserve">0.933039784431458</t>
   </si>
   <si>
     <t xml:space="preserve">0.776836335659027</t>
@@ -2405,61 +2405,61 @@
     <t xml:space="preserve">0.719200670719147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.695811867713928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54670923948288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613534271717072</t>
+    <t xml:space="preserve">0.695811808109283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.546709179878235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613534212112427</t>
   </si>
   <si>
     <t xml:space="preserve">0.519561350345612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599333763122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.674928903579712</t>
+    <t xml:space="preserve">0.599333703517914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.674928963184357</t>
   </si>
   <si>
     <t xml:space="preserve">0.725047469139099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.701658606529236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.637340486049652</t>
+    <t xml:space="preserve">0.701658546924591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.637340426445007</t>
   </si>
   <si>
     <t xml:space="preserve">0.682446956634521</t>
   </si>
   <si>
-    <t xml:space="preserve">0.680358290672302</t>
+    <t xml:space="preserve">0.680358350276947</t>
   </si>
   <si>
     <t xml:space="preserve">0.687876343727112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.659893691539764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643604516983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.65947550535202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643187165260315</t>
+    <t xml:space="preserve">0.659893751144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.643604636192322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.659475445747375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.64318722486496</t>
   </si>
   <si>
     <t xml:space="preserve">0.627316415309906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.576780557632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618128001689911</t>
+    <t xml:space="preserve">0.576780498027802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618127942085266</t>
   </si>
   <si>
     <t xml:space="preserve">0.660728454589844</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">0.650705277919769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.638175189495087</t>
+    <t xml:space="preserve">0.638175249099731</t>
   </si>
   <si>
     <t xml:space="preserve">0.649869680404663</t>
@@ -2483,61 +2483,61 @@
     <t xml:space="preserve">0.612281203269958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61562192440033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.610192477703094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.605598747730255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.611028134822845</t>
+    <t xml:space="preserve">0.615621984004974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.610192537307739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6055988073349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61102819442749</t>
   </si>
   <si>
     <t xml:space="preserve">0.651540040969849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.676599323749542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.654881715774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.642351567745209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.641516923904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.655717253684998</t>
+    <t xml:space="preserve">0.676599264144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.654881656169891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.642351627349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.641516864299774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.655717313289642</t>
   </si>
   <si>
     <t xml:space="preserve">0.639846503734589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649034917354584</t>
+    <t xml:space="preserve">0.649034857749939</t>
   </si>
   <si>
     <t xml:space="preserve">0.668246567249298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.65028703212738</t>
+    <t xml:space="preserve">0.650287091732025</t>
   </si>
   <si>
     <t xml:space="preserve">0.6264808177948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.609775245189667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.606016159057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.629822373390198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596827805042267</t>
+    <t xml:space="preserve">0.609775185585022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.606016099452972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.629822432994843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596827745437622</t>
   </si>
   <si>
     <t xml:space="preserve">0.574691832065582</t>
@@ -2546,16 +2546,16 @@
     <t xml:space="preserve">0.581792593002319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.57427453994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60183972120285</t>
+    <t xml:space="preserve">0.574274480342865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.601839780807495</t>
   </si>
   <si>
     <t xml:space="preserve">0.630658030509949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.726300418376923</t>
+    <t xml:space="preserve">0.726300477981567</t>
   </si>
   <si>
     <t xml:space="preserve">0.789366483688354</t>
@@ -2564,40 +2564,40 @@
     <t xml:space="preserve">0.763054192066193</t>
   </si>
   <si>
-    <t xml:space="preserve">0.768483519554138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827790558338165</t>
+    <t xml:space="preserve">0.768483638763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.82779061794281</t>
   </si>
   <si>
     <t xml:space="preserve">0.83530855178833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.901298046112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910486400127411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00571155548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01072347164154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968957722187042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877909064292908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924685955047607</t>
+    <t xml:space="preserve">0.901297986507416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.910486340522766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00571131706238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01072335243225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968957662582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877909004688263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924685895442963</t>
   </si>
   <si>
     <t xml:space="preserve">0.925521612167358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938051521778107</t>
+    <t xml:space="preserve">0.938051640987396</t>
   </si>
   <si>
     <t xml:space="preserve">0.922180891036987</t>
@@ -2606,13 +2606,13 @@
     <t xml:space="preserve">0.892109513282776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.893779933452606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895450294017792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823614120483398</t>
+    <t xml:space="preserve">0.893779993057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895450234413147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823614180088043</t>
   </si>
   <si>
     <t xml:space="preserve">0.781013667583466</t>
@@ -2621,28 +2621,28 @@
     <t xml:space="preserve">0.824867188930511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.806072950363159</t>
+    <t xml:space="preserve">0.806073009967804</t>
   </si>
   <si>
     <t xml:space="preserve">0.78560745716095</t>
   </si>
   <si>
-    <t xml:space="preserve">0.802313923835754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.797719240188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801895678043365</t>
+    <t xml:space="preserve">0.802313983440399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.797719299793243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801895618438721</t>
   </si>
   <si>
     <t xml:space="preserve">0.79855489730835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.776419043540955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.782266676425934</t>
+    <t xml:space="preserve">0.77641898393631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.782266616821289</t>
   </si>
   <si>
     <t xml:space="preserve">0.766394972801208</t>
@@ -2654,88 +2654,88 @@
     <t xml:space="preserve">0.795631527900696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.863708555698395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855355739593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.84449702501297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857861816883087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.836143434047699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.834890425205231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838649451732635</t>
+    <t xml:space="preserve">0.86370861530304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855355799198151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.844496965408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857861876487732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.836143314838409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834890365600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838649332523346</t>
   </si>
   <si>
     <t xml:space="preserve">0.800225257873535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.773913025856018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789783835411072</t>
+    <t xml:space="preserve">0.773912966251373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789783895015717</t>
   </si>
   <si>
     <t xml:space="preserve">0.771825313568115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.767230629920959</t>
+    <t xml:space="preserve">0.767230570316315</t>
   </si>
   <si>
     <t xml:space="preserve">0.775583386421204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.786860406398773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79270726442337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.758877754211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.765977561473846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.800642609596252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809831023216248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799807906150818</t>
+    <t xml:space="preserve">0.786860466003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.792707204818726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.758877813816071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.765977501869202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800642669200897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809831082820892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799807965755463</t>
   </si>
   <si>
     <t xml:space="preserve">0.780178070068359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.770989656448364</t>
+    <t xml:space="preserve">0.770989596843719</t>
   </si>
   <si>
     <t xml:space="preserve">0.740918278694153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.717947721481323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.712099969387054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.684117317199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69079977273941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.692888379096985</t>
+    <t xml:space="preserve">0.717947661876678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.712100088596344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.684117376804352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.690799713134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69288831949234</t>
   </si>
   <si>
     <t xml:space="preserve">0.685787737369537</t>
@@ -2747,7 +2747,7 @@
     <t xml:space="preserve">0.666576147079468</t>
   </si>
   <si>
-    <t xml:space="preserve">0.682029604911804</t>
+    <t xml:space="preserve">0.682029545307159</t>
   </si>
   <si>
     <t xml:space="preserve">0.687458992004395</t>
@@ -2759,7 +2759,7 @@
     <t xml:space="preserve">0.67785233259201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.69455873966217</t>
+    <t xml:space="preserve">0.694558799266815</t>
   </si>
   <si>
     <t xml:space="preserve">0.697482168674469</t>
@@ -2780,31 +2780,31 @@
     <t xml:space="preserve">0.742588639259338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.767647922039032</t>
+    <t xml:space="preserve">0.767647981643677</t>
   </si>
   <si>
     <t xml:space="preserve">0.718365013599396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.715024352073669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781848430633545</t>
+    <t xml:space="preserve">0.715024292469025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7818483710289</t>
   </si>
   <si>
     <t xml:space="preserve">0.75720739364624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778925061225891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79646623134613</t>
+    <t xml:space="preserve">0.778925120830536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796466290950775</t>
   </si>
   <si>
     <t xml:space="preserve">0.825284540653229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.850343763828278</t>
+    <t xml:space="preserve">0.850343704223633</t>
   </si>
   <si>
     <t xml:space="preserve">0.860367834568024</t>
@@ -2813,73 +2813,73 @@
     <t xml:space="preserve">0.847003042697906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.858696639537811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843661367893219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8720623254776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852014183998108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.854520082473755</t>
+    <t xml:space="preserve">0.858696579933167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843661308288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872062265872955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852014124393463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8545201420784</t>
   </si>
   <si>
     <t xml:space="preserve">0.812755405902863</t>
   </si>
   <si>
-    <t xml:space="preserve">0.80774337053299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.813172698020935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828626155853271</t>
+    <t xml:space="preserve">0.8077432513237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81317275762558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828626096248627</t>
   </si>
   <si>
     <t xml:space="preserve">0.832802534103394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.8206906914711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.749689340591431</t>
+    <t xml:space="preserve">0.820690810680389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.749689400196075</t>
   </si>
   <si>
     <t xml:space="preserve">0.710846960544586</t>
   </si>
   <si>
-    <t xml:space="preserve">0.654464364051819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.63399875164032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.645275950431824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.660311102867126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.684534668922424</t>
+    <t xml:space="preserve">0.654464304447174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.633998811244965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.645275831222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.660311043262482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.684534728527069</t>
   </si>
   <si>
     <t xml:space="preserve">0.68912935256958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.753030061721802</t>
+    <t xml:space="preserve">0.753030180931091</t>
   </si>
   <si>
     <t xml:space="preserve">0.784354448318481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.787696063518524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803148746490479</t>
+    <t xml:space="preserve">0.787696123123169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803148686885834</t>
   </si>
   <si>
     <t xml:space="preserve">0.856191396713257</t>
@@ -2894,16 +2894,16 @@
     <t xml:space="preserve">0.900462329387665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.889603435993195</t>
+    <t xml:space="preserve">0.889603495597839</t>
   </si>
   <si>
     <t xml:space="preserve">0.887097477912903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.89043915271759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88125067949295</t>
+    <t xml:space="preserve">0.89043927192688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.881250739097595</t>
   </si>
   <si>
     <t xml:space="preserve">0.904638826847076</t>
@@ -2912,31 +2912,31 @@
     <t xml:space="preserve">0.892944276332855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.902132749557495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882085382938385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867885053157806</t>
+    <t xml:space="preserve">0.90213280916214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882085502147675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867884993553162</t>
   </si>
   <si>
     <t xml:space="preserve">0.841155350208282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.839485049247742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841991007328033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840320646762848</t>
+    <t xml:space="preserve">0.839484930038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841990947723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840320587158203</t>
   </si>
   <si>
     <t xml:space="preserve">0.859532177448273</t>
   </si>
   <si>
-    <t xml:space="preserve">0.905474424362183</t>
+    <t xml:space="preserve">0.905474364757538</t>
   </si>
   <si>
     <t xml:space="preserve">0.849508225917816</t>
@@ -2945,67 +2945,67 @@
     <t xml:space="preserve">0.872897028923035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.906310081481934</t>
+    <t xml:space="preserve">0.906310021877289</t>
   </si>
   <si>
     <t xml:space="preserve">0.943898379802704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.953922390937805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957263290882111</t>
+    <t xml:space="preserve">0.95392245054245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957263171672821</t>
   </si>
   <si>
     <t xml:space="preserve">0.965616941452026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978146255016327</t>
+    <t xml:space="preserve">0.978146016597748</t>
   </si>
   <si>
     <t xml:space="preserve">0.961439669132233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.934710085391998</t>
+    <t xml:space="preserve">0.934710144996643</t>
   </si>
   <si>
     <t xml:space="preserve">0.902968347072601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.87456738948822</t>
+    <t xml:space="preserve">0.874567449092865</t>
   </si>
   <si>
     <t xml:space="preserve">0.852849781513214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.867050290107727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.878744721412659</t>
+    <t xml:space="preserve">0.867050230503082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.878744661808014</t>
   </si>
   <si>
     <t xml:space="preserve">0.907144784927368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.931369245052338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921345114707947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927191972732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912992358207703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947240114212036</t>
+    <t xml:space="preserve">0.931369304656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921345174312592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927191913127899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912992417812347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947240054607391</t>
   </si>
   <si>
     <t xml:space="preserve">0.899626731872559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.92969799041748</t>
+    <t xml:space="preserve">0.929697930812836</t>
   </si>
   <si>
     <t xml:space="preserve">0.938886404037476</t>
@@ -3020,13 +3020,13 @@
     <t xml:space="preserve">0.941392481327057</t>
   </si>
   <si>
-    <t xml:space="preserve">0.94640451669693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93554562330246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975640118122101</t>
+    <t xml:space="preserve">0.946404635906219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.935545742511749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975640058517456</t>
   </si>
   <si>
     <t xml:space="preserve">1.14687860012054</t>
@@ -3038,10 +3038,10 @@
     <t xml:space="preserve">1.17360830307007</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16024339199066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15773737430573</t>
+    <t xml:space="preserve">1.16024351119995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15773749351501</t>
   </si>
   <si>
     <t xml:space="preserve">1.17193794250488</t>
@@ -3050,7 +3050,7 @@
     <t xml:space="preserve">1.1385258436203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10928928852081</t>
+    <t xml:space="preserve">1.1092894077301</t>
   </si>
   <si>
     <t xml:space="preserve">1.11096060276031</t>
@@ -3062,19 +3062,19 @@
     <t xml:space="preserve">1.11179530620575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13100755214691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12098383903503</t>
+    <t xml:space="preserve">1.13100779056549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12098371982574</t>
   </si>
   <si>
     <t xml:space="preserve">1.16358518600464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14520835876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11513698101044</t>
+    <t xml:space="preserve">1.14520823955536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11513686180115</t>
   </si>
   <si>
     <t xml:space="preserve">1.10761892795563</t>
@@ -3083,16 +3083,16 @@
     <t xml:space="preserve">1.37742400169373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37241196632385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43923699855804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43673086166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44007170200348</t>
+    <t xml:space="preserve">1.37241184711456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43923687934875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43673098087311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44007182121277</t>
   </si>
   <si>
     <t xml:space="preserve">1.40665972232819</t>
@@ -3101,61 +3101,61 @@
     <t xml:space="preserve">1.41167175769806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3974711894989</t>
+    <t xml:space="preserve">1.39747130870819</t>
   </si>
   <si>
     <t xml:space="preserve">1.43840134143829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47682535648346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45928430557251</t>
+    <t xml:space="preserve">1.47682547569275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45928418636322</t>
   </si>
   <si>
     <t xml:space="preserve">1.44090735912323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43338930606842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48100197315216</t>
+    <t xml:space="preserve">1.43338942527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48100185394287</t>
   </si>
   <si>
     <t xml:space="preserve">1.41334211826324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42587125301361</t>
+    <t xml:space="preserve">1.4258713722229</t>
   </si>
   <si>
     <t xml:space="preserve">1.5879213809967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.550332903862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62634539604187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61214590072632</t>
+    <t xml:space="preserve">1.55033278465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62634551525116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61214601993561</t>
   </si>
   <si>
     <t xml:space="preserve">1.62049877643585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61966288089752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62718105316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61381614208221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45677816867828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39830696582794</t>
+    <t xml:space="preserve">1.61966300010681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62718093395233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6138162612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45677828788757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39830708503723</t>
   </si>
   <si>
     <t xml:space="preserve">1.34317636489868</t>
@@ -3170,13 +3170,13 @@
     <t xml:space="preserve">1.36489391326904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40276598930359</t>
+    <t xml:space="preserve">1.40276575088501</t>
   </si>
   <si>
     <t xml:space="preserve">1.43466711044312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41251361370087</t>
+    <t xml:space="preserve">1.41251349449158</t>
   </si>
   <si>
     <t xml:space="preserve">1.39390444755554</t>
@@ -3185,55 +3185,55 @@
     <t xml:space="preserve">1.39213228225708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33364653587341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44795918464661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49049425125122</t>
+    <t xml:space="preserve">1.3336466550827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4479593038559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49049437046051</t>
   </si>
   <si>
     <t xml:space="preserve">1.51796472072601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53214299678802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58442544937134</t>
+    <t xml:space="preserve">1.53214287757874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58442533016205</t>
   </si>
   <si>
     <t xml:space="preserve">1.52859854698181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54897975921631</t>
+    <t xml:space="preserve">1.5489798784256</t>
   </si>
   <si>
     <t xml:space="preserve">1.54454898834229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53834581375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55872738361359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57645034790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61455428600311</t>
+    <t xml:space="preserve">1.53834593296051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5587272644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5764502286911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6145544052124</t>
   </si>
   <si>
     <t xml:space="preserve">1.60657906532288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56936097145081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58885622024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6039205789566</t>
+    <t xml:space="preserve">1.5693610906601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58885610103607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60392069816589</t>
   </si>
   <si>
     <t xml:space="preserve">1.63582181930542</t>
@@ -3254,13 +3254,13 @@
     <t xml:space="preserve">1.520623087883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49315273761749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49758350849152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52505373954773</t>
+    <t xml:space="preserve">1.4931526184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49758338928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52505385875702</t>
   </si>
   <si>
     <t xml:space="preserve">1.50733089447021</t>
@@ -3269,31 +3269,31 @@
     <t xml:space="preserve">1.50112795829773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54011821746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53037059307098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55341053009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63848030567169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66329228878021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56404423713684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51707851886749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48872196674347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46568214893341</t>
+    <t xml:space="preserve">1.54011833667755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53037071228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55341041088104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63848006725311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6632924079895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56404411792755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5170783996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48872184753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4656822681427</t>
   </si>
   <si>
     <t xml:space="preserve">1.42403340339661</t>
@@ -3302,58 +3302,58 @@
     <t xml:space="preserve">1.44707322120667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46656835079193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61809909343719</t>
+    <t xml:space="preserve">1.46656823158264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61809885501862</t>
   </si>
   <si>
     <t xml:space="preserve">1.82900106906891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84672427177429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90520989894867</t>
+    <t xml:space="preserve">1.84672403335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90520942211151</t>
   </si>
   <si>
     <t xml:space="preserve">1.89634835720062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98319017887115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03635907173157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09130001068115</t>
+    <t xml:space="preserve">1.98319029808044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03635931015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09129977226257</t>
   </si>
   <si>
     <t xml:space="preserve">2.17105293273926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96015024185181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88925898075104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96192276477814</t>
+    <t xml:space="preserve">1.96015071868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88925909996033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96192288398743</t>
   </si>
   <si>
     <t xml:space="preserve">1.94597220420837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01863622665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10902285575867</t>
+    <t xml:space="preserve">2.01863646507263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10902261734009</t>
   </si>
   <si>
     <t xml:space="preserve">2.0753493309021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10547828674316</t>
+    <t xml:space="preserve">2.10547780990601</t>
   </si>
   <si>
     <t xml:space="preserve">2.13737940788269</t>
@@ -3365,10 +3365,10 @@
     <t xml:space="preserve">2.17814183235168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16396379470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17636942863464</t>
+    <t xml:space="preserve">2.16396355628967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17636966705322</t>
   </si>
   <si>
     <t xml:space="preserve">2.18168640136719</t>
@@ -3380,16 +3380,16 @@
     <t xml:space="preserve">2.1799144744873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1232008934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14624071121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19763731956482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30574655532837</t>
+    <t xml:space="preserve">2.12320113182068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14624047279358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19763708114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30574679374695</t>
   </si>
   <si>
     <t xml:space="preserve">2.28625154495239</t>
@@ -3407,16 +3407,16 @@
     <t xml:space="preserve">2.4457573890686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38372755050659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4634804725647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42448997497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47411394119263</t>
+    <t xml:space="preserve">2.38372778892517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46348023414612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42449021339417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47411417961121</t>
   </si>
   <si>
     <t xml:space="preserve">2.51310443878174</t>
@@ -3428,16 +3428,16 @@
     <t xml:space="preserve">2.43157911300659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47056937217712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39613342285156</t>
+    <t xml:space="preserve">2.4705696105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39613366127014</t>
   </si>
   <si>
     <t xml:space="preserve">2.33942031860352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37841057777405</t>
+    <t xml:space="preserve">2.37841033935547</t>
   </si>
   <si>
     <t xml:space="preserve">2.21004295349121</t>
@@ -3446,13 +3446,13 @@
     <t xml:space="preserve">2.38904428482056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47943091392517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49183702468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56095623970032</t>
+    <t xml:space="preserve">2.47943115234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4918372631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56095600128174</t>
   </si>
   <si>
     <t xml:space="preserve">2.6566596031189</t>
@@ -3461,28 +3461,28 @@
     <t xml:space="preserve">2.64070916175842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63184762001038</t>
+    <t xml:space="preserve">2.63184785842896</t>
   </si>
   <si>
     <t xml:space="preserve">2.65311503410339</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59640216827393</t>
+    <t xml:space="preserve">2.59640192985535</t>
   </si>
   <si>
     <t xml:space="preserve">2.52373814582825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33233118057251</t>
+    <t xml:space="preserve">2.33233094215393</t>
   </si>
   <si>
     <t xml:space="preserve">2.31815266609192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2968852519989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28270673751831</t>
+    <t xml:space="preserve">2.29688501358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28270721435547</t>
   </si>
   <si>
     <t xml:space="preserve">2.27561783790588</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">2.30929112434387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27916264533997</t>
+    <t xml:space="preserve">2.27916216850281</t>
   </si>
   <si>
     <t xml:space="preserve">2.28802394866943</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">2.14978551864624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16041898727417</t>
+    <t xml:space="preserve">2.16041922569275</t>
   </si>
   <si>
     <t xml:space="preserve">2.17459726333618</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">2.13915181159973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15687417984009</t>
+    <t xml:space="preserve">2.15687441825867</t>
   </si>
   <si>
     <t xml:space="preserve">2.05762648582458</t>
@@ -3536,46 +3536,46 @@
     <t xml:space="preserve">2.1958646774292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13560748100281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39258885383606</t>
+    <t xml:space="preserve">2.13560700416565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39258861541748</t>
   </si>
   <si>
     <t xml:space="preserve">2.39436101913452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06648802757263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99382376670837</t>
+    <t xml:space="preserve">2.06648778915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99382388591766</t>
   </si>
   <si>
     <t xml:space="preserve">2.12142872810364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11965680122375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09484434127808</t>
+    <t xml:space="preserve">2.11965656280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09484457969666</t>
   </si>
   <si>
     <t xml:space="preserve">2.01331901550293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08066606521606</t>
+    <t xml:space="preserve">2.08066630363464</t>
   </si>
   <si>
     <t xml:space="preserve">1.9920517206192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03458666801453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02926969528198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93179416656494</t>
+    <t xml:space="preserve">2.03458690643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0292694568634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93179404735565</t>
   </si>
   <si>
     <t xml:space="preserve">2.01509141921997</t>
@@ -3587,49 +3587,49 @@
     <t xml:space="preserve">1.86799156665802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9016649723053</t>
+    <t xml:space="preserve">1.90166485309601</t>
   </si>
   <si>
     <t xml:space="preserve">1.80596160888672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64556932449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56315815448761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56847500801086</t>
+    <t xml:space="preserve">1.6455694437027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56315803527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56847476959229</t>
   </si>
   <si>
     <t xml:space="preserve">1.6801290512085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57999467849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59505915641785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.659747838974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78646647930145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75545132160187</t>
+    <t xml:space="preserve">1.57999491691589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59505927562714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65974771976471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78646636009216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75545144081116</t>
   </si>
   <si>
     <t xml:space="preserve">1.73684227466583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73418390750885</t>
+    <t xml:space="preserve">1.73418378829956</t>
   </si>
   <si>
     <t xml:space="preserve">1.70671331882477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65088641643524</t>
+    <t xml:space="preserve">1.65088629722595</t>
   </si>
   <si>
     <t xml:space="preserve">1.66595077514648</t>
@@ -3638,22 +3638,22 @@
     <t xml:space="preserve">1.67924284934998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72798073291779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86444699764252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83431828022003</t>
+    <t xml:space="preserve">1.72798085212708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86444711685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83431804180145</t>
   </si>
   <si>
     <t xml:space="preserve">1.74570369720459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78469395637512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76254045963287</t>
+    <t xml:space="preserve">1.78469407558441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76254034042358</t>
   </si>
   <si>
     <t xml:space="preserve">1.72886693477631</t>
@@ -3662,7 +3662,7 @@
     <t xml:space="preserve">1.67038142681122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64113867282867</t>
+    <t xml:space="preserve">1.64113879203796</t>
   </si>
   <si>
     <t xml:space="preserve">1.60126233100891</t>
@@ -3674,7 +3674,7 @@
     <t xml:space="preserve">1.71025788784027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70051050186157</t>
+    <t xml:space="preserve">1.70051038265228</t>
   </si>
   <si>
     <t xml:space="preserve">1.67835676670074</t>
@@ -3683,31 +3683,31 @@
     <t xml:space="preserve">1.62961876392365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63936638832092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63050508499146</t>
+    <t xml:space="preserve">1.63936650753021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63050496578217</t>
   </si>
   <si>
     <t xml:space="preserve">1.60923755168915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62075746059418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55075216293335</t>
+    <t xml:space="preserve">1.62075734138489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55075204372406</t>
   </si>
   <si>
     <t xml:space="preserve">1.46302378177643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47897446155548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5418906211853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60835158824921</t>
+    <t xml:space="preserve">1.47897434234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54189074039459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60835134983063</t>
   </si>
   <si>
     <t xml:space="preserve">1.58974242210388</t>
@@ -3719,13 +3719,13 @@
     <t xml:space="preserve">1.6074652671814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60037612915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52593994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52150917053223</t>
+    <t xml:space="preserve">1.6003760099411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52594006061554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52150928974152</t>
   </si>
   <si>
     <t xml:space="preserve">1.6313910484314</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">1.690762758255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71646106243134</t>
+    <t xml:space="preserve">1.71646094322205</t>
   </si>
   <si>
     <t xml:space="preserve">1.78114938735962</t>
@@ -3749,28 +3749,28 @@
     <t xml:space="preserve">1.84495174884796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80773365497589</t>
+    <t xml:space="preserve">1.80773389339447</t>
   </si>
   <si>
     <t xml:space="preserve">1.79887235164642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79532778263092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65797555446625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45593452453613</t>
+    <t xml:space="preserve">1.79532790184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65797543525696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45593464374542</t>
   </si>
   <si>
     <t xml:space="preserve">1.41871654987335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46506786346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47688281536102</t>
+    <t xml:space="preserve">1.46506798267365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4768830537796</t>
   </si>
   <si>
     <t xml:space="preserve">1.48960697650909</t>
@@ -3779,22 +3779,22 @@
     <t xml:space="preserve">1.45779705047607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47597420215607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43689334392548</t>
+    <t xml:space="preserve">1.47597408294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43689346313477</t>
   </si>
   <si>
     <t xml:space="preserve">1.47415637969971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48142719268799</t>
+    <t xml:space="preserve">1.48142731189728</t>
   </si>
   <si>
     <t xml:space="preserve">1.41417229175568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37236499786377</t>
+    <t xml:space="preserve">1.37236511707306</t>
   </si>
   <si>
     <t xml:space="preserve">1.37872707843781</t>
@@ -3809,55 +3809,55 @@
     <t xml:space="preserve">1.37418282032013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40781044960022</t>
+    <t xml:space="preserve">1.40781033039093</t>
   </si>
   <si>
     <t xml:space="preserve">1.38599789142609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31510746479034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28420674800873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27966237068176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30874562263489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3269225358963</t>
+    <t xml:space="preserve">1.31510758399963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28420650959015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27966225147247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30874574184418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32692265510559</t>
   </si>
   <si>
     <t xml:space="preserve">1.39781296253204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37145614624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35782337188721</t>
+    <t xml:space="preserve">1.37145626544952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3578234910965</t>
   </si>
   <si>
     <t xml:space="preserve">1.35691475868225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29693055152893</t>
+    <t xml:space="preserve">1.29693043231964</t>
   </si>
   <si>
     <t xml:space="preserve">1.31328976154327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33328461647034</t>
+    <t xml:space="preserve">1.33328449726105</t>
   </si>
   <si>
     <t xml:space="preserve">1.41962540149689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42689621448517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40144848823547</t>
+    <t xml:space="preserve">1.42689633369446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40144836902618</t>
   </si>
   <si>
     <t xml:space="preserve">1.44416439533234</t>
@@ -3872,64 +3872,64 @@
     <t xml:space="preserve">1.48778915405273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49505996704102</t>
+    <t xml:space="preserve">1.49506008625031</t>
   </si>
   <si>
     <t xml:space="preserve">1.48869812488556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51596367359161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5050573348999</t>
+    <t xml:space="preserve">1.51596355438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50505745410919</t>
   </si>
   <si>
     <t xml:space="preserve">1.50051307678223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48051846027374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40326619148254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43234920501709</t>
+    <t xml:space="preserve">1.48051834106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40326607227325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43234932422638</t>
   </si>
   <si>
     <t xml:space="preserve">1.41144573688507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34691739082336</t>
+    <t xml:space="preserve">1.34691727161407</t>
   </si>
   <si>
     <t xml:space="preserve">1.34328198432922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37327408790588</t>
+    <t xml:space="preserve">1.3732738494873</t>
   </si>
   <si>
     <t xml:space="preserve">1.3760005235672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36236763000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39235973358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33601117134094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35237050056458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36963844299316</t>
+    <t xml:space="preserve">1.36236774921417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39235985279083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33601105213165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35237038135529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36963856220245</t>
   </si>
   <si>
     <t xml:space="preserve">1.35964119434357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41326332092285</t>
+    <t xml:space="preserve">1.41326344013214</t>
   </si>
   <si>
     <t xml:space="preserve">1.43507587909698</t>
@@ -3947,13 +3947,13 @@
     <t xml:space="preserve">1.39872181415558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70591342449188</t>
+    <t xml:space="preserve">1.70591354370117</t>
   </si>
   <si>
     <t xml:space="preserve">1.6859188079834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58412730693817</t>
+    <t xml:space="preserve">1.58412742614746</t>
   </si>
   <si>
     <t xml:space="preserve">1.57867431640625</t>
@@ -3962,13 +3962,13 @@
     <t xml:space="preserve">1.59139823913574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56322395801544</t>
+    <t xml:space="preserve">1.56322383880615</t>
   </si>
   <si>
     <t xml:space="preserve">1.49960422515869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55777084827423</t>
+    <t xml:space="preserve">1.55777072906494</t>
   </si>
   <si>
     <t xml:space="preserve">1.55231761932373</t>
@@ -3989,10 +3989,10 @@
     <t xml:space="preserve">1.56049728393555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53323173522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59503364562988</t>
+    <t xml:space="preserve">1.53323185443878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59503352642059</t>
   </si>
   <si>
     <t xml:space="preserve">1.59412467479706</t>
@@ -4001,7 +4001,7 @@
     <t xml:space="preserve">1.64047610759735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65774440765381</t>
+    <t xml:space="preserve">1.65774428844452</t>
   </si>
   <si>
     <t xml:space="preserve">1.65865325927734</t>
@@ -4013,7 +4013,7 @@
     <t xml:space="preserve">1.6704683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76317119598389</t>
+    <t xml:space="preserve">1.7631710767746</t>
   </si>
   <si>
     <t xml:space="preserve">1.79225432872772</t>
@@ -4022,7 +4022,7 @@
     <t xml:space="preserve">1.78861904144287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73045253753662</t>
+    <t xml:space="preserve">1.73045241832733</t>
   </si>
   <si>
     <t xml:space="preserve">1.71772849559784</t>
@@ -4037,7 +4037,7 @@
     <t xml:space="preserve">1.73136126995087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75135612487793</t>
+    <t xml:space="preserve">1.75135600566864</t>
   </si>
   <si>
     <t xml:space="preserve">1.78771007061005</t>
@@ -4046,16 +4046,16 @@
     <t xml:space="preserve">1.84860301017761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86678004264832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87223315238953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89949870109558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9340353012085</t>
+    <t xml:space="preserve">1.8667801618576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87223327159882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89949882030487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93403518199921</t>
   </si>
   <si>
     <t xml:space="preserve">1.94494140148163</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">1.90676963329315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95403003692627</t>
+    <t xml:space="preserve">1.9540296792984</t>
   </si>
   <si>
     <t xml:space="preserve">1.97038900852203</t>
@@ -4073,13 +4073,13 @@
     <t xml:space="preserve">2.00492548942566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99583697319031</t>
+    <t xml:space="preserve">1.99583685398102</t>
   </si>
   <si>
     <t xml:space="preserve">1.97220683097839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97402453422546</t>
+    <t xml:space="preserve">1.97402465343475</t>
   </si>
   <si>
     <t xml:space="preserve">1.99038398265839</t>
@@ -4094,73 +4094,73 @@
     <t xml:space="preserve">2.15397691726685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12307620048523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11944103240967</t>
+    <t xml:space="preserve">2.12307596206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11944079399109</t>
   </si>
   <si>
     <t xml:space="preserve">2.13761782646179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16851854324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11035227775574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10308122634888</t>
+    <t xml:space="preserve">2.16851878166199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11035203933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10308146476746</t>
   </si>
   <si>
     <t xml:space="preserve">2.10126399993896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97584211826324</t>
+    <t xml:space="preserve">1.97584235668182</t>
   </si>
   <si>
     <t xml:space="preserve">2.02128481864929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85223853588104</t>
+    <t xml:space="preserve">1.85223865509033</t>
   </si>
   <si>
     <t xml:space="preserve">1.89041018486023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91222274303436</t>
+    <t xml:space="preserve">1.91222286224365</t>
   </si>
   <si>
     <t xml:space="preserve">1.92676424980164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93585288524628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93948829174042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90131640434265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91404032707214</t>
+    <t xml:space="preserve">1.93585300445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93948817253113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90131664276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91404044628143</t>
   </si>
   <si>
     <t xml:space="preserve">1.96311855316162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96857142448425</t>
+    <t xml:space="preserve">1.96857130527496</t>
   </si>
   <si>
     <t xml:space="preserve">2.03219103813171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05945682525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10489892959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12852954864502</t>
+    <t xml:space="preserve">2.05945658683777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10489916801453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12852907180786</t>
   </si>
   <si>
     <t xml:space="preserve">2.12671136856079</t>
@@ -4175,7 +4175,7 @@
     <t xml:space="preserve">2.07218050956726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06309199333191</t>
+    <t xml:space="preserve">2.06309175491333</t>
   </si>
   <si>
     <t xml:space="preserve">2.03764414787292</t>
@@ -4190,10 +4190,10 @@
     <t xml:space="preserve">2.01764941215515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00128984451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27394580841064</t>
+    <t xml:space="preserve">2.00129008293152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27394556999207</t>
   </si>
   <si>
     <t xml:space="preserve">2.2484974861145</t>
@@ -4205,16 +4205,16 @@
     <t xml:space="preserve">2.30848169326782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33211183547974</t>
+    <t xml:space="preserve">2.33211159706116</t>
   </si>
   <si>
     <t xml:space="preserve">2.37210130691528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41572594642639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.375736951828</t>
+    <t xml:space="preserve">2.41572618484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37573671340942</t>
   </si>
   <si>
     <t xml:space="preserve">2.40845561027527</t>
@@ -4226,13 +4226,13 @@
     <t xml:space="preserve">2.38846063613892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39209604263306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3575599193573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34483575820923</t>
+    <t xml:space="preserve">2.39209580421448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35755968093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34483551979065</t>
   </si>
   <si>
     <t xml:space="preserve">2.30666422843933</t>
@@ -4241,7 +4241,7 @@
     <t xml:space="preserve">2.3157525062561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3357470035553</t>
+    <t xml:space="preserve">2.33574724197388</t>
   </si>
   <si>
     <t xml:space="preserve">2.33938264846802</t>
@@ -4250,7 +4250,7 @@
     <t xml:space="preserve">2.38118982315063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40663743019104</t>
+    <t xml:space="preserve">2.40663766860962</t>
   </si>
   <si>
     <t xml:space="preserve">2.40481972694397</t>
@@ -4259,34 +4259,34 @@
     <t xml:space="preserve">2.39027833938599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37937188148499</t>
+    <t xml:space="preserve">2.37937211990356</t>
   </si>
   <si>
     <t xml:space="preserve">2.32302331924438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28666925430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18487787246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23213839530945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18306040763855</t>
+    <t xml:space="preserve">2.28666949272156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18487811088562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23213815689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18306016921997</t>
   </si>
   <si>
     <t xml:space="preserve">2.143070936203</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20487260818481</t>
+    <t xml:space="preserve">2.20487284660339</t>
   </si>
   <si>
     <t xml:space="preserve">2.20669031143188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17033624649048</t>
+    <t xml:space="preserve">2.17033648490906</t>
   </si>
   <si>
     <t xml:space="preserve">2.13943552970886</t>
@@ -4295,70 +4295,70 @@
     <t xml:space="preserve">2.14670634269714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14852380752563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19578385353088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19033122062683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26849246025085</t>
+    <t xml:space="preserve">2.14852404594421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19578409194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19033098220825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26849222183228</t>
   </si>
   <si>
     <t xml:space="preserve">2.24667978286743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24304437637329</t>
+    <t xml:space="preserve">2.24304461479187</t>
   </si>
   <si>
     <t xml:space="preserve">2.25213289260864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30121111869812</t>
+    <t xml:space="preserve">2.30121088027954</t>
   </si>
   <si>
     <t xml:space="preserve">2.28303408622742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34120011329651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47934556007385</t>
+    <t xml:space="preserve">2.34120059013367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47934579849243</t>
   </si>
   <si>
     <t xml:space="preserve">2.44844484329224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48843431472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46843957901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47207498550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45935082435608</t>
+    <t xml:space="preserve">2.4884340763092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46843934059143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47207474708557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45935106277466</t>
   </si>
   <si>
     <t xml:space="preserve">2.45753335952759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43390321731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51388192176819</t>
+    <t xml:space="preserve">2.43390297889709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51388216018677</t>
   </si>
   <si>
     <t xml:space="preserve">2.46480393409729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50297594070435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4702570438385</t>
+    <t xml:space="preserve">2.50297570228577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47025680541992</t>
   </si>
   <si>
     <t xml:space="preserve">2.40118432044983</t>
@@ -4373,25 +4373,25 @@
     <t xml:space="preserve">2.2793984413147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28485131263733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29212260246277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27030968666077</t>
+    <t xml:space="preserve">2.28485155105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29212236404419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27031016349792</t>
   </si>
   <si>
     <t xml:space="preserve">2.22668528556824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30302858352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32484102249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33029413223267</t>
+    <t xml:space="preserve">2.30302834510803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32484126091003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33029389381409</t>
   </si>
   <si>
     <t xml:space="preserve">2.29939317703247</t>
@@ -4409,22 +4409,22 @@
     <t xml:space="preserve">2.43935632705688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25599455833435</t>
+    <t xml:space="preserve">2.25599431991577</t>
   </si>
   <si>
     <t xml:space="preserve">2.28207540512085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27462387084961</t>
+    <t xml:space="preserve">2.27462339401245</t>
   </si>
   <si>
     <t xml:space="preserve">2.24854278564453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22991347312927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30070447921753</t>
+    <t xml:space="preserve">2.22991371154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30070471763611</t>
   </si>
   <si>
     <t xml:space="preserve">2.31188225746155</t>
@@ -4436,19 +4436,19 @@
     <t xml:space="preserve">2.40130209922791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36404371261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29697871208191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32678508758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34168839454651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33982610702515</t>
+    <t xml:space="preserve">2.36404395103455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29697895050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32678556442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34168863296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33982586860657</t>
   </si>
   <si>
     <t xml:space="preserve">2.36963248252869</t>
@@ -4457,49 +4457,49 @@
     <t xml:space="preserve">2.36776971817017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32864832878113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29884147644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28580093383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28021216392517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29511570930481</t>
+    <t xml:space="preserve">2.32864856719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29884171485901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28580117225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28021240234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29511594772339</t>
   </si>
   <si>
     <t xml:space="preserve">2.30443024635315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29325294494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33051156997681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31374478340149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28952693939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22432470321655</t>
+    <t xml:space="preserve">2.29325270652771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33051133155823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31374502182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28952670097351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22432494163513</t>
   </si>
   <si>
     <t xml:space="preserve">2.20569562911987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16098570823669</t>
+    <t xml:space="preserve">2.16098546981812</t>
   </si>
   <si>
     <t xml:space="preserve">2.14049363136292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10696077346802</t>
+    <t xml:space="preserve">2.1069610118866</t>
   </si>
   <si>
     <t xml:space="preserve">2.09950923919678</t>
@@ -4520,19 +4520,19 @@
     <t xml:space="preserve">2.04362177848816</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04921078681946</t>
+    <t xml:space="preserve">2.04921054840088</t>
   </si>
   <si>
     <t xml:space="preserve">2.08460593223572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06411409378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05107307434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04175853729248</t>
+    <t xml:space="preserve">2.06411385536194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0510733127594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04175877571106</t>
   </si>
   <si>
     <t xml:space="preserve">2.09205770492554</t>
@@ -4541,25 +4541,25 @@
     <t xml:space="preserve">2.15912270545959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15353393554688</t>
+    <t xml:space="preserve">2.15353417396545</t>
   </si>
   <si>
     <t xml:space="preserve">2.13863062858582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12186431884766</t>
+    <t xml:space="preserve">2.12186455726624</t>
   </si>
   <si>
     <t xml:space="preserve">2.06970238685608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0231294631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01754093170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99891149997711</t>
+    <t xml:space="preserve">2.02312970161438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01754069328308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9989116191864</t>
   </si>
   <si>
     <t xml:space="preserve">2.01195240020752</t>
@@ -4568,16 +4568,16 @@
     <t xml:space="preserve">2.0007746219635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99332296848297</t>
+    <t xml:space="preserve">1.99332308769226</t>
   </si>
   <si>
     <t xml:space="preserve">1.97469365596771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95606458187103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92625796794891</t>
+    <t xml:space="preserve">1.95606446266174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92625784873962</t>
   </si>
   <si>
     <t xml:space="preserve">1.86478161811829</t>
@@ -4586,10 +4586,10 @@
     <t xml:space="preserve">1.77349853515625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78095006942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78467619419098</t>
+    <t xml:space="preserve">1.78095018863678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78467607498169</t>
   </si>
   <si>
     <t xml:space="preserve">1.80330526828766</t>
@@ -4598,40 +4598,40 @@
     <t xml:space="preserve">1.83311200141907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80237376689911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75673234462738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71109068393707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70829629898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71947395801544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67196953296661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69991338253021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66638076305389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61608195304871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63005387783051</t>
+    <t xml:space="preserve">1.80237364768982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75673222541809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71109080314636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70829641819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71947383880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67196941375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69991326332092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6663806438446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61608183383942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63005375862122</t>
   </si>
   <si>
     <t xml:space="preserve">1.63377952575684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63564252853394</t>
+    <t xml:space="preserve">1.63564264774323</t>
   </si>
   <si>
     <t xml:space="preserve">1.64775156974792</t>
@@ -4646,22 +4646,22 @@
     <t xml:space="preserve">1.54994833469391</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53877079486847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54529106616974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54249656200409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55087983608246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55646848678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56485164165497</t>
+    <t xml:space="preserve">1.53877067565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54529094696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54249668121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55087971687317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55646860599518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56485152244568</t>
   </si>
   <si>
     <t xml:space="preserve">1.57975494861603</t>
@@ -4673,25 +4673,25 @@
     <t xml:space="preserve">1.60117852687836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60956180095673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61980772018433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6281909942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59745287895203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61235594749451</t>
+    <t xml:space="preserve">1.60956168174744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61980783939362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62819087505341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59745275974274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6123560667038</t>
   </si>
   <si>
     <t xml:space="preserve">1.62073934078217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67755818367004</t>
+    <t xml:space="preserve">1.67755830287933</t>
   </si>
   <si>
     <t xml:space="preserve">1.64123129844666</t>
@@ -4703,13 +4703,13 @@
     <t xml:space="preserve">1.68966722488403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69153010845184</t>
+    <t xml:space="preserve">1.69153022766113</t>
   </si>
   <si>
     <t xml:space="preserve">1.66917514801025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66824352741241</t>
+    <t xml:space="preserve">1.6682436466217</t>
   </si>
   <si>
     <t xml:space="preserve">1.67662680149078</t>
@@ -4721,7 +4721,7 @@
     <t xml:space="preserve">1.72785711288452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84242653846741</t>
+    <t xml:space="preserve">1.84242641925812</t>
   </si>
   <si>
     <t xml:space="preserve">1.84801530838013</t>
@@ -4730,19 +4730,19 @@
     <t xml:space="preserve">1.90390276908875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92998361587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97655665874481</t>
+    <t xml:space="preserve">1.92998373508453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97655689716339</t>
   </si>
   <si>
     <t xml:space="preserve">1.96165335178375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91508042812347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93557262420654</t>
+    <t xml:space="preserve">1.91508030891418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93557250499725</t>
   </si>
   <si>
     <t xml:space="preserve">1.90949153900146</t>
@@ -4757,13 +4757,13 @@
     <t xml:space="preserve">1.99704885482788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09764623641968</t>
+    <t xml:space="preserve">2.09764647483826</t>
   </si>
   <si>
     <t xml:space="preserve">2.09392046928406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1106870174408</t>
+    <t xml:space="preserve">2.11068677902222</t>
   </si>
   <si>
     <t xml:space="preserve">2.08646893501282</t>
@@ -4772,34 +4772,34 @@
     <t xml:space="preserve">2.12000155448914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11441278457642</t>
+    <t xml:space="preserve">2.11441254615784</t>
   </si>
   <si>
     <t xml:space="preserve">2.10137224197388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03617024421692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00263786315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98028242588043</t>
+    <t xml:space="preserve">2.03617000579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00263738632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98028254508972</t>
   </si>
   <si>
     <t xml:space="preserve">2.01008915901184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01567792892456</t>
+    <t xml:space="preserve">2.01567816734314</t>
   </si>
   <si>
     <t xml:space="preserve">1.98214554786682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90017688274384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91694331169128</t>
+    <t xml:space="preserve">1.90017700195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91694343090057</t>
   </si>
   <si>
     <t xml:space="preserve">1.8927253484726</t>
@@ -4811,7 +4811,7 @@
     <t xml:space="preserve">1.95420169830322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06783986091614</t>
+    <t xml:space="preserve">2.06783962249756</t>
   </si>
   <si>
     <t xml:space="preserve">2.03989601135254</t>
@@ -4826,7 +4826,7 @@
     <t xml:space="preserve">2.11813831329346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07715439796448</t>
+    <t xml:space="preserve">2.0771541595459</t>
   </si>
   <si>
     <t xml:space="preserve">2.08281922340393</t>
@@ -4838,7 +4838,7 @@
     <t xml:space="preserve">2.05827116966248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07148909568787</t>
+    <t xml:space="preserve">2.07148933410645</t>
   </si>
   <si>
     <t xml:space="preserve">2.12813878059387</t>
@@ -4859,7 +4859,7 @@
     <t xml:space="preserve">2.08093070983887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14135718345642</t>
+    <t xml:space="preserve">2.14135694503784</t>
   </si>
   <si>
     <t xml:space="preserve">2.10170245170593</t>
@@ -4871,7 +4871,7 @@
     <t xml:space="preserve">2.06771278381348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09981393814087</t>
+    <t xml:space="preserve">2.09981417655945</t>
   </si>
   <si>
     <t xml:space="preserve">2.15835213661194</t>
@@ -4901,13 +4901,13 @@
     <t xml:space="preserve">2.24143815040588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33396601676941</t>
+    <t xml:space="preserve">2.33396577835083</t>
   </si>
   <si>
     <t xml:space="preserve">2.32263612747192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22255492210388</t>
+    <t xml:space="preserve">2.22255516052246</t>
   </si>
   <si>
     <t xml:space="preserve">2.14702200889587</t>
@@ -4922,7 +4922,7 @@
     <t xml:space="preserve">2.09414911270142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04882955551147</t>
+    <t xml:space="preserve">2.0488293170929</t>
   </si>
   <si>
     <t xml:space="preserve">2.19989514350891</t>
@@ -4931,13 +4931,13 @@
     <t xml:space="preserve">2.2471034526825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31130599975586</t>
+    <t xml:space="preserve">2.31130623817444</t>
   </si>
   <si>
     <t xml:space="preserve">2.33207774162292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29431128501892</t>
+    <t xml:space="preserve">2.2943115234375</t>
   </si>
   <si>
     <t xml:space="preserve">2.35662579536438</t>
@@ -4955,13 +4955,13 @@
     <t xml:space="preserve">2.36040258407593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37550902366638</t>
+    <t xml:space="preserve">2.37550926208496</t>
   </si>
   <si>
     <t xml:space="preserve">2.41705203056335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46237182617188</t>
+    <t xml:space="preserve">2.46237206459045</t>
   </si>
   <si>
     <t xml:space="preserve">2.44160032272339</t>
@@ -4970,13 +4970,13 @@
     <t xml:space="preserve">2.46992492675781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48692035675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50202679634094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5265748500824</t>
+    <t xml:space="preserve">2.48692011833191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50202655792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52657508850098</t>
   </si>
   <si>
     <t xml:space="preserve">2.54168128967285</t>
@@ -4991,7 +4991,7 @@
     <t xml:space="preserve">2.50957989692688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5548996925354</t>
+    <t xml:space="preserve">2.55489993095398</t>
   </si>
   <si>
     <t xml:space="preserve">2.56811785697937</t>
@@ -5006,19 +5006,19 @@
     <t xml:space="preserve">2.70407724380493</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66442251205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64553928375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63798594474792</t>
+    <t xml:space="preserve">2.66442227363586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64553904533386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63798570632935</t>
   </si>
   <si>
     <t xml:space="preserve">2.63609766960144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70218873023987</t>
+    <t xml:space="preserve">2.70218896865845</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309238433838</t>
@@ -5039,7 +5039,7 @@
     <t xml:space="preserve">2.60210776329041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55867624282837</t>
+    <t xml:space="preserve">2.55867648124695</t>
   </si>
   <si>
     <t xml:space="preserve">2.60882019996643</t>
@@ -5910,6 +5910,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.38800001144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37200021743774</t>
   </si>
 </sst>
 </file>
@@ -71248,7 +71251,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.6911342593</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>230953</v>
@@ -71269,6 +71272,32 @@
         <v>1965</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.6910185185</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>309204</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>4.39599990844727</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>4.31599998474121</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>4.38199996948242</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>4.37200021743774</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>1966</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/OVS.MI.xlsx
+++ b/data/OVS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1967" uniqueCount="1967">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1968" uniqueCount="1968">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,40 +38,40 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03756427764893</t>
+    <t xml:space="preserve">5.03756332397461</t>
   </si>
   <si>
     <t xml:space="preserve">OVS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89862394332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76365327835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64456272125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71998643875122</t>
+    <t xml:space="preserve">4.89862489700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76365375518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64456224441528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71998739242554</t>
   </si>
   <si>
     <t xml:space="preserve">4.65647077560425</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78747177124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94229030609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69219923019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60486507415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6366229057312</t>
+    <t xml:space="preserve">4.78747224807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94228982925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69219827651978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6048641204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63662338256836</t>
   </si>
   <si>
     <t xml:space="preserve">4.616774559021</t>
@@ -86,16 +86,16 @@
     <t xml:space="preserve">4.53341007232666</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45798587799072</t>
+    <t xml:space="preserve">4.45798540115356</t>
   </si>
   <si>
     <t xml:space="preserve">4.47783422470093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49768304824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5135612487793</t>
+    <t xml:space="preserve">4.49768352508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51356172561646</t>
   </si>
   <si>
     <t xml:space="preserve">4.4460768699646</t>
@@ -110,10 +110,10 @@
     <t xml:space="preserve">4.51753187179565</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54531908035278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32698583602905</t>
+    <t xml:space="preserve">4.54531955718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32698535919189</t>
   </si>
   <si>
     <t xml:space="preserve">4.03322601318359</t>
@@ -122,73 +122,73 @@
     <t xml:space="preserve">4.02925682067871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2793493270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22377252578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38256072998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30316734313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.469895362854</t>
+    <t xml:space="preserve">4.27934837341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22377300262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38256120681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30316686630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46989488601685</t>
   </si>
   <si>
     <t xml:space="preserve">4.46592473983765</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48577451705933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48974275588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.271409034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23965167999268</t>
+    <t xml:space="preserve">4.48577404022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48974323272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27140951156616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23965215682983</t>
   </si>
   <si>
     <t xml:space="preserve">4.43813705444336</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5651683807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67234992980957</t>
+    <t xml:space="preserve">4.56516933441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67235040664673</t>
   </si>
   <si>
     <t xml:space="preserve">4.71601724624634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58898687362671</t>
+    <t xml:space="preserve">4.58898639678955</t>
   </si>
   <si>
     <t xml:space="preserve">4.50562238693237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52547216415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38653087615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43019819259644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40241003036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29125785827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12056064605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09674167633057</t>
+    <t xml:space="preserve">4.52547121047974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38653039932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43019771575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40240955352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29125833511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12055969238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09674263000488</t>
   </si>
   <si>
     <t xml:space="preserve">4.0649847984314</t>
@@ -200,46 +200,46 @@
     <t xml:space="preserve">4.15628719329834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21186447143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04910612106323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02131843566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31110668182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16422700881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23568201065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50959205627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73586559295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54928922653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50165271759033</t>
+    <t xml:space="preserve">4.21186351776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04910564422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02131748199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31110620498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16422748565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23568153381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50959157943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73586654663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54928970336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50165224075317</t>
   </si>
   <si>
     <t xml:space="preserve">4.56119823455811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48180389404297</t>
+    <t xml:space="preserve">4.48180437088013</t>
   </si>
   <si>
     <t xml:space="preserve">4.5215015411377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55325937271118</t>
+    <t xml:space="preserve">4.55325841903687</t>
   </si>
   <si>
     <t xml:space="preserve">4.5413498878479</t>
@@ -248,76 +248,76 @@
     <t xml:space="preserve">4.56913757324219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53737926483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64853191375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7041072845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84304714202881</t>
+    <t xml:space="preserve">4.53737878799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64853239059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70410776138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84304809570312</t>
   </si>
   <si>
     <t xml:space="preserve">4.89068412780762</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81525945663452</t>
+    <t xml:space="preserve">4.81525993347168</t>
   </si>
   <si>
     <t xml:space="preserve">4.87877511978149</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91053295135498</t>
+    <t xml:space="preserve">4.91053247451782</t>
   </si>
   <si>
     <t xml:space="preserve">4.75968360900879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73826837539673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76678705215454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90123462677002</t>
+    <t xml:space="preserve">4.73826885223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7667875289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90123510360718</t>
   </si>
   <si>
     <t xml:space="preserve">4.7341947555542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56715393066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51826333999634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47344732284546</t>
+    <t xml:space="preserve">4.5671534538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51826286315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4734468460083</t>
   </si>
   <si>
     <t xml:space="preserve">4.47752046585083</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48974370956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6323390007019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61196899414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55085563659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51418828964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33085060119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94706320762634</t>
+    <t xml:space="preserve">4.48974418640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63233947753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61196851730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55085611343384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51418924331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33085012435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94706296920776</t>
   </si>
   <si>
     <t xml:space="preserve">4.13528966903687</t>
@@ -329,55 +329,55 @@
     <t xml:space="preserve">4.26566314697266</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30233192443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2575159072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11084461212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0904746055603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05299091339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18825435638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16380929946899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15566110610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15973472595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10677051544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04321432113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11899280548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16788339614868</t>
+    <t xml:space="preserve">4.30233144760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25751543045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11084413528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09047412872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05299139022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18825387954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16380882263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15566062927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15973424911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10677099227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04321384429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1189923286438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16788291931152</t>
   </si>
   <si>
     <t xml:space="preserve">4.26158952713013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20047760009766</t>
+    <t xml:space="preserve">4.2004771232605</t>
   </si>
   <si>
     <t xml:space="preserve">4.20862483978271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.233069896698</t>
+    <t xml:space="preserve">4.23307037353516</t>
   </si>
   <si>
     <t xml:space="preserve">4.37159299850464</t>
@@ -386,16 +386,16 @@
     <t xml:space="preserve">4.36751842498779</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28603363037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27788639068604</t>
+    <t xml:space="preserve">4.28603410720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27788591384888</t>
   </si>
   <si>
     <t xml:space="preserve">4.24121809005737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25344133377075</t>
+    <t xml:space="preserve">4.25344085693359</t>
   </si>
   <si>
     <t xml:space="preserve">4.29825735092163</t>
@@ -404,28 +404,28 @@
     <t xml:space="preserve">4.22899580001831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07254695892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17195749282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19232845306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10269737243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04158306121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13936376571655</t>
+    <t xml:space="preserve">4.0725474357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17195796966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19232749938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10269641876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04158353805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13936424255371</t>
   </si>
   <si>
     <t xml:space="preserve">4.09862232208252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00084209442139</t>
+    <t xml:space="preserve">4.00084161758423</t>
   </si>
   <si>
     <t xml:space="preserve">3.99269390106201</t>
@@ -434,16 +434,16 @@
     <t xml:space="preserve">4.0334358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19640254974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15158653259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08640003204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0611400604248</t>
+    <t xml:space="preserve">4.19640302658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15158605575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0863995552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06114053726196</t>
   </si>
   <si>
     <t xml:space="preserve">4.35936975479126</t>
@@ -452,7 +452,7 @@
     <t xml:space="preserve">4.37566661834717</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4408540725708</t>
+    <t xml:space="preserve">4.44085311889648</t>
   </si>
   <si>
     <t xml:space="preserve">4.41233348846436</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">4.31455326080322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2697377204895</t>
+    <t xml:space="preserve">4.26973724365234</t>
   </si>
   <si>
     <t xml:space="preserve">4.21677303314209</t>
@@ -479,37 +479,37 @@
     <t xml:space="preserve">4.14343786239624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11491823196411</t>
+    <t xml:space="preserve">4.11491870880127</t>
   </si>
   <si>
     <t xml:space="preserve">4.07417774200439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06928873062134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08232545852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06439971923828</t>
+    <t xml:space="preserve">4.06928825378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08232593536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06439876556396</t>
   </si>
   <si>
     <t xml:space="preserve">4.00573110580444</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96010041236877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05462074279785</t>
+    <t xml:space="preserve">3.96010065078735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05462121963501</t>
   </si>
   <si>
     <t xml:space="preserve">4.13121604919434</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04647302627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98128509521484</t>
+    <t xml:space="preserve">4.04647254943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98128581047058</t>
   </si>
   <si>
     <t xml:space="preserve">4.00410175323486</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">3.98617482185364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02528762817383</t>
+    <t xml:space="preserve">4.02528810501099</t>
   </si>
   <si>
     <t xml:space="preserve">3.97476744651794</t>
@@ -527,37 +527,37 @@
     <t xml:space="preserve">4.02365779876709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05951023101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04810190200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05136156082153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97965621948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03017616271973</t>
+    <t xml:space="preserve">4.05950975418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04810237884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05136203765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97965574264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03017568588257</t>
   </si>
   <si>
     <t xml:space="preserve">4.02039813995361</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99921154975891</t>
+    <t xml:space="preserve">3.99921202659607</t>
   </si>
   <si>
     <t xml:space="preserve">4.07825136184692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1475133895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23714399337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20455121994019</t>
+    <t xml:space="preserve">4.14751291275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23714351654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20455074310303</t>
   </si>
   <si>
     <t xml:space="preserve">4.22492218017578</t>
@@ -566,40 +566,40 @@
     <t xml:space="preserve">4.01713895797729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02202701568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93076610565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91283988952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8949134349823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87535762786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94054460525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93402552604675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89654326438904</t>
+    <t xml:space="preserve">4.02202749252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93076586723328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91283965110779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89491319656372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87535691261292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94054484367371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93402576446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89654350280762</t>
   </si>
   <si>
     <t xml:space="preserve">3.95521116256714</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00247240066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3797402381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38381433486938</t>
+    <t xml:space="preserve">4.00247192382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37974071502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38381385803223</t>
   </si>
   <si>
     <t xml:space="preserve">4.39196348190308</t>
@@ -614,28 +614,28 @@
     <t xml:space="preserve">4.28196048736572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32677698135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2941837310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33899879455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33492469787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34307289123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46529865264893</t>
+    <t xml:space="preserve">4.32677602767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29418325424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33899927139282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33492422103882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34307336807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46529912948608</t>
   </si>
   <si>
     <t xml:space="preserve">4.48159503936768</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40826034545898</t>
+    <t xml:space="preserve">4.40825986862183</t>
   </si>
   <si>
     <t xml:space="preserve">4.53863382339478</t>
@@ -644,43 +644,43 @@
     <t xml:space="preserve">4.55493021011353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52641105651855</t>
+    <t xml:space="preserve">4.52641153335571</t>
   </si>
   <si>
     <t xml:space="preserve">4.50604009628296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43270444869995</t>
+    <t xml:space="preserve">4.43270492553711</t>
   </si>
   <si>
     <t xml:space="preserve">4.59567165374756</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68530416488647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67308139801025</t>
+    <t xml:space="preserve">4.68530464172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67308187484741</t>
   </si>
   <si>
     <t xml:space="preserve">4.60382032394409</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70160055160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85641956329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8238263130188</t>
+    <t xml:space="preserve">4.70160102844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85642004013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82382583618164</t>
   </si>
   <si>
     <t xml:space="preserve">4.77493572235107</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7993803024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74234247207642</t>
+    <t xml:space="preserve">4.79938077926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74234294891357</t>
   </si>
   <si>
     <t xml:space="preserve">4.78308486938477</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">4.72604560852051</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77900981903076</t>
+    <t xml:space="preserve">4.77901029586792</t>
   </si>
   <si>
     <t xml:space="preserve">4.80752992630005</t>
@@ -698,16 +698,16 @@
     <t xml:space="preserve">4.86456775665283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04790544509888</t>
+    <t xml:space="preserve">5.04790592193604</t>
   </si>
   <si>
     <t xml:space="preserve">5.01531267166138</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89716148376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91753196716309</t>
+    <t xml:space="preserve">4.89716100692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91753149032593</t>
   </si>
   <si>
     <t xml:space="preserve">4.88901329040527</t>
@@ -716,34 +716,34 @@
     <t xml:space="preserve">5.04383134841919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90531015396118</t>
+    <t xml:space="preserve">4.90531063079834</t>
   </si>
   <si>
     <t xml:space="preserve">4.9501256942749</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05198097229004</t>
+    <t xml:space="preserve">5.05198001861572</t>
   </si>
   <si>
     <t xml:space="preserve">4.97864484786987</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03160953521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08457374572754</t>
+    <t xml:space="preserve">5.03160905838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08457326889038</t>
   </si>
   <si>
     <t xml:space="preserve">5.23939180374146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19864988327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14568519592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19457626342773</t>
+    <t xml:space="preserve">5.19865036010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14568471908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19457578659058</t>
   </si>
   <si>
     <t xml:space="preserve">5.05605459213257</t>
@@ -758,16 +758,16 @@
     <t xml:space="preserve">5.11716651916504</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25161504745483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18235349655151</t>
+    <t xml:space="preserve">5.25161552429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18235397338867</t>
   </si>
   <si>
     <t xml:space="preserve">5.17827987670898</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25568914413452</t>
+    <t xml:space="preserve">5.25568962097168</t>
   </si>
   <si>
     <t xml:space="preserve">5.27198505401611</t>
@@ -776,10 +776,10 @@
     <t xml:space="preserve">5.17420482635498</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16605663299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18642807006836</t>
+    <t xml:space="preserve">5.16605710983276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1864275932312</t>
   </si>
   <si>
     <t xml:space="preserve">5.10494470596313</t>
@@ -788,28 +788,28 @@
     <t xml:space="preserve">5.07235050201416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94605159759521</t>
+    <t xml:space="preserve">4.94605112075806</t>
   </si>
   <si>
     <t xml:space="preserve">5.06827592849731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98679399490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0369119644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3626823425293</t>
+    <t xml:space="preserve">4.98679304122925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03691148757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36268186569214</t>
   </si>
   <si>
     <t xml:space="preserve">5.39191818237305</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31256341934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27915048599243</t>
+    <t xml:space="preserve">5.3125638961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27915096282959</t>
   </si>
   <si>
     <t xml:space="preserve">5.34597587585449</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">5.35432863235474</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32091665267944</t>
+    <t xml:space="preserve">5.32091617584229</t>
   </si>
   <si>
     <t xml:space="preserve">5.33762264251709</t>
@@ -827,34 +827,34 @@
     <t xml:space="preserve">5.27079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27497386932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18726778030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.132972240448</t>
+    <t xml:space="preserve">5.27497434616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1872673034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13297271728516</t>
   </si>
   <si>
     <t xml:space="preserve">5.2039737701416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22903299331665</t>
+    <t xml:space="preserve">5.22903347015381</t>
   </si>
   <si>
     <t xml:space="preserve">5.25409126281738</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2624454498291</t>
+    <t xml:space="preserve">5.26244497299194</t>
   </si>
   <si>
     <t xml:space="preserve">5.18309116363525</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21232652664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17891502380371</t>
+    <t xml:space="preserve">5.212327003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17891454696655</t>
   </si>
   <si>
     <t xml:space="preserve">5.24991512298584</t>
@@ -863,28 +863,28 @@
     <t xml:space="preserve">5.24573850631714</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28332805633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22485637664795</t>
+    <t xml:space="preserve">5.28332757949829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22485589981079</t>
   </si>
   <si>
     <t xml:space="preserve">5.30003356933594</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33344697952271</t>
+    <t xml:space="preserve">5.33344650268555</t>
   </si>
   <si>
     <t xml:space="preserve">5.40444707870483</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37521123886108</t>
+    <t xml:space="preserve">5.37521171569824</t>
   </si>
   <si>
     <t xml:space="preserve">5.40027093887329</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38356494903564</t>
+    <t xml:space="preserve">5.3835654258728</t>
   </si>
   <si>
     <t xml:space="preserve">5.37938785552979</t>
@@ -893,19 +893,19 @@
     <t xml:space="preserve">5.23320960998535</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3083872795105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2582688331604</t>
+    <t xml:space="preserve">5.30838775634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25826930999756</t>
   </si>
   <si>
     <t xml:space="preserve">5.20814990997314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13714790344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11209011077881</t>
+    <t xml:space="preserve">5.1371488571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11208963394165</t>
   </si>
   <si>
     <t xml:space="preserve">5.1538553237915</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">5.32509326934814</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30420970916748</t>
+    <t xml:space="preserve">5.30421018600464</t>
   </si>
   <si>
     <t xml:space="preserve">5.29585695266724</t>
@@ -926,10 +926,10 @@
     <t xml:space="preserve">5.32926893234253</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48797798156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5380973815918</t>
+    <t xml:space="preserve">5.48797845840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53809642791748</t>
   </si>
   <si>
     <t xml:space="preserve">5.59656810760498</t>
@@ -941,37 +941,37 @@
     <t xml:space="preserve">5.68845272064209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6132755279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57568597793579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44203615188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62162780761719</t>
+    <t xml:space="preserve">5.61327505111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57568550109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44203662872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62162828445435</t>
   </si>
   <si>
     <t xml:space="preserve">5.68009901046753</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64251041412354</t>
+    <t xml:space="preserve">5.64250993728638</t>
   </si>
   <si>
     <t xml:space="preserve">5.37103462219238</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39609384536743</t>
+    <t xml:space="preserve">5.39609336853027</t>
   </si>
   <si>
     <t xml:space="preserve">5.38774156570435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2415623664856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29168081283569</t>
+    <t xml:space="preserve">5.24156284332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29168128967285</t>
   </si>
   <si>
     <t xml:space="preserve">5.19561958312988</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">5.08285331726074</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88655567169189</t>
+    <t xml:space="preserve">4.88655614852905</t>
   </si>
   <si>
     <t xml:space="preserve">4.90743923187256</t>
@@ -989,10 +989,10 @@
     <t xml:space="preserve">4.81973123550415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8030252456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8447904586792</t>
+    <t xml:space="preserve">4.80302572250366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84478998184204</t>
   </si>
   <si>
     <t xml:space="preserve">4.83643770217896</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">4.94502782821655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90326261520386</t>
+    <t xml:space="preserve">4.9032621383667</t>
   </si>
   <si>
     <t xml:space="preserve">4.86567354202271</t>
@@ -1010,19 +1010,19 @@
     <t xml:space="preserve">4.87820339202881</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85314416885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81137800216675</t>
+    <t xml:space="preserve">4.8531436920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81137847900391</t>
   </si>
   <si>
     <t xml:space="preserve">4.9575572013855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92832183837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77796602249146</t>
+    <t xml:space="preserve">4.92832136154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7779655456543</t>
   </si>
   <si>
     <t xml:space="preserve">4.861496925354</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">4.83226156234741</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72367000579834</t>
+    <t xml:space="preserve">4.7236704826355</t>
   </si>
   <si>
     <t xml:space="preserve">4.66102266311646</t>
@@ -1043,10 +1043,10 @@
     <t xml:space="preserve">4.6693754196167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63596343994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70278835296631</t>
+    <t xml:space="preserve">4.63596296310425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70278787612915</t>
   </si>
   <si>
     <t xml:space="preserve">4.67355155944824</t>
@@ -1055,13 +1055,13 @@
     <t xml:space="preserve">4.64014005661011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71949434280396</t>
+    <t xml:space="preserve">4.7194938659668</t>
   </si>
   <si>
     <t xml:space="preserve">4.7904953956604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74872922897339</t>
+    <t xml:space="preserve">4.74872970581055</t>
   </si>
   <si>
     <t xml:space="preserve">4.73202419281006</t>
@@ -1076,70 +1076,67 @@
     <t xml:space="preserve">4.9157919883728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92414379119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8949089050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8406138420105</t>
+    <t xml:space="preserve">4.92414426803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89490842819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84061431884766</t>
   </si>
   <si>
     <t xml:space="preserve">5.16220760345459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99932193756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0202054977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17056083679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09955930709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95338153839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98679304122925</t>
+    <t xml:space="preserve">4.99932241439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02020502090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17056035995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09955978393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95338106155396</t>
   </si>
   <si>
     <t xml:space="preserve">4.7863187789917</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6860818862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60672760009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59419775009155</t>
+    <t xml:space="preserve">4.68608140945435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60672807693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59419822692871</t>
   </si>
   <si>
     <t xml:space="preserve">4.6150803565979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63178730010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70696449279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58584547042847</t>
+    <t xml:space="preserve">4.63178777694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70696496963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58584451675415</t>
   </si>
   <si>
     <t xml:space="preserve">4.55243301391602</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53990316390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57749223709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4897837638855</t>
+    <t xml:space="preserve">4.53990268707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57749176025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48978424072266</t>
   </si>
   <si>
     <t xml:space="preserve">4.41043043136597</t>
@@ -1148,22 +1145,25 @@
     <t xml:space="preserve">4.44384241104126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4939603805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47307825088501</t>
+    <t xml:space="preserve">4.49396085739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47307777404785</t>
   </si>
   <si>
     <t xml:space="preserve">4.51902055740356</t>
   </si>
   <si>
+    <t xml:space="preserve">4.5691385269165</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.59002113342285</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65684652328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64849281311035</t>
+    <t xml:space="preserve">4.65684604644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64849233627319</t>
   </si>
   <si>
     <t xml:space="preserve">4.59837436676025</t>
@@ -1187,46 +1187,46 @@
     <t xml:space="preserve">4.18907308578491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16150808334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15148448944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15649557113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19325017929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09802389144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15315437316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10303688049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12642526626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16986131668091</t>
+    <t xml:space="preserve">4.16150760650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15148496627808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15649604797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19324970245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09802484512329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1531548500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10303640365601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12642621994019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16986179351807</t>
   </si>
   <si>
     <t xml:space="preserve">4.17654418945312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1431303024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16819047927856</t>
+    <t xml:space="preserve">4.14313077926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16819000244141</t>
   </si>
   <si>
     <t xml:space="preserve">2.83002591133118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90687417984009</t>
+    <t xml:space="preserve">2.90687441825867</t>
   </si>
   <si>
     <t xml:space="preserve">2.84339070320129</t>
@@ -1235,46 +1235,46 @@
     <t xml:space="preserve">2.87179160118103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89350891113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80162501335144</t>
+    <t xml:space="preserve">2.89350938796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80162477493286</t>
   </si>
   <si>
     <t xml:space="preserve">2.92358064651489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94863963127136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01713514328003</t>
+    <t xml:space="preserve">2.94863986968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01713538169861</t>
   </si>
   <si>
     <t xml:space="preserve">3.08061838150024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17083120346069</t>
+    <t xml:space="preserve">3.17083144187927</t>
   </si>
   <si>
     <t xml:space="preserve">3.14911389350891</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15746665000916</t>
+    <t xml:space="preserve">3.15746688842773</t>
   </si>
   <si>
     <t xml:space="preserve">3.14410185813904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17918515205383</t>
+    <t xml:space="preserve">3.17918539047241</t>
   </si>
   <si>
     <t xml:space="preserve">3.17417311668396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10400748252869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01212286949158</t>
+    <t xml:space="preserve">3.10400724411011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01212334632874</t>
   </si>
   <si>
     <t xml:space="preserve">3.02882957458496</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">2.94529819488525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95699238777161</t>
+    <t xml:space="preserve">2.95699262619019</t>
   </si>
   <si>
     <t xml:space="preserve">2.89852118492126</t>
@@ -1292,10 +1292,10 @@
     <t xml:space="preserve">2.84004902839661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8250138759613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85007333755493</t>
+    <t xml:space="preserve">2.82501363754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85007286071777</t>
   </si>
   <si>
     <t xml:space="preserve">2.74649548530579</t>
@@ -1307,31 +1307,31 @@
     <t xml:space="preserve">2.54769134521484</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51093792915344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58945751190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5009138584137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51594996452332</t>
+    <t xml:space="preserve">2.51093769073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58945727348328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50091361999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51594972610474</t>
   </si>
   <si>
     <t xml:space="preserve">2.50592589378357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47919607162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41905355453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39566564559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36058187484741</t>
+    <t xml:space="preserve">2.47919631004333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41905331611633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39566540718079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36058235168457</t>
   </si>
   <si>
     <t xml:space="preserve">2.36726450920105</t>
@@ -1346,25 +1346,25 @@
     <t xml:space="preserve">2.313805103302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26201558113098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27203941345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41404247283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38062953948975</t>
+    <t xml:space="preserve">2.2620153427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27203965187073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41404223442078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38062930107117</t>
   </si>
   <si>
     <t xml:space="preserve">2.30043959617615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30211067199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29709887504578</t>
+    <t xml:space="preserve">2.30211091041565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29709911346436</t>
   </si>
   <si>
     <t xml:space="preserve">2.32382869720459</t>
@@ -1376,13 +1376,13 @@
     <t xml:space="preserve">2.35389971733093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36559438705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35055804252625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35222935676575</t>
+    <t xml:space="preserve">2.36559414863586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35055828094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35222911834717</t>
   </si>
   <si>
     <t xml:space="preserve">2.35557007789612</t>
@@ -1391,22 +1391,22 @@
     <t xml:space="preserve">2.25533294677734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22025060653687</t>
+    <t xml:space="preserve">2.22025084495544</t>
   </si>
   <si>
     <t xml:space="preserve">2.28039240837097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22526144981384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23027372360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40067648887634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44912481307983</t>
+    <t xml:space="preserve">2.22526168823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23027396202087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40067625045776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44912457466125</t>
   </si>
   <si>
     <t xml:space="preserve">2.42406558990479</t>
@@ -1415,16 +1415,16 @@
     <t xml:space="preserve">2.31881666183472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30879306793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34387588500977</t>
+    <t xml:space="preserve">2.30879330635071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34387564659119</t>
   </si>
   <si>
     <t xml:space="preserve">2.33218145370483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27371001243591</t>
+    <t xml:space="preserve">2.27370977401733</t>
   </si>
   <si>
     <t xml:space="preserve">2.18850874900818</t>
@@ -1439,16 +1439,16 @@
     <t xml:space="preserve">2.21022653579712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2118968963623</t>
+    <t xml:space="preserve">2.21189713478088</t>
   </si>
   <si>
     <t xml:space="preserve">2.05485892295837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01142263412476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97466897964478</t>
+    <t xml:space="preserve">2.01142287254333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97466921806335</t>
   </si>
   <si>
     <t xml:space="preserve">2.00474047660828</t>
@@ -1460,28 +1460,28 @@
     <t xml:space="preserve">2.1517550945282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17180252075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1818253993988</t>
+    <t xml:space="preserve">2.17180228233337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18182587623596</t>
   </si>
   <si>
     <t xml:space="preserve">2.16679048538208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16846084594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15509605407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15676665306091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11500120162964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07657718658447</t>
+    <t xml:space="preserve">2.16846060752869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15509581565857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15676641464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11500144004822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07657742500305</t>
   </si>
   <si>
     <t xml:space="preserve">2.08994245529175</t>
@@ -1493,34 +1493,34 @@
     <t xml:space="preserve">2.16010808944702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09662508964539</t>
+    <t xml:space="preserve">2.09662485122681</t>
   </si>
   <si>
     <t xml:space="preserve">2.09161257743835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02478766441345</t>
+    <t xml:space="preserve">2.02478742599487</t>
   </si>
   <si>
     <t xml:space="preserve">2.02645897865295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12502479553223</t>
+    <t xml:space="preserve">2.12502455711365</t>
   </si>
   <si>
     <t xml:space="preserve">2.23695611953735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18683767318726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11834216117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06989526748657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06321263313293</t>
+    <t xml:space="preserve">2.18683791160583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11834239959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06989502906799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06321310997009</t>
   </si>
   <si>
     <t xml:space="preserve">2.00139951705933</t>
@@ -1529,16 +1529,16 @@
     <t xml:space="preserve">1.99972856044769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9830230474472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94626903533936</t>
+    <t xml:space="preserve">1.98302292823792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94626927375793</t>
   </si>
   <si>
     <t xml:space="preserve">1.87610328197479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75748932361603</t>
+    <t xml:space="preserve">1.75748944282532</t>
   </si>
   <si>
     <t xml:space="preserve">1.695676445961</t>
@@ -1553,10 +1553,10 @@
     <t xml:space="preserve">1.62968707084656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50439059734344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48601388931274</t>
+    <t xml:space="preserve">1.50439071655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48601377010345</t>
   </si>
   <si>
     <t xml:space="preserve">1.39663565158844</t>
@@ -1565,7 +1565,7 @@
     <t xml:space="preserve">1.31728136539459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28553974628448</t>
+    <t xml:space="preserve">1.2855396270752</t>
   </si>
   <si>
     <t xml:space="preserve">1.27133929729462</t>
@@ -1580,22 +1580,22 @@
     <t xml:space="preserve">1.2897162437439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27635133266449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30391645431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3156111240387</t>
+    <t xml:space="preserve">1.2763512134552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30391657352448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31561100482941</t>
   </si>
   <si>
     <t xml:space="preserve">1.31310510635376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2838693857193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27969300746918</t>
+    <t xml:space="preserve">1.28386926651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27969288825989</t>
   </si>
   <si>
     <t xml:space="preserve">1.33899998664856</t>
@@ -1610,49 +1610,49 @@
     <t xml:space="preserve">1.29639852046967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2429393529892</t>
+    <t xml:space="preserve">1.24293923377991</t>
   </si>
   <si>
     <t xml:space="preserve">1.2521276473999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26799845695496</t>
+    <t xml:space="preserve">1.26799857616425</t>
   </si>
   <si>
     <t xml:space="preserve">1.25296247005463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2337509393692</t>
+    <t xml:space="preserve">1.23375082015991</t>
   </si>
   <si>
     <t xml:space="preserve">1.25630414485931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2579745054245</t>
+    <t xml:space="preserve">1.25797438621521</t>
   </si>
   <si>
     <t xml:space="preserve">1.26048040390015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36823582649231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36990594863892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36405909061432</t>
+    <t xml:space="preserve">1.36823570728302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36990606784821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36405920982361</t>
   </si>
   <si>
     <t xml:space="preserve">1.34568238258362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31477546691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34484684467316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25129210948944</t>
+    <t xml:space="preserve">1.31477534770966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34484672546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25129199028015</t>
   </si>
   <si>
     <t xml:space="preserve">1.23876285552979</t>
@@ -1661,22 +1661,22 @@
     <t xml:space="preserve">1.06835913658142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962275207042694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989840626716614</t>
+    <t xml:space="preserve">0.962275326251984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989840686321259</t>
   </si>
   <si>
     <t xml:space="preserve">0.633163154125214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.703329861164093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.705000281333923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862038195133209</t>
+    <t xml:space="preserve">0.703329801559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.705000162124634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.862038135528564</t>
   </si>
   <si>
     <t xml:space="preserve">0.958098888397217</t>
@@ -1694,13 +1694,13 @@
     <t xml:space="preserve">0.9447340965271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.91883909702301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917168855667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00487577915192</t>
+    <t xml:space="preserve">0.918839156627655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917168796062469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00487565994263</t>
   </si>
   <si>
     <t xml:space="preserve">1.14771413803101</t>
@@ -1712,16 +1712,16 @@
     <t xml:space="preserve">1.09926605224609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13184344768524</t>
+    <t xml:space="preserve">1.13184356689453</t>
   </si>
   <si>
     <t xml:space="preserve">1.10344254970551</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0357825756073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01155829429626</t>
+    <t xml:space="preserve">1.03578269481659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01155817508698</t>
   </si>
   <si>
     <t xml:space="preserve">1.01824069023132</t>
@@ -1736,16 +1736,16 @@
     <t xml:space="preserve">1.01322948932648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.082559466362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10177218914032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12766623497009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12933731079102</t>
+    <t xml:space="preserve">1.08255958557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10177206993103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1276661157608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12933743000031</t>
   </si>
   <si>
     <t xml:space="preserve">1.13017225265503</t>
@@ -1754,34 +1754,34 @@
     <t xml:space="preserve">1.1368545293808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11346662044525</t>
+    <t xml:space="preserve">1.11346673965454</t>
   </si>
   <si>
     <t xml:space="preserve">1.10260689258575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06585299968719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03244113922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07086527347565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06334805488586</t>
+    <t xml:space="preserve">1.06585311889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0324410200119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07086515426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06334817409515</t>
   </si>
   <si>
     <t xml:space="preserve">1.01907622814178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03494715690613</t>
+    <t xml:space="preserve">1.03494727611542</t>
   </si>
   <si>
     <t xml:space="preserve">1.06501841545105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12850165367126</t>
+    <t xml:space="preserve">1.12850177288055</t>
   </si>
   <si>
     <t xml:space="preserve">1.08506560325623</t>
@@ -1793,25 +1793,25 @@
     <t xml:space="preserve">1.07253646850586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0808892250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1051127910614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07838332653046</t>
+    <t xml:space="preserve">1.08088910579681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10511291027069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07838320732117</t>
   </si>
   <si>
     <t xml:space="preserve">1.10010087490082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11263072490692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11012482643127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22623288631439</t>
+    <t xml:space="preserve">1.11263084411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11012494564056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2262327671051</t>
   </si>
   <si>
     <t xml:space="preserve">1.46179032325745</t>
@@ -1823,40 +1823,40 @@
     <t xml:space="preserve">1.41417765617371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36071753501892</t>
+    <t xml:space="preserve">1.36071765422821</t>
   </si>
   <si>
     <t xml:space="preserve">1.33064615726471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29806971549988</t>
+    <t xml:space="preserve">1.29806983470917</t>
   </si>
   <si>
     <t xml:space="preserve">1.37324774265289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38744723796844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32981157302856</t>
+    <t xml:space="preserve">1.38744711875916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32981145381927</t>
   </si>
   <si>
     <t xml:space="preserve">1.35069346427917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3548709154129</t>
+    <t xml:space="preserve">1.35487079620361</t>
   </si>
   <si>
     <t xml:space="preserve">1.32897591590881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36572968959808</t>
+    <t xml:space="preserve">1.36572957038879</t>
   </si>
   <si>
     <t xml:space="preserve">1.37157642841339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40248310565948</t>
+    <t xml:space="preserve">1.40248322486877</t>
   </si>
   <si>
     <t xml:space="preserve">1.41918885707855</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">1.39412951469421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4534364938736</t>
+    <t xml:space="preserve">1.45343661308289</t>
   </si>
   <si>
     <t xml:space="preserve">1.43589532375336</t>
@@ -1889,13 +1889,13 @@
     <t xml:space="preserve">1.52861440181732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61131036281586</t>
+    <t xml:space="preserve">1.61131024360657</t>
   </si>
   <si>
     <t xml:space="preserve">1.5971097946167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59376895427704</t>
+    <t xml:space="preserve">1.59376907348633</t>
   </si>
   <si>
     <t xml:space="preserve">1.57455658912659</t>
@@ -1913,19 +1913,19 @@
     <t xml:space="preserve">1.47097861766815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41751849651337</t>
+    <t xml:space="preserve">1.41751837730408</t>
   </si>
   <si>
     <t xml:space="preserve">1.43422496318817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38828277587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38327074050903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33231663703918</t>
+    <t xml:space="preserve">1.3882828950882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38327085971832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3323165178299</t>
   </si>
   <si>
     <t xml:space="preserve">1.36739993095398</t>
@@ -1934,16 +1934,16 @@
     <t xml:space="preserve">1.34985876083374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3030811548233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32229351997375</t>
+    <t xml:space="preserve">1.30308103561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32229340076447</t>
   </si>
   <si>
     <t xml:space="preserve">1.31644582748413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2989045381546</t>
+    <t xml:space="preserve">1.29890441894531</t>
   </si>
   <si>
     <t xml:space="preserve">1.30892860889435</t>
@@ -1955,13 +1955,13 @@
     <t xml:space="preserve">1.31895172595978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29222226142883</t>
+    <t xml:space="preserve">1.29222214221954</t>
   </si>
   <si>
     <t xml:space="preserve">1.28721010684967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25045645236969</t>
+    <t xml:space="preserve">1.2504563331604</t>
   </si>
   <si>
     <t xml:space="preserve">1.32730543613434</t>
@@ -1976,25 +1976,25 @@
     <t xml:space="preserve">1.3490229845047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34651708602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30725824832916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26215088367462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26883327960968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22205638885498</t>
+    <t xml:space="preserve">1.34651696681976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30725836753845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26215076446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26883316040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22205626964569</t>
   </si>
   <si>
     <t xml:space="preserve">1.19198513031006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35821151733398</t>
+    <t xml:space="preserve">1.35821163654327</t>
   </si>
   <si>
     <t xml:space="preserve">1.32312917709351</t>
@@ -2015,13 +2015,13 @@
     <t xml:space="preserve">1.32646989822388</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3381644487381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42503666877747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48183739185333</t>
+    <t xml:space="preserve">1.33816432952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42503643035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48183751106262</t>
   </si>
   <si>
     <t xml:space="preserve">1.49603796005249</t>
@@ -2030,16 +2030,16 @@
     <t xml:space="preserve">1.50272035598755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50355494022369</t>
+    <t xml:space="preserve">1.50355517864227</t>
   </si>
   <si>
     <t xml:space="preserve">1.54448533058167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56369757652283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53863835334778</t>
+    <t xml:space="preserve">1.56369781494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53863847255707</t>
   </si>
   <si>
     <t xml:space="preserve">1.54866254329681</t>
@@ -2048,7 +2048,7 @@
     <t xml:space="preserve">1.49186074733734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41668295860291</t>
+    <t xml:space="preserve">1.41668283939362</t>
   </si>
   <si>
     <t xml:space="preserve">1.39329481124878</t>
@@ -2069,10 +2069,10 @@
     <t xml:space="preserve">1.33148193359375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32814025878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29723417758942</t>
+    <t xml:space="preserve">1.32814013957977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29723429679871</t>
   </si>
   <si>
     <t xml:space="preserve">1.29974031448364</t>
@@ -2102,25 +2102,25 @@
     <t xml:space="preserve">1.38911855220795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37993001937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45260167121887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48852002620697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49687266349792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50104904174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44758975505829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39914166927338</t>
+    <t xml:space="preserve">1.37993013858795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45260179042816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48851978778839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49687278270721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50104916095734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.447589635849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39914155006409</t>
   </si>
   <si>
     <t xml:space="preserve">1.54281485080719</t>
@@ -2129,10 +2129,10 @@
     <t xml:space="preserve">1.46095454692841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39162361621857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41000056266785</t>
+    <t xml:space="preserve">1.39162349700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41000032424927</t>
   </si>
   <si>
     <t xml:space="preserve">1.40833008289337</t>
@@ -2141,22 +2141,22 @@
     <t xml:space="preserve">1.4292129278183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40749442577362</t>
+    <t xml:space="preserve">1.40749430656433</t>
   </si>
   <si>
     <t xml:space="preserve">1.3339878320694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32563400268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33732867240906</t>
+    <t xml:space="preserve">1.32563412189484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33732855319977</t>
   </si>
   <si>
     <t xml:space="preserve">1.36155319213867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36907041072845</t>
+    <t xml:space="preserve">1.36907029151917</t>
   </si>
   <si>
     <t xml:space="preserve">1.44508373737335</t>
@@ -2171,25 +2171,25 @@
     <t xml:space="preserve">1.47181332111359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46513092517853</t>
+    <t xml:space="preserve">1.46513104438782</t>
   </si>
   <si>
     <t xml:space="preserve">1.47264909744263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51190876960754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47014319896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49269616603851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52276754379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54030883312225</t>
+    <t xml:space="preserve">1.51190888881683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47014307975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4926962852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52276766300201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54030871391296</t>
   </si>
   <si>
     <t xml:space="preserve">1.53529679775238</t>
@@ -2201,13 +2201,13 @@
     <t xml:space="preserve">1.60629820823669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58625102043152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64555776119232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59293341636658</t>
+    <t xml:space="preserve">1.58625113964081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64555788040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59293353557587</t>
   </si>
   <si>
     <t xml:space="preserve">1.63219308853149</t>
@@ -2225,10 +2225,10 @@
     <t xml:space="preserve">1.55868566036224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56620371341705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56703841686249</t>
+    <t xml:space="preserve">1.56620383262634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56703853607178</t>
   </si>
   <si>
     <t xml:space="preserve">1.58708655834198</t>
@@ -2240,7 +2240,7 @@
     <t xml:space="preserve">1.74078285694122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70737087726593</t>
+    <t xml:space="preserve">1.70737075805664</t>
   </si>
   <si>
     <t xml:space="preserve">1.71906530857086</t>
@@ -2249,34 +2249,34 @@
     <t xml:space="preserve">1.72908842563629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71238279342651</t>
+    <t xml:space="preserve">1.7123829126358</t>
   </si>
   <si>
     <t xml:space="preserve">1.73243021965027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69233477115631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76584208011627</t>
+    <t xml:space="preserve">1.69233465194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76584219932556</t>
   </si>
   <si>
     <t xml:space="preserve">1.74913573265076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72073566913605</t>
+    <t xml:space="preserve">1.72073554992676</t>
   </si>
   <si>
     <t xml:space="preserve">1.63887548446655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60880410671234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68565249443054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67061710357666</t>
+    <t xml:space="preserve">1.60880422592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68565225601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67061698436737</t>
   </si>
   <si>
     <t xml:space="preserve">1.68732357025146</t>
@@ -2288,22 +2288,22 @@
     <t xml:space="preserve">1.68064117431641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61715698242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6154865026474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62467503547668</t>
+    <t xml:space="preserve">1.61715710163116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61548674106598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62467527389526</t>
   </si>
   <si>
     <t xml:space="preserve">1.61047458648682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64054584503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62383937835693</t>
+    <t xml:space="preserve">1.64054596424103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62383949756622</t>
   </si>
   <si>
     <t xml:space="preserve">1.60963988304138</t>
@@ -2312,28 +2312,28 @@
     <t xml:space="preserve">1.57789814472198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59126305580139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56202733516693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59209764003754</t>
+    <t xml:space="preserve">1.59126317501068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56202745437622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59209775924683</t>
   </si>
   <si>
     <t xml:space="preserve">1.59543943405151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58290922641754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60379219055176</t>
+    <t xml:space="preserve">1.58290934562683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60379207134247</t>
   </si>
   <si>
     <t xml:space="preserve">1.60045146942139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58541512489319</t>
+    <t xml:space="preserve">1.58541536331177</t>
   </si>
   <si>
     <t xml:space="preserve">1.54532086849213</t>
@@ -2342,13 +2342,13 @@
     <t xml:space="preserve">1.54699122905731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57706248760223</t>
+    <t xml:space="preserve">1.57706260681152</t>
   </si>
   <si>
     <t xml:space="preserve">1.43756568431854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49436676502228</t>
+    <t xml:space="preserve">1.49436688423157</t>
   </si>
   <si>
     <t xml:space="preserve">1.48935544490814</t>
@@ -2360,10 +2360,10 @@
     <t xml:space="preserve">1.51274359226227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52610838413239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53195595741272</t>
+    <t xml:space="preserve">1.52610850334167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53195607662201</t>
   </si>
   <si>
     <t xml:space="preserve">1.54782688617706</t>
@@ -2372,16 +2372,16 @@
     <t xml:space="preserve">1.51691997051239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50940275192261</t>
+    <t xml:space="preserve">1.5094028711319</t>
   </si>
   <si>
     <t xml:space="preserve">1.48267221450806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26465690135956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23208045959473</t>
+    <t xml:space="preserve">1.26465678215027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23208034038544</t>
   </si>
   <si>
     <t xml:space="preserve">1.18029081821442</t>
@@ -2390,25 +2390,25 @@
     <t xml:space="preserve">1.16692590713501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13601970672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02742898464203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933039784431458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776836335659027</t>
+    <t xml:space="preserve">1.13601982593536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02742910385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933039665222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776836395263672</t>
   </si>
   <si>
     <t xml:space="preserve">0.719200670719147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.695811808109283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.546709179878235</t>
+    <t xml:space="preserve">0.695811748504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54670923948288</t>
   </si>
   <si>
     <t xml:space="preserve">0.613534212112427</t>
@@ -2417,10 +2417,10 @@
     <t xml:space="preserve">0.519561350345612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599333703517914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.674928963184357</t>
+    <t xml:space="preserve">0.599333763122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.674928903579712</t>
   </si>
   <si>
     <t xml:space="preserve">0.725047469139099</t>
@@ -2432,7 +2432,7 @@
     <t xml:space="preserve">0.637340426445007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.682446956634521</t>
+    <t xml:space="preserve">0.682447016239166</t>
   </si>
   <si>
     <t xml:space="preserve">0.680358350276947</t>
@@ -2447,19 +2447,19 @@
     <t xml:space="preserve">0.643604636192322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.659475445747375</t>
+    <t xml:space="preserve">0.659475386142731</t>
   </si>
   <si>
     <t xml:space="preserve">0.64318722486496</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627316415309906</t>
+    <t xml:space="preserve">0.627316355705261</t>
   </si>
   <si>
     <t xml:space="preserve">0.576780498027802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618127942085266</t>
+    <t xml:space="preserve">0.618128001689911</t>
   </si>
   <si>
     <t xml:space="preserve">0.660728454589844</t>
@@ -2468,19 +2468,19 @@
     <t xml:space="preserve">0.646528899669647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.650705277919769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.638175249099731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.649869680404663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640263855457306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612281203269958</t>
+    <t xml:space="preserve">0.650705337524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.638175189495087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.649869620800018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640263795852661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612281143665314</t>
   </si>
   <si>
     <t xml:space="preserve">0.615621984004974</t>
@@ -2489,16 +2489,16 @@
     <t xml:space="preserve">0.610192537307739</t>
   </si>
   <si>
-    <t xml:space="preserve">0.6055988073349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61102819442749</t>
+    <t xml:space="preserve">0.605598747730255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.611028134822845</t>
   </si>
   <si>
     <t xml:space="preserve">0.651540040969849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.676599264144897</t>
+    <t xml:space="preserve">0.676599323749542</t>
   </si>
   <si>
     <t xml:space="preserve">0.654881656169891</t>
@@ -2507,49 +2507,49 @@
     <t xml:space="preserve">0.642351627349854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641516864299774</t>
+    <t xml:space="preserve">0.641516804695129</t>
   </si>
   <si>
     <t xml:space="preserve">0.655717313289642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639846503734589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.649034857749939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.668246567249298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.650287091732025</t>
+    <t xml:space="preserve">0.639846444129944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.649034917354584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.668246507644653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.65028703212738</t>
   </si>
   <si>
     <t xml:space="preserve">0.6264808177948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.609775185585022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.606016099452972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.629822432994843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596827745437622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.574691832065582</t>
+    <t xml:space="preserve">0.609775125980377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.606016159057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.629822373390198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596827805042267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.574691951274872</t>
   </si>
   <si>
     <t xml:space="preserve">0.581792593002319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.574274480342865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.601839780807495</t>
+    <t xml:space="preserve">0.57427453994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.601839661598206</t>
   </si>
   <si>
     <t xml:space="preserve">0.630658030509949</t>
@@ -2561,25 +2561,25 @@
     <t xml:space="preserve">0.789366483688354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.763054192066193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768483638763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.82779061794281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83530855178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901297986507416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910486340522766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00571131706238</t>
+    <t xml:space="preserve">0.763054251670837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.768483579158783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.827790558338165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.835308492183685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901297926902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.910486400127411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00571143627167</t>
   </si>
   <si>
     <t xml:space="preserve">1.01072335243225</t>
@@ -2591,10 +2591,10 @@
     <t xml:space="preserve">0.877909004688263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.924685895442963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925521612167358</t>
+    <t xml:space="preserve">0.924685955047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925521552562714</t>
   </si>
   <si>
     <t xml:space="preserve">0.938051640987396</t>
@@ -2603,10 +2603,10 @@
     <t xml:space="preserve">0.922180891036987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.892109513282776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.893779993057251</t>
+    <t xml:space="preserve">0.892109453678131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.893779873847961</t>
   </si>
   <si>
     <t xml:space="preserve">0.895450234413147</t>
@@ -2615,22 +2615,22 @@
     <t xml:space="preserve">0.823614180088043</t>
   </si>
   <si>
-    <t xml:space="preserve">0.781013667583466</t>
+    <t xml:space="preserve">0.78101372718811</t>
   </si>
   <si>
     <t xml:space="preserve">0.824867188930511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.806073009967804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78560745716095</t>
+    <t xml:space="preserve">0.806072890758514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785607516765594</t>
   </si>
   <si>
     <t xml:space="preserve">0.802313983440399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.797719299793243</t>
+    <t xml:space="preserve">0.797719240188599</t>
   </si>
   <si>
     <t xml:space="preserve">0.801895618438721</t>
@@ -2639,22 +2639,22 @@
     <t xml:space="preserve">0.79855489730835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77641898393631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.782266616821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766394972801208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821525514125824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.795631527900696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86370861530304</t>
+    <t xml:space="preserve">0.776419043540955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.782266676425934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766394913196564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821525573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.795631587505341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863708555698395</t>
   </si>
   <si>
     <t xml:space="preserve">0.855355799198151</t>
@@ -2663,28 +2663,28 @@
     <t xml:space="preserve">0.844496965408325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.857861876487732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.836143314838409</t>
+    <t xml:space="preserve">0.857861816883087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.836143374443054</t>
   </si>
   <si>
     <t xml:space="preserve">0.834890365600586</t>
   </si>
   <si>
-    <t xml:space="preserve">0.838649332523346</t>
+    <t xml:space="preserve">0.838649392127991</t>
   </si>
   <si>
     <t xml:space="preserve">0.800225257873535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.773912966251373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789783895015717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.771825313568115</t>
+    <t xml:space="preserve">0.773913025856018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789783835411072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77182525396347</t>
   </si>
   <si>
     <t xml:space="preserve">0.767230570316315</t>
@@ -2702,16 +2702,16 @@
     <t xml:space="preserve">0.758877813816071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.765977501869202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.800642669200897</t>
+    <t xml:space="preserve">0.765977561473846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800642609596252</t>
   </si>
   <si>
     <t xml:space="preserve">0.809831082820892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.799807965755463</t>
+    <t xml:space="preserve">0.799807906150818</t>
   </si>
   <si>
     <t xml:space="preserve">0.780178070068359</t>
@@ -2720,13 +2720,13 @@
     <t xml:space="preserve">0.770989596843719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.740918278694153</t>
+    <t xml:space="preserve">0.740918338298798</t>
   </si>
   <si>
     <t xml:space="preserve">0.717947661876678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.712100088596344</t>
+    <t xml:space="preserve">0.712100028991699</t>
   </si>
   <si>
     <t xml:space="preserve">0.684117376804352</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">0.690799713134766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.69288831949234</t>
+    <t xml:space="preserve">0.692888379096985</t>
   </si>
   <si>
     <t xml:space="preserve">0.685787737369537</t>
@@ -2747,7 +2747,7 @@
     <t xml:space="preserve">0.666576147079468</t>
   </si>
   <si>
-    <t xml:space="preserve">0.682029545307159</t>
+    <t xml:space="preserve">0.682029604911804</t>
   </si>
   <si>
     <t xml:space="preserve">0.687458992004395</t>
@@ -2759,13 +2759,13 @@
     <t xml:space="preserve">0.67785233259201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.694558799266815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.697482168674469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.70374721288681</t>
+    <t xml:space="preserve">0.69455873966217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.697482109069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.703747153282166</t>
   </si>
   <si>
     <t xml:space="preserve">0.69831782579422</t>
@@ -2777,19 +2777,19 @@
     <t xml:space="preserve">0.720453679561615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.742588639259338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.767647981643677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.718365013599396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.715024292469025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7818483710289</t>
+    <t xml:space="preserve">0.742588698863983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767647922039032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.718365073204041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.715024352073669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781848430633545</t>
   </si>
   <si>
     <t xml:space="preserve">0.75720739364624</t>
@@ -2801,40 +2801,40 @@
     <t xml:space="preserve">0.796466290950775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.825284540653229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.850343704223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860367834568024</t>
+    <t xml:space="preserve">0.825284600257874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.850343823432922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860367774963379</t>
   </si>
   <si>
     <t xml:space="preserve">0.847003042697906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.858696579933167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843661308288574</t>
+    <t xml:space="preserve">0.858696699142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843661367893219</t>
   </si>
   <si>
     <t xml:space="preserve">0.872062265872955</t>
   </si>
   <si>
-    <t xml:space="preserve">0.852014124393463</t>
+    <t xml:space="preserve">0.852014183998108</t>
   </si>
   <si>
     <t xml:space="preserve">0.8545201420784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.812755405902863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8077432513237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81317275762558</t>
+    <t xml:space="preserve">0.812755346298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80774337053299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.813172817230225</t>
   </si>
   <si>
     <t xml:space="preserve">0.828626096248627</t>
@@ -2843,22 +2843,22 @@
     <t xml:space="preserve">0.832802534103394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.820690810680389</t>
+    <t xml:space="preserve">0.820690751075745</t>
   </si>
   <si>
     <t xml:space="preserve">0.749689400196075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.710846960544586</t>
+    <t xml:space="preserve">0.710847020149231</t>
   </si>
   <si>
     <t xml:space="preserve">0.654464304447174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.633998811244965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.645275831222534</t>
+    <t xml:space="preserve">0.63399875164032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.645275890827179</t>
   </si>
   <si>
     <t xml:space="preserve">0.660311043262482</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">0.68912935256958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.753030180931091</t>
+    <t xml:space="preserve">0.753030121326447</t>
   </si>
   <si>
     <t xml:space="preserve">0.784354448318481</t>
@@ -2879,10 +2879,10 @@
     <t xml:space="preserve">0.787696123123169</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803148686885834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856191396713257</t>
+    <t xml:space="preserve">0.803148746490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856191456317902</t>
   </si>
   <si>
     <t xml:space="preserve">0.845331788063049</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">0.877073407173157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.900462329387665</t>
+    <t xml:space="preserve">0.90046226978302</t>
   </si>
   <si>
     <t xml:space="preserve">0.889603495597839</t>
@@ -2900,7 +2900,7 @@
     <t xml:space="preserve">0.887097477912903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.89043927192688</t>
+    <t xml:space="preserve">0.890439212322235</t>
   </si>
   <si>
     <t xml:space="preserve">0.881250739097595</t>
@@ -2909,10 +2909,10 @@
     <t xml:space="preserve">0.904638826847076</t>
   </si>
   <si>
-    <t xml:space="preserve">0.892944276332855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.90213280916214</t>
+    <t xml:space="preserve">0.89294421672821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.90213268995285</t>
   </si>
   <si>
     <t xml:space="preserve">0.882085502147675</t>
@@ -2921,7 +2921,7 @@
     <t xml:space="preserve">0.867884993553162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.841155350208282</t>
+    <t xml:space="preserve">0.841155469417572</t>
   </si>
   <si>
     <t xml:space="preserve">0.839484930038452</t>
@@ -2933,10 +2933,10 @@
     <t xml:space="preserve">0.840320587158203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.859532177448273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905474364757538</t>
+    <t xml:space="preserve">0.859532117843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905474305152893</t>
   </si>
   <si>
     <t xml:space="preserve">0.849508225917816</t>
@@ -2948,55 +2948,55 @@
     <t xml:space="preserve">0.906310021877289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.943898379802704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95392245054245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957263171672821</t>
+    <t xml:space="preserve">0.943898439407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953922390937805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957263350486755</t>
   </si>
   <si>
     <t xml:space="preserve">0.965616941452026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978146016597748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961439669132233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934710144996643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902968347072601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874567449092865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852849781513214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867050230503082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.878744661808014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907144784927368</t>
+    <t xml:space="preserve">0.978146195411682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961439728736877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934710025787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902968287467957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87456750869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852849721908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867050170898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.878744721412659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.907144844532013</t>
   </si>
   <si>
     <t xml:space="preserve">0.931369304656982</t>
   </si>
   <si>
-    <t xml:space="preserve">0.921345174312592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927191913127899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912992417812347</t>
+    <t xml:space="preserve">0.921345233917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927191853523254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912992477416992</t>
   </si>
   <si>
     <t xml:space="preserve">0.947240054607391</t>
@@ -3005,34 +3005,34 @@
     <t xml:space="preserve">0.899626731872559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.929697930812836</t>
+    <t xml:space="preserve">0.92969799041748</t>
   </si>
   <si>
     <t xml:space="preserve">0.938886404037476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.93721604347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.942228078842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941392481327057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946404635906219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.935545742511749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975640058517456</t>
+    <t xml:space="preserve">0.937215983867645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942228019237518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941392421722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94640451669693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.935545682907104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975639998912811</t>
   </si>
   <si>
     <t xml:space="preserve">1.14687860012054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18947911262512</t>
+    <t xml:space="preserve">1.18947923183441</t>
   </si>
   <si>
     <t xml:space="preserve">1.17360830307007</t>
@@ -3041,10 +3041,10 @@
     <t xml:space="preserve">1.16024351119995</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15773749351501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17193794250488</t>
+    <t xml:space="preserve">1.1577376127243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17193782329559</t>
   </si>
   <si>
     <t xml:space="preserve">1.1385258436203</t>
@@ -3056,61 +3056,61 @@
     <t xml:space="preserve">1.11096060276031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1067841053009</t>
+    <t xml:space="preserve">1.10678422451019</t>
   </si>
   <si>
     <t xml:space="preserve">1.11179530620575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13100779056549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12098371982574</t>
+    <t xml:space="preserve">1.1310076713562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12098383903503</t>
   </si>
   <si>
     <t xml:space="preserve">1.16358518600464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14520823955536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11513686180115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10761892795563</t>
+    <t xml:space="preserve">1.14520835876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11513698101044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10761904716492</t>
   </si>
   <si>
     <t xml:space="preserve">1.37742400169373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37241184711456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43923687934875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43673098087311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44007182121277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40665972232819</t>
+    <t xml:space="preserve">1.37241196632385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43923699855804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4367311000824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44007170200348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4066596031189</t>
   </si>
   <si>
     <t xml:space="preserve">1.41167175769806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39747130870819</t>
+    <t xml:space="preserve">1.3974711894989</t>
   </si>
   <si>
     <t xml:space="preserve">1.43840134143829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47682547569275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45928418636322</t>
+    <t xml:space="preserve">1.47682535648346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45928430557251</t>
   </si>
   <si>
     <t xml:space="preserve">1.44090735912323</t>
@@ -3119,76 +3119,76 @@
     <t xml:space="preserve">1.43338942527771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48100185394287</t>
+    <t xml:space="preserve">1.48100173473358</t>
   </si>
   <si>
     <t xml:space="preserve">1.41334211826324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4258713722229</t>
+    <t xml:space="preserve">1.42587125301361</t>
   </si>
   <si>
     <t xml:space="preserve">1.5879213809967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55033278465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62634551525116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61214601993561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62049877643585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61966300010681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62718093395233</t>
+    <t xml:space="preserve">1.550332903862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62634563446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61214578151703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62049865722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6196631193161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62718117237091</t>
   </si>
   <si>
     <t xml:space="preserve">1.6138162612915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45677828788757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39830708503723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34317636489868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3565411567688</t>
+    <t xml:space="preserve">1.45677816867828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39830696582794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34317624568939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35654103755951</t>
   </si>
   <si>
     <t xml:space="preserve">1.35904717445374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36489391326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40276575088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43466711044312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41251349449158</t>
+    <t xml:space="preserve">1.36489403247833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4027658700943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43466734886169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41251361370087</t>
   </si>
   <si>
     <t xml:space="preserve">1.39390444755554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39213228225708</t>
+    <t xml:space="preserve">1.39213216304779</t>
   </si>
   <si>
     <t xml:space="preserve">1.3336466550827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4479593038559</t>
+    <t xml:space="preserve">1.44795918464661</t>
   </si>
   <si>
     <t xml:space="preserve">1.49049437046051</t>
@@ -3200,13 +3200,13 @@
     <t xml:space="preserve">1.53214287757874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58442533016205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52859854698181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5489798784256</t>
+    <t xml:space="preserve">1.58442544937134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52859842777252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54897964000702</t>
   </si>
   <si>
     <t xml:space="preserve">1.54454898834229</t>
@@ -3224,13 +3224,13 @@
     <t xml:space="preserve">1.6145544052124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60657906532288</t>
+    <t xml:space="preserve">1.60657894611359</t>
   </si>
   <si>
     <t xml:space="preserve">1.5693610906601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58885610103607</t>
+    <t xml:space="preserve">1.58885622024536</t>
   </si>
   <si>
     <t xml:space="preserve">1.60392069816589</t>
@@ -3254,22 +3254,22 @@
     <t xml:space="preserve">1.520623087883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4931526184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49758338928223</t>
+    <t xml:space="preserve">1.49315237998962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49758350849152</t>
   </si>
   <si>
     <t xml:space="preserve">1.52505385875702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50733089447021</t>
+    <t xml:space="preserve">1.5073310136795</t>
   </si>
   <si>
     <t xml:space="preserve">1.50112795829773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54011833667755</t>
+    <t xml:space="preserve">1.54011821746826</t>
   </si>
   <si>
     <t xml:space="preserve">1.53037071228027</t>
@@ -3278,34 +3278,34 @@
     <t xml:space="preserve">1.55341041088104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63848006725311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6632924079895</t>
+    <t xml:space="preserve">1.6384801864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66329228878021</t>
   </si>
   <si>
     <t xml:space="preserve">1.56404411792755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5170783996582</t>
+    <t xml:space="preserve">1.51707863807678</t>
   </si>
   <si>
     <t xml:space="preserve">1.48872184753418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4656822681427</t>
+    <t xml:space="preserve">1.46568238735199</t>
   </si>
   <si>
     <t xml:space="preserve">1.42403340339661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44707322120667</t>
+    <t xml:space="preserve">1.44707310199738</t>
   </si>
   <si>
     <t xml:space="preserve">1.46656823158264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61809885501862</t>
+    <t xml:space="preserve">1.61809897422791</t>
   </si>
   <si>
     <t xml:space="preserve">1.82900106906891</t>
@@ -3314,16 +3314,16 @@
     <t xml:space="preserve">1.84672403335571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90520942211151</t>
+    <t xml:space="preserve">1.9052095413208</t>
   </si>
   <si>
     <t xml:space="preserve">1.89634835720062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98319029808044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03635931015015</t>
+    <t xml:space="preserve">1.98319017887115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03635907173157</t>
   </si>
   <si>
     <t xml:space="preserve">2.09129977226257</t>
@@ -3332,22 +3332,22 @@
     <t xml:space="preserve">2.17105293273926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96015071868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88925909996033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96192288398743</t>
+    <t xml:space="preserve">1.96015048027039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88925898075104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96192300319672</t>
   </si>
   <si>
     <t xml:space="preserve">1.94597220420837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01863646507263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10902261734009</t>
+    <t xml:space="preserve">2.01863622665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10902309417725</t>
   </si>
   <si>
     <t xml:space="preserve">2.0753493309021</t>
@@ -3374,13 +3374,13 @@
     <t xml:space="preserve">2.18168640136719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24371671676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1799144744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12320113182068</t>
+    <t xml:space="preserve">2.24371647834778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17991423606873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1232008934021</t>
   </si>
   <si>
     <t xml:space="preserve">2.14624047279358</t>
@@ -3389,37 +3389,37 @@
     <t xml:space="preserve">2.19763708114624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30574679374695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28625154495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31992506980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34828186035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41740083694458</t>
+    <t xml:space="preserve">2.30574655532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28625130653381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31992483139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34828162193298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.417400598526</t>
   </si>
   <si>
     <t xml:space="preserve">2.4457573890686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38372778892517</t>
+    <t xml:space="preserve">2.38372755050659</t>
   </si>
   <si>
     <t xml:space="preserve">2.46348023414612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42449021339417</t>
+    <t xml:space="preserve">2.42448997497559</t>
   </si>
   <si>
     <t xml:space="preserve">2.47411417961121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51310443878174</t>
+    <t xml:space="preserve">2.51310420036316</t>
   </si>
   <si>
     <t xml:space="preserve">2.50955986976624</t>
@@ -3428,10 +3428,10 @@
     <t xml:space="preserve">2.43157911300659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4705696105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39613366127014</t>
+    <t xml:space="preserve">2.47056937217712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39613342285156</t>
   </si>
   <si>
     <t xml:space="preserve">2.33942031860352</t>
@@ -3440,70 +3440,70 @@
     <t xml:space="preserve">2.37841033935547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21004295349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38904428482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47943115234375</t>
+    <t xml:space="preserve">2.21004319190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38904452323914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47943091392517</t>
   </si>
   <si>
     <t xml:space="preserve">2.4918372631073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56095600128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6566596031189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64070916175842</t>
+    <t xml:space="preserve">2.56095623970032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65665984153748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.640709400177</t>
   </si>
   <si>
     <t xml:space="preserve">2.63184785842896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65311503410339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59640192985535</t>
+    <t xml:space="preserve">2.65311479568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59640216827393</t>
   </si>
   <si>
     <t xml:space="preserve">2.52373814582825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33233094215393</t>
+    <t xml:space="preserve">2.33233070373535</t>
   </si>
   <si>
     <t xml:space="preserve">2.31815266609192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29688501358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28270721435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27561783790588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25966739654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30929112434387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27916216850281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28802394866943</t>
+    <t xml:space="preserve">2.2968852519989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28270697593689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27561807632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25966715812683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30929136276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27916240692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28802371025085</t>
   </si>
   <si>
     <t xml:space="preserve">2.26852869987488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36600470542908</t>
+    <t xml:space="preserve">2.36600494384766</t>
   </si>
   <si>
     <t xml:space="preserve">2.30751919746399</t>
@@ -3512,22 +3512,22 @@
     <t xml:space="preserve">2.24017214775085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14978551864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16041922569275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17459726333618</t>
+    <t xml:space="preserve">2.14978528022766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16041898727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17459750175476</t>
   </si>
   <si>
     <t xml:space="preserve">2.13915181159973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15687441825867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05762648582458</t>
+    <t xml:space="preserve">2.15687465667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05762624740601</t>
   </si>
   <si>
     <t xml:space="preserve">2.16928052902222</t>
@@ -3536,10 +3536,10 @@
     <t xml:space="preserve">2.1958646774292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13560700416565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39258861541748</t>
+    <t xml:space="preserve">2.13560724258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39258885383606</t>
   </si>
   <si>
     <t xml:space="preserve">2.39436101913452</t>
@@ -3548,13 +3548,13 @@
     <t xml:space="preserve">2.06648778915405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99382388591766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12142872810364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11965656280518</t>
+    <t xml:space="preserve">1.99382412433624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12142896652222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1196563243866</t>
   </si>
   <si>
     <t xml:space="preserve">2.09484457969666</t>
@@ -3563,19 +3563,19 @@
     <t xml:space="preserve">2.01331901550293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08066630363464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9920517206192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03458690643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0292694568634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93179404735565</t>
+    <t xml:space="preserve">2.08066606521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99205148220062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03458666801453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02926993370056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93179392814636</t>
   </si>
   <si>
     <t xml:space="preserve">2.01509141921997</t>
@@ -3584,10 +3584,10 @@
     <t xml:space="preserve">2.00445795059204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86799156665802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90166485309601</t>
+    <t xml:space="preserve">1.86799168586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9016649723053</t>
   </si>
   <si>
     <t xml:space="preserve">1.80596160888672</t>
@@ -3605,10 +3605,10 @@
     <t xml:space="preserve">1.6801290512085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57999491691589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59505927562714</t>
+    <t xml:space="preserve">1.5799947977066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59505903720856</t>
   </si>
   <si>
     <t xml:space="preserve">1.65974771976471</t>
@@ -3617,13 +3617,13 @@
     <t xml:space="preserve">1.78646636009216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75545144081116</t>
+    <t xml:space="preserve">1.75545120239258</t>
   </si>
   <si>
     <t xml:space="preserve">1.73684227466583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73418378829956</t>
+    <t xml:space="preserve">1.73418390750885</t>
   </si>
   <si>
     <t xml:space="preserve">1.70671331882477</t>
@@ -3635,16 +3635,16 @@
     <t xml:space="preserve">1.66595077514648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67924284934998</t>
+    <t xml:space="preserve">1.67924296855927</t>
   </si>
   <si>
     <t xml:space="preserve">1.72798085212708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86444711685181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83431804180145</t>
+    <t xml:space="preserve">1.8644472360611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83431816101074</t>
   </si>
   <si>
     <t xml:space="preserve">1.74570369720459</t>
@@ -3653,19 +3653,19 @@
     <t xml:space="preserve">1.78469407558441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76254034042358</t>
+    <t xml:space="preserve">1.76254045963287</t>
   </si>
   <si>
     <t xml:space="preserve">1.72886693477631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67038142681122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64113879203796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60126233100891</t>
+    <t xml:space="preserve">1.67038154602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64113867282867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6012624502182</t>
   </si>
   <si>
     <t xml:space="preserve">1.61987113952637</t>
@@ -3674,10 +3674,10 @@
     <t xml:space="preserve">1.71025788784027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70051038265228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67835676670074</t>
+    <t xml:space="preserve">1.70051050186157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67835688591003</t>
   </si>
   <si>
     <t xml:space="preserve">1.62961876392365</t>
@@ -3686,13 +3686,13 @@
     <t xml:space="preserve">1.63936650753021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63050496578217</t>
+    <t xml:space="preserve">1.63050508499146</t>
   </si>
   <si>
     <t xml:space="preserve">1.60923755168915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62075734138489</t>
+    <t xml:space="preserve">1.62075746059418</t>
   </si>
   <si>
     <t xml:space="preserve">1.55075204372406</t>
@@ -3704,7 +3704,7 @@
     <t xml:space="preserve">1.47897434234619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54189074039459</t>
+    <t xml:space="preserve">1.54189050197601</t>
   </si>
   <si>
     <t xml:space="preserve">1.60835134983063</t>
@@ -3716,7 +3716,7 @@
     <t xml:space="preserve">1.64468324184418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6074652671814</t>
+    <t xml:space="preserve">1.60746514797211</t>
   </si>
   <si>
     <t xml:space="preserve">1.6003760099411</t>
@@ -3725,25 +3725,25 @@
     <t xml:space="preserve">1.52594006061554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52150928974152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6313910484314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64734172821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72266399860382</t>
+    <t xml:space="preserve">1.52150940895081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63139092922211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64734184741974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72266387939453</t>
   </si>
   <si>
     <t xml:space="preserve">1.690762758255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71646094322205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78114938735962</t>
+    <t xml:space="preserve">1.71646106243134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78114950656891</t>
   </si>
   <si>
     <t xml:space="preserve">1.84495174884796</t>
@@ -3755,7 +3755,7 @@
     <t xml:space="preserve">1.79887235164642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79532790184021</t>
+    <t xml:space="preserve">1.79532778263092</t>
   </si>
   <si>
     <t xml:space="preserve">1.65797543525696</t>
@@ -3767,22 +3767,22 @@
     <t xml:space="preserve">1.41871654987335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46506798267365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4768830537796</t>
+    <t xml:space="preserve">1.46506786346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47688293457031</t>
   </si>
   <si>
     <t xml:space="preserve">1.48960697650909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45779705047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47597408294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43689346313477</t>
+    <t xml:space="preserve">1.45779716968536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47597420215607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43689358234406</t>
   </si>
   <si>
     <t xml:space="preserve">1.47415637969971</t>
@@ -3800,13 +3800,13 @@
     <t xml:space="preserve">1.37872707843781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30147480964661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32783138751984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37418282032013</t>
+    <t xml:space="preserve">1.30147469043732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32783150672913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37418270111084</t>
   </si>
   <si>
     <t xml:space="preserve">1.40781033039093</t>
@@ -3818,22 +3818,22 @@
     <t xml:space="preserve">1.31510758399963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28420650959015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27966225147247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30874574184418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32692265510559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39781296253204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37145626544952</t>
+    <t xml:space="preserve">1.28420662879944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27966237068176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30874562263489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3269225358963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39781284332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37145614624023</t>
   </si>
   <si>
     <t xml:space="preserve">1.3578234910965</t>
@@ -3845,7 +3845,7 @@
     <t xml:space="preserve">1.29693043231964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31328976154327</t>
+    <t xml:space="preserve">1.31328988075256</t>
   </si>
   <si>
     <t xml:space="preserve">1.33328449726105</t>
@@ -3863,7 +3863,7 @@
     <t xml:space="preserve">1.44416439533234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46961212158203</t>
+    <t xml:space="preserve">1.46961200237274</t>
   </si>
   <si>
     <t xml:space="preserve">1.45961475372314</t>
@@ -3872,7 +3872,7 @@
     <t xml:space="preserve">1.48778915405273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49506008625031</t>
+    <t xml:space="preserve">1.49505996704102</t>
   </si>
   <si>
     <t xml:space="preserve">1.48869812488556</t>
@@ -3887,10 +3887,10 @@
     <t xml:space="preserve">1.50051307678223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48051834106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40326607227325</t>
+    <t xml:space="preserve">1.48051846027374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40326619148254</t>
   </si>
   <si>
     <t xml:space="preserve">1.43234932422638</t>
@@ -3902,46 +3902,46 @@
     <t xml:space="preserve">1.34691727161407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34328198432922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3732738494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3760005235672</t>
+    <t xml:space="preserve">1.34328186511993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37327396869659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37600040435791</t>
   </si>
   <si>
     <t xml:space="preserve">1.36236774921417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39235985279083</t>
+    <t xml:space="preserve">1.39235973358154</t>
   </si>
   <si>
     <t xml:space="preserve">1.33601105213165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35237038135529</t>
+    <t xml:space="preserve">1.35237050056458</t>
   </si>
   <si>
     <t xml:space="preserve">1.36963856220245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35964119434357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41326344013214</t>
+    <t xml:space="preserve">1.35964131355286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41326332092285</t>
   </si>
   <si>
     <t xml:space="preserve">1.43507587909698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41689884662628</t>
+    <t xml:space="preserve">1.41689896583557</t>
   </si>
   <si>
     <t xml:space="preserve">1.46870338916779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41235458850861</t>
+    <t xml:space="preserve">1.4123547077179</t>
   </si>
   <si>
     <t xml:space="preserve">1.39872181415558</t>
@@ -3965,10 +3965,10 @@
     <t xml:space="preserve">1.56322383880615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49960422515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55777072906494</t>
+    <t xml:space="preserve">1.4996041059494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55777084827423</t>
   </si>
   <si>
     <t xml:space="preserve">1.55231761932373</t>
@@ -3977,16 +3977,16 @@
     <t xml:space="preserve">1.64956474304199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58140099048615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53777599334717</t>
+    <t xml:space="preserve">1.58140087127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53777611255646</t>
   </si>
   <si>
     <t xml:space="preserve">1.52323436737061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56049728393555</t>
+    <t xml:space="preserve">1.56049740314484</t>
   </si>
   <si>
     <t xml:space="preserve">1.53323185443878</t>
@@ -4007,37 +4007,37 @@
     <t xml:space="preserve">1.65865325927734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65956199169159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6704683303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7631710767746</t>
+    <t xml:space="preserve">1.65956211090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67046821117401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76317119598389</t>
   </si>
   <si>
     <t xml:space="preserve">1.79225432872772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78861904144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73045241832733</t>
+    <t xml:space="preserve">1.78861892223358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73045253753662</t>
   </si>
   <si>
     <t xml:space="preserve">1.71772849559784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72681701183319</t>
+    <t xml:space="preserve">1.72681713104248</t>
   </si>
   <si>
     <t xml:space="preserve">1.77135074138641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73136126995087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75135600566864</t>
+    <t xml:space="preserve">1.73136138916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75135612487793</t>
   </si>
   <si>
     <t xml:space="preserve">1.78771007061005</t>
@@ -4046,16 +4046,16 @@
     <t xml:space="preserve">1.84860301017761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8667801618576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87223327159882</t>
+    <t xml:space="preserve">1.86678004264832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87223315238953</t>
   </si>
   <si>
     <t xml:space="preserve">1.89949882030487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93403518199921</t>
+    <t xml:space="preserve">1.93403506278992</t>
   </si>
   <si>
     <t xml:space="preserve">1.94494140148163</t>
@@ -4064,31 +4064,31 @@
     <t xml:space="preserve">1.90676963329315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9540296792984</t>
+    <t xml:space="preserve">1.95402979850769</t>
   </si>
   <si>
     <t xml:space="preserve">1.97038900852203</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00492548942566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99583685398102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97220683097839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97402465343475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99038398265839</t>
+    <t xml:space="preserve">2.00492525100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99583697319031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97220695018768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97402453422546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9903838634491</t>
   </si>
   <si>
     <t xml:space="preserve">2.04491496086121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13398265838623</t>
+    <t xml:space="preserve">2.13398241996765</t>
   </si>
   <si>
     <t xml:space="preserve">2.15397691726685</t>
@@ -4100,55 +4100,55 @@
     <t xml:space="preserve">2.11944079399109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13761782646179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16851878166199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11035203933716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10308146476746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10126399993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97584235668182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02128481864929</t>
+    <t xml:space="preserve">2.13761758804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16851854324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11035227775574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10308122634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10126376152039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97584247589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02128505706787</t>
   </si>
   <si>
     <t xml:space="preserve">1.85223865509033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89041018486023</t>
+    <t xml:space="preserve">1.89041006565094</t>
   </si>
   <si>
     <t xml:space="preserve">1.91222286224365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92676424980164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93585300445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93948817253113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90131664276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91404044628143</t>
+    <t xml:space="preserve">1.92676436901093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93585288524628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93948805332184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90131652355194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91404032707214</t>
   </si>
   <si>
     <t xml:space="preserve">1.96311855316162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96857130527496</t>
+    <t xml:space="preserve">1.96857118606567</t>
   </si>
   <si>
     <t xml:space="preserve">2.03219103813171</t>
@@ -4157,7 +4157,7 @@
     <t xml:space="preserve">2.05945658683777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10489916801453</t>
+    <t xml:space="preserve">2.10489892959595</t>
   </si>
   <si>
     <t xml:space="preserve">2.12852907180786</t>
@@ -4175,22 +4175,22 @@
     <t xml:space="preserve">2.07218050956726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06309175491333</t>
+    <t xml:space="preserve">2.06309199333191</t>
   </si>
   <si>
     <t xml:space="preserve">2.03764414787292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00310778617859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01219630241394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01764941215515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00129008293152</t>
+    <t xml:space="preserve">2.00310754776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01219654083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01764965057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00128984451294</t>
   </si>
   <si>
     <t xml:space="preserve">2.27394556999207</t>
@@ -4199,13 +4199,13 @@
     <t xml:space="preserve">2.2484974861145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31757020950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30848169326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33211159706116</t>
+    <t xml:space="preserve">2.31757044792175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3084819316864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33211183547974</t>
   </si>
   <si>
     <t xml:space="preserve">2.37210130691528</t>
@@ -4229,13 +4229,13 @@
     <t xml:space="preserve">2.39209580421448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35755968093872</t>
+    <t xml:space="preserve">2.3575599193573</t>
   </si>
   <si>
     <t xml:space="preserve">2.34483551979065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30666422843933</t>
+    <t xml:space="preserve">2.30666399002075</t>
   </si>
   <si>
     <t xml:space="preserve">2.3157525062561</t>
@@ -4259,10 +4259,10 @@
     <t xml:space="preserve">2.39027833938599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37937211990356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32302331924438</t>
+    <t xml:space="preserve">2.37937188148499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32302355766296</t>
   </si>
   <si>
     <t xml:space="preserve">2.28666949272156</t>
@@ -4277,13 +4277,13 @@
     <t xml:space="preserve">2.18306016921997</t>
   </si>
   <si>
-    <t xml:space="preserve">2.143070936203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20487284660339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20669031143188</t>
+    <t xml:space="preserve">2.14307069778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20487260818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20669007301331</t>
   </si>
   <si>
     <t xml:space="preserve">2.17033648490906</t>
@@ -4292,7 +4292,7 @@
     <t xml:space="preserve">2.13943552970886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14670634269714</t>
+    <t xml:space="preserve">2.14670610427856</t>
   </si>
   <si>
     <t xml:space="preserve">2.14852404594421</t>
@@ -4301,49 +4301,49 @@
     <t xml:space="preserve">2.19578409194946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19033098220825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26849222183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24667978286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24304461479187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25213289260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30121088027954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28303408622742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34120059013367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47934579849243</t>
+    <t xml:space="preserve">2.19033122062683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26849246025085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24667954444885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24304437637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25213265419006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30121064186096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28303384780884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34120035171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47934556007385</t>
   </si>
   <si>
     <t xml:space="preserve">2.44844484329224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4884340763092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46843934059143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47207474708557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45935106277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45753335952759</t>
+    <t xml:space="preserve">2.48843383789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46843957901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47207498550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45935130119324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45753359794617</t>
   </si>
   <si>
     <t xml:space="preserve">2.43390297889709</t>
@@ -4358,7 +4358,7 @@
     <t xml:space="preserve">2.50297570228577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47025680541992</t>
+    <t xml:space="preserve">2.4702570438385</t>
   </si>
   <si>
     <t xml:space="preserve">2.40118432044983</t>
@@ -4367,7 +4367,7 @@
     <t xml:space="preserve">2.36664843559265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41754388809204</t>
+    <t xml:space="preserve">2.41754412651062</t>
   </si>
   <si>
     <t xml:space="preserve">2.2793984413147</t>
@@ -4379,16 +4379,16 @@
     <t xml:space="preserve">2.29212236404419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27031016349792</t>
+    <t xml:space="preserve">2.27030992507935</t>
   </si>
   <si>
     <t xml:space="preserve">2.22668528556824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30302834510803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32484126091003</t>
+    <t xml:space="preserve">2.30302858352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32484102249146</t>
   </si>
   <si>
     <t xml:space="preserve">2.33029389381409</t>
@@ -4397,19 +4397,19 @@
     <t xml:space="preserve">2.29939317703247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41936159133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4320855140686</t>
+    <t xml:space="preserve">2.41936135292053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43208575248718</t>
   </si>
   <si>
     <t xml:space="preserve">2.42117929458618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43935632705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25599431991577</t>
+    <t xml:space="preserve">2.43935608863831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25599455833435</t>
   </si>
   <si>
     <t xml:space="preserve">2.28207540512085</t>
@@ -4418,13 +4418,13 @@
     <t xml:space="preserve">2.27462339401245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24854278564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22991371154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30070471763611</t>
+    <t xml:space="preserve">2.24854302406311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22991347312927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30070447921753</t>
   </si>
   <si>
     <t xml:space="preserve">2.31188225746155</t>
@@ -4439,25 +4439,25 @@
     <t xml:space="preserve">2.36404395103455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29697895050049</t>
+    <t xml:space="preserve">2.29697871208191</t>
   </si>
   <si>
     <t xml:space="preserve">2.32678556442261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34168863296509</t>
+    <t xml:space="preserve">2.34168839454651</t>
   </si>
   <si>
     <t xml:space="preserve">2.33982586860657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36963248252869</t>
+    <t xml:space="preserve">2.36963224411011</t>
   </si>
   <si>
     <t xml:space="preserve">2.36776971817017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32864856719971</t>
+    <t xml:space="preserve">2.32864832878113</t>
   </si>
   <si>
     <t xml:space="preserve">2.29884171485901</t>
@@ -4478,13 +4478,13 @@
     <t xml:space="preserve">2.29325270652771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33051133155823</t>
+    <t xml:space="preserve">2.33051156997681</t>
   </si>
   <si>
     <t xml:space="preserve">2.31374502182007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28952670097351</t>
+    <t xml:space="preserve">2.28952693939209</t>
   </si>
   <si>
     <t xml:space="preserve">2.22432494163513</t>
@@ -4493,7 +4493,7 @@
     <t xml:space="preserve">2.20569562911987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16098546981812</t>
+    <t xml:space="preserve">2.16098570823669</t>
   </si>
   <si>
     <t xml:space="preserve">2.14049363136292</t>
@@ -4523,7 +4523,7 @@
     <t xml:space="preserve">2.04921054840088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08460593223572</t>
+    <t xml:space="preserve">2.08460569381714</t>
   </si>
   <si>
     <t xml:space="preserve">2.06411385536194</t>
@@ -4559,7 +4559,7 @@
     <t xml:space="preserve">2.01754069328308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9989116191864</t>
+    <t xml:space="preserve">1.99891173839569</t>
   </si>
   <si>
     <t xml:space="preserve">2.01195240020752</t>
@@ -4574,7 +4574,7 @@
     <t xml:space="preserve">1.97469365596771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95606446266174</t>
+    <t xml:space="preserve">1.95606434345245</t>
   </si>
   <si>
     <t xml:space="preserve">1.92625784873962</t>
@@ -4583,13 +4583,13 @@
     <t xml:space="preserve">1.86478161811829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77349853515625</t>
+    <t xml:space="preserve">1.77349865436554</t>
   </si>
   <si>
     <t xml:space="preserve">1.78095018863678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78467607498169</t>
+    <t xml:space="preserve">1.7846759557724</t>
   </si>
   <si>
     <t xml:space="preserve">1.80330526828766</t>
@@ -4601,7 +4601,7 @@
     <t xml:space="preserve">1.80237364768982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75673222541809</t>
+    <t xml:space="preserve">1.75673234462738</t>
   </si>
   <si>
     <t xml:space="preserve">1.71109080314636</t>
@@ -4619,10 +4619,10 @@
     <t xml:space="preserve">1.69991326332092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6663806438446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61608183383942</t>
+    <t xml:space="preserve">1.66638076305389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61608195304871</t>
   </si>
   <si>
     <t xml:space="preserve">1.63005375862122</t>
@@ -4661,37 +4661,37 @@
     <t xml:space="preserve">1.55646860599518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56485152244568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57975494861603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61887633800507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60117852687836</t>
+    <t xml:space="preserve">1.56485164165497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57975506782532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61887621879578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60117840766907</t>
   </si>
   <si>
     <t xml:space="preserve">1.60956168174744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61980783939362</t>
+    <t xml:space="preserve">1.61980772018433</t>
   </si>
   <si>
     <t xml:space="preserve">1.62819087505341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59745275974274</t>
+    <t xml:space="preserve">1.59745287895203</t>
   </si>
   <si>
     <t xml:space="preserve">1.6123560667038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62073934078217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67755830287933</t>
+    <t xml:space="preserve">1.62073922157288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67755818367004</t>
   </si>
   <si>
     <t xml:space="preserve">1.64123129844666</t>
@@ -4700,10 +4700,10 @@
     <t xml:space="preserve">1.65706610679626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68966722488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69153022766113</t>
+    <t xml:space="preserve">1.68966710567474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69153010845184</t>
   </si>
   <si>
     <t xml:space="preserve">1.66917514801025</t>
@@ -4721,7 +4721,7 @@
     <t xml:space="preserve">1.72785711288452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84242641925812</t>
+    <t xml:space="preserve">1.84242653846741</t>
   </si>
   <si>
     <t xml:space="preserve">1.84801530838013</t>
@@ -4733,13 +4733,13 @@
     <t xml:space="preserve">1.92998373508453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97655689716339</t>
+    <t xml:space="preserve">1.9765567779541</t>
   </si>
   <si>
     <t xml:space="preserve">1.96165335178375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91508030891418</t>
+    <t xml:space="preserve">1.91508042812347</t>
   </si>
   <si>
     <t xml:space="preserve">1.93557250499725</t>
@@ -4775,7 +4775,7 @@
     <t xml:space="preserve">2.11441254615784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10137224197388</t>
+    <t xml:space="preserve">2.1013720035553</t>
   </si>
   <si>
     <t xml:space="preserve">2.03617000579834</t>
@@ -4790,25 +4790,25 @@
     <t xml:space="preserve">2.01008915901184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01567816734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98214554786682</t>
+    <t xml:space="preserve">2.01567792892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98214542865753</t>
   </si>
   <si>
     <t xml:space="preserve">1.90017700195312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91694343090057</t>
+    <t xml:space="preserve">1.91694331169128</t>
   </si>
   <si>
     <t xml:space="preserve">1.8927253484726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92812073230743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95420169830322</t>
+    <t xml:space="preserve">1.92812085151672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95420157909393</t>
   </si>
   <si>
     <t xml:space="preserve">2.06783962249756</t>
@@ -4817,7 +4817,7 @@
     <t xml:space="preserve">2.03989601135254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0752911567688</t>
+    <t xml:space="preserve">2.07529139518738</t>
   </si>
   <si>
     <t xml:space="preserve">2.09578347206116</t>
@@ -5913,6 +5913,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.37200021743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34999990463257</t>
   </si>
 </sst>
 </file>
@@ -20101,7 +20104,7 @@
         <v>5.6275200843811</v>
       </c>
       <c r="G533" t="s">
-        <v>363</v>
+        <v>260</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -20179,7 +20182,7 @@
         <v>5.40128803253174</v>
       </c>
       <c r="G536" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -20205,7 +20208,7 @@
         <v>5.28817176818848</v>
       </c>
       <c r="G537" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -20309,7 +20312,7 @@
         <v>5.19862222671509</v>
       </c>
       <c r="G541" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -20335,7 +20338,7 @@
         <v>5.18448209762573</v>
       </c>
       <c r="G542" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -20361,7 +20364,7 @@
         <v>5.20804786682129</v>
       </c>
       <c r="G543" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -20387,7 +20390,7 @@
         <v>5.22690105438232</v>
       </c>
       <c r="G544" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -20413,7 +20416,7 @@
         <v>5.31173801422119</v>
       </c>
       <c r="G545" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -20465,7 +20468,7 @@
         <v>5.17505598068237</v>
       </c>
       <c r="G547" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -20491,7 +20494,7 @@
         <v>5.13735103607178</v>
       </c>
       <c r="G548" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -20517,7 +20520,7 @@
         <v>5.13735103607178</v>
       </c>
       <c r="G549" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -20543,7 +20546,7 @@
         <v>5.12321090698242</v>
       </c>
       <c r="G550" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -20569,7 +20572,7 @@
         <v>5.19862222671509</v>
       </c>
       <c r="G551" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -20595,7 +20598,7 @@
         <v>5.16562986373901</v>
       </c>
       <c r="G552" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -20621,7 +20624,7 @@
         <v>5.06665277481079</v>
       </c>
       <c r="G553" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -20647,7 +20650,7 @@
         <v>4.9771032333374</v>
       </c>
       <c r="G554" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -20673,7 +20676,7 @@
         <v>5.014808177948</v>
       </c>
       <c r="G555" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -20699,7 +20702,7 @@
         <v>5.07136583328247</v>
       </c>
       <c r="G556" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -20725,7 +20728,7 @@
         <v>5.04780006408691</v>
       </c>
       <c r="G557" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -20751,7 +20754,7 @@
         <v>5.09964513778687</v>
       </c>
       <c r="G558" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -20777,7 +20780,7 @@
         <v>5.15620279312134</v>
       </c>
       <c r="G559" t="s">
-        <v>77</v>
+        <v>380</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -20803,7 +20806,7 @@
         <v>5.12321090698242</v>
       </c>
       <c r="G560" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -20959,7 +20962,7 @@
         <v>5.16562986373901</v>
       </c>
       <c r="G566" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -20985,7 +20988,7 @@
         <v>5.19862222671509</v>
       </c>
       <c r="G567" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -71277,7 +71280,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6910185185</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>309204</v>
@@ -71298,6 +71301,32 @@
         <v>1966</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6913078704</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>315640</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>4.38600015640259</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>4.32600021362305</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>4.35200023651123</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>4.34999990463257</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>1967</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/OVS.MI.xlsx
+++ b/data/OVS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1968" uniqueCount="1968">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1969" uniqueCount="1969">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,16 +44,16 @@
     <t xml:space="preserve">OVS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89862489700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76365375518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64456224441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71998739242554</t>
+    <t xml:space="preserve">4.89862442016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76365423202515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64456272125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71998691558838</t>
   </si>
   <si>
     <t xml:space="preserve">4.65647077560425</t>
@@ -62,13 +62,13 @@
     <t xml:space="preserve">4.78747224807739</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94228982925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69219827651978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6048641204834</t>
+    <t xml:space="preserve">4.94229030609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69219875335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60486507415771</t>
   </si>
   <si>
     <t xml:space="preserve">4.63662338256836</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">4.25156021118164</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22774219512939</t>
+    <t xml:space="preserve">4.22774171829224</t>
   </si>
   <si>
     <t xml:space="preserve">4.53341007232666</t>
@@ -89,19 +89,19 @@
     <t xml:space="preserve">4.45798540115356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47783422470093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49768352508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51356172561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4460768699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62868309020996</t>
+    <t xml:space="preserve">4.47783470153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49768257141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5135612487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44607639312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62868356704712</t>
   </si>
   <si>
     <t xml:space="preserve">4.59295654296875</t>
@@ -113,58 +113,58 @@
     <t xml:space="preserve">4.54531955718994</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32698535919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03322601318359</t>
+    <t xml:space="preserve">4.32698631286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03322649002075</t>
   </si>
   <si>
     <t xml:space="preserve">4.02925682067871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27934837341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22377300262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38256120681763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30316686630249</t>
+    <t xml:space="preserve">4.27934885025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22377252578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38256168365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30316734313965</t>
   </si>
   <si>
     <t xml:space="preserve">4.46989488601685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46592473983765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48577404022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48974323272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27140951156616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23965215682983</t>
+    <t xml:space="preserve">4.4659252166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48577356338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48974275588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.271409034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23965120315552</t>
   </si>
   <si>
     <t xml:space="preserve">4.43813705444336</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56516933441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67235040664673</t>
+    <t xml:space="preserve">4.5651683807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67235088348389</t>
   </si>
   <si>
     <t xml:space="preserve">4.71601724624634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58898639678955</t>
+    <t xml:space="preserve">4.58898687362671</t>
   </si>
   <si>
     <t xml:space="preserve">4.50562238693237</t>
@@ -173,73 +173,73 @@
     <t xml:space="preserve">4.52547121047974</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38653039932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43019771575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40240955352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29125833511353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12055969238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09674263000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0649847984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08880281448364</t>
+    <t xml:space="preserve">4.38653087615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43019819259644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40241003036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29125785827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12056064605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09674215316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06498432159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08880233764648</t>
   </si>
   <si>
     <t xml:space="preserve">4.15628719329834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21186351776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04910564422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02131748199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31110620498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16422748565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23568153381348</t>
+    <t xml:space="preserve">4.21186447143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04910516738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02131700515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31110572814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16422700881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23568201065063</t>
   </si>
   <si>
     <t xml:space="preserve">4.50959157943726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73586654663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54928970336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50165224075317</t>
+    <t xml:space="preserve">4.7358660697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54928922653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50165271759033</t>
   </si>
   <si>
     <t xml:space="preserve">4.56119823455811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48180437088013</t>
+    <t xml:space="preserve">4.48180341720581</t>
   </si>
   <si>
     <t xml:space="preserve">4.5215015411377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55325841903687</t>
+    <t xml:space="preserve">4.55325889587402</t>
   </si>
   <si>
     <t xml:space="preserve">4.5413498878479</t>
@@ -248,16 +248,16 @@
     <t xml:space="preserve">4.56913757324219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53737878799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64853239059448</t>
+    <t xml:space="preserve">4.5373797416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64853191375732</t>
   </si>
   <si>
     <t xml:space="preserve">4.70410776138306</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84304809570312</t>
+    <t xml:space="preserve">4.84304761886597</t>
   </si>
   <si>
     <t xml:space="preserve">4.89068412780762</t>
@@ -266,10 +266,10 @@
     <t xml:space="preserve">4.81525993347168</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87877511978149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91053247451782</t>
+    <t xml:space="preserve">4.87877559661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91053295135498</t>
   </si>
   <si>
     <t xml:space="preserve">4.75968360900879</t>
@@ -281,10 +281,10 @@
     <t xml:space="preserve">4.7667875289917</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90123510360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7341947555542</t>
+    <t xml:space="preserve">4.90123558044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73419427871704</t>
   </si>
   <si>
     <t xml:space="preserve">4.5671534538269</t>
@@ -293,22 +293,22 @@
     <t xml:space="preserve">4.51826286315918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4734468460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47752046585083</t>
+    <t xml:space="preserve">4.47344636917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47752094268799</t>
   </si>
   <si>
     <t xml:space="preserve">4.48974418640137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63233947753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61196851730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55085611343384</t>
+    <t xml:space="preserve">4.6323390007019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61196899414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55085563659668</t>
   </si>
   <si>
     <t xml:space="preserve">4.51418924331665</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">4.13528966903687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24529314041138</t>
+    <t xml:space="preserve">4.24529361724854</t>
   </si>
   <si>
     <t xml:space="preserve">4.26566314697266</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">4.25751543045044</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11084413528442</t>
+    <t xml:space="preserve">4.11084461212158</t>
   </si>
   <si>
     <t xml:space="preserve">4.09047412872314</t>
@@ -347,22 +347,22 @@
     <t xml:space="preserve">4.18825387954712</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16380882263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15566062927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15973424911499</t>
+    <t xml:space="preserve">4.16380929946899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15566110610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15973472595215</t>
   </si>
   <si>
     <t xml:space="preserve">4.10677099227905</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04321384429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1189923286438</t>
+    <t xml:space="preserve">4.04321432113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11899280548096</t>
   </si>
   <si>
     <t xml:space="preserve">4.16788291931152</t>
@@ -371,91 +371,91 @@
     <t xml:space="preserve">4.26158952713013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2004771232605</t>
+    <t xml:space="preserve">4.20047760009766</t>
   </si>
   <si>
     <t xml:space="preserve">4.20862483978271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23307037353516</t>
+    <t xml:space="preserve">4.233069896698</t>
   </si>
   <si>
     <t xml:space="preserve">4.37159299850464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36751842498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28603410720825</t>
+    <t xml:space="preserve">4.36751794815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28603363037109</t>
   </si>
   <si>
     <t xml:space="preserve">4.27788591384888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24121809005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25344085693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29825735092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22899580001831</t>
+    <t xml:space="preserve">4.24121856689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25344133377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29825782775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22899627685547</t>
   </si>
   <si>
     <t xml:space="preserve">4.0725474357605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17195796966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19232749938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10269641876221</t>
+    <t xml:space="preserve">4.17195749282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19232797622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10269737243652</t>
   </si>
   <si>
     <t xml:space="preserve">4.04158353805542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13936424255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09862232208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00084161758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99269390106201</t>
+    <t xml:space="preserve">4.13936376571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09862279891968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00084209442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99269413948059</t>
   </si>
   <si>
     <t xml:space="preserve">4.0334358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19640302658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15158605575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0863995552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06114053726196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35936975479126</t>
+    <t xml:space="preserve">4.19640254974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15158700942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08640003204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06114101409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35937023162842</t>
   </si>
   <si>
     <t xml:space="preserve">4.37566661834717</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44085311889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41233348846436</t>
+    <t xml:space="preserve">4.44085454940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41233444213867</t>
   </si>
   <si>
     <t xml:space="preserve">4.31862831115723</t>
@@ -467,13 +467,13 @@
     <t xml:space="preserve">4.31455326080322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26973724365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21677303314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1801061630249</t>
+    <t xml:space="preserve">4.26973819732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21677398681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18010568618774</t>
   </si>
   <si>
     <t xml:space="preserve">4.14343786239624</t>
@@ -488,46 +488,46 @@
     <t xml:space="preserve">4.06928825378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08232593536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06439876556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00573110580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96010065078735</t>
+    <t xml:space="preserve">4.08232498168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06440019607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00573062896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96010041236877</t>
   </si>
   <si>
     <t xml:space="preserve">4.05462121963501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13121604919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04647254943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98128581047058</t>
+    <t xml:space="preserve">4.13121557235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04647302627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98128533363342</t>
   </si>
   <si>
     <t xml:space="preserve">4.00410175323486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98617482185364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02528810501099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97476744651794</t>
+    <t xml:space="preserve">3.98617577552795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02528762817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97476696968079</t>
   </si>
   <si>
     <t xml:space="preserve">4.02365779876709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05950975418091</t>
+    <t xml:space="preserve">4.05951023101807</t>
   </si>
   <si>
     <t xml:space="preserve">4.04810237884521</t>
@@ -536,13 +536,13 @@
     <t xml:space="preserve">4.05136203765869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97965574264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03017568588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02039813995361</t>
+    <t xml:space="preserve">3.97965598106384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03017616271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02039861679077</t>
   </si>
   <si>
     <t xml:space="preserve">3.99921202659607</t>
@@ -551,37 +551,37 @@
     <t xml:space="preserve">4.07825136184692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14751291275024</t>
+    <t xml:space="preserve">4.1475133895874</t>
   </si>
   <si>
     <t xml:space="preserve">4.23714351654053</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20455074310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22492218017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01713895797729</t>
+    <t xml:space="preserve">4.20455121994019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22492170333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01713848114014</t>
   </si>
   <si>
     <t xml:space="preserve">4.02202749252319</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93076586723328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91283965110779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89491319656372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87535691261292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94054484367371</t>
+    <t xml:space="preserve">3.93076658248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91283893585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8949134349823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87535715103149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94054460525513</t>
   </si>
   <si>
     <t xml:space="preserve">3.93402576446533</t>
@@ -590,19 +590,19 @@
     <t xml:space="preserve">3.89654350280762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95521116256714</t>
+    <t xml:space="preserve">3.95521140098572</t>
   </si>
   <si>
     <t xml:space="preserve">4.00247192382812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37974071502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38381385803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39196348190308</t>
+    <t xml:space="preserve">4.37973976135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38381433486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39196300506592</t>
   </si>
   <si>
     <t xml:space="preserve">4.35529565811157</t>
@@ -611,85 +611,85 @@
     <t xml:space="preserve">4.2901086807251</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28196048736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32677602767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29418325424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33899927139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33492422103882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34307336807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46529912948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48159503936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40825986862183</t>
+    <t xml:space="preserve">4.28196001052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3267765045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2941837310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33899831771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33492469787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34307384490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46529865264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48159456253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40825939178467</t>
   </si>
   <si>
     <t xml:space="preserve">4.53863382339478</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55493021011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52641153335571</t>
+    <t xml:space="preserve">4.55493068695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52641105651855</t>
   </si>
   <si>
     <t xml:space="preserve">4.50604009628296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43270492553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59567165374756</t>
+    <t xml:space="preserve">4.43270444869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59567260742188</t>
   </si>
   <si>
     <t xml:space="preserve">4.68530464172363</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67308187484741</t>
+    <t xml:space="preserve">4.67308139801025</t>
   </si>
   <si>
     <t xml:space="preserve">4.60382032394409</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70160102844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85642004013062</t>
+    <t xml:space="preserve">4.70160055160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85641956329346</t>
   </si>
   <si>
     <t xml:space="preserve">4.82382583618164</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77493572235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79938077926636</t>
+    <t xml:space="preserve">4.77493524551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7993803024292</t>
   </si>
   <si>
     <t xml:space="preserve">4.74234294891357</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78308486938477</t>
+    <t xml:space="preserve">4.78308439254761</t>
   </si>
   <si>
     <t xml:space="preserve">4.72604560852051</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77901029586792</t>
+    <t xml:space="preserve">4.77900981903076</t>
   </si>
   <si>
     <t xml:space="preserve">4.80752992630005</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">5.04790592193604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01531267166138</t>
+    <t xml:space="preserve">5.01531219482422</t>
   </si>
   <si>
     <t xml:space="preserve">4.89716100692749</t>
@@ -713,10 +713,10 @@
     <t xml:space="preserve">4.88901329040527</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04383134841919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90531063079834</t>
+    <t xml:space="preserve">5.04383182525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90531015396118</t>
   </si>
   <si>
     <t xml:space="preserve">4.9501256942749</t>
@@ -725,22 +725,22 @@
     <t xml:space="preserve">5.05198001861572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97864484786987</t>
+    <t xml:space="preserve">4.97864532470703</t>
   </si>
   <si>
     <t xml:space="preserve">5.03160905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08457326889038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23939180374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19865036010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14568471908569</t>
+    <t xml:space="preserve">5.08457374572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23939228057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19864988327026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14568519592285</t>
   </si>
   <si>
     <t xml:space="preserve">5.19457578659058</t>
@@ -749,37 +749,37 @@
     <t xml:space="preserve">5.05605459213257</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06420278549194</t>
+    <t xml:space="preserve">5.06420230865479</t>
   </si>
   <si>
     <t xml:space="preserve">5.13346385955811</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11716651916504</t>
+    <t xml:space="preserve">5.11716604232788</t>
   </si>
   <si>
     <t xml:space="preserve">5.25161552429199</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18235397338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17827987670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25568962097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27198505401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17420482635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16605710983276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1864275932312</t>
+    <t xml:space="preserve">5.18235349655151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17828035354614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25568914413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2719841003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17420434951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16605663299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18642807006836</t>
   </si>
   <si>
     <t xml:space="preserve">5.10494470596313</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">5.07235050201416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94605112075806</t>
+    <t xml:space="preserve">4.94605159759521</t>
   </si>
   <si>
     <t xml:space="preserve">5.06827592849731</t>
@@ -797,43 +797,43 @@
     <t xml:space="preserve">4.98679304122925</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03691148757935</t>
+    <t xml:space="preserve">5.03691244125366</t>
   </si>
   <si>
     <t xml:space="preserve">5.36268186569214</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39191818237305</t>
+    <t xml:space="preserve">5.39191770553589</t>
   </si>
   <si>
     <t xml:space="preserve">5.3125638961792</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27915096282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34597587585449</t>
+    <t xml:space="preserve">5.27915000915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34597635269165</t>
   </si>
   <si>
     <t xml:space="preserve">5.35432863235474</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32091617584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33762264251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27079772949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27497434616089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1872673034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13297271728516</t>
+    <t xml:space="preserve">5.32091569900513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33762311935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27079820632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27497386932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18726778030396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.132972240448</t>
   </si>
   <si>
     <t xml:space="preserve">5.2039737701416</t>
@@ -845,7 +845,7 @@
     <t xml:space="preserve">5.25409126281738</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26244497299194</t>
+    <t xml:space="preserve">5.2624454498291</t>
   </si>
   <si>
     <t xml:space="preserve">5.18309116363525</t>
@@ -875,13 +875,13 @@
     <t xml:space="preserve">5.33344650268555</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40444707870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37521171569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40027093887329</t>
+    <t xml:space="preserve">5.40444660186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37521123886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40027046203613</t>
   </si>
   <si>
     <t xml:space="preserve">5.3835654258728</t>
@@ -893,10 +893,10 @@
     <t xml:space="preserve">5.23320960998535</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30838775634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25826930999756</t>
+    <t xml:space="preserve">5.3083872795105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2582688331604</t>
   </si>
   <si>
     <t xml:space="preserve">5.20814990997314</t>
@@ -905,16 +905,16 @@
     <t xml:space="preserve">5.1371488571167</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11208963394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1538553237915</t>
+    <t xml:space="preserve">5.11208915710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15385484695435</t>
   </si>
   <si>
     <t xml:space="preserve">5.23738527297974</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32509326934814</t>
+    <t xml:space="preserve">5.32509279251099</t>
   </si>
   <si>
     <t xml:space="preserve">5.30421018600464</t>
@@ -923,31 +923,31 @@
     <t xml:space="preserve">5.29585695266724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32926893234253</t>
+    <t xml:space="preserve">5.32926940917969</t>
   </si>
   <si>
     <t xml:space="preserve">5.48797845840454</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53809642791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59656810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62580347061157</t>
+    <t xml:space="preserve">5.5380973815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59656763076782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62580394744873</t>
   </si>
   <si>
     <t xml:space="preserve">5.68845272064209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61327505111694</t>
+    <t xml:space="preserve">5.61327457427979</t>
   </si>
   <si>
     <t xml:space="preserve">5.57568550109863</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44203662872314</t>
+    <t xml:space="preserve">5.44203615188599</t>
   </si>
   <si>
     <t xml:space="preserve">5.62162828445435</t>
@@ -956,37 +956,37 @@
     <t xml:space="preserve">5.68009901046753</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64250993728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37103462219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39609336853027</t>
+    <t xml:space="preserve">5.64251089096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37103509902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39609432220459</t>
   </si>
   <si>
     <t xml:space="preserve">5.38774156570435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24156284332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29168128967285</t>
+    <t xml:space="preserve">5.24156188964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29168033599854</t>
   </si>
   <si>
     <t xml:space="preserve">5.19561958312988</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08285331726074</t>
+    <t xml:space="preserve">5.0828537940979</t>
   </si>
   <si>
     <t xml:space="preserve">4.88655614852905</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90743923187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81973123550415</t>
+    <t xml:space="preserve">4.9074387550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81973075866699</t>
   </si>
   <si>
     <t xml:space="preserve">4.80302572250366</t>
@@ -995,34 +995,34 @@
     <t xml:space="preserve">4.84478998184204</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83643770217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94502782821655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9032621383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86567354202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87820339202881</t>
+    <t xml:space="preserve">4.8364372253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94502735137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90326261520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86567306518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87820291519165</t>
   </si>
   <si>
     <t xml:space="preserve">4.8531436920166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81137847900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9575572013855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92832136154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7779655456543</t>
+    <t xml:space="preserve">4.81137800216675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95755767822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92832183837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77796602249146</t>
   </si>
   <si>
     <t xml:space="preserve">4.861496925354</t>
@@ -1037,13 +1037,13 @@
     <t xml:space="preserve">4.66102266311646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69861125946045</t>
+    <t xml:space="preserve">4.69861078262329</t>
   </si>
   <si>
     <t xml:space="preserve">4.6693754196167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63596296310425</t>
+    <t xml:space="preserve">4.63596343994141</t>
   </si>
   <si>
     <t xml:space="preserve">4.70278787612915</t>
@@ -1055,19 +1055,19 @@
     <t xml:space="preserve">4.64014005661011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7194938659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7904953956604</t>
+    <t xml:space="preserve">4.71949434280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79049587249756</t>
   </si>
   <si>
     <t xml:space="preserve">4.74872970581055</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73202419281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71114063262939</t>
+    <t xml:space="preserve">4.7320237159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71114110946655</t>
   </si>
   <si>
     <t xml:space="preserve">4.67772912979126</t>
@@ -1079,10 +1079,10 @@
     <t xml:space="preserve">4.92414426803589</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89490842819214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84061431884766</t>
+    <t xml:space="preserve">4.89490938186646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8406138420105</t>
   </si>
   <si>
     <t xml:space="preserve">5.16220760345459</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">5.17056035995483</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09955978393555</t>
+    <t xml:space="preserve">5.09955930709839</t>
   </si>
   <si>
     <t xml:space="preserve">4.95338106155396</t>
@@ -1106,25 +1106,25 @@
     <t xml:space="preserve">4.7863187789917</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68608140945435</t>
+    <t xml:space="preserve">4.6860818862915</t>
   </si>
   <si>
     <t xml:space="preserve">4.60672807693481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59419822692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6150803565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63178777694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70696496963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58584451675415</t>
+    <t xml:space="preserve">4.59419775009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61508083343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63178682327271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70696449279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58584499359131</t>
   </si>
   <si>
     <t xml:space="preserve">4.55243301391602</t>
@@ -1139,22 +1139,22 @@
     <t xml:space="preserve">4.48978424072266</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41043043136597</t>
+    <t xml:space="preserve">4.41042995452881</t>
   </si>
   <si>
     <t xml:space="preserve">4.44384241104126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49396085739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47307777404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51902055740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5691385269165</t>
+    <t xml:space="preserve">4.49395990371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47307825088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51902008056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56913805007935</t>
   </si>
   <si>
     <t xml:space="preserve">4.59002113342285</t>
@@ -1163,16 +1163,16 @@
     <t xml:space="preserve">4.65684604644775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64849233627319</t>
+    <t xml:space="preserve">4.64849281311035</t>
   </si>
   <si>
     <t xml:space="preserve">4.59837436676025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56078577041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48560810089111</t>
+    <t xml:space="preserve">4.5607852935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48560857772827</t>
   </si>
   <si>
     <t xml:space="preserve">4.43966579437256</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">4.16150760650635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15148496627808</t>
+    <t xml:space="preserve">4.15148448944092</t>
   </si>
   <si>
     <t xml:space="preserve">4.15649604797363</t>
@@ -1208,10 +1208,10 @@
     <t xml:space="preserve">4.10303640365601</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12642621994019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16986179351807</t>
+    <t xml:space="preserve">4.12642526626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16986131668091</t>
   </si>
   <si>
     <t xml:space="preserve">4.17654418945312</t>
@@ -1220,13 +1220,13 @@
     <t xml:space="preserve">4.14313077926636</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16819000244141</t>
+    <t xml:space="preserve">4.16819047927856</t>
   </si>
   <si>
     <t xml:space="preserve">2.83002591133118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90687441825867</t>
+    <t xml:space="preserve">2.90687417984009</t>
   </si>
   <si>
     <t xml:space="preserve">2.84339070320129</t>
@@ -1238,7 +1238,7 @@
     <t xml:space="preserve">2.89350938796997</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80162477493286</t>
+    <t xml:space="preserve">2.80162501335144</t>
   </si>
   <si>
     <t xml:space="preserve">2.92358064651489</t>
@@ -1247,34 +1247,34 @@
     <t xml:space="preserve">2.94863986968994</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01713538169861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08061838150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17083144187927</t>
+    <t xml:space="preserve">3.01713514328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08061861991882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17083120346069</t>
   </si>
   <si>
     <t xml:space="preserve">3.14911389350891</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15746688842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14410185813904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17918539047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17417311668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10400724411011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01212334632874</t>
+    <t xml:space="preserve">3.15746665000916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14410161972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17918515205383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17417335510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10400748252869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01212310791016</t>
   </si>
   <si>
     <t xml:space="preserve">3.02882957458496</t>
@@ -1283,28 +1283,28 @@
     <t xml:space="preserve">2.94529819488525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95699262619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89852118492126</t>
+    <t xml:space="preserve">2.95699238777161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89852142333984</t>
   </si>
   <si>
     <t xml:space="preserve">2.84004902839661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82501363754272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85007286071777</t>
+    <t xml:space="preserve">2.8250138759613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85007309913635</t>
   </si>
   <si>
     <t xml:space="preserve">2.74649548530579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55771470069885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54769134521484</t>
+    <t xml:space="preserve">2.55771493911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54769158363342</t>
   </si>
   <si>
     <t xml:space="preserve">2.51093769073486</t>
@@ -1313,25 +1313,25 @@
     <t xml:space="preserve">2.58945727348328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50091361999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51594972610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50592589378357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47919631004333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41905331611633</t>
+    <t xml:space="preserve">2.5009138584137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51594996452332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50592565536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47919607162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41905379295349</t>
   </si>
   <si>
     <t xml:space="preserve">2.39566540718079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36058235168457</t>
+    <t xml:space="preserve">2.36058187484741</t>
   </si>
   <si>
     <t xml:space="preserve">2.36726450920105</t>
@@ -1340,10 +1340,10 @@
     <t xml:space="preserve">2.3772885799408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27538061141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.313805103302</t>
+    <t xml:space="preserve">2.2753803730011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31380534172058</t>
   </si>
   <si>
     <t xml:space="preserve">2.2620153427124</t>
@@ -1352,73 +1352,73 @@
     <t xml:space="preserve">2.27203965187073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41404223442078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38062930107117</t>
+    <t xml:space="preserve">2.41404247283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38062953948975</t>
   </si>
   <si>
     <t xml:space="preserve">2.30043959617615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30211091041565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29709911346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32382869720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33552312850952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35389971733093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36559414863586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35055828094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35222911834717</t>
+    <t xml:space="preserve">2.30211067199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29709887504578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32382822036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33552289009094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35389995574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36559438705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35055804252625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35222935676575</t>
   </si>
   <si>
     <t xml:space="preserve">2.35557007789612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25533294677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22025084495544</t>
+    <t xml:space="preserve">2.25533318519592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22025060653687</t>
   </si>
   <si>
     <t xml:space="preserve">2.28039240837097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22526168823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23027396202087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40067625045776</t>
+    <t xml:space="preserve">2.225261926651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23027372360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40067648887634</t>
   </si>
   <si>
     <t xml:space="preserve">2.44912457466125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42406558990479</t>
+    <t xml:space="preserve">2.42406582832336</t>
   </si>
   <si>
     <t xml:space="preserve">2.31881666183472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30879330635071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34387564659119</t>
+    <t xml:space="preserve">2.30879354476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34387588500977</t>
   </si>
   <si>
     <t xml:space="preserve">2.33218145370483</t>
@@ -1427,7 +1427,7 @@
     <t xml:space="preserve">2.27370977401733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18850874900818</t>
+    <t xml:space="preserve">2.18850898742676</t>
   </si>
   <si>
     <t xml:space="preserve">2.17681455612183</t>
@@ -1448,19 +1448,19 @@
     <t xml:space="preserve">2.01142287254333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97466921806335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00474047660828</t>
+    <t xml:space="preserve">1.97466897964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00474071502686</t>
   </si>
   <si>
     <t xml:space="preserve">2.03815340995789</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1517550945282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17180228233337</t>
+    <t xml:space="preserve">2.15175533294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17180252075195</t>
   </si>
   <si>
     <t xml:space="preserve">2.18182587623596</t>
@@ -1469,10 +1469,10 @@
     <t xml:space="preserve">2.16679048538208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16846060752869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15509581565857</t>
+    <t xml:space="preserve">2.16846084594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15509629249573</t>
   </si>
   <si>
     <t xml:space="preserve">2.15676641464233</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">2.07657742500305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08994245529175</t>
+    <t xml:space="preserve">2.08994221687317</t>
   </si>
   <si>
     <t xml:space="preserve">2.09829497337341</t>
@@ -1499,46 +1499,46 @@
     <t xml:space="preserve">2.09161257743835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02478742599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02645897865295</t>
+    <t xml:space="preserve">2.02478766441345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02645921707153</t>
   </si>
   <si>
     <t xml:space="preserve">2.12502455711365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23695611953735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18683791160583</t>
+    <t xml:space="preserve">2.23695635795593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18683767318726</t>
   </si>
   <si>
     <t xml:space="preserve">2.11834239959717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06989502906799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06321310997009</t>
+    <t xml:space="preserve">2.06989526748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06321263313293</t>
   </si>
   <si>
     <t xml:space="preserve">2.00139951705933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99972856044769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98302292823792</t>
+    <t xml:space="preserve">1.99972879886627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9830230474472</t>
   </si>
   <si>
     <t xml:space="preserve">1.94626927375793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87610328197479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75748944282532</t>
+    <t xml:space="preserve">1.87610340118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75748932361603</t>
   </si>
   <si>
     <t xml:space="preserve">1.695676445961</t>
@@ -1547,16 +1547,16 @@
     <t xml:space="preserve">1.65391063690186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6288515329361</t>
+    <t xml:space="preserve">1.62885165214539</t>
   </si>
   <si>
     <t xml:space="preserve">1.62968707084656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50439071655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48601377010345</t>
+    <t xml:space="preserve">1.50439083576202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48601388931274</t>
   </si>
   <si>
     <t xml:space="preserve">1.39663565158844</t>
@@ -1565,13 +1565,13 @@
     <t xml:space="preserve">1.31728136539459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2855396270752</t>
+    <t xml:space="preserve">1.28553974628448</t>
   </si>
   <si>
     <t xml:space="preserve">1.27133929729462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24962174892426</t>
+    <t xml:space="preserve">1.24962162971497</t>
   </si>
   <si>
     <t xml:space="preserve">1.24460959434509</t>
@@ -1580,19 +1580,19 @@
     <t xml:space="preserve">1.2897162437439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2763512134552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30391657352448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31561100482941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31310510635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28386926651001</t>
+    <t xml:space="preserve">1.27635133266449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30391645431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3156111240387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31310498714447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2838693857193</t>
   </si>
   <si>
     <t xml:space="preserve">1.27969288825989</t>
@@ -1604,7 +1604,7 @@
     <t xml:space="preserve">1.35152912139893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29472827911377</t>
+    <t xml:space="preserve">1.29472839832306</t>
   </si>
   <si>
     <t xml:space="preserve">1.29639852046967</t>
@@ -1613,7 +1613,7 @@
     <t xml:space="preserve">1.24293923377991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2521276473999</t>
+    <t xml:space="preserve">1.25212776660919</t>
   </si>
   <si>
     <t xml:space="preserve">1.26799857616425</t>
@@ -1628,13 +1628,13 @@
     <t xml:space="preserve">1.25630414485931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25797438621521</t>
+    <t xml:space="preserve">1.2579745054245</t>
   </si>
   <si>
     <t xml:space="preserve">1.26048040390015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36823570728302</t>
+    <t xml:space="preserve">1.36823558807373</t>
   </si>
   <si>
     <t xml:space="preserve">1.36990606784821</t>
@@ -1646,37 +1646,37 @@
     <t xml:space="preserve">1.34568238258362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31477534770966</t>
+    <t xml:space="preserve">1.31477546691895</t>
   </si>
   <si>
     <t xml:space="preserve">1.34484672546387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25129199028015</t>
+    <t xml:space="preserve">1.25129210948944</t>
   </si>
   <si>
     <t xml:space="preserve">1.23876285552979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06835913658142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962275326251984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989840686321259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.633163154125214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.703329801559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.705000162124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862038135528564</t>
+    <t xml:space="preserve">1.06835925579071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962275266647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989840507507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.633163213729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.703329861164093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.705000221729279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.862038195133209</t>
   </si>
   <si>
     <t xml:space="preserve">0.958098888397217</t>
@@ -1688,7 +1688,7 @@
     <t xml:space="preserve">0.848673403263092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.913827121257782</t>
+    <t xml:space="preserve">0.913827180862427</t>
   </si>
   <si>
     <t xml:space="preserve">0.9447340965271</t>
@@ -1700,19 +1700,19 @@
     <t xml:space="preserve">0.917168796062469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00487565994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14771413803101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11430144309998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09926605224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13184356689453</t>
+    <t xml:space="preserve">1.00487577915192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1477142572403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11430132389069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09926617145538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13184344768524</t>
   </si>
   <si>
     <t xml:space="preserve">1.10344254970551</t>
@@ -1724,16 +1724,16 @@
     <t xml:space="preserve">1.01155817508698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01824069023132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999028921127319</t>
+    <t xml:space="preserve">1.01824057102203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999029040336609</t>
   </si>
   <si>
     <t xml:space="preserve">1.01573550701141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01322948932648</t>
+    <t xml:space="preserve">1.01322960853577</t>
   </si>
   <si>
     <t xml:space="preserve">1.08255958557129</t>
@@ -1748,64 +1748,64 @@
     <t xml:space="preserve">1.12933743000031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13017225265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1368545293808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11346673965454</t>
+    <t xml:space="preserve">1.13017213344574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13685441017151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11346662044525</t>
   </si>
   <si>
     <t xml:space="preserve">1.10260689258575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06585311889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0324410200119</t>
+    <t xml:space="preserve">1.06585299968719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03244113922119</t>
   </si>
   <si>
     <t xml:space="preserve">1.07086515426636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06334817409515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01907622814178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03494727611542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06501841545105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12850177288055</t>
+    <t xml:space="preserve">1.06334805488586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01907634735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03494715690613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06501829624176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12850165367126</t>
   </si>
   <si>
     <t xml:space="preserve">1.08506560325623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08673596382141</t>
+    <t xml:space="preserve">1.08673584461212</t>
   </si>
   <si>
     <t xml:space="preserve">1.07253646850586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08088910579681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10511291027069</t>
+    <t xml:space="preserve">1.0808892250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1051127910614</t>
   </si>
   <si>
     <t xml:space="preserve">1.07838320732117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10010087490082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11263084411621</t>
+    <t xml:space="preserve">1.10010075569153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1126309633255</t>
   </si>
   <si>
     <t xml:space="preserve">1.11012494564056</t>
@@ -1817,28 +1817,28 @@
     <t xml:space="preserve">1.46179032325745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4158478975296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41417765617371</t>
+    <t xml:space="preserve">1.41584801673889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41417789459229</t>
   </si>
   <si>
     <t xml:space="preserve">1.36071765422821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33064615726471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29806983470917</t>
+    <t xml:space="preserve">1.330646276474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29806971549988</t>
   </si>
   <si>
     <t xml:space="preserve">1.37324774265289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38744711875916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32981145381927</t>
+    <t xml:space="preserve">1.38744723796844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32981157302856</t>
   </si>
   <si>
     <t xml:space="preserve">1.35069346427917</t>
@@ -1859,34 +1859,34 @@
     <t xml:space="preserve">1.40248322486877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41918885707855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42169499397278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42253041267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42837738990784</t>
+    <t xml:space="preserve">1.41918897628784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42169487476349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42253053188324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42837727069855</t>
   </si>
   <si>
     <t xml:space="preserve">1.39997732639313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37575268745422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39412951469421</t>
+    <t xml:space="preserve">1.37575280666351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3941296339035</t>
   </si>
   <si>
     <t xml:space="preserve">1.45343661308289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43589532375336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52861440181732</t>
+    <t xml:space="preserve">1.43589544296265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52861428260803</t>
   </si>
   <si>
     <t xml:space="preserve">1.61131024360657</t>
@@ -1898,10 +1898,10 @@
     <t xml:space="preserve">1.59376907348633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57455658912659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55283880233765</t>
+    <t xml:space="preserve">1.5745564699173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55283892154694</t>
   </si>
   <si>
     <t xml:space="preserve">1.55116772651672</t>
@@ -1913,55 +1913,55 @@
     <t xml:space="preserve">1.47097861766815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41751837730408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43422496318817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3882828950882</t>
+    <t xml:space="preserve">1.41751849651337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43422508239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38828277587891</t>
   </si>
   <si>
     <t xml:space="preserve">1.38327085971832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3323165178299</t>
+    <t xml:space="preserve">1.33231663703918</t>
   </si>
   <si>
     <t xml:space="preserve">1.36739993095398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34985876083374</t>
+    <t xml:space="preserve">1.34985888004303</t>
   </si>
   <si>
     <t xml:space="preserve">1.30308103561401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32229340076447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31644582748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29890441894531</t>
+    <t xml:space="preserve">1.32229351997375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31644594669342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2989045381546</t>
   </si>
   <si>
     <t xml:space="preserve">1.30892860889435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31059908866882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31895172595978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29222214221954</t>
+    <t xml:space="preserve">1.31059896945953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31895184516907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29222238063812</t>
   </si>
   <si>
     <t xml:space="preserve">1.28721010684967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2504563331604</t>
+    <t xml:space="preserve">1.25045657157898</t>
   </si>
   <si>
     <t xml:space="preserve">1.32730543613434</t>
@@ -1970,10 +1970,10 @@
     <t xml:space="preserve">1.31143462657928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31978750228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3490229845047</t>
+    <t xml:space="preserve">1.31978738307953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34902310371399</t>
   </si>
   <si>
     <t xml:space="preserve">1.34651696681976</t>
@@ -1991,7 +1991,7 @@
     <t xml:space="preserve">1.22205626964569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19198513031006</t>
+    <t xml:space="preserve">1.19198501110077</t>
   </si>
   <si>
     <t xml:space="preserve">1.35821163654327</t>
@@ -2006,22 +2006,22 @@
     <t xml:space="preserve">1.24043321609497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27384519577026</t>
+    <t xml:space="preserve">1.27384531497955</t>
   </si>
   <si>
     <t xml:space="preserve">1.2613160610199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32646989822388</t>
+    <t xml:space="preserve">1.32646977901459</t>
   </si>
   <si>
     <t xml:space="preserve">1.33816432952881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42503643035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48183751106262</t>
+    <t xml:space="preserve">1.42503654956818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48183739185333</t>
   </si>
   <si>
     <t xml:space="preserve">1.49603796005249</t>
@@ -2030,31 +2030,31 @@
     <t xml:space="preserve">1.50272035598755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50355517864227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54448533058167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56369781494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53863847255707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54866254329681</t>
+    <t xml:space="preserve">1.50355494022369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54448521137238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56369757652283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53863835334778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5486626625061</t>
   </si>
   <si>
     <t xml:space="preserve">1.49186074733734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41668283939362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39329481124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39078879356384</t>
+    <t xml:space="preserve">1.41668295860291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39329493045807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39078891277313</t>
   </si>
   <si>
     <t xml:space="preserve">1.4200245141983</t>
@@ -2063,19 +2063,19 @@
     <t xml:space="preserve">1.37491798400879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34818840026855</t>
+    <t xml:space="preserve">1.34818828105927</t>
   </si>
   <si>
     <t xml:space="preserve">1.33148193359375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32814013957977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29723429679871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29974031448364</t>
+    <t xml:space="preserve">1.32814037799835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29723417758942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29974019527435</t>
   </si>
   <si>
     <t xml:space="preserve">1.30224621295929</t>
@@ -2084,7 +2084,7 @@
     <t xml:space="preserve">1.33315229415894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26549243927002</t>
+    <t xml:space="preserve">1.26549255847931</t>
   </si>
   <si>
     <t xml:space="preserve">1.24210357666016</t>
@@ -2102,37 +2102,37 @@
     <t xml:space="preserve">1.38911855220795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37993013858795</t>
+    <t xml:space="preserve">1.37992990016937</t>
   </si>
   <si>
     <t xml:space="preserve">1.45260179042816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48851978778839</t>
+    <t xml:space="preserve">1.48852002620697</t>
   </si>
   <si>
     <t xml:space="preserve">1.49687278270721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50104916095734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.447589635849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39914155006409</t>
+    <t xml:space="preserve">1.50104892253876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44758987426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39914166927338</t>
   </si>
   <si>
     <t xml:space="preserve">1.54281485080719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46095454692841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39162349700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41000032424927</t>
+    <t xml:space="preserve">1.4609546661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39162361621857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41000044345856</t>
   </si>
   <si>
     <t xml:space="preserve">1.40833008289337</t>
@@ -2141,22 +2141,22 @@
     <t xml:space="preserve">1.4292129278183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40749430656433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3339878320694</t>
+    <t xml:space="preserve">1.40749454498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33398795127869</t>
   </si>
   <si>
     <t xml:space="preserve">1.32563412189484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33732855319977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36155319213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36907029151917</t>
+    <t xml:space="preserve">1.33732867240906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36155307292938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36907052993774</t>
   </si>
   <si>
     <t xml:space="preserve">1.44508373737335</t>
@@ -2168,28 +2168,28 @@
     <t xml:space="preserve">1.46596658229828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47181332111359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46513104438782</t>
+    <t xml:space="preserve">1.47181344032288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46513092517853</t>
   </si>
   <si>
     <t xml:space="preserve">1.47264909744263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51190888881683</t>
+    <t xml:space="preserve">1.51190876960754</t>
   </si>
   <si>
     <t xml:space="preserve">1.47014307975769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4926962852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52276766300201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54030871391296</t>
+    <t xml:space="preserve">1.49269616603851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52276754379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54030883312225</t>
   </si>
   <si>
     <t xml:space="preserve">1.53529679775238</t>
@@ -2201,13 +2201,13 @@
     <t xml:space="preserve">1.60629820823669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58625113964081</t>
+    <t xml:space="preserve">1.58625090122223</t>
   </si>
   <si>
     <t xml:space="preserve">1.64555788040161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59293353557587</t>
+    <t xml:space="preserve">1.59293341636658</t>
   </si>
   <si>
     <t xml:space="preserve">1.63219308853149</t>
@@ -2219,31 +2219,31 @@
     <t xml:space="preserve">1.56035614013672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54197919368744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55868566036224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56620383262634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56703853607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58708655834198</t>
+    <t xml:space="preserve">1.54197907447815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55868554115295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56620371341705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56703841686249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58708667755127</t>
   </si>
   <si>
     <t xml:space="preserve">1.64973437786102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74078285694122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70737075805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71906530857086</t>
+    <t xml:space="preserve">1.74078297615051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70737087726593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71906518936157</t>
   </si>
   <si>
     <t xml:space="preserve">1.72908842563629</t>
@@ -2255,16 +2255,16 @@
     <t xml:space="preserve">1.73243021965027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69233465194702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76584219932556</t>
+    <t xml:space="preserve">1.69233477115631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76584208011627</t>
   </si>
   <si>
     <t xml:space="preserve">1.74913573265076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72073554992676</t>
+    <t xml:space="preserve">1.72073566913605</t>
   </si>
   <si>
     <t xml:space="preserve">1.63887548446655</t>
@@ -2273,16 +2273,16 @@
     <t xml:space="preserve">1.60880422592163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68565225601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67061698436737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68732357025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67562901973724</t>
+    <t xml:space="preserve">1.68565237522125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67061722278595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68732368946075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67562913894653</t>
   </si>
   <si>
     <t xml:space="preserve">1.68064117431641</t>
@@ -2294,16 +2294,16 @@
     <t xml:space="preserve">1.61548674106598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62467527389526</t>
+    <t xml:space="preserve">1.62467503547668</t>
   </si>
   <si>
     <t xml:space="preserve">1.61047458648682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64054596424103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62383949756622</t>
+    <t xml:space="preserve">1.64054572582245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62383937835693</t>
   </si>
   <si>
     <t xml:space="preserve">1.60963988304138</t>
@@ -2312,46 +2312,46 @@
     <t xml:space="preserve">1.57789814472198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59126317501068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56202745437622</t>
+    <t xml:space="preserve">1.59126305580139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56202733516693</t>
   </si>
   <si>
     <t xml:space="preserve">1.59209775924683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59543943405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58290934562683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60379207134247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60045146942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58541536331177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54532086849213</t>
+    <t xml:space="preserve">1.5954395532608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58290922641754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60379219055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6004513502121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58541512489319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54532074928284</t>
   </si>
   <si>
     <t xml:space="preserve">1.54699122905731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57706260681152</t>
+    <t xml:space="preserve">1.57706236839294</t>
   </si>
   <si>
     <t xml:space="preserve">1.43756568431854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49436688423157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48935544490814</t>
+    <t xml:space="preserve">1.49436664581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48935556411743</t>
   </si>
   <si>
     <t xml:space="preserve">1.46763694286346</t>
@@ -2360,43 +2360,43 @@
     <t xml:space="preserve">1.51274359226227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52610850334167</t>
+    <t xml:space="preserve">1.52610838413239</t>
   </si>
   <si>
     <t xml:space="preserve">1.53195607662201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54782688617706</t>
+    <t xml:space="preserve">1.54782676696777</t>
   </si>
   <si>
     <t xml:space="preserve">1.51691997051239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5094028711319</t>
+    <t xml:space="preserve">1.50940275192261</t>
   </si>
   <si>
     <t xml:space="preserve">1.48267221450806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26465678215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23208034038544</t>
+    <t xml:space="preserve">1.26465690135956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23208045959473</t>
   </si>
   <si>
     <t xml:space="preserve">1.18029081821442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16692590713501</t>
+    <t xml:space="preserve">1.16692578792572</t>
   </si>
   <si>
     <t xml:space="preserve">1.13601982593536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02742910385132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933039665222168</t>
+    <t xml:space="preserve">1.02742898464203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933039724826813</t>
   </si>
   <si>
     <t xml:space="preserve">0.776836395263672</t>
@@ -2405,49 +2405,49 @@
     <t xml:space="preserve">0.719200670719147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.695811748504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54670923948288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613534212112427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519561350345612</t>
+    <t xml:space="preserve">0.695811808109283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.546709179878235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613534152507782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519561290740967</t>
   </si>
   <si>
     <t xml:space="preserve">0.599333763122559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674928903579712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.725047469139099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.701658546924591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.637340426445007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.682447016239166</t>
+    <t xml:space="preserve">0.674928963184357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.725047409534454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.701658606529236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.637340486049652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.682446956634521</t>
   </si>
   <si>
     <t xml:space="preserve">0.680358350276947</t>
   </si>
   <si>
-    <t xml:space="preserve">0.687876343727112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.659893751144409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643604636192322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.659475386142731</t>
+    <t xml:space="preserve">0.687876403331757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.659893691539764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.643604576587677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.65947550535202</t>
   </si>
   <si>
     <t xml:space="preserve">0.64318722486496</t>
@@ -2462,28 +2462,28 @@
     <t xml:space="preserve">0.618128001689911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.660728454589844</t>
+    <t xml:space="preserve">0.660728514194489</t>
   </si>
   <si>
     <t xml:space="preserve">0.646528899669647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.650705337524414</t>
+    <t xml:space="preserve">0.650705277919769</t>
   </si>
   <si>
     <t xml:space="preserve">0.638175189495087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649869620800018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640263795852661</t>
+    <t xml:space="preserve">0.649869680404663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640263855457306</t>
   </si>
   <si>
     <t xml:space="preserve">0.612281143665314</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615621984004974</t>
+    <t xml:space="preserve">0.61562192440033</t>
   </si>
   <si>
     <t xml:space="preserve">0.610192537307739</t>
@@ -2498,7 +2498,7 @@
     <t xml:space="preserve">0.651540040969849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.676599323749542</t>
+    <t xml:space="preserve">0.676599264144897</t>
   </si>
   <si>
     <t xml:space="preserve">0.654881656169891</t>
@@ -2516,10 +2516,10 @@
     <t xml:space="preserve">0.639846444129944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649034917354584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.668246507644653</t>
+    <t xml:space="preserve">0.649034857749939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.668246567249298</t>
   </si>
   <si>
     <t xml:space="preserve">0.65028703212738</t>
@@ -2534,13 +2534,13 @@
     <t xml:space="preserve">0.606016159057617</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629822373390198</t>
+    <t xml:space="preserve">0.629822432994843</t>
   </si>
   <si>
     <t xml:space="preserve">0.596827805042267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.574691951274872</t>
+    <t xml:space="preserve">0.574691832065582</t>
   </si>
   <si>
     <t xml:space="preserve">0.581792593002319</t>
@@ -2549,7 +2549,7 @@
     <t xml:space="preserve">0.57427453994751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.601839661598206</t>
+    <t xml:space="preserve">0.601839780807495</t>
   </si>
   <si>
     <t xml:space="preserve">0.630658030509949</t>
@@ -2558,37 +2558,37 @@
     <t xml:space="preserve">0.726300477981567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.789366483688354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.763054251670837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768483579158783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827790558338165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.835308492183685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901297926902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910486400127411</t>
+    <t xml:space="preserve">0.78936642408371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.763054192066193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.768483638763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.82779061794281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.835308611392975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901297986507416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.910486340522766</t>
   </si>
   <si>
     <t xml:space="preserve">1.00571143627167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01072335243225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968957662582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877909004688263</t>
+    <t xml:space="preserve">1.01072347164154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968957722187042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877909064292908</t>
   </si>
   <si>
     <t xml:space="preserve">0.924685955047607</t>
@@ -2597,40 +2597,40 @@
     <t xml:space="preserve">0.925521552562714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938051640987396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922180891036987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892109453678131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.893779873847961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895450234413147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823614180088043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78101372718811</t>
+    <t xml:space="preserve">0.938051700592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922180950641632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892109572887421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.893779933452606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895450294017792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823614120483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781013667583466</t>
   </si>
   <si>
     <t xml:space="preserve">0.824867188930511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.806072890758514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785607516765594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.802313983440399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.797719240188599</t>
+    <t xml:space="preserve">0.806073009967804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78560745716095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.802313923835754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.797719299793243</t>
   </si>
   <si>
     <t xml:space="preserve">0.801895618438721</t>
@@ -2639,7 +2639,7 @@
     <t xml:space="preserve">0.79855489730835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.776419043540955</t>
+    <t xml:space="preserve">0.77641898393631</t>
   </si>
   <si>
     <t xml:space="preserve">0.782266676425934</t>
@@ -2648,22 +2648,22 @@
     <t xml:space="preserve">0.766394913196564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.821525573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.795631587505341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863708555698395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855355799198151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.844496965408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857861816883087</t>
+    <t xml:space="preserve">0.821525514125824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.795631527900696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86370861530304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855355858802795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84449702501297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857861876487732</t>
   </si>
   <si>
     <t xml:space="preserve">0.836143374443054</t>
@@ -2675,13 +2675,13 @@
     <t xml:space="preserve">0.838649392127991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.800225257873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.773913025856018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789783835411072</t>
+    <t xml:space="preserve">0.80022531747818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.773912966251373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789783895015717</t>
   </si>
   <si>
     <t xml:space="preserve">0.77182525396347</t>
@@ -2693,43 +2693,43 @@
     <t xml:space="preserve">0.775583386421204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.786860466003418</t>
+    <t xml:space="preserve">0.786860525608063</t>
   </si>
   <si>
     <t xml:space="preserve">0.792707204818726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.758877813816071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.765977561473846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.800642609596252</t>
+    <t xml:space="preserve">0.758877754211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.765977621078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800642669200897</t>
   </si>
   <si>
     <t xml:space="preserve">0.809831082820892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.799807906150818</t>
+    <t xml:space="preserve">0.799807846546173</t>
   </si>
   <si>
     <t xml:space="preserve">0.780178070068359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.770989596843719</t>
+    <t xml:space="preserve">0.770989537239075</t>
   </si>
   <si>
     <t xml:space="preserve">0.740918338298798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.717947661876678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.712100028991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.684117376804352</t>
+    <t xml:space="preserve">0.717947721481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.712100088596344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.684117317199707</t>
   </si>
   <si>
     <t xml:space="preserve">0.690799713134766</t>
@@ -2741,7 +2741,7 @@
     <t xml:space="preserve">0.685787737369537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674094200134277</t>
+    <t xml:space="preserve">0.674094140529633</t>
   </si>
   <si>
     <t xml:space="preserve">0.666576147079468</t>
@@ -2765,7 +2765,7 @@
     <t xml:space="preserve">0.697482109069824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.703747153282166</t>
+    <t xml:space="preserve">0.703747272491455</t>
   </si>
   <si>
     <t xml:space="preserve">0.69831782579422</t>
@@ -2774,10 +2774,10 @@
     <t xml:space="preserve">0.721288442611694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.720453679561615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.742588698863983</t>
+    <t xml:space="preserve">0.72045373916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.742588639259338</t>
   </si>
   <si>
     <t xml:space="preserve">0.767647922039032</t>
@@ -2786,16 +2786,16 @@
     <t xml:space="preserve">0.718365073204041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.715024352073669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781848430633545</t>
+    <t xml:space="preserve">0.715024292469025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7818483710289</t>
   </si>
   <si>
     <t xml:space="preserve">0.75720739364624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778925120830536</t>
+    <t xml:space="preserve">0.778925061225891</t>
   </si>
   <si>
     <t xml:space="preserve">0.796466290950775</t>
@@ -2804,19 +2804,19 @@
     <t xml:space="preserve">0.825284600257874</t>
   </si>
   <si>
-    <t xml:space="preserve">0.850343823432922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860367774963379</t>
+    <t xml:space="preserve">0.850343704223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860367834568024</t>
   </si>
   <si>
     <t xml:space="preserve">0.847003042697906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.858696699142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843661367893219</t>
+    <t xml:space="preserve">0.858696579933167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843661308288574</t>
   </si>
   <si>
     <t xml:space="preserve">0.872062265872955</t>
@@ -2834,52 +2834,52 @@
     <t xml:space="preserve">0.80774337053299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.813172817230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828626096248627</t>
+    <t xml:space="preserve">0.813172698020935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828626155853271</t>
   </si>
   <si>
     <t xml:space="preserve">0.832802534103394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.820690751075745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.749689400196075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.710847020149231</t>
+    <t xml:space="preserve">0.8206906914711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.749689340591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.710846960544586</t>
   </si>
   <si>
     <t xml:space="preserve">0.654464304447174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.63399875164032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.645275890827179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.660311043262482</t>
+    <t xml:space="preserve">0.633998811244965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.645275831222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.660311102867126</t>
   </si>
   <si>
     <t xml:space="preserve">0.684534728527069</t>
   </si>
   <si>
-    <t xml:space="preserve">0.68912935256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.753030121326447</t>
+    <t xml:space="preserve">0.689129412174225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.753030061721802</t>
   </si>
   <si>
     <t xml:space="preserve">0.784354448318481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.787696123123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803148746490479</t>
+    <t xml:space="preserve">0.787696063518524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803148686885834</t>
   </si>
   <si>
     <t xml:space="preserve">0.856191456317902</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">0.877073407173157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.90046226978302</t>
+    <t xml:space="preserve">0.900462329387665</t>
   </si>
   <si>
     <t xml:space="preserve">0.889603495597839</t>
@@ -2906,22 +2906,22 @@
     <t xml:space="preserve">0.881250739097595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.904638826847076</t>
+    <t xml:space="preserve">0.904638767242432</t>
   </si>
   <si>
     <t xml:space="preserve">0.89294421672821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.90213268995285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882085502147675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867884993553162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841155469417572</t>
+    <t xml:space="preserve">0.90213280916214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88208544254303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867885053157806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841155350208282</t>
   </si>
   <si>
     <t xml:space="preserve">0.839484930038452</t>
@@ -2933,22 +2933,22 @@
     <t xml:space="preserve">0.840320587158203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.859532117843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905474305152893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849508225917816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872897028923035</t>
+    <t xml:space="preserve">0.859532237052917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905474364757538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849508166313171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87289696931839</t>
   </si>
   <si>
     <t xml:space="preserve">0.906310021877289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.943898439407349</t>
+    <t xml:space="preserve">0.943898499011993</t>
   </si>
   <si>
     <t xml:space="preserve">0.953922390937805</t>
@@ -2960,10 +2960,10 @@
     <t xml:space="preserve">0.965616941452026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978146195411682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961439728736877</t>
+    <t xml:space="preserve">0.978146135807037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961439669132233</t>
   </si>
   <si>
     <t xml:space="preserve">0.934710025787354</t>
@@ -2972,16 +2972,16 @@
     <t xml:space="preserve">0.902968287467957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.87456750869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852849721908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867050170898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.878744721412659</t>
+    <t xml:space="preserve">0.874567449092865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852849841117859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867050290107727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.878744661808014</t>
   </si>
   <si>
     <t xml:space="preserve">0.907144844532013</t>
@@ -2990,49 +2990,49 @@
     <t xml:space="preserve">0.931369304656982</t>
   </si>
   <si>
-    <t xml:space="preserve">0.921345233917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927191853523254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912992477416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947240054607391</t>
+    <t xml:space="preserve">0.921345114707947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927191972732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912992417812347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947239995002747</t>
   </si>
   <si>
     <t xml:space="preserve">0.899626731872559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.92969799041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938886404037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.937215983867645</t>
+    <t xml:space="preserve">0.929697930812836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93888646364212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.937216103076935</t>
   </si>
   <si>
     <t xml:space="preserve">0.942228019237518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941392421722412</t>
+    <t xml:space="preserve">0.941392540931702</t>
   </si>
   <si>
     <t xml:space="preserve">0.94640451669693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.935545682907104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975639998912811</t>
+    <t xml:space="preserve">0.935545802116394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975640118122101</t>
   </si>
   <si>
     <t xml:space="preserve">1.14687860012054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18947923183441</t>
+    <t xml:space="preserve">1.18947899341583</t>
   </si>
   <si>
     <t xml:space="preserve">1.17360830307007</t>
@@ -3041,22 +3041,22 @@
     <t xml:space="preserve">1.16024351119995</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1577376127243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17193782329559</t>
+    <t xml:space="preserve">1.15773737430573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17193794250488</t>
   </si>
   <si>
     <t xml:space="preserve">1.1385258436203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1092894077301</t>
+    <t xml:space="preserve">1.10928916931152</t>
   </si>
   <si>
     <t xml:space="preserve">1.11096060276031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10678422451019</t>
+    <t xml:space="preserve">1.10678398609161</t>
   </si>
   <si>
     <t xml:space="preserve">1.11179530620575</t>
@@ -3065,19 +3065,19 @@
     <t xml:space="preserve">1.1310076713562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12098383903503</t>
+    <t xml:space="preserve">1.12098371982574</t>
   </si>
   <si>
     <t xml:space="preserve">1.16358518600464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14520835876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11513698101044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10761904716492</t>
+    <t xml:space="preserve">1.14520812034607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11513686180115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10761880874634</t>
   </si>
   <si>
     <t xml:space="preserve">1.37742400169373</t>
@@ -3086,43 +3086,43 @@
     <t xml:space="preserve">1.37241196632385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43923699855804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4367311000824</t>
+    <t xml:space="preserve">1.43923687934875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43673098087311</t>
   </si>
   <si>
     <t xml:space="preserve">1.44007170200348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4066596031189</t>
+    <t xml:space="preserve">1.40665972232819</t>
   </si>
   <si>
     <t xml:space="preserve">1.41167175769806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3974711894989</t>
+    <t xml:space="preserve">1.39747130870819</t>
   </si>
   <si>
     <t xml:space="preserve">1.43840134143829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47682535648346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45928430557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44090735912323</t>
+    <t xml:space="preserve">1.47682547569275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45928406715393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44090747833252</t>
   </si>
   <si>
     <t xml:space="preserve">1.43338942527771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48100173473358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41334211826324</t>
+    <t xml:space="preserve">1.48100185394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41334223747253</t>
   </si>
   <si>
     <t xml:space="preserve">1.42587125301361</t>
@@ -3131,25 +3131,25 @@
     <t xml:space="preserve">1.5879213809967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.550332903862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62634563446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61214578151703</t>
+    <t xml:space="preserve">1.55033278465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62634539604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61214601993561</t>
   </si>
   <si>
     <t xml:space="preserve">1.62049865722656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6196631193161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62718117237091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6138162612915</t>
+    <t xml:space="preserve">1.61966288089752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62718093395233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61381614208221</t>
   </si>
   <si>
     <t xml:space="preserve">1.45677816867828</t>
@@ -3158,22 +3158,22 @@
     <t xml:space="preserve">1.39830696582794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34317624568939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35654103755951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35904717445374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36489403247833</t>
+    <t xml:space="preserve">1.34317636489868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35654127597809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35904705524445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36489391326904</t>
   </si>
   <si>
     <t xml:space="preserve">1.4027658700943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43466734886169</t>
+    <t xml:space="preserve">1.43466711044312</t>
   </si>
   <si>
     <t xml:space="preserve">1.41251361370087</t>
@@ -3191,25 +3191,25 @@
     <t xml:space="preserve">1.44795918464661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49049437046051</t>
+    <t xml:space="preserve">1.49049425125122</t>
   </si>
   <si>
     <t xml:space="preserve">1.51796472072601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53214287757874</t>
+    <t xml:space="preserve">1.53214299678802</t>
   </si>
   <si>
     <t xml:space="preserve">1.58442544937134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52859842777252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54897964000702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54454898834229</t>
+    <t xml:space="preserve">1.52859854698181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54897975921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54454910755157</t>
   </si>
   <si>
     <t xml:space="preserve">1.53834593296051</t>
@@ -3224,13 +3224,13 @@
     <t xml:space="preserve">1.6145544052124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60657894611359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5693610906601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58885622024536</t>
+    <t xml:space="preserve">1.60657906532288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56936120986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58885610103607</t>
   </si>
   <si>
     <t xml:space="preserve">1.60392069816589</t>
@@ -3239,37 +3239,37 @@
     <t xml:space="preserve">1.63582181930542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6251882314682</t>
+    <t xml:space="preserve">1.62518811225891</t>
   </si>
   <si>
     <t xml:space="preserve">1.61278212070465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58353924751282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51885092258453</t>
+    <t xml:space="preserve">1.58353936672211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51885080337524</t>
   </si>
   <si>
     <t xml:space="preserve">1.520623087883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49315237998962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49758350849152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52505385875702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5073310136795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50112795829773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54011821746826</t>
+    <t xml:space="preserve">1.4931526184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49758338928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52505362033844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50733089447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50112807750702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54011833667755</t>
   </si>
   <si>
     <t xml:space="preserve">1.53037071228027</t>
@@ -3287,13 +3287,13 @@
     <t xml:space="preserve">1.56404411792755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51707863807678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48872184753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46568238735199</t>
+    <t xml:space="preserve">1.51707851886749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48872196674347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46568214893341</t>
   </si>
   <si>
     <t xml:space="preserve">1.42403340339661</t>
@@ -3308,22 +3308,22 @@
     <t xml:space="preserve">1.61809897422791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82900106906891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84672403335571</t>
+    <t xml:space="preserve">1.8290011882782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.846724152565</t>
   </si>
   <si>
     <t xml:space="preserve">1.9052095413208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89634835720062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98319017887115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03635907173157</t>
+    <t xml:space="preserve">1.89634823799133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98319053649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03635883331299</t>
   </si>
   <si>
     <t xml:space="preserve">2.09129977226257</t>
@@ -3335,34 +3335,34 @@
     <t xml:space="preserve">1.96015048027039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88925898075104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96192300319672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94597220420837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01863622665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10902309417725</t>
+    <t xml:space="preserve">1.88925921916962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96192264556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94597232341766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01863646507263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10902261734009</t>
   </si>
   <si>
     <t xml:space="preserve">2.0753493309021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10547780990601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13737940788269</t>
+    <t xml:space="preserve">2.10547828674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13737964630127</t>
   </si>
   <si>
     <t xml:space="preserve">2.12674570083618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17814183235168</t>
+    <t xml:space="preserve">2.17814207077026</t>
   </si>
   <si>
     <t xml:space="preserve">2.16396355628967</t>
@@ -3374,13 +3374,13 @@
     <t xml:space="preserve">2.18168640136719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24371647834778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17991423606873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1232008934021</t>
+    <t xml:space="preserve">2.24371671676636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1799144744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12320113182068</t>
   </si>
   <si>
     <t xml:space="preserve">2.14624047279358</t>
@@ -3389,13 +3389,13 @@
     <t xml:space="preserve">2.19763708114624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30574655532837</t>
+    <t xml:space="preserve">2.30574679374695</t>
   </si>
   <si>
     <t xml:space="preserve">2.28625130653381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31992483139038</t>
+    <t xml:space="preserve">2.31992506980896</t>
   </si>
   <si>
     <t xml:space="preserve">2.34828162193298</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">2.417400598526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4457573890686</t>
+    <t xml:space="preserve">2.44575762748718</t>
   </si>
   <si>
     <t xml:space="preserve">2.38372755050659</t>
@@ -3413,10 +3413,10 @@
     <t xml:space="preserve">2.46348023414612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42448997497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47411417961121</t>
+    <t xml:space="preserve">2.42449021339417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47411441802979</t>
   </si>
   <si>
     <t xml:space="preserve">2.51310420036316</t>
@@ -3428,16 +3428,16 @@
     <t xml:space="preserve">2.43157911300659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47056937217712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39613342285156</t>
+    <t xml:space="preserve">2.4705696105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39613318443298</t>
   </si>
   <si>
     <t xml:space="preserve">2.33942031860352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37841033935547</t>
+    <t xml:space="preserve">2.37841057777405</t>
   </si>
   <si>
     <t xml:space="preserve">2.21004319190979</t>
@@ -3449,22 +3449,22 @@
     <t xml:space="preserve">2.47943091392517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4918372631073</t>
+    <t xml:space="preserve">2.49183702468872</t>
   </si>
   <si>
     <t xml:space="preserve">2.56095623970032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65665984153748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.640709400177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63184785842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65311479568481</t>
+    <t xml:space="preserve">2.6566596031189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64070916175842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63184762001038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65311527252197</t>
   </si>
   <si>
     <t xml:space="preserve">2.59640216827393</t>
@@ -3473,7 +3473,7 @@
     <t xml:space="preserve">2.52373814582825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33233070373535</t>
+    <t xml:space="preserve">2.33233118057251</t>
   </si>
   <si>
     <t xml:space="preserve">2.31815266609192</t>
@@ -3482,16 +3482,16 @@
     <t xml:space="preserve">2.2968852519989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28270697593689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27561807632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25966715812683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30929136276245</t>
+    <t xml:space="preserve">2.28270721435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27561783790588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25966739654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30929112434387</t>
   </si>
   <si>
     <t xml:space="preserve">2.27916240692139</t>
@@ -3503,7 +3503,7 @@
     <t xml:space="preserve">2.26852869987488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36600494384766</t>
+    <t xml:space="preserve">2.3660044670105</t>
   </si>
   <si>
     <t xml:space="preserve">2.30751919746399</t>
@@ -3512,28 +3512,28 @@
     <t xml:space="preserve">2.24017214775085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14978528022766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16041898727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17459750175476</t>
+    <t xml:space="preserve">2.14978551864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16041922569275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17459726333618</t>
   </si>
   <si>
     <t xml:space="preserve">2.13915181159973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15687465667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05762624740601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16928052902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1958646774292</t>
+    <t xml:space="preserve">2.15687441825867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05762648582458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16928029060364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19586491584778</t>
   </si>
   <si>
     <t xml:space="preserve">2.13560724258423</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">2.39258885383606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39436101913452</t>
+    <t xml:space="preserve">2.39436078071594</t>
   </si>
   <si>
     <t xml:space="preserve">2.06648778915405</t>
@@ -3551,31 +3551,31 @@
     <t xml:space="preserve">1.99382412433624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12142896652222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1196563243866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09484457969666</t>
+    <t xml:space="preserve">2.12142872810364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11965656280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09484434127808</t>
   </si>
   <si>
     <t xml:space="preserve">2.01331901550293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08066606521606</t>
+    <t xml:space="preserve">2.08066630363464</t>
   </si>
   <si>
     <t xml:space="preserve">1.99205148220062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03458666801453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02926993370056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93179392814636</t>
+    <t xml:space="preserve">2.03458690643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02926969528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93179368972778</t>
   </si>
   <si>
     <t xml:space="preserve">2.01509141921997</t>
@@ -3587,7 +3587,7 @@
     <t xml:space="preserve">1.86799168586731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9016649723053</t>
+    <t xml:space="preserve">1.90166509151459</t>
   </si>
   <si>
     <t xml:space="preserve">1.80596160888672</t>
@@ -3596,25 +3596,25 @@
     <t xml:space="preserve">1.6455694437027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56315803527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56847476959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6801290512085</t>
+    <t xml:space="preserve">1.56315815448761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56847488880157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68012917041779</t>
   </si>
   <si>
     <t xml:space="preserve">1.5799947977066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59505903720856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65974771976471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78646636009216</t>
+    <t xml:space="preserve">1.59505915641785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65974760055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78646647930145</t>
   </si>
   <si>
     <t xml:space="preserve">1.75545120239258</t>
@@ -3623,7 +3623,7 @@
     <t xml:space="preserve">1.73684227466583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73418390750885</t>
+    <t xml:space="preserve">1.73418402671814</t>
   </si>
   <si>
     <t xml:space="preserve">1.70671331882477</t>
@@ -3635,49 +3635,49 @@
     <t xml:space="preserve">1.66595077514648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67924296855927</t>
+    <t xml:space="preserve">1.67924284934998</t>
   </si>
   <si>
     <t xml:space="preserve">1.72798085212708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8644472360611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83431816101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74570369720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78469407558441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76254045963287</t>
+    <t xml:space="preserve">1.86444699764252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83431792259216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74570381641388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78469395637512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76254034042358</t>
   </si>
   <si>
     <t xml:space="preserve">1.72886693477631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67038154602051</t>
+    <t xml:space="preserve">1.67038142681122</t>
   </si>
   <si>
     <t xml:space="preserve">1.64113867282867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6012624502182</t>
+    <t xml:space="preserve">1.60126221179962</t>
   </si>
   <si>
     <t xml:space="preserve">1.61987113952637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71025788784027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70051050186157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67835688591003</t>
+    <t xml:space="preserve">1.71025800704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70051038265228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67835664749146</t>
   </si>
   <si>
     <t xml:space="preserve">1.62961876392365</t>
@@ -3686,22 +3686,22 @@
     <t xml:space="preserve">1.63936650753021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63050508499146</t>
+    <t xml:space="preserve">1.63050496578217</t>
   </si>
   <si>
     <t xml:space="preserve">1.60923755168915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62075746059418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55075204372406</t>
+    <t xml:space="preserve">1.62075757980347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55075216293335</t>
   </si>
   <si>
     <t xml:space="preserve">1.46302378177643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47897434234619</t>
+    <t xml:space="preserve">1.47897446155548</t>
   </si>
   <si>
     <t xml:space="preserve">1.54189050197601</t>
@@ -3719,46 +3719,46 @@
     <t xml:space="preserve">1.60746514797211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6003760099411</t>
+    <t xml:space="preserve">1.60037612915039</t>
   </si>
   <si>
     <t xml:space="preserve">1.52594006061554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52150940895081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63139092922211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64734184741974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72266387939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.690762758255</t>
+    <t xml:space="preserve">1.52150928974152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6313910484314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64734172821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72266411781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69076263904572</t>
   </si>
   <si>
     <t xml:space="preserve">1.71646106243134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78114950656891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84495174884796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80773389339447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79887235164642</t>
+    <t xml:space="preserve">1.78114938735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84495186805725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80773377418518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79887223243713</t>
   </si>
   <si>
     <t xml:space="preserve">1.79532778263092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65797543525696</t>
+    <t xml:space="preserve">1.65797555446625</t>
   </si>
   <si>
     <t xml:space="preserve">1.45593464374542</t>
@@ -3767,10 +3767,10 @@
     <t xml:space="preserve">1.41871654987335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46506786346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47688293457031</t>
+    <t xml:space="preserve">1.46506798267365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4768830537796</t>
   </si>
   <si>
     <t xml:space="preserve">1.48960697650909</t>
@@ -3779,13 +3779,13 @@
     <t xml:space="preserve">1.45779716968536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47597420215607</t>
+    <t xml:space="preserve">1.47597408294678</t>
   </si>
   <si>
     <t xml:space="preserve">1.43689358234406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47415637969971</t>
+    <t xml:space="preserve">1.474156498909</t>
   </si>
   <si>
     <t xml:space="preserve">1.48142731189728</t>
@@ -3803,67 +3803,67 @@
     <t xml:space="preserve">1.30147469043732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32783150672913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37418270111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40781033039093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38599789142609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31510758399963</t>
+    <t xml:space="preserve">1.32783138751984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37418282032013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40781044960022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3859977722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31510746479034</t>
   </si>
   <si>
     <t xml:space="preserve">1.28420662879944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27966237068176</t>
+    <t xml:space="preserve">1.27966225147247</t>
   </si>
   <si>
     <t xml:space="preserve">1.30874562263489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3269225358963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39781284332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37145614624023</t>
+    <t xml:space="preserve">1.32692265510559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39781296253204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37145626544952</t>
   </si>
   <si>
     <t xml:space="preserve">1.3578234910965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35691475868225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29693043231964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31328988075256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33328449726105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41962540149689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42689633369446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40144836902618</t>
+    <t xml:space="preserve">1.35691463947296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29693055152893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31328976154327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33328461647034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41962552070618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42689621448517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40144848823547</t>
   </si>
   <si>
     <t xml:space="preserve">1.44416439533234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46961200237274</t>
+    <t xml:space="preserve">1.46961212158203</t>
   </si>
   <si>
     <t xml:space="preserve">1.45961475372314</t>
@@ -3872,7 +3872,7 @@
     <t xml:space="preserve">1.48778915405273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49505996704102</t>
+    <t xml:space="preserve">1.49506008625031</t>
   </si>
   <si>
     <t xml:space="preserve">1.48869812488556</t>
@@ -3887,19 +3887,19 @@
     <t xml:space="preserve">1.50051307678223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48051846027374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40326619148254</t>
+    <t xml:space="preserve">1.48051834106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40326607227325</t>
   </si>
   <si>
     <t xml:space="preserve">1.43234932422638</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41144573688507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34691727161407</t>
+    <t xml:space="preserve">1.41144561767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34691739082336</t>
   </si>
   <si>
     <t xml:space="preserve">1.34328186511993</t>
@@ -3908,52 +3908,52 @@
     <t xml:space="preserve">1.37327396869659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37600040435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36236774921417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39235973358154</t>
+    <t xml:space="preserve">1.37600064277649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36236763000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39235985279083</t>
   </si>
   <si>
     <t xml:space="preserve">1.33601105213165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35237050056458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36963856220245</t>
+    <t xml:space="preserve">1.35237038135529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36963868141174</t>
   </si>
   <si>
     <t xml:space="preserve">1.35964131355286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41326332092285</t>
+    <t xml:space="preserve">1.41326344013214</t>
   </si>
   <si>
     <t xml:space="preserve">1.43507587909698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41689896583557</t>
+    <t xml:space="preserve">1.41689884662628</t>
   </si>
   <si>
     <t xml:space="preserve">1.46870338916779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4123547077179</t>
+    <t xml:space="preserve">1.41235458850861</t>
   </si>
   <si>
     <t xml:space="preserve">1.39872181415558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70591354370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6859188079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58412742614746</t>
+    <t xml:space="preserve">1.70591342449188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68591868877411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58412754535675</t>
   </si>
   <si>
     <t xml:space="preserve">1.57867431640625</t>
@@ -3965,10 +3965,10 @@
     <t xml:space="preserve">1.56322383880615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4996041059494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55777084827423</t>
+    <t xml:space="preserve">1.49960434436798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55777060985565</t>
   </si>
   <si>
     <t xml:space="preserve">1.55231761932373</t>
@@ -3980,13 +3980,13 @@
     <t xml:space="preserve">1.58140087127686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53777611255646</t>
+    <t xml:space="preserve">1.53777599334717</t>
   </si>
   <si>
     <t xml:space="preserve">1.52323436737061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56049740314484</t>
+    <t xml:space="preserve">1.56049728393555</t>
   </si>
   <si>
     <t xml:space="preserve">1.53323185443878</t>
@@ -3998,7 +3998,7 @@
     <t xml:space="preserve">1.59412467479706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64047610759735</t>
+    <t xml:space="preserve">1.64047622680664</t>
   </si>
   <si>
     <t xml:space="preserve">1.65774428844452</t>
@@ -4007,10 +4007,10 @@
     <t xml:space="preserve">1.65865325927734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65956211090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67046821117401</t>
+    <t xml:space="preserve">1.65956199169159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6704683303833</t>
   </si>
   <si>
     <t xml:space="preserve">1.76317119598389</t>
@@ -4019,154 +4019,154 @@
     <t xml:space="preserve">1.79225432872772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78861892223358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73045253753662</t>
+    <t xml:space="preserve">1.78861904144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73045241832733</t>
   </si>
   <si>
     <t xml:space="preserve">1.71772849559784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72681713104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77135074138641</t>
+    <t xml:space="preserve">1.72681701183319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77135062217712</t>
   </si>
   <si>
     <t xml:space="preserve">1.73136138916016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75135612487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78771007061005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84860301017761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86678004264832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87223315238953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89949882030487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93403506278992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94494140148163</t>
+    <t xml:space="preserve">1.75135600566864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78770995140076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84860324859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8667801618576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87223303318024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89949870109558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93403518199921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94494128227234</t>
   </si>
   <si>
     <t xml:space="preserve">1.90676963329315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95402979850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97038900852203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00492525100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99583697319031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97220695018768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97402453422546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9903838634491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04491496086121</t>
+    <t xml:space="preserve">1.95402991771698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97038924694061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00492548942566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99583733081818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97220706939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97402441501617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99038398265839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04491519927979</t>
   </si>
   <si>
     <t xml:space="preserve">2.13398241996765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15397691726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12307596206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11944079399109</t>
+    <t xml:space="preserve">2.15397715568542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12307620048523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11944055557251</t>
   </si>
   <si>
     <t xml:space="preserve">2.13761758804321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16851854324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11035227775574</t>
+    <t xml:space="preserve">2.16851878166199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11035203933716</t>
   </si>
   <si>
     <t xml:space="preserve">2.10308122634888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10126376152039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97584247589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02128505706787</t>
+    <t xml:space="preserve">2.10126352310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97584235668182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02128481864929</t>
   </si>
   <si>
     <t xml:space="preserve">1.85223865509033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89041006565094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91222286224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92676436901093</t>
+    <t xml:space="preserve">1.89041018486023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91222274303436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92676424980164</t>
   </si>
   <si>
     <t xml:space="preserve">1.93585288524628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93948805332184</t>
+    <t xml:space="preserve">1.93948829174042</t>
   </si>
   <si>
     <t xml:space="preserve">1.90131652355194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91404032707214</t>
+    <t xml:space="preserve">1.91404044628143</t>
   </si>
   <si>
     <t xml:space="preserve">1.96311855316162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96857118606567</t>
+    <t xml:space="preserve">1.96857130527496</t>
   </si>
   <si>
     <t xml:space="preserve">2.03219103813171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05945658683777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10489892959595</t>
+    <t xml:space="preserve">2.05945682525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10489916801453</t>
   </si>
   <si>
     <t xml:space="preserve">2.12852907180786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12671136856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09944605827332</t>
+    <t xml:space="preserve">2.12671160697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09944581985474</t>
   </si>
   <si>
     <t xml:space="preserve">2.01946687698364</t>
@@ -4175,22 +4175,22 @@
     <t xml:space="preserve">2.07218050956726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06309199333191</t>
+    <t xml:space="preserve">2.06309175491333</t>
   </si>
   <si>
     <t xml:space="preserve">2.03764414787292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00310754776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01219654083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01764965057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00128984451294</t>
+    <t xml:space="preserve">2.00310778617859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01219630241394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01764941215515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00129008293152</t>
   </si>
   <si>
     <t xml:space="preserve">2.27394556999207</t>
@@ -4199,16 +4199,16 @@
     <t xml:space="preserve">2.2484974861145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31757044792175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3084819316864</t>
+    <t xml:space="preserve">2.31757020950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30848145484924</t>
   </si>
   <si>
     <t xml:space="preserve">2.33211183547974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37210130691528</t>
+    <t xml:space="preserve">2.3721010684967</t>
   </si>
   <si>
     <t xml:space="preserve">2.41572618484497</t>
@@ -4217,7 +4217,7 @@
     <t xml:space="preserve">2.37573671340942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40845561027527</t>
+    <t xml:space="preserve">2.40845537185669</t>
   </si>
   <si>
     <t xml:space="preserve">2.39754915237427</t>
@@ -4226,10 +4226,10 @@
     <t xml:space="preserve">2.38846063613892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39209580421448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3575599193573</t>
+    <t xml:space="preserve">2.39209604263306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35755968093872</t>
   </si>
   <si>
     <t xml:space="preserve">2.34483551979065</t>
@@ -4244,49 +4244,49 @@
     <t xml:space="preserve">2.33574724197388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33938264846802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38118982315063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40663766860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40481972694397</t>
+    <t xml:space="preserve">2.33938241004944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38118958473206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40663743019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40481996536255</t>
   </si>
   <si>
     <t xml:space="preserve">2.39027833938599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37937188148499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32302355766296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28666949272156</t>
+    <t xml:space="preserve">2.37937211990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32302331924438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28666925430298</t>
   </si>
   <si>
     <t xml:space="preserve">2.18487811088562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23213815689087</t>
+    <t xml:space="preserve">2.23213839530945</t>
   </si>
   <si>
     <t xml:space="preserve">2.18306016921997</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14307069778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20487260818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20669007301331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17033648490906</t>
+    <t xml:space="preserve">2.143070936203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20487308502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20669031143188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17033624649048</t>
   </si>
   <si>
     <t xml:space="preserve">2.13943552970886</t>
@@ -4301,28 +4301,28 @@
     <t xml:space="preserve">2.19578409194946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19033122062683</t>
+    <t xml:space="preserve">2.19033145904541</t>
   </si>
   <si>
     <t xml:space="preserve">2.26849246025085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24667954444885</t>
+    <t xml:space="preserve">2.24668002128601</t>
   </si>
   <si>
     <t xml:space="preserve">2.24304437637329</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25213265419006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30121064186096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28303384780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34120035171509</t>
+    <t xml:space="preserve">2.25213289260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30121111869812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28303408622742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34120059013367</t>
   </si>
   <si>
     <t xml:space="preserve">2.47934556007385</t>
@@ -4331,7 +4331,7 @@
     <t xml:space="preserve">2.44844484329224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48843383789062</t>
+    <t xml:space="preserve">2.48843431472778</t>
   </si>
   <si>
     <t xml:space="preserve">2.46843957901001</t>
@@ -4340,13 +4340,13 @@
     <t xml:space="preserve">2.47207498550415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45935130119324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45753359794617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43390297889709</t>
+    <t xml:space="preserve">2.45935106277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45753312110901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43390321731567</t>
   </si>
   <si>
     <t xml:space="preserve">2.51388216018677</t>
@@ -4361,13 +4361,13 @@
     <t xml:space="preserve">2.4702570438385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40118432044983</t>
+    <t xml:space="preserve">2.40118455886841</t>
   </si>
   <si>
     <t xml:space="preserve">2.36664843559265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41754412651062</t>
+    <t xml:space="preserve">2.41754388809204</t>
   </si>
   <si>
     <t xml:space="preserve">2.2793984413147</t>
@@ -4376,49 +4376,49 @@
     <t xml:space="preserve">2.28485155105591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29212236404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27030992507935</t>
+    <t xml:space="preserve">2.29212260246277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27030968666077</t>
   </si>
   <si>
     <t xml:space="preserve">2.22668528556824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30302858352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32484102249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33029389381409</t>
+    <t xml:space="preserve">2.30302834510803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32484126091003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33029413223267</t>
   </si>
   <si>
     <t xml:space="preserve">2.29939317703247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41936135292053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43208575248718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42117929458618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43935608863831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25599455833435</t>
+    <t xml:space="preserve">2.41936159133911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4320855140686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4211790561676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43935632705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25599431991577</t>
   </si>
   <si>
     <t xml:space="preserve">2.28207540512085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27462339401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24854302406311</t>
+    <t xml:space="preserve">2.27462363243103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24854278564453</t>
   </si>
   <si>
     <t xml:space="preserve">2.22991347312927</t>
@@ -4430,28 +4430,28 @@
     <t xml:space="preserve">2.31188225746155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36590671539307</t>
+    <t xml:space="preserve">2.36590647697449</t>
   </si>
   <si>
     <t xml:space="preserve">2.40130209922791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36404395103455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29697871208191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32678556442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34168839454651</t>
+    <t xml:space="preserve">2.36404371261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29697895050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32678508758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34168863296509</t>
   </si>
   <si>
     <t xml:space="preserve">2.33982586860657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36963224411011</t>
+    <t xml:space="preserve">2.36963248252869</t>
   </si>
   <si>
     <t xml:space="preserve">2.36776971817017</t>
@@ -4460,16 +4460,16 @@
     <t xml:space="preserve">2.32864832878113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29884171485901</t>
+    <t xml:space="preserve">2.29884147644043</t>
   </si>
   <si>
     <t xml:space="preserve">2.28580117225647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28021240234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29511594772339</t>
+    <t xml:space="preserve">2.28021216392517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29511570930481</t>
   </si>
   <si>
     <t xml:space="preserve">2.30443024635315</t>
@@ -4478,16 +4478,16 @@
     <t xml:space="preserve">2.29325270652771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33051156997681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31374502182007</t>
+    <t xml:space="preserve">2.33051133155823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31374478340149</t>
   </si>
   <si>
     <t xml:space="preserve">2.28952693939209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22432494163513</t>
+    <t xml:space="preserve">2.22432470321655</t>
   </si>
   <si>
     <t xml:space="preserve">2.20569562911987</t>
@@ -4496,7 +4496,7 @@
     <t xml:space="preserve">2.16098570823669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14049363136292</t>
+    <t xml:space="preserve">2.14049339294434</t>
   </si>
   <si>
     <t xml:space="preserve">2.1069610118866</t>
@@ -4505,10 +4505,10 @@
     <t xml:space="preserve">2.09950923919678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12559032440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10882377624512</t>
+    <t xml:space="preserve">2.12559008598328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1088240146637</t>
   </si>
   <si>
     <t xml:space="preserve">2.09019470214844</t>
@@ -4517,22 +4517,22 @@
     <t xml:space="preserve">2.0585253238678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04362177848816</t>
+    <t xml:space="preserve">2.04362154006958</t>
   </si>
   <si>
     <t xml:space="preserve">2.04921054840088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08460569381714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06411385536194</t>
+    <t xml:space="preserve">2.08460593223572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06411409378052</t>
   </si>
   <si>
     <t xml:space="preserve">2.0510733127594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04175877571106</t>
+    <t xml:space="preserve">2.04175853729248</t>
   </si>
   <si>
     <t xml:space="preserve">2.09205770492554</t>
@@ -4541,7 +4541,7 @@
     <t xml:space="preserve">2.15912270545959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15353417396545</t>
+    <t xml:space="preserve">2.1535336971283</t>
   </si>
   <si>
     <t xml:space="preserve">2.13863062858582</t>
@@ -4553,7 +4553,7 @@
     <t xml:space="preserve">2.06970238685608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02312970161438</t>
+    <t xml:space="preserve">2.0231294631958</t>
   </si>
   <si>
     <t xml:space="preserve">2.01754069328308</t>
@@ -4568,7 +4568,7 @@
     <t xml:space="preserve">2.0007746219635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99332308769226</t>
+    <t xml:space="preserve">1.99332296848297</t>
   </si>
   <si>
     <t xml:space="preserve">1.97469365596771</t>
@@ -4577,22 +4577,22 @@
     <t xml:space="preserve">1.95606434345245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92625784873962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86478161811829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77349865436554</t>
+    <t xml:space="preserve">1.92625796794891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.864781498909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77349853515625</t>
   </si>
   <si>
     <t xml:space="preserve">1.78095018863678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7846759557724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80330526828766</t>
+    <t xml:space="preserve">1.78467607498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80330514907837</t>
   </si>
   <si>
     <t xml:space="preserve">1.83311200141907</t>
@@ -4607,10 +4607,10 @@
     <t xml:space="preserve">1.71109080314636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70829641819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71947383880615</t>
+    <t xml:space="preserve">1.70829629898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71947395801544</t>
   </si>
   <si>
     <t xml:space="preserve">1.67196941375732</t>
@@ -4625,7 +4625,7 @@
     <t xml:space="preserve">1.61608195304871</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63005375862122</t>
+    <t xml:space="preserve">1.63005387783051</t>
   </si>
   <si>
     <t xml:space="preserve">1.63377952575684</t>
@@ -4640,16 +4640,16 @@
     <t xml:space="preserve">1.64682006835938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53131926059723</t>
+    <t xml:space="preserve">1.53131914138794</t>
   </si>
   <si>
     <t xml:space="preserve">1.54994833469391</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53877067565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54529094696045</t>
+    <t xml:space="preserve">1.53877079486847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54529106616974</t>
   </si>
   <si>
     <t xml:space="preserve">1.54249668121338</t>
@@ -4658,19 +4658,19 @@
     <t xml:space="preserve">1.55087971687317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55646860599518</t>
+    <t xml:space="preserve">1.55646848678589</t>
   </si>
   <si>
     <t xml:space="preserve">1.56485164165497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57975506782532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61887621879578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60117840766907</t>
+    <t xml:space="preserve">1.57975494861603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61887633800507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60117852687836</t>
   </si>
   <si>
     <t xml:space="preserve">1.60956168174744</t>
@@ -4685,7 +4685,7 @@
     <t xml:space="preserve">1.59745287895203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6123560667038</t>
+    <t xml:space="preserve">1.61235594749451</t>
   </si>
   <si>
     <t xml:space="preserve">1.62073922157288</t>
@@ -4712,16 +4712,16 @@
     <t xml:space="preserve">1.6682436466217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67662680149078</t>
+    <t xml:space="preserve">1.67662668228149</t>
   </si>
   <si>
     <t xml:space="preserve">1.69059872627258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72785711288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84242653846741</t>
+    <t xml:space="preserve">1.72785699367523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8424266576767</t>
   </si>
   <si>
     <t xml:space="preserve">1.84801530838013</t>
@@ -4730,16 +4730,16 @@
     <t xml:space="preserve">1.90390276908875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92998373508453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9765567779541</t>
+    <t xml:space="preserve">1.92998361587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97655665874481</t>
   </si>
   <si>
     <t xml:space="preserve">1.96165335178375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91508042812347</t>
+    <t xml:space="preserve">1.91508030891418</t>
   </si>
   <si>
     <t xml:space="preserve">1.93557250499725</t>
@@ -4760,10 +4760,10 @@
     <t xml:space="preserve">2.09764647483826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09392046928406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11068677902222</t>
+    <t xml:space="preserve">2.09392023086548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1106870174408</t>
   </si>
   <si>
     <t xml:space="preserve">2.08646893501282</t>
@@ -4775,16 +4775,16 @@
     <t xml:space="preserve">2.11441254615784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1013720035553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03617000579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00263738632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98028254508972</t>
+    <t xml:space="preserve">2.10137224197388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03617024421692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0026376247406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98028242588043</t>
   </si>
   <si>
     <t xml:space="preserve">2.01008915901184</t>
@@ -4793,22 +4793,22 @@
     <t xml:space="preserve">2.01567792892456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98214542865753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90017700195312</t>
+    <t xml:space="preserve">1.98214554786682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90017688274384</t>
   </si>
   <si>
     <t xml:space="preserve">1.91694331169128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8927253484726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92812085151672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95420157909393</t>
+    <t xml:space="preserve">1.89272522926331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92812061309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95420169830322</t>
   </si>
   <si>
     <t xml:space="preserve">2.06783962249756</t>
@@ -4817,16 +4817,16 @@
     <t xml:space="preserve">2.03989601135254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07529139518738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09578347206116</t>
+    <t xml:space="preserve">2.0752911567688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09578371047974</t>
   </si>
   <si>
     <t xml:space="preserve">2.11813831329346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0771541595459</t>
+    <t xml:space="preserve">2.07715439796448</t>
   </si>
   <si>
     <t xml:space="preserve">2.08281922340393</t>
@@ -4838,7 +4838,7 @@
     <t xml:space="preserve">2.05827116966248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07148933410645</t>
+    <t xml:space="preserve">2.07148909568787</t>
   </si>
   <si>
     <t xml:space="preserve">2.12813878059387</t>
@@ -4859,7 +4859,7 @@
     <t xml:space="preserve">2.08093070983887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14135694503784</t>
+    <t xml:space="preserve">2.14135718345642</t>
   </si>
   <si>
     <t xml:space="preserve">2.10170245170593</t>
@@ -4871,7 +4871,7 @@
     <t xml:space="preserve">2.06771278381348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09981417655945</t>
+    <t xml:space="preserve">2.09981393814087</t>
   </si>
   <si>
     <t xml:space="preserve">2.15835213661194</t>
@@ -4901,13 +4901,13 @@
     <t xml:space="preserve">2.24143815040588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33396577835083</t>
+    <t xml:space="preserve">2.33396601676941</t>
   </si>
   <si>
     <t xml:space="preserve">2.32263612747192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22255516052246</t>
+    <t xml:space="preserve">2.22255492210388</t>
   </si>
   <si>
     <t xml:space="preserve">2.14702200889587</t>
@@ -4922,7 +4922,7 @@
     <t xml:space="preserve">2.09414911270142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0488293170929</t>
+    <t xml:space="preserve">2.04882955551147</t>
   </si>
   <si>
     <t xml:space="preserve">2.19989514350891</t>
@@ -4931,13 +4931,13 @@
     <t xml:space="preserve">2.2471034526825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31130623817444</t>
+    <t xml:space="preserve">2.31130599975586</t>
   </si>
   <si>
     <t xml:space="preserve">2.33207774162292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2943115234375</t>
+    <t xml:space="preserve">2.29431128501892</t>
   </si>
   <si>
     <t xml:space="preserve">2.35662579536438</t>
@@ -4955,13 +4955,13 @@
     <t xml:space="preserve">2.36040258407593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37550926208496</t>
+    <t xml:space="preserve">2.37550902366638</t>
   </si>
   <si>
     <t xml:space="preserve">2.41705203056335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46237206459045</t>
+    <t xml:space="preserve">2.46237182617188</t>
   </si>
   <si>
     <t xml:space="preserve">2.44160032272339</t>
@@ -4970,13 +4970,13 @@
     <t xml:space="preserve">2.46992492675781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48692011833191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50202655792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52657508850098</t>
+    <t xml:space="preserve">2.48692035675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50202679634094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5265748500824</t>
   </si>
   <si>
     <t xml:space="preserve">2.54168128967285</t>
@@ -4991,7 +4991,7 @@
     <t xml:space="preserve">2.50957989692688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55489993095398</t>
+    <t xml:space="preserve">2.5548996925354</t>
   </si>
   <si>
     <t xml:space="preserve">2.56811785697937</t>
@@ -5006,19 +5006,19 @@
     <t xml:space="preserve">2.70407724380493</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66442227363586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64553904533386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63798570632935</t>
+    <t xml:space="preserve">2.66442251205444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64553928375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63798594474792</t>
   </si>
   <si>
     <t xml:space="preserve">2.63609766960144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70218896865845</t>
+    <t xml:space="preserve">2.70218873023987</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309238433838</t>
@@ -5039,7 +5039,7 @@
     <t xml:space="preserve">2.60210776329041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55867648124695</t>
+    <t xml:space="preserve">2.55867624282837</t>
   </si>
   <si>
     <t xml:space="preserve">2.60882019996643</t>
@@ -5916,6 +5916,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.34999990463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26999998092651</t>
   </si>
 </sst>
 </file>
@@ -71306,7 +71309,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.6913078704</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>315640</v>
@@ -71327,6 +71330,32 @@
         <v>1967</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6911689815</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>757597</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>4.31400012969971</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>4.23600006103516</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>4.30999994277954</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>4.26999998092651</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>1968</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/OVS.MI.xlsx
+++ b/data/OVS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1971" uniqueCount="1971">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1974" uniqueCount="1974">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">4.89862442016602</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76365423202515</t>
+    <t xml:space="preserve">4.76365375518799</t>
   </si>
   <si>
     <t xml:space="preserve">4.64456224441528</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">4.71998643875122</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65647172927856</t>
+    <t xml:space="preserve">4.65647125244141</t>
   </si>
   <si>
     <t xml:space="preserve">4.78747224807739</t>
@@ -65,64 +65,64 @@
     <t xml:space="preserve">4.94229030609131</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69219923019409</t>
+    <t xml:space="preserve">4.69219875335693</t>
   </si>
   <si>
     <t xml:space="preserve">4.60486507415771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63662338256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61677408218384</t>
+    <t xml:space="preserve">4.6366229057312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.616774559021</t>
   </si>
   <si>
     <t xml:space="preserve">4.25156021118164</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22774219512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53341007232666</t>
+    <t xml:space="preserve">4.22774267196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5334095954895</t>
   </si>
   <si>
     <t xml:space="preserve">4.45798587799072</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47783374786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49768304824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51356077194214</t>
+    <t xml:space="preserve">4.47783422470093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49768352508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51356172561646</t>
   </si>
   <si>
     <t xml:space="preserve">4.44607734680176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62868356704712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59295606613159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51753234863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54531955718994</t>
+    <t xml:space="preserve">4.6286826133728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59295654296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51753187179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5453200340271</t>
   </si>
   <si>
     <t xml:space="preserve">4.32698583602905</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03322649002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02925634384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27934980392456</t>
+    <t xml:space="preserve">4.03322696685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02925682067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27934885025024</t>
   </si>
   <si>
     <t xml:space="preserve">4.22377252578735</t>
@@ -131,31 +131,31 @@
     <t xml:space="preserve">4.38256120681763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30316734313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46989488601685</t>
+    <t xml:space="preserve">4.30316781997681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.469895362854</t>
   </si>
   <si>
     <t xml:space="preserve">4.4659252166748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48577356338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48974275588989</t>
+    <t xml:space="preserve">4.48577308654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48974323272705</t>
   </si>
   <si>
     <t xml:space="preserve">4.271409034729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23965167999268</t>
+    <t xml:space="preserve">4.23965215682983</t>
   </si>
   <si>
     <t xml:space="preserve">4.43813705444336</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5651683807373</t>
+    <t xml:space="preserve">4.56516885757446</t>
   </si>
   <si>
     <t xml:space="preserve">4.67234992980957</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">4.50562238693237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52547121047974</t>
+    <t xml:space="preserve">4.52547073364258</t>
   </si>
   <si>
     <t xml:space="preserve">4.38653087615967</t>
@@ -179,10 +179,10 @@
     <t xml:space="preserve">4.43019771575928</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40241050720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29125785827637</t>
+    <t xml:space="preserve">4.40241003036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29125738143921</t>
   </si>
   <si>
     <t xml:space="preserve">4.12056064605713</t>
@@ -191,13 +191,13 @@
     <t xml:space="preserve">4.09674167633057</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06498432159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08880233764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15628719329834</t>
+    <t xml:space="preserve">4.06498527526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08880281448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15628671646118</t>
   </si>
   <si>
     <t xml:space="preserve">4.21186399459839</t>
@@ -206,976 +206,976 @@
     <t xml:space="preserve">4.04910516738892</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02131748199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31110572814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16422748565674</t>
+    <t xml:space="preserve">4.02131795883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31110620498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16422700881958</t>
   </si>
   <si>
     <t xml:space="preserve">4.23568201065063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50959253311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7358660697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54928874969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50165224075317</t>
+    <t xml:space="preserve">4.50959205627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73586559295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54928970336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50165319442749</t>
   </si>
   <si>
     <t xml:space="preserve">4.56119823455811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48180389404297</t>
+    <t xml:space="preserve">4.48180437088013</t>
   </si>
   <si>
     <t xml:space="preserve">4.5215015411377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55325889587402</t>
+    <t xml:space="preserve">4.55325937271118</t>
   </si>
   <si>
     <t xml:space="preserve">4.54134941101074</t>
   </si>
   <si>
+    <t xml:space="preserve">4.56913805007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5373797416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64853143692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70410776138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84304761886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89068460464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81525945663452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87877511978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91053295135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75968408584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73826885223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7667875289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90123510360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73419427871704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5671534538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51826286315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4734468460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47752046585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48974418640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63233947753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61196851730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.550856590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51418876647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33085060119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94706296920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13528966903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24529314041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2656626701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30233144760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25751495361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11084413528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09047365188599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05299186706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18825435638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16380929946899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15566062927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15973472595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10677099227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04321384429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11899280548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16788244247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26158952713013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20047664642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20862483978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23307037353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37159252166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36751842498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28603458404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27788591384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24121856689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25344133377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29825782775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22899627685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0725474357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17195844650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19232797622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10269641876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04158353805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13936471939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09862279891968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00084161758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99269342422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03343534469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19640302658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15158653259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0863995552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06114053726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3593692779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37566661834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4408540725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41233348846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31862831115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31047916412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31455278396606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2697377204895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21677303314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18010663986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14343786239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11491918563843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07417821884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06928873062134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08232641220093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06439924240112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00573062896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9601001739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05462074279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13121652603149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04647207260132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98128581047058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00410175323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98617482185364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02528762817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97476696968079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02365732192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05951023101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04810285568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05136203765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97965574264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03017568588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02039813995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99921154975891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07825136184692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14751291275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23714399337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20455074310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22492170333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01713848114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02202701568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93076586723328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91283917427063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89491319656372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87535738945007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94054436683655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93402576446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89654302597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95521116256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00247144699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3797402381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38381433486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39196348190308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35529518127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2901086807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28196048736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32677602767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2941837310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33899927139282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33492422103882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34307336807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46529865264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48159503936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40825986862183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53863382339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55493021011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52641105651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50604057312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43270444869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59567213058472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68530464172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67308187484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60381984710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70160007476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85642004013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82382583618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77493572235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7993803024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74234247207642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78308439254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72604560852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77900981903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80752992630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86456823348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04790544509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01531267166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89716148376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91753149032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88901281356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04383182525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90531015396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95012521743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05198001861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97864484786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03160953521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08457374572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23939228057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19865036010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14568519592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19457578659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05605459213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0642032623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13346433639526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11716651916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25161504745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18235445022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17827987670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25568962097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27198505401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17420530319214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16605710983276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1864275932312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10494470596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07235050201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94605112075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06827640533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98679351806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03691148757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3626823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39191770553589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3125638961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27915096282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34597587585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35432863235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32091617584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33762264251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2707986831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27497386932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1872673034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.132972240448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2039737701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22903347015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25409173965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2624454498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18309116363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.212327003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17891454696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24991512298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24573850631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28332805633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22485542297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30003356933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33344697952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40444707870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37521171569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40027046203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3835654258728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37938785552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23320960998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30838775634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2582688331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20814990997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1371488571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11208963394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1538553237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23738574981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32509326934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30421018600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29585695266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32926893234253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48797845840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53809690475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59656810760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62580347061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68845272064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61327505111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57568597793579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44203662872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62162780761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68009948730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64250993728638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37103509902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39609432220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38774156570435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2415623664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29168081283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19561958312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08285331726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88655567169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90743970870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81973075866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80302572250366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84478998184204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83643770217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94502735137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9032621383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86567354202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87820291519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8531436920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81137800216675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95755767822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92832136154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7779655456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.861496925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83226156234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7236704826355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66102266311646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69861125946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6693754196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63596296310425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70278835296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6735520362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64014053344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7194938659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79049587249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74872970581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73202419281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71114110946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67772912979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91579246520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92414474487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89490842819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84061431884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16220808029175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99932241439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02020502090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17056083679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09955978393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95338106155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98679304122925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7863187789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68608140945435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60672760009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59419822692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6150803565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63178730010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70696496963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58584451675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55243301391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5399022102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57749176025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48978424072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41043090820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44384241104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4939603805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47307729721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51902008056641</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.5691385269165</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53737926483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64853143692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70410776138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84304761886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89068365097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81526041030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87877559661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91053342819214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75968360900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73826789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76678705215454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90123462677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73419523239136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56715297698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51826333999634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47344732284546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47752046585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48974370956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63233852386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61196899414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55085611343384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51418876647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33085060119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94706320762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13528966903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24529361724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26566314697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30233192443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25751543045044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11084461212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09047412872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05299091339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18825387954712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16380929946899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15566062927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15973472595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10677051544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04321384429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11899280548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16788291931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26158905029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2004771232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20862531661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23307037353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37159252166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36751890182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28603410720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27788639068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24121809005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25344181060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29825782775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22899627685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07254791259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17195796966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19232845306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10269737243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04158353805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13936424255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09862232208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00084209442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99269342422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0334358215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19640254974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15158605575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0863995552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0611400604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3593692779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37566709518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44085359573364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41233396530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31862831115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31047964096069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31455326080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2697377204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21677255630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1801061630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14343786239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11491870880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07417726516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06928873062134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08232545852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06439971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00573110580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96010041236877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05462074279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13121604919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04647350311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98128509521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00410175323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98617482185364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02528810501099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97476744651794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02365732192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05951023101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04810237884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05136203765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.979656457901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03017616271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02039813995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99921226501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07825136184692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14751291275024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23714447021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20455074310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22492218017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01713848114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02202749252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93076610565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91284012794495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89491367340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87535738945007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94054484367371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93402576446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89654326438904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95521140098572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00247240066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3797402381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38381481170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39196395874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35529565811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29010820388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28195953369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32677602767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29418325424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33899879455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33492422103882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34307289123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46529817581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48159551620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40825986862183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53863382339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55492973327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52641153335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50604009628296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43270444869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59567213058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68530416488647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67308139801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60382032394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70160055160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85642004013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8238263130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77493572235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79938077926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74234247207642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78308439254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72604608535767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77901077270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80752944946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86456823348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04790544509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01531267166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89716100692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91753244400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88901329040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04383087158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90530967712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95012521743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05198097229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97864532470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03160953521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08457326889038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23939180374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19864988327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14568567276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19457626342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05605411529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06420278549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13346385955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11716651916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25161504745483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18235397338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17827987670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25568914413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27198457717896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17420434951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16605663299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1864275932312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10494470596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07235050201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94605112075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06827688217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98679399490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03691148757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3626823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39191818237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3125638961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27915096282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34597635269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35432863235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32091617584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33762264251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27079820632935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27497386932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18726778030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13297271728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2039737701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22903299331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25409126281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26244497299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1830906867981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21232652664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17891454696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24991512298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24573850631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28332757949829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22485589981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30003356933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33344650268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40444612503052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37521171569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40027093887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3835654258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37938737869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23320960998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30838775634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2582688331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20814990997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13714838027954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11208963394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1538553237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23738527297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32509326934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30420970916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29585695266724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32926893234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48797845840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5380973815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59656810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62580394744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68845272064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61327505111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57568550109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44203567504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62162780761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68009901046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64251041412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37103509902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39609336853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38774108886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24156284332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29168081283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1956205368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08285284042358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88655567169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90743923187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81973123550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8030252456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84479093551636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83643770217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94502782821655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9032621383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86567306518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87820339202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85314464569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81137800216675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95755767822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92832183837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77796602249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.861496925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83226108551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72367000579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66102266311646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69861125946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6693754196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63596343994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70278835296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6735520362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64014005661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71949434280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7904953956604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74872922897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73202419281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71114110946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67772912979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91579151153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92414379119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89490842819214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8406138420105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16220760345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99932193756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0202054977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17056035995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09955930709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95338153839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98679351806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7863187789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68608140945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60672807693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59419822692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6150803565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63178730010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70696496963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58584547042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55243301391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53990316390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57749176025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4897837638855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41043043136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4438419342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49396085739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47307777404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51902008056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56913805007935</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.59002113342285</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65684604644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64849233627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59837436676025</t>
+    <t xml:space="preserve">4.65684652328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64849281311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5983738899231</t>
   </si>
   <si>
     <t xml:space="preserve">4.56078577041626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48560857772827</t>
+    <t xml:space="preserve">4.48560810089111</t>
   </si>
   <si>
     <t xml:space="preserve">4.43966579437256</t>
@@ -1187,13 +1187,13 @@
     <t xml:space="preserve">4.38537073135376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18907308578491</t>
+    <t xml:space="preserve">4.18907260894775</t>
   </si>
   <si>
     <t xml:space="preserve">4.16150760650635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15148496627808</t>
+    <t xml:space="preserve">4.15148448944092</t>
   </si>
   <si>
     <t xml:space="preserve">4.15649604797363</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">4.1531548500061</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10303640365601</t>
+    <t xml:space="preserve">4.10303688049316</t>
   </si>
   <si>
     <t xml:space="preserve">4.12642574310303</t>
@@ -1217,10 +1217,10 @@
     <t xml:space="preserve">4.16986131668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17654371261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14313077926636</t>
+    <t xml:space="preserve">4.17654418945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14313125610352</t>
   </si>
   <si>
     <t xml:space="preserve">4.16819047927856</t>
@@ -1229,70 +1229,70 @@
     <t xml:space="preserve">2.83002591133118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90687394142151</t>
+    <t xml:space="preserve">2.90687417984009</t>
   </si>
   <si>
     <t xml:space="preserve">2.84339070320129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87179160118103</t>
+    <t xml:space="preserve">2.87179136276245</t>
   </si>
   <si>
     <t xml:space="preserve">2.89350914955139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80162501335144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92358064651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94863963127136</t>
+    <t xml:space="preserve">2.80162477493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92358040809631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94863986968994</t>
   </si>
   <si>
     <t xml:space="preserve">3.01713538169861</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08061861991882</t>
+    <t xml:space="preserve">3.08061838150024</t>
   </si>
   <si>
     <t xml:space="preserve">3.17083144187927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14911389350891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15746665000916</t>
+    <t xml:space="preserve">3.14911413192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15746688842773</t>
   </si>
   <si>
     <t xml:space="preserve">3.14410185813904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17918515205383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17417311668396</t>
+    <t xml:space="preserve">3.17918539047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17417335510254</t>
   </si>
   <si>
     <t xml:space="preserve">3.10400748252869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01212310791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02882957458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94529795646667</t>
+    <t xml:space="preserve">3.01212358474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02882981300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94529819488525</t>
   </si>
   <si>
     <t xml:space="preserve">2.95699262619019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89852142333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84004902839661</t>
+    <t xml:space="preserve">2.89852118492126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84004926681519</t>
   </si>
   <si>
     <t xml:space="preserve">2.8250138759613</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">2.85007309913635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74649548530579</t>
+    <t xml:space="preserve">2.74649524688721</t>
   </si>
   <si>
     <t xml:space="preserve">2.55771470069885</t>
@@ -1310,19 +1310,19 @@
     <t xml:space="preserve">2.54769158363342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51093769073486</t>
+    <t xml:space="preserve">2.51093745231628</t>
   </si>
   <si>
     <t xml:space="preserve">2.58945727348328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5009138584137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51594996452332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50592589378357</t>
+    <t xml:space="preserve">2.50091338157654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51594948768616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50592565536499</t>
   </si>
   <si>
     <t xml:space="preserve">2.47919607162476</t>
@@ -1331,7 +1331,7 @@
     <t xml:space="preserve">2.41905355453491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39566540718079</t>
+    <t xml:space="preserve">2.39566516876221</t>
   </si>
   <si>
     <t xml:space="preserve">2.36058211326599</t>
@@ -1340,37 +1340,37 @@
     <t xml:space="preserve">2.36726450920105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37728881835938</t>
+    <t xml:space="preserve">2.3772885799408</t>
   </si>
   <si>
     <t xml:space="preserve">2.27538061141968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31380534172058</t>
+    <t xml:space="preserve">2.313805103302</t>
   </si>
   <si>
     <t xml:space="preserve">2.2620153427124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27203917503357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41404247283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38062930107117</t>
+    <t xml:space="preserve">2.27203965187073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41404223442078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38062906265259</t>
   </si>
   <si>
     <t xml:space="preserve">2.30043959617615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30211067199707</t>
+    <t xml:space="preserve">2.30211091041565</t>
   </si>
   <si>
     <t xml:space="preserve">2.29709911346436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32382845878601</t>
+    <t xml:space="preserve">2.32382869720459</t>
   </si>
   <si>
     <t xml:space="preserve">2.33552289009094</t>
@@ -1382,55 +1382,55 @@
     <t xml:space="preserve">2.36559414863586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35055804252625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35222935676575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3555703163147</t>
+    <t xml:space="preserve">2.35055828094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35222911834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35557007789612</t>
   </si>
   <si>
     <t xml:space="preserve">2.25533318519592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22025060653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28039240837097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22526168823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23027372360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40067672729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44912481307983</t>
+    <t xml:space="preserve">2.22025084495544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28039264678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.225261926651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23027396202087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40067625045776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44912457466125</t>
   </si>
   <si>
     <t xml:space="preserve">2.42406558990479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31881666183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30879306793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34387588500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33218121528625</t>
+    <t xml:space="preserve">2.31881642341614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30879330635071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34387564659119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33218145370483</t>
   </si>
   <si>
     <t xml:space="preserve">2.27370977401733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18850874900818</t>
+    <t xml:space="preserve">2.18850898742676</t>
   </si>
   <si>
     <t xml:space="preserve">2.17681455612183</t>
@@ -1439,10 +1439,10 @@
     <t xml:space="preserve">2.15342593193054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21022653579712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21189665794373</t>
+    <t xml:space="preserve">2.2102267742157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21189713478088</t>
   </si>
   <si>
     <t xml:space="preserve">2.05485892295837</t>
@@ -1451,37 +1451,37 @@
     <t xml:space="preserve">2.01142287254333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97466921806335</t>
+    <t xml:space="preserve">1.97466897964478</t>
   </si>
   <si>
     <t xml:space="preserve">2.00474047660828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03815340995789</t>
+    <t xml:space="preserve">2.03815317153931</t>
   </si>
   <si>
     <t xml:space="preserve">2.1517550945282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17180275917053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18182563781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16679048538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16846060752869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15509581565857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15676665306091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11500120162964</t>
+    <t xml:space="preserve">2.17180252075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18182587623596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16679072380066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16846084594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15509629249573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15676641464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1150016784668</t>
   </si>
   <si>
     <t xml:space="preserve">2.07657742500305</t>
@@ -1490,16 +1490,16 @@
     <t xml:space="preserve">2.08994245529175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09829497337341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16010808944702</t>
+    <t xml:space="preserve">2.09829521179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1601083278656</t>
   </si>
   <si>
     <t xml:space="preserve">2.09662485122681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09161257743835</t>
+    <t xml:space="preserve">2.09161281585693</t>
   </si>
   <si>
     <t xml:space="preserve">2.02478742599487</t>
@@ -1517,28 +1517,28 @@
     <t xml:space="preserve">2.18683791160583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11834192276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06989526748657</t>
+    <t xml:space="preserve">2.11834263801575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06989479064941</t>
   </si>
   <si>
     <t xml:space="preserve">2.06321287155151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00139951705933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99972856044769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98302292823792</t>
+    <t xml:space="preserve">2.00139975547791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99972832202911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98302268981934</t>
   </si>
   <si>
     <t xml:space="preserve">1.94626927375793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87610328197479</t>
+    <t xml:space="preserve">1.8761031627655</t>
   </si>
   <si>
     <t xml:space="preserve">1.75748944282532</t>
@@ -1547,16 +1547,16 @@
     <t xml:space="preserve">1.695676445961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65391063690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62885141372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62968695163727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50439059734344</t>
+    <t xml:space="preserve">1.65391075611115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6288515329361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62968707084656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50439083576202</t>
   </si>
   <si>
     <t xml:space="preserve">1.48601388931274</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">1.31728136539459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2855396270752</t>
+    <t xml:space="preserve">1.28553974628448</t>
   </si>
   <si>
     <t xml:space="preserve">1.27133929729462</t>
@@ -1577,19 +1577,19 @@
     <t xml:space="preserve">1.24962162971497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24460971355438</t>
+    <t xml:space="preserve">1.24460959434509</t>
   </si>
   <si>
     <t xml:space="preserve">1.2897162437439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27635145187378</t>
+    <t xml:space="preserve">1.27635133266449</t>
   </si>
   <si>
     <t xml:space="preserve">1.30391657352448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31561100482941</t>
+    <t xml:space="preserve">1.3156111240387</t>
   </si>
   <si>
     <t xml:space="preserve">1.31310510635376</t>
@@ -1598,7 +1598,7 @@
     <t xml:space="preserve">1.2838693857193</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27969288825989</t>
+    <t xml:space="preserve">1.27969300746918</t>
   </si>
   <si>
     <t xml:space="preserve">1.33899998664856</t>
@@ -1607,49 +1607,49 @@
     <t xml:space="preserve">1.35152912139893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29472827911377</t>
+    <t xml:space="preserve">1.29472815990448</t>
   </si>
   <si>
     <t xml:space="preserve">1.29639852046967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2429393529892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25212776660919</t>
+    <t xml:space="preserve">1.24293911457062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2521276473999</t>
   </si>
   <si>
     <t xml:space="preserve">1.26799857616425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25296247005463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2337509393692</t>
+    <t xml:space="preserve">1.25296258926392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23375070095062</t>
   </si>
   <si>
     <t xml:space="preserve">1.25630402565002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25797462463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26048040390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36823582649231</t>
+    <t xml:space="preserve">1.2579745054245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26048052310944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36823570728302</t>
   </si>
   <si>
     <t xml:space="preserve">1.36990594863892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36405909061432</t>
+    <t xml:space="preserve">1.36405920982361</t>
   </si>
   <si>
     <t xml:space="preserve">1.34568238258362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31477546691895</t>
+    <t xml:space="preserve">1.31477534770966</t>
   </si>
   <si>
     <t xml:space="preserve">1.34484672546387</t>
@@ -1661,7 +1661,7 @@
     <t xml:space="preserve">1.23876285552979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06835901737213</t>
+    <t xml:space="preserve">1.06835913658142</t>
   </si>
   <si>
     <t xml:space="preserve">0.962275207042694</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">0.989840567111969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.633163154125214</t>
+    <t xml:space="preserve">0.633163213729858</t>
   </si>
   <si>
     <t xml:space="preserve">0.703329801559448</t>
@@ -1682,13 +1682,13 @@
     <t xml:space="preserve">0.862038195133209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958099007606506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948074817657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848673462867737</t>
+    <t xml:space="preserve">0.958098948001862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948074877262115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848673343658447</t>
   </si>
   <si>
     <t xml:space="preserve">0.913827121257782</t>
@@ -1703,28 +1703,28 @@
     <t xml:space="preserve">0.917168855667114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00487577915192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14771413803101</t>
+    <t xml:space="preserve">1.00487565994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1477142572403</t>
   </si>
   <si>
     <t xml:space="preserve">1.11430132389069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09926605224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13184344768524</t>
+    <t xml:space="preserve">1.09926617145538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13184356689453</t>
   </si>
   <si>
     <t xml:space="preserve">1.10344243049622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03578269481659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01155817508698</t>
+    <t xml:space="preserve">1.03578281402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01155829429626</t>
   </si>
   <si>
     <t xml:space="preserve">1.01824069023132</t>
@@ -1733,25 +1733,25 @@
     <t xml:space="preserve">0.999028921127319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01573538780212</t>
+    <t xml:space="preserve">1.01573550701141</t>
   </si>
   <si>
     <t xml:space="preserve">1.01322948932648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08255958557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10177218914032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12766623497009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12933731079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13017213344574</t>
+    <t xml:space="preserve">1.08255970478058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10177206993103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1276661157608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12933743000031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13017225265503</t>
   </si>
   <si>
     <t xml:space="preserve">1.1368545293808</t>
@@ -1766,13 +1766,13 @@
     <t xml:space="preserve">1.06585311889648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0324410200119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07086527347565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06334805488586</t>
+    <t xml:space="preserve">1.03244113922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07086515426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06334817409515</t>
   </si>
   <si>
     <t xml:space="preserve">1.01907622814178</t>
@@ -1784,64 +1784,64 @@
     <t xml:space="preserve">1.06501841545105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12850165367126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08506548404694</t>
+    <t xml:space="preserve">1.12850177288055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08506572246552</t>
   </si>
   <si>
     <t xml:space="preserve">1.08673596382141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07253634929657</t>
+    <t xml:space="preserve">1.07253646850586</t>
   </si>
   <si>
     <t xml:space="preserve">1.0808892250061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1051127910614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07838332653046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10010075569153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11263084411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11012482643127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22623288631439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46179032325745</t>
+    <t xml:space="preserve">1.10511291027069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07838320732117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10010087490082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1126309633255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11012494564056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22623264789581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46179020404816</t>
   </si>
   <si>
     <t xml:space="preserve">1.41584801673889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41417765617371</t>
+    <t xml:space="preserve">1.414177775383</t>
   </si>
   <si>
     <t xml:space="preserve">1.36071765422821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33064615726471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29806971549988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37324774265289</t>
+    <t xml:space="preserve">1.330646276474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29806983470917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3732476234436</t>
   </si>
   <si>
     <t xml:space="preserve">1.38744723796844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32981157302856</t>
+    <t xml:space="preserve">1.32981145381927</t>
   </si>
   <si>
     <t xml:space="preserve">1.35069346427917</t>
@@ -1862,82 +1862,82 @@
     <t xml:space="preserve">1.40248322486877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41918897628784</t>
+    <t xml:space="preserve">1.41918885707855</t>
   </si>
   <si>
     <t xml:space="preserve">1.42169487476349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42253041267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42837738990784</t>
+    <t xml:space="preserve">1.42253053188324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42837715148926</t>
   </si>
   <si>
     <t xml:space="preserve">1.39997732639313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37575280666351</t>
+    <t xml:space="preserve">1.37575268745422</t>
   </si>
   <si>
     <t xml:space="preserve">1.3941296339035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4534364938736</t>
+    <t xml:space="preserve">1.45343661308289</t>
   </si>
   <si>
     <t xml:space="preserve">1.43589532375336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52861440181732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61131036281586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59710967540741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59376895427704</t>
+    <t xml:space="preserve">1.52861452102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61131012439728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59710991382599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59376907348633</t>
   </si>
   <si>
     <t xml:space="preserve">1.57455658912659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55283880233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55116772651672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51441478729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47097873687744</t>
+    <t xml:space="preserve">1.55283892154694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55116760730743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51441490650177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47097861766815</t>
   </si>
   <si>
     <t xml:space="preserve">1.41751849651337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43422496318817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38828277587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38327085971832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33231663703918</t>
+    <t xml:space="preserve">1.43422484397888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3882828950882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38327074050903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3323165178299</t>
   </si>
   <si>
     <t xml:space="preserve">1.36739981174469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34985888004303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3030811548233</t>
+    <t xml:space="preserve">1.34985876083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30308103561401</t>
   </si>
   <si>
     <t xml:space="preserve">1.32229340076447</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">1.31644582748413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29890465736389</t>
+    <t xml:space="preserve">1.29890441894531</t>
   </si>
   <si>
     <t xml:space="preserve">1.30892860889435</t>
@@ -1955,10 +1955,10 @@
     <t xml:space="preserve">1.31059908866882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31895172595978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29222214221954</t>
+    <t xml:space="preserve">1.31895184516907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29222226142883</t>
   </si>
   <si>
     <t xml:space="preserve">1.28721010684967</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">1.25045645236969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32730543613434</t>
+    <t xml:space="preserve">1.32730555534363</t>
   </si>
   <si>
     <t xml:space="preserve">1.31143462657928</t>
@@ -1976,22 +1976,22 @@
     <t xml:space="preserve">1.31978750228882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34902286529541</t>
+    <t xml:space="preserve">1.34902310371399</t>
   </si>
   <si>
     <t xml:space="preserve">1.34651708602905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30725824832916</t>
+    <t xml:space="preserve">1.30725836753845</t>
   </si>
   <si>
     <t xml:space="preserve">1.26215088367462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26883339881897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22205638885498</t>
+    <t xml:space="preserve">1.26883327960968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22205626964569</t>
   </si>
   <si>
     <t xml:space="preserve">1.19198513031006</t>
@@ -2000,10 +2000,10 @@
     <t xml:space="preserve">1.35821151733398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32312905788422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28219890594482</t>
+    <t xml:space="preserve">1.32312917709351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28219902515411</t>
   </si>
   <si>
     <t xml:space="preserve">1.24043309688568</t>
@@ -2015,7 +2015,7 @@
     <t xml:space="preserve">1.26131594181061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32646989822388</t>
+    <t xml:space="preserve">1.32646977901459</t>
   </si>
   <si>
     <t xml:space="preserve">1.33816432952881</t>
@@ -2024,34 +2024,34 @@
     <t xml:space="preserve">1.42503654956818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48183751106262</t>
+    <t xml:space="preserve">1.48183739185333</t>
   </si>
   <si>
     <t xml:space="preserve">1.49603796005249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50272035598755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50355505943298</t>
+    <t xml:space="preserve">1.50272047519684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50355517864227</t>
   </si>
   <si>
     <t xml:space="preserve">1.54448533058167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56369769573212</t>
+    <t xml:space="preserve">1.56369781494141</t>
   </si>
   <si>
     <t xml:space="preserve">1.53863847255707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54866254329681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49186074733734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41668295860291</t>
+    <t xml:space="preserve">1.5486626625061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49186062812805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41668283939362</t>
   </si>
   <si>
     <t xml:space="preserve">1.39329481124878</t>
@@ -2060,22 +2060,22 @@
     <t xml:space="preserve">1.39078879356384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4200245141983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3749178647995</t>
+    <t xml:space="preserve">1.42002463340759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37491798400879</t>
   </si>
   <si>
     <t xml:space="preserve">1.34818840026855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33148205280304</t>
+    <t xml:space="preserve">1.33148193359375</t>
   </si>
   <si>
     <t xml:space="preserve">1.32814013957977</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29723417758942</t>
+    <t xml:space="preserve">1.29723429679871</t>
   </si>
   <si>
     <t xml:space="preserve">1.29974031448364</t>
@@ -2087,7 +2087,7 @@
     <t xml:space="preserve">1.33315229415894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26549255847931</t>
+    <t xml:space="preserve">1.26549243927002</t>
   </si>
   <si>
     <t xml:space="preserve">1.24210357666016</t>
@@ -2096,16 +2096,16 @@
     <t xml:space="preserve">1.38995325565338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37074160575867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38494122028351</t>
+    <t xml:space="preserve">1.37074172496796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3849413394928</t>
   </si>
   <si>
     <t xml:space="preserve">1.38911855220795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37993013858795</t>
+    <t xml:space="preserve">1.37993001937866</t>
   </si>
   <si>
     <t xml:space="preserve">1.45260179042816</t>
@@ -2114,13 +2114,13 @@
     <t xml:space="preserve">1.48851990699768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49687266349792</t>
+    <t xml:space="preserve">1.49687278270721</t>
   </si>
   <si>
     <t xml:space="preserve">1.50104916095734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.447589635849</t>
+    <t xml:space="preserve">1.44758975505829</t>
   </si>
   <si>
     <t xml:space="preserve">1.39914155006409</t>
@@ -2129,19 +2129,19 @@
     <t xml:space="preserve">1.54281485080719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46095454692841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39162361621857</t>
+    <t xml:space="preserve">1.4609546661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39162349700928</t>
   </si>
   <si>
     <t xml:space="preserve">1.41000044345856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40833020210266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42921280860901</t>
+    <t xml:space="preserve">1.40833008289337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4292129278183</t>
   </si>
   <si>
     <t xml:space="preserve">1.40749442577362</t>
@@ -2150,34 +2150,34 @@
     <t xml:space="preserve">1.3339878320694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32563412189484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33732855319977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36155331134796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36907029151917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44508385658264</t>
+    <t xml:space="preserve">1.32563424110413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33732867240906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36155319213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36907041072845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44508373737335</t>
   </si>
   <si>
     <t xml:space="preserve">1.4350597858429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46596658229828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47181332111359</t>
+    <t xml:space="preserve">1.46596646308899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4718132019043</t>
   </si>
   <si>
     <t xml:space="preserve">1.46513104438782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47264897823334</t>
+    <t xml:space="preserve">1.47264909744263</t>
   </si>
   <si>
     <t xml:space="preserve">1.51190888881683</t>
@@ -2186,16 +2186,16 @@
     <t xml:space="preserve">1.47014307975769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49269616603851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52276754379272</t>
+    <t xml:space="preserve">1.49269640445709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52276766300201</t>
   </si>
   <si>
     <t xml:space="preserve">1.54030883312225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53529667854309</t>
+    <t xml:space="preserve">1.53529679775238</t>
   </si>
   <si>
     <t xml:space="preserve">1.59794533252716</t>
@@ -2210,10 +2210,10 @@
     <t xml:space="preserve">1.64555788040161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59293341636658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63219320774078</t>
+    <t xml:space="preserve">1.59293353557587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63219308853149</t>
   </si>
   <si>
     <t xml:space="preserve">1.58458065986633</t>
@@ -2231,16 +2231,16 @@
     <t xml:space="preserve">1.56620371341705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56703841686249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58708655834198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64973437786102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74078285694122</t>
+    <t xml:space="preserve">1.56703853607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58708667755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64973425865173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74078297615051</t>
   </si>
   <si>
     <t xml:space="preserve">1.70737075805664</t>
@@ -2249,31 +2249,31 @@
     <t xml:space="preserve">1.71906530857086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72908842563629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7123829126358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73243010044098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69233477115631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76584208011627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74913573265076</t>
+    <t xml:space="preserve">1.72908854484558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71238279342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73243021965027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69233465194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76584219932556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74913585186005</t>
   </si>
   <si>
     <t xml:space="preserve">1.72073566913605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63887548446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60880398750305</t>
+    <t xml:space="preserve">1.63887536525726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60880422592163</t>
   </si>
   <si>
     <t xml:space="preserve">1.68565225601196</t>
@@ -2291,37 +2291,37 @@
     <t xml:space="preserve">1.68064117431641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61715698242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61548662185669</t>
+    <t xml:space="preserve">1.61715710163116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61548674106598</t>
   </si>
   <si>
     <t xml:space="preserve">1.62467515468597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61047458648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64054584503174</t>
+    <t xml:space="preserve">1.61047470569611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64054596424103</t>
   </si>
   <si>
     <t xml:space="preserve">1.62383937835693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60964000225067</t>
+    <t xml:space="preserve">1.60963988304138</t>
   </si>
   <si>
     <t xml:space="preserve">1.57789814472198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59126305580139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56202733516693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59209764003754</t>
+    <t xml:space="preserve">1.59126317501068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56202745437622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59209775924683</t>
   </si>
   <si>
     <t xml:space="preserve">1.59543943405151</t>
@@ -2330,34 +2330,34 @@
     <t xml:space="preserve">1.58290934562683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60379219055176</t>
+    <t xml:space="preserve">1.60379207134247</t>
   </si>
   <si>
     <t xml:space="preserve">1.60045146942139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58541524410248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54532074928284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54699122905731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57706248760223</t>
+    <t xml:space="preserve">1.58541548252106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54532086849213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5469913482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57706260681152</t>
   </si>
   <si>
     <t xml:space="preserve">1.43756568431854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49436664581299</t>
+    <t xml:space="preserve">1.49436676502228</t>
   </si>
   <si>
     <t xml:space="preserve">1.48935544490814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46763706207275</t>
+    <t xml:space="preserve">1.46763694286346</t>
   </si>
   <si>
     <t xml:space="preserve">1.51274359226227</t>
@@ -2366,49 +2366,49 @@
     <t xml:space="preserve">1.52610850334167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53195595741272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54782700538635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5169198513031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50940275192261</t>
+    <t xml:space="preserve">1.53195607662201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54782688617706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51691997051239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5094028711319</t>
   </si>
   <si>
     <t xml:space="preserve">1.48267221450806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26465678215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23208045959473</t>
+    <t xml:space="preserve">1.26465690135956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23208034038544</t>
   </si>
   <si>
     <t xml:space="preserve">1.18029069900513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16692590713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13601958751678</t>
+    <t xml:space="preserve">1.16692578792572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13601982593536</t>
   </si>
   <si>
     <t xml:space="preserve">1.02742910385132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.933039784431458</t>
+    <t xml:space="preserve">0.933039605617523</t>
   </si>
   <si>
     <t xml:space="preserve">0.776836395263672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.719200730323792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.695811808109283</t>
+    <t xml:space="preserve">0.719200611114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.695811748504639</t>
   </si>
   <si>
     <t xml:space="preserve">0.54670923948288</t>
@@ -2417,43 +2417,43 @@
     <t xml:space="preserve">0.613534212112427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519561350345612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599333643913269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.674928963184357</t>
+    <t xml:space="preserve">0.519561290740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599333763122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.674928843975067</t>
   </si>
   <si>
     <t xml:space="preserve">0.725047469139099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.701658606529236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.637340486049652</t>
+    <t xml:space="preserve">0.701658546924591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.637340426445007</t>
   </si>
   <si>
     <t xml:space="preserve">0.682446956634521</t>
   </si>
   <si>
-    <t xml:space="preserve">0.680358350276947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.687876403331757</t>
+    <t xml:space="preserve">0.680358290672302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.687876343727112</t>
   </si>
   <si>
     <t xml:space="preserve">0.659893751144409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643604695796967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.65947550535202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643187165260315</t>
+    <t xml:space="preserve">0.643604576587677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.659475386142731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.64318722486496</t>
   </si>
   <si>
     <t xml:space="preserve">0.627316415309906</t>
@@ -2468,22 +2468,22 @@
     <t xml:space="preserve">0.660728454589844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.646528840065002</t>
+    <t xml:space="preserve">0.646528899669647</t>
   </si>
   <si>
     <t xml:space="preserve">0.650705277919769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.638175249099731</t>
+    <t xml:space="preserve">0.638175189495087</t>
   </si>
   <si>
     <t xml:space="preserve">0.649869620800018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.640263855457306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612281203269958</t>
+    <t xml:space="preserve">0.640263915061951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612281143665314</t>
   </si>
   <si>
     <t xml:space="preserve">0.615621984004974</t>
@@ -2492,10 +2492,10 @@
     <t xml:space="preserve">0.610192537307739</t>
   </si>
   <si>
-    <t xml:space="preserve">0.605598866939545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61102819442749</t>
+    <t xml:space="preserve">0.605598747730255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.611028134822845</t>
   </si>
   <si>
     <t xml:space="preserve">0.651540040969849</t>
@@ -2507,7 +2507,7 @@
     <t xml:space="preserve">0.654881656169891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.642351567745209</t>
+    <t xml:space="preserve">0.642351627349854</t>
   </si>
   <si>
     <t xml:space="preserve">0.641516864299774</t>
@@ -2516,10 +2516,10 @@
     <t xml:space="preserve">0.655717313289642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639846444129944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.649034857749939</t>
+    <t xml:space="preserve">0.639846503734589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.649034917354584</t>
   </si>
   <si>
     <t xml:space="preserve">0.668246507644653</t>
@@ -2528,37 +2528,37 @@
     <t xml:space="preserve">0.65028703212738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.626480758190155</t>
+    <t xml:space="preserve">0.626480877399445</t>
   </si>
   <si>
     <t xml:space="preserve">0.609775125980377</t>
   </si>
   <si>
-    <t xml:space="preserve">0.606016099452972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.629822432994843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596827685832977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.574691891670227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.581792533397675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.57427453994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.601839780807495</t>
+    <t xml:space="preserve">0.606016159057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.629822373390198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596827805042267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.574691832065582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.581792593002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.574274599552155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60183972120285</t>
   </si>
   <si>
     <t xml:space="preserve">0.630657970905304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.726300477981567</t>
+    <t xml:space="preserve">0.726300418376923</t>
   </si>
   <si>
     <t xml:space="preserve">0.789366483688354</t>
@@ -2579,82 +2579,82 @@
     <t xml:space="preserve">0.901297986507416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.910486340522766</t>
+    <t xml:space="preserve">0.910486400127411</t>
   </si>
   <si>
     <t xml:space="preserve">1.00571143627167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01072335243225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968957602977753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877909064292908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924685895442963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925521671772003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938051640987396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922180891036987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892109453678131</t>
+    <t xml:space="preserve">1.01072347164154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968957662582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877909004688263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924685955047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925521552562714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938051581382751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922180950641632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892109513282776</t>
   </si>
   <si>
     <t xml:space="preserve">0.893779933452606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.895450294017792</t>
+    <t xml:space="preserve">0.895450234413147</t>
   </si>
   <si>
     <t xml:space="preserve">0.823614180088043</t>
   </si>
   <si>
-    <t xml:space="preserve">0.781013667583466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824867188930511</t>
+    <t xml:space="preserve">0.78101372718811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.824867129325867</t>
   </si>
   <si>
     <t xml:space="preserve">0.806072950363159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.785607397556305</t>
+    <t xml:space="preserve">0.78560745716095</t>
   </si>
   <si>
     <t xml:space="preserve">0.802313983440399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.797719240188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801895618438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798554837703705</t>
+    <t xml:space="preserve">0.797719299793243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80189573764801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.798554956912994</t>
   </si>
   <si>
     <t xml:space="preserve">0.77641898393631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.782266676425934</t>
+    <t xml:space="preserve">0.782266736030579</t>
   </si>
   <si>
     <t xml:space="preserve">0.766394972801208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.821525514125824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.795631527900696</t>
+    <t xml:space="preserve">0.821525573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.795631587505341</t>
   </si>
   <si>
     <t xml:space="preserve">0.86370861530304</t>
@@ -2669,52 +2669,52 @@
     <t xml:space="preserve">0.857861816883087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.836143314838409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.834890305995941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838649332523346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.800225257873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.773913025856018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789783895015717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.771825194358826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.767230570316315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.775583446025848</t>
+    <t xml:space="preserve">0.836143434047699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834890425205231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838649392127991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80022531747818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.773912966251373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789783835411072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.771825313568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767230629920959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775583326816559</t>
   </si>
   <si>
     <t xml:space="preserve">0.786860466003418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.792707204818726</t>
+    <t xml:space="preserve">0.79270726442337</t>
   </si>
   <si>
     <t xml:space="preserve">0.758877813816071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.765977561473846</t>
+    <t xml:space="preserve">0.765977621078491</t>
   </si>
   <si>
     <t xml:space="preserve">0.800642669200897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.809831082820892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799807965755463</t>
+    <t xml:space="preserve">0.809831023216248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799807906150818</t>
   </si>
   <si>
     <t xml:space="preserve">0.780178010463715</t>
@@ -2723,22 +2723,22 @@
     <t xml:space="preserve">0.770989656448364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.740918338298798</t>
+    <t xml:space="preserve">0.740918278694153</t>
   </si>
   <si>
     <t xml:space="preserve">0.717947661876678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.712100028991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.684117376804352</t>
+    <t xml:space="preserve">0.712099969387054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.684117317199707</t>
   </si>
   <si>
     <t xml:space="preserve">0.690799713134766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.69288831949234</t>
+    <t xml:space="preserve">0.692888379096985</t>
   </si>
   <si>
     <t xml:space="preserve">0.685787737369537</t>
@@ -2750,10 +2750,10 @@
     <t xml:space="preserve">0.666576147079468</t>
   </si>
   <si>
-    <t xml:space="preserve">0.682029545307159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.68745893239975</t>
+    <t xml:space="preserve">0.682029604911804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.687458992004395</t>
   </si>
   <si>
     <t xml:space="preserve">0.685370326042175</t>
@@ -2765,7 +2765,7 @@
     <t xml:space="preserve">0.69455873966217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.697482109069824</t>
+    <t xml:space="preserve">0.697482168674469</t>
   </si>
   <si>
     <t xml:space="preserve">0.70374721288681</t>
@@ -2774,13 +2774,13 @@
     <t xml:space="preserve">0.69831782579422</t>
   </si>
   <si>
-    <t xml:space="preserve">0.721288502216339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.72045361995697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.742588639259338</t>
+    <t xml:space="preserve">0.721288442611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.720453679561615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.742588698863983</t>
   </si>
   <si>
     <t xml:space="preserve">0.767647981643677</t>
@@ -2792,10 +2792,10 @@
     <t xml:space="preserve">0.715024292469025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.7818483710289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.75720739364624</t>
+    <t xml:space="preserve">0.781848430633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.757207453250885</t>
   </si>
   <si>
     <t xml:space="preserve">0.778925061225891</t>
@@ -2807,46 +2807,46 @@
     <t xml:space="preserve">0.825284600257874</t>
   </si>
   <si>
-    <t xml:space="preserve">0.850343763828278</t>
+    <t xml:space="preserve">0.850343823432922</t>
   </si>
   <si>
     <t xml:space="preserve">0.860367834568024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.847003042697906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858696639537811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843661308288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872062265872955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852014183998108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8545201420784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812755405902863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807743310928345</t>
+    <t xml:space="preserve">0.847002983093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858696699142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843661367893219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8720623254776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852014243602753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.854520201683044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812755346298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80774337053299</t>
   </si>
   <si>
     <t xml:space="preserve">0.81317275762558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.828626155853271</t>
+    <t xml:space="preserve">0.828626096248627</t>
   </si>
   <si>
     <t xml:space="preserve">0.832802534103394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.820690810680389</t>
+    <t xml:space="preserve">0.8206906914711</t>
   </si>
   <si>
     <t xml:space="preserve">0.749689340591431</t>
@@ -2858,79 +2858,79 @@
     <t xml:space="preserve">0.654464304447174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.63399875164032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.645275831222534</t>
+    <t xml:space="preserve">0.633998811244965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.645275890827179</t>
   </si>
   <si>
     <t xml:space="preserve">0.660311043262482</t>
   </si>
   <si>
-    <t xml:space="preserve">0.684534728527069</t>
+    <t xml:space="preserve">0.684534668922424</t>
   </si>
   <si>
     <t xml:space="preserve">0.68912935256958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.753030180931091</t>
+    <t xml:space="preserve">0.753030121326447</t>
   </si>
   <si>
     <t xml:space="preserve">0.784354448318481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.787696063518524</t>
+    <t xml:space="preserve">0.787696123123169</t>
   </si>
   <si>
     <t xml:space="preserve">0.803148686885834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.856191456317902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.845331728458405</t>
+    <t xml:space="preserve">0.856191396713257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.845331788063049</t>
   </si>
   <si>
     <t xml:space="preserve">0.877073407173157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.900462329387665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.889603435993195</t>
+    <t xml:space="preserve">0.90046226978302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.889603495597839</t>
   </si>
   <si>
     <t xml:space="preserve">0.887097477912903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.89043915271759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88125067949295</t>
+    <t xml:space="preserve">0.890439212322235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88125079870224</t>
   </si>
   <si>
     <t xml:space="preserve">0.904638767242432</t>
   </si>
   <si>
-    <t xml:space="preserve">0.892944276332855</t>
+    <t xml:space="preserve">0.89294421672821</t>
   </si>
   <si>
     <t xml:space="preserve">0.902132749557495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.882085502147675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867884933948517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841155409812927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.839484989643097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841990947723389</t>
+    <t xml:space="preserve">0.88208544254303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867884993553162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841155469417572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.839484930038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841991007328033</t>
   </si>
   <si>
     <t xml:space="preserve">0.840320587158203</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">0.872897028923035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.906310021877289</t>
+    <t xml:space="preserve">0.906310081481934</t>
   </si>
   <si>
     <t xml:space="preserve">0.943898439407349</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">0.95392245054245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.957263290882111</t>
+    <t xml:space="preserve">0.957263350486755</t>
   </si>
   <si>
     <t xml:space="preserve">0.965616941452026</t>
@@ -2966,10 +2966,10 @@
     <t xml:space="preserve">0.978146076202393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.961439669132233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934710144996643</t>
+    <t xml:space="preserve">0.961439549922943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934709966182709</t>
   </si>
   <si>
     <t xml:space="preserve">0.902968347072601</t>
@@ -2978,16 +2978,16 @@
     <t xml:space="preserve">0.874567449092865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.852849721908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867050290107727</t>
+    <t xml:space="preserve">0.852849781513214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867050230503082</t>
   </si>
   <si>
     <t xml:space="preserve">0.878744721412659</t>
   </si>
   <si>
-    <t xml:space="preserve">0.907144784927368</t>
+    <t xml:space="preserve">0.907144725322723</t>
   </si>
   <si>
     <t xml:space="preserve">0.931369304656982</t>
@@ -3002,13 +3002,13 @@
     <t xml:space="preserve">0.912992417812347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947240054607391</t>
+    <t xml:space="preserve">0.947240114212036</t>
   </si>
   <si>
     <t xml:space="preserve">0.899626731872559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.929697930812836</t>
+    <t xml:space="preserve">0.92969799041748</t>
   </si>
   <si>
     <t xml:space="preserve">0.938886404037476</t>
@@ -3017,67 +3017,67 @@
     <t xml:space="preserve">0.93721604347229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.942228138446808</t>
+    <t xml:space="preserve">0.942228078842163</t>
   </si>
   <si>
     <t xml:space="preserve">0.941392421722412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.946404576301575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.935545682907104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975640058517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14687848091125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18947911262512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17360842227936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16024339199066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15773737430573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17193794250488</t>
+    <t xml:space="preserve">0.946404457092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93554562330246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975639998912811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14687860012054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18947923183441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17360830307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16024351119995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15773749351501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17193782329559</t>
   </si>
   <si>
     <t xml:space="preserve">1.1385258436203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10928928852081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11096048355103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1067841053009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11179542541504</t>
+    <t xml:space="preserve">1.1092894077301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11096060276031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10678422451019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11179530620575</t>
   </si>
   <si>
     <t xml:space="preserve">1.1310076713562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12098371982574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16358506679535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14520823955536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11513686180115</t>
+    <t xml:space="preserve">1.12098383903503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16358518600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14520835876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11513698101044</t>
   </si>
   <si>
     <t xml:space="preserve">1.10761892795563</t>
@@ -3092,49 +3092,49 @@
     <t xml:space="preserve">1.43923699855804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43673086166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44007170200348</t>
+    <t xml:space="preserve">1.43673098087311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44007158279419</t>
   </si>
   <si>
     <t xml:space="preserve">1.4066596031189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41167163848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39747130870819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43840146064758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47682547569275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45928418636322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44090723991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43338942527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48100185394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41334223747253</t>
+    <t xml:space="preserve">1.41167175769806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3974711894989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.438401222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47682535648346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45928430557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44090735912323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43338930606842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48100197315216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41334211826324</t>
   </si>
   <si>
     <t xml:space="preserve">1.42587125301361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58792126178741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55033278465271</t>
+    <t xml:space="preserve">1.5879213809967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.550332903862</t>
   </si>
   <si>
     <t xml:space="preserve">1.62634551525116</t>
@@ -3149,16 +3149,16 @@
     <t xml:space="preserve">1.61966300010681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62718093395233</t>
+    <t xml:space="preserve">1.62718105316162</t>
   </si>
   <si>
     <t xml:space="preserve">1.6138162612915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45677828788757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39830708503723</t>
+    <t xml:space="preserve">1.45677816867828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39830696582794</t>
   </si>
   <si>
     <t xml:space="preserve">1.34317636489868</t>
@@ -3167,16 +3167,16 @@
     <t xml:space="preserve">1.3565411567688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35904717445374</t>
+    <t xml:space="preserve">1.35904729366302</t>
   </si>
   <si>
     <t xml:space="preserve">1.36489391326904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40276575088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43466711044312</t>
+    <t xml:space="preserve">1.4027658700943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4346672296524</t>
   </si>
   <si>
     <t xml:space="preserve">1.41251361370087</t>
@@ -3185,7 +3185,7 @@
     <t xml:space="preserve">1.39390444755554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39213228225708</t>
+    <t xml:space="preserve">1.39213216304779</t>
   </si>
   <si>
     <t xml:space="preserve">1.3336466550827</t>
@@ -3197,22 +3197,22 @@
     <t xml:space="preserve">1.49049437046051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5179648399353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53214287757874</t>
+    <t xml:space="preserve">1.51796472072601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53214299678802</t>
   </si>
   <si>
     <t xml:space="preserve">1.58442544937134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52859854698181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54897975921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54454898834229</t>
+    <t xml:space="preserve">1.52859842777252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54897964000702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54454910755157</t>
   </si>
   <si>
     <t xml:space="preserve">1.53834593296051</t>
@@ -3227,7 +3227,7 @@
     <t xml:space="preserve">1.6145544052124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60657918453217</t>
+    <t xml:space="preserve">1.60657906532288</t>
   </si>
   <si>
     <t xml:space="preserve">1.5693610906601</t>
@@ -3236,10 +3236,10 @@
     <t xml:space="preserve">1.58885622024536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6039205789566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63582181930542</t>
+    <t xml:space="preserve">1.60392069816589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63582193851471</t>
   </si>
   <si>
     <t xml:space="preserve">1.62518811225891</t>
@@ -3251,10 +3251,10 @@
     <t xml:space="preserve">1.58353924751282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51885080337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.520623087883</t>
+    <t xml:space="preserve">1.51885092258453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52062296867371</t>
   </si>
   <si>
     <t xml:space="preserve">1.4931526184082</t>
@@ -3263,16 +3263,16 @@
     <t xml:space="preserve">1.49758350849152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52505397796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5073310136795</t>
+    <t xml:space="preserve">1.52505385875702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50733089447021</t>
   </si>
   <si>
     <t xml:space="preserve">1.50112795829773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54011833667755</t>
+    <t xml:space="preserve">1.54011821746826</t>
   </si>
   <si>
     <t xml:space="preserve">1.53037071228027</t>
@@ -3281,49 +3281,49 @@
     <t xml:space="preserve">1.55341041088104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63848006725311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6632924079895</t>
+    <t xml:space="preserve">1.6384801864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66329216957092</t>
   </si>
   <si>
     <t xml:space="preserve">1.56404423713684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5170783996582</t>
+    <t xml:space="preserve">1.51707851886749</t>
   </si>
   <si>
     <t xml:space="preserve">1.48872184753418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4656822681427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4240335226059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44707322120667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46656847000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61809885501862</t>
+    <t xml:space="preserve">1.46568238735199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42403340339661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44707310199738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46656823158264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61809897422791</t>
   </si>
   <si>
     <t xml:space="preserve">1.82900106906891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84672403335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9052095413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89634823799133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98319029808044</t>
+    <t xml:space="preserve">1.846724152565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90520989894867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89634835720062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98319041728973</t>
   </si>
   <si>
     <t xml:space="preserve">2.03635907173157</t>
@@ -3335,88 +3335,88 @@
     <t xml:space="preserve">2.17105293273926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9601503610611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88925898075104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96192288398743</t>
+    <t xml:space="preserve">1.96015048027039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88925886154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96192276477814</t>
   </si>
   <si>
     <t xml:space="preserve">1.94597220420837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01863646507263</t>
+    <t xml:space="preserve">2.01863598823547</t>
   </si>
   <si>
     <t xml:space="preserve">2.10902285575867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07534909248352</t>
+    <t xml:space="preserve">2.07534956932068</t>
   </si>
   <si>
     <t xml:space="preserve">2.10547804832458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13737916946411</t>
+    <t xml:space="preserve">2.13737940788269</t>
   </si>
   <si>
     <t xml:space="preserve">2.12674570083618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17814159393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16396331787109</t>
+    <t xml:space="preserve">2.17814183235168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16396355628967</t>
   </si>
   <si>
     <t xml:space="preserve">2.17636966705322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18168640136719</t>
+    <t xml:space="preserve">2.18168663978577</t>
   </si>
   <si>
     <t xml:space="preserve">2.24371671676636</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17991423606873</t>
+    <t xml:space="preserve">2.1799144744873</t>
   </si>
   <si>
     <t xml:space="preserve">2.1232008934021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14624071121216</t>
+    <t xml:space="preserve">2.14624094963074</t>
   </si>
   <si>
     <t xml:space="preserve">2.19763708114624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30574679374695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28625130653381</t>
+    <t xml:space="preserve">2.30574655532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28625154495239</t>
   </si>
   <si>
     <t xml:space="preserve">2.31992506980896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34828186035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41740083694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44575762748718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38372778892517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46348023414612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42448997497559</t>
+    <t xml:space="preserve">2.34828162193298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.417400598526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4457573890686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38372731208801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46347999572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42448973655701</t>
   </si>
   <si>
     <t xml:space="preserve">2.47411417961121</t>
@@ -3425,7 +3425,7 @@
     <t xml:space="preserve">2.51310443878174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50955963134766</t>
+    <t xml:space="preserve">2.50955986976624</t>
   </si>
   <si>
     <t xml:space="preserve">2.43157935142517</t>
@@ -3443,28 +3443,28 @@
     <t xml:space="preserve">2.37841057777405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21004295349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38904452323914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47943115234375</t>
+    <t xml:space="preserve">2.21004319190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38904428482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47943091392517</t>
   </si>
   <si>
     <t xml:space="preserve">2.49183702468872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56095600128174</t>
+    <t xml:space="preserve">2.56095623970032</t>
   </si>
   <si>
     <t xml:space="preserve">2.65665984153748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64070916175842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63184762001038</t>
+    <t xml:space="preserve">2.640709400177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63184785842896</t>
   </si>
   <si>
     <t xml:space="preserve">2.65311503410339</t>
@@ -3473,52 +3473,52 @@
     <t xml:space="preserve">2.59640192985535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52373838424683</t>
+    <t xml:space="preserve">2.52373814582825</t>
   </si>
   <si>
     <t xml:space="preserve">2.33233070373535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31815266609192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2968852519989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28270721435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27561783790588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25966715812683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30929136276245</t>
+    <t xml:space="preserve">2.31815242767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29688549041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28270673751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27561807632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25966691970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30929112434387</t>
   </si>
   <si>
     <t xml:space="preserve">2.27916240692139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28802371025085</t>
+    <t xml:space="preserve">2.28802394866943</t>
   </si>
   <si>
     <t xml:space="preserve">2.26852869987488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3660044670105</t>
+    <t xml:space="preserve">2.36600470542908</t>
   </si>
   <si>
     <t xml:space="preserve">2.30751919746399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24017190933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14978551864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16041922569275</t>
+    <t xml:space="preserve">2.24017214775085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14978528022766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16041898727417</t>
   </si>
   <si>
     <t xml:space="preserve">2.17459726333618</t>
@@ -3533,16 +3533,16 @@
     <t xml:space="preserve">2.05762624740601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16928052902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1958646774292</t>
+    <t xml:space="preserve">2.16928029060364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19586491584778</t>
   </si>
   <si>
     <t xml:space="preserve">2.13560700416565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39258885383606</t>
+    <t xml:space="preserve">2.39258909225464</t>
   </si>
   <si>
     <t xml:space="preserve">2.39436101913452</t>
@@ -3554,7 +3554,7 @@
     <t xml:space="preserve">1.99382412433624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12142896652222</t>
+    <t xml:space="preserve">2.12142872810364</t>
   </si>
   <si>
     <t xml:space="preserve">2.11965656280518</t>
@@ -3563,22 +3563,22 @@
     <t xml:space="preserve">2.09484457969666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01331925392151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08066654205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99205183982849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03458666801453</t>
+    <t xml:space="preserve">2.01331901550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08066606521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99205148220062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03458642959595</t>
   </si>
   <si>
     <t xml:space="preserve">2.02926969528198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93179404735565</t>
+    <t xml:space="preserve">1.93179416656494</t>
   </si>
   <si>
     <t xml:space="preserve">2.01509141921997</t>
@@ -3590,16 +3590,16 @@
     <t xml:space="preserve">1.86799156665802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90166509151459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80596160888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64556932449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56315803527832</t>
+    <t xml:space="preserve">1.90166485309601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80596148967743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6455694437027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56315815448761</t>
   </si>
   <si>
     <t xml:space="preserve">1.56847488880157</t>
@@ -3611,25 +3611,25 @@
     <t xml:space="preserve">1.5799947977066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59505927562714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65974771976471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78646624088287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75545132160187</t>
+    <t xml:space="preserve">1.59505915641785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.659747838974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78646636009216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75545120239258</t>
   </si>
   <si>
     <t xml:space="preserve">1.73684227466583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73418378829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70671331882477</t>
+    <t xml:space="preserve">1.73418390750885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70671343803406</t>
   </si>
   <si>
     <t xml:space="preserve">1.65088629722595</t>
@@ -3638,34 +3638,34 @@
     <t xml:space="preserve">1.66595065593719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67924284934998</t>
+    <t xml:space="preserve">1.67924296855927</t>
   </si>
   <si>
     <t xml:space="preserve">1.72798085212708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8644472360611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83431804180145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7457035779953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78469407558441</t>
+    <t xml:space="preserve">1.86444711685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83431816101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74570369720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78469395637512</t>
   </si>
   <si>
     <t xml:space="preserve">1.76254045963287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72886693477631</t>
+    <t xml:space="preserve">1.7288670539856</t>
   </si>
   <si>
     <t xml:space="preserve">1.67038154602051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64113879203796</t>
+    <t xml:space="preserve">1.64113855361938</t>
   </si>
   <si>
     <t xml:space="preserve">1.60126221179962</t>
@@ -3674,22 +3674,22 @@
     <t xml:space="preserve">1.61987113952637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71025788784027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70051050186157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67835688591003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62961888313293</t>
+    <t xml:space="preserve">1.71025800704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70051038265228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67835676670074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62961876392365</t>
   </si>
   <si>
     <t xml:space="preserve">1.63936650753021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63050496578217</t>
+    <t xml:space="preserve">1.63050508499146</t>
   </si>
   <si>
     <t xml:space="preserve">1.60923767089844</t>
@@ -3701,13 +3701,13 @@
     <t xml:space="preserve">1.55075204372406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46302366256714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47897434234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54189074039459</t>
+    <t xml:space="preserve">1.46302378177643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47897446155548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5418906211853</t>
   </si>
   <si>
     <t xml:space="preserve">1.60835146903992</t>
@@ -3716,13 +3716,13 @@
     <t xml:space="preserve">1.58974242210388</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64468324184418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6074652671814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6003760099411</t>
+    <t xml:space="preserve">1.64468336105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60746514797211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60037612915039</t>
   </si>
   <si>
     <t xml:space="preserve">1.52594006061554</t>
@@ -3731,7 +3731,7 @@
     <t xml:space="preserve">1.52150928974152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63139092922211</t>
+    <t xml:space="preserve">1.63139116764069</t>
   </si>
   <si>
     <t xml:space="preserve">1.64734172821045</t>
@@ -3740,37 +3740,37 @@
     <t xml:space="preserve">1.72266399860382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69076287746429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71646106243134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78114938735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84495162963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80773377418518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79887235164642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79532778263092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65797555446625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45593452453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41871654987335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46506798267365</t>
+    <t xml:space="preserve">1.690762758255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71646094322205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78114950656891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84495174884796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80773389339447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79887223243713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79532790184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65797543525696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45593464374542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41871643066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46506786346436</t>
   </si>
   <si>
     <t xml:space="preserve">1.4768830537796</t>
@@ -3779,25 +3779,25 @@
     <t xml:space="preserve">1.48960697650909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45779705047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47597408294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43689346313477</t>
+    <t xml:space="preserve">1.45779716968536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47597420215607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43689358234406</t>
   </si>
   <si>
     <t xml:space="preserve">1.47415637969971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48142731189728</t>
+    <t xml:space="preserve">1.48142719268799</t>
   </si>
   <si>
     <t xml:space="preserve">1.41417229175568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37236511707306</t>
+    <t xml:space="preserve">1.37236499786377</t>
   </si>
   <si>
     <t xml:space="preserve">1.37872707843781</t>
@@ -3806,40 +3806,40 @@
     <t xml:space="preserve">1.30147480964661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32783138751984</t>
+    <t xml:space="preserve">1.32783150672913</t>
   </si>
   <si>
     <t xml:space="preserve">1.37418282032013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40781033039093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38599789142609</t>
+    <t xml:space="preserve">1.40781044960022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3859977722168</t>
   </si>
   <si>
     <t xml:space="preserve">1.31510758399963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28420650959015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27966225147247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30874574184418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32692265510559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39781296253204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37145626544952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3578234910965</t>
+    <t xml:space="preserve">1.28420662879944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27966237068176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30874562263489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3269225358963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39781284332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37145614624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35782337188721</t>
   </si>
   <si>
     <t xml:space="preserve">1.35691475868225</t>
@@ -3848,16 +3848,16 @@
     <t xml:space="preserve">1.29693043231964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31328976154327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33328449726105</t>
+    <t xml:space="preserve">1.31328988075256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33328461647034</t>
   </si>
   <si>
     <t xml:space="preserve">1.41962540149689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42689633369446</t>
+    <t xml:space="preserve">1.42689621448517</t>
   </si>
   <si>
     <t xml:space="preserve">1.40144836902618</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">1.48778915405273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49506008625031</t>
+    <t xml:space="preserve">1.49505996704102</t>
   </si>
   <si>
     <t xml:space="preserve">1.48869812488556</t>
@@ -3890,13 +3890,13 @@
     <t xml:space="preserve">1.50051307678223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48051834106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40326607227325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43234932422638</t>
+    <t xml:space="preserve">1.48051846027374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40326619148254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43234920501709</t>
   </si>
   <si>
     <t xml:space="preserve">1.41144573688507</t>
@@ -3908,7 +3908,7 @@
     <t xml:space="preserve">1.34328198432922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3732738494873</t>
+    <t xml:space="preserve">1.37327396869659</t>
   </si>
   <si>
     <t xml:space="preserve">1.3760005235672</t>
@@ -3917,28 +3917,28 @@
     <t xml:space="preserve">1.36236774921417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39235985279083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33601105213165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35237038135529</t>
+    <t xml:space="preserve">1.39235973358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33601117134094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35237050056458</t>
   </si>
   <si>
     <t xml:space="preserve">1.36963856220245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35964119434357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41326344013214</t>
+    <t xml:space="preserve">1.35964131355286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41326332092285</t>
   </si>
   <si>
     <t xml:space="preserve">1.43507587909698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41689884662628</t>
+    <t xml:space="preserve">1.41689896583557</t>
   </si>
   <si>
     <t xml:space="preserve">1.46870338916779</t>
@@ -3947,31 +3947,31 @@
     <t xml:space="preserve">1.41235458850861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39872181415558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70591354370117</t>
+    <t xml:space="preserve">1.39872169494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70591342449188</t>
   </si>
   <si>
     <t xml:space="preserve">1.6859188079834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58412742614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57867431640625</t>
+    <t xml:space="preserve">1.58412754535675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57867443561554</t>
   </si>
   <si>
     <t xml:space="preserve">1.59139823913574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56322383880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49960422515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55777072906494</t>
+    <t xml:space="preserve">1.56322395801544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4996041059494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55777084827423</t>
   </si>
   <si>
     <t xml:space="preserve">1.55231761932373</t>
@@ -3983,7 +3983,7 @@
     <t xml:space="preserve">1.58140099048615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53777599334717</t>
+    <t xml:space="preserve">1.53777611255646</t>
   </si>
   <si>
     <t xml:space="preserve">1.52323436737061</t>
@@ -3992,10 +3992,10 @@
     <t xml:space="preserve">1.56049728393555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53323185443878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59503352642059</t>
+    <t xml:space="preserve">1.53323173522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59503364562988</t>
   </si>
   <si>
     <t xml:space="preserve">1.59412467479706</t>
@@ -4004,13 +4004,13 @@
     <t xml:space="preserve">1.64047610759735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65774428844452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65865325927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65956199169159</t>
+    <t xml:space="preserve">1.65774440765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65865337848663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65956211090088</t>
   </si>
   <si>
     <t xml:space="preserve">1.6704683303833</t>
@@ -4022,16 +4022,16 @@
     <t xml:space="preserve">1.79225432872772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78861904144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73045241832733</t>
+    <t xml:space="preserve">1.78861892223358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73045253753662</t>
   </si>
   <si>
     <t xml:space="preserve">1.71772849559784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72681701183319</t>
+    <t xml:space="preserve">1.72681713104248</t>
   </si>
   <si>
     <t xml:space="preserve">1.77135074138641</t>
@@ -4040,19 +4040,19 @@
     <t xml:space="preserve">1.73136126995087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75135600566864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78771007061005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84860301017761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8667801618576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87223327159882</t>
+    <t xml:space="preserve">1.75135612487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78771018981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8486031293869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86677992343903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87223315238953</t>
   </si>
   <si>
     <t xml:space="preserve">1.89949882030487</t>
@@ -4067,31 +4067,31 @@
     <t xml:space="preserve">1.90676963329315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9540296792984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97038900852203</t>
+    <t xml:space="preserve">1.95403015613556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97038912773132</t>
   </si>
   <si>
     <t xml:space="preserve">2.00492548942566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99583685398102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97220683097839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97402465343475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99038398265839</t>
+    <t xml:space="preserve">1.99583697319031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97220695018768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97402429580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9903838634491</t>
   </si>
   <si>
     <t xml:space="preserve">2.04491496086121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13398265838623</t>
+    <t xml:space="preserve">2.13398241996765</t>
   </si>
   <si>
     <t xml:space="preserve">2.15397691726685</t>
@@ -4100,37 +4100,37 @@
     <t xml:space="preserve">2.12307596206665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11944079399109</t>
+    <t xml:space="preserve">2.11944103240967</t>
   </si>
   <si>
     <t xml:space="preserve">2.13761782646179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16851878166199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11035203933716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10308146476746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10126399993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97584235668182</t>
+    <t xml:space="preserve">2.16851854324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11035227775574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10308122634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10126376152039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97584223747253</t>
   </si>
   <si>
     <t xml:space="preserve">2.02128481864929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85223865509033</t>
+    <t xml:space="preserve">1.85223853588104</t>
   </si>
   <si>
     <t xml:space="preserve">1.89041018486023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91222286224365</t>
+    <t xml:space="preserve">1.91222274303436</t>
   </si>
   <si>
     <t xml:space="preserve">1.92676424980164</t>
@@ -4142,13 +4142,13 @@
     <t xml:space="preserve">1.93948817253113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90131664276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91404044628143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96311855316162</t>
+    <t xml:space="preserve">1.90131640434265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91404032707214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96311843395233</t>
   </si>
   <si>
     <t xml:space="preserve">1.96857130527496</t>
@@ -4160,16 +4160,16 @@
     <t xml:space="preserve">2.05945658683777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10489916801453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12852907180786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12671136856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09944605827332</t>
+    <t xml:space="preserve">2.10489892959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12852931022644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12671160697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09944581985474</t>
   </si>
   <si>
     <t xml:space="preserve">2.01946687698364</t>
@@ -4178,13 +4178,13 @@
     <t xml:space="preserve">2.07218050956726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06309175491333</t>
+    <t xml:space="preserve">2.06309223175049</t>
   </si>
   <si>
     <t xml:space="preserve">2.03764414787292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00310778617859</t>
+    <t xml:space="preserve">2.00310754776001</t>
   </si>
   <si>
     <t xml:space="preserve">2.01219630241394</t>
@@ -4193,22 +4193,22 @@
     <t xml:space="preserve">2.01764941215515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00129008293152</t>
+    <t xml:space="preserve">2.00128960609436</t>
   </si>
   <si>
     <t xml:space="preserve">2.27394556999207</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2484974861145</t>
+    <t xml:space="preserve">2.24849724769592</t>
   </si>
   <si>
     <t xml:space="preserve">2.31757020950317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30848169326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33211159706116</t>
+    <t xml:space="preserve">2.3084819316864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33211183547974</t>
   </si>
   <si>
     <t xml:space="preserve">2.37210130691528</t>
@@ -4217,13 +4217,13 @@
     <t xml:space="preserve">2.41572618484497</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37573671340942</t>
+    <t xml:space="preserve">2.375736951828</t>
   </si>
   <si>
     <t xml:space="preserve">2.40845561027527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39754915237427</t>
+    <t xml:space="preserve">2.39754891395569</t>
   </si>
   <si>
     <t xml:space="preserve">2.38846063613892</t>
@@ -4232,16 +4232,16 @@
     <t xml:space="preserve">2.39209580421448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35755968093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34483551979065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30666422843933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3157525062561</t>
+    <t xml:space="preserve">2.3575599193573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34483575820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30666399002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31575274467468</t>
   </si>
   <si>
     <t xml:space="preserve">2.33574724197388</t>
@@ -4250,16 +4250,16 @@
     <t xml:space="preserve">2.33938264846802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38118982315063</t>
+    <t xml:space="preserve">2.38118958473206</t>
   </si>
   <si>
     <t xml:space="preserve">2.40663766860962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40481972694397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39027833938599</t>
+    <t xml:space="preserve">2.40481948852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39027857780457</t>
   </si>
   <si>
     <t xml:space="preserve">2.37937211990356</t>
@@ -4268,22 +4268,22 @@
     <t xml:space="preserve">2.32302331924438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28666949272156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18487811088562</t>
+    <t xml:space="preserve">2.28666925430298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18487787246704</t>
   </si>
   <si>
     <t xml:space="preserve">2.23213815689087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18306016921997</t>
+    <t xml:space="preserve">2.18306040763855</t>
   </si>
   <si>
     <t xml:space="preserve">2.143070936203</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20487284660339</t>
+    <t xml:space="preserve">2.20487260818481</t>
   </si>
   <si>
     <t xml:space="preserve">2.20669031143188</t>
@@ -4292,13 +4292,13 @@
     <t xml:space="preserve">2.17033648490906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13943552970886</t>
+    <t xml:space="preserve">2.13943529129028</t>
   </si>
   <si>
     <t xml:space="preserve">2.14670634269714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14852404594421</t>
+    <t xml:space="preserve">2.14852380752563</t>
   </si>
   <si>
     <t xml:space="preserve">2.19578409194946</t>
@@ -4307,13 +4307,13 @@
     <t xml:space="preserve">2.19033098220825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26849222183228</t>
+    <t xml:space="preserve">2.26849246025085</t>
   </si>
   <si>
     <t xml:space="preserve">2.24667978286743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24304461479187</t>
+    <t xml:space="preserve">2.24304413795471</t>
   </si>
   <si>
     <t xml:space="preserve">2.25213289260864</t>
@@ -4322,13 +4322,13 @@
     <t xml:space="preserve">2.30121088027954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28303408622742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34120059013367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47934579849243</t>
+    <t xml:space="preserve">2.28303384780884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34120011329651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47934556007385</t>
   </si>
   <si>
     <t xml:space="preserve">2.44844484329224</t>
@@ -4337,34 +4337,34 @@
     <t xml:space="preserve">2.4884340763092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46843934059143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47207474708557</t>
+    <t xml:space="preserve">2.46843957901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47207498550415</t>
   </si>
   <si>
     <t xml:space="preserve">2.45935106277466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45753335952759</t>
+    <t xml:space="preserve">2.45753359794617</t>
   </si>
   <si>
     <t xml:space="preserve">2.43390297889709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51388216018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46480393409729</t>
+    <t xml:space="preserve">2.51388192176819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46480417251587</t>
   </si>
   <si>
     <t xml:space="preserve">2.50297570228577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47025680541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40118432044983</t>
+    <t xml:space="preserve">2.47025728225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40118455886841</t>
   </si>
   <si>
     <t xml:space="preserve">2.36664843559265</t>
@@ -4376,25 +4376,25 @@
     <t xml:space="preserve">2.2793984413147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28485155105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29212236404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27031016349792</t>
+    <t xml:space="preserve">2.28485131263733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29212260246277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27030992507935</t>
   </si>
   <si>
     <t xml:space="preserve">2.22668528556824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30302834510803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32484126091003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33029389381409</t>
+    <t xml:space="preserve">2.30302858352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32484102249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33029413223267</t>
   </si>
   <si>
     <t xml:space="preserve">2.29939317703247</t>
@@ -4403,7 +4403,7 @@
     <t xml:space="preserve">2.41936159133911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4320855140686</t>
+    <t xml:space="preserve">2.43208527565002</t>
   </si>
   <si>
     <t xml:space="preserve">2.42117929458618</t>
@@ -4412,22 +4412,22 @@
     <t xml:space="preserve">2.43935632705688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25599431991577</t>
+    <t xml:space="preserve">2.25599455833435</t>
   </si>
   <si>
     <t xml:space="preserve">2.28207540512085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27462339401245</t>
+    <t xml:space="preserve">2.27462363243103</t>
   </si>
   <si>
     <t xml:space="preserve">2.24854278564453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22991371154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30070471763611</t>
+    <t xml:space="preserve">2.22991347312927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30070447921753</t>
   </si>
   <si>
     <t xml:space="preserve">2.31188225746155</t>
@@ -4436,22 +4436,22 @@
     <t xml:space="preserve">2.36590671539307</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40130209922791</t>
+    <t xml:space="preserve">2.40130233764648</t>
   </si>
   <si>
     <t xml:space="preserve">2.36404395103455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29697895050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32678556442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34168863296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33982586860657</t>
+    <t xml:space="preserve">2.29697847366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32678532600403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34168839454651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33982610702515</t>
   </si>
   <si>
     <t xml:space="preserve">2.36963248252869</t>
@@ -4460,34 +4460,34 @@
     <t xml:space="preserve">2.36776971817017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32864856719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29884171485901</t>
+    <t xml:space="preserve">2.32864832878113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29884147644043</t>
   </si>
   <si>
     <t xml:space="preserve">2.28580117225647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28021240234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29511594772339</t>
+    <t xml:space="preserve">2.28021216392517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29511570930481</t>
   </si>
   <si>
     <t xml:space="preserve">2.30443024635315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29325270652771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33051133155823</t>
+    <t xml:space="preserve">2.29325294494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33051156997681</t>
   </si>
   <si>
     <t xml:space="preserve">2.31374502182007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28952670097351</t>
+    <t xml:space="preserve">2.28952693939209</t>
   </si>
   <si>
     <t xml:space="preserve">2.22432494163513</t>
@@ -4496,7 +4496,7 @@
     <t xml:space="preserve">2.20569562911987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16098546981812</t>
+    <t xml:space="preserve">2.16098570823669</t>
   </si>
   <si>
     <t xml:space="preserve">2.14049363136292</t>
@@ -4514,16 +4514,16 @@
     <t xml:space="preserve">2.10882377624512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09019470214844</t>
+    <t xml:space="preserve">2.09019446372986</t>
   </si>
   <si>
     <t xml:space="preserve">2.0585253238678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04362177848816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04921054840088</t>
+    <t xml:space="preserve">2.04362154006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04921078681946</t>
   </si>
   <si>
     <t xml:space="preserve">2.08460593223572</t>
@@ -4550,19 +4550,19 @@
     <t xml:space="preserve">2.13863062858582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12186455726624</t>
+    <t xml:space="preserve">2.12186431884766</t>
   </si>
   <si>
     <t xml:space="preserve">2.06970238685608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02312970161438</t>
+    <t xml:space="preserve">2.0231294631958</t>
   </si>
   <si>
     <t xml:space="preserve">2.01754069328308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9989116191864</t>
+    <t xml:space="preserve">1.99891173839569</t>
   </si>
   <si>
     <t xml:space="preserve">2.01195240020752</t>
@@ -4577,19 +4577,19 @@
     <t xml:space="preserve">1.97469365596771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95606446266174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92625784873962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86478161811829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77349853515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78095018863678</t>
+    <t xml:space="preserve">1.95606458187103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9262580871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86478173732758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77349865436554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78095006942749</t>
   </si>
   <si>
     <t xml:space="preserve">1.78467607498169</t>
@@ -4601,40 +4601,40 @@
     <t xml:space="preserve">1.83311200141907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80237364768982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75673222541809</t>
+    <t xml:space="preserve">1.80237376689911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75673234462738</t>
   </si>
   <si>
     <t xml:space="preserve">1.71109080314636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70829641819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71947383880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67196941375732</t>
+    <t xml:space="preserve">1.70829629898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71947395801544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67196953296661</t>
   </si>
   <si>
     <t xml:space="preserve">1.69991326332092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6663806438446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61608183383942</t>
+    <t xml:space="preserve">1.66638076305389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.616082072258</t>
   </si>
   <si>
     <t xml:space="preserve">1.63005375862122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63377952575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63564264774323</t>
+    <t xml:space="preserve">1.63377964496613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63564252853394</t>
   </si>
   <si>
     <t xml:space="preserve">1.64775156974792</t>
@@ -4646,25 +4646,25 @@
     <t xml:space="preserve">1.53131926059723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54994833469391</t>
+    <t xml:space="preserve">1.5499484539032</t>
   </si>
   <si>
     <t xml:space="preserve">1.53877067565918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54529094696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54249668121338</t>
+    <t xml:space="preserve">1.54529106616974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54249656200409</t>
   </si>
   <si>
     <t xml:space="preserve">1.55087971687317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55646860599518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56485152244568</t>
+    <t xml:space="preserve">1.55646848678589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56485164165497</t>
   </si>
   <si>
     <t xml:space="preserve">1.57975494861603</t>
@@ -4679,22 +4679,22 @@
     <t xml:space="preserve">1.60956168174744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61980783939362</t>
+    <t xml:space="preserve">1.61980772018433</t>
   </si>
   <si>
     <t xml:space="preserve">1.62819087505341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59745275974274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6123560667038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62073934078217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67755830287933</t>
+    <t xml:space="preserve">1.59745287895203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61235594749451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62073922157288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67755818367004</t>
   </si>
   <si>
     <t xml:space="preserve">1.64123129844666</t>
@@ -4706,10 +4706,10 @@
     <t xml:space="preserve">1.68966722488403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69153022766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66917514801025</t>
+    <t xml:space="preserve">1.69153010845184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66917502880096</t>
   </si>
   <si>
     <t xml:space="preserve">1.6682436466217</t>
@@ -4724,7 +4724,7 @@
     <t xml:space="preserve">1.72785711288452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84242641925812</t>
+    <t xml:space="preserve">1.84242653846741</t>
   </si>
   <si>
     <t xml:space="preserve">1.84801530838013</t>
@@ -4733,10 +4733,10 @@
     <t xml:space="preserve">1.90390276908875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92998373508453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97655689716339</t>
+    <t xml:space="preserve">1.92998361587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97655653953552</t>
   </si>
   <si>
     <t xml:space="preserve">1.96165335178375</t>
@@ -4760,7 +4760,7 @@
     <t xml:space="preserve">1.99704885482788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09764647483826</t>
+    <t xml:space="preserve">2.09764623641968</t>
   </si>
   <si>
     <t xml:space="preserve">2.09392046928406</t>
@@ -4784,7 +4784,7 @@
     <t xml:space="preserve">2.03617000579834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00263738632202</t>
+    <t xml:space="preserve">2.0026376247406</t>
   </si>
   <si>
     <t xml:space="preserve">1.98028254508972</t>
@@ -4793,34 +4793,34 @@
     <t xml:space="preserve">2.01008915901184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01567816734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98214554786682</t>
+    <t xml:space="preserve">2.01567792892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98214542865753</t>
   </si>
   <si>
     <t xml:space="preserve">1.90017700195312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91694343090057</t>
+    <t xml:space="preserve">1.91694331169128</t>
   </si>
   <si>
     <t xml:space="preserve">1.8927253484726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92812073230743</t>
+    <t xml:space="preserve">1.92812085151672</t>
   </si>
   <si>
     <t xml:space="preserve">1.95420169830322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06783962249756</t>
+    <t xml:space="preserve">2.06783986091614</t>
   </si>
   <si>
     <t xml:space="preserve">2.03989601135254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0752911567688</t>
+    <t xml:space="preserve">2.07529139518738</t>
   </si>
   <si>
     <t xml:space="preserve">2.09578347206116</t>
@@ -4829,7 +4829,7 @@
     <t xml:space="preserve">2.11813831329346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0771541595459</t>
+    <t xml:space="preserve">2.07715439796448</t>
   </si>
   <si>
     <t xml:space="preserve">2.08281922340393</t>
@@ -4841,7 +4841,7 @@
     <t xml:space="preserve">2.05827116966248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07148933410645</t>
+    <t xml:space="preserve">2.07148909568787</t>
   </si>
   <si>
     <t xml:space="preserve">2.12813878059387</t>
@@ -4862,7 +4862,7 @@
     <t xml:space="preserve">2.08093070983887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14135694503784</t>
+    <t xml:space="preserve">2.14135718345642</t>
   </si>
   <si>
     <t xml:space="preserve">2.10170245170593</t>
@@ -4874,7 +4874,7 @@
     <t xml:space="preserve">2.06771278381348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09981417655945</t>
+    <t xml:space="preserve">2.09981393814087</t>
   </si>
   <si>
     <t xml:space="preserve">2.15835213661194</t>
@@ -4904,13 +4904,13 @@
     <t xml:space="preserve">2.24143815040588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33396577835083</t>
+    <t xml:space="preserve">2.33396601676941</t>
   </si>
   <si>
     <t xml:space="preserve">2.32263612747192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22255516052246</t>
+    <t xml:space="preserve">2.22255492210388</t>
   </si>
   <si>
     <t xml:space="preserve">2.14702200889587</t>
@@ -4925,7 +4925,7 @@
     <t xml:space="preserve">2.09414911270142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0488293170929</t>
+    <t xml:space="preserve">2.04882955551147</t>
   </si>
   <si>
     <t xml:space="preserve">2.19989514350891</t>
@@ -4934,13 +4934,13 @@
     <t xml:space="preserve">2.2471034526825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31130623817444</t>
+    <t xml:space="preserve">2.31130599975586</t>
   </si>
   <si>
     <t xml:space="preserve">2.33207774162292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2943115234375</t>
+    <t xml:space="preserve">2.29431128501892</t>
   </si>
   <si>
     <t xml:space="preserve">2.35662579536438</t>
@@ -4958,13 +4958,13 @@
     <t xml:space="preserve">2.36040258407593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37550926208496</t>
+    <t xml:space="preserve">2.37550902366638</t>
   </si>
   <si>
     <t xml:space="preserve">2.41705203056335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46237206459045</t>
+    <t xml:space="preserve">2.46237182617188</t>
   </si>
   <si>
     <t xml:space="preserve">2.44160032272339</t>
@@ -4973,13 +4973,13 @@
     <t xml:space="preserve">2.46992492675781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48692011833191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50202655792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52657508850098</t>
+    <t xml:space="preserve">2.48692035675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50202679634094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5265748500824</t>
   </si>
   <si>
     <t xml:space="preserve">2.54168128967285</t>
@@ -4994,7 +4994,7 @@
     <t xml:space="preserve">2.50957989692688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55489993095398</t>
+    <t xml:space="preserve">2.5548996925354</t>
   </si>
   <si>
     <t xml:space="preserve">2.56811785697937</t>
@@ -5009,19 +5009,19 @@
     <t xml:space="preserve">2.70407724380493</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66442227363586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64553904533386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63798570632935</t>
+    <t xml:space="preserve">2.66442251205444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64553928375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63798594474792</t>
   </si>
   <si>
     <t xml:space="preserve">2.63609766960144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70218896865845</t>
+    <t xml:space="preserve">2.70218873023987</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309238433838</t>
@@ -5042,7 +5042,7 @@
     <t xml:space="preserve">2.60210776329041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55867648124695</t>
+    <t xml:space="preserve">2.55867624282837</t>
   </si>
   <si>
     <t xml:space="preserve">2.60882019996643</t>
@@ -5924,7 +5924,16 @@
     <t xml:space="preserve">4.26999998092651</t>
   </si>
   <si>
+    <t xml:space="preserve">4.30999994277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25600004196167</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.26200008392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30399990081787</t>
   </si>
 </sst>
 </file>
@@ -71367,27 +71376,105 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45968.6935648148</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2505" t="n">
-        <v>383114</v>
+        <v>276705</v>
       </c>
       <c r="C2505" t="n">
-        <v>4.32200002670288</v>
+        <v>4.30999994277954</v>
       </c>
       <c r="D2505" t="n">
-        <v>4.23199987411499</v>
+        <v>4.24200010299683</v>
       </c>
       <c r="E2505" t="n">
-        <v>4.25600004196167</v>
+        <v>4.27799987792969</v>
       </c>
       <c r="F2505" t="n">
-        <v>4.26200008392334</v>
+        <v>4.30999994277954</v>
       </c>
       <c r="G2505" t="s">
         <v>1970</v>
       </c>
       <c r="H2505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>252298</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>4.32600021362305</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>4.25600004196167</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>4.29199981689453</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>4.25600004196167</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>1971</v>
+      </c>
+      <c r="H2506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2507" t="n">
+        <v>383114</v>
+      </c>
+      <c r="C2507" t="n">
+        <v>4.32200002670288</v>
+      </c>
+      <c r="D2507" t="n">
+        <v>4.23199987411499</v>
+      </c>
+      <c r="E2507" t="n">
+        <v>4.25600004196167</v>
+      </c>
+      <c r="F2507" t="n">
+        <v>4.26200008392334</v>
+      </c>
+      <c r="G2507" t="s">
+        <v>1972</v>
+      </c>
+      <c r="H2507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>45971.6912731481</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>322312</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>4.32600021362305</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>4.27199983596802</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>4.28399991989136</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>4.30399990081787</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>1973</v>
+      </c>
+      <c r="H2508" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/OVS.MI.xlsx
+++ b/data/OVS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1974" uniqueCount="1974">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1975" uniqueCount="1975">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03756332397461</t>
+    <t xml:space="preserve">5.03756380081177</t>
   </si>
   <si>
     <t xml:space="preserve">OVS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89862442016602</t>
+    <t xml:space="preserve">4.89862394332886</t>
   </si>
   <si>
     <t xml:space="preserve">4.76365375518799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64456224441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71998643875122</t>
+    <t xml:space="preserve">4.64456176757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71998691558838</t>
   </si>
   <si>
     <t xml:space="preserve">4.65647125244141</t>
@@ -65,34 +65,34 @@
     <t xml:space="preserve">4.94229030609131</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69219875335693</t>
+    <t xml:space="preserve">4.69219923019409</t>
   </si>
   <si>
     <t xml:space="preserve">4.60486507415771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6366229057312</t>
+    <t xml:space="preserve">4.63662338256836</t>
   </si>
   <si>
     <t xml:space="preserve">4.616774559021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25156021118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22774267196655</t>
+    <t xml:space="preserve">4.25155973434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22774219512939</t>
   </si>
   <si>
     <t xml:space="preserve">4.5334095954895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45798587799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47783422470093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49768352508545</t>
+    <t xml:space="preserve">4.45798540115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47783470153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49768304824829</t>
   </si>
   <si>
     <t xml:space="preserve">4.51356172561646</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">4.44607734680176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6286826133728</t>
+    <t xml:space="preserve">4.62868356704712</t>
   </si>
   <si>
     <t xml:space="preserve">4.59295654296875</t>
@@ -110,16 +110,16 @@
     <t xml:space="preserve">4.51753187179565</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5453200340271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32698583602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03322696685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02925682067871</t>
+    <t xml:space="preserve">4.54531955718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32698535919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03322649002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02925634384155</t>
   </si>
   <si>
     <t xml:space="preserve">4.27934885025024</t>
@@ -131,37 +131,37 @@
     <t xml:space="preserve">4.38256120681763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30316781997681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.469895362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4659252166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48577308654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48974323272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.271409034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23965215682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43813705444336</t>
+    <t xml:space="preserve">4.30316734313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46989488601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46592473983765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48577356338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48974275588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27140951156616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23965167999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43813753128052</t>
   </si>
   <si>
     <t xml:space="preserve">4.56516885757446</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67234992980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71601676940918</t>
+    <t xml:space="preserve">4.67235040664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71601629257202</t>
   </si>
   <si>
     <t xml:space="preserve">4.58898639678955</t>
@@ -173,85 +173,85 @@
     <t xml:space="preserve">4.52547073364258</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38653087615967</t>
+    <t xml:space="preserve">4.38653039932251</t>
   </si>
   <si>
     <t xml:space="preserve">4.43019771575928</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40241003036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29125738143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12056064605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09674167633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06498527526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08880281448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15628671646118</t>
+    <t xml:space="preserve">4.40241050720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29125833511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12056016921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09674215316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06498432159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08880233764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15628719329834</t>
   </si>
   <si>
     <t xml:space="preserve">4.21186399459839</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04910516738892</t>
+    <t xml:space="preserve">4.04910564422607</t>
   </si>
   <si>
     <t xml:space="preserve">4.02131795883179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31110620498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16422700881958</t>
+    <t xml:space="preserve">4.31110668182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16422653198242</t>
   </si>
   <si>
     <t xml:space="preserve">4.23568201065063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50959205627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73586559295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54928970336914</t>
+    <t xml:space="preserve">4.50959157943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7358660697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54928922653198</t>
   </si>
   <si>
     <t xml:space="preserve">4.50165319442749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56119823455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48180437088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5215015411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55325937271118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54134941101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56913805007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5373797416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64853143692017</t>
+    <t xml:space="preserve">4.56119775772095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48180389404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52150249481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55325841903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5413498878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56913757324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53738021850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64853191375732</t>
   </si>
   <si>
     <t xml:space="preserve">4.70410776138306</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">4.84304761886597</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89068460464478</t>
+    <t xml:space="preserve">4.89068412780762</t>
   </si>
   <si>
     <t xml:space="preserve">4.81525945663452</t>
@@ -275,19 +275,19 @@
     <t xml:space="preserve">4.75968408584595</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73826885223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7667875289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90123510360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73419427871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5671534538269</t>
+    <t xml:space="preserve">4.73826837539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76678800582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90123558044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7341947555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56715297698975</t>
   </si>
   <si>
     <t xml:space="preserve">4.51826286315918</t>
@@ -296,76 +296,76 @@
     <t xml:space="preserve">4.4734468460083</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47752046585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48974418640137</t>
+    <t xml:space="preserve">4.47752141952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48974370956421</t>
   </si>
   <si>
     <t xml:space="preserve">4.63233947753906</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61196851730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.550856590271</t>
+    <t xml:space="preserve">4.61196899414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55085563659668</t>
   </si>
   <si>
     <t xml:space="preserve">4.51418876647949</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33085060119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94706296920776</t>
+    <t xml:space="preserve">4.33085012435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94706320762634</t>
   </si>
   <si>
     <t xml:space="preserve">4.13528966903687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24529314041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2656626701355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30233144760132</t>
+    <t xml:space="preserve">4.24529361724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26566314697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30233192443848</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751495361328</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11084413528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09047365188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05299186706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18825435638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16380929946899</t>
+    <t xml:space="preserve">4.11084461212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09047412872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05299139022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18825387954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16380882263184</t>
   </si>
   <si>
     <t xml:space="preserve">4.15566062927246</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15973472595215</t>
+    <t xml:space="preserve">4.15973520278931</t>
   </si>
   <si>
     <t xml:space="preserve">4.10677099227905</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04321384429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11899280548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16788244247437</t>
+    <t xml:space="preserve">4.04321432113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1189923286438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16788339614868</t>
   </si>
   <si>
     <t xml:space="preserve">4.26158952713013</t>
@@ -374,40 +374,40 @@
     <t xml:space="preserve">4.20047664642334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20862483978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23307037353516</t>
+    <t xml:space="preserve">4.20862579345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.233069896698</t>
   </si>
   <si>
     <t xml:space="preserve">4.37159252166748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36751842498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28603458404541</t>
+    <t xml:space="preserve">4.36751890182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28603506088257</t>
   </si>
   <si>
     <t xml:space="preserve">4.27788591384888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24121856689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25344133377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29825782775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22899627685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0725474357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17195844650269</t>
+    <t xml:space="preserve">4.24121809005737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25344085693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29825735092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22899580001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07254695892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17195749282837</t>
   </si>
   <si>
     <t xml:space="preserve">4.19232797622681</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">4.04158353805542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13936471939087</t>
+    <t xml:space="preserve">4.13936424255371</t>
   </si>
   <si>
     <t xml:space="preserve">4.09862279891968</t>
@@ -428,67 +428,67 @@
     <t xml:space="preserve">4.00084161758423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99269342422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03343534469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19640302658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15158653259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0863995552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06114053726196</t>
+    <t xml:space="preserve">3.99269366264343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0334358215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19640254974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15158748626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08640003204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0611400604248</t>
   </si>
   <si>
     <t xml:space="preserve">4.3593692779541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37566661834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4408540725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41233348846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31862831115723</t>
+    <t xml:space="preserve">4.37566709518433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44085359573364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41233396530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31862878799438</t>
   </si>
   <si>
     <t xml:space="preserve">4.31047916412354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31455278396606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2697377204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21677303314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18010663986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14343786239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11491918563843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07417821884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06928873062134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08232641220093</t>
+    <t xml:space="preserve">4.31455326080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26973819732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21677350997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1801061630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1434383392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11491870880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07417774200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06928825378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08232545852661</t>
   </si>
   <si>
     <t xml:space="preserve">4.06439924240112</t>
@@ -503,40 +503,40 @@
     <t xml:space="preserve">4.05462074279785</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13121652603149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04647207260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98128581047058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00410175323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98617482185364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02528762817383</t>
+    <t xml:space="preserve">4.13121604919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04647302627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98128533363342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00410127639771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98617506027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02528715133667</t>
   </si>
   <si>
     <t xml:space="preserve">3.97476696968079</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02365732192993</t>
+    <t xml:space="preserve">4.02365684509277</t>
   </si>
   <si>
     <t xml:space="preserve">4.05951023101807</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04810285568237</t>
+    <t xml:space="preserve">4.04810190200806</t>
   </si>
   <si>
     <t xml:space="preserve">4.05136203765869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97965574264526</t>
+    <t xml:space="preserve">3.97965621948242</t>
   </si>
   <si>
     <t xml:space="preserve">4.03017568588257</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">4.02039813995361</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99921154975891</t>
+    <t xml:space="preserve">3.99921250343323</t>
   </si>
   <si>
     <t xml:space="preserve">4.07825136184692</t>
@@ -560,67 +560,67 @@
     <t xml:space="preserve">4.20455074310303</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22492170333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01713848114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02202701568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93076586723328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91283917427063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89491319656372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87535738945007</t>
+    <t xml:space="preserve">4.22492218017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01713800430298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02202796936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93076658248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91283965110779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8949134349823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87535643577576</t>
   </si>
   <si>
     <t xml:space="preserve">3.94054436683655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93402576446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89654302597046</t>
+    <t xml:space="preserve">3.93402600288391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89654326438904</t>
   </si>
   <si>
     <t xml:space="preserve">3.95521116256714</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00247144699097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3797402381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38381433486938</t>
+    <t xml:space="preserve">4.00247192382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37974071502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38381481170654</t>
   </si>
   <si>
     <t xml:space="preserve">4.39196348190308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35529518127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2901086807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28196048736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32677602767944</t>
+    <t xml:space="preserve">4.35529470443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29010820388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28196001052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3267765045166</t>
   </si>
   <si>
     <t xml:space="preserve">4.2941837310791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33899927139282</t>
+    <t xml:space="preserve">4.33899879455566</t>
   </si>
   <si>
     <t xml:space="preserve">4.33492422103882</t>
@@ -635,19 +635,19 @@
     <t xml:space="preserve">4.48159503936768</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40825986862183</t>
+    <t xml:space="preserve">4.40825939178467</t>
   </si>
   <si>
     <t xml:space="preserve">4.53863382339478</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55493021011353</t>
+    <t xml:space="preserve">4.55493068695068</t>
   </si>
   <si>
     <t xml:space="preserve">4.52641105651855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50604057312012</t>
+    <t xml:space="preserve">4.50604009628296</t>
   </si>
   <si>
     <t xml:space="preserve">4.43270444869995</t>
@@ -656,31 +656,31 @@
     <t xml:space="preserve">4.59567213058472</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68530464172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67308187484741</t>
+    <t xml:space="preserve">4.68530416488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67308139801025</t>
   </si>
   <si>
     <t xml:space="preserve">4.60381984710693</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70160007476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85642004013062</t>
+    <t xml:space="preserve">4.70160102844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85641956329346</t>
   </si>
   <si>
     <t xml:space="preserve">4.82382583618164</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77493572235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7993803024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74234247207642</t>
+    <t xml:space="preserve">4.77493524551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79938077926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74234294891357</t>
   </si>
   <si>
     <t xml:space="preserve">4.78308439254761</t>
@@ -689,49 +689,49 @@
     <t xml:space="preserve">4.72604560852051</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77900981903076</t>
+    <t xml:space="preserve">4.7790093421936</t>
   </si>
   <si>
     <t xml:space="preserve">4.80752992630005</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86456823348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04790544509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01531267166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89716148376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91753149032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88901281356812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04383182525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90531015396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95012521743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05198001861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97864484786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03160953521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08457374572754</t>
+    <t xml:space="preserve">4.86456775665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04790592193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01531219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89716100692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91753244400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88901329040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04383134841919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90530967712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9501256942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05198097229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97864532470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03160905838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08457326889038</t>
   </si>
   <si>
     <t xml:space="preserve">5.23939228057861</t>
@@ -740,49 +740,49 @@
     <t xml:space="preserve">5.19865036010742</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14568519592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19457578659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05605459213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0642032623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13346433639526</t>
+    <t xml:space="preserve">5.14568567276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19457530975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05605411529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06420230865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13346385955811</t>
   </si>
   <si>
     <t xml:space="preserve">5.11716651916504</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25161504745483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18235445022583</t>
+    <t xml:space="preserve">5.25161457061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18235397338867</t>
   </si>
   <si>
     <t xml:space="preserve">5.17827987670898</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25568962097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27198505401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17420530319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16605710983276</t>
+    <t xml:space="preserve">5.25568914413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27198457717896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17420434951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16605615615845</t>
   </si>
   <si>
     <t xml:space="preserve">5.1864275932312</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10494470596313</t>
+    <t xml:space="preserve">5.10494518280029</t>
   </si>
   <si>
     <t xml:space="preserve">5.07235050201416</t>
@@ -797,10 +797,10 @@
     <t xml:space="preserve">4.98679351806641</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03691148757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3626823425293</t>
+    <t xml:space="preserve">5.0369119644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36268186569214</t>
   </si>
   <si>
     <t xml:space="preserve">5.39191770553589</t>
@@ -809,25 +809,25 @@
     <t xml:space="preserve">5.3125638961792</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27915096282959</t>
+    <t xml:space="preserve">5.27915048599243</t>
   </si>
   <si>
     <t xml:space="preserve">5.34597587585449</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35432863235474</t>
+    <t xml:space="preserve">5.35432815551758</t>
   </si>
   <si>
     <t xml:space="preserve">5.32091617584229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33762264251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2707986831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27497386932373</t>
+    <t xml:space="preserve">5.33762311935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27079820632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27497434616089</t>
   </si>
   <si>
     <t xml:space="preserve">5.1872673034668</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">5.2039737701416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22903347015381</t>
+    <t xml:space="preserve">5.22903299331665</t>
   </si>
   <si>
     <t xml:space="preserve">5.25409173965454</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">5.18309116363525</t>
   </si>
   <si>
-    <t xml:space="preserve">5.212327003479</t>
+    <t xml:space="preserve">5.21232604980469</t>
   </si>
   <si>
     <t xml:space="preserve">5.17891454696655</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">5.24573850631714</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28332805633545</t>
+    <t xml:space="preserve">5.28332757949829</t>
   </si>
   <si>
     <t xml:space="preserve">5.22485542297363</t>
@@ -878,13 +878,13 @@
     <t xml:space="preserve">5.40444707870483</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37521171569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40027046203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3835654258728</t>
+    <t xml:space="preserve">5.37521123886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40026998519897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38356494903564</t>
   </si>
   <si>
     <t xml:space="preserve">5.37938785552979</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">5.23320960998535</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30838775634766</t>
+    <t xml:space="preserve">5.3083872795105</t>
   </si>
   <si>
     <t xml:space="preserve">5.2582688331604</t>
@@ -908,34 +908,34 @@
     <t xml:space="preserve">5.11208963394165</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1538553237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23738574981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32509326934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30421018600464</t>
+    <t xml:space="preserve">5.15385484695435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23738527297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32509231567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30420970916748</t>
   </si>
   <si>
     <t xml:space="preserve">5.29585695266724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32926893234253</t>
+    <t xml:space="preserve">5.32926940917969</t>
   </si>
   <si>
     <t xml:space="preserve">5.48797845840454</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53809690475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59656810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62580347061157</t>
+    <t xml:space="preserve">5.5380973815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59656858444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62580394744873</t>
   </si>
   <si>
     <t xml:space="preserve">5.68845272064209</t>
@@ -944,52 +944,52 @@
     <t xml:space="preserve">5.61327505111694</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57568597793579</t>
+    <t xml:space="preserve">5.57568502426147</t>
   </si>
   <si>
     <t xml:space="preserve">5.44203662872314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62162780761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68009948730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64250993728638</t>
+    <t xml:space="preserve">5.62162733078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68009901046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64251041412354</t>
   </si>
   <si>
     <t xml:space="preserve">5.37103509902954</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39609432220459</t>
+    <t xml:space="preserve">5.39609384536743</t>
   </si>
   <si>
     <t xml:space="preserve">5.38774156570435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2415623664856</t>
+    <t xml:space="preserve">5.24156188964844</t>
   </si>
   <si>
     <t xml:space="preserve">5.29168081283569</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19561958312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08285331726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88655567169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90743970870972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81973075866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80302572250366</t>
+    <t xml:space="preserve">5.19562005996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08285427093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88655614852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9074387550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81973171234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8030252456665</t>
   </si>
   <si>
     <t xml:space="preserve">4.84478998184204</t>
@@ -998,7 +998,7 @@
     <t xml:space="preserve">4.83643770217896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94502735137939</t>
+    <t xml:space="preserve">4.94502782821655</t>
   </si>
   <si>
     <t xml:space="preserve">4.9032621383667</t>
@@ -1007,64 +1007,64 @@
     <t xml:space="preserve">4.86567354202271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87820291519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8531436920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81137800216675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95755767822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92832136154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7779655456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.861496925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83226156234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7236704826355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66102266311646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69861125946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6693754196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63596296310425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70278835296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6735520362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64014053344727</t>
+    <t xml:space="preserve">4.87820339202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85314464569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81137752532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95755815505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92832183837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77796602249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86149644851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83226203918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72367000579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66102313995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69861078262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66937589645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63596343994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70278882980347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67355155944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64013910293579</t>
   </si>
   <si>
     <t xml:space="preserve">4.7194938659668</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79049587249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74872970581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73202419281006</t>
+    <t xml:space="preserve">4.79049491882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74873018264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73202323913574</t>
   </si>
   <si>
     <t xml:space="preserve">4.71114110946655</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">4.67772912979126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91579246520996</t>
+    <t xml:space="preserve">4.9157919883728</t>
   </si>
   <si>
     <t xml:space="preserve">4.92414474487305</t>
@@ -1082,13 +1082,13 @@
     <t xml:space="preserve">4.89490842819214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84061431884766</t>
+    <t xml:space="preserve">4.84061479568481</t>
   </si>
   <si>
     <t xml:space="preserve">5.16220808029175</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99932241439819</t>
+    <t xml:space="preserve">4.99932193756104</t>
   </si>
   <si>
     <t xml:space="preserve">5.02020502090454</t>
@@ -1106,43 +1106,43 @@
     <t xml:space="preserve">4.98679304122925</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7863187789917</t>
+    <t xml:space="preserve">4.78631925582886</t>
   </si>
   <si>
     <t xml:space="preserve">4.68608140945435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60672760009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59419822692871</t>
+    <t xml:space="preserve">4.60672807693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59419775009155</t>
   </si>
   <si>
     <t xml:space="preserve">4.6150803565979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63178730010986</t>
+    <t xml:space="preserve">4.63178682327271</t>
   </si>
   <si>
     <t xml:space="preserve">4.70696496963501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58584451675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55243301391602</t>
+    <t xml:space="preserve">4.58584499359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55243253707886</t>
   </si>
   <si>
     <t xml:space="preserve">4.5399022102356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57749176025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48978424072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41043090820312</t>
+    <t xml:space="preserve">4.57749223709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48978471755981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41043043136597</t>
   </si>
   <si>
     <t xml:space="preserve">4.44384241104126</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">4.4939603805542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47307729721069</t>
+    <t xml:space="preserve">4.47307777404785</t>
   </si>
   <si>
     <t xml:space="preserve">4.51902008056641</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">4.5691385269165</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59002113342285</t>
+    <t xml:space="preserve">4.59002161026001</t>
   </si>
   <si>
     <t xml:space="preserve">4.65684652328491</t>
@@ -1169,10 +1169,10 @@
     <t xml:space="preserve">4.64849281311035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5983738899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56078577041626</t>
+    <t xml:space="preserve">4.59837436676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5607852935791</t>
   </si>
   <si>
     <t xml:space="preserve">4.48560810089111</t>
@@ -1187,19 +1187,19 @@
     <t xml:space="preserve">4.38537073135376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18907260894775</t>
+    <t xml:space="preserve">4.18907308578491</t>
   </si>
   <si>
     <t xml:space="preserve">4.16150760650635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15148448944092</t>
+    <t xml:space="preserve">4.15148496627808</t>
   </si>
   <si>
     <t xml:space="preserve">4.15649604797363</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19324970245361</t>
+    <t xml:space="preserve">4.19324922561646</t>
   </si>
   <si>
     <t xml:space="preserve">4.09802436828613</t>
@@ -1208,25 +1208,25 @@
     <t xml:space="preserve">4.1531548500061</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10303688049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12642574310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16986131668091</t>
+    <t xml:space="preserve">4.10303640365601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12642478942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16986179351807</t>
   </si>
   <si>
     <t xml:space="preserve">4.17654418945312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14313125610352</t>
+    <t xml:space="preserve">4.14313077926636</t>
   </si>
   <si>
     <t xml:space="preserve">4.16819047927856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83002591133118</t>
+    <t xml:space="preserve">2.8300256729126</t>
   </si>
   <si>
     <t xml:space="preserve">2.90687417984009</t>
@@ -1235,7 +1235,7 @@
     <t xml:space="preserve">2.84339070320129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87179136276245</t>
+    <t xml:space="preserve">2.87179160118103</t>
   </si>
   <si>
     <t xml:space="preserve">2.89350914955139</t>
@@ -1244,13 +1244,13 @@
     <t xml:space="preserve">2.80162477493286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92358040809631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94863986968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01713538169861</t>
+    <t xml:space="preserve">2.92358088493347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94863963127136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01713514328003</t>
   </si>
   <si>
     <t xml:space="preserve">3.08061838150024</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">3.17083144187927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14911413192749</t>
+    <t xml:space="preserve">3.14911365509033</t>
   </si>
   <si>
     <t xml:space="preserve">3.15746688842773</t>
@@ -1268,31 +1268,31 @@
     <t xml:space="preserve">3.14410185813904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17918539047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17417335510254</t>
+    <t xml:space="preserve">3.17918515205383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17417311668396</t>
   </si>
   <si>
     <t xml:space="preserve">3.10400748252869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01212358474731</t>
+    <t xml:space="preserve">3.01212334632874</t>
   </si>
   <si>
     <t xml:space="preserve">3.02882981300354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94529819488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95699262619019</t>
+    <t xml:space="preserve">2.94529795646667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95699238777161</t>
   </si>
   <si>
     <t xml:space="preserve">2.89852118492126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84004926681519</t>
+    <t xml:space="preserve">2.84004902839661</t>
   </si>
   <si>
     <t xml:space="preserve">2.8250138759613</t>
@@ -1304,22 +1304,22 @@
     <t xml:space="preserve">2.74649524688721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55771470069885</t>
+    <t xml:space="preserve">2.55771446228027</t>
   </si>
   <si>
     <t xml:space="preserve">2.54769158363342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51093745231628</t>
+    <t xml:space="preserve">2.51093792915344</t>
   </si>
   <si>
     <t xml:space="preserve">2.58945727348328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50091338157654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51594948768616</t>
+    <t xml:space="preserve">2.5009138584137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51594972610474</t>
   </si>
   <si>
     <t xml:space="preserve">2.50592565536499</t>
@@ -1328,22 +1328,22 @@
     <t xml:space="preserve">2.47919607162476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41905355453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39566516876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36058211326599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36726450920105</t>
+    <t xml:space="preserve">2.41905379295349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39566540718079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36058259010315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36726474761963</t>
   </si>
   <si>
     <t xml:space="preserve">2.3772885799408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27538061141968</t>
+    <t xml:space="preserve">2.2753803730011</t>
   </si>
   <si>
     <t xml:space="preserve">2.313805103302</t>
@@ -1352,25 +1352,25 @@
     <t xml:space="preserve">2.2620153427124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27203965187073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41404223442078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38062906265259</t>
+    <t xml:space="preserve">2.27203941345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41404247283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38062953948975</t>
   </si>
   <si>
     <t xml:space="preserve">2.30043959617615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30211091041565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29709911346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32382869720459</t>
+    <t xml:space="preserve">2.30211067199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29709887504578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32382845878601</t>
   </si>
   <si>
     <t xml:space="preserve">2.33552289009094</t>
@@ -1379,13 +1379,13 @@
     <t xml:space="preserve">2.35389947891235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36559414863586</t>
+    <t xml:space="preserve">2.36559438705444</t>
   </si>
   <si>
     <t xml:space="preserve">2.35055828094482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35222911834717</t>
+    <t xml:space="preserve">2.35222935676575</t>
   </si>
   <si>
     <t xml:space="preserve">2.35557007789612</t>
@@ -1394,25 +1394,25 @@
     <t xml:space="preserve">2.25533318519592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22025084495544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28039264678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.225261926651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23027396202087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40067625045776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44912457466125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42406558990479</t>
+    <t xml:space="preserve">2.22025060653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28039240837097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22526168823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23027372360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40067672729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44912481307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42406535148621</t>
   </si>
   <si>
     <t xml:space="preserve">2.31881642341614</t>
@@ -1421,49 +1421,49 @@
     <t xml:space="preserve">2.30879330635071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387564659119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33218145370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27370977401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18850898742676</t>
+    <t xml:space="preserve">2.34387588500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33218121528625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27371001243591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18850874900818</t>
   </si>
   <si>
     <t xml:space="preserve">2.17681455612183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15342593193054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2102267742157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21189713478088</t>
+    <t xml:space="preserve">2.15342545509338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21022629737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21189737319946</t>
   </si>
   <si>
     <t xml:space="preserve">2.05485892295837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01142287254333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97466897964478</t>
+    <t xml:space="preserve">2.01142311096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97466933727264</t>
   </si>
   <si>
     <t xml:space="preserve">2.00474047660828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03815317153931</t>
+    <t xml:space="preserve">2.03815340995789</t>
   </si>
   <si>
     <t xml:space="preserve">2.1517550945282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17180252075195</t>
+    <t xml:space="preserve">2.17180228233337</t>
   </si>
   <si>
     <t xml:space="preserve">2.18182587623596</t>
@@ -1472,10 +1472,10 @@
     <t xml:space="preserve">2.16679072380066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16846084594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15509629249573</t>
+    <t xml:space="preserve">2.16846060752869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15509605407715</t>
   </si>
   <si>
     <t xml:space="preserve">2.15676641464233</t>
@@ -1487,28 +1487,28 @@
     <t xml:space="preserve">2.07657742500305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08994245529175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09829521179199</t>
+    <t xml:space="preserve">2.08994221687317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09829497337341</t>
   </si>
   <si>
     <t xml:space="preserve">2.1601083278656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09662485122681</t>
+    <t xml:space="preserve">2.09662461280823</t>
   </si>
   <si>
     <t xml:space="preserve">2.09161281585693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02478742599487</t>
+    <t xml:space="preserve">2.02478766441345</t>
   </si>
   <si>
     <t xml:space="preserve">2.02645897865295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12502455711365</t>
+    <t xml:space="preserve">2.12502479553223</t>
   </si>
   <si>
     <t xml:space="preserve">2.23695611953735</t>
@@ -1517,19 +1517,19 @@
     <t xml:space="preserve">2.18683791160583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11834263801575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06989479064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06321287155151</t>
+    <t xml:space="preserve">2.11834239959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06989526748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06321239471436</t>
   </si>
   <si>
     <t xml:space="preserve">2.00139975547791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99972832202911</t>
+    <t xml:space="preserve">1.9997284412384</t>
   </si>
   <si>
     <t xml:space="preserve">1.98302268981934</t>
@@ -1538,16 +1538,16 @@
     <t xml:space="preserve">1.94626927375793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8761031627655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75748944282532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.695676445961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65391075611115</t>
+    <t xml:space="preserve">1.87610328197479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75748932361603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69567656517029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65391063690186</t>
   </si>
   <si>
     <t xml:space="preserve">1.6288515329361</t>
@@ -1556,22 +1556,22 @@
     <t xml:space="preserve">1.62968707084656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50439083576202</t>
+    <t xml:space="preserve">1.50439071655273</t>
   </si>
   <si>
     <t xml:space="preserve">1.48601388931274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39663565158844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31728136539459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28553974628448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27133929729462</t>
+    <t xml:space="preserve">1.39663553237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31728148460388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2855396270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27133941650391</t>
   </si>
   <si>
     <t xml:space="preserve">1.24962162971497</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">1.3156111240387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31310510635376</t>
+    <t xml:space="preserve">1.31310498714447</t>
   </si>
   <si>
     <t xml:space="preserve">1.2838693857193</t>
@@ -1604,16 +1604,16 @@
     <t xml:space="preserve">1.33899998664856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35152912139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29472815990448</t>
+    <t xml:space="preserve">1.35152924060822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29472827911377</t>
   </si>
   <si>
     <t xml:space="preserve">1.29639852046967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24293911457062</t>
+    <t xml:space="preserve">1.24293923377991</t>
   </si>
   <si>
     <t xml:space="preserve">1.2521276473999</t>
@@ -1622,10 +1622,10 @@
     <t xml:space="preserve">1.26799857616425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25296258926392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23375070095062</t>
+    <t xml:space="preserve">1.25296247005463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23375082015991</t>
   </si>
   <si>
     <t xml:space="preserve">1.25630402565002</t>
@@ -1637,19 +1637,19 @@
     <t xml:space="preserve">1.26048052310944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36823570728302</t>
+    <t xml:space="preserve">1.36823558807373</t>
   </si>
   <si>
     <t xml:space="preserve">1.36990594863892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36405920982361</t>
+    <t xml:space="preserve">1.36405909061432</t>
   </si>
   <si>
     <t xml:space="preserve">1.34568238258362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31477534770966</t>
+    <t xml:space="preserve">1.31477522850037</t>
   </si>
   <si>
     <t xml:space="preserve">1.34484672546387</t>
@@ -1664,34 +1664,34 @@
     <t xml:space="preserve">1.06835913658142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962275207042694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989840567111969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.633163213729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.703329801559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.705000221729279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862038195133209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958098948001862</t>
+    <t xml:space="preserve">0.962275147438049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989840507507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.633163154125214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.703329920768738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.705000281333923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.862038254737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958098888397217</t>
   </si>
   <si>
     <t xml:space="preserve">0.948074877262115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.848673343658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913827121257782</t>
+    <t xml:space="preserve">0.848673522472382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913827180862427</t>
   </si>
   <si>
     <t xml:space="preserve">0.9447340965271</t>
@@ -1700,10 +1700,10 @@
     <t xml:space="preserve">0.918839156627655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.917168855667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00487565994263</t>
+    <t xml:space="preserve">0.917168796062469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00487577915192</t>
   </si>
   <si>
     <t xml:space="preserve">1.1477142572403</t>
@@ -1712,22 +1712,22 @@
     <t xml:space="preserve">1.11430132389069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09926617145538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13184356689453</t>
+    <t xml:space="preserve">1.09926605224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13184344768524</t>
   </si>
   <si>
     <t xml:space="preserve">1.10344243049622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03578281402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01155829429626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01824069023132</t>
+    <t xml:space="preserve">1.03578269481659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01155817508698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01824057102203</t>
   </si>
   <si>
     <t xml:space="preserve">0.999028921127319</t>
@@ -1739,7 +1739,7 @@
     <t xml:space="preserve">1.01322948932648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08255970478058</t>
+    <t xml:space="preserve">1.08255958557129</t>
   </si>
   <si>
     <t xml:space="preserve">1.10177206993103</t>
@@ -1751,28 +1751,28 @@
     <t xml:space="preserve">1.12933743000031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13017225265503</t>
+    <t xml:space="preserve">1.13017213344574</t>
   </si>
   <si>
     <t xml:space="preserve">1.1368545293808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11346662044525</t>
+    <t xml:space="preserve">1.11346638202667</t>
   </si>
   <si>
     <t xml:space="preserve">1.10260689258575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06585311889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03244113922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07086515426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06334817409515</t>
+    <t xml:space="preserve">1.06585323810577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0324410200119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07086503505707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06334805488586</t>
   </si>
   <si>
     <t xml:space="preserve">1.01907622814178</t>
@@ -1790,49 +1790,49 @@
     <t xml:space="preserve">1.08506572246552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08673596382141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07253646850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0808892250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10511291027069</t>
+    <t xml:space="preserve">1.0867360830307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07253634929657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08088910579681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1051127910614</t>
   </si>
   <si>
     <t xml:space="preserve">1.07838320732117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10010087490082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1126309633255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11012494564056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22623264789581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46179020404816</t>
+    <t xml:space="preserve">1.10010075569153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11263084411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11012482643127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22623288631439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46179044246674</t>
   </si>
   <si>
     <t xml:space="preserve">1.41584801673889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.414177775383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36071765422821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.330646276474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29806983470917</t>
+    <t xml:space="preserve">1.41417789459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36071753501892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33064615726471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29806971549988</t>
   </si>
   <si>
     <t xml:space="preserve">1.3732476234436</t>
@@ -1847,16 +1847,16 @@
     <t xml:space="preserve">1.35069346427917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35487079620361</t>
+    <t xml:space="preserve">1.35487067699432</t>
   </si>
   <si>
     <t xml:space="preserve">1.32897591590881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36572957038879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37157642841339</t>
+    <t xml:space="preserve">1.36572968959808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3715763092041</t>
   </si>
   <si>
     <t xml:space="preserve">1.40248322486877</t>
@@ -1865,13 +1865,13 @@
     <t xml:space="preserve">1.41918885707855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42169487476349</t>
+    <t xml:space="preserve">1.42169499397278</t>
   </si>
   <si>
     <t xml:space="preserve">1.42253053188324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42837715148926</t>
+    <t xml:space="preserve">1.42837727069855</t>
   </si>
   <si>
     <t xml:space="preserve">1.39997732639313</t>
@@ -1880,34 +1880,34 @@
     <t xml:space="preserve">1.37575268745422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3941296339035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45343661308289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43589532375336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52861452102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61131012439728</t>
+    <t xml:space="preserve">1.39412951469421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4534364938736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43589544296265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52861428260803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61131024360657</t>
   </si>
   <si>
     <t xml:space="preserve">1.59710991382599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59376907348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57455658912659</t>
+    <t xml:space="preserve">1.59376895427704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5745564699173</t>
   </si>
   <si>
     <t xml:space="preserve">1.55283892154694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55116760730743</t>
+    <t xml:space="preserve">1.55116772651672</t>
   </si>
   <si>
     <t xml:space="preserve">1.51441490650177</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">1.41751849651337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43422484397888</t>
+    <t xml:space="preserve">1.43422496318817</t>
   </si>
   <si>
     <t xml:space="preserve">1.3882828950882</t>
@@ -1928,34 +1928,34 @@
     <t xml:space="preserve">1.38327074050903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3323165178299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36739981174469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34985876083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30308103561401</t>
+    <t xml:space="preserve">1.33231663703918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36739993095398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34985888004303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30308091640472</t>
   </si>
   <si>
     <t xml:space="preserve">1.32229340076447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31644582748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29890441894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30892860889435</t>
+    <t xml:space="preserve">1.31644570827484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2989045381546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30892872810364</t>
   </si>
   <si>
     <t xml:space="preserve">1.31059908866882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31895184516907</t>
+    <t xml:space="preserve">1.31895196437836</t>
   </si>
   <si>
     <t xml:space="preserve">1.29222226142883</t>
@@ -1967,25 +1967,25 @@
     <t xml:space="preserve">1.25045645236969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32730555534363</t>
+    <t xml:space="preserve">1.32730543613434</t>
   </si>
   <si>
     <t xml:space="preserve">1.31143462657928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31978750228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34902310371399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34651708602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30725836753845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26215088367462</t>
+    <t xml:space="preserve">1.31978738307953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3490229845047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34651720523834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30725824832916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26215100288391</t>
   </si>
   <si>
     <t xml:space="preserve">1.26883327960968</t>
@@ -2012,7 +2012,7 @@
     <t xml:space="preserve">1.27384531497955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26131594181061</t>
+    <t xml:space="preserve">1.2613160610199</t>
   </si>
   <si>
     <t xml:space="preserve">1.32646977901459</t>
@@ -2024,13 +2024,13 @@
     <t xml:space="preserve">1.42503654956818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48183739185333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49603796005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50272047519684</t>
+    <t xml:space="preserve">1.48183727264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49603807926178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50272023677826</t>
   </si>
   <si>
     <t xml:space="preserve">1.50355517864227</t>
@@ -2039,13 +2039,13 @@
     <t xml:space="preserve">1.54448533058167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56369781494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53863847255707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5486626625061</t>
+    <t xml:space="preserve">1.56369757652283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53863835334778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54866242408752</t>
   </si>
   <si>
     <t xml:space="preserve">1.49186062812805</t>
@@ -2054,13 +2054,13 @@
     <t xml:space="preserve">1.41668283939362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39329481124878</t>
+    <t xml:space="preserve">1.39329493045807</t>
   </si>
   <si>
     <t xml:space="preserve">1.39078879356384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42002463340759</t>
+    <t xml:space="preserve">1.4200245141983</t>
   </si>
   <si>
     <t xml:space="preserve">1.37491798400879</t>
@@ -2072,22 +2072,22 @@
     <t xml:space="preserve">1.33148193359375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32814013957977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29723429679871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29974031448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30224621295929</t>
+    <t xml:space="preserve">1.32814025878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29723417758942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29974019527435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30224633216858</t>
   </si>
   <si>
     <t xml:space="preserve">1.33315229415894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26549243927002</t>
+    <t xml:space="preserve">1.26549255847931</t>
   </si>
   <si>
     <t xml:space="preserve">1.24210357666016</t>
@@ -2099,49 +2099,49 @@
     <t xml:space="preserve">1.37074172496796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3849413394928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38911855220795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37993001937866</t>
+    <t xml:space="preserve">1.38494122028351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38911843299866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37993013858795</t>
   </si>
   <si>
     <t xml:space="preserve">1.45260179042816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48851990699768</t>
+    <t xml:space="preserve">1.48852002620697</t>
   </si>
   <si>
     <t xml:space="preserve">1.49687278270721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50104916095734</t>
+    <t xml:space="preserve">1.50104892253876</t>
   </si>
   <si>
     <t xml:space="preserve">1.44758975505829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39914155006409</t>
+    <t xml:space="preserve">1.39914166927338</t>
   </si>
   <si>
     <t xml:space="preserve">1.54281485080719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4609546661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39162349700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41000044345856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40833008289337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4292129278183</t>
+    <t xml:space="preserve">1.46095454692841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39162373542786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41000056266785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40833020210266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42921304702759</t>
   </si>
   <si>
     <t xml:space="preserve">1.40749442577362</t>
@@ -2168,25 +2168,25 @@
     <t xml:space="preserve">1.4350597858429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46596646308899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4718132019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46513104438782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47264909744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51190888881683</t>
+    <t xml:space="preserve">1.46596658229828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47181332111359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46513092517853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47264897823334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51190876960754</t>
   </si>
   <si>
     <t xml:space="preserve">1.47014307975769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49269640445709</t>
+    <t xml:space="preserve">1.4926962852478</t>
   </si>
   <si>
     <t xml:space="preserve">1.52276766300201</t>
@@ -2195,46 +2195,46 @@
     <t xml:space="preserve">1.54030883312225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53529679775238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59794533252716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60629820823669</t>
+    <t xml:space="preserve">1.53529667854309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59794545173645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60629832744598</t>
   </si>
   <si>
     <t xml:space="preserve">1.58625102043152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64555788040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59293353557587</t>
+    <t xml:space="preserve">1.64555776119232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59293341636658</t>
   </si>
   <si>
     <t xml:space="preserve">1.63219308853149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58458065986633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56035602092743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54197931289673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55868566036224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56620371341705</t>
+    <t xml:space="preserve">1.58458054065704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56035614013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54197919368744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55868577957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56620359420776</t>
   </si>
   <si>
     <t xml:space="preserve">1.56703853607178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58708667755127</t>
+    <t xml:space="preserve">1.58708655834198</t>
   </si>
   <si>
     <t xml:space="preserve">1.64973425865173</t>
@@ -2243,13 +2243,13 @@
     <t xml:space="preserve">1.74078297615051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70737075805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71906530857086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72908854484558</t>
+    <t xml:space="preserve">1.70737087726593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71906542778015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72908842563629</t>
   </si>
   <si>
     <t xml:space="preserve">1.71238279342651</t>
@@ -2258,7 +2258,7 @@
     <t xml:space="preserve">1.73243021965027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69233465194702</t>
+    <t xml:space="preserve">1.69233477115631</t>
   </si>
   <si>
     <t xml:space="preserve">1.76584219932556</t>
@@ -2270,79 +2270,79 @@
     <t xml:space="preserve">1.72073566913605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63887536525726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60880422592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68565225601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67061698436737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68732357025146</t>
+    <t xml:space="preserve">1.63887560367584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60880410671234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68565237522125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67061710357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68732368946075</t>
   </si>
   <si>
     <t xml:space="preserve">1.67562913894653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68064117431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61715710163116</t>
+    <t xml:space="preserve">1.6806412935257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61715698242188</t>
   </si>
   <si>
     <t xml:space="preserve">1.61548674106598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62467515468597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61047470569611</t>
+    <t xml:space="preserve">1.62467503547668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61047458648682</t>
   </si>
   <si>
     <t xml:space="preserve">1.64054596424103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62383937835693</t>
+    <t xml:space="preserve">1.62383949756622</t>
   </si>
   <si>
     <t xml:space="preserve">1.60963988304138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57789814472198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59126317501068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56202745437622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59209775924683</t>
+    <t xml:space="preserve">1.57789838314056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59126305580139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56202733516693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59209764003754</t>
   </si>
   <si>
     <t xml:space="preserve">1.59543943405151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58290934562683</t>
+    <t xml:space="preserve">1.58290910720825</t>
   </si>
   <si>
     <t xml:space="preserve">1.60379207134247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60045146942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58541548252106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54532086849213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5469913482666</t>
+    <t xml:space="preserve">1.6004513502121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58541536331177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54532074928284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54699110984802</t>
   </si>
   <si>
     <t xml:space="preserve">1.57706260681152</t>
@@ -2354,19 +2354,19 @@
     <t xml:space="preserve">1.49436676502228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48935544490814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46763694286346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51274359226227</t>
+    <t xml:space="preserve">1.48935556411743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46763706207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51274347305298</t>
   </si>
   <si>
     <t xml:space="preserve">1.52610850334167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53195607662201</t>
+    <t xml:space="preserve">1.53195595741272</t>
   </si>
   <si>
     <t xml:space="preserve">1.54782688617706</t>
@@ -2375,40 +2375,40 @@
     <t xml:space="preserve">1.51691997051239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5094028711319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48267221450806</t>
+    <t xml:space="preserve">1.50940275192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48267209529877</t>
   </si>
   <si>
     <t xml:space="preserve">1.26465690135956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23208034038544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18029069900513</t>
+    <t xml:space="preserve">1.23208045959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18029081821442</t>
   </si>
   <si>
     <t xml:space="preserve">1.16692578792572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13601982593536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02742910385132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933039605617523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776836395263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.719200611114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.695811748504639</t>
+    <t xml:space="preserve">1.13601970672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02742898464203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933039784431458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776836335659027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.719200670719147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.695811867713928</t>
   </si>
   <si>
     <t xml:space="preserve">0.54670923948288</t>
@@ -2417,13 +2417,13 @@
     <t xml:space="preserve">0.613534212112427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519561290740967</t>
+    <t xml:space="preserve">0.519561350345612</t>
   </si>
   <si>
     <t xml:space="preserve">0.599333763122559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674928843975067</t>
+    <t xml:space="preserve">0.674928903579712</t>
   </si>
   <si>
     <t xml:space="preserve">0.725047469139099</t>
@@ -2444,13 +2444,13 @@
     <t xml:space="preserve">0.687876343727112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.659893751144409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643604576587677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.659475386142731</t>
+    <t xml:space="preserve">0.659893691539764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.643604516983032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.65947550535202</t>
   </si>
   <si>
     <t xml:space="preserve">0.64318722486496</t>
@@ -2477,16 +2477,16 @@
     <t xml:space="preserve">0.638175189495087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649869620800018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640263915061951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612281143665314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.615621984004974</t>
+    <t xml:space="preserve">0.649869740009308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640263855457306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612281203269958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61562192440033</t>
   </si>
   <si>
     <t xml:space="preserve">0.610192537307739</t>
@@ -2501,16 +2501,16 @@
     <t xml:space="preserve">0.651540040969849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.676599264144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.654881656169891</t>
+    <t xml:space="preserve">0.676599323749542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.654881715774536</t>
   </si>
   <si>
     <t xml:space="preserve">0.642351627349854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641516864299774</t>
+    <t xml:space="preserve">0.641516923904419</t>
   </si>
   <si>
     <t xml:space="preserve">0.655717313289642</t>
@@ -2519,46 +2519,46 @@
     <t xml:space="preserve">0.639846503734589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649034917354584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.668246507644653</t>
+    <t xml:space="preserve">0.649034857749939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.668246567249298</t>
   </si>
   <si>
     <t xml:space="preserve">0.65028703212738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.626480877399445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609775125980377</t>
+    <t xml:space="preserve">0.626480758190155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609775185585022</t>
   </si>
   <si>
     <t xml:space="preserve">0.606016159057617</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629822373390198</t>
+    <t xml:space="preserve">0.629822313785553</t>
   </si>
   <si>
     <t xml:space="preserve">0.596827805042267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.574691832065582</t>
+    <t xml:space="preserve">0.574691891670227</t>
   </si>
   <si>
     <t xml:space="preserve">0.581792593002319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.574274599552155</t>
+    <t xml:space="preserve">0.57427453994751</t>
   </si>
   <si>
     <t xml:space="preserve">0.60183972120285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.630657970905304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.726300418376923</t>
+    <t xml:space="preserve">0.630658030509949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.726300477981567</t>
   </si>
   <si>
     <t xml:space="preserve">0.789366483688354</t>
@@ -2567,43 +2567,43 @@
     <t xml:space="preserve">0.763054251670837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.768483638763428</t>
+    <t xml:space="preserve">0.768483519554138</t>
   </si>
   <si>
     <t xml:space="preserve">0.827790558338165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.835308492183685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901297986507416</t>
+    <t xml:space="preserve">0.83530855178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901298046112061</t>
   </si>
   <si>
     <t xml:space="preserve">0.910486400127411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00571143627167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01072347164154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968957662582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877909004688263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924685955047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925521552562714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938051581382751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922180950641632</t>
+    <t xml:space="preserve">1.00571155548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01072335243225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968957722187042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877909064292908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924685895442963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925521671772003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938051640987396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922180891036987</t>
   </si>
   <si>
     <t xml:space="preserve">0.892109513282776</t>
@@ -2612,13 +2612,13 @@
     <t xml:space="preserve">0.893779933452606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.895450234413147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823614180088043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78101372718811</t>
+    <t xml:space="preserve">0.895450294017792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823614120483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781013667583466</t>
   </si>
   <si>
     <t xml:space="preserve">0.824867129325867</t>
@@ -2630,31 +2630,31 @@
     <t xml:space="preserve">0.78560745716095</t>
   </si>
   <si>
-    <t xml:space="preserve">0.802313983440399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.797719299793243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80189573764801</t>
+    <t xml:space="preserve">0.802313923835754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.797719240188599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801895678043365</t>
   </si>
   <si>
     <t xml:space="preserve">0.798554956912994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77641898393631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.782266736030579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766394972801208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821525573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.795631587505341</t>
+    <t xml:space="preserve">0.776419103145599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.782266676425934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766394913196564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821525514125824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.795631527900696</t>
   </si>
   <si>
     <t xml:space="preserve">0.86370861530304</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">0.855355799198151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.844496965408325</t>
+    <t xml:space="preserve">0.84449702501297</t>
   </si>
   <si>
     <t xml:space="preserve">0.857861816883087</t>
@@ -2672,16 +2672,16 @@
     <t xml:space="preserve">0.836143434047699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.834890425205231</t>
+    <t xml:space="preserve">0.834890365600586</t>
   </si>
   <si>
     <t xml:space="preserve">0.838649392127991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.80022531747818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.773912966251373</t>
+    <t xml:space="preserve">0.800225257873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.773913025856018</t>
   </si>
   <si>
     <t xml:space="preserve">0.789783835411072</t>
@@ -2693,7 +2693,7 @@
     <t xml:space="preserve">0.767230629920959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.775583326816559</t>
+    <t xml:space="preserve">0.775583386421204</t>
   </si>
   <si>
     <t xml:space="preserve">0.786860466003418</t>
@@ -2702,31 +2702,31 @@
     <t xml:space="preserve">0.79270726442337</t>
   </si>
   <si>
-    <t xml:space="preserve">0.758877813816071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.765977621078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.800642669200897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809831023216248</t>
+    <t xml:space="preserve">0.758877754211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.765977561473846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800642609596252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809831082820892</t>
   </si>
   <si>
     <t xml:space="preserve">0.799807906150818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.780178010463715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.770989656448364</t>
+    <t xml:space="preserve">0.780178070068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.770989596843719</t>
   </si>
   <si>
     <t xml:space="preserve">0.740918278694153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.717947661876678</t>
+    <t xml:space="preserve">0.717947721481323</t>
   </si>
   <si>
     <t xml:space="preserve">0.712099969387054</t>
@@ -2735,13 +2735,13 @@
     <t xml:space="preserve">0.684117317199707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.690799713134766</t>
+    <t xml:space="preserve">0.690799832344055</t>
   </si>
   <si>
     <t xml:space="preserve">0.692888379096985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.685787737369537</t>
+    <t xml:space="preserve">0.685787677764893</t>
   </si>
   <si>
     <t xml:space="preserve">0.674094200134277</t>
@@ -2750,19 +2750,19 @@
     <t xml:space="preserve">0.666576147079468</t>
   </si>
   <si>
-    <t xml:space="preserve">0.682029604911804</t>
+    <t xml:space="preserve">0.682029545307159</t>
   </si>
   <si>
     <t xml:space="preserve">0.687458992004395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.685370326042175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.677852272987366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69455873966217</t>
+    <t xml:space="preserve">0.68537038564682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.67785233259201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.694558799266815</t>
   </si>
   <si>
     <t xml:space="preserve">0.697482168674469</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">0.70374721288681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.69831782579422</t>
+    <t xml:space="preserve">0.698317766189575</t>
   </si>
   <si>
     <t xml:space="preserve">0.721288442611694</t>
@@ -2780,13 +2780,13 @@
     <t xml:space="preserve">0.720453679561615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.742588698863983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.767647981643677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.718365013599396</t>
+    <t xml:space="preserve">0.742588639259338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767647922039032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.718365073204041</t>
   </si>
   <si>
     <t xml:space="preserve">0.715024292469025</t>
@@ -2801,22 +2801,22 @@
     <t xml:space="preserve">0.778925061225891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.796466290950775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825284600257874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.850343823432922</t>
+    <t xml:space="preserve">0.79646623134613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825284540653229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.850343763828278</t>
   </si>
   <si>
     <t xml:space="preserve">0.860367834568024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.847002983093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858696699142456</t>
+    <t xml:space="preserve">0.847003042697906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858696579933167</t>
   </si>
   <si>
     <t xml:space="preserve">0.843661367893219</t>
@@ -2825,19 +2825,19 @@
     <t xml:space="preserve">0.8720623254776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.852014243602753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.854520201683044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812755346298218</t>
+    <t xml:space="preserve">0.852014183998108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8545201420784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812755405902863</t>
   </si>
   <si>
     <t xml:space="preserve">0.80774337053299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.81317275762558</t>
+    <t xml:space="preserve">0.813172698020935</t>
   </si>
   <si>
     <t xml:space="preserve">0.828626096248627</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">0.832802534103394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.8206906914711</t>
+    <t xml:space="preserve">0.820690751075745</t>
   </si>
   <si>
     <t xml:space="preserve">0.749689340591431</t>
@@ -2855,16 +2855,16 @@
     <t xml:space="preserve">0.710846960544586</t>
   </si>
   <si>
-    <t xml:space="preserve">0.654464304447174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.633998811244965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.645275890827179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.660311043262482</t>
+    <t xml:space="preserve">0.654464364051819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.63399875164032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.645275950431824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.660311102867126</t>
   </si>
   <si>
     <t xml:space="preserve">0.684534668922424</t>
@@ -2873,13 +2873,13 @@
     <t xml:space="preserve">0.68912935256958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.753030121326447</t>
+    <t xml:space="preserve">0.753030061721802</t>
   </si>
   <si>
     <t xml:space="preserve">0.784354448318481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.787696123123169</t>
+    <t xml:space="preserve">0.787696063518524</t>
   </si>
   <si>
     <t xml:space="preserve">0.803148686885834</t>
@@ -2891,10 +2891,10 @@
     <t xml:space="preserve">0.845331788063049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.877073407173157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.90046226978302</t>
+    <t xml:space="preserve">0.877073466777802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900462329387665</t>
   </si>
   <si>
     <t xml:space="preserve">0.889603495597839</t>
@@ -2903,13 +2903,13 @@
     <t xml:space="preserve">0.887097477912903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.890439212322235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88125079870224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.904638767242432</t>
+    <t xml:space="preserve">0.89043915271759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88125067949295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.904638826847076</t>
   </si>
   <si>
     <t xml:space="preserve">0.89294421672821</t>
@@ -2921,19 +2921,19 @@
     <t xml:space="preserve">0.88208544254303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.867884993553162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841155469417572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.839484930038452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841991007328033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840320587158203</t>
+    <t xml:space="preserve">0.867885053157806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841155409812927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.839485049247742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841990947723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840320646762848</t>
   </si>
   <si>
     <t xml:space="preserve">0.859532177448273</t>
@@ -2948,70 +2948,70 @@
     <t xml:space="preserve">0.872897028923035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.906310081481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943898439407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95392245054245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957263350486755</t>
+    <t xml:space="preserve">0.906310021877289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943898379802704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953922390937805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957263290882111</t>
   </si>
   <si>
     <t xml:space="preserve">0.965616941452026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978146076202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961439549922943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934709966182709</t>
+    <t xml:space="preserve">0.978146135807037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961439788341522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934710085391998</t>
   </si>
   <si>
     <t xml:space="preserve">0.902968347072601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.874567449092865</t>
+    <t xml:space="preserve">0.87456738948822</t>
   </si>
   <si>
     <t xml:space="preserve">0.852849781513214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.867050230503082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.878744721412659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907144725322723</t>
+    <t xml:space="preserve">0.867050290107727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.878744661808014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.907144784927368</t>
   </si>
   <si>
     <t xml:space="preserve">0.931369304656982</t>
   </si>
   <si>
-    <t xml:space="preserve">0.921345174312592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927191913127899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912992417812347</t>
+    <t xml:space="preserve">0.921345114707947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927192032337189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912992358207703</t>
   </si>
   <si>
     <t xml:space="preserve">0.947240114212036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.899626731872559</t>
+    <t xml:space="preserve">0.899626672267914</t>
   </si>
   <si>
     <t xml:space="preserve">0.92969799041748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938886404037476</t>
+    <t xml:space="preserve">0.938886523246765</t>
   </si>
   <si>
     <t xml:space="preserve">0.93721604347229</t>
@@ -3020,46 +3020,46 @@
     <t xml:space="preserve">0.942228078842163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941392421722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946404457092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93554562330246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975639998912811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14687860012054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18947923183441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17360830307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16024351119995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15773749351501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17193782329559</t>
+    <t xml:space="preserve">0.941392481327057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94640451669693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.935545682907104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975640118122101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14687871932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18947911262512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17360818386078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16024339199066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15773737430573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17193794250488</t>
   </si>
   <si>
     <t xml:space="preserve">1.1385258436203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1092894077301</t>
+    <t xml:space="preserve">1.10928928852081</t>
   </si>
   <si>
     <t xml:space="preserve">1.11096060276031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10678422451019</t>
+    <t xml:space="preserve">1.1067841053009</t>
   </si>
   <si>
     <t xml:space="preserve">1.11179530620575</t>
@@ -3077,49 +3077,49 @@
     <t xml:space="preserve">1.14520835876465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11513698101044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10761892795563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37742400169373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37241196632385</t>
+    <t xml:space="preserve">1.11513686180115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10761880874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37742412090302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37241208553314</t>
   </si>
   <si>
     <t xml:space="preserve">1.43923699855804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43673098087311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44007158279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4066596031189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41167175769806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3974711894989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.438401222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47682535648346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45928430557251</t>
+    <t xml:space="preserve">1.43673086166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44007170200348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40665984153748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41167163848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39747130870819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43840134143829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47682547569275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45928418636322</t>
   </si>
   <si>
     <t xml:space="preserve">1.44090735912323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43338930606842</t>
+    <t xml:space="preserve">1.43338942527771</t>
   </si>
   <si>
     <t xml:space="preserve">1.48100197315216</t>
@@ -3128,7 +3128,7 @@
     <t xml:space="preserve">1.41334211826324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42587125301361</t>
+    <t xml:space="preserve">1.4258713722229</t>
   </si>
   <si>
     <t xml:space="preserve">1.5879213809967</t>
@@ -3137,16 +3137,16 @@
     <t xml:space="preserve">1.550332903862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62634551525116</t>
+    <t xml:space="preserve">1.62634539604187</t>
   </si>
   <si>
     <t xml:space="preserve">1.61214590072632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62049877643585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61966300010681</t>
+    <t xml:space="preserve">1.62049865722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61966288089752</t>
   </si>
   <si>
     <t xml:space="preserve">1.62718105316162</t>
@@ -3164,28 +3164,28 @@
     <t xml:space="preserve">1.34317636489868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3565411567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35904729366302</t>
+    <t xml:space="preserve">1.35654103755951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35904717445374</t>
   </si>
   <si>
     <t xml:space="preserve">1.36489391326904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4027658700943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4346672296524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41251361370087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39390444755554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39213216304779</t>
+    <t xml:space="preserve">1.40276598930359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43466711044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41251349449158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39390432834625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39213240146637</t>
   </si>
   <si>
     <t xml:space="preserve">1.3336466550827</t>
@@ -3206,13 +3206,13 @@
     <t xml:space="preserve">1.58442544937134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52859842777252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54897964000702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54454910755157</t>
+    <t xml:space="preserve">1.52859854698181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54897975921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54454898834229</t>
   </si>
   <si>
     <t xml:space="preserve">1.53834593296051</t>
@@ -3221,28 +3221,28 @@
     <t xml:space="preserve">1.55872738361359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5764502286911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6145544052124</t>
+    <t xml:space="preserve">1.57645034790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61455428600311</t>
   </si>
   <si>
     <t xml:space="preserve">1.60657906532288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5693610906601</t>
+    <t xml:space="preserve">1.56936097145081</t>
   </si>
   <si>
     <t xml:space="preserve">1.58885622024536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60392069816589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63582193851471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62518811225891</t>
+    <t xml:space="preserve">1.6039205789566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63582181930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6251882314682</t>
   </si>
   <si>
     <t xml:space="preserve">1.61278212070465</t>
@@ -3251,10 +3251,10 @@
     <t xml:space="preserve">1.58353924751282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51885092258453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52062296867371</t>
+    <t xml:space="preserve">1.51885080337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.520623087883</t>
   </si>
   <si>
     <t xml:space="preserve">1.4931526184082</t>
@@ -3263,10 +3263,10 @@
     <t xml:space="preserve">1.49758350849152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52505385875702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50733089447021</t>
+    <t xml:space="preserve">1.52505373954773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5073310136795</t>
   </si>
   <si>
     <t xml:space="preserve">1.50112795829773</t>
@@ -3275,16 +3275,16 @@
     <t xml:space="preserve">1.54011821746826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53037071228027</t>
+    <t xml:space="preserve">1.53037059307098</t>
   </si>
   <si>
     <t xml:space="preserve">1.55341041088104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6384801864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66329216957092</t>
+    <t xml:space="preserve">1.63848030567169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66329228878021</t>
   </si>
   <si>
     <t xml:space="preserve">1.56404423713684</t>
@@ -3293,22 +3293,22 @@
     <t xml:space="preserve">1.51707851886749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48872184753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46568238735199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42403340339661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44707310199738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46656823158264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61809897422791</t>
+    <t xml:space="preserve">1.48872196674347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46568214893341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4240335226059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44707322120667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46656835079193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61809909343719</t>
   </si>
   <si>
     <t xml:space="preserve">1.82900106906891</t>
@@ -3317,19 +3317,19 @@
     <t xml:space="preserve">1.846724152565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90520989894867</t>
+    <t xml:space="preserve">1.90520966053009</t>
   </si>
   <si>
     <t xml:space="preserve">1.89634835720062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98319041728973</t>
+    <t xml:space="preserve">1.98319017887115</t>
   </si>
   <si>
     <t xml:space="preserve">2.03635907173157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09129977226257</t>
+    <t xml:space="preserve">2.09130001068115</t>
   </si>
   <si>
     <t xml:space="preserve">2.17105293273926</t>
@@ -3338,25 +3338,25 @@
     <t xml:space="preserve">1.96015048027039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88925886154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96192276477814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94597220420837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01863598823547</t>
+    <t xml:space="preserve">1.88925898075104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96192300319672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94597244262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01863622665405</t>
   </si>
   <si>
     <t xml:space="preserve">2.10902285575867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07534956932068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10547804832458</t>
+    <t xml:space="preserve">2.0753493309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10547828674316</t>
   </si>
   <si>
     <t xml:space="preserve">2.13737940788269</t>
@@ -3368,13 +3368,13 @@
     <t xml:space="preserve">2.17814183235168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16396355628967</t>
+    <t xml:space="preserve">2.16396379470825</t>
   </si>
   <si>
     <t xml:space="preserve">2.17636966705322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18168663978577</t>
+    <t xml:space="preserve">2.18168640136719</t>
   </si>
   <si>
     <t xml:space="preserve">2.24371671676636</t>
@@ -3383,13 +3383,13 @@
     <t xml:space="preserve">2.1799144744873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1232008934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14624094963074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19763708114624</t>
+    <t xml:space="preserve">2.12320065498352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14624071121216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19763731956482</t>
   </si>
   <si>
     <t xml:space="preserve">2.30574655532837</t>
@@ -3401,7 +3401,7 @@
     <t xml:space="preserve">2.31992506980896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34828162193298</t>
+    <t xml:space="preserve">2.34828186035156</t>
   </si>
   <si>
     <t xml:space="preserve">2.417400598526</t>
@@ -3410,16 +3410,16 @@
     <t xml:space="preserve">2.4457573890686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38372731208801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46347999572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42448973655701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47411417961121</t>
+    <t xml:space="preserve">2.38372755050659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4634804725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42448997497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47411394119263</t>
   </si>
   <si>
     <t xml:space="preserve">2.51310443878174</t>
@@ -3428,25 +3428,25 @@
     <t xml:space="preserve">2.50955986976624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43157935142517</t>
+    <t xml:space="preserve">2.43157911300659</t>
   </si>
   <si>
     <t xml:space="preserve">2.4705696105957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39613342285156</t>
+    <t xml:space="preserve">2.39613318443298</t>
   </si>
   <si>
     <t xml:space="preserve">2.33942031860352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37841057777405</t>
+    <t xml:space="preserve">2.37841033935547</t>
   </si>
   <si>
     <t xml:space="preserve">2.21004319190979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38904428482056</t>
+    <t xml:space="preserve">2.38904452323914</t>
   </si>
   <si>
     <t xml:space="preserve">2.47943091392517</t>
@@ -3461,7 +3461,7 @@
     <t xml:space="preserve">2.65665984153748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.640709400177</t>
+    <t xml:space="preserve">2.64070916175842</t>
   </si>
   <si>
     <t xml:space="preserve">2.63184785842896</t>
@@ -3476,28 +3476,28 @@
     <t xml:space="preserve">2.52373814582825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33233070373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31815242767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29688549041748</t>
+    <t xml:space="preserve">2.33233094215393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31815266609192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2968852519989</t>
   </si>
   <si>
     <t xml:space="preserve">2.28270673751831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27561807632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25966691970825</t>
+    <t xml:space="preserve">2.27561783790588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25966739654541</t>
   </si>
   <si>
     <t xml:space="preserve">2.30929112434387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27916240692139</t>
+    <t xml:space="preserve">2.27916264533997</t>
   </si>
   <si>
     <t xml:space="preserve">2.28802394866943</t>
@@ -3506,16 +3506,16 @@
     <t xml:space="preserve">2.26852869987488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36600470542908</t>
+    <t xml:space="preserve">2.3660044670105</t>
   </si>
   <si>
     <t xml:space="preserve">2.30751919746399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24017214775085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14978528022766</t>
+    <t xml:space="preserve">2.24017238616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14978551864624</t>
   </si>
   <si>
     <t xml:space="preserve">2.16041898727417</t>
@@ -3524,25 +3524,25 @@
     <t xml:space="preserve">2.17459726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13915157318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15687465667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05762624740601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16928029060364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19586491584778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13560700416565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39258909225464</t>
+    <t xml:space="preserve">2.13915181159973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15687441825867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05762648582458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16928052902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1958646774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13560724258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39258885383606</t>
   </si>
   <si>
     <t xml:space="preserve">2.39436101913452</t>
@@ -3551,49 +3551,49 @@
     <t xml:space="preserve">2.06648802757263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99382412433624</t>
+    <t xml:space="preserve">1.99382376670837</t>
   </si>
   <si>
     <t xml:space="preserve">2.12142872810364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11965656280518</t>
+    <t xml:space="preserve">2.11965680122375</t>
   </si>
   <si>
     <t xml:space="preserve">2.09484457969666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01331901550293</t>
+    <t xml:space="preserve">2.01331925392151</t>
   </si>
   <si>
     <t xml:space="preserve">2.08066606521606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99205148220062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03458642959595</t>
+    <t xml:space="preserve">1.9920517206192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03458666801453</t>
   </si>
   <si>
     <t xml:space="preserve">2.02926969528198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93179416656494</t>
+    <t xml:space="preserve">1.93179392814636</t>
   </si>
   <si>
     <t xml:space="preserve">2.01509141921997</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00445771217346</t>
+    <t xml:space="preserve">2.00445795059204</t>
   </si>
   <si>
     <t xml:space="preserve">1.86799156665802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90166485309601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80596148967743</t>
+    <t xml:space="preserve">1.9016649723053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80596160888672</t>
   </si>
   <si>
     <t xml:space="preserve">1.6455694437027</t>
@@ -3617,10 +3617,10 @@
     <t xml:space="preserve">1.659747838974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78646636009216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75545120239258</t>
+    <t xml:space="preserve">1.78646647930145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75545132160187</t>
   </si>
   <si>
     <t xml:space="preserve">1.73684227466583</t>
@@ -3629,52 +3629,52 @@
     <t xml:space="preserve">1.73418390750885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70671343803406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65088629722595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66595065593719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67924296855927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72798085212708</t>
+    <t xml:space="preserve">1.70671319961548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65088641643524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66595077514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67924284934998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72798073291779</t>
   </si>
   <si>
     <t xml:space="preserve">1.86444711685181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83431816101074</t>
+    <t xml:space="preserve">1.83431828022003</t>
   </si>
   <si>
     <t xml:space="preserve">1.74570369720459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78469395637512</t>
+    <t xml:space="preserve">1.78469407558441</t>
   </si>
   <si>
     <t xml:space="preserve">1.76254045963287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7288670539856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67038154602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64113855361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60126221179962</t>
+    <t xml:space="preserve">1.72886693477631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67038142681122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64113867282867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60126233100891</t>
   </si>
   <si>
     <t xml:space="preserve">1.61987113952637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71025800704956</t>
+    <t xml:space="preserve">1.71025788784027</t>
   </si>
   <si>
     <t xml:space="preserve">1.70051038265228</t>
@@ -3686,16 +3686,16 @@
     <t xml:space="preserve">1.62961876392365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63936650753021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63050508499146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60923767089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62075734138489</t>
+    <t xml:space="preserve">1.63936638832092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63050496578217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60923743247986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62075746059418</t>
   </si>
   <si>
     <t xml:space="preserve">1.55075204372406</t>
@@ -3704,7 +3704,7 @@
     <t xml:space="preserve">1.46302378177643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47897446155548</t>
+    <t xml:space="preserve">1.47897434234619</t>
   </si>
   <si>
     <t xml:space="preserve">1.5418906211853</t>
@@ -3716,22 +3716,22 @@
     <t xml:space="preserve">1.58974242210388</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64468336105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60746514797211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60037612915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52594006061554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52150928974152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63139116764069</t>
+    <t xml:space="preserve">1.64468324184418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6074652671814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6003760099411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52593994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52150917053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6313910484314</t>
   </si>
   <si>
     <t xml:space="preserve">1.64734172821045</t>
@@ -3743,49 +3743,49 @@
     <t xml:space="preserve">1.690762758255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71646094322205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78114950656891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84495174884796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80773389339447</t>
+    <t xml:space="preserve">1.71646106243134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78114938735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84495186805725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80773365497589</t>
   </si>
   <si>
     <t xml:space="preserve">1.79887223243713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79532790184021</t>
+    <t xml:space="preserve">1.79532778263092</t>
   </si>
   <si>
     <t xml:space="preserve">1.65797543525696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45593464374542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41871643066406</t>
+    <t xml:space="preserve">1.45593452453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41871654987335</t>
   </si>
   <si>
     <t xml:space="preserve">1.46506786346436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4768830537796</t>
+    <t xml:space="preserve">1.47688281536102</t>
   </si>
   <si>
     <t xml:space="preserve">1.48960697650909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45779716968536</t>
+    <t xml:space="preserve">1.45779705047607</t>
   </si>
   <si>
     <t xml:space="preserve">1.47597420215607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43689358234406</t>
+    <t xml:space="preserve">1.43689334392548</t>
   </si>
   <si>
     <t xml:space="preserve">1.47415637969971</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">1.30147480964661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32783150672913</t>
+    <t xml:space="preserve">1.32783138751984</t>
   </si>
   <si>
     <t xml:space="preserve">1.37418282032013</t>
@@ -3815,13 +3815,13 @@
     <t xml:space="preserve">1.40781044960022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3859977722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31510758399963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28420662879944</t>
+    <t xml:space="preserve">1.38599789142609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31510746479034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28420674800873</t>
   </si>
   <si>
     <t xml:space="preserve">1.27966237068176</t>
@@ -3833,7 +3833,7 @@
     <t xml:space="preserve">1.3269225358963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39781284332275</t>
+    <t xml:space="preserve">1.39781296253204</t>
   </si>
   <si>
     <t xml:space="preserve">1.37145614624023</t>
@@ -3845,10 +3845,10 @@
     <t xml:space="preserve">1.35691475868225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29693043231964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31328988075256</t>
+    <t xml:space="preserve">1.29693055152893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31328976154327</t>
   </si>
   <si>
     <t xml:space="preserve">1.33328461647034</t>
@@ -3860,7 +3860,7 @@
     <t xml:space="preserve">1.42689621448517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40144836902618</t>
+    <t xml:space="preserve">1.40144848823547</t>
   </si>
   <si>
     <t xml:space="preserve">1.44416439533234</t>
@@ -3881,10 +3881,10 @@
     <t xml:space="preserve">1.48869812488556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51596355438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50505745410919</t>
+    <t xml:space="preserve">1.51596367359161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5050573348999</t>
   </si>
   <si>
     <t xml:space="preserve">1.50051307678223</t>
@@ -3902,19 +3902,19 @@
     <t xml:space="preserve">1.41144573688507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34691727161407</t>
+    <t xml:space="preserve">1.34691739082336</t>
   </si>
   <si>
     <t xml:space="preserve">1.34328198432922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37327396869659</t>
+    <t xml:space="preserve">1.37327408790588</t>
   </si>
   <si>
     <t xml:space="preserve">1.3760005235672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36236774921417</t>
+    <t xml:space="preserve">1.36236763000488</t>
   </si>
   <si>
     <t xml:space="preserve">1.39235973358154</t>
@@ -3926,10 +3926,10 @@
     <t xml:space="preserve">1.35237050056458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36963856220245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35964131355286</t>
+    <t xml:space="preserve">1.36963844299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35964119434357</t>
   </si>
   <si>
     <t xml:space="preserve">1.41326332092285</t>
@@ -3938,7 +3938,7 @@
     <t xml:space="preserve">1.43507587909698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41689896583557</t>
+    <t xml:space="preserve">1.41689884662628</t>
   </si>
   <si>
     <t xml:space="preserve">1.46870338916779</t>
@@ -3947,7 +3947,7 @@
     <t xml:space="preserve">1.41235458850861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39872169494629</t>
+    <t xml:space="preserve">1.39872181415558</t>
   </si>
   <si>
     <t xml:space="preserve">1.70591342449188</t>
@@ -3956,10 +3956,10 @@
     <t xml:space="preserve">1.6859188079834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58412754535675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57867443561554</t>
+    <t xml:space="preserve">1.58412730693817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57867431640625</t>
   </si>
   <si>
     <t xml:space="preserve">1.59139823913574</t>
@@ -3968,7 +3968,7 @@
     <t xml:space="preserve">1.56322395801544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4996041059494</t>
+    <t xml:space="preserve">1.49960422515869</t>
   </si>
   <si>
     <t xml:space="preserve">1.55777084827423</t>
@@ -3983,7 +3983,7 @@
     <t xml:space="preserve">1.58140099048615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53777611255646</t>
+    <t xml:space="preserve">1.53777599334717</t>
   </si>
   <si>
     <t xml:space="preserve">1.52323436737061</t>
@@ -4007,22 +4007,22 @@
     <t xml:space="preserve">1.65774440765381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65865337848663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65956211090088</t>
+    <t xml:space="preserve">1.65865325927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65956199169159</t>
   </si>
   <si>
     <t xml:space="preserve">1.6704683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7631710767746</t>
+    <t xml:space="preserve">1.76317119598389</t>
   </si>
   <si>
     <t xml:space="preserve">1.79225432872772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78861892223358</t>
+    <t xml:space="preserve">1.78861904144287</t>
   </si>
   <si>
     <t xml:space="preserve">1.73045253753662</t>
@@ -4031,7 +4031,7 @@
     <t xml:space="preserve">1.71772849559784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72681713104248</t>
+    <t xml:space="preserve">1.72681701183319</t>
   </si>
   <si>
     <t xml:space="preserve">1.77135074138641</t>
@@ -4043,22 +4043,22 @@
     <t xml:space="preserve">1.75135612487793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78771018981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8486031293869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86677992343903</t>
+    <t xml:space="preserve">1.78771007061005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84860301017761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86678004264832</t>
   </si>
   <si>
     <t xml:space="preserve">1.87223315238953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89949882030487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93403518199921</t>
+    <t xml:space="preserve">1.89949870109558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9340353012085</t>
   </si>
   <si>
     <t xml:space="preserve">1.94494140148163</t>
@@ -4067,10 +4067,10 @@
     <t xml:space="preserve">1.90676963329315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95403015613556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97038912773132</t>
+    <t xml:space="preserve">1.95403003692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97038900852203</t>
   </si>
   <si>
     <t xml:space="preserve">2.00492548942566</t>
@@ -4079,25 +4079,25 @@
     <t xml:space="preserve">1.99583697319031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97220695018768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97402429580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9903838634491</t>
+    <t xml:space="preserve">1.97220683097839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97402453422546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99038398265839</t>
   </si>
   <si>
     <t xml:space="preserve">2.04491496086121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13398241996765</t>
+    <t xml:space="preserve">2.13398265838623</t>
   </si>
   <si>
     <t xml:space="preserve">2.15397691726685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12307596206665</t>
+    <t xml:space="preserve">2.12307620048523</t>
   </si>
   <si>
     <t xml:space="preserve">2.11944103240967</t>
@@ -4115,10 +4115,10 @@
     <t xml:space="preserve">2.10308122634888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10126376152039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97584223747253</t>
+    <t xml:space="preserve">2.10126399993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97584211826324</t>
   </si>
   <si>
     <t xml:space="preserve">2.02128481864929</t>
@@ -4136,10 +4136,10 @@
     <t xml:space="preserve">1.92676424980164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93585300445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93948817253113</t>
+    <t xml:space="preserve">1.93585288524628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93948829174042</t>
   </si>
   <si>
     <t xml:space="preserve">1.90131640434265</t>
@@ -4148,28 +4148,28 @@
     <t xml:space="preserve">1.91404032707214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96311843395233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96857130527496</t>
+    <t xml:space="preserve">1.96311855316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96857142448425</t>
   </si>
   <si>
     <t xml:space="preserve">2.03219103813171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05945658683777</t>
+    <t xml:space="preserve">2.05945682525635</t>
   </si>
   <si>
     <t xml:space="preserve">2.10489892959595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12852931022644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12671160697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09944581985474</t>
+    <t xml:space="preserve">2.12852954864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12671136856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09944605827332</t>
   </si>
   <si>
     <t xml:space="preserve">2.01946687698364</t>
@@ -4178,13 +4178,13 @@
     <t xml:space="preserve">2.07218050956726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06309223175049</t>
+    <t xml:space="preserve">2.06309199333191</t>
   </si>
   <si>
     <t xml:space="preserve">2.03764414787292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00310754776001</t>
+    <t xml:space="preserve">2.00310778617859</t>
   </si>
   <si>
     <t xml:space="preserve">2.01219630241394</t>
@@ -4193,19 +4193,19 @@
     <t xml:space="preserve">2.01764941215515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00128960609436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27394556999207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24849724769592</t>
+    <t xml:space="preserve">2.00128984451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27394580841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2484974861145</t>
   </si>
   <si>
     <t xml:space="preserve">2.31757020950317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3084819316864</t>
+    <t xml:space="preserve">2.30848169326782</t>
   </si>
   <si>
     <t xml:space="preserve">2.33211183547974</t>
@@ -4214,7 +4214,7 @@
     <t xml:space="preserve">2.37210130691528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41572618484497</t>
+    <t xml:space="preserve">2.41572594642639</t>
   </si>
   <si>
     <t xml:space="preserve">2.375736951828</t>
@@ -4223,13 +4223,13 @@
     <t xml:space="preserve">2.40845561027527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39754891395569</t>
+    <t xml:space="preserve">2.39754915237427</t>
   </si>
   <si>
     <t xml:space="preserve">2.38846063613892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39209580421448</t>
+    <t xml:space="preserve">2.39209604263306</t>
   </si>
   <si>
     <t xml:space="preserve">2.3575599193573</t>
@@ -4238,31 +4238,31 @@
     <t xml:space="preserve">2.34483575820923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30666399002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31575274467468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33574724197388</t>
+    <t xml:space="preserve">2.30666422843933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3157525062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3357470035553</t>
   </si>
   <si>
     <t xml:space="preserve">2.33938264846802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38118958473206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40663766860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40481948852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39027857780457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37937211990356</t>
+    <t xml:space="preserve">2.38118982315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40663743019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40481972694397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39027833938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37937188148499</t>
   </si>
   <si>
     <t xml:space="preserve">2.32302331924438</t>
@@ -4274,7 +4274,7 @@
     <t xml:space="preserve">2.18487787246704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23213815689087</t>
+    <t xml:space="preserve">2.23213839530945</t>
   </si>
   <si>
     <t xml:space="preserve">2.18306040763855</t>
@@ -4289,10 +4289,10 @@
     <t xml:space="preserve">2.20669031143188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17033648490906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13943529129028</t>
+    <t xml:space="preserve">2.17033624649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13943552970886</t>
   </si>
   <si>
     <t xml:space="preserve">2.14670634269714</t>
@@ -4301,10 +4301,10 @@
     <t xml:space="preserve">2.14852380752563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19578409194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19033098220825</t>
+    <t xml:space="preserve">2.19578385353088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19033122062683</t>
   </si>
   <si>
     <t xml:space="preserve">2.26849246025085</t>
@@ -4313,16 +4313,16 @@
     <t xml:space="preserve">2.24667978286743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24304413795471</t>
+    <t xml:space="preserve">2.24304437637329</t>
   </si>
   <si>
     <t xml:space="preserve">2.25213289260864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30121088027954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28303384780884</t>
+    <t xml:space="preserve">2.30121111869812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28303408622742</t>
   </si>
   <si>
     <t xml:space="preserve">2.34120011329651</t>
@@ -4334,7 +4334,7 @@
     <t xml:space="preserve">2.44844484329224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4884340763092</t>
+    <t xml:space="preserve">2.48843431472778</t>
   </si>
   <si>
     <t xml:space="preserve">2.46843957901001</t>
@@ -4343,28 +4343,28 @@
     <t xml:space="preserve">2.47207498550415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45935106277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45753359794617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43390297889709</t>
+    <t xml:space="preserve">2.45935082435608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45753335952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43390321731567</t>
   </si>
   <si>
     <t xml:space="preserve">2.51388192176819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46480417251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50297570228577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47025728225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40118455886841</t>
+    <t xml:space="preserve">2.46480393409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50297594070435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4702570438385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40118432044983</t>
   </si>
   <si>
     <t xml:space="preserve">2.36664843559265</t>
@@ -4382,7 +4382,7 @@
     <t xml:space="preserve">2.29212260246277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27030992507935</t>
+    <t xml:space="preserve">2.27030968666077</t>
   </si>
   <si>
     <t xml:space="preserve">2.22668528556824</t>
@@ -4403,7 +4403,7 @@
     <t xml:space="preserve">2.41936159133911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43208527565002</t>
+    <t xml:space="preserve">2.4320855140686</t>
   </si>
   <si>
     <t xml:space="preserve">2.42117929458618</t>
@@ -4418,7 +4418,7 @@
     <t xml:space="preserve">2.28207540512085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27462363243103</t>
+    <t xml:space="preserve">2.27462387084961</t>
   </si>
   <si>
     <t xml:space="preserve">2.24854278564453</t>
@@ -4436,16 +4436,16 @@
     <t xml:space="preserve">2.36590671539307</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40130233764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36404395103455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29697847366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32678532600403</t>
+    <t xml:space="preserve">2.40130209922791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36404371261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29697871208191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32678508758545</t>
   </si>
   <si>
     <t xml:space="preserve">2.34168839454651</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">2.29884147644043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28580117225647</t>
+    <t xml:space="preserve">2.28580093383789</t>
   </si>
   <si>
     <t xml:space="preserve">2.28021216392517</t>
@@ -4484,13 +4484,13 @@
     <t xml:space="preserve">2.33051156997681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31374502182007</t>
+    <t xml:space="preserve">2.31374478340149</t>
   </si>
   <si>
     <t xml:space="preserve">2.28952693939209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22432494163513</t>
+    <t xml:space="preserve">2.22432470321655</t>
   </si>
   <si>
     <t xml:space="preserve">2.20569562911987</t>
@@ -4502,7 +4502,7 @@
     <t xml:space="preserve">2.14049363136292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1069610118866</t>
+    <t xml:space="preserve">2.10696077346802</t>
   </si>
   <si>
     <t xml:space="preserve">2.09950923919678</t>
@@ -4514,13 +4514,13 @@
     <t xml:space="preserve">2.10882377624512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09019446372986</t>
+    <t xml:space="preserve">2.09019470214844</t>
   </si>
   <si>
     <t xml:space="preserve">2.0585253238678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04362154006958</t>
+    <t xml:space="preserve">2.04362177848816</t>
   </si>
   <si>
     <t xml:space="preserve">2.04921078681946</t>
@@ -4529,13 +4529,13 @@
     <t xml:space="preserve">2.08460593223572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06411385536194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0510733127594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04175877571106</t>
+    <t xml:space="preserve">2.06411409378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05107307434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04175853729248</t>
   </si>
   <si>
     <t xml:space="preserve">2.09205770492554</t>
@@ -4544,7 +4544,7 @@
     <t xml:space="preserve">2.15912270545959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15353417396545</t>
+    <t xml:space="preserve">2.15353393554688</t>
   </si>
   <si>
     <t xml:space="preserve">2.13863062858582</t>
@@ -4559,10 +4559,10 @@
     <t xml:space="preserve">2.0231294631958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01754069328308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99891173839569</t>
+    <t xml:space="preserve">2.01754093170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99891149997711</t>
   </si>
   <si>
     <t xml:space="preserve">2.01195240020752</t>
@@ -4571,7 +4571,7 @@
     <t xml:space="preserve">2.0007746219635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99332308769226</t>
+    <t xml:space="preserve">1.99332296848297</t>
   </si>
   <si>
     <t xml:space="preserve">1.97469365596771</t>
@@ -4580,19 +4580,19 @@
     <t xml:space="preserve">1.95606458187103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9262580871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86478173732758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77349865436554</t>
+    <t xml:space="preserve">1.92625796794891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86478161811829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77349853515625</t>
   </si>
   <si>
     <t xml:space="preserve">1.78095006942749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78467607498169</t>
+    <t xml:space="preserve">1.78467619419098</t>
   </si>
   <si>
     <t xml:space="preserve">1.80330526828766</t>
@@ -4607,7 +4607,7 @@
     <t xml:space="preserve">1.75673234462738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71109080314636</t>
+    <t xml:space="preserve">1.71109068393707</t>
   </si>
   <si>
     <t xml:space="preserve">1.70829629898071</t>
@@ -4619,19 +4619,19 @@
     <t xml:space="preserve">1.67196953296661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69991326332092</t>
+    <t xml:space="preserve">1.69991338253021</t>
   </si>
   <si>
     <t xml:space="preserve">1.66638076305389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.616082072258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63005375862122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63377964496613</t>
+    <t xml:space="preserve">1.61608195304871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63005387783051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63377952575684</t>
   </si>
   <si>
     <t xml:space="preserve">1.63564252853394</t>
@@ -4646,10 +4646,10 @@
     <t xml:space="preserve">1.53131926059723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5499484539032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53877067565918</t>
+    <t xml:space="preserve">1.54994833469391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53877079486847</t>
   </si>
   <si>
     <t xml:space="preserve">1.54529106616974</t>
@@ -4658,7 +4658,7 @@
     <t xml:space="preserve">1.54249656200409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55087971687317</t>
+    <t xml:space="preserve">1.55087983608246</t>
   </si>
   <si>
     <t xml:space="preserve">1.55646848678589</t>
@@ -4676,13 +4676,13 @@
     <t xml:space="preserve">1.60117852687836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60956168174744</t>
+    <t xml:space="preserve">1.60956180095673</t>
   </si>
   <si>
     <t xml:space="preserve">1.61980772018433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62819087505341</t>
+    <t xml:space="preserve">1.6281909942627</t>
   </si>
   <si>
     <t xml:space="preserve">1.59745287895203</t>
@@ -4691,7 +4691,7 @@
     <t xml:space="preserve">1.61235594749451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62073922157288</t>
+    <t xml:space="preserve">1.62073934078217</t>
   </si>
   <si>
     <t xml:space="preserve">1.67755818367004</t>
@@ -4709,10 +4709,10 @@
     <t xml:space="preserve">1.69153010845184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66917502880096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6682436466217</t>
+    <t xml:space="preserve">1.66917514801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66824352741241</t>
   </si>
   <si>
     <t xml:space="preserve">1.67662680149078</t>
@@ -4736,16 +4736,16 @@
     <t xml:space="preserve">1.92998361587524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97655653953552</t>
+    <t xml:space="preserve">1.97655665874481</t>
   </si>
   <si>
     <t xml:space="preserve">1.96165335178375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91508030891418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93557250499725</t>
+    <t xml:space="preserve">1.91508042812347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93557262420654</t>
   </si>
   <si>
     <t xml:space="preserve">1.90949153900146</t>
@@ -4766,7 +4766,7 @@
     <t xml:space="preserve">2.09392046928406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11068677902222</t>
+    <t xml:space="preserve">2.1106870174408</t>
   </si>
   <si>
     <t xml:space="preserve">2.08646893501282</t>
@@ -4775,19 +4775,19 @@
     <t xml:space="preserve">2.12000155448914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11441254615784</t>
+    <t xml:space="preserve">2.11441278457642</t>
   </si>
   <si>
     <t xml:space="preserve">2.10137224197388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03617000579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0026376247406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98028254508972</t>
+    <t xml:space="preserve">2.03617024421692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00263786315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98028242588043</t>
   </si>
   <si>
     <t xml:space="preserve">2.01008915901184</t>
@@ -4796,10 +4796,10 @@
     <t xml:space="preserve">2.01567792892456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98214542865753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90017700195312</t>
+    <t xml:space="preserve">1.98214554786682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90017688274384</t>
   </si>
   <si>
     <t xml:space="preserve">1.91694331169128</t>
@@ -4808,7 +4808,7 @@
     <t xml:space="preserve">1.8927253484726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92812085151672</t>
+    <t xml:space="preserve">1.92812073230743</t>
   </si>
   <si>
     <t xml:space="preserve">1.95420169830322</t>
@@ -4820,7 +4820,7 @@
     <t xml:space="preserve">2.03989601135254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07529139518738</t>
+    <t xml:space="preserve">2.0752911567688</t>
   </si>
   <si>
     <t xml:space="preserve">2.09578347206116</t>
@@ -5934,6 +5934,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.30399990081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40999984741211</t>
   </si>
 </sst>
 </file>
@@ -71454,7 +71457,7 @@
     </row>
     <row r="2508">
       <c r="A2508" s="1" t="n">
-        <v>45971.6912731481</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B2508" t="n">
         <v>322312</v>
@@ -71475,6 +71478,32 @@
         <v>1973</v>
       </c>
       <c r="H2508" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" s="1" t="n">
+        <v>45972.691099537</v>
+      </c>
+      <c r="B2509" t="n">
+        <v>714498</v>
+      </c>
+      <c r="C2509" t="n">
+        <v>4.41800022125244</v>
+      </c>
+      <c r="D2509" t="n">
+        <v>4.32600021362305</v>
+      </c>
+      <c r="E2509" t="n">
+        <v>4.32999992370605</v>
+      </c>
+      <c r="F2509" t="n">
+        <v>4.40999984741211</v>
+      </c>
+      <c r="G2509" t="s">
+        <v>1974</v>
+      </c>
+      <c r="H2509" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/OVS.MI.xlsx
+++ b/data/OVS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1975" uniqueCount="1975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1976" uniqueCount="1976">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03756332397461</t>
+    <t xml:space="preserve">5.03756380081177</t>
   </si>
   <si>
     <t xml:space="preserve">OVS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89862394332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76365375518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64456176757812</t>
+    <t xml:space="preserve">4.89862442016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76365327835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64456272125244</t>
   </si>
   <si>
     <t xml:space="preserve">4.71998643875122</t>
@@ -65,28 +65,28 @@
     <t xml:space="preserve">4.94229030609131</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69219875335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60486507415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6366229057312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.616774559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25156021118164</t>
+    <t xml:space="preserve">4.69219923019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60486459732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63662385940552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61677408218384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2515606880188</t>
   </si>
   <si>
     <t xml:space="preserve">4.22774267196655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53341007232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45798540115356</t>
+    <t xml:space="preserve">4.53341054916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45798587799072</t>
   </si>
   <si>
     <t xml:space="preserve">4.47783422470093</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">4.49768304824829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5135612487793</t>
+    <t xml:space="preserve">4.51356172561646</t>
   </si>
   <si>
     <t xml:space="preserve">4.44607734680176</t>
@@ -104,10 +104,10 @@
     <t xml:space="preserve">4.62868356704712</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59295606613159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5175313949585</t>
+    <t xml:space="preserve">4.59295654296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51753234863281</t>
   </si>
   <si>
     <t xml:space="preserve">4.54531955718994</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">4.32698535919189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03322601318359</t>
+    <t xml:space="preserve">4.03322649002075</t>
   </si>
   <si>
     <t xml:space="preserve">4.02925682067871</t>
@@ -128,43 +128,43 @@
     <t xml:space="preserve">4.22377252578735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38256120681763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30316734313965</t>
+    <t xml:space="preserve">4.38256168365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30316781997681</t>
   </si>
   <si>
     <t xml:space="preserve">4.46989488601685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46592426300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48577356338501</t>
+    <t xml:space="preserve">4.46592473983765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48577404022217</t>
   </si>
   <si>
     <t xml:space="preserve">4.48974275588989</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27140951156616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23965167999268</t>
+    <t xml:space="preserve">4.271409034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23965215682983</t>
   </si>
   <si>
     <t xml:space="preserve">4.43813753128052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5651683807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67235088348389</t>
+    <t xml:space="preserve">4.56516885757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67235040664673</t>
   </si>
   <si>
     <t xml:space="preserve">4.71601676940918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58898735046387</t>
+    <t xml:space="preserve">4.58898687362671</t>
   </si>
   <si>
     <t xml:space="preserve">4.50562238693237</t>
@@ -173,55 +173,55 @@
     <t xml:space="preserve">4.52547121047974</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38653039932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43019819259644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40241003036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29125738143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12055969238281</t>
+    <t xml:space="preserve">4.38653135299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43019866943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40241050720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29125785827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12056016921997</t>
   </si>
   <si>
     <t xml:space="preserve">4.09674215316772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06498432159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08880233764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15628623962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21186351776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04910564422607</t>
+    <t xml:space="preserve">4.0649847984314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08880281448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15628719329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21186399459839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04910516738892</t>
   </si>
   <si>
     <t xml:space="preserve">4.02131748199463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31110620498657</t>
+    <t xml:space="preserve">4.31110668182373</t>
   </si>
   <si>
     <t xml:space="preserve">4.16422700881958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23568153381348</t>
+    <t xml:space="preserve">4.23568201065063</t>
   </si>
   <si>
     <t xml:space="preserve">4.50959205627441</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7358660697937</t>
+    <t xml:space="preserve">4.73586654663086</t>
   </si>
   <si>
     <t xml:space="preserve">4.54928922653198</t>
@@ -230,13 +230,13 @@
     <t xml:space="preserve">4.50165271759033</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56119823455811</t>
+    <t xml:space="preserve">4.56119775772095</t>
   </si>
   <si>
     <t xml:space="preserve">4.48180437088013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52150249481201</t>
+    <t xml:space="preserve">4.52150201797485</t>
   </si>
   <si>
     <t xml:space="preserve">4.55325889587402</t>
@@ -248,22 +248,22 @@
     <t xml:space="preserve">4.56913757324219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5373797416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64853143692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70410776138306</t>
+    <t xml:space="preserve">4.53738021850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64853191375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70410823822021</t>
   </si>
   <si>
     <t xml:space="preserve">4.84304809570312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89068412780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81525945663452</t>
+    <t xml:space="preserve">4.89068460464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81525993347168</t>
   </si>
   <si>
     <t xml:space="preserve">4.87877559661865</t>
@@ -272,22 +272,22 @@
     <t xml:space="preserve">4.91053295135498</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75968456268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73826837539673</t>
+    <t xml:space="preserve">4.75968360900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73826789855957</t>
   </si>
   <si>
     <t xml:space="preserve">4.7667875289917</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90123558044434</t>
+    <t xml:space="preserve">4.90123510360718</t>
   </si>
   <si>
     <t xml:space="preserve">4.73419427871704</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56715393066406</t>
+    <t xml:space="preserve">4.5671534538269</t>
   </si>
   <si>
     <t xml:space="preserve">4.51826286315918</t>
@@ -296,7 +296,7 @@
     <t xml:space="preserve">4.4734468460083</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47752094268799</t>
+    <t xml:space="preserve">4.47751998901367</t>
   </si>
   <si>
     <t xml:space="preserve">4.48974418640137</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">4.33085060119629</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94706320762634</t>
+    <t xml:space="preserve">3.94706296920776</t>
   </si>
   <si>
     <t xml:space="preserve">4.13529014587402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24529361724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26566219329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30233144760132</t>
+    <t xml:space="preserve">4.24529314041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26566314697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30233192443848</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751543045044</t>
@@ -338,34 +338,34 @@
     <t xml:space="preserve">4.11084461212158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09047317504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05299091339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18825387954712</t>
+    <t xml:space="preserve">4.09047412872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05299139022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18825340270996</t>
   </si>
   <si>
     <t xml:space="preserve">4.16380882263184</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15566110610962</t>
+    <t xml:space="preserve">4.15566062927246</t>
   </si>
   <si>
     <t xml:space="preserve">4.15973472595215</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10677051544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04321384429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11899328231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16788339614868</t>
+    <t xml:space="preserve">4.10677146911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04321432113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11899280548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16788291931152</t>
   </si>
   <si>
     <t xml:space="preserve">4.26158952713013</t>
@@ -374,10 +374,10 @@
     <t xml:space="preserve">4.2004771232605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20862483978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.233069896698</t>
+    <t xml:space="preserve">4.20862531661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23307037353516</t>
   </si>
   <si>
     <t xml:space="preserve">4.37159252166748</t>
@@ -386,16 +386,16 @@
     <t xml:space="preserve">4.36751842498779</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28603458404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27788543701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24121809005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25344085693359</t>
+    <t xml:space="preserve">4.28603410720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27788639068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24121856689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25344181060791</t>
   </si>
   <si>
     <t xml:space="preserve">4.29825735092163</t>
@@ -407,22 +407,22 @@
     <t xml:space="preserve">4.0725474357605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17195749282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19232797622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10269641876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04158401489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13936376571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09862327575684</t>
+    <t xml:space="preserve">4.17195796966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19232749938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10269689559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04158353805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13936424255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09862279891968</t>
   </si>
   <si>
     <t xml:space="preserve">4.00084209442139</t>
@@ -431,22 +431,22 @@
     <t xml:space="preserve">3.99269366264343</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03343534469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19640207290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15158700942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08640003204346</t>
+    <t xml:space="preserve">4.0334358215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19640302658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15158653259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0863995552063</t>
   </si>
   <si>
     <t xml:space="preserve">4.06114053726196</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3593692779541</t>
+    <t xml:space="preserve">4.35936975479126</t>
   </si>
   <si>
     <t xml:space="preserve">4.37566709518433</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">4.31047916412354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31455373764038</t>
+    <t xml:space="preserve">4.31455326080322</t>
   </si>
   <si>
     <t xml:space="preserve">4.26973819732666</t>
@@ -473,19 +473,19 @@
     <t xml:space="preserve">4.21677350997925</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1801061630249</t>
+    <t xml:space="preserve">4.18010568618774</t>
   </si>
   <si>
     <t xml:space="preserve">4.1434383392334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11491823196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07417821884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06928825378418</t>
+    <t xml:space="preserve">4.11491870880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07417774200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06928873062134</t>
   </si>
   <si>
     <t xml:space="preserve">4.08232545852661</t>
@@ -500,61 +500,61 @@
     <t xml:space="preserve">3.96010065078735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05462074279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13121652603149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04647254943848</t>
+    <t xml:space="preserve">4.05462121963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13121557235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04647302627563</t>
   </si>
   <si>
     <t xml:space="preserve">3.98128533363342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00410223007202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98617458343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02528762817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97476696968079</t>
+    <t xml:space="preserve">4.00410127639771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98617482185364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02528715133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97476649284363</t>
   </si>
   <si>
     <t xml:space="preserve">4.02365684509277</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05951023101807</t>
+    <t xml:space="preserve">4.05950975418091</t>
   </si>
   <si>
     <t xml:space="preserve">4.04810190200806</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05136251449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97965621948242</t>
+    <t xml:space="preserve">4.05136156082153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.979656457901</t>
   </si>
   <si>
     <t xml:space="preserve">4.03017568588257</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02039813995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99921202659607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07825136184692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14751291275024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23714447021484</t>
+    <t xml:space="preserve">4.02039861679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99921226501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07825183868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1475133895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23714399337769</t>
   </si>
   <si>
     <t xml:space="preserve">4.20455121994019</t>
@@ -569,31 +569,31 @@
     <t xml:space="preserve">4.02202749252319</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93076610565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91284012794495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89491295814514</t>
+    <t xml:space="preserve">3.93076586723328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91283941268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89491271972656</t>
   </si>
   <si>
     <t xml:space="preserve">3.87535738945007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94054484367371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93402600288391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89654350280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9552116394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00247240066528</t>
+    <t xml:space="preserve">3.94054436683655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93402552604675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89654302597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95521116256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00247192382812</t>
   </si>
   <si>
     <t xml:space="preserve">4.37974071502686</t>
@@ -605,19 +605,19 @@
     <t xml:space="preserve">4.39196348190308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35529518127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29010820388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28196001052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32677698135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2941837310791</t>
+    <t xml:space="preserve">4.35529565811157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2901086807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28196048736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3267765045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29418325424194</t>
   </si>
   <si>
     <t xml:space="preserve">4.33899927139282</t>
@@ -629,25 +629,25 @@
     <t xml:space="preserve">4.34307336807251</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46529912948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48159503936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40825986862183</t>
+    <t xml:space="preserve">4.46529865264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48159551620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40826034545898</t>
   </si>
   <si>
     <t xml:space="preserve">4.53863382339478</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55493068695068</t>
+    <t xml:space="preserve">4.55492973327637</t>
   </si>
   <si>
     <t xml:space="preserve">4.52641105651855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5060396194458</t>
+    <t xml:space="preserve">4.50604009628296</t>
   </si>
   <si>
     <t xml:space="preserve">4.43270492553711</t>
@@ -656,7 +656,7 @@
     <t xml:space="preserve">4.59567213058472</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68530416488647</t>
+    <t xml:space="preserve">4.68530511856079</t>
   </si>
   <si>
     <t xml:space="preserve">4.67308187484741</t>
@@ -665,25 +665,25 @@
     <t xml:space="preserve">4.60382032394409</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70160055160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85641956329346</t>
+    <t xml:space="preserve">4.70160007476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85642004013062</t>
   </si>
   <si>
     <t xml:space="preserve">4.82382583618164</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77493524551392</t>
+    <t xml:space="preserve">4.77493572235107</t>
   </si>
   <si>
     <t xml:space="preserve">4.79938077926636</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74234294891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78308439254761</t>
+    <t xml:space="preserve">4.74234247207642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78308534622192</t>
   </si>
   <si>
     <t xml:space="preserve">4.72604560852051</t>
@@ -692,28 +692,28 @@
     <t xml:space="preserve">4.77900981903076</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80752992630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86456775665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04790639877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01531219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89716053009033</t>
+    <t xml:space="preserve">4.80752944946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86456823348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04790544509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01531314849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89716148376465</t>
   </si>
   <si>
     <t xml:space="preserve">4.91753196716309</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88901329040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04383134841919</t>
+    <t xml:space="preserve">4.88901281356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04383182525635</t>
   </si>
   <si>
     <t xml:space="preserve">4.90531015396118</t>
@@ -722,19 +722,19 @@
     <t xml:space="preserve">4.95012521743774</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05198049545288</t>
+    <t xml:space="preserve">5.05198097229004</t>
   </si>
   <si>
     <t xml:space="preserve">4.97864532470703</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03160858154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08457326889038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23939180374146</t>
+    <t xml:space="preserve">5.03160905838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08457374572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23939228057861</t>
   </si>
   <si>
     <t xml:space="preserve">5.19865083694458</t>
@@ -743,382 +743,385 @@
     <t xml:space="preserve">5.14568567276001</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19457530975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05605411529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06420278549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13346385955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11716747283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25161504745483</t>
+    <t xml:space="preserve">5.19457674026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05605506896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0642032623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13346338272095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11716651916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25161457061768</t>
   </si>
   <si>
     <t xml:space="preserve">5.18235397338867</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17827939987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25568962097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27198457717896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17420530319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16605663299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18642807006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10494518280029</t>
+    <t xml:space="preserve">5.17827987670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25568914413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27198553085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17420482635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16605710983276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1864275932312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10494470596313</t>
   </si>
   <si>
     <t xml:space="preserve">5.07235050201416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94605112075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06827592849731</t>
+    <t xml:space="preserve">4.94605207443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06827640533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98679351806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0369119644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3626823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39191770553589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3125638961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27915048599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34597587585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35432863235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32091617584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33762311935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27079772949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27497434616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18726778030396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.132972240448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2039737701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22903347015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25409126281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2624454498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18309116363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21232652664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17891407012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24991512298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24573850631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28332805633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22485589981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30003356933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33344650268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40444707870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37521171569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40027046203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38356494903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37938737869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23320960998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3083872795105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2582688331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2081503868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1371488571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11208963394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1538553237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23738527297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32509279251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30420970916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29585742950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32926988601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48797845840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53809690475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59656810760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62580394744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68845272064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61327457427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57568550109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44203615188599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62162828445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68009901046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64251041412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37103509902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39609384536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3877420425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2415623664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29168033599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19562005996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0828537940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88655614852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90743923187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81973075866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80302572250366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8447904586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83643770217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94502687454224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90326309204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86567306518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87820339202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8531436920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81137847900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95755767822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92832136154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77796649932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.861496925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8322606086731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72367000579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6610221862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69861078262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6693754196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63596343994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70278882980347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6735520362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64014005661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71949434280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79049587249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74872970581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7320237159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71114110946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67772912979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91579246520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92414474487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8949089050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8406138420105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16220760345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99932193756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02020454406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17056083679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09955930709839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95338153839111</t>
   </si>
   <si>
     <t xml:space="preserve">4.98679304122925</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0369119644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36268186569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39191770553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31256341934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27915048599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34597587585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35432863235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32091617584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33762264251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27079820632935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27497434616089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18726778030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.132972240448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2039737701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22903299331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25409126281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2624454498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1830906867981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21232652664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17891454696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24991512298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2457389831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28332805633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22485589981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30003356933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33344697952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40444660186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37521171569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40027093887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38356494903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37938785552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23320960998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3083872795105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25826930999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20814990997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1371488571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11208915710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1538553237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23738527297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32509183883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30421018600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29585742950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32926988601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48797798156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5380973815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59656858444214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62580394744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68845272064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61327505111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57568502426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44203615188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62162780761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68009901046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64251041412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37103462219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39609336853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3877420425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24156188964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29168081283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19561958312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08285427093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88655567169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90743923187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81973123550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8030252456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8447904586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83643770217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94502735137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9032621383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86567354202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87820339202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85314416885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81137800216675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95755767822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92832183837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77796602249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.861496925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83226156234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72367000579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66102313995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69861078262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66937589645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63596343994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70278835296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6735520362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64013957977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7194938659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7904953956604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74872970581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7320237159729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71114110946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67772912979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91579246520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92414474487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89490842819214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84061431884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16220855712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99932241439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02020502090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17056083679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09955930709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95338153839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78631925582886</t>
+    <t xml:space="preserve">4.7863187789917</t>
   </si>
   <si>
     <t xml:space="preserve">4.6860818862915</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60672760009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59419775009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61508083343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63178682327271</t>
+    <t xml:space="preserve">4.60672807693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59419822692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6150803565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63178730010986</t>
   </si>
   <si>
     <t xml:space="preserve">4.70696496963501</t>
@@ -1133,10 +1136,10 @@
     <t xml:space="preserve">4.53990268707275</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57749271392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48978424072266</t>
+    <t xml:space="preserve">4.57749223709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4897837638855</t>
   </si>
   <si>
     <t xml:space="preserve">4.41043043136597</t>
@@ -1145,31 +1148,28 @@
     <t xml:space="preserve">4.4438419342041</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49396085739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47307777404785</t>
+    <t xml:space="preserve">4.4939603805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47307825088501</t>
   </si>
   <si>
     <t xml:space="preserve">4.51902008056641</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5691385269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59002161026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65684604644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64849281311035</t>
+    <t xml:space="preserve">4.59002113342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65684652328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64849233627319</t>
   </si>
   <si>
     <t xml:space="preserve">4.59837436676025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5607852935791</t>
+    <t xml:space="preserve">4.56078577041626</t>
   </si>
   <si>
     <t xml:space="preserve">4.48560857772827</t>
@@ -1181,13 +1181,13 @@
     <t xml:space="preserve">4.36031150817871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3853702545166</t>
+    <t xml:space="preserve">4.38537073135376</t>
   </si>
   <si>
     <t xml:space="preserve">4.18907308578491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16150808334351</t>
+    <t xml:space="preserve">4.16150760650635</t>
   </si>
   <si>
     <t xml:space="preserve">4.15148448944092</t>
@@ -1199,25 +1199,25 @@
     <t xml:space="preserve">4.19324922561646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09802484512329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15315532684326</t>
+    <t xml:space="preserve">4.09802436828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1531548500061</t>
   </si>
   <si>
     <t xml:space="preserve">4.10303688049316</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12642526626587</t>
+    <t xml:space="preserve">4.12642574310303</t>
   </si>
   <si>
     <t xml:space="preserve">4.16986131668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17654418945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14313125610352</t>
+    <t xml:space="preserve">4.17654371261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14313077926636</t>
   </si>
   <si>
     <t xml:space="preserve">4.16819047927856</t>
@@ -1226,22 +1226,22 @@
     <t xml:space="preserve">2.83002591133118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90687417984009</t>
+    <t xml:space="preserve">2.90687441825867</t>
   </si>
   <si>
     <t xml:space="preserve">2.84339070320129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87179136276245</t>
+    <t xml:space="preserve">2.87179160118103</t>
   </si>
   <si>
     <t xml:space="preserve">2.89350914955139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80162501335144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92358064651489</t>
+    <t xml:space="preserve">2.80162525177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92358040809631</t>
   </si>
   <si>
     <t xml:space="preserve">2.94863963127136</t>
@@ -1250,13 +1250,13 @@
     <t xml:space="preserve">3.01713514328003</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08061861991882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17083168029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14911365509033</t>
+    <t xml:space="preserve">3.0806188583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17083144187927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14911389350891</t>
   </si>
   <si>
     <t xml:space="preserve">3.15746665000916</t>
@@ -1265,7 +1265,7 @@
     <t xml:space="preserve">3.14410161972046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17918515205383</t>
+    <t xml:space="preserve">3.17918491363525</t>
   </si>
   <si>
     <t xml:space="preserve">3.17417311668396</t>
@@ -1277,7 +1277,7 @@
     <t xml:space="preserve">3.01212334632874</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02882981300354</t>
+    <t xml:space="preserve">3.02882957458496</t>
   </si>
   <si>
     <t xml:space="preserve">2.94529795646667</t>
@@ -1304,37 +1304,37 @@
     <t xml:space="preserve">2.55771470069885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54769158363342</t>
+    <t xml:space="preserve">2.547691822052</t>
   </si>
   <si>
     <t xml:space="preserve">2.51093792915344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58945727348328</t>
+    <t xml:space="preserve">2.5894570350647</t>
   </si>
   <si>
     <t xml:space="preserve">2.5009138584137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51594972610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50592589378357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47919631004333</t>
+    <t xml:space="preserve">2.51594996452332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50592565536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47919607162476</t>
   </si>
   <si>
     <t xml:space="preserve">2.41905355453491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39566540718079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36058235168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36726474761963</t>
+    <t xml:space="preserve">2.39566516876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36058211326599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36726450920105</t>
   </si>
   <si>
     <t xml:space="preserve">2.3772885799408</t>
@@ -1343,7 +1343,7 @@
     <t xml:space="preserve">2.2753803730011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.313805103302</t>
+    <t xml:space="preserve">2.31380534172058</t>
   </si>
   <si>
     <t xml:space="preserve">2.26201558113098</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">2.27203965187073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41404271125793</t>
+    <t xml:space="preserve">2.41404247283936</t>
   </si>
   <si>
     <t xml:space="preserve">2.38062930107117</t>
@@ -1364,22 +1364,22 @@
     <t xml:space="preserve">2.30211091041565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29709887504578</t>
+    <t xml:space="preserve">2.29709911346436</t>
   </si>
   <si>
     <t xml:space="preserve">2.32382845878601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33552289009094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35389947891235</t>
+    <t xml:space="preserve">2.33552312850952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35389995574951</t>
   </si>
   <si>
     <t xml:space="preserve">2.36559414863586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35055828094482</t>
+    <t xml:space="preserve">2.35055804252625</t>
   </si>
   <si>
     <t xml:space="preserve">2.35222911834717</t>
@@ -1397,19 +1397,19 @@
     <t xml:space="preserve">2.28039240837097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22526168823242</t>
+    <t xml:space="preserve">2.225261926651</t>
   </si>
   <si>
     <t xml:space="preserve">2.23027372360229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40067672729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44912481307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42406535148621</t>
+    <t xml:space="preserve">2.40067648887634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44912457466125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42406558990479</t>
   </si>
   <si>
     <t xml:space="preserve">2.31881666183472</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">2.34387564659119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33218145370483</t>
+    <t xml:space="preserve">2.33218121528625</t>
   </si>
   <si>
     <t xml:space="preserve">2.27371001243591</t>
@@ -1445,7 +1445,7 @@
     <t xml:space="preserve">2.05485892295837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01142287254333</t>
+    <t xml:space="preserve">2.01142311096191</t>
   </si>
   <si>
     <t xml:space="preserve">1.97466909885406</t>
@@ -1457,7 +1457,7 @@
     <t xml:space="preserve">2.03815340995789</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15175533294678</t>
+    <t xml:space="preserve">2.1517550945282</t>
   </si>
   <si>
     <t xml:space="preserve">2.17180252075195</t>
@@ -1466,7 +1466,7 @@
     <t xml:space="preserve">2.18182587623596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16679072380066</t>
+    <t xml:space="preserve">2.16679048538208</t>
   </si>
   <si>
     <t xml:space="preserve">2.16846084594727</t>
@@ -1481,16 +1481,16 @@
     <t xml:space="preserve">2.1150016784668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07657766342163</t>
+    <t xml:space="preserve">2.07657742500305</t>
   </si>
   <si>
     <t xml:space="preserve">2.08994221687317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09829521179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16010808944702</t>
+    <t xml:space="preserve">2.09829497337341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16010785102844</t>
   </si>
   <si>
     <t xml:space="preserve">2.09662461280823</t>
@@ -1502,10 +1502,10 @@
     <t xml:space="preserve">2.02478766441345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02645874023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12502479553223</t>
+    <t xml:space="preserve">2.02645921707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12502455711365</t>
   </si>
   <si>
     <t xml:space="preserve">2.23695635795593</t>
@@ -1520,22 +1520,22 @@
     <t xml:space="preserve">2.06989502906799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06321263313293</t>
+    <t xml:space="preserve">2.06321287155151</t>
   </si>
   <si>
     <t xml:space="preserve">2.00139951705933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9997284412384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98302292823792</t>
+    <t xml:space="preserve">1.99972856044769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98302280902863</t>
   </si>
   <si>
     <t xml:space="preserve">1.94626939296722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8761031627655</t>
+    <t xml:space="preserve">1.87610340118408</t>
   </si>
   <si>
     <t xml:space="preserve">1.75748944282532</t>
@@ -1544,25 +1544,25 @@
     <t xml:space="preserve">1.69567656517029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65391063690186</t>
+    <t xml:space="preserve">1.65391051769257</t>
   </si>
   <si>
     <t xml:space="preserve">1.6288515329361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62968707084656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50439083576202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48601388931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39663553237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31728160381317</t>
+    <t xml:space="preserve">1.62968695163727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50439071655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48601400852203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39663565158844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31728136539459</t>
   </si>
   <si>
     <t xml:space="preserve">1.28553974628448</t>
@@ -1571,13 +1571,13 @@
     <t xml:space="preserve">1.27133929729462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24962162971497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24460959434509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28971612453461</t>
+    <t xml:space="preserve">1.24962174892426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24460971355438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2897162437439</t>
   </si>
   <si>
     <t xml:space="preserve">1.27635133266449</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">1.31310498714447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28386926651001</t>
+    <t xml:space="preserve">1.2838693857193</t>
   </si>
   <si>
     <t xml:space="preserve">1.27969300746918</t>
@@ -1601,28 +1601,28 @@
     <t xml:space="preserve">1.33899998664856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35152924060822</t>
+    <t xml:space="preserve">1.35152912139893</t>
   </si>
   <si>
     <t xml:space="preserve">1.29472815990448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29639852046967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2429393529892</t>
+    <t xml:space="preserve">1.29639863967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24293923377991</t>
   </si>
   <si>
     <t xml:space="preserve">1.25212776660919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26799857616425</t>
+    <t xml:space="preserve">1.26799869537354</t>
   </si>
   <si>
     <t xml:space="preserve">1.25296247005463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2337509393692</t>
+    <t xml:space="preserve">1.23375082015991</t>
   </si>
   <si>
     <t xml:space="preserve">1.25630402565002</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">1.2579745054245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26048052310944</t>
+    <t xml:space="preserve">1.26048040390015</t>
   </si>
   <si>
     <t xml:space="preserve">1.36823558807373</t>
@@ -1655,22 +1655,22 @@
     <t xml:space="preserve">1.25129199028015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2387627363205</t>
+    <t xml:space="preserve">1.23876285552979</t>
   </si>
   <si>
     <t xml:space="preserve">1.06835913658142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962275207042694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989840507507324</t>
+    <t xml:space="preserve">0.962275326251984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989840567111969</t>
   </si>
   <si>
     <t xml:space="preserve">0.633163154125214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.703329920768738</t>
+    <t xml:space="preserve">0.703329861164093</t>
   </si>
   <si>
     <t xml:space="preserve">0.705000281333923</t>
@@ -1679,10 +1679,10 @@
     <t xml:space="preserve">0.862038254737854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958098948001862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94807493686676</t>
+    <t xml:space="preserve">0.958098828792572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948074817657471</t>
   </si>
   <si>
     <t xml:space="preserve">0.848673403263092</t>
@@ -1691,55 +1691,55 @@
     <t xml:space="preserve">0.913827180862427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.94473397731781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918839156627655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917168796062469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00487577915192</t>
+    <t xml:space="preserve">0.944734156131744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.91883909702301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917168915271759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00487565994263</t>
   </si>
   <si>
     <t xml:space="preserve">1.1477142572403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1143012046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09926605224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13184332847595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10344243049622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03578281402588</t>
+    <t xml:space="preserve">1.11430132389069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09926617145538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13184344768524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10344254970551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03578269481659</t>
   </si>
   <si>
     <t xml:space="preserve">1.01155817508698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01824069023132</t>
+    <t xml:space="preserve">1.01824057102203</t>
   </si>
   <si>
     <t xml:space="preserve">0.999029040336609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01573538780212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01322937011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08255958557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10177206993103</t>
+    <t xml:space="preserve">1.01573550701141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01322960853577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08255970478058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10177218914032</t>
   </si>
   <si>
     <t xml:space="preserve">1.1276661157608</t>
@@ -1754,19 +1754,19 @@
     <t xml:space="preserve">1.1368545293808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11346638202667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10260701179504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06585323810577</t>
+    <t xml:space="preserve">1.11346650123596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10260689258575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06585311889648</t>
   </si>
   <si>
     <t xml:space="preserve">1.0324410200119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07086515426636</t>
+    <t xml:space="preserve">1.07086503505707</t>
   </si>
   <si>
     <t xml:space="preserve">1.06334793567657</t>
@@ -1778,19 +1778,19 @@
     <t xml:space="preserve">1.03494703769684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06501841545105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12850165367126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08506572246552</t>
+    <t xml:space="preserve">1.06501829624176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12850177288055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08506560325623</t>
   </si>
   <si>
     <t xml:space="preserve">1.08673596382141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07253646850586</t>
+    <t xml:space="preserve">1.07253634929657</t>
   </si>
   <si>
     <t xml:space="preserve">1.08088910579681</t>
@@ -1802,19 +1802,19 @@
     <t xml:space="preserve">1.07838308811188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10010087490082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11263084411621</t>
+    <t xml:space="preserve">1.10010075569153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1126309633255</t>
   </si>
   <si>
     <t xml:space="preserve">1.11012494564056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22623288631439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46179032325745</t>
+    <t xml:space="preserve">1.22623264789581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46179020404816</t>
   </si>
   <si>
     <t xml:space="preserve">1.41584801673889</t>
@@ -1823,13 +1823,13 @@
     <t xml:space="preserve">1.414177775383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36071753501892</t>
+    <t xml:space="preserve">1.36071765422821</t>
   </si>
   <si>
     <t xml:space="preserve">1.330646276474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29806983470917</t>
+    <t xml:space="preserve">1.29806995391846</t>
   </si>
   <si>
     <t xml:space="preserve">1.37324750423431</t>
@@ -1847,22 +1847,22 @@
     <t xml:space="preserve">1.35487067699432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32897591590881</t>
+    <t xml:space="preserve">1.32897579669952</t>
   </si>
   <si>
     <t xml:space="preserve">1.36572957038879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37157642841339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40248310565948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41918885707855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42169499397278</t>
+    <t xml:space="preserve">1.3715763092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40248334407806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41918897628784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42169487476349</t>
   </si>
   <si>
     <t xml:space="preserve">1.42253053188324</t>
@@ -1874,16 +1874,16 @@
     <t xml:space="preserve">1.39997732639313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37575268745422</t>
+    <t xml:space="preserve">1.37575280666351</t>
   </si>
   <si>
     <t xml:space="preserve">1.3941296339035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4534364938736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43589544296265</t>
+    <t xml:space="preserve">1.45343661308289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43589532375336</t>
   </si>
   <si>
     <t xml:space="preserve">1.52861440181732</t>
@@ -1892,13 +1892,13 @@
     <t xml:space="preserve">1.61131012439728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59710991382599</t>
+    <t xml:space="preserve">1.5971097946167</t>
   </si>
   <si>
     <t xml:space="preserve">1.59376907348633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5745564699173</t>
+    <t xml:space="preserve">1.57455658912659</t>
   </si>
   <si>
     <t xml:space="preserve">1.55283880233765</t>
@@ -1907,28 +1907,28 @@
     <t xml:space="preserve">1.55116760730743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51441490650177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47097861766815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41751849651337</t>
+    <t xml:space="preserve">1.51441478729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47097873687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41751861572266</t>
   </si>
   <si>
     <t xml:space="preserve">1.43422496318817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3882828950882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38327074050903</t>
+    <t xml:space="preserve">1.38828277587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38327085971832</t>
   </si>
   <si>
     <t xml:space="preserve">1.33231675624847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36740005016327</t>
+    <t xml:space="preserve">1.36739993095398</t>
   </si>
   <si>
     <t xml:space="preserve">1.34985888004303</t>
@@ -1937,25 +1937,25 @@
     <t xml:space="preserve">1.30308091640472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32229340076447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31644570827484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29890465736389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30892872810364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31059896945953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31895196437836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29222214221954</t>
+    <t xml:space="preserve">1.32229351997375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31644582748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2989045381546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30892860889435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31059908866882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31895184516907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29222226142883</t>
   </si>
   <si>
     <t xml:space="preserve">1.28721022605896</t>
@@ -1964,43 +1964,43 @@
     <t xml:space="preserve">1.25045645236969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32730555534363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31143474578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31978750228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3490229845047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34651720523834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30725824832916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26215076446533</t>
+    <t xml:space="preserve">1.32730543613434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31143462657928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31978738307953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34902310371399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34651696681976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30725836753845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26215088367462</t>
   </si>
   <si>
     <t xml:space="preserve">1.26883316040039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22205638885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19198524951935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35821151733398</t>
+    <t xml:space="preserve">1.22205626964569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19198501110077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35821163654327</t>
   </si>
   <si>
     <t xml:space="preserve">1.32312917709351</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28219902515411</t>
+    <t xml:space="preserve">1.28219890594482</t>
   </si>
   <si>
     <t xml:space="preserve">1.24043321609497</t>
@@ -2015,16 +2015,16 @@
     <t xml:space="preserve">1.32646989822388</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33816432952881</t>
+    <t xml:space="preserve">1.33816421031952</t>
   </si>
   <si>
     <t xml:space="preserve">1.42503654956818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48183739185333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49603807926178</t>
+    <t xml:space="preserve">1.48183751106262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49603796005249</t>
   </si>
   <si>
     <t xml:space="preserve">1.50272023677826</t>
@@ -2036,19 +2036,19 @@
     <t xml:space="preserve">1.54448533058167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56369757652283</t>
+    <t xml:space="preserve">1.56369769573212</t>
   </si>
   <si>
     <t xml:space="preserve">1.53863847255707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54866242408752</t>
+    <t xml:space="preserve">1.54866254329681</t>
   </si>
   <si>
     <t xml:space="preserve">1.49186062812805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41668295860291</t>
+    <t xml:space="preserve">1.41668307781219</t>
   </si>
   <si>
     <t xml:space="preserve">1.39329493045807</t>
@@ -2063,10 +2063,10 @@
     <t xml:space="preserve">1.37491798400879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34818840026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33148181438446</t>
+    <t xml:space="preserve">1.34818828105927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33148193359375</t>
   </si>
   <si>
     <t xml:space="preserve">1.32814025878906</t>
@@ -2081,10 +2081,10 @@
     <t xml:space="preserve">1.30224633216858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33315229415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26549243927002</t>
+    <t xml:space="preserve">1.33315217494965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2654926776886</t>
   </si>
   <si>
     <t xml:space="preserve">1.24210357666016</t>
@@ -2093,43 +2093,43 @@
     <t xml:space="preserve">1.38995325565338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37074172496796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38494110107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38911855220795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37993025779724</t>
+    <t xml:space="preserve">1.37074160575867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3849413394928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38911843299866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37993001937866</t>
   </si>
   <si>
     <t xml:space="preserve">1.45260179042816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48852002620697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49687278270721</t>
+    <t xml:space="preserve">1.48851990699768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49687266349792</t>
   </si>
   <si>
     <t xml:space="preserve">1.50104892253876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.447589635849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39914178848267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5428147315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46095454692841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39162373542786</t>
+    <t xml:space="preserve">1.44758987426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39914166927338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54281485080719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4609546661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39162361621857</t>
   </si>
   <si>
     <t xml:space="preserve">1.41000056266785</t>
@@ -2138,22 +2138,22 @@
     <t xml:space="preserve">1.40833020210266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42921280860901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40749442577362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3339878320694</t>
+    <t xml:space="preserve">1.4292129278183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40749454498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33398795127869</t>
   </si>
   <si>
     <t xml:space="preserve">1.32563424110413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33732867240906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36155319213867</t>
+    <t xml:space="preserve">1.33732855319977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36155307292938</t>
   </si>
   <si>
     <t xml:space="preserve">1.36907041072845</t>
@@ -2165,31 +2165,31 @@
     <t xml:space="preserve">1.4350597858429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46596658229828</t>
+    <t xml:space="preserve">1.46596646308899</t>
   </si>
   <si>
     <t xml:space="preserve">1.47181344032288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46513092517853</t>
+    <t xml:space="preserve">1.46513104438782</t>
   </si>
   <si>
     <t xml:space="preserve">1.47264897823334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51190888881683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47014307975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4926962852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5227677822113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54030883312225</t>
+    <t xml:space="preserve">1.51190876960754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4701429605484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49269616603851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52276766300201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54030895233154</t>
   </si>
   <si>
     <t xml:space="preserve">1.53529667854309</t>
@@ -2207,13 +2207,13 @@
     <t xml:space="preserve">1.64555788040161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59293329715729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63219308853149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58458054065704</t>
+    <t xml:space="preserve">1.59293341636658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6321929693222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58458065986633</t>
   </si>
   <si>
     <t xml:space="preserve">1.56035614013672</t>
@@ -2225,10 +2225,10 @@
     <t xml:space="preserve">1.55868566036224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56620359420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56703841686249</t>
+    <t xml:space="preserve">1.56620383262634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56703853607178</t>
   </si>
   <si>
     <t xml:space="preserve">1.58708655834198</t>
@@ -2237,22 +2237,22 @@
     <t xml:space="preserve">1.64973425865173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74078297615051</t>
+    <t xml:space="preserve">1.74078285694122</t>
   </si>
   <si>
     <t xml:space="preserve">1.70737087726593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71906542778015</t>
+    <t xml:space="preserve">1.71906530857086</t>
   </si>
   <si>
     <t xml:space="preserve">1.72908842563629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71238279342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73243021965027</t>
+    <t xml:space="preserve">1.7123829126358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73243010044098</t>
   </si>
   <si>
     <t xml:space="preserve">1.69233477115631</t>
@@ -2261,40 +2261,40 @@
     <t xml:space="preserve">1.76584219932556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74913573265076</t>
+    <t xml:space="preserve">1.74913561344147</t>
   </si>
   <si>
     <t xml:space="preserve">1.72073566913605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63887560367584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60880410671234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68565225601196</t>
+    <t xml:space="preserve">1.63887548446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60880422592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68565249443054</t>
   </si>
   <si>
     <t xml:space="preserve">1.67061710357666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68732380867004</t>
+    <t xml:space="preserve">1.68732368946075</t>
   </si>
   <si>
     <t xml:space="preserve">1.67562913894653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68064117431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61715686321259</t>
+    <t xml:space="preserve">1.68064105510712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61715698242188</t>
   </si>
   <si>
     <t xml:space="preserve">1.61548662185669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62467503547668</t>
+    <t xml:space="preserve">1.62467515468597</t>
   </si>
   <si>
     <t xml:space="preserve">1.61047458648682</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">1.64054584503174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62383949756622</t>
+    <t xml:space="preserve">1.62383937835693</t>
   </si>
   <si>
     <t xml:space="preserve">1.60963988304138</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">1.59126305580139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56202733516693</t>
+    <t xml:space="preserve">1.56202745437622</t>
   </si>
   <si>
     <t xml:space="preserve">1.59209775924683</t>
@@ -2324,52 +2324,52 @@
     <t xml:space="preserve">1.59543931484222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58290910720825</t>
+    <t xml:space="preserve">1.58290934562683</t>
   </si>
   <si>
     <t xml:space="preserve">1.60379207134247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6004513502121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58541536331177</t>
+    <t xml:space="preserve">1.60045146942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58541524410248</t>
   </si>
   <si>
     <t xml:space="preserve">1.54532074928284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54699122905731</t>
+    <t xml:space="preserve">1.5469913482666</t>
   </si>
   <si>
     <t xml:space="preserve">1.57706248760223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43756556510925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49436676502228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48935544490814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46763706207275</t>
+    <t xml:space="preserve">1.43756568431854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49436664581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48935556411743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46763694286346</t>
   </si>
   <si>
     <t xml:space="preserve">1.51274347305298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52610850334167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53195595741272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54782676696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51691997051239</t>
+    <t xml:space="preserve">1.52610838413239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53195607662201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54782688617706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5169198513031</t>
   </si>
   <si>
     <t xml:space="preserve">1.50940275192261</t>
@@ -2381,13 +2381,13 @@
     <t xml:space="preserve">1.26465678215027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23208045959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18029069900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16692578792572</t>
+    <t xml:space="preserve">1.23208034038544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18029057979584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16692590713501</t>
   </si>
   <si>
     <t xml:space="preserve">1.13601982593536</t>
@@ -2396,25 +2396,25 @@
     <t xml:space="preserve">1.02742898464203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.933039784431458</t>
+    <t xml:space="preserve">0.933039665222168</t>
   </si>
   <si>
     <t xml:space="preserve">0.776836395263672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.719200670719147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.695811867713928</t>
+    <t xml:space="preserve">0.719200730323792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.695811808109283</t>
   </si>
   <si>
     <t xml:space="preserve">0.546709179878235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.613534212112427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519561290740967</t>
+    <t xml:space="preserve">0.613534152507782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519561231136322</t>
   </si>
   <si>
     <t xml:space="preserve">0.599333703517914</t>
@@ -2426,22 +2426,22 @@
     <t xml:space="preserve">0.725047469139099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.701658546924591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.637340426445007</t>
+    <t xml:space="preserve">0.701658606529236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.637340486049652</t>
   </si>
   <si>
     <t xml:space="preserve">0.682447016239166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.680358290672302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.687876343727112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.659893751144409</t>
+    <t xml:space="preserve">0.680358350276947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.687876403331757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.659893691539764</t>
   </si>
   <si>
     <t xml:space="preserve">0.643604576587677</t>
@@ -2450,16 +2450,16 @@
     <t xml:space="preserve">0.659475445747375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.64318722486496</t>
+    <t xml:space="preserve">0.643187284469604</t>
   </si>
   <si>
     <t xml:space="preserve">0.627316415309906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.576780557632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618127942085266</t>
+    <t xml:space="preserve">0.576780498027802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618128001689911</t>
   </si>
   <si>
     <t xml:space="preserve">0.660728454589844</t>
@@ -2474,13 +2474,13 @@
     <t xml:space="preserve">0.638175189495087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649869680404663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640263795852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612281203269958</t>
+    <t xml:space="preserve">0.649869620800018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640263855457306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612281143665314</t>
   </si>
   <si>
     <t xml:space="preserve">0.61562192440033</t>
@@ -2492,10 +2492,10 @@
     <t xml:space="preserve">0.6055988073349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61102819442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.651539981365204</t>
+    <t xml:space="preserve">0.611028134822845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.651540040969849</t>
   </si>
   <si>
     <t xml:space="preserve">0.676599323749542</t>
@@ -2504,19 +2504,19 @@
     <t xml:space="preserve">0.654881656169891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.642351627349854</t>
+    <t xml:space="preserve">0.642351567745209</t>
   </si>
   <si>
     <t xml:space="preserve">0.641516864299774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.655717372894287</t>
+    <t xml:space="preserve">0.655717313289642</t>
   </si>
   <si>
     <t xml:space="preserve">0.639846503734589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649034917354584</t>
+    <t xml:space="preserve">0.649034976959229</t>
   </si>
   <si>
     <t xml:space="preserve">0.668246507644653</t>
@@ -2525,7 +2525,7 @@
     <t xml:space="preserve">0.650286972522736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.626480758190155</t>
+    <t xml:space="preserve">0.6264808177948</t>
   </si>
   <si>
     <t xml:space="preserve">0.609775185585022</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">0.606016099452972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629822313785553</t>
+    <t xml:space="preserve">0.629822373390198</t>
   </si>
   <si>
     <t xml:space="preserve">0.596827805042267</t>
@@ -2549,19 +2549,19 @@
     <t xml:space="preserve">0.57427453994751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.601839661598206</t>
+    <t xml:space="preserve">0.601839780807495</t>
   </si>
   <si>
     <t xml:space="preserve">0.630658090114594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.726300477981567</t>
+    <t xml:space="preserve">0.726300418376923</t>
   </si>
   <si>
     <t xml:space="preserve">0.789366483688354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.763054251670837</t>
+    <t xml:space="preserve">0.763054192066193</t>
   </si>
   <si>
     <t xml:space="preserve">0.768483579158783</t>
@@ -2573,13 +2573,13 @@
     <t xml:space="preserve">0.83530855178833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.901298046112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910486400127411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00571143627167</t>
+    <t xml:space="preserve">0.901297986507416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.910486340522766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00571155548096</t>
   </si>
   <si>
     <t xml:space="preserve">1.01072347164154</t>
@@ -2597,31 +2597,31 @@
     <t xml:space="preserve">0.925521671772003</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938051581382751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922180891036987</t>
+    <t xml:space="preserve">0.938051700592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922180950641632</t>
   </si>
   <si>
     <t xml:space="preserve">0.892109513282776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.893779993057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895450294017792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823614180088043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781013667583466</t>
+    <t xml:space="preserve">0.893779933452606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895450353622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823614120483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78101372718811</t>
   </si>
   <si>
     <t xml:space="preserve">0.824867129325867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.806073009967804</t>
+    <t xml:space="preserve">0.806072950363159</t>
   </si>
   <si>
     <t xml:space="preserve">0.78560745716095</t>
@@ -2633,19 +2633,19 @@
     <t xml:space="preserve">0.797719240188599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801895678043365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798554956912994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776419103145599</t>
+    <t xml:space="preserve">0.801895618438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79855489730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776419043540955</t>
   </si>
   <si>
     <t xml:space="preserve">0.782266736030579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.766394913196564</t>
+    <t xml:space="preserve">0.766394972801208</t>
   </si>
   <si>
     <t xml:space="preserve">0.821525514125824</t>
@@ -2654,19 +2654,19 @@
     <t xml:space="preserve">0.795631527900696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.86370861530304</t>
+    <t xml:space="preserve">0.863708555698395</t>
   </si>
   <si>
     <t xml:space="preserve">0.855355799198151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.844496965408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857861816883087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.836143434047699</t>
+    <t xml:space="preserve">0.84449702501297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857861876487732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.836143374443054</t>
   </si>
   <si>
     <t xml:space="preserve">0.834890365600586</t>
@@ -2681,13 +2681,13 @@
     <t xml:space="preserve">0.773912966251373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.789783895015717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.771825313568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.767230629920959</t>
+    <t xml:space="preserve">0.789783835411072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77182525396347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767230570316315</t>
   </si>
   <si>
     <t xml:space="preserve">0.775583386421204</t>
@@ -2696,7 +2696,7 @@
     <t xml:space="preserve">0.786860466003418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.79270726442337</t>
+    <t xml:space="preserve">0.792707204818726</t>
   </si>
   <si>
     <t xml:space="preserve">0.758877754211426</t>
@@ -2720,10 +2720,10 @@
     <t xml:space="preserve">0.770989656448364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.740918338298798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.717947721481323</t>
+    <t xml:space="preserve">0.740918278694153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.717947661876678</t>
   </si>
   <si>
     <t xml:space="preserve">0.712099969387054</t>
@@ -2732,19 +2732,19 @@
     <t xml:space="preserve">0.684117317199707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.69079977273941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69288843870163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.685787677764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.674094200134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.666576147079468</t>
+    <t xml:space="preserve">0.690799832344055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.692888379096985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.685787796974182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.674094140529633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.666576087474823</t>
   </si>
   <si>
     <t xml:space="preserve">0.682029545307159</t>
@@ -2753,22 +2753,22 @@
     <t xml:space="preserve">0.687458992004395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.685370326042175</t>
+    <t xml:space="preserve">0.68537038564682</t>
   </si>
   <si>
     <t xml:space="preserve">0.67785233259201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.69455885887146</t>
+    <t xml:space="preserve">0.694558799266815</t>
   </si>
   <si>
     <t xml:space="preserve">0.697482168674469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.70374721288681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.698317766189575</t>
+    <t xml:space="preserve">0.703747272491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69831782579422</t>
   </si>
   <si>
     <t xml:space="preserve">0.721288442611694</t>
@@ -2783,16 +2783,16 @@
     <t xml:space="preserve">0.767647981643677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.718365132808685</t>
+    <t xml:space="preserve">0.718365073204041</t>
   </si>
   <si>
     <t xml:space="preserve">0.715024292469025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.78184849023819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.757207453250885</t>
+    <t xml:space="preserve">0.781848430633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.75720739364624</t>
   </si>
   <si>
     <t xml:space="preserve">0.778925061225891</t>
@@ -2801,7 +2801,7 @@
     <t xml:space="preserve">0.79646623134613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.825284600257874</t>
+    <t xml:space="preserve">0.825284540653229</t>
   </si>
   <si>
     <t xml:space="preserve">0.850343763828278</t>
@@ -2819,13 +2819,13 @@
     <t xml:space="preserve">0.843661367893219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.872062265872955</t>
+    <t xml:space="preserve">0.8720623254776</t>
   </si>
   <si>
     <t xml:space="preserve">0.852014243602753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.8545201420784</t>
+    <t xml:space="preserve">0.854520201683044</t>
   </si>
   <si>
     <t xml:space="preserve">0.812755346298218</t>
@@ -2840,31 +2840,31 @@
     <t xml:space="preserve">0.828626155853271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.832802593708038</t>
+    <t xml:space="preserve">0.832802534103394</t>
   </si>
   <si>
     <t xml:space="preserve">0.820690751075745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.749689400196075</t>
+    <t xml:space="preserve">0.749689340591431</t>
   </si>
   <si>
     <t xml:space="preserve">0.710846960544586</t>
   </si>
   <si>
-    <t xml:space="preserve">0.654464364051819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.63399875164032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.645275950431824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.660311102867126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.684534668922424</t>
+    <t xml:space="preserve">0.654464304447174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.633998811244965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.645275831222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.660311043262482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.684534728527069</t>
   </si>
   <si>
     <t xml:space="preserve">0.689129412174225</t>
@@ -2876,22 +2876,22 @@
     <t xml:space="preserve">0.784354448318481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.787696063518524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803148686885834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856191396713257</t>
+    <t xml:space="preserve">0.787696123123169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803148627281189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856191456317902</t>
   </si>
   <si>
     <t xml:space="preserve">0.845331728458405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.877073466777802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.90046226978302</t>
+    <t xml:space="preserve">0.877073407173157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.90046238899231</t>
   </si>
   <si>
     <t xml:space="preserve">0.889603495597839</t>
@@ -2900,19 +2900,19 @@
     <t xml:space="preserve">0.887097477912903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.89043915271759</t>
+    <t xml:space="preserve">0.890439212322235</t>
   </si>
   <si>
     <t xml:space="preserve">0.88125067949295</t>
   </si>
   <si>
-    <t xml:space="preserve">0.904638767242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89294421672821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902132749557495</t>
+    <t xml:space="preserve">0.904638826847076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892944276332855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.90213280916214</t>
   </si>
   <si>
     <t xml:space="preserve">0.88208544254303</t>
@@ -2927,10 +2927,10 @@
     <t xml:space="preserve">0.839484989643097</t>
   </si>
   <si>
-    <t xml:space="preserve">0.841990947723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840320587158203</t>
+    <t xml:space="preserve">0.841991007328033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840320527553558</t>
   </si>
   <si>
     <t xml:space="preserve">0.859532177448273</t>
@@ -2939,7 +2939,7 @@
     <t xml:space="preserve">0.905474364757538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.849508225917816</t>
+    <t xml:space="preserve">0.849508166313171</t>
   </si>
   <si>
     <t xml:space="preserve">0.872897028923035</t>
@@ -2948,28 +2948,28 @@
     <t xml:space="preserve">0.906310021877289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.943898379802704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95392256975174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957263290882111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965616881847382</t>
+    <t xml:space="preserve">0.943898558616638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95392245054245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957263231277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965616941452026</t>
   </si>
   <si>
     <t xml:space="preserve">0.978146135807037</t>
   </si>
   <si>
-    <t xml:space="preserve">0.961439669132233</t>
+    <t xml:space="preserve">0.961439609527588</t>
   </si>
   <si>
     <t xml:space="preserve">0.934710085391998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.902968406677246</t>
+    <t xml:space="preserve">0.902968347072601</t>
   </si>
   <si>
     <t xml:space="preserve">0.87456738948822</t>
@@ -2984,13 +2984,13 @@
     <t xml:space="preserve">0.878744721412659</t>
   </si>
   <si>
-    <t xml:space="preserve">0.907144784927368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931369304656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921345114707947</t>
+    <t xml:space="preserve">0.907144844532013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931369364261627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921345174312592</t>
   </si>
   <si>
     <t xml:space="preserve">0.927192032337189</t>
@@ -3002,13 +3002,13 @@
     <t xml:space="preserve">0.947240114212036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.899626731872559</t>
+    <t xml:space="preserve">0.899626791477203</t>
   </si>
   <si>
     <t xml:space="preserve">0.929697930812836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.93888658285141</t>
+    <t xml:space="preserve">0.93888646364212</t>
   </si>
   <si>
     <t xml:space="preserve">0.93721604347229</t>
@@ -3023,7 +3023,7 @@
     <t xml:space="preserve">0.94640451669693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.93554562330246</t>
+    <t xml:space="preserve">0.935545802116394</t>
   </si>
   <si>
     <t xml:space="preserve">0.975640118122101</t>
@@ -3032,16 +3032,16 @@
     <t xml:space="preserve">1.14687860012054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18947923183441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17360818386078</t>
+    <t xml:space="preserve">1.18947911262512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17360806465149</t>
   </si>
   <si>
     <t xml:space="preserve">1.16024339199066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15773737430573</t>
+    <t xml:space="preserve">1.15773725509644</t>
   </si>
   <si>
     <t xml:space="preserve">1.17193782329559</t>
@@ -3056,16 +3056,16 @@
     <t xml:space="preserve">1.11096048355103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1067841053009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11179542541504</t>
+    <t xml:space="preserve">1.10678398609161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11179530620575</t>
   </si>
   <si>
     <t xml:space="preserve">1.13100779056549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12098383903503</t>
+    <t xml:space="preserve">1.12098371982574</t>
   </si>
   <si>
     <t xml:space="preserve">1.16358518600464</t>
@@ -3077,37 +3077,37 @@
     <t xml:space="preserve">1.11513686180115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10761880874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37742400169373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37241208553314</t>
+    <t xml:space="preserve">1.10761892795563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37742388248444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37241184711456</t>
   </si>
   <si>
     <t xml:space="preserve">1.43923699855804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43673086166382</t>
+    <t xml:space="preserve">1.43673098087311</t>
   </si>
   <si>
     <t xml:space="preserve">1.44007158279419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40665984153748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41167163848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39747142791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43840134143829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47682535648346</t>
+    <t xml:space="preserve">1.40665972232819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41167175769806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39747130870819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43840146064758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47682523727417</t>
   </si>
   <si>
     <t xml:space="preserve">1.45928418636322</t>
@@ -3116,31 +3116,31 @@
     <t xml:space="preserve">1.44090747833252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43338942527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48100197315216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41334211826324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4258713722229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5879213809967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55033278465271</t>
+    <t xml:space="preserve">1.43338930606842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48100173473358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41334223747253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42587125301361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58792126178741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.550332903862</t>
   </si>
   <si>
     <t xml:space="preserve">1.62634551525116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61214601993561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62049877643585</t>
+    <t xml:space="preserve">1.61214590072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62049865722656</t>
   </si>
   <si>
     <t xml:space="preserve">1.61966288089752</t>
@@ -3149,10 +3149,10 @@
     <t xml:space="preserve">1.62718105316162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6138162612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45677828788757</t>
+    <t xml:space="preserve">1.61381614208221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45677816867828</t>
   </si>
   <si>
     <t xml:space="preserve">1.39830696582794</t>
@@ -3164,31 +3164,31 @@
     <t xml:space="preserve">1.3565411567688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35904729366302</t>
+    <t xml:space="preserve">1.35904705524445</t>
   </si>
   <si>
     <t xml:space="preserve">1.36489403247833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40276598930359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4346672296524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41251361370087</t>
+    <t xml:space="preserve">1.4027658700943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43466711044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41251349449158</t>
   </si>
   <si>
     <t xml:space="preserve">1.39390432834625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39213240146637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33364677429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4479593038559</t>
+    <t xml:space="preserve">1.39213216304779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3336466550827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44795918464661</t>
   </si>
   <si>
     <t xml:space="preserve">1.49049425125122</t>
@@ -3197,25 +3197,25 @@
     <t xml:space="preserve">1.51796472072601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53214287757874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58442544937134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52859854698181</t>
+    <t xml:space="preserve">1.53214299678802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58442533016205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52859842777252</t>
   </si>
   <si>
     <t xml:space="preserve">1.54897975921631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54454898834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53834593296051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55872738361359</t>
+    <t xml:space="preserve">1.54454910755157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5383460521698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55872714519501</t>
   </si>
   <si>
     <t xml:space="preserve">1.5764502286911</t>
@@ -3224,16 +3224,16 @@
     <t xml:space="preserve">1.6145544052124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60657894611359</t>
+    <t xml:space="preserve">1.60657906532288</t>
   </si>
   <si>
     <t xml:space="preserve">1.5693610906601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58885633945465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6039205789566</t>
+    <t xml:space="preserve">1.58885610103607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60392069816589</t>
   </si>
   <si>
     <t xml:space="preserve">1.63582181930542</t>
@@ -3242,7 +3242,7 @@
     <t xml:space="preserve">1.62518811225891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61278212070465</t>
+    <t xml:space="preserve">1.61278223991394</t>
   </si>
   <si>
     <t xml:space="preserve">1.58353924751282</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">1.50733089447021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50112807750702</t>
+    <t xml:space="preserve">1.50112783908844</t>
   </si>
   <si>
     <t xml:space="preserve">1.54011833667755</t>
@@ -3275,13 +3275,13 @@
     <t xml:space="preserve">1.53037071228027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55341053009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63848042488098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6632924079895</t>
+    <t xml:space="preserve">1.55341041088104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63848030567169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66329228878021</t>
   </si>
   <si>
     <t xml:space="preserve">1.56404411792755</t>
@@ -3293,34 +3293,34 @@
     <t xml:space="preserve">1.48872184753418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46568214893341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42403340339661</t>
+    <t xml:space="preserve">1.4656822681427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42403328418732</t>
   </si>
   <si>
     <t xml:space="preserve">1.44707322120667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46656823158264</t>
+    <t xml:space="preserve">1.46656835079193</t>
   </si>
   <si>
     <t xml:space="preserve">1.61809897422791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82900106906891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.846724152565</t>
+    <t xml:space="preserve">1.8290011882782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84672403335571</t>
   </si>
   <si>
     <t xml:space="preserve">1.90520966053009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89634823799133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98319041728973</t>
+    <t xml:space="preserve">1.89634811878204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98319053649902</t>
   </si>
   <si>
     <t xml:space="preserve">2.03635907173157</t>
@@ -3332,34 +3332,34 @@
     <t xml:space="preserve">2.17105293273926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96015048027039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88925898075104</t>
+    <t xml:space="preserve">1.96015059947968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88925909996033</t>
   </si>
   <si>
     <t xml:space="preserve">1.96192300319672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94597220420837</t>
+    <t xml:space="preserve">1.94597256183624</t>
   </si>
   <si>
     <t xml:space="preserve">2.01863622665405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10902285575867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07534909248352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10547828674316</t>
+    <t xml:space="preserve">2.10902261734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0753493309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10547804832458</t>
   </si>
   <si>
     <t xml:space="preserve">2.13737940788269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12674570083618</t>
+    <t xml:space="preserve">2.12674593925476</t>
   </si>
   <si>
     <t xml:space="preserve">2.17814183235168</t>
@@ -3383,7 +3383,7 @@
     <t xml:space="preserve">2.1232008934021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14624071121216</t>
+    <t xml:space="preserve">2.14624047279358</t>
   </si>
   <si>
     <t xml:space="preserve">2.19763731956482</t>
@@ -3395,25 +3395,25 @@
     <t xml:space="preserve">2.28625130653381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31992506980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34828186035156</t>
+    <t xml:space="preserve">2.31992483139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34828162193298</t>
   </si>
   <si>
     <t xml:space="preserve">2.41740083694458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44575762748718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38372778892517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46348023414612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42448997497559</t>
+    <t xml:space="preserve">2.4457573890686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38372755050659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46347999572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42449021339417</t>
   </si>
   <si>
     <t xml:space="preserve">2.47411394119263</t>
@@ -3425,13 +3425,13 @@
     <t xml:space="preserve">2.50955963134766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43157935142517</t>
+    <t xml:space="preserve">2.43157911300659</t>
   </si>
   <si>
     <t xml:space="preserve">2.4705696105957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39613318443298</t>
+    <t xml:space="preserve">2.39613342285156</t>
   </si>
   <si>
     <t xml:space="preserve">2.33942031860352</t>
@@ -3446,22 +3446,22 @@
     <t xml:space="preserve">2.38904428482056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47943115234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4918372631073</t>
+    <t xml:space="preserve">2.47943091392517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49183678627014</t>
   </si>
   <si>
     <t xml:space="preserve">2.56095623970032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65665984153748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64070916175842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63184785842896</t>
+    <t xml:space="preserve">2.6566596031189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64070892333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63184762001038</t>
   </si>
   <si>
     <t xml:space="preserve">2.65311527252197</t>
@@ -3479,28 +3479,28 @@
     <t xml:space="preserve">2.31815266609192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2968852519989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28270697593689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27561783790588</t>
+    <t xml:space="preserve">2.29688501358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28270673751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2756175994873</t>
   </si>
   <si>
     <t xml:space="preserve">2.25966715812683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30929136276245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27916264533997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28802394866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26852869987488</t>
+    <t xml:space="preserve">2.30929112434387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27916240692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28802371025085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2685284614563</t>
   </si>
   <si>
     <t xml:space="preserve">2.3660044670105</t>
@@ -3518,22 +3518,22 @@
     <t xml:space="preserve">2.16041922569275</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17459726333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13915181159973</t>
+    <t xml:space="preserve">2.17459750175476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13915157318115</t>
   </si>
   <si>
     <t xml:space="preserve">2.15687441825867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05762624740601</t>
+    <t xml:space="preserve">2.05762648582458</t>
   </si>
   <si>
     <t xml:space="preserve">2.16928029060364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1958646774292</t>
+    <t xml:space="preserve">2.19586491584778</t>
   </si>
   <si>
     <t xml:space="preserve">2.13560724258423</t>
@@ -3545,7 +3545,7 @@
     <t xml:space="preserve">2.39436101913452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06648802757263</t>
+    <t xml:space="preserve">2.06648826599121</t>
   </si>
   <si>
     <t xml:space="preserve">1.99382400512695</t>
@@ -3554,7 +3554,7 @@
     <t xml:space="preserve">2.12142848968506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11965656280518</t>
+    <t xml:space="preserve">2.1196563243866</t>
   </si>
   <si>
     <t xml:space="preserve">2.09484457969666</t>
@@ -3566,13 +3566,13 @@
     <t xml:space="preserve">2.08066630363464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9920517206192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03458690643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02926969528198</t>
+    <t xml:space="preserve">1.99205160140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03458666801453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02926993370056</t>
   </si>
   <si>
     <t xml:space="preserve">1.93179392814636</t>
@@ -3581,28 +3581,28 @@
     <t xml:space="preserve">2.01509141921997</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00445747375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86799156665802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9016649723053</t>
+    <t xml:space="preserve">2.00445771217346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86799168586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90166509151459</t>
   </si>
   <si>
     <t xml:space="preserve">1.80596160888672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64556956291199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56315815448761</t>
+    <t xml:space="preserve">1.6455694437027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56315803527832</t>
   </si>
   <si>
     <t xml:space="preserve">1.56847488880157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68012917041779</t>
+    <t xml:space="preserve">1.68012928962708</t>
   </si>
   <si>
     <t xml:space="preserve">1.5799947977066</t>
@@ -3614,19 +3614,19 @@
     <t xml:space="preserve">1.65974771976471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78646647930145</t>
+    <t xml:space="preserve">1.78646636009216</t>
   </si>
   <si>
     <t xml:space="preserve">1.75545120239258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73684215545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73418378829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70671331882477</t>
+    <t xml:space="preserve">1.73684227466583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73418390750885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70671343803406</t>
   </si>
   <si>
     <t xml:space="preserve">1.65088641643524</t>
@@ -3641,25 +3641,25 @@
     <t xml:space="preserve">1.72798085212708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86444711685181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83431828022003</t>
+    <t xml:space="preserve">1.8644472360611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83431804180145</t>
   </si>
   <si>
     <t xml:space="preserve">1.74570381641388</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78469407558441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76254045963287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7288670539856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67038154602051</t>
+    <t xml:space="preserve">1.78469395637512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76254034042358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72886693477631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67038142681122</t>
   </si>
   <si>
     <t xml:space="preserve">1.64113867282867</t>
@@ -3668,19 +3668,19 @@
     <t xml:space="preserve">1.60126233100891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61987102031708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71025800704956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70051050186157</t>
+    <t xml:space="preserve">1.61987125873566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71025812625885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70051038265228</t>
   </si>
   <si>
     <t xml:space="preserve">1.67835676670074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62961876392365</t>
+    <t xml:space="preserve">1.62961888313293</t>
   </si>
   <si>
     <t xml:space="preserve">1.63936650753021</t>
@@ -3689,70 +3689,70 @@
     <t xml:space="preserve">1.63050496578217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60923743247986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62075746059418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55075204372406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46302378177643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4789742231369</t>
+    <t xml:space="preserve">1.60923767089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62075757980347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55075216293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46302390098572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47897434234619</t>
   </si>
   <si>
     <t xml:space="preserve">1.5418906211853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60835146903992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58974230289459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64468336105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6074652671814</t>
+    <t xml:space="preserve">1.60835134983063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58974242210388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64468324184418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60746514797211</t>
   </si>
   <si>
     <t xml:space="preserve">1.6003760099411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52593994140625</t>
+    <t xml:space="preserve">1.52594006061554</t>
   </si>
   <si>
     <t xml:space="preserve">1.52150928974152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6313910484314</t>
+    <t xml:space="preserve">1.63139116764069</t>
   </si>
   <si>
     <t xml:space="preserve">1.64734160900116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72266411781311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.690762758255</t>
+    <t xml:space="preserve">1.72266399860382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69076263904572</t>
   </si>
   <si>
     <t xml:space="preserve">1.71646106243134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78114950656891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84495174884796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80773377418518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79887223243713</t>
+    <t xml:space="preserve">1.78114938735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84495186805725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80773365497589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79887235164642</t>
   </si>
   <si>
     <t xml:space="preserve">1.79532778263092</t>
@@ -3761,22 +3761,22 @@
     <t xml:space="preserve">1.65797555446625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45593452453613</t>
+    <t xml:space="preserve">1.45593476295471</t>
   </si>
   <si>
     <t xml:space="preserve">1.41871654987335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46506786346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47688293457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48960697650909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45779705047607</t>
+    <t xml:space="preserve">1.46506798267365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4768830537796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48960709571838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45779716968536</t>
   </si>
   <si>
     <t xml:space="preserve">1.47597420215607</t>
@@ -3791,10 +3791,10 @@
     <t xml:space="preserve">1.48142719268799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41417229175568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37236511707306</t>
+    <t xml:space="preserve">1.41417241096497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37236499786377</t>
   </si>
   <si>
     <t xml:space="preserve">1.37872695922852</t>
@@ -3815,7 +3815,7 @@
     <t xml:space="preserve">1.3859977722168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31510746479034</t>
+    <t xml:space="preserve">1.31510758399963</t>
   </si>
   <si>
     <t xml:space="preserve">1.28420662879944</t>
@@ -3827,7 +3827,7 @@
     <t xml:space="preserve">1.30874562263489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32692265510559</t>
+    <t xml:space="preserve">1.32692277431488</t>
   </si>
   <si>
     <t xml:space="preserve">1.39781284332275</t>
@@ -3845,7 +3845,7 @@
     <t xml:space="preserve">1.29693043231964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31328976154327</t>
+    <t xml:space="preserve">1.31328988075256</t>
   </si>
   <si>
     <t xml:space="preserve">1.33328461647034</t>
@@ -3863,10 +3863,10 @@
     <t xml:space="preserve">1.44416439533234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46961224079132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45961475372314</t>
+    <t xml:space="preserve">1.46961212158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45961463451385</t>
   </si>
   <si>
     <t xml:space="preserve">1.48778915405273</t>
@@ -3878,22 +3878,22 @@
     <t xml:space="preserve">1.48869800567627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51596367359161</t>
+    <t xml:space="preserve">1.51596355438232</t>
   </si>
   <si>
     <t xml:space="preserve">1.50505745410919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50051307678223</t>
+    <t xml:space="preserve">1.50051319599152</t>
   </si>
   <si>
     <t xml:space="preserve">1.48051834106445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40326607227325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43234920501709</t>
+    <t xml:space="preserve">1.40326619148254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43234932422638</t>
   </si>
   <si>
     <t xml:space="preserve">1.41144561767578</t>
@@ -3905,16 +3905,16 @@
     <t xml:space="preserve">1.34328186511993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37327408790588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3760005235672</t>
+    <t xml:space="preserve">1.37327396869659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37600064277649</t>
   </si>
   <si>
     <t xml:space="preserve">1.36236763000488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39235961437225</t>
+    <t xml:space="preserve">1.39235973358154</t>
   </si>
   <si>
     <t xml:space="preserve">1.33601117134094</t>
@@ -3923,22 +3923,22 @@
     <t xml:space="preserve">1.35237050056458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36963856220245</t>
+    <t xml:space="preserve">1.36963868141174</t>
   </si>
   <si>
     <t xml:space="preserve">1.35964131355286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41326332092285</t>
+    <t xml:space="preserve">1.41326344013214</t>
   </si>
   <si>
     <t xml:space="preserve">1.43507587909698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41689884662628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46870338916779</t>
+    <t xml:space="preserve">1.41689872741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4687032699585</t>
   </si>
   <si>
     <t xml:space="preserve">1.41235458850861</t>
@@ -3947,7 +3947,7 @@
     <t xml:space="preserve">1.39872181415558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70591342449188</t>
+    <t xml:space="preserve">1.70591354370117</t>
   </si>
   <si>
     <t xml:space="preserve">1.68591868877411</t>
@@ -3956,7 +3956,7 @@
     <t xml:space="preserve">1.58412742614746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57867431640625</t>
+    <t xml:space="preserve">1.57867419719696</t>
   </si>
   <si>
     <t xml:space="preserve">1.59139823913574</t>
@@ -3968,7 +3968,7 @@
     <t xml:space="preserve">1.49960434436798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55777072906494</t>
+    <t xml:space="preserve">1.55777060985565</t>
   </si>
   <si>
     <t xml:space="preserve">1.55231761932373</t>
@@ -3989,13 +3989,13 @@
     <t xml:space="preserve">1.56049728393555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53323173522949</t>
+    <t xml:space="preserve">1.53323185443878</t>
   </si>
   <si>
     <t xml:space="preserve">1.59503364562988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59412467479706</t>
+    <t xml:space="preserve">1.59412479400635</t>
   </si>
   <si>
     <t xml:space="preserve">1.64047610759735</t>
@@ -4016,13 +4016,13 @@
     <t xml:space="preserve">1.7631710767746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79225432872772</t>
+    <t xml:space="preserve">1.79225444793701</t>
   </si>
   <si>
     <t xml:space="preserve">1.78861892223358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73045265674591</t>
+    <t xml:space="preserve">1.73045253753662</t>
   </si>
   <si>
     <t xml:space="preserve">1.71772861480713</t>
@@ -4031,13 +4031,13 @@
     <t xml:space="preserve">1.72681701183319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77135062217712</t>
+    <t xml:space="preserve">1.77135074138641</t>
   </si>
   <si>
     <t xml:space="preserve">1.73136126995087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75135612487793</t>
+    <t xml:space="preserve">1.75135600566864</t>
   </si>
   <si>
     <t xml:space="preserve">1.78771007061005</t>
@@ -4067,7 +4067,7 @@
     <t xml:space="preserve">1.95402979850769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97038924694061</t>
+    <t xml:space="preserve">1.97038912773132</t>
   </si>
   <si>
     <t xml:space="preserve">2.00492548942566</t>
@@ -4082,7 +4082,7 @@
     <t xml:space="preserve">1.97402453422546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99038398265839</t>
+    <t xml:space="preserve">1.9903838634491</t>
   </si>
   <si>
     <t xml:space="preserve">2.04491519927979</t>
@@ -4115,7 +4115,7 @@
     <t xml:space="preserve">2.10126376152039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97584235668182</t>
+    <t xml:space="preserve">1.97584247589111</t>
   </si>
   <si>
     <t xml:space="preserve">2.02128481864929</t>
@@ -4124,37 +4124,37 @@
     <t xml:space="preserve">1.85223865509033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89041006565094</t>
+    <t xml:space="preserve">1.89041018486023</t>
   </si>
   <si>
     <t xml:space="preserve">1.91222286224365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92676424980164</t>
+    <t xml:space="preserve">1.92676413059235</t>
   </si>
   <si>
     <t xml:space="preserve">1.93585300445557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93948817253113</t>
+    <t xml:space="preserve">1.93948829174042</t>
   </si>
   <si>
     <t xml:space="preserve">1.90131652355194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91404032707214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96311855316162</t>
+    <t xml:space="preserve">1.91404020786285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96311843395233</t>
   </si>
   <si>
     <t xml:space="preserve">1.96857118606567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03219103813171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05945682525635</t>
+    <t xml:space="preserve">2.03219127655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05945658683777</t>
   </si>
   <si>
     <t xml:space="preserve">2.10489916801453</t>
@@ -4211,7 +4211,7 @@
     <t xml:space="preserve">2.3721010684967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41572618484497</t>
+    <t xml:space="preserve">2.41572642326355</t>
   </si>
   <si>
     <t xml:space="preserve">2.375736951828</t>
@@ -4223,22 +4223,22 @@
     <t xml:space="preserve">2.39754915237427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38846063613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39209580421448</t>
+    <t xml:space="preserve">2.3884608745575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39209604263306</t>
   </si>
   <si>
     <t xml:space="preserve">2.35755968093872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34483575820923</t>
+    <t xml:space="preserve">2.34483551979065</t>
   </si>
   <si>
     <t xml:space="preserve">2.30666422843933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31575274467468</t>
+    <t xml:space="preserve">2.3157525062561</t>
   </si>
   <si>
     <t xml:space="preserve">2.3357470035553</t>
@@ -4247,10 +4247,10 @@
     <t xml:space="preserve">2.33938264846802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38118982315063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40663743019104</t>
+    <t xml:space="preserve">2.38118958473206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40663766860962</t>
   </si>
   <si>
     <t xml:space="preserve">2.40481996536255</t>
@@ -4274,13 +4274,13 @@
     <t xml:space="preserve">2.23213839530945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18306040763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14307117462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20487260818481</t>
+    <t xml:space="preserve">2.18306016921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.143070936203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20487284660339</t>
   </si>
   <si>
     <t xml:space="preserve">2.20669031143188</t>
@@ -4295,25 +4295,25 @@
     <t xml:space="preserve">2.14670634269714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14852380752563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19578409194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19033145904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26849246025085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24667978286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24304437637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25213289260864</t>
+    <t xml:space="preserve">2.14852404594421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19578433036804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19033122062683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26849222183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24667954444885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24304461479187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25213313102722</t>
   </si>
   <si>
     <t xml:space="preserve">2.30121111869812</t>
@@ -4331,22 +4331,22 @@
     <t xml:space="preserve">2.44844484329224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48843431472778</t>
+    <t xml:space="preserve">2.4884340763092</t>
   </si>
   <si>
     <t xml:space="preserve">2.46843934059143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47207498550415</t>
+    <t xml:space="preserve">2.47207522392273</t>
   </si>
   <si>
     <t xml:space="preserve">2.45935130119324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45753312110901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43390321731567</t>
+    <t xml:space="preserve">2.45753335952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43390345573425</t>
   </si>
   <si>
     <t xml:space="preserve">2.51388216018677</t>
@@ -4358,7 +4358,7 @@
     <t xml:space="preserve">2.50297594070435</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47025728225708</t>
+    <t xml:space="preserve">2.4702570438385</t>
   </si>
   <si>
     <t xml:space="preserve">2.40118455886841</t>
@@ -4373,19 +4373,19 @@
     <t xml:space="preserve">2.2793984413147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28485131263733</t>
+    <t xml:space="preserve">2.28485155105591</t>
   </si>
   <si>
     <t xml:space="preserve">2.29212260246277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27030968666077</t>
+    <t xml:space="preserve">2.27030992507935</t>
   </si>
   <si>
     <t xml:space="preserve">2.22668528556824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30302834510803</t>
+    <t xml:space="preserve">2.30302858352661</t>
   </si>
   <si>
     <t xml:space="preserve">2.32484126091003</t>
@@ -4394,10 +4394,10 @@
     <t xml:space="preserve">2.33029413223267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29939293861389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41936159133911</t>
+    <t xml:space="preserve">2.29939317703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41936135292053</t>
   </si>
   <si>
     <t xml:space="preserve">2.4320855140686</t>
@@ -4415,16 +4415,16 @@
     <t xml:space="preserve">2.28207540512085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27462363243103</t>
+    <t xml:space="preserve">2.27462339401245</t>
   </si>
   <si>
     <t xml:space="preserve">2.24854278564453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22991347312927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30070447921753</t>
+    <t xml:space="preserve">2.22991371154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30070471763611</t>
   </si>
   <si>
     <t xml:space="preserve">2.31188225746155</t>
@@ -4442,7 +4442,7 @@
     <t xml:space="preserve">2.29697895050049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32678508758545</t>
+    <t xml:space="preserve">2.32678532600403</t>
   </si>
   <si>
     <t xml:space="preserve">2.34168863296509</t>
@@ -4454,13 +4454,13 @@
     <t xml:space="preserve">2.36963248252869</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36776971817017</t>
+    <t xml:space="preserve">2.36776947975159</t>
   </si>
   <si>
     <t xml:space="preserve">2.32864832878113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29884147644043</t>
+    <t xml:space="preserve">2.29884171485901</t>
   </si>
   <si>
     <t xml:space="preserve">2.28580117225647</t>
@@ -4469,7 +4469,7 @@
     <t xml:space="preserve">2.28021216392517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29511570930481</t>
+    <t xml:space="preserve">2.29511594772339</t>
   </si>
   <si>
     <t xml:space="preserve">2.30443024635315</t>
@@ -4478,25 +4478,25 @@
     <t xml:space="preserve">2.29325270652771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33051133155823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31374478340149</t>
+    <t xml:space="preserve">2.33051109313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31374502182007</t>
   </si>
   <si>
     <t xml:space="preserve">2.28952693939209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22432470321655</t>
+    <t xml:space="preserve">2.22432494163513</t>
   </si>
   <si>
     <t xml:space="preserve">2.20569562911987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16098570823669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14049339294434</t>
+    <t xml:space="preserve">2.16098546981812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14049363136292</t>
   </si>
   <si>
     <t xml:space="preserve">2.1069610118866</t>
@@ -4505,19 +4505,19 @@
     <t xml:space="preserve">2.09950923919678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12559008598328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1088240146637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09019470214844</t>
+    <t xml:space="preserve">2.12559032440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10882377624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09019446372986</t>
   </si>
   <si>
     <t xml:space="preserve">2.0585253238678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04362154006958</t>
+    <t xml:space="preserve">2.04362177848816</t>
   </si>
   <si>
     <t xml:space="preserve">2.04921054840088</t>
@@ -4526,22 +4526,22 @@
     <t xml:space="preserve">2.08460593223572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06411409378052</t>
+    <t xml:space="preserve">2.06411385536194</t>
   </si>
   <si>
     <t xml:space="preserve">2.0510733127594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04175853729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09205770492554</t>
+    <t xml:space="preserve">2.04175877571106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09205746650696</t>
   </si>
   <si>
     <t xml:space="preserve">2.15912270545959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1535336971283</t>
+    <t xml:space="preserve">2.15353393554688</t>
   </si>
   <si>
     <t xml:space="preserve">2.13863062858582</t>
@@ -4550,40 +4550,40 @@
     <t xml:space="preserve">2.12186455726624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06970238685608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0231294631958</t>
+    <t xml:space="preserve">2.06970262527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02312970161438</t>
   </si>
   <si>
     <t xml:space="preserve">2.01754069328308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99891173839569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01195240020752</t>
+    <t xml:space="preserve">1.9989116191864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01195216178894</t>
   </si>
   <si>
     <t xml:space="preserve">2.0007746219635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99332296848297</t>
+    <t xml:space="preserve">1.99332284927368</t>
   </si>
   <si>
     <t xml:space="preserve">1.97469365596771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95606434345245</t>
+    <t xml:space="preserve">1.95606446266174</t>
   </si>
   <si>
     <t xml:space="preserve">1.92625796794891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.864781498909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77349853515625</t>
+    <t xml:space="preserve">1.86478161811829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77349865436554</t>
   </si>
   <si>
     <t xml:space="preserve">1.78095018863678</t>
@@ -4601,7 +4601,7 @@
     <t xml:space="preserve">1.80237364768982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75673234462738</t>
+    <t xml:space="preserve">1.75673222541809</t>
   </si>
   <si>
     <t xml:space="preserve">1.71109080314636</t>
@@ -4610,10 +4610,10 @@
     <t xml:space="preserve">1.70829629898071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71947395801544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67196941375732</t>
+    <t xml:space="preserve">1.71947383880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67196929454803</t>
   </si>
   <si>
     <t xml:space="preserve">1.69991326332092</t>
@@ -4625,16 +4625,16 @@
     <t xml:space="preserve">1.61608195304871</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63005387783051</t>
+    <t xml:space="preserve">1.63005375862122</t>
   </si>
   <si>
     <t xml:space="preserve">1.63377952575684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63564264774323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64775156974792</t>
+    <t xml:space="preserve">1.63564252853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64775168895721</t>
   </si>
   <si>
     <t xml:space="preserve">1.64682006835938</t>
@@ -4646,10 +4646,10 @@
     <t xml:space="preserve">1.54994833469391</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53877079486847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54529106616974</t>
+    <t xml:space="preserve">1.53877067565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54529094696045</t>
   </si>
   <si>
     <t xml:space="preserve">1.54249668121338</t>
@@ -4658,10 +4658,10 @@
     <t xml:space="preserve">1.55087971687317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55646848678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56485164165497</t>
+    <t xml:space="preserve">1.55646860599518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56485152244568</t>
   </si>
   <si>
     <t xml:space="preserve">1.57975494861603</t>
@@ -4685,7 +4685,7 @@
     <t xml:space="preserve">1.59745287895203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61235594749451</t>
+    <t xml:space="preserve">1.6123560667038</t>
   </si>
   <si>
     <t xml:space="preserve">1.62073922157288</t>
@@ -4694,16 +4694,16 @@
     <t xml:space="preserve">1.67755818367004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64123129844666</t>
+    <t xml:space="preserve">1.64123141765594</t>
   </si>
   <si>
     <t xml:space="preserve">1.65706610679626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68966710567474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69153010845184</t>
+    <t xml:space="preserve">1.68966722488403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69153022766113</t>
   </si>
   <si>
     <t xml:space="preserve">1.66917514801025</t>
@@ -4718,16 +4718,16 @@
     <t xml:space="preserve">1.69059872627258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72785699367523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8424266576767</t>
+    <t xml:space="preserve">1.72785711288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84242653846741</t>
   </si>
   <si>
     <t xml:space="preserve">1.84801530838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90390276908875</t>
+    <t xml:space="preserve">1.90390264987946</t>
   </si>
   <si>
     <t xml:space="preserve">1.92998361587524</t>
@@ -4745,10 +4745,10 @@
     <t xml:space="preserve">1.93557250499725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90949153900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91135454177856</t>
+    <t xml:space="preserve">1.90949165821075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91135466098785</t>
   </si>
   <si>
     <t xml:space="preserve">1.88899958133698</t>
@@ -4772,7 +4772,7 @@
     <t xml:space="preserve">2.12000155448914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11441254615784</t>
+    <t xml:space="preserve">2.11441278457642</t>
   </si>
   <si>
     <t xml:space="preserve">2.10137224197388</t>
@@ -4781,10 +4781,10 @@
     <t xml:space="preserve">2.03617024421692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0026376247406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98028242588043</t>
+    <t xml:space="preserve">2.00263738632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98028230667114</t>
   </si>
   <si>
     <t xml:space="preserve">2.01008915901184</t>
@@ -4820,13 +4820,13 @@
     <t xml:space="preserve">2.0752911567688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09578371047974</t>
+    <t xml:space="preserve">2.09578347206116</t>
   </si>
   <si>
     <t xml:space="preserve">2.11813831329346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07715439796448</t>
+    <t xml:space="preserve">2.0771541595459</t>
   </si>
   <si>
     <t xml:space="preserve">2.08281922340393</t>
@@ -4838,7 +4838,7 @@
     <t xml:space="preserve">2.05827116966248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07148909568787</t>
+    <t xml:space="preserve">2.07148933410645</t>
   </si>
   <si>
     <t xml:space="preserve">2.12813878059387</t>
@@ -4859,7 +4859,7 @@
     <t xml:space="preserve">2.08093070983887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14135718345642</t>
+    <t xml:space="preserve">2.14135694503784</t>
   </si>
   <si>
     <t xml:space="preserve">2.10170245170593</t>
@@ -4871,7 +4871,7 @@
     <t xml:space="preserve">2.06771278381348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09981393814087</t>
+    <t xml:space="preserve">2.09981417655945</t>
   </si>
   <si>
     <t xml:space="preserve">2.15835213661194</t>
@@ -4901,13 +4901,13 @@
     <t xml:space="preserve">2.24143815040588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33396601676941</t>
+    <t xml:space="preserve">2.33396577835083</t>
   </si>
   <si>
     <t xml:space="preserve">2.32263612747192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22255492210388</t>
+    <t xml:space="preserve">2.22255516052246</t>
   </si>
   <si>
     <t xml:space="preserve">2.14702200889587</t>
@@ -4922,7 +4922,7 @@
     <t xml:space="preserve">2.09414911270142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04882955551147</t>
+    <t xml:space="preserve">2.0488293170929</t>
   </si>
   <si>
     <t xml:space="preserve">2.19989514350891</t>
@@ -4931,13 +4931,13 @@
     <t xml:space="preserve">2.2471034526825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31130599975586</t>
+    <t xml:space="preserve">2.31130623817444</t>
   </si>
   <si>
     <t xml:space="preserve">2.33207774162292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29431128501892</t>
+    <t xml:space="preserve">2.2943115234375</t>
   </si>
   <si>
     <t xml:space="preserve">2.35662579536438</t>
@@ -4955,13 +4955,13 @@
     <t xml:space="preserve">2.36040258407593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37550902366638</t>
+    <t xml:space="preserve">2.37550926208496</t>
   </si>
   <si>
     <t xml:space="preserve">2.41705203056335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46237182617188</t>
+    <t xml:space="preserve">2.46237206459045</t>
   </si>
   <si>
     <t xml:space="preserve">2.44160032272339</t>
@@ -4970,13 +4970,13 @@
     <t xml:space="preserve">2.46992492675781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48692035675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50202679634094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5265748500824</t>
+    <t xml:space="preserve">2.48692011833191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50202655792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52657508850098</t>
   </si>
   <si>
     <t xml:space="preserve">2.54168128967285</t>
@@ -4991,7 +4991,7 @@
     <t xml:space="preserve">2.50957989692688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5548996925354</t>
+    <t xml:space="preserve">2.55489993095398</t>
   </si>
   <si>
     <t xml:space="preserve">2.56811785697937</t>
@@ -5006,19 +5006,19 @@
     <t xml:space="preserve">2.70407724380493</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66442251205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64553928375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63798594474792</t>
+    <t xml:space="preserve">2.66442227363586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64553904533386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63798570632935</t>
   </si>
   <si>
     <t xml:space="preserve">2.63609766960144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70218873023987</t>
+    <t xml:space="preserve">2.70218896865845</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309238433838</t>
@@ -5039,7 +5039,7 @@
     <t xml:space="preserve">2.60210776329041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55867624282837</t>
+    <t xml:space="preserve">2.55867648124695</t>
   </si>
   <si>
     <t xml:space="preserve">2.60882019996643</t>
@@ -5937,6 +5937,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.48000001907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44799995422363</t>
   </si>
 </sst>
 </file>
@@ -20125,7 +20128,7 @@
         <v>5.6275200843811</v>
       </c>
       <c r="G533" t="s">
-        <v>260</v>
+        <v>363</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -20203,7 +20206,7 @@
         <v>5.40128803253174</v>
       </c>
       <c r="G536" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -20229,7 +20232,7 @@
         <v>5.28817176818848</v>
       </c>
       <c r="G537" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -20333,7 +20336,7 @@
         <v>5.19862222671509</v>
       </c>
       <c r="G541" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -20359,7 +20362,7 @@
         <v>5.18448209762573</v>
       </c>
       <c r="G542" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -20385,7 +20388,7 @@
         <v>5.20804786682129</v>
       </c>
       <c r="G543" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -20411,7 +20414,7 @@
         <v>5.22690105438232</v>
       </c>
       <c r="G544" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -20437,7 +20440,7 @@
         <v>5.31173801422119</v>
       </c>
       <c r="G545" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -20489,7 +20492,7 @@
         <v>5.17505598068237</v>
       </c>
       <c r="G547" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -20515,7 +20518,7 @@
         <v>5.13735103607178</v>
       </c>
       <c r="G548" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -20541,7 +20544,7 @@
         <v>5.13735103607178</v>
       </c>
       <c r="G549" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -20567,7 +20570,7 @@
         <v>5.12321090698242</v>
       </c>
       <c r="G550" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -20593,7 +20596,7 @@
         <v>5.19862222671509</v>
       </c>
       <c r="G551" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -20619,7 +20622,7 @@
         <v>5.16562986373901</v>
       </c>
       <c r="G552" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -20645,7 +20648,7 @@
         <v>5.06665277481079</v>
       </c>
       <c r="G553" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -20671,7 +20674,7 @@
         <v>4.9771032333374</v>
       </c>
       <c r="G554" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -20697,7 +20700,7 @@
         <v>5.014808177948</v>
       </c>
       <c r="G555" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -20723,7 +20726,7 @@
         <v>5.07136583328247</v>
       </c>
       <c r="G556" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -20749,7 +20752,7 @@
         <v>5.04780006408691</v>
       </c>
       <c r="G557" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -20775,7 +20778,7 @@
         <v>5.09964513778687</v>
       </c>
       <c r="G558" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -20801,7 +20804,7 @@
         <v>5.15620279312134</v>
       </c>
       <c r="G559" t="s">
-        <v>380</v>
+        <v>77</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -20827,7 +20830,7 @@
         <v>5.12321090698242</v>
       </c>
       <c r="G560" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -20983,7 +20986,7 @@
         <v>5.16562986373901</v>
       </c>
       <c r="G566" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -21009,7 +21012,7 @@
         <v>5.19862222671509</v>
       </c>
       <c r="G567" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -71509,7 +71512,7 @@
     </row>
     <row r="2510">
       <c r="A2510" s="1" t="n">
-        <v>45973.6912152778</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B2510" t="n">
         <v>700435</v>
@@ -71530,6 +71533,32 @@
         <v>1974</v>
       </c>
       <c r="H2510" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" s="1" t="n">
+        <v>45974.691087963</v>
+      </c>
+      <c r="B2511" t="n">
+        <v>625473</v>
+      </c>
+      <c r="C2511" t="n">
+        <v>4.51599979400635</v>
+      </c>
+      <c r="D2511" t="n">
+        <v>4.41599988937378</v>
+      </c>
+      <c r="E2511" t="n">
+        <v>4.50400018692017</v>
+      </c>
+      <c r="F2511" t="n">
+        <v>4.44799995422363</v>
+      </c>
+      <c r="G2511" t="s">
+        <v>1975</v>
+      </c>
+      <c r="H2511" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/OVS.MI.xlsx
+++ b/data/OVS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1978" uniqueCount="1978">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1979" uniqueCount="1979">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,22 +47,22 @@
     <t xml:space="preserve">4.89862442016602</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76365375518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64456224441528</t>
+    <t xml:space="preserve">4.76365423202515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64456272125244</t>
   </si>
   <si>
     <t xml:space="preserve">4.71998643875122</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65647077560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78747224807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94229030609131</t>
+    <t xml:space="preserve">4.65647125244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78747177124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94228982925415</t>
   </si>
   <si>
     <t xml:space="preserve">4.69219923019409</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">4.63662338256836</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61677503585815</t>
+    <t xml:space="preserve">4.616774559021</t>
   </si>
   <si>
     <t xml:space="preserve">4.2515606880188</t>
@@ -83,19 +83,19 @@
     <t xml:space="preserve">4.22774219512939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53341054916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45798587799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47783470153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49768304824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51356172561646</t>
+    <t xml:space="preserve">4.53341007232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45798492431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47783422470093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49768352508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5135612487793</t>
   </si>
   <si>
     <t xml:space="preserve">4.4460768699646</t>
@@ -107,43 +107,43 @@
     <t xml:space="preserve">4.59295654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5175313949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5453200340271</t>
+    <t xml:space="preserve">4.51753187179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54531955718994</t>
   </si>
   <si>
     <t xml:space="preserve">4.32698583602905</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03322649002075</t>
+    <t xml:space="preserve">4.03322601318359</t>
   </si>
   <si>
     <t xml:space="preserve">4.02925729751587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27934980392456</t>
+    <t xml:space="preserve">4.2793493270874</t>
   </si>
   <si>
     <t xml:space="preserve">4.22377252578735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38256072998047</t>
+    <t xml:space="preserve">4.38256025314331</t>
   </si>
   <si>
     <t xml:space="preserve">4.30316781997681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46989488601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46592473983765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48577356338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48974275588989</t>
+    <t xml:space="preserve">4.469895362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46592426300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48577404022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48974323272705</t>
   </si>
   <si>
     <t xml:space="preserve">4.271409034729</t>
@@ -152,10 +152,10 @@
     <t xml:space="preserve">4.23965167999268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43813753128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56516790390015</t>
+    <t xml:space="preserve">4.43813705444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5651683807373</t>
   </si>
   <si>
     <t xml:space="preserve">4.67235040664673</t>
@@ -164,34 +164,34 @@
     <t xml:space="preserve">4.71601724624634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58898687362671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50562286376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52547121047974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38653087615967</t>
+    <t xml:space="preserve">4.58898639678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50562238693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52547073364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38653135299683</t>
   </si>
   <si>
     <t xml:space="preserve">4.43019771575928</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40241003036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29125833511353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12056064605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09674263000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06498527526855</t>
+    <t xml:space="preserve">4.40241050720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29125785827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12056016921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09674167633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0649847984314</t>
   </si>
   <si>
     <t xml:space="preserve">4.08880281448364</t>
@@ -200,109 +200,109 @@
     <t xml:space="preserve">4.15628719329834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21186447143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04910564422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02131843566895</t>
+    <t xml:space="preserve">4.21186399459839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04910612106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02131748199463</t>
   </si>
   <si>
     <t xml:space="preserve">4.31110620498657</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16422748565674</t>
+    <t xml:space="preserve">4.16422700881958</t>
   </si>
   <si>
     <t xml:space="preserve">4.23568201065063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50959253311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7358660697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54928970336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50165319442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56119775772095</t>
+    <t xml:space="preserve">4.50959205627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73586559295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54928922653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50165176391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56119823455811</t>
   </si>
   <si>
     <t xml:space="preserve">4.48180389404297</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52150106430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55325889587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54135036468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56913757324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5373797416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64853191375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7041072845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84304761886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89068365097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81525945663452</t>
+    <t xml:space="preserve">4.5215015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55325841903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5413498878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56913805007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53737926483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64853096008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70410776138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84304714202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89068412780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81525993347168</t>
   </si>
   <si>
     <t xml:space="preserve">4.87877559661865</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91053295135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75968456268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73826885223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76678705215454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90123510360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73419427871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5671534538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51826286315918</t>
+    <t xml:space="preserve">4.91053342819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75968360900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73826837539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7667875289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90123462677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7341947555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56715297698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51826333999634</t>
   </si>
   <si>
     <t xml:space="preserve">4.4734468460083</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47752094268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48974370956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63233947753906</t>
+    <t xml:space="preserve">4.47752046585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48974418640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6323390007019</t>
   </si>
   <si>
     <t xml:space="preserve">4.61196899414062</t>
@@ -314,10 +314,10 @@
     <t xml:space="preserve">4.51418924331665</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33085107803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9470636844635</t>
+    <t xml:space="preserve">4.33085060119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94706320762634</t>
   </si>
   <si>
     <t xml:space="preserve">4.13529014587402</t>
@@ -326,16 +326,16 @@
     <t xml:space="preserve">4.24529314041138</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26566362380981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30233192443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25751495361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11084413528442</t>
+    <t xml:space="preserve">4.26566314697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30233144760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2575159072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11084461212158</t>
   </si>
   <si>
     <t xml:space="preserve">4.09047365188599</t>
@@ -344,10 +344,10 @@
     <t xml:space="preserve">4.05299139022827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18825387954712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16380929946899</t>
+    <t xml:space="preserve">4.18825340270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16380882263184</t>
   </si>
   <si>
     <t xml:space="preserve">4.15566062927246</t>
@@ -356,22 +356,22 @@
     <t xml:space="preserve">4.15973472595215</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10677051544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04321432113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11899375915527</t>
+    <t xml:space="preserve">4.10677099227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04321384429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11899280548096</t>
   </si>
   <si>
     <t xml:space="preserve">4.16788339614868</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26158952713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2004771232605</t>
+    <t xml:space="preserve">4.26158905029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20047664642334</t>
   </si>
   <si>
     <t xml:space="preserve">4.20862531661987</t>
@@ -383,25 +383,25 @@
     <t xml:space="preserve">4.37159299850464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36751842498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28603458404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27788639068604</t>
+    <t xml:space="preserve">4.36751890182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28603410720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27788591384888</t>
   </si>
   <si>
     <t xml:space="preserve">4.24121856689453</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25344133377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29825782775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22899627685547</t>
+    <t xml:space="preserve">4.25344085693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29825735092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22899580001831</t>
   </si>
   <si>
     <t xml:space="preserve">4.07254695892334</t>
@@ -416,46 +416,46 @@
     <t xml:space="preserve">4.10269737243652</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04158401489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13936424255371</t>
+    <t xml:space="preserve">4.04158353805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13936328887939</t>
   </si>
   <si>
     <t xml:space="preserve">4.09862279891968</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00084257125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99269390106201</t>
+    <t xml:space="preserve">4.00084209442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99269342422485</t>
   </si>
   <si>
     <t xml:space="preserve">4.0334358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19640254974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15158700942993</t>
+    <t xml:space="preserve">4.19640302658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15158653259277</t>
   </si>
   <si>
     <t xml:space="preserve">4.08640003204346</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0611400604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35936975479126</t>
+    <t xml:space="preserve">4.06114053726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3593692779541</t>
   </si>
   <si>
     <t xml:space="preserve">4.37566709518433</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44085359573364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41233396530151</t>
+    <t xml:space="preserve">4.44085454940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41233348846436</t>
   </si>
   <si>
     <t xml:space="preserve">4.31862831115723</t>
@@ -464,52 +464,52 @@
     <t xml:space="preserve">4.31047964096069</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31455421447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26973819732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21677398681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18010663986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1434383392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11491870880127</t>
+    <t xml:space="preserve">4.31455278396606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26973724365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21677303314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1801061630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14343786239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11491823196411</t>
   </si>
   <si>
     <t xml:space="preserve">4.07417774200439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06928825378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08232593536377</t>
+    <t xml:space="preserve">4.06928873062134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08232545852661</t>
   </si>
   <si>
     <t xml:space="preserve">4.06439971923828</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00573062896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96010041236877</t>
+    <t xml:space="preserve">4.00573110580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96009993553162</t>
   </si>
   <si>
     <t xml:space="preserve">4.05462074279785</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13121652603149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04647254943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98128509521484</t>
+    <t xml:space="preserve">4.13121557235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04647302627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.981285572052</t>
   </si>
   <si>
     <t xml:space="preserve">4.00410175323486</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">4.02528810501099</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97476696968079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02365732192993</t>
+    <t xml:space="preserve">3.97476744651794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02365779876709</t>
   </si>
   <si>
     <t xml:space="preserve">4.05951023101807</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04810190200806</t>
+    <t xml:space="preserve">4.04810237884521</t>
   </si>
   <si>
     <t xml:space="preserve">4.05136156082153</t>
@@ -545,94 +545,94 @@
     <t xml:space="preserve">4.02039813995361</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99921202659607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07825183868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1475133895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23714399337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20455121994019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22492265701294</t>
+    <t xml:space="preserve">3.99921226501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07825136184692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14751291275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23714351654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20455026626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22492218017578</t>
   </si>
   <si>
     <t xml:space="preserve">4.01713848114014</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02202749252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93076658248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91283988952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89491319656372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87535762786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94054460525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93402552604675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89654350280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95521116256714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00247192382812</t>
+    <t xml:space="preserve">4.02202796936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93076610565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91284012794495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89491295814514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87535715103149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94054436683655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93402576446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8965437412262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95521140098572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00247144699097</t>
   </si>
   <si>
     <t xml:space="preserve">4.37974071502686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38381433486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39196395874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35529518127441</t>
+    <t xml:space="preserve">4.38381481170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39196348190308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35529565811157</t>
   </si>
   <si>
     <t xml:space="preserve">4.2901086807251</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28196048736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32677698135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2941837310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33899879455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33492422103882</t>
+    <t xml:space="preserve">4.28196001052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32677602767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29418325424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33899831771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33492469787598</t>
   </si>
   <si>
     <t xml:space="preserve">4.34307336807251</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46529912948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48159551620483</t>
+    <t xml:space="preserve">4.46529865264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48159503936768</t>
   </si>
   <si>
     <t xml:space="preserve">4.40826034545898</t>
@@ -641,37 +641,37 @@
     <t xml:space="preserve">4.53863382339478</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55493068695068</t>
+    <t xml:space="preserve">4.55493021011353</t>
   </si>
   <si>
     <t xml:space="preserve">4.52641105651855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50604009628296</t>
+    <t xml:space="preserve">4.50604057312012</t>
   </si>
   <si>
     <t xml:space="preserve">4.43270492553711</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59567260742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68530416488647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67308139801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60382032394409</t>
+    <t xml:space="preserve">4.59567213058472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68530464172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6730809211731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60382080078125</t>
   </si>
   <si>
     <t xml:space="preserve">4.70160055160522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85641956329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82382583618164</t>
+    <t xml:space="preserve">4.85642004013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8238263130188</t>
   </si>
   <si>
     <t xml:space="preserve">4.77493572235107</t>
@@ -680,76 +680,76 @@
     <t xml:space="preserve">4.79938077926636</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74234294891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78308439254761</t>
+    <t xml:space="preserve">4.74234247207642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78308486938477</t>
   </si>
   <si>
     <t xml:space="preserve">4.72604560852051</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7790093421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80752992630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86456775665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04790592193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01531219482422</t>
+    <t xml:space="preserve">4.77901029586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80752944946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86456823348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04790544509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01531267166138</t>
   </si>
   <si>
     <t xml:space="preserve">4.89716100692749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91753149032593</t>
+    <t xml:space="preserve">4.91753196716309</t>
   </si>
   <si>
     <t xml:space="preserve">4.88901329040527</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04383182525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90531015396118</t>
+    <t xml:space="preserve">5.04383087158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90530967712402</t>
   </si>
   <si>
     <t xml:space="preserve">4.9501256942749</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05198049545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97864532470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03160905838013</t>
+    <t xml:space="preserve">5.05198097229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97864484786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03160953521729</t>
   </si>
   <si>
     <t xml:space="preserve">5.08457374572754</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23939228057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19865036010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14568519592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19457530975342</t>
+    <t xml:space="preserve">5.2393913269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19864988327026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14568614959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19457626342773</t>
   </si>
   <si>
     <t xml:space="preserve">5.05605459213257</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06420230865479</t>
+    <t xml:space="preserve">5.0642032623291</t>
   </si>
   <si>
     <t xml:space="preserve">5.13346385955811</t>
@@ -773,10 +773,10 @@
     <t xml:space="preserve">5.27198505401611</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17420530319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16605710983276</t>
+    <t xml:space="preserve">5.17420482635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16605663299561</t>
   </si>
   <si>
     <t xml:space="preserve">5.1864275932312</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.94605112075806</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06827592849731</t>
+    <t xml:space="preserve">5.06827640533447</t>
   </si>
   <si>
     <t xml:space="preserve">4.98679399490356</t>
@@ -800,19 +800,19 @@
     <t xml:space="preserve">5.03691148757935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3626823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39191722869873</t>
+    <t xml:space="preserve">5.36268186569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39191818237305</t>
   </si>
   <si>
     <t xml:space="preserve">5.3125638961792</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27915048599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34597635269165</t>
+    <t xml:space="preserve">5.27915096282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34597587585449</t>
   </si>
   <si>
     <t xml:space="preserve">5.35432863235474</t>
@@ -821,124 +821,124 @@
     <t xml:space="preserve">5.32091617584229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33762311935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27079820632935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27497386932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18726778030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.132972240448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20397424697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22903299331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25409173965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2624454498291</t>
+    <t xml:space="preserve">5.33762264251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27079772949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27497434616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1872673034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13297271728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2039737701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22903347015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25409126281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26244497299194</t>
   </si>
   <si>
     <t xml:space="preserve">5.18309116363525</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21232652664185</t>
+    <t xml:space="preserve">5.212327003479</t>
   </si>
   <si>
     <t xml:space="preserve">5.17891454696655</t>
   </si>
   <si>
-    <t xml:space="preserve">5.249915599823</t>
+    <t xml:space="preserve">5.24991512298584</t>
   </si>
   <si>
     <t xml:space="preserve">5.24573850631714</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28332805633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22485542297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3000340461731</t>
+    <t xml:space="preserve">5.28332757949829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22485589981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30003356933594</t>
   </si>
   <si>
     <t xml:space="preserve">5.33344650268555</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40444707870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37521123886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40027046203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38356494903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37938737869263</t>
+    <t xml:space="preserve">5.40444660186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37521171569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40027093887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3835654258728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37938785552979</t>
   </si>
   <si>
     <t xml:space="preserve">5.23320960998535</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3083872795105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2582688331604</t>
+    <t xml:space="preserve">5.30838775634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25826930999756</t>
   </si>
   <si>
     <t xml:space="preserve">5.20814990997314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13714838027954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11209011077881</t>
+    <t xml:space="preserve">5.1371488571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11208963394165</t>
   </si>
   <si>
     <t xml:space="preserve">5.1538553237915</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23738574981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32509231567383</t>
+    <t xml:space="preserve">5.23738527297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32509326934814</t>
   </si>
   <si>
     <t xml:space="preserve">5.30421018600464</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29585742950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32926940917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48797798156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53809690475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59656858444214</t>
+    <t xml:space="preserve">5.29585695266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32926893234253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48797845840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53809642791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59656810760498</t>
   </si>
   <si>
     <t xml:space="preserve">5.62580394744873</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68845319747925</t>
+    <t xml:space="preserve">5.68845224380493</t>
   </si>
   <si>
     <t xml:space="preserve">5.61327457427979</t>
@@ -956,40 +956,40 @@
     <t xml:space="preserve">5.68009853363037</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64251089096069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37103509902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39609384536743</t>
+    <t xml:space="preserve">5.64251041412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37103462219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39609336853027</t>
   </si>
   <si>
     <t xml:space="preserve">5.38774156570435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24156141281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29168033599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19561958312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0828537940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88655567169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90743970870972</t>
+    <t xml:space="preserve">5.24156284332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29168128967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19562005996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08285331726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88655614852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90743923187256</t>
   </si>
   <si>
     <t xml:space="preserve">4.81973123550415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8030252456665</t>
+    <t xml:space="preserve">4.80302572250366</t>
   </si>
   <si>
     <t xml:space="preserve">4.8447904586792</t>
@@ -998,19 +998,19 @@
     <t xml:space="preserve">4.83643770217896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94502735137939</t>
+    <t xml:space="preserve">4.94502782821655</t>
   </si>
   <si>
     <t xml:space="preserve">4.9032621383667</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86567354202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87820386886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8531436920166</t>
+    <t xml:space="preserve">4.86567306518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87820339202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85314416885376</t>
   </si>
   <si>
     <t xml:space="preserve">4.81137847900391</t>
@@ -1022,10 +1022,10 @@
     <t xml:space="preserve">4.92832183837891</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77796649932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86149740219116</t>
+    <t xml:space="preserve">4.77796602249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.861496925354</t>
   </si>
   <si>
     <t xml:space="preserve">4.83226108551025</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">4.69861078262329</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66937589645386</t>
+    <t xml:space="preserve">4.6693754196167</t>
   </si>
   <si>
     <t xml:space="preserve">4.63596343994141</t>
@@ -1049,43 +1049,43 @@
     <t xml:space="preserve">4.70278835296631</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67355251312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64014005661011</t>
+    <t xml:space="preserve">4.67355155944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64013957977295</t>
   </si>
   <si>
     <t xml:space="preserve">4.71949434280396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7904953956604</t>
+    <t xml:space="preserve">4.79049491882324</t>
   </si>
   <si>
     <t xml:space="preserve">4.74872970581055</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7320237159729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71114158630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67772960662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91579246520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92414474487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8949089050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84061431884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16220808029175</t>
+    <t xml:space="preserve">4.73202419281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71114110946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67772912979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9157919883728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92414426803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89490842819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8406138420105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16220760345459</t>
   </si>
   <si>
     <t xml:space="preserve">4.99932241439819</t>
@@ -1094,64 +1094,64 @@
     <t xml:space="preserve">5.02020502090454</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17056131362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09955930709839</t>
+    <t xml:space="preserve">5.17056035995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09955978393555</t>
   </si>
   <si>
     <t xml:space="preserve">4.95338106155396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98679304122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7863187789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6860818862915</t>
+    <t xml:space="preserve">4.98679351806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78631925582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68608140945435</t>
   </si>
   <si>
     <t xml:space="preserve">4.60672807693481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59419822692871</t>
+    <t xml:space="preserve">4.59419775009155</t>
   </si>
   <si>
     <t xml:space="preserve">4.6150803565979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63178682327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70696496963501</t>
+    <t xml:space="preserve">4.63178730010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70696449279785</t>
   </si>
   <si>
     <t xml:space="preserve">4.58584499359131</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55243253707886</t>
+    <t xml:space="preserve">4.55243301391602</t>
   </si>
   <si>
     <t xml:space="preserve">4.53990268707275</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57749271392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48978424072266</t>
+    <t xml:space="preserve">4.57749176025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4897837638855</t>
   </si>
   <si>
     <t xml:space="preserve">4.41043043136597</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4438419342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4939603805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47307825088501</t>
+    <t xml:space="preserve">4.44384241104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49396085739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47307777404785</t>
   </si>
   <si>
     <t xml:space="preserve">4.51902055740356</t>
@@ -1160,25 +1160,25 @@
     <t xml:space="preserve">4.5691385269165</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59002161026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65684652328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64849233627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5983738899231</t>
+    <t xml:space="preserve">4.59002113342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65684604644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64849185943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59837436676025</t>
   </si>
   <si>
     <t xml:space="preserve">4.56078577041626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48560857772827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43966627120972</t>
+    <t xml:space="preserve">4.48560810089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4396653175354</t>
   </si>
   <si>
     <t xml:space="preserve">4.36031150817871</t>
@@ -1187,31 +1187,31 @@
     <t xml:space="preserve">4.38537073135376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18907356262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16150808334351</t>
+    <t xml:space="preserve">4.18907308578491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16150760650635</t>
   </si>
   <si>
     <t xml:space="preserve">4.15148496627808</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15649557113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19324922561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09802436828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15315437316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10303640365601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12642574310303</t>
+    <t xml:space="preserve">4.15649604797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19324970245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09802484512329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1531548500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10303592681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12642621994019</t>
   </si>
   <si>
     <t xml:space="preserve">4.16986131668091</t>
@@ -1220,10 +1220,10 @@
     <t xml:space="preserve">4.17654418945312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14313125610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16819047927856</t>
+    <t xml:space="preserve">4.14313077926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16819000244141</t>
   </si>
   <si>
     <t xml:space="preserve">2.83002591133118</t>
@@ -1232,25 +1232,25 @@
     <t xml:space="preserve">2.90687417984009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84339046478271</t>
+    <t xml:space="preserve">2.84339070320129</t>
   </si>
   <si>
     <t xml:space="preserve">2.87179160118103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89350914955139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80162501335144</t>
+    <t xml:space="preserve">2.89350938796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80162477493286</t>
   </si>
   <si>
     <t xml:space="preserve">2.92358064651489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94863986968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01713514328003</t>
+    <t xml:space="preserve">2.94863963127136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01713538169861</t>
   </si>
   <si>
     <t xml:space="preserve">3.08061838150024</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">3.17083144187927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14911389350891</t>
+    <t xml:space="preserve">3.14911365509033</t>
   </si>
   <si>
     <t xml:space="preserve">3.15746665000916</t>
@@ -1268,25 +1268,25 @@
     <t xml:space="preserve">3.14410185813904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17918539047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17417287826538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10400748252869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01212334632874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02882933616638</t>
+    <t xml:space="preserve">3.17918515205383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17417311668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10400724411011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01212310791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02882957458496</t>
   </si>
   <si>
     <t xml:space="preserve">2.94529795646667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95699238777161</t>
+    <t xml:space="preserve">2.95699262619019</t>
   </si>
   <si>
     <t xml:space="preserve">2.89852118492126</t>
@@ -1295,19 +1295,19 @@
     <t xml:space="preserve">2.84004878997803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82501411437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85007333755493</t>
+    <t xml:space="preserve">2.82501339912415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85007286071777</t>
   </si>
   <si>
     <t xml:space="preserve">2.74649548530579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55771446228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54769158363342</t>
+    <t xml:space="preserve">2.55771470069885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54769134521484</t>
   </si>
   <si>
     <t xml:space="preserve">2.51093769073486</t>
@@ -1319,25 +1319,25 @@
     <t xml:space="preserve">2.5009138584137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51594972610474</t>
+    <t xml:space="preserve">2.51594996452332</t>
   </si>
   <si>
     <t xml:space="preserve">2.50592589378357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47919607162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41905379295349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39566516876221</t>
+    <t xml:space="preserve">2.47919631004333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41905355453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39566540718079</t>
   </si>
   <si>
     <t xml:space="preserve">2.36058235168457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36726450920105</t>
+    <t xml:space="preserve">2.36726474761963</t>
   </si>
   <si>
     <t xml:space="preserve">2.37728881835938</t>
@@ -1346,43 +1346,43 @@
     <t xml:space="preserve">2.2753803730011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31380558013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26201558113098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27203965187073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41404271125793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38062953948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30043959617615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30211091041565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29709911346436</t>
+    <t xml:space="preserve">2.31380534172058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2620153427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27203941345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41404223442078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38062930107117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30043935775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30211067199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29709887504578</t>
   </si>
   <si>
     <t xml:space="preserve">2.32382845878601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33552289009094</t>
+    <t xml:space="preserve">2.33552312850952</t>
   </si>
   <si>
     <t xml:space="preserve">2.35389971733093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36559438705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35055828094482</t>
+    <t xml:space="preserve">2.36559414863586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35055804252625</t>
   </si>
   <si>
     <t xml:space="preserve">2.35222935676575</t>
@@ -1391,67 +1391,67 @@
     <t xml:space="preserve">2.3555703163147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25533318519592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22025060653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28039264678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.225261926651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23027348518372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40067672729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44912457466125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42406535148621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31881642341614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30879330635071</t>
+    <t xml:space="preserve">2.25533294677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22025084495544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28039240837097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22526168823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23027372360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40067648887634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44912481307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42406558990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31881666183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30879306793213</t>
   </si>
   <si>
     <t xml:space="preserve">2.34387588500977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33218097686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27371001243591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18850898742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17681479454041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15342545509338</t>
+    <t xml:space="preserve">2.33218145370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27370977401733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18850874900818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17681455612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15342569351196</t>
   </si>
   <si>
     <t xml:space="preserve">2.21022653579712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21189713478088</t>
+    <t xml:space="preserve">2.2118968963623</t>
   </si>
   <si>
     <t xml:space="preserve">2.05485892295837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01142311096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97466909885406</t>
+    <t xml:space="preserve">2.01142287254333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97466921806335</t>
   </si>
   <si>
     <t xml:space="preserve">2.00474047660828</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">2.03815340995789</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15175557136536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17180252075195</t>
+    <t xml:space="preserve">2.1517550945282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17180228233337</t>
   </si>
   <si>
     <t xml:space="preserve">2.18182563781738</t>
@@ -1472,31 +1472,31 @@
     <t xml:space="preserve">2.1667902469635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16846084594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15509605407715</t>
+    <t xml:space="preserve">2.16846060752869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15509581565857</t>
   </si>
   <si>
     <t xml:space="preserve">2.15676641464233</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11500144004822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07657718658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08994221687317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09829521179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1601083278656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09662461280823</t>
+    <t xml:space="preserve">2.11500120162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07657742500305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08994245529175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09829497337341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16010808944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09662485122681</t>
   </si>
   <si>
     <t xml:space="preserve">2.09161257743835</t>
@@ -1514,16 +1514,16 @@
     <t xml:space="preserve">2.23695611953735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18683767318726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11834239959717</t>
+    <t xml:space="preserve">2.18683791160583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11834216117859</t>
   </si>
   <si>
     <t xml:space="preserve">2.06989502906799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06321287155151</t>
+    <t xml:space="preserve">2.06321310997009</t>
   </si>
   <si>
     <t xml:space="preserve">2.00139951705933</t>
@@ -1532,52 +1532,52 @@
     <t xml:space="preserve">1.99972856044769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98302280902863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94626915454865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87610304355621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75748932361603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69567656517029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65391075611115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62885165214539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62968695163727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50439071655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48601388931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39663553237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31728148460388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28553986549377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27133941650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24962162971497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24460959434509</t>
+    <t xml:space="preserve">1.98302292823792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94626939296722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87610328197479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75748944282532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.695676445961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65391051769257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62885141372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62968707084656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50439059734344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48601377010345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39663565158844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31728136539459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2855396270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27133929729462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24962174892426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24460971355438</t>
   </si>
   <si>
     <t xml:space="preserve">1.2897162437439</t>
@@ -1589,34 +1589,34 @@
     <t xml:space="preserve">1.30391657352448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3156111240387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31310498714447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28386950492859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27969300746918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33899986743927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35152900218964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29472815990448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29639863967896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24293923377991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2521276473999</t>
+    <t xml:space="preserve">1.31561100482941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31310510635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2838693857193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27969288825989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33899998664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35152912139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29472827911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29639852046967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2429393529892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25212776660919</t>
   </si>
   <si>
     <t xml:space="preserve">1.26799857616425</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">1.25296247005463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23375105857849</t>
+    <t xml:space="preserve">1.2337509393692</t>
   </si>
   <si>
     <t xml:space="preserve">1.25630414485931</t>
@@ -1634,16 +1634,16 @@
     <t xml:space="preserve">1.2579745054245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26048064231873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36823558807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36990582942963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36405909061432</t>
+    <t xml:space="preserve">1.26048040390015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36823570728302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36990606784821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36405920982361</t>
   </si>
   <si>
     <t xml:space="preserve">1.34568238258362</t>
@@ -1661,31 +1661,31 @@
     <t xml:space="preserve">1.23876285552979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06835913658142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962275266647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989840567111969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.633163213729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.703329920768738</t>
+    <t xml:space="preserve">1.06835901737213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962275326251984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989840686321259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.633163094520569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.703329801559448</t>
   </si>
   <si>
     <t xml:space="preserve">0.705000162124634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.862038254737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958098888397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948074877262115</t>
+    <t xml:space="preserve">0.862038195133209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958098948001862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948074817657471</t>
   </si>
   <si>
     <t xml:space="preserve">0.848673403263092</t>
@@ -1694,22 +1694,22 @@
     <t xml:space="preserve">0.913827121257782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944734156131744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918839156627655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917168796062469</t>
+    <t xml:space="preserve">0.9447340965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9188392162323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917168855667114</t>
   </si>
   <si>
     <t xml:space="preserve">1.00487565994263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14771413803101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11430132389069</t>
+    <t xml:space="preserve">1.1477142572403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11430144309998</t>
   </si>
   <si>
     <t xml:space="preserve">1.09926605224609</t>
@@ -1718,37 +1718,37 @@
     <t xml:space="preserve">1.13184344768524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10344243049622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03578281402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01155829429626</t>
+    <t xml:space="preserve">1.10344254970551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03578269481659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01155817508698</t>
   </si>
   <si>
     <t xml:space="preserve">1.01824069023132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999029040336609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0157356262207</t>
+    <t xml:space="preserve">0.999028921127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01573550701141</t>
   </si>
   <si>
     <t xml:space="preserve">1.01322948932648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08255970478058</t>
+    <t xml:space="preserve">1.08255958557129</t>
   </si>
   <si>
     <t xml:space="preserve">1.10177206993103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12766623497009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12933731079102</t>
+    <t xml:space="preserve">1.1276661157608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12933743000031</t>
   </si>
   <si>
     <t xml:space="preserve">1.13017213344574</t>
@@ -1766,22 +1766,22 @@
     <t xml:space="preserve">1.06585311889648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03244113922119</t>
+    <t xml:space="preserve">1.0324410200119</t>
   </si>
   <si>
     <t xml:space="preserve">1.07086515426636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06334805488586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01907634735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03494703769684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06501829624176</t>
+    <t xml:space="preserve">1.06334817409515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01907622814178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03494715690613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06501841545105</t>
   </si>
   <si>
     <t xml:space="preserve">1.12850165367126</t>
@@ -1790,7 +1790,7 @@
     <t xml:space="preserve">1.08506560325623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0867360830307</t>
+    <t xml:space="preserve">1.08673596382141</t>
   </si>
   <si>
     <t xml:space="preserve">1.07253634929657</t>
@@ -1799,22 +1799,22 @@
     <t xml:space="preserve">1.08088910579681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1051127910614</t>
+    <t xml:space="preserve">1.10511291027069</t>
   </si>
   <si>
     <t xml:space="preserve">1.07838320732117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10010087490082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1126309633255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11012482643127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2262327671051</t>
+    <t xml:space="preserve">1.10010075569153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11263084411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11012494564056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22623288631439</t>
   </si>
   <si>
     <t xml:space="preserve">1.46179032325745</t>
@@ -1823,25 +1823,25 @@
     <t xml:space="preserve">1.4158478975296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.414177775383</t>
+    <t xml:space="preserve">1.41417765617371</t>
   </si>
   <si>
     <t xml:space="preserve">1.36071765422821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.330646276474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29806995391846</t>
+    <t xml:space="preserve">1.33064615726471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29806983470917</t>
   </si>
   <si>
     <t xml:space="preserve">1.37324774265289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38744735717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32981157302856</t>
+    <t xml:space="preserve">1.38744711875916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32981145381927</t>
   </si>
   <si>
     <t xml:space="preserve">1.35069346427917</t>
@@ -1862,16 +1862,16 @@
     <t xml:space="preserve">1.40248322486877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41918897628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42169487476349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42253053188324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42837727069855</t>
+    <t xml:space="preserve">1.41918885707855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42169499397278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42253041267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42837738990784</t>
   </si>
   <si>
     <t xml:space="preserve">1.39997732639313</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">1.37575268745422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3941296339035</t>
+    <t xml:space="preserve">1.39412951469421</t>
   </si>
   <si>
     <t xml:space="preserve">1.4534364938736</t>
@@ -1889,16 +1889,16 @@
     <t xml:space="preserve">1.43589532375336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52861440181732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61131012439728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59710991382599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59376907348633</t>
+    <t xml:space="preserve">1.52861428260803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61131024360657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59710967540741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59376895427704</t>
   </si>
   <si>
     <t xml:space="preserve">1.5745564699173</t>
@@ -1907,19 +1907,19 @@
     <t xml:space="preserve">1.55283868312836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55116760730743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51441466808319</t>
+    <t xml:space="preserve">1.55116772651672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51441478729248</t>
   </si>
   <si>
     <t xml:space="preserve">1.47097861766815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41751849651337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43422484397888</t>
+    <t xml:space="preserve">1.41751837730408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43422496318817</t>
   </si>
   <si>
     <t xml:space="preserve">1.38828277587891</t>
@@ -1937,13 +1937,13 @@
     <t xml:space="preserve">1.34985876083374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30308091640472</t>
+    <t xml:space="preserve">1.30308103561401</t>
   </si>
   <si>
     <t xml:space="preserve">1.32229340076447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31644594669342</t>
+    <t xml:space="preserve">1.31644582748413</t>
   </si>
   <si>
     <t xml:space="preserve">1.2989045381546</t>
@@ -1955,34 +1955,34 @@
     <t xml:space="preserve">1.31059908866882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31895184516907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29222226142883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28720998764038</t>
+    <t xml:space="preserve">1.31895172595978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29222214221954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28721010684967</t>
   </si>
   <si>
     <t xml:space="preserve">1.25045645236969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32730555534363</t>
+    <t xml:space="preserve">1.32730543613434</t>
   </si>
   <si>
     <t xml:space="preserve">1.31143462657928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31978738307953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34902310371399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34651708602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30725824832916</t>
+    <t xml:space="preserve">1.31978750228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3490229845047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34651696681976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30725836753845</t>
   </si>
   <si>
     <t xml:space="preserve">1.26215076446533</t>
@@ -1991,46 +1991,46 @@
     <t xml:space="preserve">1.26883327960968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22205638885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19198513031006</t>
+    <t xml:space="preserve">1.22205626964569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19198501110077</t>
   </si>
   <si>
     <t xml:space="preserve">1.35821163654327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3231292963028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28219890594482</t>
+    <t xml:space="preserve">1.32312917709351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28219902515411</t>
   </si>
   <si>
     <t xml:space="preserve">1.24043321609497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27384543418884</t>
+    <t xml:space="preserve">1.27384519577026</t>
   </si>
   <si>
     <t xml:space="preserve">1.2613160610199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32646977901459</t>
+    <t xml:space="preserve">1.32646989822388</t>
   </si>
   <si>
     <t xml:space="preserve">1.33816432952881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42503666877747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48183751106262</t>
+    <t xml:space="preserve">1.42503643035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48183739185333</t>
   </si>
   <si>
     <t xml:space="preserve">1.49603796005249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50272023677826</t>
+    <t xml:space="preserve">1.50272035598755</t>
   </si>
   <si>
     <t xml:space="preserve">1.50355505943298</t>
@@ -2051,10 +2051,10 @@
     <t xml:space="preserve">1.49186074733734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41668295860291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39329493045807</t>
+    <t xml:space="preserve">1.41668283939362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39329481124878</t>
   </si>
   <si>
     <t xml:space="preserve">1.39078879356384</t>
@@ -2063,10 +2063,10 @@
     <t xml:space="preserve">1.42002439498901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37491810321808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34818851947784</t>
+    <t xml:space="preserve">1.37491798400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34818840026855</t>
   </si>
   <si>
     <t xml:space="preserve">1.33148193359375</t>
@@ -2075,16 +2075,16 @@
     <t xml:space="preserve">1.32814013957977</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29723417758942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29974007606506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30224645137787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33315217494965</t>
+    <t xml:space="preserve">1.29723429679871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29974031448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30224621295929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33315229415894</t>
   </si>
   <si>
     <t xml:space="preserve">1.26549255847931</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">1.38494122028351</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38911843299866</t>
+    <t xml:space="preserve">1.38911855220795</t>
   </si>
   <si>
     <t xml:space="preserve">1.37993013858795</t>
@@ -2111,61 +2111,61 @@
     <t xml:space="preserve">1.45260179042816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48851990699768</t>
+    <t xml:space="preserve">1.48851978778839</t>
   </si>
   <si>
     <t xml:space="preserve">1.49687266349792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50104904174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44758975505829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39914166927338</t>
+    <t xml:space="preserve">1.50104916095734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.447589635849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39914155006409</t>
   </si>
   <si>
     <t xml:space="preserve">1.5428147315979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46095454692841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39162361621857</t>
+    <t xml:space="preserve">1.46095442771912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39162349700928</t>
   </si>
   <si>
     <t xml:space="preserve">1.41000032424927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40833020210266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42921304702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40749442577362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33398795127869</t>
+    <t xml:space="preserve">1.40833008289337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42921280860901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40749430656433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3339878320694</t>
   </si>
   <si>
     <t xml:space="preserve">1.32563412189484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33732879161835</t>
+    <t xml:space="preserve">1.33732855319977</t>
   </si>
   <si>
     <t xml:space="preserve">1.36155319213867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36907052993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44508385658264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4350597858429</t>
+    <t xml:space="preserve">1.36907029151917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44508373737335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43505966663361</t>
   </si>
   <si>
     <t xml:space="preserve">1.46596658229828</t>
@@ -2174,16 +2174,16 @@
     <t xml:space="preserve">1.47181332111359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46513092517853</t>
+    <t xml:space="preserve">1.46513104438782</t>
   </si>
   <si>
     <t xml:space="preserve">1.47264897823334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51190888881683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47014307975769</t>
+    <t xml:space="preserve">1.51190876960754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4701429605484</t>
   </si>
   <si>
     <t xml:space="preserve">1.49269616603851</t>
@@ -2192,7 +2192,7 @@
     <t xml:space="preserve">1.52276754379272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54030883312225</t>
+    <t xml:space="preserve">1.54030871391296</t>
   </si>
   <si>
     <t xml:space="preserve">1.53529667854309</t>
@@ -2201,7 +2201,7 @@
     <t xml:space="preserve">1.59794533252716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60629820823669</t>
+    <t xml:space="preserve">1.6062980890274</t>
   </si>
   <si>
     <t xml:space="preserve">1.58625102043152</t>
@@ -2219,46 +2219,46 @@
     <t xml:space="preserve">1.58458054065704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56035614013672</t>
+    <t xml:space="preserve">1.56035602092743</t>
   </si>
   <si>
     <t xml:space="preserve">1.54197919368744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55868577957153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56620359420776</t>
+    <t xml:space="preserve">1.55868566036224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56620371341705</t>
   </si>
   <si>
     <t xml:space="preserve">1.56703841686249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58708643913269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64973425865173</t>
+    <t xml:space="preserve">1.58708655834198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64973437786102</t>
   </si>
   <si>
     <t xml:space="preserve">1.74078285694122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70737087726593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71906542778015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72908842563629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71238279342651</t>
+    <t xml:space="preserve">1.70737075805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71906530857086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72908854484558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7123829126358</t>
   </si>
   <si>
     <t xml:space="preserve">1.73243010044098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69233477115631</t>
+    <t xml:space="preserve">1.69233465194702</t>
   </si>
   <si>
     <t xml:space="preserve">1.76584219932556</t>
@@ -2267,25 +2267,25 @@
     <t xml:space="preserve">1.74913573265076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72073566913605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63887560367584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60880422592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68565249443054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67061710357666</t>
+    <t xml:space="preserve">1.72073554992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63887548446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60880410671234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68565225601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67061698436737</t>
   </si>
   <si>
     <t xml:space="preserve">1.68732357025146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67562925815582</t>
+    <t xml:space="preserve">1.67562901973724</t>
   </si>
   <si>
     <t xml:space="preserve">1.68064117431641</t>
@@ -2297,13 +2297,13 @@
     <t xml:space="preserve">1.61548662185669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62467503547668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61047470569611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64054596424103</t>
+    <t xml:space="preserve">1.62467515468597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61047446727753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64054584503174</t>
   </si>
   <si>
     <t xml:space="preserve">1.62383937835693</t>
@@ -2312,10 +2312,10 @@
     <t xml:space="preserve">1.60963988304138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57789826393127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5912629365921</t>
+    <t xml:space="preserve">1.57789814472198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59126305580139</t>
   </si>
   <si>
     <t xml:space="preserve">1.56202733516693</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">1.58290934562683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60379219055176</t>
+    <t xml:space="preserve">1.60379207134247</t>
   </si>
   <si>
     <t xml:space="preserve">1.6004513502121</t>
@@ -2339,31 +2339,31 @@
     <t xml:space="preserve">1.58541524410248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54532086849213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54699122905731</t>
+    <t xml:space="preserve">1.54532074928284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54699110984802</t>
   </si>
   <si>
     <t xml:space="preserve">1.57706248760223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43756580352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49436664581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48935544490814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46763706207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51274347305298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52610850334167</t>
+    <t xml:space="preserve">1.43756568431854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49436676502228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48935532569885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46763694286346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51274359226227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52610838413239</t>
   </si>
   <si>
     <t xml:space="preserve">1.53195595741272</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">1.48267221450806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26465690135956</t>
+    <t xml:space="preserve">1.26465678215027</t>
   </si>
   <si>
     <t xml:space="preserve">1.23208045959473</t>
@@ -2393,46 +2393,46 @@
     <t xml:space="preserve">1.16692590713501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13601982593536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02742898464203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933039665222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776836395263672</t>
+    <t xml:space="preserve">1.13601970672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02742910385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933039724826813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776836335659027</t>
   </si>
   <si>
     <t xml:space="preserve">0.719200670719147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.695811808109283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.546709179878235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613534152507782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519561290740967</t>
+    <t xml:space="preserve">0.695811748504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54670923948288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613534212112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519561350345612</t>
   </si>
   <si>
     <t xml:space="preserve">0.599333703517914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674928963184357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.725047528743744</t>
+    <t xml:space="preserve">0.674928903579712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.725047469139099</t>
   </si>
   <si>
     <t xml:space="preserve">0.701658546924591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.637340366840363</t>
+    <t xml:space="preserve">0.637340486049652</t>
   </si>
   <si>
     <t xml:space="preserve">0.682447016239166</t>
@@ -2444,64 +2444,64 @@
     <t xml:space="preserve">0.687876343727112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.659893691539764</t>
+    <t xml:space="preserve">0.659893751144409</t>
   </si>
   <si>
     <t xml:space="preserve">0.643604636192322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.65947550535202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643187284469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627316415309906</t>
+    <t xml:space="preserve">0.659475445747375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.64318722486496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627316355705261</t>
   </si>
   <si>
     <t xml:space="preserve">0.576780498027802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618128001689911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.660728394985199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.646528840065002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.650705218315125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.638175129890442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.649869740009308</t>
+    <t xml:space="preserve">0.618127942085266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.660728454589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.646528899669647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.650705337524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.638175249099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.649869620800018</t>
   </si>
   <si>
     <t xml:space="preserve">0.640263795852661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612281143665314</t>
+    <t xml:space="preserve">0.612281203269958</t>
   </si>
   <si>
     <t xml:space="preserve">0.615621984004974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610192477703094</t>
+    <t xml:space="preserve">0.610192537307739</t>
   </si>
   <si>
     <t xml:space="preserve">0.6055988073349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61102819442749</t>
+    <t xml:space="preserve">0.611028134822845</t>
   </si>
   <si>
     <t xml:space="preserve">0.651539981365204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.676599264144897</t>
+    <t xml:space="preserve">0.676599323749542</t>
   </si>
   <si>
     <t xml:space="preserve">0.654881656169891</t>
@@ -2516,10 +2516,10 @@
     <t xml:space="preserve">0.655717313289642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639846503734589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.649034976959229</t>
+    <t xml:space="preserve">0.639846444129944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.649034917354584</t>
   </si>
   <si>
     <t xml:space="preserve">0.668246507644653</t>
@@ -2531,64 +2531,64 @@
     <t xml:space="preserve">0.626480758190155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.609775185585022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.606016039848328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.629822373390198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596827805042267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.574691891670227</t>
+    <t xml:space="preserve">0.609775125980377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.606016099452972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.629822432994843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596827745437622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.574691951274872</t>
   </si>
   <si>
     <t xml:space="preserve">0.581792593002319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.57427453994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.601839780807495</t>
+    <t xml:space="preserve">0.574274480342865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60183972120285</t>
   </si>
   <si>
     <t xml:space="preserve">0.630658030509949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.726300418376923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789366483688354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.763054251670837</t>
+    <t xml:space="preserve">0.726300477981567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78936642408371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.763054192066193</t>
   </si>
   <si>
     <t xml:space="preserve">0.768483519554138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.827790558338165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83530855178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901298046112061</t>
+    <t xml:space="preserve">0.827790498733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.835308492183685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901297986507416</t>
   </si>
   <si>
     <t xml:space="preserve">0.910486459732056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00571155548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01072347164154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968957781791687</t>
+    <t xml:space="preserve">1.00571143627167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01072335243225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968957662582397</t>
   </si>
   <si>
     <t xml:space="preserve">0.877909064292908</t>
@@ -2597,100 +2597,100 @@
     <t xml:space="preserve">0.924685955047607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.925521671772003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938051521778107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922180950641632</t>
+    <t xml:space="preserve">0.925521612167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938051640987396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922180891036987</t>
   </si>
   <si>
     <t xml:space="preserve">0.892109513282776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.893779993057251</t>
+    <t xml:space="preserve">0.893779933452606</t>
   </si>
   <si>
     <t xml:space="preserve">0.895450294017792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.823614180088043</t>
+    <t xml:space="preserve">0.823614120483398</t>
   </si>
   <si>
     <t xml:space="preserve">0.781013667583466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.824867129325867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806072950363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785607397556305</t>
+    <t xml:space="preserve">0.824867188930511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806072890758514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78560745716095</t>
   </si>
   <si>
     <t xml:space="preserve">0.802313923835754</t>
   </si>
   <si>
-    <t xml:space="preserve">0.797719299793243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801895678043365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798554956912994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776419103145599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.782266736030579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766394972801208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821525573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.795631468296051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86370861530304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855355858802795</t>
+    <t xml:space="preserve">0.797719180583954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801895618438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.798554837703705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77641898393631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.782266676425934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766394913196564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821525514125824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.795631527900696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863708555698395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855355799198151</t>
   </si>
   <si>
     <t xml:space="preserve">0.844496965408325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.857861816883087</t>
+    <t xml:space="preserve">0.857861757278442</t>
   </si>
   <si>
     <t xml:space="preserve">0.836143374443054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.834890305995941</t>
+    <t xml:space="preserve">0.834890365600586</t>
   </si>
   <si>
     <t xml:space="preserve">0.838649392127991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.800225257873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.773912966251373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789783775806427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77182525396347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.767230629920959</t>
+    <t xml:space="preserve">0.80022519826889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.773913025856018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789783835411072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.771825194358826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767230570316315</t>
   </si>
   <si>
     <t xml:space="preserve">0.775583386421204</t>
@@ -2699,13 +2699,13 @@
     <t xml:space="preserve">0.786860466003418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.79270726442337</t>
+    <t xml:space="preserve">0.792707145214081</t>
   </si>
   <si>
     <t xml:space="preserve">0.758877813816071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.765977561473846</t>
+    <t xml:space="preserve">0.765977501869202</t>
   </si>
   <si>
     <t xml:space="preserve">0.800642669200897</t>
@@ -2717,88 +2717,88 @@
     <t xml:space="preserve">0.799807846546173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.780178070068359</t>
+    <t xml:space="preserve">0.780178010463715</t>
   </si>
   <si>
     <t xml:space="preserve">0.770989596843719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.740918278694153</t>
+    <t xml:space="preserve">0.740918338298798</t>
   </si>
   <si>
     <t xml:space="preserve">0.717947661876678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.712099969387054</t>
+    <t xml:space="preserve">0.712100028991699</t>
   </si>
   <si>
     <t xml:space="preserve">0.684117376804352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.690799832344055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69288843870163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.685787677764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.674094259738922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.666576087474823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.682029545307159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.687459051609039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.68537038564682</t>
+    <t xml:space="preserve">0.690799713134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.692888379096985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.685787737369537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.674094200134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.666576147079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.682029604911804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.687458992004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.685370326042175</t>
   </si>
   <si>
     <t xml:space="preserve">0.67785233259201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.694558799266815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.697482168674469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.70374721288681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.698317766189575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.72128838300705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.720453679561615</t>
+    <t xml:space="preserve">0.69455873966217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.697482109069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.703747153282166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69831782579422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.721288442611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.72045361995697</t>
   </si>
   <si>
     <t xml:space="preserve">0.742588639259338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.767647981643677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.718365073204041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.715024292469025</t>
+    <t xml:space="preserve">0.767647862434387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.718365013599396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.715024352073669</t>
   </si>
   <si>
     <t xml:space="preserve">0.7818483710289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.757207334041595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778925001621246</t>
+    <t xml:space="preserve">0.75720739364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778925061225891</t>
   </si>
   <si>
     <t xml:space="preserve">0.79646623134613</t>
@@ -2807,22 +2807,22 @@
     <t xml:space="preserve">0.825284540653229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.850343704223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860367834568024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.847002983093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858696579933167</t>
+    <t xml:space="preserve">0.850343823432922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860367774963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.847003042697906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858696699142456</t>
   </si>
   <si>
     <t xml:space="preserve">0.843661308288574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.8720623254776</t>
+    <t xml:space="preserve">0.872062265872955</t>
   </si>
   <si>
     <t xml:space="preserve">0.852014183998108</t>
@@ -2837,19 +2837,19 @@
     <t xml:space="preserve">0.807743310928345</t>
   </si>
   <si>
-    <t xml:space="preserve">0.813172698020935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828626155853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.832802593708038</t>
+    <t xml:space="preserve">0.81317275762558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828626096248627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.832802534103394</t>
   </si>
   <si>
     <t xml:space="preserve">0.820690751075745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.749689340591431</t>
+    <t xml:space="preserve">0.749689400196075</t>
   </si>
   <si>
     <t xml:space="preserve">0.710846960544586</t>
@@ -2858,13 +2858,13 @@
     <t xml:space="preserve">0.654464304447174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.633998811244965</t>
+    <t xml:space="preserve">0.63399875164032</t>
   </si>
   <si>
     <t xml:space="preserve">0.645275890827179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.660311162471771</t>
+    <t xml:space="preserve">0.660311043262482</t>
   </si>
   <si>
     <t xml:space="preserve">0.684534728527069</t>
@@ -2876,19 +2876,19 @@
     <t xml:space="preserve">0.753030121326447</t>
   </si>
   <si>
-    <t xml:space="preserve">0.784354448318481</t>
+    <t xml:space="preserve">0.784354388713837</t>
   </si>
   <si>
     <t xml:space="preserve">0.787696063518524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803148627281189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856191396713257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.845331728458405</t>
+    <t xml:space="preserve">0.803148686885834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856191456317902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.845331788063049</t>
   </si>
   <si>
     <t xml:space="preserve">0.877073466777802</t>
@@ -2897,10 +2897,10 @@
     <t xml:space="preserve">0.900462329387665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.889603555202484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887097477912903</t>
+    <t xml:space="preserve">0.889603495597839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887097537517548</t>
   </si>
   <si>
     <t xml:space="preserve">0.89043915271759</t>
@@ -2909,25 +2909,25 @@
     <t xml:space="preserve">0.88125067949295</t>
   </si>
   <si>
-    <t xml:space="preserve">0.904638767242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89294421672821</t>
+    <t xml:space="preserve">0.904638886451721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892944276332855</t>
   </si>
   <si>
     <t xml:space="preserve">0.902132749557495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.88208544254303</t>
+    <t xml:space="preserve">0.882085502147675</t>
   </si>
   <si>
     <t xml:space="preserve">0.867884993553162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.841155350208282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.839484989643097</t>
+    <t xml:space="preserve">0.841155409812927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.839484930038452</t>
   </si>
   <si>
     <t xml:space="preserve">0.841990947723389</t>
@@ -2936,34 +2936,34 @@
     <t xml:space="preserve">0.840320587158203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.859532237052917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905474364757538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849508166313171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872897028923035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906310141086578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943898439407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953922510147095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957263231277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965617060661316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978146016597748</t>
+    <t xml:space="preserve">0.859532177448273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905474305152893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849508225917816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872897088527679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906309962272644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943898499011993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953922390937805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957263350486755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965617001056671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978146195411682</t>
   </si>
   <si>
     <t xml:space="preserve">0.961439728736877</t>
@@ -2975,100 +2975,100 @@
     <t xml:space="preserve">0.902968347072601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.874567449092865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852849841117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867050290107727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.878744661808014</t>
+    <t xml:space="preserve">0.87456750869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852849781513214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867050170898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.878744721412659</t>
   </si>
   <si>
     <t xml:space="preserve">0.907144844532013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.931369364261627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921345114707947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927191972732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912992358207703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947240114212036</t>
+    <t xml:space="preserve">0.931369304656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921345233917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927191913127899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912992477416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947240054607391</t>
   </si>
   <si>
     <t xml:space="preserve">0.899626731872559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.929697930812836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93888646364212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93721604347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.942228019237518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941392540931702</t>
+    <t xml:space="preserve">0.92969799041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938886404037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.937215983867645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942228078842163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941392481327057</t>
   </si>
   <si>
     <t xml:space="preserve">0.94640451669693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.935545802116394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975639998912811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14687860012054</t>
+    <t xml:space="preserve">0.935545682907104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975640058517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14687848091125</t>
   </si>
   <si>
     <t xml:space="preserve">1.18947911262512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17360818386078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16024327278137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15773737430573</t>
+    <t xml:space="preserve">1.17360830307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16024339199066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15773749351501</t>
   </si>
   <si>
     <t xml:space="preserve">1.17193794250488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13852596282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10928916931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11096048355103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1067841053009</t>
+    <t xml:space="preserve">1.1385258436203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10928928852081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11096060276031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10678422451019</t>
   </si>
   <si>
     <t xml:space="preserve">1.11179530620575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13100779056549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12098383903503</t>
+    <t xml:space="preserve">1.1310076713562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12098371982574</t>
   </si>
   <si>
     <t xml:space="preserve">1.16358518600464</t>
@@ -3077,10 +3077,10 @@
     <t xml:space="preserve">1.14520823955536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11513674259186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10761880874634</t>
+    <t xml:space="preserve">1.11513686180115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10761892795563</t>
   </si>
   <si>
     <t xml:space="preserve">1.37742400169373</t>
@@ -3092,37 +3092,37 @@
     <t xml:space="preserve">1.43923699855804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43673086166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44007158279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40665984153748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41167163848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39747130870819</t>
+    <t xml:space="preserve">1.43673098087311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44007170200348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4066596031189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41167175769806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3974711894989</t>
   </si>
   <si>
     <t xml:space="preserve">1.43840134143829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47682547569275</t>
+    <t xml:space="preserve">1.47682535648346</t>
   </si>
   <si>
     <t xml:space="preserve">1.45928418636322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44090735912323</t>
+    <t xml:space="preserve">1.44090723991394</t>
   </si>
   <si>
     <t xml:space="preserve">1.43338942527771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48100185394287</t>
+    <t xml:space="preserve">1.48100173473358</t>
   </si>
   <si>
     <t xml:space="preserve">1.41334211826324</t>
@@ -3134,13 +3134,13 @@
     <t xml:space="preserve">1.58792126178741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.550332903862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62634539604187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61214590072632</t>
+    <t xml:space="preserve">1.55033278465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62634551525116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61214578151703</t>
   </si>
   <si>
     <t xml:space="preserve">1.62049865722656</t>
@@ -3149,13 +3149,13 @@
     <t xml:space="preserve">1.61966300010681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62718117237091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6138162612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45677828788757</t>
+    <t xml:space="preserve">1.62718105316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61381614208221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45677816867828</t>
   </si>
   <si>
     <t xml:space="preserve">1.39830696582794</t>
@@ -3164,7 +3164,7 @@
     <t xml:space="preserve">1.34317624568939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3565411567688</t>
+    <t xml:space="preserve">1.35654103755951</t>
   </si>
   <si>
     <t xml:space="preserve">1.35904717445374</t>
@@ -3173,61 +3173,61 @@
     <t xml:space="preserve">1.36489403247833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40276598930359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43466711044312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41251349449158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39390444755554</t>
+    <t xml:space="preserve">1.4027658700943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4346672296524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41251361370087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39390456676483</t>
   </si>
   <si>
     <t xml:space="preserve">1.39213228225708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3336466550827</t>
+    <t xml:space="preserve">1.33364677429199</t>
   </si>
   <si>
     <t xml:space="preserve">1.4479593038559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49049413204193</t>
+    <t xml:space="preserve">1.49049437046051</t>
   </si>
   <si>
     <t xml:space="preserve">1.5179648399353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53214299678802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58442544937134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52859854698181</t>
+    <t xml:space="preserve">1.53214287757874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58442556858063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52859842777252</t>
   </si>
   <si>
     <t xml:space="preserve">1.54897975921631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54454910755157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53834593296051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55872714519501</t>
+    <t xml:space="preserve">1.54454898834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5383460521698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5587272644043</t>
   </si>
   <si>
     <t xml:space="preserve">1.5764502286911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61455452442169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60657906532288</t>
+    <t xml:space="preserve">1.6145544052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60657894611359</t>
   </si>
   <si>
     <t xml:space="preserve">1.5693610906601</t>
@@ -3236,31 +3236,31 @@
     <t xml:space="preserve">1.58885622024536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60392069816589</t>
+    <t xml:space="preserve">1.6039205789566</t>
   </si>
   <si>
     <t xml:space="preserve">1.63582181930542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6251882314682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61278223991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58353936672211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51885080337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52062320709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4931526184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49758338928223</t>
+    <t xml:space="preserve">1.62518811225891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61278212070465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58353924751282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51885092258453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.520623087883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49315249919891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49758350849152</t>
   </si>
   <si>
     <t xml:space="preserve">1.52505385875702</t>
@@ -3278,25 +3278,25 @@
     <t xml:space="preserve">1.53037071228027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55341041088104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63848030567169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66329228878021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56404411792755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51707851886749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48872184753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4656822681427</t>
+    <t xml:space="preserve">1.55341029167175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6384801864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6632924079895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56404423713684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51707863807678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48872196674347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46568238735199</t>
   </si>
   <si>
     <t xml:space="preserve">1.42403340339661</t>
@@ -3320,16 +3320,16 @@
     <t xml:space="preserve">1.90520966053009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89634835720062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98319029808044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03635883331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09130001068115</t>
+    <t xml:space="preserve">1.89634823799133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98319005966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03635907173157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09129977226257</t>
   </si>
   <si>
     <t xml:space="preserve">2.17105293273926</t>
@@ -3341,25 +3341,25 @@
     <t xml:space="preserve">1.88925898075104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96192276477814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94597256183624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01863622665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10902285575867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0753493309021</t>
+    <t xml:space="preserve">1.96192312240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94597232341766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01863646507263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10902309417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07534909248352</t>
   </si>
   <si>
     <t xml:space="preserve">2.10547804832458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13737940788269</t>
+    <t xml:space="preserve">2.13737916946411</t>
   </si>
   <si>
     <t xml:space="preserve">2.12674570083618</t>
@@ -3374,109 +3374,109 @@
     <t xml:space="preserve">2.17636966705322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18168640136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24371695518494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1799144744873</t>
+    <t xml:space="preserve">2.18168616294861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24371647834778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17991423606873</t>
   </si>
   <si>
     <t xml:space="preserve">2.1232008934021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14624071121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19763731956482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30574655532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28625154495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31992506980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34828162193298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41740107536316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44575715065002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38372778892517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46348023414612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42449021339417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47411394119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51310443878174</t>
+    <t xml:space="preserve">2.14624047279358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19763708114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30574679374695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28625130653381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31992483139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34828186035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.417400598526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44575762748718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38372755050659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4634804725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42448997497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47411417961121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51310420036316</t>
   </si>
   <si>
     <t xml:space="preserve">2.50955986976624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43157935142517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4705696105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39613342285156</t>
+    <t xml:space="preserve">2.43157911300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47056937217712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39613366127014</t>
   </si>
   <si>
     <t xml:space="preserve">2.33942031860352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37841057777405</t>
+    <t xml:space="preserve">2.37841033935547</t>
   </si>
   <si>
     <t xml:space="preserve">2.21004319190979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38904452323914</t>
+    <t xml:space="preserve">2.38904428482056</t>
   </si>
   <si>
     <t xml:space="preserve">2.47943091392517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49183702468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5609564781189</t>
+    <t xml:space="preserve">2.4918372631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56095623970032</t>
   </si>
   <si>
     <t xml:space="preserve">2.65665984153748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64070916175842</t>
+    <t xml:space="preserve">2.640709400177</t>
   </si>
   <si>
     <t xml:space="preserve">2.63184762001038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65311527252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59640192985535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52373838424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33233094215393</t>
+    <t xml:space="preserve">2.65311503410339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59640216827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52373814582825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33233070373535</t>
   </si>
   <si>
     <t xml:space="preserve">2.31815266609192</t>
@@ -3488,22 +3488,22 @@
     <t xml:space="preserve">2.28270697593689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2756175994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25966715812683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30929112434387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27916216850281</t>
+    <t xml:space="preserve">2.27561807632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25966739654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30929160118103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27916240692139</t>
   </si>
   <si>
     <t xml:space="preserve">2.28802371025085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2685284614563</t>
+    <t xml:space="preserve">2.26852869987488</t>
   </si>
   <si>
     <t xml:space="preserve">2.36600470542908</t>
@@ -3512,37 +3512,37 @@
     <t xml:space="preserve">2.30751919746399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24017238616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14978551864624</t>
+    <t xml:space="preserve">2.24017190933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14978528022766</t>
   </si>
   <si>
     <t xml:space="preserve">2.16041898727417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17459726333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13915133476257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15687441825867</t>
+    <t xml:space="preserve">2.17459750175476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13915181159973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15687465667725</t>
   </si>
   <si>
     <t xml:space="preserve">2.05762648582458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16928052902222</t>
+    <t xml:space="preserve">2.1692807674408</t>
   </si>
   <si>
     <t xml:space="preserve">2.1958646774292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13560700416565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39258909225464</t>
+    <t xml:space="preserve">2.13560724258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39258861541748</t>
   </si>
   <si>
     <t xml:space="preserve">2.39436101913452</t>
@@ -3551,13 +3551,13 @@
     <t xml:space="preserve">2.06648802757263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99382400512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12142872810364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11965656280518</t>
+    <t xml:space="preserve">1.99382412433624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12142896652222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1196563243866</t>
   </si>
   <si>
     <t xml:space="preserve">2.09484457969666</t>
@@ -3569,55 +3569,55 @@
     <t xml:space="preserve">2.08066630363464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99205183982849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03458690643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02926969528198</t>
+    <t xml:space="preserve">1.99205160140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03458666801453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02926993370056</t>
   </si>
   <si>
     <t xml:space="preserve">1.93179392814636</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01509141921997</t>
+    <t xml:space="preserve">2.01509165763855</t>
   </si>
   <si>
     <t xml:space="preserve">2.00445771217346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86799156665802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90166485309601</t>
+    <t xml:space="preserve">1.86799168586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90166509151459</t>
   </si>
   <si>
     <t xml:space="preserve">1.80596160888672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6455694437027</t>
+    <t xml:space="preserve">1.64556932449341</t>
   </si>
   <si>
     <t xml:space="preserve">1.56315803527832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56847488880157</t>
+    <t xml:space="preserve">1.56847476959229</t>
   </si>
   <si>
     <t xml:space="preserve">1.6801290512085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5799947977066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59505927562714</t>
+    <t xml:space="preserve">1.57999467849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59505915641785</t>
   </si>
   <si>
     <t xml:space="preserve">1.65974771976471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78646647930145</t>
+    <t xml:space="preserve">1.78646636009216</t>
   </si>
   <si>
     <t xml:space="preserve">1.75545132160187</t>
@@ -3626,22 +3626,22 @@
     <t xml:space="preserve">1.73684227466583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73418378829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70671343803406</t>
+    <t xml:space="preserve">1.73418390750885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70671331882477</t>
   </si>
   <si>
     <t xml:space="preserve">1.65088629722595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66595065593719</t>
+    <t xml:space="preserve">1.66595077514648</t>
   </si>
   <si>
     <t xml:space="preserve">1.67924284934998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72798073291779</t>
+    <t xml:space="preserve">1.72798085212708</t>
   </si>
   <si>
     <t xml:space="preserve">1.8644472360611</t>
@@ -3650,7 +3650,7 @@
     <t xml:space="preserve">1.83431816101074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74570381641388</t>
+    <t xml:space="preserve">1.74570369720459</t>
   </si>
   <si>
     <t xml:space="preserve">1.78469407558441</t>
@@ -3659,13 +3659,13 @@
     <t xml:space="preserve">1.76254045963287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72886693477631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67038142681122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64113867282867</t>
+    <t xml:space="preserve">1.72886681556702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67038154602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64113879203796</t>
   </si>
   <si>
     <t xml:space="preserve">1.60126233100891</t>
@@ -3677,34 +3677,34 @@
     <t xml:space="preserve">1.71025788784027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70051038265228</t>
+    <t xml:space="preserve">1.70051050186157</t>
   </si>
   <si>
     <t xml:space="preserve">1.67835688591003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62961900234222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63936638832092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63050496578217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60923743247986</t>
+    <t xml:space="preserve">1.62961876392365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6393666267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63050508499146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60923755168915</t>
   </si>
   <si>
     <t xml:space="preserve">1.62075746059418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55075216293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46302378177643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4789742231369</t>
+    <t xml:space="preserve">1.55075204372406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46302366256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47897434234619</t>
   </si>
   <si>
     <t xml:space="preserve">1.5418906211853</t>
@@ -3713,31 +3713,31 @@
     <t xml:space="preserve">1.60835146903992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58974230289459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64468312263489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6074652671814</t>
+    <t xml:space="preserve">1.58974242210388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64468324184418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60746514797211</t>
   </si>
   <si>
     <t xml:space="preserve">1.6003760099411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52593994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52150917053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63139116764069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64734160900116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72266399860382</t>
+    <t xml:space="preserve">1.52594006061554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52150940895081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63139092922211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64734172821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72266387939453</t>
   </si>
   <si>
     <t xml:space="preserve">1.690762758255</t>
@@ -3752,28 +3752,28 @@
     <t xml:space="preserve">1.84495174884796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80773365497589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79887223243713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79532778263092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65797531604767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45593464374542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41871643066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46506798267365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4768830537796</t>
+    <t xml:space="preserve">1.80773377418518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79887235164642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79532766342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65797555446625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45593452453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41871654987335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46506786346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47688293457031</t>
   </si>
   <si>
     <t xml:space="preserve">1.48960697650909</t>
@@ -3782,10 +3782,10 @@
     <t xml:space="preserve">1.45779716968536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47597408294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43689334392548</t>
+    <t xml:space="preserve">1.47597420215607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43689358234406</t>
   </si>
   <si>
     <t xml:space="preserve">1.47415637969971</t>
@@ -3794,19 +3794,19 @@
     <t xml:space="preserve">1.48142731189728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41417241096497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37236499786377</t>
+    <t xml:space="preserve">1.41417229175568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37236511707306</t>
   </si>
   <si>
     <t xml:space="preserve">1.37872707843781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30147480964661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32783138751984</t>
+    <t xml:space="preserve">1.30147469043732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32783150672913</t>
   </si>
   <si>
     <t xml:space="preserve">1.37418270111084</t>
@@ -3818,19 +3818,19 @@
     <t xml:space="preserve">1.38599789142609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31510770320892</t>
+    <t xml:space="preserve">1.31510758399963</t>
   </si>
   <si>
     <t xml:space="preserve">1.28420662879944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27966225147247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3087455034256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32692265510559</t>
+    <t xml:space="preserve">1.27966237068176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30874562263489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3269225358963</t>
   </si>
   <si>
     <t xml:space="preserve">1.39781284332275</t>
@@ -3839,43 +3839,43 @@
     <t xml:space="preserve">1.37145614624023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35782337188721</t>
+    <t xml:space="preserve">1.3578234910965</t>
   </si>
   <si>
     <t xml:space="preserve">1.35691475868225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29693055152893</t>
+    <t xml:space="preserve">1.29693043231964</t>
   </si>
   <si>
     <t xml:space="preserve">1.31328988075256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33328461647034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41962552070618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42689621448517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40144848823547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44416427612305</t>
+    <t xml:space="preserve">1.33328449726105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41962540149689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42689633369446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40144836902618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44416439533234</t>
   </si>
   <si>
     <t xml:space="preserve">1.46961200237274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45961463451385</t>
+    <t xml:space="preserve">1.45961475372314</t>
   </si>
   <si>
     <t xml:space="preserve">1.48778915405273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49505984783173</t>
+    <t xml:space="preserve">1.49505996704102</t>
   </si>
   <si>
     <t xml:space="preserve">1.48869812488556</t>
@@ -3884,13 +3884,13 @@
     <t xml:space="preserve">1.51596355438232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5050573348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50051319599152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48051834106445</t>
+    <t xml:space="preserve">1.50505745410919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50051307678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48051846027374</t>
   </si>
   <si>
     <t xml:space="preserve">1.40326619148254</t>
@@ -3899,31 +3899,31 @@
     <t xml:space="preserve">1.43234932422638</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41144561767578</t>
+    <t xml:space="preserve">1.41144573688507</t>
   </si>
   <si>
     <t xml:space="preserve">1.34691727161407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34328198432922</t>
+    <t xml:space="preserve">1.34328186511993</t>
   </si>
   <si>
     <t xml:space="preserve">1.37327396869659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37600064277649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36236763000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39235985279083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33601117134094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35237038135529</t>
+    <t xml:space="preserve">1.37600040435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36236774921417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39235973358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33601105213165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35237050056458</t>
   </si>
   <si>
     <t xml:space="preserve">1.36963856220245</t>
@@ -3932,13 +3932,13 @@
     <t xml:space="preserve">1.35964131355286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41326344013214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43507599830627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41689884662628</t>
+    <t xml:space="preserve">1.41326332092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43507587909698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41689896583557</t>
   </si>
   <si>
     <t xml:space="preserve">1.46870338916779</t>
@@ -3953,7 +3953,7 @@
     <t xml:space="preserve">1.70591354370117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68591868877411</t>
+    <t xml:space="preserve">1.6859188079834</t>
   </si>
   <si>
     <t xml:space="preserve">1.58412742614746</t>
@@ -3965,13 +3965,13 @@
     <t xml:space="preserve">1.59139823913574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56322395801544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49960422515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55777072906494</t>
+    <t xml:space="preserve">1.56322383880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4996041059494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55777084827423</t>
   </si>
   <si>
     <t xml:space="preserve">1.55231761932373</t>
@@ -3983,19 +3983,19 @@
     <t xml:space="preserve">1.58140087127686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53777599334717</t>
+    <t xml:space="preserve">1.53777611255646</t>
   </si>
   <si>
     <t xml:space="preserve">1.52323436737061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56049728393555</t>
+    <t xml:space="preserve">1.56049740314484</t>
   </si>
   <si>
     <t xml:space="preserve">1.53323185443878</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59503364562988</t>
+    <t xml:space="preserve">1.59503352642059</t>
   </si>
   <si>
     <t xml:space="preserve">1.59412467479706</t>
@@ -4004,52 +4004,52 @@
     <t xml:space="preserve">1.64047610759735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65774440765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65865314006805</t>
+    <t xml:space="preserve">1.65774428844452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65865325927734</t>
   </si>
   <si>
     <t xml:space="preserve">1.65956211090088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6704683303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76317095756531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79225444793701</t>
+    <t xml:space="preserve">1.67046821117401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76317119598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79225432872772</t>
   </si>
   <si>
     <t xml:space="preserve">1.78861892223358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73045241832733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71772861480713</t>
+    <t xml:space="preserve">1.73045253753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71772849559784</t>
   </si>
   <si>
     <t xml:space="preserve">1.72681713104248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7713508605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73136126995087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75135600566864</t>
+    <t xml:space="preserve">1.77135074138641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73136138916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75135612487793</t>
   </si>
   <si>
     <t xml:space="preserve">1.78771007061005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84860289096832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8667801618576</t>
+    <t xml:space="preserve">1.84860301017761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86678004264832</t>
   </si>
   <si>
     <t xml:space="preserve">1.87223315238953</t>
@@ -4061,37 +4061,37 @@
     <t xml:space="preserve">1.93403506278992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94494116306305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90676951408386</t>
+    <t xml:space="preserve">1.94494140148163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90676963329315</t>
   </si>
   <si>
     <t xml:space="preserve">1.95402979850769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97038912773132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00492548942566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99583721160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97220683097839</t>
+    <t xml:space="preserve">1.97038900852203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00492525100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99583697319031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97220695018768</t>
   </si>
   <si>
     <t xml:space="preserve">1.97402453422546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99038362503052</t>
+    <t xml:space="preserve">1.9903838634491</t>
   </si>
   <si>
     <t xml:space="preserve">2.04491496086121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13398218154907</t>
+    <t xml:space="preserve">2.13398241996765</t>
   </si>
   <si>
     <t xml:space="preserve">2.15397691726685</t>
@@ -4115,28 +4115,28 @@
     <t xml:space="preserve">2.10308122634888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10126352310181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97584223747253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02128481864929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85223853588104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89041018486023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91222274303436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92676424980164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93585312366486</t>
+    <t xml:space="preserve">2.10126376152039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97584247589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02128505706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85223865509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89041006565094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91222286224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92676436901093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93585288524628</t>
   </si>
   <si>
     <t xml:space="preserve">1.93948805332184</t>
@@ -4145,37 +4145,37 @@
     <t xml:space="preserve">1.90131652355194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91404020786285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96311843395233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96857142448425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03219079971313</t>
+    <t xml:space="preserve">1.91404032707214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96311855316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96857118606567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03219103813171</t>
   </si>
   <si>
     <t xml:space="preserve">2.05945658683777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10489916801453</t>
+    <t xml:space="preserve">2.10489892959595</t>
   </si>
   <si>
     <t xml:space="preserve">2.12852907180786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12671160697937</t>
+    <t xml:space="preserve">2.12671136856079</t>
   </si>
   <si>
     <t xml:space="preserve">2.09944605827332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01946711540222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07218027114868</t>
+    <t xml:space="preserve">2.01946687698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07218050956726</t>
   </si>
   <si>
     <t xml:space="preserve">2.06309199333191</t>
@@ -4184,16 +4184,16 @@
     <t xml:space="preserve">2.03764414787292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00310778617859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01219630241394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01764941215515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00129008293152</t>
+    <t xml:space="preserve">2.00310754776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01219654083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01764965057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00128984451294</t>
   </si>
   <si>
     <t xml:space="preserve">2.27394556999207</t>
@@ -4202,13 +4202,13 @@
     <t xml:space="preserve">2.2484974861145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31756997108459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30848169326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33211159706116</t>
+    <t xml:space="preserve">2.31757044792175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3084819316864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33211183547974</t>
   </si>
   <si>
     <t xml:space="preserve">2.37210130691528</t>
@@ -4220,28 +4220,28 @@
     <t xml:space="preserve">2.37573671340942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40845537185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39754891395569</t>
+    <t xml:space="preserve">2.40845561027527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39754915237427</t>
   </si>
   <si>
     <t xml:space="preserve">2.38846063613892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39209604263306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35755968093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34483575820923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30666422843933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31575274467468</t>
+    <t xml:space="preserve">2.39209580421448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3575599193573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34483551979065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30666399002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3157525062561</t>
   </si>
   <si>
     <t xml:space="preserve">2.33574724197388</t>
@@ -4256,25 +4256,25 @@
     <t xml:space="preserve">2.40663766860962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40481996536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39027857780457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37937211990356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32302331924438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28666925430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18487787246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23213839530945</t>
+    <t xml:space="preserve">2.40481972694397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39027833938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37937188148499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32302355766296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28666949272156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18487811088562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23213815689087</t>
   </si>
   <si>
     <t xml:space="preserve">2.18306016921997</t>
@@ -4283,10 +4283,10 @@
     <t xml:space="preserve">2.14307069778442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20487284660339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20669031143188</t>
+    <t xml:space="preserve">2.20487260818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20669007301331</t>
   </si>
   <si>
     <t xml:space="preserve">2.17033648490906</t>
@@ -4295,46 +4295,46 @@
     <t xml:space="preserve">2.13943552970886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14670634269714</t>
+    <t xml:space="preserve">2.14670610427856</t>
   </si>
   <si>
     <t xml:space="preserve">2.14852404594421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19578433036804</t>
+    <t xml:space="preserve">2.19578409194946</t>
   </si>
   <si>
     <t xml:space="preserve">2.19033122062683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26849222183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24667978286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24304461479187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25213289260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30121111869812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.283034324646</t>
+    <t xml:space="preserve">2.26849246025085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24667954444885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24304437637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25213265419006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30121064186096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28303384780884</t>
   </si>
   <si>
     <t xml:space="preserve">2.34120035171509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47934579849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44844460487366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4884340763092</t>
+    <t xml:space="preserve">2.47934556007385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44844484329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48843383789062</t>
   </si>
   <si>
     <t xml:space="preserve">2.46843957901001</t>
@@ -4346,10 +4346,10 @@
     <t xml:space="preserve">2.45935130119324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45753335952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43390321731567</t>
+    <t xml:space="preserve">2.45753359794617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43390297889709</t>
   </si>
   <si>
     <t xml:space="preserve">2.51388216018677</t>
@@ -4358,19 +4358,19 @@
     <t xml:space="preserve">2.46480393409729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50297594070435</t>
+    <t xml:space="preserve">2.50297570228577</t>
   </si>
   <si>
     <t xml:space="preserve">2.4702570438385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40118455886841</t>
+    <t xml:space="preserve">2.40118432044983</t>
   </si>
   <si>
     <t xml:space="preserve">2.36664843559265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41754388809204</t>
+    <t xml:space="preserve">2.41754412651062</t>
   </si>
   <si>
     <t xml:space="preserve">2.2793984413147</t>
@@ -4385,16 +4385,16 @@
     <t xml:space="preserve">2.27030992507935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22668504714966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30302882194519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32484126091003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33029413223267</t>
+    <t xml:space="preserve">2.22668528556824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30302858352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32484102249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33029389381409</t>
   </si>
   <si>
     <t xml:space="preserve">2.29939317703247</t>
@@ -4412,7 +4412,7 @@
     <t xml:space="preserve">2.43935608863831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25599431991577</t>
+    <t xml:space="preserve">2.25599455833435</t>
   </si>
   <si>
     <t xml:space="preserve">2.28207540512085</t>
@@ -4421,13 +4421,13 @@
     <t xml:space="preserve">2.27462339401245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24854278564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22991371154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30070471763611</t>
+    <t xml:space="preserve">2.24854302406311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22991347312927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30070447921753</t>
   </si>
   <si>
     <t xml:space="preserve">2.31188225746155</t>
@@ -4442,25 +4442,25 @@
     <t xml:space="preserve">2.36404395103455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29697895050049</t>
+    <t xml:space="preserve">2.29697871208191</t>
   </si>
   <si>
     <t xml:space="preserve">2.32678556442261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34168863296509</t>
+    <t xml:space="preserve">2.34168839454651</t>
   </si>
   <si>
     <t xml:space="preserve">2.33982586860657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36963248252869</t>
+    <t xml:space="preserve">2.36963224411011</t>
   </si>
   <si>
     <t xml:space="preserve">2.36776971817017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32864856719971</t>
+    <t xml:space="preserve">2.32864832878113</t>
   </si>
   <si>
     <t xml:space="preserve">2.29884171485901</t>
@@ -4481,13 +4481,13 @@
     <t xml:space="preserve">2.29325270652771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33051133155823</t>
+    <t xml:space="preserve">2.33051156997681</t>
   </si>
   <si>
     <t xml:space="preserve">2.31374502182007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28952670097351</t>
+    <t xml:space="preserve">2.28952693939209</t>
   </si>
   <si>
     <t xml:space="preserve">2.22432494163513</t>
@@ -4496,7 +4496,7 @@
     <t xml:space="preserve">2.20569562911987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16098546981812</t>
+    <t xml:space="preserve">2.16098570823669</t>
   </si>
   <si>
     <t xml:space="preserve">2.14049363136292</t>
@@ -4526,7 +4526,7 @@
     <t xml:space="preserve">2.04921054840088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08460593223572</t>
+    <t xml:space="preserve">2.08460569381714</t>
   </si>
   <si>
     <t xml:space="preserve">2.06411385536194</t>
@@ -4562,7 +4562,7 @@
     <t xml:space="preserve">2.01754069328308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9989116191864</t>
+    <t xml:space="preserve">1.99891173839569</t>
   </si>
   <si>
     <t xml:space="preserve">2.01195240020752</t>
@@ -4577,7 +4577,7 @@
     <t xml:space="preserve">1.97469365596771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95606446266174</t>
+    <t xml:space="preserve">1.95606434345245</t>
   </si>
   <si>
     <t xml:space="preserve">1.92625784873962</t>
@@ -4586,13 +4586,13 @@
     <t xml:space="preserve">1.86478161811829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77349853515625</t>
+    <t xml:space="preserve">1.77349865436554</t>
   </si>
   <si>
     <t xml:space="preserve">1.78095018863678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78467607498169</t>
+    <t xml:space="preserve">1.7846759557724</t>
   </si>
   <si>
     <t xml:space="preserve">1.80330526828766</t>
@@ -4604,7 +4604,7 @@
     <t xml:space="preserve">1.80237364768982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75673222541809</t>
+    <t xml:space="preserve">1.75673234462738</t>
   </si>
   <si>
     <t xml:space="preserve">1.71109080314636</t>
@@ -4622,10 +4622,10 @@
     <t xml:space="preserve">1.69991326332092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6663806438446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61608183383942</t>
+    <t xml:space="preserve">1.66638076305389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61608195304871</t>
   </si>
   <si>
     <t xml:space="preserve">1.63005375862122</t>
@@ -4664,37 +4664,37 @@
     <t xml:space="preserve">1.55646860599518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56485152244568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57975494861603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61887633800507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60117852687836</t>
+    <t xml:space="preserve">1.56485164165497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57975506782532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61887621879578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60117840766907</t>
   </si>
   <si>
     <t xml:space="preserve">1.60956168174744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61980783939362</t>
+    <t xml:space="preserve">1.61980772018433</t>
   </si>
   <si>
     <t xml:space="preserve">1.62819087505341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59745275974274</t>
+    <t xml:space="preserve">1.59745287895203</t>
   </si>
   <si>
     <t xml:space="preserve">1.6123560667038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62073934078217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67755830287933</t>
+    <t xml:space="preserve">1.62073922157288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67755818367004</t>
   </si>
   <si>
     <t xml:space="preserve">1.64123129844666</t>
@@ -4703,10 +4703,10 @@
     <t xml:space="preserve">1.65706610679626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68966722488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69153022766113</t>
+    <t xml:space="preserve">1.68966710567474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69153010845184</t>
   </si>
   <si>
     <t xml:space="preserve">1.66917514801025</t>
@@ -4724,7 +4724,7 @@
     <t xml:space="preserve">1.72785711288452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84242641925812</t>
+    <t xml:space="preserve">1.84242653846741</t>
   </si>
   <si>
     <t xml:space="preserve">1.84801530838013</t>
@@ -4736,13 +4736,13 @@
     <t xml:space="preserve">1.92998373508453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97655689716339</t>
+    <t xml:space="preserve">1.9765567779541</t>
   </si>
   <si>
     <t xml:space="preserve">1.96165335178375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91508030891418</t>
+    <t xml:space="preserve">1.91508042812347</t>
   </si>
   <si>
     <t xml:space="preserve">1.93557250499725</t>
@@ -4778,7 +4778,7 @@
     <t xml:space="preserve">2.11441254615784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10137224197388</t>
+    <t xml:space="preserve">2.1013720035553</t>
   </si>
   <si>
     <t xml:space="preserve">2.03617000579834</t>
@@ -4793,25 +4793,25 @@
     <t xml:space="preserve">2.01008915901184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01567816734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98214554786682</t>
+    <t xml:space="preserve">2.01567792892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98214542865753</t>
   </si>
   <si>
     <t xml:space="preserve">1.90017700195312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91694343090057</t>
+    <t xml:space="preserve">1.91694331169128</t>
   </si>
   <si>
     <t xml:space="preserve">1.8927253484726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92812073230743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95420169830322</t>
+    <t xml:space="preserve">1.92812085151672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95420157909393</t>
   </si>
   <si>
     <t xml:space="preserve">2.06783962249756</t>
@@ -4820,7 +4820,7 @@
     <t xml:space="preserve">2.03989601135254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0752911567688</t>
+    <t xml:space="preserve">2.07529139518738</t>
   </si>
   <si>
     <t xml:space="preserve">2.09578347206116</t>
@@ -5946,6 +5946,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.44600009918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42000007629395</t>
   </si>
 </sst>
 </file>
@@ -71570,7 +71573,7 @@
     </row>
     <row r="2512">
       <c r="A2512" s="1" t="n">
-        <v>45975.6912615741</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2512" t="n">
         <v>539671</v>
@@ -71591,6 +71594,32 @@
         <v>1977</v>
       </c>
       <c r="H2512" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" s="1" t="n">
+        <v>45978.69125</v>
+      </c>
+      <c r="B2513" t="n">
+        <v>203175</v>
+      </c>
+      <c r="C2513" t="n">
+        <v>4.45800018310547</v>
+      </c>
+      <c r="D2513" t="n">
+        <v>4.41400003433228</v>
+      </c>
+      <c r="E2513" t="n">
+        <v>4.44000005722046</v>
+      </c>
+      <c r="F2513" t="n">
+        <v>4.42000007629395</v>
+      </c>
+      <c r="G2513" t="s">
+        <v>1978</v>
+      </c>
+      <c r="H2513" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/OVS.MI.xlsx
+++ b/data/OVS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1979" uniqueCount="1979">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1980" uniqueCount="1980">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,70 +38,70 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03756332397461</t>
+    <t xml:space="preserve">5.03756380081177</t>
   </si>
   <si>
     <t xml:space="preserve">OVS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89862442016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76365423202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64456272125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71998643875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65647125244141</t>
+    <t xml:space="preserve">4.89862394332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76365375518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64456224441528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71998596191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65647077560425</t>
   </si>
   <si>
     <t xml:space="preserve">4.78747177124023</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94228982925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69219923019409</t>
+    <t xml:space="preserve">4.94229030609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69219875335693</t>
   </si>
   <si>
     <t xml:space="preserve">4.60486459732056</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63662338256836</t>
+    <t xml:space="preserve">4.6366229057312</t>
   </si>
   <si>
     <t xml:space="preserve">4.616774559021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2515606880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22774219512939</t>
+    <t xml:space="preserve">4.25155973434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22774267196655</t>
   </si>
   <si>
     <t xml:space="preserve">4.53341007232666</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45798492431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47783422470093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49768352508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5135612487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4460768699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62868309020996</t>
+    <t xml:space="preserve">4.45798540115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47783374786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49768304824829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51356172561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44607734680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62868356704712</t>
   </si>
   <si>
     <t xml:space="preserve">4.59295654296875</t>
@@ -110,16 +110,16 @@
     <t xml:space="preserve">4.51753187179565</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54531955718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32698583602905</t>
+    <t xml:space="preserve">4.54531908035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32698535919189</t>
   </si>
   <si>
     <t xml:space="preserve">4.03322601318359</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02925729751587</t>
+    <t xml:space="preserve">4.02925682067871</t>
   </si>
   <si>
     <t xml:space="preserve">4.2793493270874</t>
@@ -128,31 +128,31 @@
     <t xml:space="preserve">4.22377252578735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38256025314331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30316781997681</t>
+    <t xml:space="preserve">4.38256120681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30316734313965</t>
   </si>
   <si>
     <t xml:space="preserve">4.469895362854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46592426300049</t>
+    <t xml:space="preserve">4.46592473983765</t>
   </si>
   <si>
     <t xml:space="preserve">4.48577404022217</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48974323272705</t>
+    <t xml:space="preserve">4.48974227905273</t>
   </si>
   <si>
     <t xml:space="preserve">4.271409034729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23965167999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43813705444336</t>
+    <t xml:space="preserve">4.23965120315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43813753128052</t>
   </si>
   <si>
     <t xml:space="preserve">4.5651683807373</t>
@@ -161,61 +161,61 @@
     <t xml:space="preserve">4.67235040664673</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71601724624634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58898639678955</t>
+    <t xml:space="preserve">4.71601676940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58898735046387</t>
   </si>
   <si>
     <t xml:space="preserve">4.50562238693237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52547073364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38653135299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43019771575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40241050720215</t>
+    <t xml:space="preserve">4.52547121047974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38653087615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43019819259644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40241003036499</t>
   </si>
   <si>
     <t xml:space="preserve">4.29125785827637</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12056016921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09674167633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0649847984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08880281448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15628719329834</t>
+    <t xml:space="preserve">4.12056064605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09674215316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06498432159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08880233764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15628671646118</t>
   </si>
   <si>
     <t xml:space="preserve">4.21186399459839</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04910612106323</t>
+    <t xml:space="preserve">4.04910516738892</t>
   </si>
   <si>
     <t xml:space="preserve">4.02131748199463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31110620498657</t>
+    <t xml:space="preserve">4.31110668182373</t>
   </si>
   <si>
     <t xml:space="preserve">4.16422700881958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23568201065063</t>
+    <t xml:space="preserve">4.23568153381348</t>
   </si>
   <si>
     <t xml:space="preserve">4.50959205627441</t>
@@ -227,7 +227,7 @@
     <t xml:space="preserve">4.54928922653198</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50165176391602</t>
+    <t xml:space="preserve">4.50165271759033</t>
   </si>
   <si>
     <t xml:space="preserve">4.56119823455811</t>
@@ -239,934 +239,934 @@
     <t xml:space="preserve">4.5215015411377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55325841903687</t>
+    <t xml:space="preserve">4.55325889587402</t>
   </si>
   <si>
     <t xml:space="preserve">4.5413498878479</t>
   </si>
   <si>
+    <t xml:space="preserve">4.56913709640503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5373797416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64853191375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70410776138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84304809570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89068412780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81525993347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87877464294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91053295135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75968408584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73826837539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76678705215454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90123510360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7341947555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56715393066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51826286315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47344732284546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47752046585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48974370956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63233947753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61196851730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55085611343384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51418876647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33085107803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94706273078918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13528966903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24529314041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26566314697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30233192443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25751543045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11084461212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09047412872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05299091339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18825435638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16380929946899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15566062927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15973472595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10677099227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04321432113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11899328231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16788291931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26158952713013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2004771232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20862483978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.233069896698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37159299850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36751842498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28603410720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27788639068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24121856689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25344133377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29825782775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22899627685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07254695892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17195749282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19232749938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10269689559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04158353805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13936376571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09862279891968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00084209442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99269390106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0334358215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19640254974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15158653259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08640003204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0611400604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35936975479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37566661834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44085359573364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41233348846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31862878799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31047916412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31455373764038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2697377204895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21677303314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18010568618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14343786239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11491823196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07417774200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06928825378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08232545852661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06439971923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00573062896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96010041236877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05462074279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13121604919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04647254943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98128509521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00410175323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98617482185364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02528762817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97476696968079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02365779876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05951023101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04810190200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05136203765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97965621948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03017568588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02039861679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99921202659607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07825136184692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14751291275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23714399337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20455121994019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22492265701294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01713895797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02202701568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93076658248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91283941268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8949134349823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87535715103149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94054460525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93402600288391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89654326438904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95521116256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00247192382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3797402381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38381433486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39196348190308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35529518127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2901086807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28196001052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32677698135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2941837310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33899879455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33492469787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34307289123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46529865264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48159503936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40825986862183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53863430023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55493068695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52641105651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50604009628296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43270492553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59567165374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68530416488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67308139801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60382032394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70160055160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8564190864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82382583618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77493619918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7993803024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74234247207642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78308439254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72604513168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7790093421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80752992630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86456775665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04790592193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01531219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89716100692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91753196716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88901329040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04383134841919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90531015396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9501256942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05198049545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97864532470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03160858154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08457374572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23939180374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19865036010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14568519592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19457578659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05605459213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06420230865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13346385955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11716651916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25161504745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18235349655151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17827987670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25568914413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27198505401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17420530319214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16605710983276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18642807006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10494422912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07235050201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94605207443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06827592849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98679351806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0369119644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3626823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39191722869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31256341934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27915048599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34597587585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35432863235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32091665267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33762311935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27079772949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27497386932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18726778030396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13297176361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20397329330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22903299331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25409173965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2624454498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18309116363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21232652664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17891454696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24991512298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24573850631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28332853317261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22485589981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30003356933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33344697952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40444707870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37521123886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40027046203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38356494903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37938737869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23320913314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3083872795105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2582688331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20814990997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13714838027954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11208963394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15385484695435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23738527297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32509279251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30421018600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29585742950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32926940917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48797798156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5380973815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59656810760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62580347061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68845272064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61327505111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57568597793579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44203662872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62162733078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68009901046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64251041412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37103462219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39609384536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38774156570435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24156188964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29168081283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19561958312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08285427093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88655567169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90743923187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81973123550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8030252456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84478998184204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83643817901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94502735137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9032621383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86567354202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87820339202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85314416885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81137800216675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9575572013855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92832183837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77796602249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.861496925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83226156234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72367000579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66102313995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69861078262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66937589645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63596343994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70278835296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6735520362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64014005661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71949434280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7904953956604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74872970581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7320237159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71114063262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67772912979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9157919883728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92414379119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89490938186646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84061431884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16220808029175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99932241439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02020502090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17056083679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09955930709839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95338106155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98679304122925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7863187789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68608140945435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60672760009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59419775009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61508083343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63178682327271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70696449279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58584547042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55243253707886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53990268707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57749223709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4897837638855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41043043136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44384241104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4939603805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47307729721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51902008056641</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.56913805007935</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53737926483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64853096008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70410776138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84304714202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89068412780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81525993347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87877559661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91053342819214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75968360900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73826837539673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7667875289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90123462677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7341947555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56715297698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51826333999634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4734468460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47752046585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48974418640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6323390007019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61196899414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55085611343384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51418924331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33085060119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94706320762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13529014587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24529314041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26566314697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30233144760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2575159072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11084461212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09047365188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05299139022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18825340270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16380882263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15566062927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15973472595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10677099227905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04321384429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11899280548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16788339614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26158905029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20047664642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20862531661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23307037353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37159299850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36751890182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28603410720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27788591384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24121856689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25344085693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29825735092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22899580001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07254695892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17195796966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19232797622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10269737243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04158353805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13936328887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09862279891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00084209442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99269342422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0334358215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19640302658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15158653259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08640003204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06114053726196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3593692779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37566709518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44085454940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41233348846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31862831115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31047964096069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31455278396606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26973724365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21677303314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1801061630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14343786239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11491823196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07417774200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06928873062134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08232545852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06439971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00573110580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96009993553162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05462074279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13121557235718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04647302627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.981285572052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00410175323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98617482185364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02528810501099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97476744651794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02365779876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05951023101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04810237884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05136156082153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97965621948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03017568588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02039813995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99921226501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07825136184692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14751291275024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23714351654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20455026626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22492218017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01713848114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02202796936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93076610565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91284012794495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89491295814514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87535715103149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94054436683655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93402576446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8965437412262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95521140098572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00247144699097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37974071502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38381481170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39196348190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35529565811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2901086807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28196001052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32677602767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29418325424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33899831771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33492469787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34307336807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46529865264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48159503936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40826034545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53863382339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55493021011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52641105651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50604057312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43270492553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59567213058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68530464172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6730809211731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60382080078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70160055160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85642004013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8238263130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77493572235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79938077926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74234247207642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78308486938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72604560852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77901029586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80752944946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86456823348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04790544509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01531267166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89716100692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91753196716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88901329040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04383087158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90530967712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9501256942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05198097229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97864484786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03160953521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08457374572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2393913269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19864988327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14568614959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19457626342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05605459213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0642032623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13346385955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11716651916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25161504745483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18235397338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17827987670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25568914413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27198505401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17420482635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16605663299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1864275932312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10494470596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07235097885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94605112075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06827640533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98679399490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03691148757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36268186569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39191818237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3125638961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27915096282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34597587585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35432863235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32091617584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33762264251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27079772949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27497434616089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1872673034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13297271728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2039737701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22903347015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25409126281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26244497299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18309116363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.212327003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17891454696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24991512298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24573850631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28332757949829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22485589981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30003356933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33344650268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40444660186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37521171569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40027093887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3835654258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37938785552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23320960998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30838775634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25826930999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20814990997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1371488571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11208963394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1538553237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23738527297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32509326934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30421018600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29585695266724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32926893234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48797845840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53809642791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59656810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62580394744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68845224380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61327457427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57568550109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44203615188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62162780761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68009853363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64251041412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37103462219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39609336853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38774156570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24156284332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29168128967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19562005996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08285331726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88655614852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90743923187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81973123550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80302572250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8447904586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83643770217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94502782821655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9032621383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86567306518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87820339202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85314416885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81137847900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95755767822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92832183837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77796602249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.861496925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83226108551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72367000579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66102266311646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69861078262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6693754196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63596343994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70278835296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67355155944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64013957977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71949434280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79049491882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74872970581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73202419281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71114110946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67772912979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9157919883728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92414426803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89490842819214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8406138420105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16220760345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99932241439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02020502090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17056035995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09955978393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95338106155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98679351806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78631925582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68608140945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60672807693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59419775009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6150803565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63178730010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70696449279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58584499359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55243301391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53990268707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57749176025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4897837638855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41043043136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44384241104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49396085739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47307777404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51902055740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5691385269165</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.59002113342285</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65684604644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64849185943604</t>
+    <t xml:space="preserve">4.65684652328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64849281311035</t>
   </si>
   <si>
     <t xml:space="preserve">4.59837436676025</t>
@@ -1178,7 +1178,7 @@
     <t xml:space="preserve">4.48560810089111</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4396653175354</t>
+    <t xml:space="preserve">4.43966627120972</t>
   </si>
   <si>
     <t xml:space="preserve">4.36031150817871</t>
@@ -1190,31 +1190,31 @@
     <t xml:space="preserve">4.18907308578491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16150760650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15148496627808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15649604797363</t>
+    <t xml:space="preserve">4.16150808334351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15148448944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15649557113647</t>
   </si>
   <si>
     <t xml:space="preserve">4.19324970245361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09802484512329</t>
+    <t xml:space="preserve">4.09802389144897</t>
   </si>
   <si>
     <t xml:space="preserve">4.1531548500061</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10303592681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12642621994019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16986131668091</t>
+    <t xml:space="preserve">4.10303640365601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12642526626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16986083984375</t>
   </si>
   <si>
     <t xml:space="preserve">4.17654418945312</t>
@@ -1223,7 +1223,7 @@
     <t xml:space="preserve">4.14313077926636</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16819000244141</t>
+    <t xml:space="preserve">4.16819047927856</t>
   </si>
   <si>
     <t xml:space="preserve">2.83002591133118</t>
@@ -1232,25 +1232,25 @@
     <t xml:space="preserve">2.90687417984009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84339070320129</t>
+    <t xml:space="preserve">2.84339046478271</t>
   </si>
   <si>
     <t xml:space="preserve">2.87179160118103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89350938796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80162477493286</t>
+    <t xml:space="preserve">2.89350914955139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80162525177002</t>
   </si>
   <si>
     <t xml:space="preserve">2.92358064651489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94863963127136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01713538169861</t>
+    <t xml:space="preserve">2.94863986968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01713514328003</t>
   </si>
   <si>
     <t xml:space="preserve">3.08061838150024</t>
@@ -1259,22 +1259,22 @@
     <t xml:space="preserve">3.17083144187927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14911365509033</t>
+    <t xml:space="preserve">3.14911389350891</t>
   </si>
   <si>
     <t xml:space="preserve">3.15746665000916</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14410185813904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17918515205383</t>
+    <t xml:space="preserve">3.14410209655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17918539047241</t>
   </si>
   <si>
     <t xml:space="preserve">3.17417311668396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10400724411011</t>
+    <t xml:space="preserve">3.10400748252869</t>
   </si>
   <si>
     <t xml:space="preserve">3.01212310791016</t>
@@ -1283,34 +1283,34 @@
     <t xml:space="preserve">3.02882957458496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94529795646667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95699262619019</t>
+    <t xml:space="preserve">2.94529819488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95699214935303</t>
   </si>
   <si>
     <t xml:space="preserve">2.89852118492126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84004878997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82501339912415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85007286071777</t>
+    <t xml:space="preserve">2.84004902839661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8250138759613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85007333755493</t>
   </si>
   <si>
     <t xml:space="preserve">2.74649548530579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55771470069885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54769134521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51093769073486</t>
+    <t xml:space="preserve">2.55771446228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54769158363342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51093792915344</t>
   </si>
   <si>
     <t xml:space="preserve">2.58945727348328</t>
@@ -1328,19 +1328,19 @@
     <t xml:space="preserve">2.47919631004333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41905355453491</t>
+    <t xml:space="preserve">2.41905379295349</t>
   </si>
   <si>
     <t xml:space="preserve">2.39566540718079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36058235168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36726474761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37728881835938</t>
+    <t xml:space="preserve">2.36058211326599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36726427078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3772885799408</t>
   </si>
   <si>
     <t xml:space="preserve">2.2753803730011</t>
@@ -1349,22 +1349,22 @@
     <t xml:space="preserve">2.31380534172058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2620153427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27203941345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41404223442078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38062930107117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30043935775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30211067199707</t>
+    <t xml:space="preserve">2.26201558113098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27203965187073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41404271125793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38062953948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30043959617615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30211091041565</t>
   </si>
   <si>
     <t xml:space="preserve">2.29709887504578</t>
@@ -1373,31 +1373,31 @@
     <t xml:space="preserve">2.32382845878601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33552312850952</t>
+    <t xml:space="preserve">2.33552289009094</t>
   </si>
   <si>
     <t xml:space="preserve">2.35389971733093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36559414863586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35055804252625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35222935676575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3555703163147</t>
+    <t xml:space="preserve">2.36559438705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35055828094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35222911834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35556983947754</t>
   </si>
   <si>
     <t xml:space="preserve">2.25533294677734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22025084495544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28039240837097</t>
+    <t xml:space="preserve">2.22025060653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28039264678955</t>
   </si>
   <si>
     <t xml:space="preserve">2.22526168823242</t>
@@ -1412,22 +1412,22 @@
     <t xml:space="preserve">2.44912481307983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42406558990479</t>
+    <t xml:space="preserve">2.42406535148621</t>
   </si>
   <si>
     <t xml:space="preserve">2.31881666183472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30879306793213</t>
+    <t xml:space="preserve">2.30879330635071</t>
   </si>
   <si>
     <t xml:space="preserve">2.34387588500977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33218145370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27370977401733</t>
+    <t xml:space="preserve">2.33218121528625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27371001243591</t>
   </si>
   <si>
     <t xml:space="preserve">2.18850874900818</t>
@@ -1442,10 +1442,10 @@
     <t xml:space="preserve">2.21022653579712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2118968963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05485892295837</t>
+    <t xml:space="preserve">2.21189737319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05485868453979</t>
   </si>
   <si>
     <t xml:space="preserve">2.01142287254333</t>
@@ -1460,34 +1460,34 @@
     <t xml:space="preserve">2.03815340995789</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1517550945282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17180228233337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18182563781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1667902469635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16846060752869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15509581565857</t>
+    <t xml:space="preserve">2.15175533294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17180252075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18182587623596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16679048538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16846084594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15509605407715</t>
   </si>
   <si>
     <t xml:space="preserve">2.15676641464233</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11500120162964</t>
+    <t xml:space="preserve">2.11500144004822</t>
   </si>
   <si>
     <t xml:space="preserve">2.07657742500305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08994245529175</t>
+    <t xml:space="preserve">2.08994221687317</t>
   </si>
   <si>
     <t xml:space="preserve">2.09829497337341</t>
@@ -1499,31 +1499,31 @@
     <t xml:space="preserve">2.09662485122681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09161257743835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02478742599487</t>
+    <t xml:space="preserve">2.09161281585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02478766441345</t>
   </si>
   <si>
     <t xml:space="preserve">2.02645897865295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12502455711365</t>
+    <t xml:space="preserve">2.12502479553223</t>
   </si>
   <si>
     <t xml:space="preserve">2.23695611953735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18683791160583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11834216117859</t>
+    <t xml:space="preserve">2.18683743476868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11834239959717</t>
   </si>
   <si>
     <t xml:space="preserve">2.06989502906799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06321310997009</t>
+    <t xml:space="preserve">2.06321263313293</t>
   </si>
   <si>
     <t xml:space="preserve">2.00139951705933</t>
@@ -1532,13 +1532,13 @@
     <t xml:space="preserve">1.99972856044769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98302292823792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94626939296722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87610328197479</t>
+    <t xml:space="preserve">1.9830230474472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94626927375793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8761031627655</t>
   </si>
   <si>
     <t xml:space="preserve">1.75748944282532</t>
@@ -1547,28 +1547,28 @@
     <t xml:space="preserve">1.695676445961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65391051769257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62885141372681</t>
+    <t xml:space="preserve">1.65391063690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62885165214539</t>
   </si>
   <si>
     <t xml:space="preserve">1.62968707084656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50439059734344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48601377010345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39663565158844</t>
+    <t xml:space="preserve">1.50439071655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48601388931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39663553237915</t>
   </si>
   <si>
     <t xml:space="preserve">1.31728136539459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2855396270752</t>
+    <t xml:space="preserve">1.28553974628448</t>
   </si>
   <si>
     <t xml:space="preserve">1.27133929729462</t>
@@ -1577,28 +1577,28 @@
     <t xml:space="preserve">1.24962174892426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24460971355438</t>
+    <t xml:space="preserve">1.2446094751358</t>
   </si>
   <si>
     <t xml:space="preserve">1.2897162437439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27635133266449</t>
+    <t xml:space="preserve">1.27635145187378</t>
   </si>
   <si>
     <t xml:space="preserve">1.30391657352448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31561100482941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31310510635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2838693857193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27969288825989</t>
+    <t xml:space="preserve">1.3156111240387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31310498714447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28386950492859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27969300746918</t>
   </si>
   <si>
     <t xml:space="preserve">1.33899998664856</t>
@@ -1607,16 +1607,16 @@
     <t xml:space="preserve">1.35152912139893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29472827911377</t>
+    <t xml:space="preserve">1.29472815990448</t>
   </si>
   <si>
     <t xml:space="preserve">1.29639852046967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2429393529892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25212776660919</t>
+    <t xml:space="preserve">1.24293923377991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2521276473999</t>
   </si>
   <si>
     <t xml:space="preserve">1.26799857616425</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">1.25630414485931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2579745054245</t>
+    <t xml:space="preserve">1.25797462463379</t>
   </si>
   <si>
     <t xml:space="preserve">1.26048040390015</t>
@@ -1640,49 +1640,49 @@
     <t xml:space="preserve">1.36823570728302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36990606784821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36405920982361</t>
+    <t xml:space="preserve">1.36990594863892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36405909061432</t>
   </si>
   <si>
     <t xml:space="preserve">1.34568238258362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31477534770966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34484672546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25129199028015</t>
+    <t xml:space="preserve">1.31477522850037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34484660625458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25129210948944</t>
   </si>
   <si>
     <t xml:space="preserve">1.23876285552979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06835901737213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962275326251984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989840686321259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.633163094520569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.703329801559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.705000162124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862038195133209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958098948001862</t>
+    <t xml:space="preserve">1.06835925579071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962275207042694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989840626716614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.633163154125214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.703329920768738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.705000221729279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.862038254737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958098888397217</t>
   </si>
   <si>
     <t xml:space="preserve">0.948074817657471</t>
@@ -1691,31 +1691,31 @@
     <t xml:space="preserve">0.848673403263092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.913827121257782</t>
+    <t xml:space="preserve">0.913827180862427</t>
   </si>
   <si>
     <t xml:space="preserve">0.9447340965271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9188392162323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917168855667114</t>
+    <t xml:space="preserve">0.918839156627655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917168796062469</t>
   </si>
   <si>
     <t xml:space="preserve">1.00487565994263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1477142572403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11430144309998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09926605224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13184344768524</t>
+    <t xml:space="preserve">1.14771413803101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11430132389069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0992659330368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13184332847595</t>
   </si>
   <si>
     <t xml:space="preserve">1.10344254970551</t>
@@ -1733,7 +1733,7 @@
     <t xml:space="preserve">0.999028921127319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01573550701141</t>
+    <t xml:space="preserve">1.0157356262207</t>
   </si>
   <si>
     <t xml:space="preserve">1.01322948932648</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">1.1276661157608</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12933743000031</t>
+    <t xml:space="preserve">1.12933731079102</t>
   </si>
   <si>
     <t xml:space="preserve">1.13017213344574</t>
@@ -1757,31 +1757,31 @@
     <t xml:space="preserve">1.1368545293808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11346662044525</t>
+    <t xml:space="preserve">1.11346650123596</t>
   </si>
   <si>
     <t xml:space="preserve">1.10260689258575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06585311889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0324410200119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07086515426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06334817409515</t>
+    <t xml:space="preserve">1.06585299968719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03244113922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07086527347565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06334793567657</t>
   </si>
   <si>
     <t xml:space="preserve">1.01907622814178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03494715690613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06501841545105</t>
+    <t xml:space="preserve">1.03494703769684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06501829624176</t>
   </si>
   <si>
     <t xml:space="preserve">1.12850165367126</t>
@@ -1790,13 +1790,13 @@
     <t xml:space="preserve">1.08506560325623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08673596382141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07253634929657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08088910579681</t>
+    <t xml:space="preserve">1.0867360830307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07253646850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0808892250061</t>
   </si>
   <si>
     <t xml:space="preserve">1.10511291027069</t>
@@ -1805,13 +1805,13 @@
     <t xml:space="preserve">1.07838320732117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10010075569153</t>
+    <t xml:space="preserve">1.10010087490082</t>
   </si>
   <si>
     <t xml:space="preserve">1.11263084411621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11012494564056</t>
+    <t xml:space="preserve">1.11012482643127</t>
   </si>
   <si>
     <t xml:space="preserve">1.22623288631439</t>
@@ -1823,22 +1823,22 @@
     <t xml:space="preserve">1.4158478975296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41417765617371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36071765422821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33064615726471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29806983470917</t>
+    <t xml:space="preserve">1.414177775383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36071753501892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.330646276474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29806971549988</t>
   </si>
   <si>
     <t xml:space="preserve">1.37324774265289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38744711875916</t>
+    <t xml:space="preserve">1.38744723796844</t>
   </si>
   <si>
     <t xml:space="preserve">1.32981145381927</t>
@@ -1850,13 +1850,13 @@
     <t xml:space="preserve">1.35487079620361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32897591590881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36572957038879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3715763092041</t>
+    <t xml:space="preserve">1.32897579669952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36572968959808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37157642841339</t>
   </si>
   <si>
     <t xml:space="preserve">1.40248322486877</t>
@@ -1868,10 +1868,10 @@
     <t xml:space="preserve">1.42169499397278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42253041267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42837738990784</t>
+    <t xml:space="preserve">1.42253053188324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42837727069855</t>
   </si>
   <si>
     <t xml:space="preserve">1.39997732639313</t>
@@ -1883,7 +1883,7 @@
     <t xml:space="preserve">1.39412951469421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4534364938736</t>
+    <t xml:space="preserve">1.45343661308289</t>
   </si>
   <si>
     <t xml:space="preserve">1.43589532375336</t>
@@ -1892,10 +1892,10 @@
     <t xml:space="preserve">1.52861428260803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61131024360657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59710967540741</t>
+    <t xml:space="preserve">1.61131012439728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5971097946167</t>
   </si>
   <si>
     <t xml:space="preserve">1.59376895427704</t>
@@ -1904,10 +1904,10 @@
     <t xml:space="preserve">1.5745564699173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55283868312836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55116772651672</t>
+    <t xml:space="preserve">1.55283880233765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55116760730743</t>
   </si>
   <si>
     <t xml:space="preserve">1.51441478729248</t>
@@ -1925,10 +1925,10 @@
     <t xml:space="preserve">1.38828277587891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38327085971832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33231663703918</t>
+    <t xml:space="preserve">1.38327062129974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33231675624847</t>
   </si>
   <si>
     <t xml:space="preserve">1.36739993095398</t>
@@ -1940,25 +1940,25 @@
     <t xml:space="preserve">1.30308103561401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32229340076447</t>
+    <t xml:space="preserve">1.32229351997375</t>
   </si>
   <si>
     <t xml:space="preserve">1.31644582748413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2989045381546</t>
+    <t xml:space="preserve">1.29890441894531</t>
   </si>
   <si>
     <t xml:space="preserve">1.30892860889435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31059908866882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31895172595978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29222214221954</t>
+    <t xml:space="preserve">1.31059896945953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31895184516907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29222226142883</t>
   </si>
   <si>
     <t xml:space="preserve">1.28721010684967</t>
@@ -1979,37 +1979,37 @@
     <t xml:space="preserve">1.3490229845047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34651696681976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30725836753845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26215076446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26883327960968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22205626964569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19198501110077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35821163654327</t>
+    <t xml:space="preserve">1.34651708602905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30725824832916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26215088367462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26883316040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22205638885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19198513031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35821151733398</t>
   </si>
   <si>
     <t xml:space="preserve">1.32312917709351</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28219902515411</t>
+    <t xml:space="preserve">1.28219890594482</t>
   </si>
   <si>
     <t xml:space="preserve">1.24043321609497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27384519577026</t>
+    <t xml:space="preserve">1.27384531497955</t>
   </si>
   <si>
     <t xml:space="preserve">1.2613160610199</t>
@@ -2018,10 +2018,10 @@
     <t xml:space="preserve">1.32646989822388</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33816432952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42503643035889</t>
+    <t xml:space="preserve">1.3381644487381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42503666877747</t>
   </si>
   <si>
     <t xml:space="preserve">1.48183739185333</t>
@@ -2036,19 +2036,19 @@
     <t xml:space="preserve">1.50355505943298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54448521137238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56369769573212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53863847255707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54866242408752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49186074733734</t>
+    <t xml:space="preserve">1.54448509216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56369757652283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53863835334778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54866254329681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49186086654663</t>
   </si>
   <si>
     <t xml:space="preserve">1.41668283939362</t>
@@ -2057,94 +2057,94 @@
     <t xml:space="preserve">1.39329481124878</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39078879356384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42002439498901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37491798400879</t>
+    <t xml:space="preserve">1.39078891277313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4200245141983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37491810321808</t>
   </si>
   <si>
     <t xml:space="preserve">1.34818840026855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33148193359375</t>
+    <t xml:space="preserve">1.33148181438446</t>
   </si>
   <si>
     <t xml:space="preserve">1.32814013957977</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29723429679871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29974031448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30224621295929</t>
+    <t xml:space="preserve">1.29723417758942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29974019527435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30224633216858</t>
   </si>
   <si>
     <t xml:space="preserve">1.33315229415894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26549255847931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24210357666016</t>
+    <t xml:space="preserve">1.26549243927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24210369586945</t>
   </si>
   <si>
     <t xml:space="preserve">1.38995325565338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37074172496796</t>
+    <t xml:space="preserve">1.37074184417725</t>
   </si>
   <si>
     <t xml:space="preserve">1.38494122028351</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38911855220795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37993013858795</t>
+    <t xml:space="preserve">1.38911843299866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37993001937866</t>
   </si>
   <si>
     <t xml:space="preserve">1.45260179042816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48851978778839</t>
+    <t xml:space="preserve">1.48852002620697</t>
   </si>
   <si>
     <t xml:space="preserve">1.49687266349792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50104916095734</t>
+    <t xml:space="preserve">1.50104892253876</t>
   </si>
   <si>
     <t xml:space="preserve">1.447589635849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39914155006409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5428147315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46095442771912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39162349700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41000032424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40833008289337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42921280860901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40749430656433</t>
+    <t xml:space="preserve">1.39914178848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54281485080719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46095454692841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39162361621857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41000044345856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40833020210266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4292129278183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40749442577362</t>
   </si>
   <si>
     <t xml:space="preserve">1.3339878320694</t>
@@ -2153,46 +2153,46 @@
     <t xml:space="preserve">1.32563412189484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33732855319977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36155319213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36907029151917</t>
+    <t xml:space="preserve">1.33732867240906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36155307292938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36907052993774</t>
   </si>
   <si>
     <t xml:space="preserve">1.44508373737335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43505966663361</t>
+    <t xml:space="preserve">1.4350597858429</t>
   </si>
   <si>
     <t xml:space="preserve">1.46596658229828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47181332111359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46513104438782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47264897823334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51190876960754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4701429605484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49269616603851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52276754379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54030871391296</t>
+    <t xml:space="preserve">1.47181344032288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46513092517853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47264909744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51190865039825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47014307975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4926962852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52276766300201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54030883312225</t>
   </si>
   <si>
     <t xml:space="preserve">1.53529667854309</t>
@@ -2201,13 +2201,13 @@
     <t xml:space="preserve">1.59794533252716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6062980890274</t>
+    <t xml:space="preserve">1.60629832744598</t>
   </si>
   <si>
     <t xml:space="preserve">1.58625102043152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64555788040161</t>
+    <t xml:space="preserve">1.64555776119232</t>
   </si>
   <si>
     <t xml:space="preserve">1.59293341636658</t>
@@ -2219,16 +2219,16 @@
     <t xml:space="preserve">1.58458054065704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56035602092743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54197919368744</t>
+    <t xml:space="preserve">1.56035625934601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54197931289673</t>
   </si>
   <si>
     <t xml:space="preserve">1.55868566036224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56620371341705</t>
+    <t xml:space="preserve">1.56620359420776</t>
   </si>
   <si>
     <t xml:space="preserve">1.56703841686249</t>
@@ -2237,73 +2237,73 @@
     <t xml:space="preserve">1.58708655834198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64973437786102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74078285694122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70737075805664</t>
+    <t xml:space="preserve">1.64973425865173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74078297615051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70737087726593</t>
   </si>
   <si>
     <t xml:space="preserve">1.71906530857086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72908854484558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7123829126358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73243010044098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69233465194702</t>
+    <t xml:space="preserve">1.72908842563629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71238279342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73243021965027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69233477115631</t>
   </si>
   <si>
     <t xml:space="preserve">1.76584219932556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74913573265076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72073554992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63887548446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60880410671234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68565225601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67061698436737</t>
+    <t xml:space="preserve">1.74913585186005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72073578834534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63887560367584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60880422592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68565237522125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67061710357666</t>
   </si>
   <si>
     <t xml:space="preserve">1.68732357025146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67562901973724</t>
+    <t xml:space="preserve">1.67562913894653</t>
   </si>
   <si>
     <t xml:space="preserve">1.68064117431641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61715698242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61548662185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62467515468597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61047446727753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64054584503174</t>
+    <t xml:space="preserve">1.61715686321259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6154865026474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62467503547668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61047470569611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64054596424103</t>
   </si>
   <si>
     <t xml:space="preserve">1.62383937835693</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">1.60963988304138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57789814472198</t>
+    <t xml:space="preserve">1.57789826393127</t>
   </si>
   <si>
     <t xml:space="preserve">1.59126305580139</t>
@@ -2321,49 +2321,49 @@
     <t xml:space="preserve">1.56202733516693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59209764003754</t>
+    <t xml:space="preserve">1.59209775924683</t>
   </si>
   <si>
     <t xml:space="preserve">1.59543931484222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58290934562683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60379207134247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6004513502121</t>
+    <t xml:space="preserve">1.58290910720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60379219055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60045146942139</t>
   </si>
   <si>
     <t xml:space="preserve">1.58541524410248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54532074928284</t>
+    <t xml:space="preserve">1.54532086849213</t>
   </si>
   <si>
     <t xml:space="preserve">1.54699110984802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57706248760223</t>
+    <t xml:space="preserve">1.57706236839294</t>
   </si>
   <si>
     <t xml:space="preserve">1.43756568431854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49436676502228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48935532569885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46763694286346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51274359226227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52610838413239</t>
+    <t xml:space="preserve">1.49436664581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48935556411743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46763706207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51274347305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52610850334167</t>
   </si>
   <si>
     <t xml:space="preserve">1.53195595741272</t>
@@ -2372,10 +2372,10 @@
     <t xml:space="preserve">1.54782688617706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5169198513031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50940275192261</t>
+    <t xml:space="preserve">1.51691997051239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5094028711319</t>
   </si>
   <si>
     <t xml:space="preserve">1.48267221450806</t>
@@ -2393,13 +2393,13 @@
     <t xml:space="preserve">1.16692590713501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13601970672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02742910385132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933039724826813</t>
+    <t xml:space="preserve">1.13601982593536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02742898464203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933039784431458</t>
   </si>
   <si>
     <t xml:space="preserve">0.776836335659027</t>
@@ -2408,13 +2408,13 @@
     <t xml:space="preserve">0.719200670719147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.695811748504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54670923948288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613534212112427</t>
+    <t xml:space="preserve">0.695811808109283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.546709179878235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613534152507782</t>
   </si>
   <si>
     <t xml:space="preserve">0.519561350345612</t>
@@ -2432,13 +2432,13 @@
     <t xml:space="preserve">0.701658546924591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.637340486049652</t>
+    <t xml:space="preserve">0.637340426445007</t>
   </si>
   <si>
     <t xml:space="preserve">0.682447016239166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.680358350276947</t>
+    <t xml:space="preserve">0.680358409881592</t>
   </si>
   <si>
     <t xml:space="preserve">0.687876343727112</t>
@@ -2447,13 +2447,13 @@
     <t xml:space="preserve">0.659893751144409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643604636192322</t>
+    <t xml:space="preserve">0.643604576587677</t>
   </si>
   <si>
     <t xml:space="preserve">0.659475445747375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.64318722486496</t>
+    <t xml:space="preserve">0.643187284469604</t>
   </si>
   <si>
     <t xml:space="preserve">0.627316355705261</t>
@@ -2465,19 +2465,19 @@
     <t xml:space="preserve">0.618127942085266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.660728454589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.646528899669647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.650705337524414</t>
+    <t xml:space="preserve">0.660728394985199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.646528840065002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.650705218315125</t>
   </si>
   <si>
     <t xml:space="preserve">0.638175249099731</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649869620800018</t>
+    <t xml:space="preserve">0.649869680404663</t>
   </si>
   <si>
     <t xml:space="preserve">0.640263795852661</t>
@@ -2486,43 +2486,43 @@
     <t xml:space="preserve">0.612281203269958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615621984004974</t>
+    <t xml:space="preserve">0.61562192440033</t>
   </si>
   <si>
     <t xml:space="preserve">0.610192537307739</t>
   </si>
   <si>
-    <t xml:space="preserve">0.6055988073349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.611028134822845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.651539981365204</t>
+    <t xml:space="preserve">0.605598747730255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61102819442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.651540040969849</t>
   </si>
   <si>
     <t xml:space="preserve">0.676599323749542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.654881656169891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.642351567745209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.641516804695129</t>
+    <t xml:space="preserve">0.654881715774536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.642351627349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.641516864299774</t>
   </si>
   <si>
     <t xml:space="preserve">0.655717313289642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639846444129944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.649034917354584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.668246507644653</t>
+    <t xml:space="preserve">0.639846503734589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.649034857749939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.668246567249298</t>
   </si>
   <si>
     <t xml:space="preserve">0.65028703212738</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">0.626480758190155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.609775125980377</t>
+    <t xml:space="preserve">0.609775185585022</t>
   </si>
   <si>
     <t xml:space="preserve">0.606016099452972</t>
@@ -2540,10 +2540,10 @@
     <t xml:space="preserve">0.629822432994843</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596827745437622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.574691951274872</t>
+    <t xml:space="preserve">0.596827864646912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.574691891670227</t>
   </si>
   <si>
     <t xml:space="preserve">0.581792593002319</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">0.574274480342865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.60183972120285</t>
+    <t xml:space="preserve">0.601839780807495</t>
   </si>
   <si>
     <t xml:space="preserve">0.630658030509949</t>
@@ -2564,43 +2564,43 @@
     <t xml:space="preserve">0.78936642408371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.763054192066193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768483519554138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827790498733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.835308492183685</t>
+    <t xml:space="preserve">0.763054251670837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.768483579158783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.82779061794281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83530855178833</t>
   </si>
   <si>
     <t xml:space="preserve">0.901297986507416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.910486459732056</t>
+    <t xml:space="preserve">0.910486400127411</t>
   </si>
   <si>
     <t xml:space="preserve">1.00571143627167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01072335243225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968957662582397</t>
+    <t xml:space="preserve">1.01072323322296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968957781791687</t>
   </si>
   <si>
     <t xml:space="preserve">0.877909064292908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.924685955047607</t>
+    <t xml:space="preserve">0.924685835838318</t>
   </si>
   <si>
     <t xml:space="preserve">0.925521612167358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938051640987396</t>
+    <t xml:space="preserve">0.938051581382751</t>
   </si>
   <si>
     <t xml:space="preserve">0.922180891036987</t>
@@ -2609,10 +2609,10 @@
     <t xml:space="preserve">0.892109513282776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.893779933452606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895450294017792</t>
+    <t xml:space="preserve">0.893779993057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895450234413147</t>
   </si>
   <si>
     <t xml:space="preserve">0.823614120483398</t>
@@ -2621,10 +2621,10 @@
     <t xml:space="preserve">0.781013667583466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.824867188930511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806072890758514</t>
+    <t xml:space="preserve">0.824867129325867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806073009967804</t>
   </si>
   <si>
     <t xml:space="preserve">0.78560745716095</t>
@@ -2633,13 +2633,13 @@
     <t xml:space="preserve">0.802313923835754</t>
   </si>
   <si>
-    <t xml:space="preserve">0.797719180583954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801895618438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798554837703705</t>
+    <t xml:space="preserve">0.797719240188599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801895678043365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79855489730835</t>
   </si>
   <si>
     <t xml:space="preserve">0.77641898393631</t>
@@ -2648,7 +2648,7 @@
     <t xml:space="preserve">0.782266676425934</t>
   </si>
   <si>
-    <t xml:space="preserve">0.766394913196564</t>
+    <t xml:space="preserve">0.766394972801208</t>
   </si>
   <si>
     <t xml:space="preserve">0.821525514125824</t>
@@ -2657,73 +2657,73 @@
     <t xml:space="preserve">0.795631527900696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.863708555698395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855355799198151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.844496965408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857861757278442</t>
+    <t xml:space="preserve">0.863708674907684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855355858802795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84449702501297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857861816883087</t>
   </si>
   <si>
     <t xml:space="preserve">0.836143374443054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.834890365600586</t>
+    <t xml:space="preserve">0.834890305995941</t>
   </si>
   <si>
     <t xml:space="preserve">0.838649392127991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.80022519826889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.773913025856018</t>
+    <t xml:space="preserve">0.80022531747818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.773912966251373</t>
   </si>
   <si>
     <t xml:space="preserve">0.789783835411072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.771825194358826</t>
+    <t xml:space="preserve">0.771825313568115</t>
   </si>
   <si>
     <t xml:space="preserve">0.767230570316315</t>
   </si>
   <si>
-    <t xml:space="preserve">0.775583386421204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786860466003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.792707145214081</t>
+    <t xml:space="preserve">0.775583326816559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786860525608063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.792707204818726</t>
   </si>
   <si>
     <t xml:space="preserve">0.758877813816071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.765977501869202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.800642669200897</t>
+    <t xml:space="preserve">0.765977561473846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800642609596252</t>
   </si>
   <si>
     <t xml:space="preserve">0.809831082820892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.799807846546173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.780178010463715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.770989596843719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.740918338298798</t>
+    <t xml:space="preserve">0.799807906150818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.780178129673004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.770989656448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.740918278694153</t>
   </si>
   <si>
     <t xml:space="preserve">0.717947661876678</t>
@@ -2750,46 +2750,46 @@
     <t xml:space="preserve">0.666576147079468</t>
   </si>
   <si>
-    <t xml:space="preserve">0.682029604911804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.687458992004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.685370326042175</t>
+    <t xml:space="preserve">0.682029545307159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.687459051609039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.68537038564682</t>
   </si>
   <si>
     <t xml:space="preserve">0.67785233259201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.69455873966217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.697482109069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.703747153282166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69831782579422</t>
+    <t xml:space="preserve">0.694558799266815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.697482228279114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.70374721288681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.698317766189575</t>
   </si>
   <si>
     <t xml:space="preserve">0.721288442611694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.72045361995697</t>
+    <t xml:space="preserve">0.72045373916626</t>
   </si>
   <si>
     <t xml:space="preserve">0.742588639259338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.767647862434387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.718365013599396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.715024352073669</t>
+    <t xml:space="preserve">0.767647981643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.718365073204041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.715024292469025</t>
   </si>
   <si>
     <t xml:space="preserve">0.7818483710289</t>
@@ -2801,40 +2801,40 @@
     <t xml:space="preserve">0.778925061225891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.79646623134613</t>
+    <t xml:space="preserve">0.79646635055542</t>
   </si>
   <si>
     <t xml:space="preserve">0.825284540653229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.850343823432922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860367774963379</t>
+    <t xml:space="preserve">0.850343704223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860367894172668</t>
   </si>
   <si>
     <t xml:space="preserve">0.847003042697906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.858696699142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843661308288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872062265872955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852014183998108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8545201420784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812755346298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807743310928345</t>
+    <t xml:space="preserve">0.858696579933167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843661367893219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872062206268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852014124393463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.854520201683044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812755405902863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8077432513237</t>
   </si>
   <si>
     <t xml:space="preserve">0.81317275762558</t>
@@ -2849,22 +2849,22 @@
     <t xml:space="preserve">0.820690751075745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.749689400196075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.710846960544586</t>
+    <t xml:space="preserve">0.749689340591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.710847020149231</t>
   </si>
   <si>
     <t xml:space="preserve">0.654464304447174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.63399875164032</t>
+    <t xml:space="preserve">0.633998811244965</t>
   </si>
   <si>
     <t xml:space="preserve">0.645275890827179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.660311043262482</t>
+    <t xml:space="preserve">0.660311102867126</t>
   </si>
   <si>
     <t xml:space="preserve">0.684534728527069</t>
@@ -2873,19 +2873,19 @@
     <t xml:space="preserve">0.68912935256958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.753030121326447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784354388713837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787696063518524</t>
+    <t xml:space="preserve">0.753030180931091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784354448318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787696123123169</t>
   </si>
   <si>
     <t xml:space="preserve">0.803148686885834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.856191456317902</t>
+    <t xml:space="preserve">0.856191396713257</t>
   </si>
   <si>
     <t xml:space="preserve">0.845331788063049</t>
@@ -2897,28 +2897,28 @@
     <t xml:space="preserve">0.900462329387665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.889603495597839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887097537517548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89043915271759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88125067949295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.904638886451721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892944276332855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902132749557495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882085502147675</t>
+    <t xml:space="preserve">0.889603555202484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887097477912903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.890439212322235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.881250739097595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.904638826847076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.89294421672821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.90213280916214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88208544254303</t>
   </si>
   <si>
     <t xml:space="preserve">0.867884993553162</t>
@@ -2930,94 +2930,94 @@
     <t xml:space="preserve">0.839484930038452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.841990947723389</t>
+    <t xml:space="preserve">0.841990888118744</t>
   </si>
   <si>
     <t xml:space="preserve">0.840320587158203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.859532177448273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905474305152893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849508225917816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872897088527679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906309962272644</t>
+    <t xml:space="preserve">0.859532237052917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905474364757538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849508166313171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872897028923035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906310021877289</t>
   </si>
   <si>
     <t xml:space="preserve">0.943898499011993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.953922390937805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957263350486755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965617001056671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978146195411682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961439728736877</t>
+    <t xml:space="preserve">0.95392245054245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957263290882111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965617060661316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978146016597748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961439669132233</t>
   </si>
   <si>
     <t xml:space="preserve">0.934710085391998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.902968347072601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87456750869751</t>
+    <t xml:space="preserve">0.902968406677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87456738948822</t>
   </si>
   <si>
     <t xml:space="preserve">0.852849781513214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.867050170898438</t>
+    <t xml:space="preserve">0.867050230503082</t>
   </si>
   <si>
     <t xml:space="preserve">0.878744721412659</t>
   </si>
   <si>
-    <t xml:space="preserve">0.907144844532013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931369304656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921345233917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927191913127899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912992477416992</t>
+    <t xml:space="preserve">0.907144784927368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931369245052338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921345114707947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927191972732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912992417812347</t>
   </si>
   <si>
     <t xml:space="preserve">0.947240054607391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.899626731872559</t>
+    <t xml:space="preserve">0.899626672267914</t>
   </si>
   <si>
     <t xml:space="preserve">0.92969799041748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938886404037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.937215983867645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.942228078842163</t>
+    <t xml:space="preserve">0.938886523246765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.937216103076935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942227959632874</t>
   </si>
   <si>
     <t xml:space="preserve">0.941392481327057</t>
@@ -3026,16 +3026,16 @@
     <t xml:space="preserve">0.94640451669693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.935545682907104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975640058517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14687848091125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18947911262512</t>
+    <t xml:space="preserve">0.935545802116394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975640177726746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14687860012054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18947923183441</t>
   </si>
   <si>
     <t xml:space="preserve">1.17360830307007</t>
@@ -3050,10 +3050,10 @@
     <t xml:space="preserve">1.17193794250488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1385258436203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10928928852081</t>
+    <t xml:space="preserve">1.13852596282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1092894077301</t>
   </si>
   <si>
     <t xml:space="preserve">1.11096060276031</t>
@@ -3065,7 +3065,7 @@
     <t xml:space="preserve">1.11179530620575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1310076713562</t>
+    <t xml:space="preserve">1.13100779056549</t>
   </si>
   <si>
     <t xml:space="preserve">1.12098371982574</t>
@@ -3080,16 +3080,16 @@
     <t xml:space="preserve">1.11513686180115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10761892795563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37742400169373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37241196632385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43923699855804</t>
+    <t xml:space="preserve">1.10761880874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37742388248444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37241208553314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43923711776733</t>
   </si>
   <si>
     <t xml:space="preserve">1.43673098087311</t>
@@ -3098,40 +3098,40 @@
     <t xml:space="preserve">1.44007170200348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4066596031189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41167175769806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3974711894989</t>
+    <t xml:space="preserve">1.40665984153748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41167163848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39747130870819</t>
   </si>
   <si>
     <t xml:space="preserve">1.43840134143829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47682535648346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45928418636322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44090723991394</t>
+    <t xml:space="preserve">1.47682547569275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45928430557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44090747833252</t>
   </si>
   <si>
     <t xml:space="preserve">1.43338942527771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48100173473358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41334211826324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42587125301361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58792126178741</t>
+    <t xml:space="preserve">1.48100197315216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41334199905396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4258713722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5879213809967</t>
   </si>
   <si>
     <t xml:space="preserve">1.55033278465271</t>
@@ -3140,22 +3140,22 @@
     <t xml:space="preserve">1.62634551525116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61214578151703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62049865722656</t>
+    <t xml:space="preserve">1.61214601993561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62049877643585</t>
   </si>
   <si>
     <t xml:space="preserve">1.61966300010681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62718105316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61381614208221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45677816867828</t>
+    <t xml:space="preserve">1.62718093395233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6138162612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45677828788757</t>
   </si>
   <si>
     <t xml:space="preserve">1.39830696582794</t>
@@ -3164,7 +3164,7 @@
     <t xml:space="preserve">1.34317624568939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35654103755951</t>
+    <t xml:space="preserve">1.3565411567688</t>
   </si>
   <si>
     <t xml:space="preserve">1.35904717445374</t>
@@ -3173,64 +3173,64 @@
     <t xml:space="preserve">1.36489403247833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4027658700943</t>
+    <t xml:space="preserve">1.40276598930359</t>
   </si>
   <si>
     <t xml:space="preserve">1.4346672296524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41251361370087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39390456676483</t>
+    <t xml:space="preserve">1.41251349449158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39390444755554</t>
   </si>
   <si>
     <t xml:space="preserve">1.39213228225708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33364677429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4479593038559</t>
+    <t xml:space="preserve">1.3336466550827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44795942306519</t>
   </si>
   <si>
     <t xml:space="preserve">1.49049437046051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5179648399353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53214287757874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58442556858063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52859842777252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54897975921631</t>
+    <t xml:space="preserve">1.51796472072601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53214299678802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58442544937134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52859854698181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5489798784256</t>
   </si>
   <si>
     <t xml:space="preserve">1.54454898834229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5383460521698</t>
+    <t xml:space="preserve">1.53834593296051</t>
   </si>
   <si>
     <t xml:space="preserve">1.5587272644043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5764502286911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6145544052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60657894611359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5693610906601</t>
+    <t xml:space="preserve">1.57645034790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61455452442169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60657906532288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56936120986938</t>
   </si>
   <si>
     <t xml:space="preserve">1.58885622024536</t>
@@ -3242,7 +3242,7 @@
     <t xml:space="preserve">1.63582181930542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62518811225891</t>
+    <t xml:space="preserve">1.6251882314682</t>
   </si>
   <si>
     <t xml:space="preserve">1.61278212070465</t>
@@ -3251,34 +3251,34 @@
     <t xml:space="preserve">1.58353924751282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51885092258453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.520623087883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49315249919891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49758350849152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52505385875702</t>
+    <t xml:space="preserve">1.51885104179382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52062320709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4931526184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49758338928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52505373954773</t>
   </si>
   <si>
     <t xml:space="preserve">1.50733089447021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50112795829773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54011833667755</t>
+    <t xml:space="preserve">1.50112807750702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54011845588684</t>
   </si>
   <si>
     <t xml:space="preserve">1.53037071228027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55341029167175</t>
+    <t xml:space="preserve">1.55341041088104</t>
   </si>
   <si>
     <t xml:space="preserve">1.6384801864624</t>
@@ -3287,16 +3287,16 @@
     <t xml:space="preserve">1.6632924079895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56404423713684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51707863807678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48872196674347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46568238735199</t>
+    <t xml:space="preserve">1.56404411792755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5170783996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48872184753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4656822681427</t>
   </si>
   <si>
     <t xml:space="preserve">1.42403340339661</t>
@@ -3305,7 +3305,7 @@
     <t xml:space="preserve">1.44707322120667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46656835079193</t>
+    <t xml:space="preserve">1.46656823158264</t>
   </si>
   <si>
     <t xml:space="preserve">1.61809897422791</t>
@@ -3314,16 +3314,16 @@
     <t xml:space="preserve">1.82900106906891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84672403335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90520966053009</t>
+    <t xml:space="preserve">1.846724152565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90520942211151</t>
   </si>
   <si>
     <t xml:space="preserve">1.89634823799133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98319005966187</t>
+    <t xml:space="preserve">1.98319029808044</t>
   </si>
   <si>
     <t xml:space="preserve">2.03635907173157</t>
@@ -3335,7 +3335,7 @@
     <t xml:space="preserve">2.17105293273926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96015059947968</t>
+    <t xml:space="preserve">1.96015048027039</t>
   </si>
   <si>
     <t xml:space="preserve">1.88925898075104</t>
@@ -3344,25 +3344,25 @@
     <t xml:space="preserve">1.96192312240601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94597232341766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01863646507263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10902309417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07534909248352</t>
+    <t xml:space="preserve">1.94597244262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01863622665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10902261734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0753493309021</t>
   </si>
   <si>
     <t xml:space="preserve">2.10547804832458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13737916946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12674570083618</t>
+    <t xml:space="preserve">2.13737940788269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1267454624176</t>
   </si>
   <si>
     <t xml:space="preserve">2.17814183235168</t>
@@ -3371,22 +3371,22 @@
     <t xml:space="preserve">2.16396355628967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17636966705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18168616294861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24371647834778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17991423606873</t>
+    <t xml:space="preserve">2.1763699054718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18168640136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24371695518494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1799144744873</t>
   </si>
   <si>
     <t xml:space="preserve">2.1232008934021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14624047279358</t>
+    <t xml:space="preserve">2.14624071121216</t>
   </si>
   <si>
     <t xml:space="preserve">2.19763708114624</t>
@@ -3395,34 +3395,34 @@
     <t xml:space="preserve">2.30574679374695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28625130653381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31992483139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34828186035156</t>
+    <t xml:space="preserve">2.28625154495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31992506980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34828162193298</t>
   </si>
   <si>
     <t xml:space="preserve">2.417400598526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44575762748718</t>
+    <t xml:space="preserve">2.4457573890686</t>
   </si>
   <si>
     <t xml:space="preserve">2.38372755050659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4634804725647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42448997497559</t>
+    <t xml:space="preserve">2.46348023414612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42449021339417</t>
   </si>
   <si>
     <t xml:space="preserve">2.47411417961121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51310420036316</t>
+    <t xml:space="preserve">2.51310443878174</t>
   </si>
   <si>
     <t xml:space="preserve">2.50955986976624</t>
@@ -3431,49 +3431,49 @@
     <t xml:space="preserve">2.43157911300659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47056937217712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39613366127014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33942031860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37841033935547</t>
+    <t xml:space="preserve">2.4705696105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39613342285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33942008018494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37841057777405</t>
   </si>
   <si>
     <t xml:space="preserve">2.21004319190979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38904428482056</t>
+    <t xml:space="preserve">2.38904452323914</t>
   </si>
   <si>
     <t xml:space="preserve">2.47943091392517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4918372631073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56095623970032</t>
+    <t xml:space="preserve">2.49183702468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56095600128174</t>
   </si>
   <si>
     <t xml:space="preserve">2.65665984153748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.640709400177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63184762001038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65311503410339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59640216827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52373814582825</t>
+    <t xml:space="preserve">2.64070916175842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63184785842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65311527252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59640169143677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52373790740967</t>
   </si>
   <si>
     <t xml:space="preserve">2.33233070373535</t>
@@ -3485,79 +3485,79 @@
     <t xml:space="preserve">2.29688501358032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28270697593689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27561807632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25966739654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30929160118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27916240692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28802371025085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26852869987488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36600470542908</t>
+    <t xml:space="preserve">2.28270721435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2756175994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25966715812683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30929136276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27916216850281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28802394866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2685284614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3660044670105</t>
   </si>
   <si>
     <t xml:space="preserve">2.30751919746399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24017190933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14978528022766</t>
+    <t xml:space="preserve">2.24017214775085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14978575706482</t>
   </si>
   <si>
     <t xml:space="preserve">2.16041898727417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17459750175476</t>
+    <t xml:space="preserve">2.17459726333618</t>
   </si>
   <si>
     <t xml:space="preserve">2.13915181159973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15687465667725</t>
+    <t xml:space="preserve">2.15687441825867</t>
   </si>
   <si>
     <t xml:space="preserve">2.05762648582458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1692807674408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1958646774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13560724258423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39258861541748</t>
+    <t xml:space="preserve">2.16928052902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19586443901062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13560700416565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39258885383606</t>
   </si>
   <si>
     <t xml:space="preserve">2.39436101913452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06648802757263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99382412433624</t>
+    <t xml:space="preserve">2.06648778915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99382388591766</t>
   </si>
   <si>
     <t xml:space="preserve">2.12142896652222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1196563243866</t>
+    <t xml:space="preserve">2.11965656280518</t>
   </si>
   <si>
     <t xml:space="preserve">2.09484457969666</t>
@@ -3566,40 +3566,40 @@
     <t xml:space="preserve">2.01331925392151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08066630363464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99205160140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03458666801453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02926993370056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93179392814636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01509165763855</t>
+    <t xml:space="preserve">2.08066606521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99205148220062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03458690643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0292694568634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93179380893707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01509141921997</t>
   </si>
   <si>
     <t xml:space="preserve">2.00445771217346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86799168586731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90166509151459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80596160888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64556932449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56315803527832</t>
+    <t xml:space="preserve">1.86799156665802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90166485309601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80596172809601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6455694437027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56315815448761</t>
   </si>
   <si>
     <t xml:space="preserve">1.56847476959229</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">1.6801290512085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57999467849731</t>
+    <t xml:space="preserve">1.57999491691589</t>
   </si>
   <si>
     <t xml:space="preserve">1.59505915641785</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">1.65974771976471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78646636009216</t>
+    <t xml:space="preserve">1.78646647930145</t>
   </si>
   <si>
     <t xml:space="preserve">1.75545132160187</t>
@@ -3626,7 +3626,7 @@
     <t xml:space="preserve">1.73684227466583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73418390750885</t>
+    <t xml:space="preserve">1.73418378829956</t>
   </si>
   <si>
     <t xml:space="preserve">1.70671331882477</t>
@@ -3635,7 +3635,7 @@
     <t xml:space="preserve">1.65088629722595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66595077514648</t>
+    <t xml:space="preserve">1.66595065593719</t>
   </si>
   <si>
     <t xml:space="preserve">1.67924284934998</t>
@@ -3644,28 +3644,28 @@
     <t xml:space="preserve">1.72798085212708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8644472360611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83431816101074</t>
+    <t xml:space="preserve">1.86444711685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83431804180145</t>
   </si>
   <si>
     <t xml:space="preserve">1.74570369720459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78469407558441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76254045963287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72886681556702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67038154602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64113879203796</t>
+    <t xml:space="preserve">1.7846941947937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76254034042358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72886693477631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67038142681122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64113867282867</t>
   </si>
   <si>
     <t xml:space="preserve">1.60126233100891</t>
@@ -3677,22 +3677,22 @@
     <t xml:space="preserve">1.71025788784027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70051050186157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67835688591003</t>
+    <t xml:space="preserve">1.70051038265228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67835676670074</t>
   </si>
   <si>
     <t xml:space="preserve">1.62961876392365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6393666267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63050508499146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60923755168915</t>
+    <t xml:space="preserve">1.63936638832092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63050496578217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60923743247986</t>
   </si>
   <si>
     <t xml:space="preserve">1.62075746059418</t>
@@ -3701,16 +3701,16 @@
     <t xml:space="preserve">1.55075204372406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46302366256714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47897434234619</t>
+    <t xml:space="preserve">1.46302378177643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47897446155548</t>
   </si>
   <si>
     <t xml:space="preserve">1.5418906211853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60835146903992</t>
+    <t xml:space="preserve">1.60835134983063</t>
   </si>
   <si>
     <t xml:space="preserve">1.58974242210388</t>
@@ -3719,34 +3719,34 @@
     <t xml:space="preserve">1.64468324184418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60746514797211</t>
+    <t xml:space="preserve">1.60746538639069</t>
   </si>
   <si>
     <t xml:space="preserve">1.6003760099411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52594006061554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52150940895081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63139092922211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64734172821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72266387939453</t>
+    <t xml:space="preserve">1.52593994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52150928974152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6313910484314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64734160900116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72266411781311</t>
   </si>
   <si>
     <t xml:space="preserve">1.690762758255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71646106243134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78114950656891</t>
+    <t xml:space="preserve">1.71646094322205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78114938735962</t>
   </si>
   <si>
     <t xml:space="preserve">1.84495174884796</t>
@@ -3755,13 +3755,13 @@
     <t xml:space="preserve">1.80773377418518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79887235164642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79532766342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65797555446625</t>
+    <t xml:space="preserve">1.79887223243713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79532790184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65797543525696</t>
   </si>
   <si>
     <t xml:space="preserve">1.45593452453613</t>
@@ -3770,22 +3770,22 @@
     <t xml:space="preserve">1.41871654987335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46506786346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47688293457031</t>
+    <t xml:space="preserve">1.46506798267365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4768830537796</t>
   </si>
   <si>
     <t xml:space="preserve">1.48960697650909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45779716968536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47597420215607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43689358234406</t>
+    <t xml:space="preserve">1.45779705047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47597408294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43689346313477</t>
   </si>
   <si>
     <t xml:space="preserve">1.47415637969971</t>
@@ -3803,13 +3803,13 @@
     <t xml:space="preserve">1.37872707843781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30147469043732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32783150672913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37418270111084</t>
+    <t xml:space="preserve">1.30147480964661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32783138751984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37418282032013</t>
   </si>
   <si>
     <t xml:space="preserve">1.40781033039093</t>
@@ -3821,22 +3821,22 @@
     <t xml:space="preserve">1.31510758399963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28420662879944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27966237068176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30874562263489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3269225358963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39781284332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37145614624023</t>
+    <t xml:space="preserve">1.28420650959015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27966225147247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30874574184418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32692265510559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39781296253204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37145626544952</t>
   </si>
   <si>
     <t xml:space="preserve">1.3578234910965</t>
@@ -3848,7 +3848,7 @@
     <t xml:space="preserve">1.29693043231964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31328988075256</t>
+    <t xml:space="preserve">1.31328976154327</t>
   </si>
   <si>
     <t xml:space="preserve">1.33328449726105</t>
@@ -3866,7 +3866,7 @@
     <t xml:space="preserve">1.44416439533234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46961200237274</t>
+    <t xml:space="preserve">1.46961212158203</t>
   </si>
   <si>
     <t xml:space="preserve">1.45961475372314</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">1.48778915405273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49505996704102</t>
+    <t xml:space="preserve">1.49506008625031</t>
   </si>
   <si>
     <t xml:space="preserve">1.48869812488556</t>
@@ -3890,10 +3890,10 @@
     <t xml:space="preserve">1.50051307678223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48051846027374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40326619148254</t>
+    <t xml:space="preserve">1.48051834106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40326607227325</t>
   </si>
   <si>
     <t xml:space="preserve">1.43234932422638</t>
@@ -3905,46 +3905,46 @@
     <t xml:space="preserve">1.34691727161407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34328186511993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37327396869659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37600040435791</t>
+    <t xml:space="preserve">1.34328198432922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3732738494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3760005235672</t>
   </si>
   <si>
     <t xml:space="preserve">1.36236774921417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39235973358154</t>
+    <t xml:space="preserve">1.39235985279083</t>
   </si>
   <si>
     <t xml:space="preserve">1.33601105213165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35237050056458</t>
+    <t xml:space="preserve">1.35237038135529</t>
   </si>
   <si>
     <t xml:space="preserve">1.36963856220245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35964131355286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41326332092285</t>
+    <t xml:space="preserve">1.35964119434357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41326344013214</t>
   </si>
   <si>
     <t xml:space="preserve">1.43507587909698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41689896583557</t>
+    <t xml:space="preserve">1.41689884662628</t>
   </si>
   <si>
     <t xml:space="preserve">1.46870338916779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4123547077179</t>
+    <t xml:space="preserve">1.41235458850861</t>
   </si>
   <si>
     <t xml:space="preserve">1.39872181415558</t>
@@ -3968,10 +3968,10 @@
     <t xml:space="preserve">1.56322383880615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4996041059494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55777084827423</t>
+    <t xml:space="preserve">1.49960422515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55777072906494</t>
   </si>
   <si>
     <t xml:space="preserve">1.55231761932373</t>
@@ -3980,16 +3980,16 @@
     <t xml:space="preserve">1.64956474304199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58140087127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53777611255646</t>
+    <t xml:space="preserve">1.58140099048615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53777599334717</t>
   </si>
   <si>
     <t xml:space="preserve">1.52323436737061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56049740314484</t>
+    <t xml:space="preserve">1.56049728393555</t>
   </si>
   <si>
     <t xml:space="preserve">1.53323185443878</t>
@@ -4010,37 +4010,37 @@
     <t xml:space="preserve">1.65865325927734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65956211090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67046821117401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76317119598389</t>
+    <t xml:space="preserve">1.65956199169159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6704683303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7631710767746</t>
   </si>
   <si>
     <t xml:space="preserve">1.79225432872772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78861892223358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73045253753662</t>
+    <t xml:space="preserve">1.78861904144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73045241832733</t>
   </si>
   <si>
     <t xml:space="preserve">1.71772849559784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72681713104248</t>
+    <t xml:space="preserve">1.72681701183319</t>
   </si>
   <si>
     <t xml:space="preserve">1.77135074138641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73136138916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75135612487793</t>
+    <t xml:space="preserve">1.73136126995087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75135600566864</t>
   </si>
   <si>
     <t xml:space="preserve">1.78771007061005</t>
@@ -4049,16 +4049,16 @@
     <t xml:space="preserve">1.84860301017761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86678004264832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87223315238953</t>
+    <t xml:space="preserve">1.8667801618576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87223327159882</t>
   </si>
   <si>
     <t xml:space="preserve">1.89949882030487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93403506278992</t>
+    <t xml:space="preserve">1.93403518199921</t>
   </si>
   <si>
     <t xml:space="preserve">1.94494140148163</t>
@@ -4067,31 +4067,31 @@
     <t xml:space="preserve">1.90676963329315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95402979850769</t>
+    <t xml:space="preserve">1.9540296792984</t>
   </si>
   <si>
     <t xml:space="preserve">1.97038900852203</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00492525100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99583697319031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97220695018768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97402453422546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9903838634491</t>
+    <t xml:space="preserve">2.00492548942566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99583685398102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97220683097839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97402465343475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99038398265839</t>
   </si>
   <si>
     <t xml:space="preserve">2.04491496086121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13398241996765</t>
+    <t xml:space="preserve">2.13398265838623</t>
   </si>
   <si>
     <t xml:space="preserve">2.15397691726685</t>
@@ -4103,55 +4103,55 @@
     <t xml:space="preserve">2.11944079399109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13761758804321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16851854324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11035227775574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10308122634888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10126376152039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97584247589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02128505706787</t>
+    <t xml:space="preserve">2.13761782646179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16851878166199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11035203933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10308146476746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10126399993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97584235668182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02128481864929</t>
   </si>
   <si>
     <t xml:space="preserve">1.85223865509033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89041006565094</t>
+    <t xml:space="preserve">1.89041018486023</t>
   </si>
   <si>
     <t xml:space="preserve">1.91222286224365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92676436901093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93585288524628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93948805332184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90131652355194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91404032707214</t>
+    <t xml:space="preserve">1.92676424980164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93585300445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93948817253113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90131664276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91404044628143</t>
   </si>
   <si>
     <t xml:space="preserve">1.96311855316162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96857118606567</t>
+    <t xml:space="preserve">1.96857130527496</t>
   </si>
   <si>
     <t xml:space="preserve">2.03219103813171</t>
@@ -4160,7 +4160,7 @@
     <t xml:space="preserve">2.05945658683777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10489892959595</t>
+    <t xml:space="preserve">2.10489916801453</t>
   </si>
   <si>
     <t xml:space="preserve">2.12852907180786</t>
@@ -4178,22 +4178,22 @@
     <t xml:space="preserve">2.07218050956726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06309199333191</t>
+    <t xml:space="preserve">2.06309175491333</t>
   </si>
   <si>
     <t xml:space="preserve">2.03764414787292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00310754776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01219654083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01764965057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00128984451294</t>
+    <t xml:space="preserve">2.00310778617859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01219630241394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01764941215515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00129008293152</t>
   </si>
   <si>
     <t xml:space="preserve">2.27394556999207</t>
@@ -4202,13 +4202,13 @@
     <t xml:space="preserve">2.2484974861145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31757044792175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3084819316864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33211183547974</t>
+    <t xml:space="preserve">2.31757020950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30848169326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33211159706116</t>
   </si>
   <si>
     <t xml:space="preserve">2.37210130691528</t>
@@ -4232,13 +4232,13 @@
     <t xml:space="preserve">2.39209580421448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3575599193573</t>
+    <t xml:space="preserve">2.35755968093872</t>
   </si>
   <si>
     <t xml:space="preserve">2.34483551979065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30666399002075</t>
+    <t xml:space="preserve">2.30666422843933</t>
   </si>
   <si>
     <t xml:space="preserve">2.3157525062561</t>
@@ -4262,10 +4262,10 @@
     <t xml:space="preserve">2.39027833938599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37937188148499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32302355766296</t>
+    <t xml:space="preserve">2.37937211990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32302331924438</t>
   </si>
   <si>
     <t xml:space="preserve">2.28666949272156</t>
@@ -4280,13 +4280,13 @@
     <t xml:space="preserve">2.18306016921997</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14307069778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20487260818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20669007301331</t>
+    <t xml:space="preserve">2.143070936203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20487284660339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20669031143188</t>
   </si>
   <si>
     <t xml:space="preserve">2.17033648490906</t>
@@ -4295,7 +4295,7 @@
     <t xml:space="preserve">2.13943552970886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14670610427856</t>
+    <t xml:space="preserve">2.14670634269714</t>
   </si>
   <si>
     <t xml:space="preserve">2.14852404594421</t>
@@ -4304,49 +4304,49 @@
     <t xml:space="preserve">2.19578409194946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19033122062683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26849246025085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24667954444885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24304437637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25213265419006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30121064186096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28303384780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34120035171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47934556007385</t>
+    <t xml:space="preserve">2.19033098220825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26849222183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24667978286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24304461479187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25213289260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30121088027954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28303408622742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34120059013367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47934579849243</t>
   </si>
   <si>
     <t xml:space="preserve">2.44844484329224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48843383789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46843957901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47207498550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45935130119324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45753359794617</t>
+    <t xml:space="preserve">2.4884340763092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46843934059143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47207474708557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45935106277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45753335952759</t>
   </si>
   <si>
     <t xml:space="preserve">2.43390297889709</t>
@@ -4361,7 +4361,7 @@
     <t xml:space="preserve">2.50297570228577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4702570438385</t>
+    <t xml:space="preserve">2.47025680541992</t>
   </si>
   <si>
     <t xml:space="preserve">2.40118432044983</t>
@@ -4370,7 +4370,7 @@
     <t xml:space="preserve">2.36664843559265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41754412651062</t>
+    <t xml:space="preserve">2.41754388809204</t>
   </si>
   <si>
     <t xml:space="preserve">2.2793984413147</t>
@@ -4382,16 +4382,16 @@
     <t xml:space="preserve">2.29212236404419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27030992507935</t>
+    <t xml:space="preserve">2.27031016349792</t>
   </si>
   <si>
     <t xml:space="preserve">2.22668528556824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30302858352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32484102249146</t>
+    <t xml:space="preserve">2.30302834510803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32484126091003</t>
   </si>
   <si>
     <t xml:space="preserve">2.33029389381409</t>
@@ -4400,19 +4400,19 @@
     <t xml:space="preserve">2.29939317703247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41936135292053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43208575248718</t>
+    <t xml:space="preserve">2.41936159133911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4320855140686</t>
   </si>
   <si>
     <t xml:space="preserve">2.42117929458618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43935608863831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25599455833435</t>
+    <t xml:space="preserve">2.43935632705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25599431991577</t>
   </si>
   <si>
     <t xml:space="preserve">2.28207540512085</t>
@@ -4421,13 +4421,13 @@
     <t xml:space="preserve">2.27462339401245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24854302406311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22991347312927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30070447921753</t>
+    <t xml:space="preserve">2.24854278564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22991371154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30070471763611</t>
   </si>
   <si>
     <t xml:space="preserve">2.31188225746155</t>
@@ -4442,25 +4442,25 @@
     <t xml:space="preserve">2.36404395103455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29697871208191</t>
+    <t xml:space="preserve">2.29697895050049</t>
   </si>
   <si>
     <t xml:space="preserve">2.32678556442261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34168839454651</t>
+    <t xml:space="preserve">2.34168863296509</t>
   </si>
   <si>
     <t xml:space="preserve">2.33982586860657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36963224411011</t>
+    <t xml:space="preserve">2.36963248252869</t>
   </si>
   <si>
     <t xml:space="preserve">2.36776971817017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32864832878113</t>
+    <t xml:space="preserve">2.32864856719971</t>
   </si>
   <si>
     <t xml:space="preserve">2.29884171485901</t>
@@ -4481,13 +4481,13 @@
     <t xml:space="preserve">2.29325270652771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33051156997681</t>
+    <t xml:space="preserve">2.33051133155823</t>
   </si>
   <si>
     <t xml:space="preserve">2.31374502182007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28952693939209</t>
+    <t xml:space="preserve">2.28952670097351</t>
   </si>
   <si>
     <t xml:space="preserve">2.22432494163513</t>
@@ -4496,7 +4496,7 @@
     <t xml:space="preserve">2.20569562911987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16098570823669</t>
+    <t xml:space="preserve">2.16098546981812</t>
   </si>
   <si>
     <t xml:space="preserve">2.14049363136292</t>
@@ -4526,7 +4526,7 @@
     <t xml:space="preserve">2.04921054840088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08460569381714</t>
+    <t xml:space="preserve">2.08460593223572</t>
   </si>
   <si>
     <t xml:space="preserve">2.06411385536194</t>
@@ -4562,7 +4562,7 @@
     <t xml:space="preserve">2.01754069328308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99891173839569</t>
+    <t xml:space="preserve">1.9989116191864</t>
   </si>
   <si>
     <t xml:space="preserve">2.01195240020752</t>
@@ -4577,7 +4577,7 @@
     <t xml:space="preserve">1.97469365596771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95606434345245</t>
+    <t xml:space="preserve">1.95606446266174</t>
   </si>
   <si>
     <t xml:space="preserve">1.92625784873962</t>
@@ -4586,13 +4586,13 @@
     <t xml:space="preserve">1.86478161811829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77349865436554</t>
+    <t xml:space="preserve">1.77349853515625</t>
   </si>
   <si>
     <t xml:space="preserve">1.78095018863678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7846759557724</t>
+    <t xml:space="preserve">1.78467607498169</t>
   </si>
   <si>
     <t xml:space="preserve">1.80330526828766</t>
@@ -4604,7 +4604,7 @@
     <t xml:space="preserve">1.80237364768982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75673234462738</t>
+    <t xml:space="preserve">1.75673222541809</t>
   </si>
   <si>
     <t xml:space="preserve">1.71109080314636</t>
@@ -4622,10 +4622,10 @@
     <t xml:space="preserve">1.69991326332092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66638076305389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61608195304871</t>
+    <t xml:space="preserve">1.6663806438446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61608183383942</t>
   </si>
   <si>
     <t xml:space="preserve">1.63005375862122</t>
@@ -4664,37 +4664,37 @@
     <t xml:space="preserve">1.55646860599518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56485164165497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57975506782532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61887621879578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60117840766907</t>
+    <t xml:space="preserve">1.56485152244568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57975494861603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61887633800507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60117852687836</t>
   </si>
   <si>
     <t xml:space="preserve">1.60956168174744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61980772018433</t>
+    <t xml:space="preserve">1.61980783939362</t>
   </si>
   <si>
     <t xml:space="preserve">1.62819087505341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59745287895203</t>
+    <t xml:space="preserve">1.59745275974274</t>
   </si>
   <si>
     <t xml:space="preserve">1.6123560667038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62073922157288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67755818367004</t>
+    <t xml:space="preserve">1.62073934078217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67755830287933</t>
   </si>
   <si>
     <t xml:space="preserve">1.64123129844666</t>
@@ -4703,10 +4703,10 @@
     <t xml:space="preserve">1.65706610679626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68966710567474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69153010845184</t>
+    <t xml:space="preserve">1.68966722488403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69153022766113</t>
   </si>
   <si>
     <t xml:space="preserve">1.66917514801025</t>
@@ -4724,7 +4724,7 @@
     <t xml:space="preserve">1.72785711288452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84242653846741</t>
+    <t xml:space="preserve">1.84242641925812</t>
   </si>
   <si>
     <t xml:space="preserve">1.84801530838013</t>
@@ -4736,13 +4736,13 @@
     <t xml:space="preserve">1.92998373508453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9765567779541</t>
+    <t xml:space="preserve">1.97655689716339</t>
   </si>
   <si>
     <t xml:space="preserve">1.96165335178375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91508042812347</t>
+    <t xml:space="preserve">1.91508030891418</t>
   </si>
   <si>
     <t xml:space="preserve">1.93557250499725</t>
@@ -4778,7 +4778,7 @@
     <t xml:space="preserve">2.11441254615784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1013720035553</t>
+    <t xml:space="preserve">2.10137224197388</t>
   </si>
   <si>
     <t xml:space="preserve">2.03617000579834</t>
@@ -4793,25 +4793,25 @@
     <t xml:space="preserve">2.01008915901184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01567792892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98214542865753</t>
+    <t xml:space="preserve">2.01567816734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98214554786682</t>
   </si>
   <si>
     <t xml:space="preserve">1.90017700195312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91694331169128</t>
+    <t xml:space="preserve">1.91694343090057</t>
   </si>
   <si>
     <t xml:space="preserve">1.8927253484726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92812085151672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95420157909393</t>
+    <t xml:space="preserve">1.92812073230743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95420169830322</t>
   </si>
   <si>
     <t xml:space="preserve">2.06783962249756</t>
@@ -4820,7 +4820,7 @@
     <t xml:space="preserve">2.03989601135254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07529139518738</t>
+    <t xml:space="preserve">2.0752911567688</t>
   </si>
   <si>
     <t xml:space="preserve">2.09578347206116</t>
@@ -5949,6 +5949,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.42000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34800004959106</t>
   </si>
 </sst>
 </file>
@@ -71599,7 +71602,7 @@
     </row>
     <row r="2513">
       <c r="A2513" s="1" t="n">
-        <v>45978.69125</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B2513" t="n">
         <v>203175</v>
@@ -71620,6 +71623,32 @@
         <v>1978</v>
       </c>
       <c r="H2513" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" s="1" t="n">
+        <v>45979.6910416667</v>
+      </c>
+      <c r="B2514" t="n">
+        <v>328375</v>
+      </c>
+      <c r="C2514" t="n">
+        <v>4.3600001335144</v>
+      </c>
+      <c r="D2514" t="n">
+        <v>4.31199979782104</v>
+      </c>
+      <c r="E2514" t="n">
+        <v>4.35799980163574</v>
+      </c>
+      <c r="F2514" t="n">
+        <v>4.34800004959106</v>
+      </c>
+      <c r="G2514" t="s">
+        <v>1979</v>
+      </c>
+      <c r="H2514" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/OVS.MI.xlsx
+++ b/data/OVS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1981" uniqueCount="1981">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1982" uniqueCount="1982">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,67 +47,67 @@
     <t xml:space="preserve">4.89862394332886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76365423202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64456272125244</t>
+    <t xml:space="preserve">4.76365327835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64456176757812</t>
   </si>
   <si>
     <t xml:space="preserve">4.71998691558838</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65647077560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78747177124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94228982925415</t>
+    <t xml:space="preserve">4.65647172927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78747224807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94229030609131</t>
   </si>
   <si>
     <t xml:space="preserve">4.69219875335693</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60486459732056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63662338256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61677408218384</t>
+    <t xml:space="preserve">4.60486507415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6366229057312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.616774559021</t>
   </si>
   <si>
     <t xml:space="preserve">4.25156021118164</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22774219512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53341007232666</t>
+    <t xml:space="preserve">4.22774314880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5334095954895</t>
   </si>
   <si>
     <t xml:space="preserve">4.45798540115356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47783422470093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49768304824829</t>
+    <t xml:space="preserve">4.47783470153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49768257141113</t>
   </si>
   <si>
     <t xml:space="preserve">4.51356172561646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44607639312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62868404388428</t>
+    <t xml:space="preserve">4.4460768699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62868309020996</t>
   </si>
   <si>
     <t xml:space="preserve">4.59295606613159</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51753234863281</t>
+    <t xml:space="preserve">4.5175313949585</t>
   </si>
   <si>
     <t xml:space="preserve">4.54531908035278</t>
@@ -125,25 +125,25 @@
     <t xml:space="preserve">4.2793493270874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22377300262451</t>
+    <t xml:space="preserve">4.22377252578735</t>
   </si>
   <si>
     <t xml:space="preserve">4.38256120681763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30316734313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.469895362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46592473983765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48577356338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48974323272705</t>
+    <t xml:space="preserve">4.30316781997681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46989488601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46592426300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48577404022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48974275588989</t>
   </si>
   <si>
     <t xml:space="preserve">4.27140855789185</t>
@@ -152,25 +152,25 @@
     <t xml:space="preserve">4.23965215682983</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43813705444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56516885757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67235088348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71601724624634</t>
+    <t xml:space="preserve">4.43813753128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56516933441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67235040664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71601629257202</t>
   </si>
   <si>
     <t xml:space="preserve">4.58898687362671</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50562238693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52547121047974</t>
+    <t xml:space="preserve">4.50562191009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52547168731689</t>
   </si>
   <si>
     <t xml:space="preserve">4.38653039932251</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">4.43019771575928</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40241003036499</t>
+    <t xml:space="preserve">4.40241050720215</t>
   </si>
   <si>
     <t xml:space="preserve">4.29125785827637</t>
@@ -188,67 +188,67 @@
     <t xml:space="preserve">4.12056064605713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09674167633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0649847984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08880281448364</t>
+    <t xml:space="preserve">4.09674263000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06498432159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08880233764648</t>
   </si>
   <si>
     <t xml:space="preserve">4.15628719329834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21186399459839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04910612106323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02131748199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31110572814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16422748565674</t>
+    <t xml:space="preserve">4.21186351776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04910516738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02131795883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31110620498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16422653198242</t>
   </si>
   <si>
     <t xml:space="preserve">4.23568201065063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50959205627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7358660697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54928922653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50165224075317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56119823455811</t>
+    <t xml:space="preserve">4.50959157943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73586559295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54928970336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50165319442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56119775772095</t>
   </si>
   <si>
     <t xml:space="preserve">4.48180389404297</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52150201797485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55325841903687</t>
+    <t xml:space="preserve">4.5215015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55325889587402</t>
   </si>
   <si>
     <t xml:space="preserve">4.5413498878479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56913709640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5373797416687</t>
+    <t xml:space="preserve">4.56913805007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53738021850586</t>
   </si>
   <si>
     <t xml:space="preserve">4.64853191375732</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">4.76678800582886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90123510360718</t>
+    <t xml:space="preserve">4.90123558044434</t>
   </si>
   <si>
     <t xml:space="preserve">4.73419427871704</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">4.5671534538269</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51826286315918</t>
+    <t xml:space="preserve">4.51826333999634</t>
   </si>
   <si>
     <t xml:space="preserve">4.4734468460083</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">4.47752094268799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48974370956421</t>
+    <t xml:space="preserve">4.48974418640137</t>
   </si>
   <si>
     <t xml:space="preserve">4.63233947753906</t>
@@ -308,49 +308,49 @@
     <t xml:space="preserve">4.61196851730347</t>
   </si>
   <si>
-    <t xml:space="preserve">4.550856590271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51418972015381</t>
+    <t xml:space="preserve">4.55085611343384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51418924331665</t>
   </si>
   <si>
     <t xml:space="preserve">4.33085012435913</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94706296920776</t>
+    <t xml:space="preserve">3.94706320762634</t>
   </si>
   <si>
     <t xml:space="preserve">4.13528966903687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24529314041138</t>
+    <t xml:space="preserve">4.24529361724854</t>
   </si>
   <si>
     <t xml:space="preserve">4.26566314697266</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30233144760132</t>
+    <t xml:space="preserve">4.30233097076416</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751543045044</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11084413528442</t>
+    <t xml:space="preserve">4.11084461212158</t>
   </si>
   <si>
     <t xml:space="preserve">4.09047412872314</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05299139022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18825387954712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16380929946899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15566158294678</t>
+    <t xml:space="preserve">4.05299091339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18825340270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16380882263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15566062927246</t>
   </si>
   <si>
     <t xml:space="preserve">4.15973472595215</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">4.04321384429932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11899328231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16788291931152</t>
+    <t xml:space="preserve">4.1189923286438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16788339614868</t>
   </si>
   <si>
     <t xml:space="preserve">4.26158905029297</t>
@@ -374,10 +374,10 @@
     <t xml:space="preserve">4.2004771232605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20862531661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23307037353516</t>
+    <t xml:space="preserve">4.20862483978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23307085037231</t>
   </si>
   <si>
     <t xml:space="preserve">4.37159299850464</t>
@@ -386,37 +386,37 @@
     <t xml:space="preserve">4.36751842498779</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28603410720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27788639068604</t>
+    <t xml:space="preserve">4.28603458404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27788591384888</t>
   </si>
   <si>
     <t xml:space="preserve">4.24121809005737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25344085693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29825735092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22899627685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0725474357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17195796966553</t>
+    <t xml:space="preserve">4.25344133377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29825782775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22899580001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07254695892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17195749282837</t>
   </si>
   <si>
     <t xml:space="preserve">4.19232845306396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10269641876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04158353805542</t>
+    <t xml:space="preserve">4.10269689559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04158306121826</t>
   </si>
   <si>
     <t xml:space="preserve">4.13936424255371</t>
@@ -428,34 +428,34 @@
     <t xml:space="preserve">4.00084209442139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99269390106201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03343629837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19640302658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15158653259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0863995552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06114053726196</t>
+    <t xml:space="preserve">3.99269318580627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0334358215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19640254974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15158700942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08640003204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0611400604248</t>
   </si>
   <si>
     <t xml:space="preserve">4.35936975479126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37566614151001</t>
+    <t xml:space="preserve">4.37566709518433</t>
   </si>
   <si>
     <t xml:space="preserve">4.44085359573364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41233348846436</t>
+    <t xml:space="preserve">4.41233396530151</t>
   </si>
   <si>
     <t xml:space="preserve">4.31862831115723</t>
@@ -464,22 +464,22 @@
     <t xml:space="preserve">4.31047916412354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31455373764038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2697377204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21677303314209</t>
+    <t xml:space="preserve">4.31455278396606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26973819732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21677350997925</t>
   </si>
   <si>
     <t xml:space="preserve">4.1801061630249</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14343786239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11491870880127</t>
+    <t xml:space="preserve">4.1434383392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11491918563843</t>
   </si>
   <si>
     <t xml:space="preserve">4.07417821884155</t>
@@ -491,16 +491,16 @@
     <t xml:space="preserve">4.08232545852661</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06439876556396</t>
+    <t xml:space="preserve">4.06439971923828</t>
   </si>
   <si>
     <t xml:space="preserve">4.00573062896729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9601001739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05462121963501</t>
+    <t xml:space="preserve">3.96010065078735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05462074279785</t>
   </si>
   <si>
     <t xml:space="preserve">4.13121557235718</t>
@@ -512,37 +512,37 @@
     <t xml:space="preserve">3.98128533363342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00410127639771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98617482185364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02528715133667</t>
+    <t xml:space="preserve">4.00410175323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98617506027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02528762817383</t>
   </si>
   <si>
     <t xml:space="preserve">3.97476696968079</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02365779876709</t>
+    <t xml:space="preserve">4.02365684509277</t>
   </si>
   <si>
     <t xml:space="preserve">4.05951023101807</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04810190200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05136156082153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97965669631958</t>
+    <t xml:space="preserve">4.04810237884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05136251449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97965621948242</t>
   </si>
   <si>
     <t xml:space="preserve">4.03017520904541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02039861679077</t>
+    <t xml:space="preserve">4.02039813995361</t>
   </si>
   <si>
     <t xml:space="preserve">3.99921154975891</t>
@@ -551,31 +551,31 @@
     <t xml:space="preserve">4.07825136184692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14751243591309</t>
+    <t xml:space="preserve">4.14751291275024</t>
   </si>
   <si>
     <t xml:space="preserve">4.23714399337769</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20455026626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22492170333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01713800430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02202749252319</t>
+    <t xml:space="preserve">4.20455121994019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22492218017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01713848114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02202796936035</t>
   </si>
   <si>
     <t xml:space="preserve">3.93076610565186</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91283941268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89491295814514</t>
+    <t xml:space="preserve">3.91283965110779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8949134349823</t>
   </si>
   <si>
     <t xml:space="preserve">3.87535738945007</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">3.94054484367371</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93402576446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89654302597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95521116256714</t>
+    <t xml:space="preserve">3.93402600288391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89654326438904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95521068572998</t>
   </si>
   <si>
     <t xml:space="preserve">4.00247192382812</t>
@@ -599,19 +599,19 @@
     <t xml:space="preserve">4.3797402381897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38381385803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39196395874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35529565811157</t>
+    <t xml:space="preserve">4.38381433486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39196348190308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35529518127441</t>
   </si>
   <si>
     <t xml:space="preserve">4.29010820388794</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28196048736572</t>
+    <t xml:space="preserve">4.28196001052856</t>
   </si>
   <si>
     <t xml:space="preserve">4.3267765045166</t>
@@ -620,10 +620,10 @@
     <t xml:space="preserve">4.29418325424194</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33899879455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33492469787598</t>
+    <t xml:space="preserve">4.33899927139282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33492422103882</t>
   </si>
   <si>
     <t xml:space="preserve">4.34307336807251</t>
@@ -632,34 +632,34 @@
     <t xml:space="preserve">4.46529865264893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48159551620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40825986862183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53863382339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55493021011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52641105651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5060396194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43270492553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59567213058472</t>
+    <t xml:space="preserve">4.48159503936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40825939178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53863334655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55493068695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52641153335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50604009628296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43270444869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59567260742188</t>
   </si>
   <si>
     <t xml:space="preserve">4.68530464172363</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67308139801025</t>
+    <t xml:space="preserve">4.67308187484741</t>
   </si>
   <si>
     <t xml:space="preserve">4.60382032394409</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">4.70160055160522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85642004013062</t>
+    <t xml:space="preserve">4.8564190864563</t>
   </si>
   <si>
     <t xml:space="preserve">4.82382583618164</t>
@@ -677,58 +677,58 @@
     <t xml:space="preserve">4.77493572235107</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79938077926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74234199523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78308439254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72604513168335</t>
+    <t xml:space="preserve">4.7993803024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74234294891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78308486938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72604560852051</t>
   </si>
   <si>
     <t xml:space="preserve">4.7790093421936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80752944946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86456775665283</t>
+    <t xml:space="preserve">4.80752992630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86456823348999</t>
   </si>
   <si>
     <t xml:space="preserve">5.04790544509888</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01531267166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89716100692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91753196716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88901329040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04383134841919</t>
+    <t xml:space="preserve">5.01531171798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89716053009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91753244400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88901281356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04383087158203</t>
   </si>
   <si>
     <t xml:space="preserve">4.90531015396118</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9501256942749</t>
+    <t xml:space="preserve">4.95012521743774</t>
   </si>
   <si>
     <t xml:space="preserve">5.05198049545288</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97864484786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03160953521729</t>
+    <t xml:space="preserve">4.97864532470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03160905838013</t>
   </si>
   <si>
     <t xml:space="preserve">5.08457326889038</t>
@@ -740,16 +740,16 @@
     <t xml:space="preserve">5.19865036010742</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14568519592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19457626342773</t>
+    <t xml:space="preserve">5.14568567276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19457578659058</t>
   </si>
   <si>
     <t xml:space="preserve">5.05605459213257</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06420230865479</t>
+    <t xml:space="preserve">5.06420278549194</t>
   </si>
   <si>
     <t xml:space="preserve">5.13346385955811</t>
@@ -758,7 +758,7 @@
     <t xml:space="preserve">5.11716651916504</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25161504745483</t>
+    <t xml:space="preserve">5.25161552429199</t>
   </si>
   <si>
     <t xml:space="preserve">5.18235397338867</t>
@@ -770,46 +770,46 @@
     <t xml:space="preserve">5.25568914413452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27198553085327</t>
+    <t xml:space="preserve">5.27198457717896</t>
   </si>
   <si>
     <t xml:space="preserve">5.17420482635498</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16605710983276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18642711639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10494470596313</t>
+    <t xml:space="preserve">5.16605663299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1864275932312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10494518280029</t>
   </si>
   <si>
     <t xml:space="preserve">5.07235050201416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94605112075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06827640533447</t>
+    <t xml:space="preserve">4.94605207443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06827592849731</t>
   </si>
   <si>
     <t xml:space="preserve">4.98679304122925</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0369119644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3626823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39191722869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31256341934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27915096282959</t>
+    <t xml:space="preserve">5.03691244125366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36268186569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39191770553589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3125638961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27915000915527</t>
   </si>
   <si>
     <t xml:space="preserve">5.34597635269165</t>
@@ -821,25 +821,25 @@
     <t xml:space="preserve">5.32091569900513</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33762264251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2707986831665</t>
+    <t xml:space="preserve">5.33762311935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27079820632935</t>
   </si>
   <si>
     <t xml:space="preserve">5.27497386932373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1872673034668</t>
+    <t xml:space="preserve">5.18726778030396</t>
   </si>
   <si>
     <t xml:space="preserve">5.132972240448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20397424697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22903299331665</t>
+    <t xml:space="preserve">5.2039737701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22903347015381</t>
   </si>
   <si>
     <t xml:space="preserve">5.25409173965454</t>
@@ -848,16 +848,16 @@
     <t xml:space="preserve">5.2624454498291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1830906867981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.212327003479</t>
+    <t xml:space="preserve">5.18309116363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21232652664185</t>
   </si>
   <si>
     <t xml:space="preserve">5.17891454696655</t>
   </si>
   <si>
-    <t xml:space="preserve">5.249915599823</t>
+    <t xml:space="preserve">5.24991512298584</t>
   </si>
   <si>
     <t xml:space="preserve">5.24573850631714</t>
@@ -866,37 +866,37 @@
     <t xml:space="preserve">5.28332757949829</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22485542297363</t>
+    <t xml:space="preserve">5.22485589981079</t>
   </si>
   <si>
     <t xml:space="preserve">5.30003356933594</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33344697952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40444707870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37521171569824</t>
+    <t xml:space="preserve">5.33344650268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40444660186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37521123886108</t>
   </si>
   <si>
     <t xml:space="preserve">5.40027046203613</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38356494903564</t>
+    <t xml:space="preserve">5.3835654258728</t>
   </si>
   <si>
     <t xml:space="preserve">5.37938785552979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23320913314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30838775634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25826930999756</t>
+    <t xml:space="preserve">5.23320960998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3083872795105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2582688331604</t>
   </si>
   <si>
     <t xml:space="preserve">5.20814990997314</t>
@@ -905,10 +905,10 @@
     <t xml:space="preserve">5.1371488571167</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11208963394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1538553237915</t>
+    <t xml:space="preserve">5.11208915710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15385484695435</t>
   </si>
   <si>
     <t xml:space="preserve">5.23738527297974</t>
@@ -917,37 +917,37 @@
     <t xml:space="preserve">5.32509279251099</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30420970916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29585742950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32926893234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48797798156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53809642791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59656858444214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62580347061157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68845319747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6132755279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57568597793579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44203662872314</t>
+    <t xml:space="preserve">5.30421018600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29585695266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32926940917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48797845840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5380973815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59656810760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62580394744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68845272064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61327457427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57568502426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44203615188599</t>
   </si>
   <si>
     <t xml:space="preserve">5.62162780761719</t>
@@ -956,16 +956,16 @@
     <t xml:space="preserve">5.68009901046753</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64251041412354</t>
+    <t xml:space="preserve">5.64251089096069</t>
   </si>
   <si>
     <t xml:space="preserve">5.37103509902954</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39609384536743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38774108886719</t>
+    <t xml:space="preserve">5.39609432220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38774156570435</t>
   </si>
   <si>
     <t xml:space="preserve">5.24156188964844</t>
@@ -977,16 +977,16 @@
     <t xml:space="preserve">5.19561958312988</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0828537940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88655567169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90743970870972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81973171234131</t>
+    <t xml:space="preserve">5.08285427093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88655662536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9074387550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81973123550415</t>
   </si>
   <si>
     <t xml:space="preserve">4.80302572250366</t>
@@ -995,37 +995,37 @@
     <t xml:space="preserve">4.84478998184204</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83643770217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94502735137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9032621383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86567354202271</t>
+    <t xml:space="preserve">4.8364372253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94502782821655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90326261520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86567306518555</t>
   </si>
   <si>
     <t xml:space="preserve">4.87820339202881</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8531436920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81137847900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95755767822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92832136154175</t>
+    <t xml:space="preserve">4.85314416885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81137800216675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95755815505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92832183837891</t>
   </si>
   <si>
     <t xml:space="preserve">4.77796602249146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.861496925354</t>
+    <t xml:space="preserve">4.86149644851685</t>
   </si>
   <si>
     <t xml:space="preserve">4.83226156234741</t>
@@ -1034,25 +1034,25 @@
     <t xml:space="preserve">4.72367000579834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66102313995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69861125946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66937637329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63596343994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70278787612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6735520362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64013957977295</t>
+    <t xml:space="preserve">4.66102266311646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69861030578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66937589645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63596391677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70278835296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67355155944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64014005661011</t>
   </si>
   <si>
     <t xml:space="preserve">4.7194938659668</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">4.7904953956604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74872970581055</t>
+    <t xml:space="preserve">4.74873018264771</t>
   </si>
   <si>
     <t xml:space="preserve">4.7320237159729</t>
@@ -1073,13 +1073,13 @@
     <t xml:space="preserve">4.67772912979126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91579246520996</t>
+    <t xml:space="preserve">4.9157919883728</t>
   </si>
   <si>
     <t xml:space="preserve">4.92414474487305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89490842819214</t>
+    <t xml:space="preserve">4.8949089050293</t>
   </si>
   <si>
     <t xml:space="preserve">4.84061431884766</t>
@@ -1091,67 +1091,67 @@
     <t xml:space="preserve">4.99932193756104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0202054977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17056083679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09955978393555</t>
+    <t xml:space="preserve">5.02020502090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17056035995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09955930709839</t>
   </si>
   <si>
     <t xml:space="preserve">4.95338106155396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7863187789917</t>
+    <t xml:space="preserve">4.78631925582886</t>
   </si>
   <si>
     <t xml:space="preserve">4.68608140945435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60672760009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59419822692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6150803565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63178730010986</t>
+    <t xml:space="preserve">4.60672807693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59419775009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61508083343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63178682327271</t>
   </si>
   <si>
     <t xml:space="preserve">4.70696496963501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58584499359131</t>
+    <t xml:space="preserve">4.58584451675415</t>
   </si>
   <si>
     <t xml:space="preserve">4.55243253707886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53990268707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57749223709106</t>
+    <t xml:space="preserve">4.5399022102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57749176025391</t>
   </si>
   <si>
     <t xml:space="preserve">4.48978424072266</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41043043136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4438419342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4939603805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47307777404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51901960372925</t>
+    <t xml:space="preserve">4.41042995452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44384241104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49395990371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47307825088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51902008056641</t>
   </si>
   <si>
     <t xml:space="preserve">4.5691385269165</t>
@@ -1163,28 +1163,28 @@
     <t xml:space="preserve">4.65684604644775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64849233627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5983738899231</t>
+    <t xml:space="preserve">4.64849281311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59837436676025</t>
   </si>
   <si>
     <t xml:space="preserve">4.5607852935791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48560810089111</t>
+    <t xml:space="preserve">4.48560857772827</t>
   </si>
   <si>
     <t xml:space="preserve">4.43966579437256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36031103134155</t>
+    <t xml:space="preserve">4.36031198501587</t>
   </si>
   <si>
     <t xml:space="preserve">4.38537073135376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18907260894775</t>
+    <t xml:space="preserve">4.18907308578491</t>
   </si>
   <si>
     <t xml:space="preserve">4.16150760650635</t>
@@ -1199,19 +1199,19 @@
     <t xml:space="preserve">4.19324970245361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09802436828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15315437316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10303688049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12642526626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16986179351807</t>
+    <t xml:space="preserve">4.09802484512329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1531548500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10303640365601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12642478942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16986131668091</t>
   </si>
   <si>
     <t xml:space="preserve">4.17654418945312</t>
@@ -1220,31 +1220,31 @@
     <t xml:space="preserve">4.14313077926636</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16819000244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8300256729126</t>
+    <t xml:space="preserve">4.16819047927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83002591133118</t>
   </si>
   <si>
     <t xml:space="preserve">2.90687417984009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84339046478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87179160118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89350938796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80162501335144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92358088493347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94863986968994</t>
+    <t xml:space="preserve">2.84339070320129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87179136276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89350914955139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80162477493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92358064651489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94863963127136</t>
   </si>
   <si>
     <t xml:space="preserve">3.01713514328003</t>
@@ -1253,7 +1253,7 @@
     <t xml:space="preserve">3.08061838150024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17083144187927</t>
+    <t xml:space="preserve">3.17083120346069</t>
   </si>
   <si>
     <t xml:space="preserve">3.14911389350891</t>
@@ -1265,10 +1265,10 @@
     <t xml:space="preserve">3.14410161972046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17918539047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17417287826538</t>
+    <t xml:space="preserve">3.17918515205383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17417359352112</t>
   </si>
   <si>
     <t xml:space="preserve">3.10400748252869</t>
@@ -1277,22 +1277,22 @@
     <t xml:space="preserve">3.01212334632874</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02882957458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94529819488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95699238777161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89852118492126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84004926681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82501411437988</t>
+    <t xml:space="preserve">3.02882981300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94529795646667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95699262619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89852142333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84004902839661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8250138759613</t>
   </si>
   <si>
     <t xml:space="preserve">2.85007309913635</t>
@@ -1304,10 +1304,10 @@
     <t xml:space="preserve">2.55771493911743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54769134521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51093769073486</t>
+    <t xml:space="preserve">2.54769158363342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51093792915344</t>
   </si>
   <si>
     <t xml:space="preserve">2.58945727348328</t>
@@ -1316,25 +1316,25 @@
     <t xml:space="preserve">2.5009138584137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51594972610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50592589378357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47919631004333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41905355453491</t>
+    <t xml:space="preserve">2.51594996452332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50592565536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47919583320618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41905379295349</t>
   </si>
   <si>
     <t xml:space="preserve">2.39566540718079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36058235168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36726450920105</t>
+    <t xml:space="preserve">2.36058211326599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36726474761963</t>
   </si>
   <si>
     <t xml:space="preserve">2.3772885799408</t>
@@ -1346,25 +1346,25 @@
     <t xml:space="preserve">2.31380534172058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26201558113098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27203941345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41404247283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38062930107117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30043959617615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30211091041565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29709911346436</t>
+    <t xml:space="preserve">2.26201510429382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27203965187073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41404223442078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38062953948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30043935775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30211067199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29709887504578</t>
   </si>
   <si>
     <t xml:space="preserve">2.32382845878601</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">2.36559438705444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35055804252625</t>
+    <t xml:space="preserve">2.35055828094482</t>
   </si>
   <si>
     <t xml:space="preserve">2.35222935676575</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">2.35557007789612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25533294677734</t>
+    <t xml:space="preserve">2.25533318519592</t>
   </si>
   <si>
     <t xml:space="preserve">2.22025060653687</t>
@@ -1397,13 +1397,13 @@
     <t xml:space="preserve">2.28039240837097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.225261926651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23027372360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40067648887634</t>
+    <t xml:space="preserve">2.22526168823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23027396202087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40067672729492</t>
   </si>
   <si>
     <t xml:space="preserve">2.44912457466125</t>
@@ -1412,16 +1412,16 @@
     <t xml:space="preserve">2.42406558990479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31881642341614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30879330635071</t>
+    <t xml:space="preserve">2.31881666183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30879354476929</t>
   </si>
   <si>
     <t xml:space="preserve">2.34387588500977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33218097686768</t>
+    <t xml:space="preserve">2.33218145370483</t>
   </si>
   <si>
     <t xml:space="preserve">2.27371001243591</t>
@@ -1430,37 +1430,37 @@
     <t xml:space="preserve">2.18850874900818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17681431770325</t>
+    <t xml:space="preserve">2.17681455612183</t>
   </si>
   <si>
     <t xml:space="preserve">2.15342569351196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21022653579712</t>
+    <t xml:space="preserve">2.21022629737854</t>
   </si>
   <si>
     <t xml:space="preserve">2.21189713478088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05485868453979</t>
+    <t xml:space="preserve">2.05485892295837</t>
   </si>
   <si>
     <t xml:space="preserve">2.01142287254333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97466921806335</t>
+    <t xml:space="preserve">1.97466909885406</t>
   </si>
   <si>
     <t xml:space="preserve">2.00474047660828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03815364837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15175533294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17180252075195</t>
+    <t xml:space="preserve">2.03815340995789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1517550945282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17180228233337</t>
   </si>
   <si>
     <t xml:space="preserve">2.18182587623596</t>
@@ -1469,28 +1469,28 @@
     <t xml:space="preserve">2.16679048538208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16846060752869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15509581565857</t>
+    <t xml:space="preserve">2.16846084594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15509605407715</t>
   </si>
   <si>
     <t xml:space="preserve">2.15676641464233</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11500144004822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07657718658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08994197845459</t>
+    <t xml:space="preserve">2.1150016784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07657742500305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08994221687317</t>
   </si>
   <si>
     <t xml:space="preserve">2.09829497337341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1601083278656</t>
+    <t xml:space="preserve">2.16010808944702</t>
   </si>
   <si>
     <t xml:space="preserve">2.09662485122681</t>
@@ -1505,28 +1505,28 @@
     <t xml:space="preserve">2.02645897865295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12502479553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23695611953735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18683791160583</t>
+    <t xml:space="preserve">2.12502455711365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23695635795593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18683767318726</t>
   </si>
   <si>
     <t xml:space="preserve">2.11834239959717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06989502906799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06321263313293</t>
+    <t xml:space="preserve">2.06989526748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06321239471436</t>
   </si>
   <si>
     <t xml:space="preserve">2.00139951705933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99972856044769</t>
+    <t xml:space="preserve">1.99972867965698</t>
   </si>
   <si>
     <t xml:space="preserve">1.98302292823792</t>
@@ -1535,16 +1535,16 @@
     <t xml:space="preserve">1.94626927375793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8761031627655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75748932361603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69567656517029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65391075611115</t>
+    <t xml:space="preserve">1.87610352039337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75748944282532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.695676445961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65391063690186</t>
   </si>
   <si>
     <t xml:space="preserve">1.6288515329361</t>
@@ -1553,13 +1553,13 @@
     <t xml:space="preserve">1.62968707084656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50439071655273</t>
+    <t xml:space="preserve">1.50439083576202</t>
   </si>
   <si>
     <t xml:space="preserve">1.48601388931274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39663553237915</t>
+    <t xml:space="preserve">1.39663565158844</t>
   </si>
   <si>
     <t xml:space="preserve">1.31728136539459</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">1.24962162971497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24460959434509</t>
+    <t xml:space="preserve">1.24460971355438</t>
   </si>
   <si>
     <t xml:space="preserve">1.2897162437439</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">1.27635133266449</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30391657352448</t>
+    <t xml:space="preserve">1.30391645431519</t>
   </si>
   <si>
     <t xml:space="preserve">1.3156111240387</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">1.31310498714447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2838693857193</t>
+    <t xml:space="preserve">1.28386926651001</t>
   </si>
   <si>
     <t xml:space="preserve">1.27969288825989</t>
@@ -1604,16 +1604,16 @@
     <t xml:space="preserve">1.35152912139893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29472815990448</t>
+    <t xml:space="preserve">1.29472827911377</t>
   </si>
   <si>
     <t xml:space="preserve">1.29639852046967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24293923377991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2521276473999</t>
+    <t xml:space="preserve">1.24293911457062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25212776660919</t>
   </si>
   <si>
     <t xml:space="preserve">1.26799857616425</t>
@@ -1631,13 +1631,13 @@
     <t xml:space="preserve">1.2579745054245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26048052310944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36823570728302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36990594863892</t>
+    <t xml:space="preserve">1.26048040390015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36823558807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36990606784821</t>
   </si>
   <si>
     <t xml:space="preserve">1.36405909061432</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">1.34568238258362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31477534770966</t>
+    <t xml:space="preserve">1.31477546691895</t>
   </si>
   <si>
     <t xml:space="preserve">1.34484672546387</t>
@@ -1664,16 +1664,16 @@
     <t xml:space="preserve">0.962275266647339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989840567111969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.633163154125214</t>
+    <t xml:space="preserve">0.989840507507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.633163213729858</t>
   </si>
   <si>
     <t xml:space="preserve">0.703329861164093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.705000162124634</t>
+    <t xml:space="preserve">0.705000281333923</t>
   </si>
   <si>
     <t xml:space="preserve">0.862038254737854</t>
@@ -1682,10 +1682,10 @@
     <t xml:space="preserve">0.958098888397217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.94807493686676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848673462867737</t>
+    <t xml:space="preserve">0.948074817657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848673403263092</t>
   </si>
   <si>
     <t xml:space="preserve">0.913827180862427</t>
@@ -1700,7 +1700,7 @@
     <t xml:space="preserve">0.917168796062469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00487565994263</t>
+    <t xml:space="preserve">1.00487577915192</t>
   </si>
   <si>
     <t xml:space="preserve">1.1477142572403</t>
@@ -1709,7 +1709,7 @@
     <t xml:space="preserve">1.11430132389069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09926605224609</t>
+    <t xml:space="preserve">1.09926617145538</t>
   </si>
   <si>
     <t xml:space="preserve">1.13184344768524</t>
@@ -1724,10 +1724,10 @@
     <t xml:space="preserve">1.01155817508698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01824069023132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999028921127319</t>
+    <t xml:space="preserve">1.01824057102203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999029040336609</t>
   </si>
   <si>
     <t xml:space="preserve">1.01573550701141</t>
@@ -1736,10 +1736,10 @@
     <t xml:space="preserve">1.01322948932648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08255970478058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10177195072174</t>
+    <t xml:space="preserve">1.08255958557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10177206993103</t>
   </si>
   <si>
     <t xml:space="preserve">1.1276661157608</t>
@@ -1754,22 +1754,22 @@
     <t xml:space="preserve">1.1368545293808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11346662044525</t>
+    <t xml:space="preserve">1.11346650123596</t>
   </si>
   <si>
     <t xml:space="preserve">1.10260689258575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06585311889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03244113922119</t>
+    <t xml:space="preserve">1.06585299968719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0324410200119</t>
   </si>
   <si>
     <t xml:space="preserve">1.07086515426636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06334817409515</t>
+    <t xml:space="preserve">1.06334805488586</t>
   </si>
   <si>
     <t xml:space="preserve">1.01907634735107</t>
@@ -1778,22 +1778,22 @@
     <t xml:space="preserve">1.03494715690613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06501841545105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12850165367126</t>
+    <t xml:space="preserve">1.06501829624176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12850177288055</t>
   </si>
   <si>
     <t xml:space="preserve">1.08506560325623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08673596382141</t>
+    <t xml:space="preserve">1.08673584461212</t>
   </si>
   <si>
     <t xml:space="preserve">1.07253646850586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08088910579681</t>
+    <t xml:space="preserve">1.0808892250061</t>
   </si>
   <si>
     <t xml:space="preserve">1.1051127910614</t>
@@ -1802,52 +1802,52 @@
     <t xml:space="preserve">1.07838320732117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10010087490082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1126309633255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11012482643127</t>
+    <t xml:space="preserve">1.10010075569153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11263084411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11012494564056</t>
   </si>
   <si>
     <t xml:space="preserve">1.2262327671051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46179044246674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41584801673889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.414177775383</t>
+    <t xml:space="preserve">1.46179032325745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41584813594818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41417789459229</t>
   </si>
   <si>
     <t xml:space="preserve">1.36071753501892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33064639568329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29806983470917</t>
+    <t xml:space="preserve">1.33064615726471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29806971549988</t>
   </si>
   <si>
     <t xml:space="preserve">1.3732476234436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38744735717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32981145381927</t>
+    <t xml:space="preserve">1.38744723796844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32981157302856</t>
   </si>
   <si>
     <t xml:space="preserve">1.35069346427917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35487079620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3289760351181</t>
+    <t xml:space="preserve">1.35487067699432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32897591590881</t>
   </si>
   <si>
     <t xml:space="preserve">1.36572957038879</t>
@@ -1856,10 +1856,10 @@
     <t xml:space="preserve">1.37157642841339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40248310565948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41918885707855</t>
+    <t xml:space="preserve">1.40248322486877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41918897628784</t>
   </si>
   <si>
     <t xml:space="preserve">1.42169487476349</t>
@@ -1868,28 +1868,28 @@
     <t xml:space="preserve">1.42253053188324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42837715148926</t>
+    <t xml:space="preserve">1.42837727069855</t>
   </si>
   <si>
     <t xml:space="preserve">1.39997732639313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37575268745422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39412975311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4534364938736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43589532375336</t>
+    <t xml:space="preserve">1.37575280666351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3941296339035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45343661308289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43589544296265</t>
   </si>
   <si>
     <t xml:space="preserve">1.52861428260803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61131000518799</t>
+    <t xml:space="preserve">1.61131024360657</t>
   </si>
   <si>
     <t xml:space="preserve">1.59710991382599</t>
@@ -1901,43 +1901,43 @@
     <t xml:space="preserve">1.5745564699173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55283868312836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55116760730743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51441478729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47097861766815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41751837730408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43422484397888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3882828950882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38327074050903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3323165178299</t>
+    <t xml:space="preserve">1.55283892154694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55116772651672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51441490650177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47097873687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41751849651337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43422508239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38828277587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38327085971832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33231663703918</t>
   </si>
   <si>
     <t xml:space="preserve">1.36739993095398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34985876083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30308103561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32229351997375</t>
+    <t xml:space="preserve">1.34985888004303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30308091640472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32229340076447</t>
   </si>
   <si>
     <t xml:space="preserve">1.31644582748413</t>
@@ -1949,13 +1949,13 @@
     <t xml:space="preserve">1.30892872810364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31059908866882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31895172595978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29222226142883</t>
+    <t xml:space="preserve">1.31059896945953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31895196437836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29222238063812</t>
   </si>
   <si>
     <t xml:space="preserve">1.28721010684967</t>
@@ -1964,46 +1964,46 @@
     <t xml:space="preserve">1.25045645236969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32730555534363</t>
+    <t xml:space="preserve">1.32730543613434</t>
   </si>
   <si>
     <t xml:space="preserve">1.31143462657928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31978750228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3490229845047</t>
+    <t xml:space="preserve">1.31978726387024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34902310371399</t>
   </si>
   <si>
     <t xml:space="preserve">1.34651708602905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30725824832916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26215088367462</t>
+    <t xml:space="preserve">1.30725836753845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26215076446533</t>
   </si>
   <si>
     <t xml:space="preserve">1.26883316040039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22205650806427</t>
+    <t xml:space="preserve">1.22205626964569</t>
   </si>
   <si>
     <t xml:space="preserve">1.19198513031006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35821151733398</t>
+    <t xml:space="preserve">1.35821163654327</t>
   </si>
   <si>
     <t xml:space="preserve">1.32312917709351</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28219890594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24043321609497</t>
+    <t xml:space="preserve">1.28219902515411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24043309688568</t>
   </si>
   <si>
     <t xml:space="preserve">1.27384543418884</t>
@@ -2021,31 +2021,31 @@
     <t xml:space="preserve">1.42503654956818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48183751106262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4960378408432</t>
+    <t xml:space="preserve">1.48183739185333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49603807926178</t>
   </si>
   <si>
     <t xml:space="preserve">1.50272023677826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50355517864227</t>
+    <t xml:space="preserve">1.50355505943298</t>
   </si>
   <si>
     <t xml:space="preserve">1.54448533058167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56369769573212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53863847255707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54866242408752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49186074733734</t>
+    <t xml:space="preserve">1.56369757652283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53863835334778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54866254329681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49186062812805</t>
   </si>
   <si>
     <t xml:space="preserve">1.41668295860291</t>
@@ -2054,40 +2054,40 @@
     <t xml:space="preserve">1.39329493045807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39078879356384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42002463340759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37491810321808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34818840026855</t>
+    <t xml:space="preserve">1.39078891277313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4200245141983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37491798400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34818828105927</t>
   </si>
   <si>
     <t xml:space="preserve">1.33148193359375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32814013957977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29723429679871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29974007606506</t>
+    <t xml:space="preserve">1.32814037799835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29723417758942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29974031448364</t>
   </si>
   <si>
     <t xml:space="preserve">1.30224621295929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33315229415894</t>
+    <t xml:space="preserve">1.33315217494965</t>
   </si>
   <si>
     <t xml:space="preserve">1.26549255847931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24210357666016</t>
+    <t xml:space="preserve">1.24210345745087</t>
   </si>
   <si>
     <t xml:space="preserve">1.38995325565338</t>
@@ -2099,25 +2099,25 @@
     <t xml:space="preserve">1.38494122028351</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38911843299866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37993013858795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45260167121887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48851990699768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49687266349792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50104904174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.447589635849</t>
+    <t xml:space="preserve">1.38911855220795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37993001937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45260179042816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48852002620697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49687278270721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50104880332947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44758975505829</t>
   </si>
   <si>
     <t xml:space="preserve">1.39914166927338</t>
@@ -2126,25 +2126,25 @@
     <t xml:space="preserve">1.54281485080719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46095454692841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39162361621857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41000032424927</t>
+    <t xml:space="preserve">1.4609546661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39162373542786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41000056266785</t>
   </si>
   <si>
     <t xml:space="preserve">1.40833008289337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42921304702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40749454498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3339878320694</t>
+    <t xml:space="preserve">1.4292129278183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40749442577362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33398795127869</t>
   </si>
   <si>
     <t xml:space="preserve">1.32563412189484</t>
@@ -2153,7 +2153,7 @@
     <t xml:space="preserve">1.33732879161835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36155331134796</t>
+    <t xml:space="preserve">1.36155307292938</t>
   </si>
   <si>
     <t xml:space="preserve">1.36907041072845</t>
@@ -2162,28 +2162,28 @@
     <t xml:space="preserve">1.44508373737335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43505990505219</t>
+    <t xml:space="preserve">1.4350597858429</t>
   </si>
   <si>
     <t xml:space="preserve">1.46596658229828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4718132019043</t>
+    <t xml:space="preserve">1.47181344032288</t>
   </si>
   <si>
     <t xml:space="preserve">1.46513092517853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47264909744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51190888881683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47014319896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4926962852478</t>
+    <t xml:space="preserve">1.47264897823334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51190876960754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47014307975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49269616603851</t>
   </si>
   <si>
     <t xml:space="preserve">1.52276766300201</t>
@@ -2195,7 +2195,7 @@
     <t xml:space="preserve">1.53529679775238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59794521331787</t>
+    <t xml:space="preserve">1.59794545173645</t>
   </si>
   <si>
     <t xml:space="preserve">1.60629820823669</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">1.64555788040161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59293341636658</t>
+    <t xml:space="preserve">1.59293329715729</t>
   </si>
   <si>
     <t xml:space="preserve">1.63219308853149</t>
@@ -2225,22 +2225,22 @@
     <t xml:space="preserve">1.55868566036224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56620359420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56703841686249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58708643913269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64973425865173</t>
+    <t xml:space="preserve">1.56620371341705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56703853607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58708679676056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64973437786102</t>
   </si>
   <si>
     <t xml:space="preserve">1.74078297615051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70737075805664</t>
+    <t xml:space="preserve">1.70737087726593</t>
   </si>
   <si>
     <t xml:space="preserve">1.71906530857086</t>
@@ -2255,55 +2255,55 @@
     <t xml:space="preserve">1.73243021965027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6923348903656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76584231853485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74913597106934</t>
+    <t xml:space="preserve">1.69233477115631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76584219932556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74913573265076</t>
   </si>
   <si>
     <t xml:space="preserve">1.72073566913605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63887560367584</t>
+    <t xml:space="preserve">1.63887548446655</t>
   </si>
   <si>
     <t xml:space="preserve">1.60880422592163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68565225601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67061710357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68732357025146</t>
+    <t xml:space="preserve">1.68565237522125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67061722278595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68732368946075</t>
   </si>
   <si>
     <t xml:space="preserve">1.67562913894653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6806412935257</t>
+    <t xml:space="preserve">1.68064117431641</t>
   </si>
   <si>
     <t xml:space="preserve">1.61715698242188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61548662185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6246749162674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61047470569611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64054596424103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62383937835693</t>
+    <t xml:space="preserve">1.61548686027527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62467515468597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61047458648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64054572582245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62383949756622</t>
   </si>
   <si>
     <t xml:space="preserve">1.60963988304138</t>
@@ -2318,7 +2318,7 @@
     <t xml:space="preserve">1.56202733516693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59209775924683</t>
+    <t xml:space="preserve">1.59209764003754</t>
   </si>
   <si>
     <t xml:space="preserve">1.59543943405151</t>
@@ -2333,37 +2333,37 @@
     <t xml:space="preserve">1.6004513502121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58541536331177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54532086849213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5469913482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57706260681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43756580352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49436676502228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48935544490814</t>
+    <t xml:space="preserve">1.58541524410248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54532074928284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54699122905731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57706248760223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43756568431854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49436664581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48935568332672</t>
   </si>
   <si>
     <t xml:space="preserve">1.46763706207275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51274347305298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52610850334167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53195595741272</t>
+    <t xml:space="preserve">1.51274359226227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52610838413239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53195607662201</t>
   </si>
   <si>
     <t xml:space="preserve">1.54782676696777</t>
@@ -2372,16 +2372,16 @@
     <t xml:space="preserve">1.51691997051239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5094028711319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48267221450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26465678215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23208034038544</t>
+    <t xml:space="preserve">1.50940275192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48267209529877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26465690135956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23208045959473</t>
   </si>
   <si>
     <t xml:space="preserve">1.18029081821442</t>
@@ -2390,13 +2390,13 @@
     <t xml:space="preserve">1.16692578792572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13601970672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02742910385132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933039665222168</t>
+    <t xml:space="preserve">1.13601982593536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02742898464203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933039724826813</t>
   </si>
   <si>
     <t xml:space="preserve">0.776836395263672</t>
@@ -2405,10 +2405,10 @@
     <t xml:space="preserve">0.719200670719147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.695811808109283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54670923948288</t>
+    <t xml:space="preserve">0.695811867713928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.546709179878235</t>
   </si>
   <si>
     <t xml:space="preserve">0.613534212112427</t>
@@ -2417,67 +2417,67 @@
     <t xml:space="preserve">0.519561350345612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599333703517914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.674928963184357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.725047469139099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.701658546924591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.637340426445007</t>
+    <t xml:space="preserve">0.599333763122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.674928903579712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.725047409534454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.701658606529236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.637340486049652</t>
   </si>
   <si>
     <t xml:space="preserve">0.682446956634521</t>
   </si>
   <si>
-    <t xml:space="preserve">0.680358350276947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.687876343727112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.659893751144409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643604576587677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.659475445747375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643187284469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627316474914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.576780498027802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618127942085266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.660728454589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.646528840065002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.650705277919769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.638175129890442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.649869740009308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640263855457306</t>
+    <t xml:space="preserve">0.680358290672302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.687876403331757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.65989363193512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.643604516983032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.65947550535202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.643187165260315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627316415309906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.576780557632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618128001689911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.660728514194489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.646528899669647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.650705337524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.638175189495087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.649869680404663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640263915061951</t>
   </si>
   <si>
     <t xml:space="preserve">0.612281143665314</t>
@@ -2492,16 +2492,16 @@
     <t xml:space="preserve">0.605598747730255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611028254032135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.651539981365204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.676599323749542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.654881656169891</t>
+    <t xml:space="preserve">0.611028134822845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.651540040969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.676599264144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.654881715774536</t>
   </si>
   <si>
     <t xml:space="preserve">0.642351627349854</t>
@@ -2516,10 +2516,10 @@
     <t xml:space="preserve">0.639846444129944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649034917354584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.668246507644653</t>
+    <t xml:space="preserve">0.649034857749939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.668246567249298</t>
   </si>
   <si>
     <t xml:space="preserve">0.65028703212738</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">0.609775185585022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.606016099452972</t>
+    <t xml:space="preserve">0.606016159057617</t>
   </si>
   <si>
     <t xml:space="preserve">0.629822373390198</t>
@@ -2540,10 +2540,10 @@
     <t xml:space="preserve">0.596827805042267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.574691891670227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.581792652606964</t>
+    <t xml:space="preserve">0.574691832065582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.581792593002319</t>
   </si>
   <si>
     <t xml:space="preserve">0.57427453994751</t>
@@ -2558,10 +2558,10 @@
     <t xml:space="preserve">0.726300477981567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.789366483688354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.763054251670837</t>
+    <t xml:space="preserve">0.78936642408371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.763054192066193</t>
   </si>
   <si>
     <t xml:space="preserve">0.768483579158783</t>
@@ -2570,13 +2570,13 @@
     <t xml:space="preserve">0.827790558338165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.83530855178833</t>
+    <t xml:space="preserve">0.835308611392975</t>
   </si>
   <si>
     <t xml:space="preserve">0.901297986507416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.910486340522766</t>
+    <t xml:space="preserve">0.910486400127411</t>
   </si>
   <si>
     <t xml:space="preserve">1.00571143627167</t>
@@ -2594,16 +2594,16 @@
     <t xml:space="preserve">0.924685955047607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.925521671772003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938051581382751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922180950641632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892109513282776</t>
+    <t xml:space="preserve">0.925521612167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938051760196686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922180891036987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892109572887421</t>
   </si>
   <si>
     <t xml:space="preserve">0.893779933452606</t>
@@ -2612,16 +2612,16 @@
     <t xml:space="preserve">0.895450294017792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.823614180088043</t>
+    <t xml:space="preserve">0.823614120483398</t>
   </si>
   <si>
     <t xml:space="preserve">0.781013667583466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.824867129325867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806073009967804</t>
+    <t xml:space="preserve">0.824867188930511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806072950363159</t>
   </si>
   <si>
     <t xml:space="preserve">0.78560745716095</t>
@@ -2630,58 +2630,58 @@
     <t xml:space="preserve">0.802313923835754</t>
   </si>
   <si>
-    <t xml:space="preserve">0.797719240188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80189573764801</t>
+    <t xml:space="preserve">0.797719299793243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801895618438721</t>
   </si>
   <si>
     <t xml:space="preserve">0.798554956912994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.776419103145599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.782266736030579</t>
+    <t xml:space="preserve">0.776419043540955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.782266676425934</t>
   </si>
   <si>
     <t xml:space="preserve">0.766394913196564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.821525573730469</t>
+    <t xml:space="preserve">0.821525514125824</t>
   </si>
   <si>
     <t xml:space="preserve">0.795631527900696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.86370861530304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855355858802795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.844496965408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857861816883087</t>
+    <t xml:space="preserve">0.863708555698395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855355799198151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84449702501297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857861876487732</t>
   </si>
   <si>
     <t xml:space="preserve">0.836143374443054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.834890305995941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838649392127991</t>
+    <t xml:space="preserve">0.834890365600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838649451732635</t>
   </si>
   <si>
     <t xml:space="preserve">0.800225257873535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.773912906646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789783775806427</t>
+    <t xml:space="preserve">0.773912966251373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789783895015717</t>
   </si>
   <si>
     <t xml:space="preserve">0.77182525396347</t>
@@ -2693,10 +2693,10 @@
     <t xml:space="preserve">0.775583386421204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.786860406398773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79270726442337</t>
+    <t xml:space="preserve">0.786860466003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.792707204818726</t>
   </si>
   <si>
     <t xml:space="preserve">0.758877754211426</t>
@@ -2711,7 +2711,7 @@
     <t xml:space="preserve">0.809831023216248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.799807906150818</t>
+    <t xml:space="preserve">0.799807846546173</t>
   </si>
   <si>
     <t xml:space="preserve">0.780178070068359</t>
@@ -2720,55 +2720,55 @@
     <t xml:space="preserve">0.770989596843719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.740918278694153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.717947661876678</t>
+    <t xml:space="preserve">0.740918338298798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.717947721481323</t>
   </si>
   <si>
     <t xml:space="preserve">0.712100028991699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.684117376804352</t>
+    <t xml:space="preserve">0.684117317199707</t>
   </si>
   <si>
     <t xml:space="preserve">0.69079977273941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.69288843870163</t>
+    <t xml:space="preserve">0.692888379096985</t>
   </si>
   <si>
     <t xml:space="preserve">0.685787737369537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674094200134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.666576147079468</t>
+    <t xml:space="preserve">0.674094140529633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.666576087474823</t>
   </si>
   <si>
     <t xml:space="preserve">0.682029545307159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.687459051609039</t>
+    <t xml:space="preserve">0.687458992004395</t>
   </si>
   <si>
     <t xml:space="preserve">0.685370326042175</t>
   </si>
   <si>
-    <t xml:space="preserve">0.677852272987366</t>
+    <t xml:space="preserve">0.67785233259201</t>
   </si>
   <si>
     <t xml:space="preserve">0.69455873966217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.697482168674469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.703747272491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.698317766189575</t>
+    <t xml:space="preserve">0.697482109069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.70374721288681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69831782579422</t>
   </si>
   <si>
     <t xml:space="preserve">0.721288442611694</t>
@@ -2777,10 +2777,10 @@
     <t xml:space="preserve">0.72045373916626</t>
   </si>
   <si>
-    <t xml:space="preserve">0.742588698863983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.767648041248322</t>
+    <t xml:space="preserve">0.742588639259338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767647922039032</t>
   </si>
   <si>
     <t xml:space="preserve">0.718365073204041</t>
@@ -2789,10 +2789,10 @@
     <t xml:space="preserve">0.715024292469025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.781848430633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.75720739364624</t>
+    <t xml:space="preserve">0.7818483710289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.757207453250885</t>
   </si>
   <si>
     <t xml:space="preserve">0.778925061225891</t>
@@ -2801,7 +2801,7 @@
     <t xml:space="preserve">0.79646623134613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.825284540653229</t>
+    <t xml:space="preserve">0.825284600257874</t>
   </si>
   <si>
     <t xml:space="preserve">0.850343704223633</t>
@@ -2816,10 +2816,10 @@
     <t xml:space="preserve">0.858696639537811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.843661248683929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872062265872955</t>
+    <t xml:space="preserve">0.843661367893219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8720623254776</t>
   </si>
   <si>
     <t xml:space="preserve">0.852014183998108</t>
@@ -2828,34 +2828,34 @@
     <t xml:space="preserve">0.8545201420784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.812755405902863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807743310928345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81317275762558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828626096248627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.832802593708038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820690751075745</t>
+    <t xml:space="preserve">0.812755346298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807743430137634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.813172698020935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828626155853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.832802534103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8206906914711</t>
   </si>
   <si>
     <t xml:space="preserve">0.749689340591431</t>
   </si>
   <si>
-    <t xml:space="preserve">0.710847020149231</t>
+    <t xml:space="preserve">0.710846960544586</t>
   </si>
   <si>
     <t xml:space="preserve">0.654464364051819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.633998811244965</t>
+    <t xml:space="preserve">0.63399875164032</t>
   </si>
   <si>
     <t xml:space="preserve">0.645275890827179</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">0.684534668922424</t>
   </si>
   <si>
-    <t xml:space="preserve">0.68912935256958</t>
+    <t xml:space="preserve">0.689129412174225</t>
   </si>
   <si>
     <t xml:space="preserve">0.753030061721802</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">0.787696063518524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803148627281189</t>
+    <t xml:space="preserve">0.803148686885834</t>
   </si>
   <si>
     <t xml:space="preserve">0.856191456317902</t>
@@ -2891,19 +2891,19 @@
     <t xml:space="preserve">0.877073407173157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.90046226978302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.889603555202484</t>
+    <t xml:space="preserve">0.900462329387665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.889603435993195</t>
   </si>
   <si>
     <t xml:space="preserve">0.887097477912903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.890439212322235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.881250739097595</t>
+    <t xml:space="preserve">0.89043915271759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88125067949295</t>
   </si>
   <si>
     <t xml:space="preserve">0.904638767242432</t>
@@ -2912,28 +2912,28 @@
     <t xml:space="preserve">0.89294421672821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.90213268995285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882085502147675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867884993553162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841155409812927</t>
+    <t xml:space="preserve">0.902132749557495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88208544254303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867885053157806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841155350208282</t>
   </si>
   <si>
     <t xml:space="preserve">0.839484989643097</t>
   </si>
   <si>
-    <t xml:space="preserve">0.841991007328033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840320646762848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.859532237052917</t>
+    <t xml:space="preserve">0.841990947723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840320587158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.859532177448273</t>
   </si>
   <si>
     <t xml:space="preserve">0.905474364757538</t>
@@ -2945,52 +2945,52 @@
     <t xml:space="preserve">0.87289696931839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.906310141086578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943898379802704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953922510147095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957263290882111</t>
+    <t xml:space="preserve">0.906310081481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943898439407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953922390937805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9572634100914</t>
   </si>
   <si>
     <t xml:space="preserve">0.965616941452026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978146076202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961439728736877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934710085391998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902968347072601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874567449092865</t>
+    <t xml:space="preserve">0.978146135807037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961439669132233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934710025787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902968287467957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87456738948822</t>
   </si>
   <si>
     <t xml:space="preserve">0.852849841117859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.867050230503082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.878744661808014</t>
+    <t xml:space="preserve">0.867050290107727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.878744721412659</t>
   </si>
   <si>
     <t xml:space="preserve">0.907144844532013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.931369364261627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921345174312592</t>
+    <t xml:space="preserve">0.931369304656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921345114707947</t>
   </si>
   <si>
     <t xml:space="preserve">0.927191972732544</t>
@@ -2999,7 +2999,7 @@
     <t xml:space="preserve">0.912992417812347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947240114212036</t>
+    <t xml:space="preserve">0.947240054607391</t>
   </si>
   <si>
     <t xml:space="preserve">0.899626731872559</t>
@@ -3011,13 +3011,13 @@
     <t xml:space="preserve">0.93888646364212</t>
   </si>
   <si>
-    <t xml:space="preserve">0.937215983867645</t>
+    <t xml:space="preserve">0.937216103076935</t>
   </si>
   <si>
     <t xml:space="preserve">0.942228078842163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941392481327057</t>
+    <t xml:space="preserve">0.941392540931702</t>
   </si>
   <si>
     <t xml:space="preserve">0.94640451669693</t>
@@ -3026,22 +3026,22 @@
     <t xml:space="preserve">0.935545742511749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.975639939308167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14687848091125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18947923183441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17360818386078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16024327278137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15773749351501</t>
+    <t xml:space="preserve">0.975640118122101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14687860012054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18947911262512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17360830307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16024339199066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15773737430573</t>
   </si>
   <si>
     <t xml:space="preserve">1.17193794250488</t>
@@ -3050,31 +3050,31 @@
     <t xml:space="preserve">1.1385258436203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10928928852081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11096048355103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10678422451019</t>
+    <t xml:space="preserve">1.10928916931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11096060276031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1067841053009</t>
   </si>
   <si>
     <t xml:space="preserve">1.11179530620575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13100779056549</t>
+    <t xml:space="preserve">1.13100755214691</t>
   </si>
   <si>
     <t xml:space="preserve">1.12098371982574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16358530521393</t>
+    <t xml:space="preserve">1.16358518600464</t>
   </si>
   <si>
     <t xml:space="preserve">1.14520823955536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11513686180115</t>
+    <t xml:space="preserve">1.11513698101044</t>
   </si>
   <si>
     <t xml:space="preserve">1.10761880874634</t>
@@ -3083,16 +3083,16 @@
     <t xml:space="preserve">1.37742400169373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37241208553314</t>
+    <t xml:space="preserve">1.37241196632385</t>
   </si>
   <si>
     <t xml:space="preserve">1.43923687934875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43673098087311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44007158279419</t>
+    <t xml:space="preserve">1.43673086166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44007170200348</t>
   </si>
   <si>
     <t xml:space="preserve">1.40665972232819</t>
@@ -3107,10 +3107,10 @@
     <t xml:space="preserve">1.43840134143829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47682559490204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45928430557251</t>
+    <t xml:space="preserve">1.47682547569275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45928418636322</t>
   </si>
   <si>
     <t xml:space="preserve">1.44090747833252</t>
@@ -3119,13 +3119,13 @@
     <t xml:space="preserve">1.43338942527771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48100197315216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41334199905396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4258713722229</t>
+    <t xml:space="preserve">1.48100185394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41334223747253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42587125301361</t>
   </si>
   <si>
     <t xml:space="preserve">1.5879213809967</t>
@@ -3134,37 +3134,37 @@
     <t xml:space="preserve">1.550332903862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62634551525116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61214601993561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62049865722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61966300010681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62718117237091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6138162612915</t>
+    <t xml:space="preserve">1.62634539604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61214590072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62049853801727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61966288089752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62718093395233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61381614208221</t>
   </si>
   <si>
     <t xml:space="preserve">1.45677816867828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39830684661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34317624568939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35654091835022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35904729366302</t>
+    <t xml:space="preserve">1.39830696582794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34317636489868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35654127597809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35904705524445</t>
   </si>
   <si>
     <t xml:space="preserve">1.36489391326904</t>
@@ -3173,34 +3173,34 @@
     <t xml:space="preserve">1.40276598930359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4346672296524</t>
+    <t xml:space="preserve">1.43466711044312</t>
   </si>
   <si>
     <t xml:space="preserve">1.41251361370087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39390432834625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39213216304779</t>
+    <t xml:space="preserve">1.39390444755554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39213228225708</t>
   </si>
   <si>
     <t xml:space="preserve">1.3336466550827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44795918464661</t>
+    <t xml:space="preserve">1.44795906543732</t>
   </si>
   <si>
     <t xml:space="preserve">1.49049425125122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51796472072601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53214287757874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58442556858063</t>
+    <t xml:space="preserve">1.51796460151672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53214299678802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58442544937134</t>
   </si>
   <si>
     <t xml:space="preserve">1.52859854698181</t>
@@ -3212,16 +3212,16 @@
     <t xml:space="preserve">1.54454898834229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53834593296051</t>
+    <t xml:space="preserve">1.5383460521698</t>
   </si>
   <si>
     <t xml:space="preserve">1.5587272644043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5764502286911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61455452442169</t>
+    <t xml:space="preserve">1.57645034790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61455428600311</t>
   </si>
   <si>
     <t xml:space="preserve">1.60657906532288</t>
@@ -3230,22 +3230,22 @@
     <t xml:space="preserve">1.5693610906601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58885633945465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60392069816589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63582193851471</t>
+    <t xml:space="preserve">1.58885622024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6039205789566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63582181930542</t>
   </si>
   <si>
     <t xml:space="preserve">1.62518811225891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61278223991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58353924751282</t>
+    <t xml:space="preserve">1.61278212070465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58353936672211</t>
   </si>
   <si>
     <t xml:space="preserve">1.51885080337524</t>
@@ -3254,25 +3254,25 @@
     <t xml:space="preserve">1.520623087883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49315249919891</t>
+    <t xml:space="preserve">1.4931526184082</t>
   </si>
   <si>
     <t xml:space="preserve">1.49758338928223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52505373954773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5073310136795</t>
+    <t xml:space="preserve">1.52505362033844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50733089447021</t>
   </si>
   <si>
     <t xml:space="preserve">1.50112795829773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54011833667755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53037071228027</t>
+    <t xml:space="preserve">1.54011821746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53037059307098</t>
   </si>
   <si>
     <t xml:space="preserve">1.55341041088104</t>
@@ -3284,16 +3284,16 @@
     <t xml:space="preserve">1.66329228878021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56404411792755</t>
+    <t xml:space="preserve">1.56404423713684</t>
   </si>
   <si>
     <t xml:space="preserve">1.51707851886749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48872184753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4656822681427</t>
+    <t xml:space="preserve">1.48872196674347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46568214893341</t>
   </si>
   <si>
     <t xml:space="preserve">1.42403340339661</t>
@@ -3302,16 +3302,16 @@
     <t xml:space="preserve">1.44707310199738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46656811237335</t>
+    <t xml:space="preserve">1.46656835079193</t>
   </si>
   <si>
     <t xml:space="preserve">1.61809897422791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82900106906891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84672403335571</t>
+    <t xml:space="preserve">1.8290011882782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.846724152565</t>
   </si>
   <si>
     <t xml:space="preserve">1.90520966053009</t>
@@ -3320,13 +3320,13 @@
     <t xml:space="preserve">1.89634835720062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98319017887115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03635907173157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09129977226257</t>
+    <t xml:space="preserve">1.98319041728973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03635883331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09130001068115</t>
   </si>
   <si>
     <t xml:space="preserve">2.17105293273926</t>
@@ -3335,7 +3335,7 @@
     <t xml:space="preserve">1.96015048027039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88925898075104</t>
+    <t xml:space="preserve">1.88925909996033</t>
   </si>
   <si>
     <t xml:space="preserve">1.96192276477814</t>
@@ -3347,13 +3347,13 @@
     <t xml:space="preserve">2.01863622665405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10902309417725</t>
+    <t xml:space="preserve">2.10902285575867</t>
   </si>
   <si>
     <t xml:space="preserve">2.0753493309021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10547804832458</t>
+    <t xml:space="preserve">2.10547828674316</t>
   </si>
   <si>
     <t xml:space="preserve">2.13737940788269</t>
@@ -3371,28 +3371,28 @@
     <t xml:space="preserve">2.17636966705322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18168663978577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24371695518494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17991423606873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1232008934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14624071121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19763708114624</t>
+    <t xml:space="preserve">2.18168640136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24371671676636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1799144744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12320113182068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14624047279358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19763731956482</t>
   </si>
   <si>
     <t xml:space="preserve">2.30574655532837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28625154495239</t>
+    <t xml:space="preserve">2.28625130653381</t>
   </si>
   <si>
     <t xml:space="preserve">2.31992506980896</t>
@@ -3404,25 +3404,25 @@
     <t xml:space="preserve">2.41740083694458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4457573890686</t>
+    <t xml:space="preserve">2.44575762748718</t>
   </si>
   <si>
     <t xml:space="preserve">2.38372755050659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46348023414612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42448997497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47411394119263</t>
+    <t xml:space="preserve">2.4634804725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42449021339417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47411417961121</t>
   </si>
   <si>
     <t xml:space="preserve">2.51310443878174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50956010818481</t>
+    <t xml:space="preserve">2.50955963134766</t>
   </si>
   <si>
     <t xml:space="preserve">2.43157911300659</t>
@@ -3437,10 +3437,10 @@
     <t xml:space="preserve">2.33942031860352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37841033935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21004343032837</t>
+    <t xml:space="preserve">2.37841057777405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21004319190979</t>
   </si>
   <si>
     <t xml:space="preserve">2.38904452323914</t>
@@ -3452,28 +3452,28 @@
     <t xml:space="preserve">2.49183702468872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5609564781189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65666007995605</t>
+    <t xml:space="preserve">2.56095623970032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6566596031189</t>
   </si>
   <si>
     <t xml:space="preserve">2.64070916175842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63184785842896</t>
+    <t xml:space="preserve">2.63184762001038</t>
   </si>
   <si>
     <t xml:space="preserve">2.65311527252197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59640192985535</t>
+    <t xml:space="preserve">2.59640216827393</t>
   </si>
   <si>
     <t xml:space="preserve">2.52373814582825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33233070373535</t>
+    <t xml:space="preserve">2.33233118057251</t>
   </si>
   <si>
     <t xml:space="preserve">2.31815266609192</t>
@@ -3485,28 +3485,28 @@
     <t xml:space="preserve">2.28270697593689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2756175994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25966715812683</t>
+    <t xml:space="preserve">2.27561783790588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25966739654541</t>
   </si>
   <si>
     <t xml:space="preserve">2.30929112434387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27916216850281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28802394866943</t>
+    <t xml:space="preserve">2.27916264533997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28802371025085</t>
   </si>
   <si>
     <t xml:space="preserve">2.26852869987488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36600470542908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30751943588257</t>
+    <t xml:space="preserve">2.3660044670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30751919746399</t>
   </si>
   <si>
     <t xml:space="preserve">2.24017214775085</t>
@@ -3518,55 +3518,55 @@
     <t xml:space="preserve">2.16041922569275</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17459726333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13915157318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15687465667725</t>
+    <t xml:space="preserve">2.17459750175476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13915181159973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15687441825867</t>
   </si>
   <si>
     <t xml:space="preserve">2.05762648582458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16928052902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19586491584778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13560700416565</t>
+    <t xml:space="preserve">2.16928029060364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1958646774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13560748100281</t>
   </si>
   <si>
     <t xml:space="preserve">2.39258885383606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39436101913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06648778915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99382412433624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12142872810364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1196563243866</t>
+    <t xml:space="preserve">2.39436078071594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06648802757263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99382400512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12142848968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11965656280518</t>
   </si>
   <si>
     <t xml:space="preserve">2.09484457969666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01331901550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08066606521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9920517206192</t>
+    <t xml:space="preserve">2.01331925392151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08066630363464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99205148220062</t>
   </si>
   <si>
     <t xml:space="preserve">2.03458666801453</t>
@@ -3581,13 +3581,13 @@
     <t xml:space="preserve">2.01509141921997</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00445771217346</t>
+    <t xml:space="preserve">2.00445795059204</t>
   </si>
   <si>
     <t xml:space="preserve">1.86799156665802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90166485309601</t>
+    <t xml:space="preserve">1.90166509151459</t>
   </si>
   <si>
     <t xml:space="preserve">1.80596160888672</t>
@@ -3596,25 +3596,25 @@
     <t xml:space="preserve">1.6455694437027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5631582736969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56847476959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6801290512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57999491691589</t>
+    <t xml:space="preserve">1.56315815448761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56847500801086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68012917041779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57999467849731</t>
   </si>
   <si>
     <t xml:space="preserve">1.59505915641785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.659747838974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78646636009216</t>
+    <t xml:space="preserve">1.65974771976471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78646647930145</t>
   </si>
   <si>
     <t xml:space="preserve">1.75545120239258</t>
@@ -3623,43 +3623,43 @@
     <t xml:space="preserve">1.73684227466583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73418378829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70671319961548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65088629722595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66595077514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67924296855927</t>
+    <t xml:space="preserve">1.73418402671814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70671331882477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65088641643524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66595065593719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67924284934998</t>
   </si>
   <si>
     <t xml:space="preserve">1.72798073291779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8644472360611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83431828022003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74570381641388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78469407558441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76254034042358</t>
+    <t xml:space="preserve">1.86444699764252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83431804180145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74570369720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78469395637512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76254045963287</t>
   </si>
   <si>
     <t xml:space="preserve">1.72886693477631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67038142681122</t>
+    <t xml:space="preserve">1.67038154602051</t>
   </si>
   <si>
     <t xml:space="preserve">1.64113867282867</t>
@@ -3668,34 +3668,34 @@
     <t xml:space="preserve">1.60126221179962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61987102031708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71025788784027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70051038265228</t>
+    <t xml:space="preserve">1.61987113952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71025800704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70051050186157</t>
   </si>
   <si>
     <t xml:space="preserve">1.67835676670074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62961888313293</t>
+    <t xml:space="preserve">1.62961876392365</t>
   </si>
   <si>
     <t xml:space="preserve">1.63936650753021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63050496578217</t>
+    <t xml:space="preserve">1.63050508499146</t>
   </si>
   <si>
     <t xml:space="preserve">1.60923755168915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62075746059418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55075204372406</t>
+    <t xml:space="preserve">1.62075757980347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55075216293335</t>
   </si>
   <si>
     <t xml:space="preserve">1.46302378177643</t>
@@ -3704,7 +3704,7 @@
     <t xml:space="preserve">1.47897434234619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54189050197601</t>
+    <t xml:space="preserve">1.5418906211853</t>
   </si>
   <si>
     <t xml:space="preserve">1.60835146903992</t>
@@ -3716,7 +3716,7 @@
     <t xml:space="preserve">1.64468324184418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6074652671814</t>
+    <t xml:space="preserve">1.60746514797211</t>
   </si>
   <si>
     <t xml:space="preserve">1.6003760099411</t>
@@ -3725,82 +3725,82 @@
     <t xml:space="preserve">1.52594006061554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52150917053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6313910484314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64734160900116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72266399860382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69076287746429</t>
+    <t xml:space="preserve">1.52150928974152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63139092922211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64734172821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72266411781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.690762758255</t>
   </si>
   <si>
     <t xml:space="preserve">1.71646106243134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78114950656891</t>
+    <t xml:space="preserve">1.78114938735962</t>
   </si>
   <si>
     <t xml:space="preserve">1.84495186805725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80773377418518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79887211322784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79532790184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65797543525696</t>
+    <t xml:space="preserve">1.80773365497589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79887223243713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79532778263092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65797555446625</t>
   </si>
   <si>
     <t xml:space="preserve">1.45593464374542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41871643066406</t>
+    <t xml:space="preserve">1.41871654987335</t>
   </si>
   <si>
     <t xml:space="preserve">1.46506786346436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47688317298889</t>
+    <t xml:space="preserve">1.47688293457031</t>
   </si>
   <si>
     <t xml:space="preserve">1.48960697650909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45779716968536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47597420215607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43689358234406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47415626049042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48142731189728</t>
+    <t xml:space="preserve">1.45779705047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47597408294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43689346313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47415637969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48142719268799</t>
   </si>
   <si>
     <t xml:space="preserve">1.41417229175568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37236499786377</t>
+    <t xml:space="preserve">1.37236511707306</t>
   </si>
   <si>
     <t xml:space="preserve">1.37872707843781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30147480964661</t>
+    <t xml:space="preserve">1.30147469043732</t>
   </si>
   <si>
     <t xml:space="preserve">1.32783138751984</t>
@@ -3812,25 +3812,25 @@
     <t xml:space="preserve">1.40781044960022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3859977722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31510758399963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28420650959015</t>
+    <t xml:space="preserve">1.38599789142609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31510746479034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28420674800873</t>
   </si>
   <si>
     <t xml:space="preserve">1.27966237068176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30874574184418</t>
+    <t xml:space="preserve">1.30874562263489</t>
   </si>
   <si>
     <t xml:space="preserve">1.3269225358963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39781284332275</t>
+    <t xml:space="preserve">1.39781296253204</t>
   </si>
   <si>
     <t xml:space="preserve">1.37145614624023</t>
@@ -3842,22 +3842,22 @@
     <t xml:space="preserve">1.35691475868225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29693043231964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31328988075256</t>
+    <t xml:space="preserve">1.29693055152893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31328976154327</t>
   </si>
   <si>
     <t xml:space="preserve">1.33328461647034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41962540149689</t>
+    <t xml:space="preserve">1.41962552070618</t>
   </si>
   <si>
     <t xml:space="preserve">1.42689633369446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40144836902618</t>
+    <t xml:space="preserve">1.40144848823547</t>
   </si>
   <si>
     <t xml:space="preserve">1.44416427612305</t>
@@ -3887,31 +3887,31 @@
     <t xml:space="preserve">1.50051307678223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48051834106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40326619148254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43234920501709</t>
+    <t xml:space="preserve">1.48051846027374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40326607227325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43234932422638</t>
   </si>
   <si>
     <t xml:space="preserve">1.41144561767578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34691715240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34328198432922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37327396869659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3760005235672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36236774921417</t>
+    <t xml:space="preserve">1.34691739082336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34328186511993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37327408790588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37600064277649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36236763000488</t>
   </si>
   <si>
     <t xml:space="preserve">1.39235973358154</t>
@@ -3929,13 +3929,13 @@
     <t xml:space="preserve">1.35964131355286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41326332092285</t>
+    <t xml:space="preserve">1.41326344013214</t>
   </si>
   <si>
     <t xml:space="preserve">1.43507587909698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41689896583557</t>
+    <t xml:space="preserve">1.41689884662628</t>
   </si>
   <si>
     <t xml:space="preserve">1.46870338916779</t>
@@ -3947,16 +3947,16 @@
     <t xml:space="preserve">1.39872181415558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70591354370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6859188079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58412754535675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57867443561554</t>
+    <t xml:space="preserve">1.70591342449188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68591868877411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58412742614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57867431640625</t>
   </si>
   <si>
     <t xml:space="preserve">1.59139823913574</t>
@@ -3965,10 +3965,10 @@
     <t xml:space="preserve">1.56322383880615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4996041059494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55777084827423</t>
+    <t xml:space="preserve">1.49960434436798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55777072906494</t>
   </si>
   <si>
     <t xml:space="preserve">1.55231761932373</t>
@@ -3980,7 +3980,7 @@
     <t xml:space="preserve">1.58140087127686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53777611255646</t>
+    <t xml:space="preserve">1.53777599334717</t>
   </si>
   <si>
     <t xml:space="preserve">1.52323436737061</t>
@@ -3992,13 +3992,13 @@
     <t xml:space="preserve">1.53323173522949</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59503364562988</t>
+    <t xml:space="preserve">1.59503352642059</t>
   </si>
   <si>
     <t xml:space="preserve">1.59412467479706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64047598838806</t>
+    <t xml:space="preserve">1.64047610759735</t>
   </si>
   <si>
     <t xml:space="preserve">1.65774440765381</t>
@@ -4007,19 +4007,19 @@
     <t xml:space="preserve">1.65865325927734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65956211090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67046821117401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7631710767746</t>
+    <t xml:space="preserve">1.65956199169159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6704683303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76317119598389</t>
   </si>
   <si>
     <t xml:space="preserve">1.79225432872772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78861880302429</t>
+    <t xml:space="preserve">1.78861904144287</t>
   </si>
   <si>
     <t xml:space="preserve">1.73045253753662</t>
@@ -4028,19 +4028,19 @@
     <t xml:space="preserve">1.71772849559784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72681713104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77135074138641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73136138916016</t>
+    <t xml:space="preserve">1.72681701183319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77135062217712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73136126995087</t>
   </si>
   <si>
     <t xml:space="preserve">1.75135612487793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78771007061005</t>
+    <t xml:space="preserve">1.78770995140076</t>
   </si>
   <si>
     <t xml:space="preserve">1.8486031293869</t>
@@ -4049,52 +4049,52 @@
     <t xml:space="preserve">1.86678004264832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87223315238953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89949882030487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93403518199921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94494116306305</t>
+    <t xml:space="preserve">1.87223303318024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89949870109558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9340353012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94494140148163</t>
   </si>
   <si>
     <t xml:space="preserve">1.90676963329315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95402991771698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97038912773132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00492525100708</t>
+    <t xml:space="preserve">1.95402979850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97038924694061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00492548942566</t>
   </si>
   <si>
     <t xml:space="preserve">1.99583721160889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97220695018768</t>
+    <t xml:space="preserve">1.97220683097839</t>
   </si>
   <si>
     <t xml:space="preserve">1.97402453422546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9903838634491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04491472244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13398241996765</t>
+    <t xml:space="preserve">1.99038398265839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04491519927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13398265838623</t>
   </si>
   <si>
     <t xml:space="preserve">2.15397691726685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12307596206665</t>
+    <t xml:space="preserve">2.12307620048523</t>
   </si>
   <si>
     <t xml:space="preserve">2.11944079399109</t>
@@ -4103,7 +4103,7 @@
     <t xml:space="preserve">2.13761758804321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16851878166199</t>
+    <t xml:space="preserve">2.16851854324341</t>
   </si>
   <si>
     <t xml:space="preserve">2.11035227775574</t>
@@ -4112,52 +4112,52 @@
     <t xml:space="preserve">2.10308122634888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10126352310181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97584223747253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02128481864929</t>
+    <t xml:space="preserve">2.10126376152039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97584235668182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02128505706787</t>
   </si>
   <si>
     <t xml:space="preserve">1.85223865509033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89041018486023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91222262382507</t>
+    <t xml:space="preserve">1.89041006565094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91222274303436</t>
   </si>
   <si>
     <t xml:space="preserve">1.92676424980164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93585300445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93948817253113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90131652355194</t>
+    <t xml:space="preserve">1.93585288524628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93948829174042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90131664276123</t>
   </si>
   <si>
     <t xml:space="preserve">1.91404032707214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96311819553375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96857130527496</t>
+    <t xml:space="preserve">1.96311855316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96857118606567</t>
   </si>
   <si>
     <t xml:space="preserve">2.03219103813171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05945658683777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10489892959595</t>
+    <t xml:space="preserve">2.05945682525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10489916801453</t>
   </si>
   <si>
     <t xml:space="preserve">2.12852931022644</t>
@@ -4169,28 +4169,28 @@
     <t xml:space="preserve">2.09944581985474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01946711540222</t>
+    <t xml:space="preserve">2.01946687698364</t>
   </si>
   <si>
     <t xml:space="preserve">2.07218050956726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06309199333191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0376443862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00310754776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01219654083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01764941215515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00128984451294</t>
+    <t xml:space="preserve">2.06309175491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03764414787292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00310778617859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01219630241394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01764917373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00129008293152</t>
   </si>
   <si>
     <t xml:space="preserve">2.27394556999207</t>
@@ -4202,34 +4202,34 @@
     <t xml:space="preserve">2.31757020950317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3084819316864</t>
+    <t xml:space="preserve">2.30848145484924</t>
   </si>
   <si>
     <t xml:space="preserve">2.33211183547974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37210130691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41572618484497</t>
+    <t xml:space="preserve">2.3721010684967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41572594642639</t>
   </si>
   <si>
     <t xml:space="preserve">2.375736951828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40845561027527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39754891395569</t>
+    <t xml:space="preserve">2.40845537185669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39754915237427</t>
   </si>
   <si>
     <t xml:space="preserve">2.38846063613892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39209580421448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3575599193573</t>
+    <t xml:space="preserve">2.39209604263306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35755968093872</t>
   </si>
   <si>
     <t xml:space="preserve">2.34483575820923</t>
@@ -4238,37 +4238,37 @@
     <t xml:space="preserve">2.30666422843933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31575274467468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33574724197388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33938241004944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38118958473206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40663766860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40481972694397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39027857780457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37937188148499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32302355766296</t>
+    <t xml:space="preserve">2.3157525062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3357470035553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33938264846802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38118982315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40663743019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40481996536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39027833938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37937211990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32302331924438</t>
   </si>
   <si>
     <t xml:space="preserve">2.28666925430298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18487787246704</t>
+    <t xml:space="preserve">2.18487811088562</t>
   </si>
   <si>
     <t xml:space="preserve">2.23213839530945</t>
@@ -4277,16 +4277,16 @@
     <t xml:space="preserve">2.18306016921997</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14307069778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20487260818481</t>
+    <t xml:space="preserve">2.143070936203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20487284660339</t>
   </si>
   <si>
     <t xml:space="preserve">2.20669031143188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17033648490906</t>
+    <t xml:space="preserve">2.17033624649048</t>
   </si>
   <si>
     <t xml:space="preserve">2.13943552970886</t>
@@ -4295,13 +4295,13 @@
     <t xml:space="preserve">2.14670634269714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14852404594421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19578409194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19033122062683</t>
+    <t xml:space="preserve">2.14852380752563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19578385353088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19033145904541</t>
   </si>
   <si>
     <t xml:space="preserve">2.26849246025085</t>
@@ -4310,58 +4310,58 @@
     <t xml:space="preserve">2.24667978286743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24304413795471</t>
+    <t xml:space="preserve">2.24304437637329</t>
   </si>
   <si>
     <t xml:space="preserve">2.25213289260864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30121088027954</t>
+    <t xml:space="preserve">2.30121111869812</t>
   </si>
   <si>
     <t xml:space="preserve">2.28303384780884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34120011329651</t>
+    <t xml:space="preserve">2.34120035171509</t>
   </si>
   <si>
     <t xml:space="preserve">2.47934556007385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44844460487366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4884340763092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46843981742859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47207474708557</t>
+    <t xml:space="preserve">2.44844484329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48843431472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46843957901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47207498550415</t>
   </si>
   <si>
     <t xml:space="preserve">2.45935106277466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45753335952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43390297889709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51388216018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46480417251587</t>
+    <t xml:space="preserve">2.45753312110901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43390321731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51388192176819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46480393409729</t>
   </si>
   <si>
     <t xml:space="preserve">2.50297570228577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47025728225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40118455886841</t>
+    <t xml:space="preserve">2.4702570438385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40118432044983</t>
   </si>
   <si>
     <t xml:space="preserve">2.36664843559265</t>
@@ -4379,7 +4379,7 @@
     <t xml:space="preserve">2.29212260246277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27030992507935</t>
+    <t xml:space="preserve">2.27030968666077</t>
   </si>
   <si>
     <t xml:space="preserve">2.22668528556824</t>
@@ -4397,19 +4397,19 @@
     <t xml:space="preserve">2.29939293861389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41936135292053</t>
+    <t xml:space="preserve">2.41936159133911</t>
   </si>
   <si>
     <t xml:space="preserve">2.4320855140686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42117929458618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43935608863831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25599455833435</t>
+    <t xml:space="preserve">2.4211790561676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43935632705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25599431991577</t>
   </si>
   <si>
     <t xml:space="preserve">2.28207540512085</t>
@@ -4430,25 +4430,25 @@
     <t xml:space="preserve">2.31188225746155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36590671539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40130233764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36404395103455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29697847366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32678532600403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34168839454651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33982610702515</t>
+    <t xml:space="preserve">2.36590647697449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40130209922791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36404371261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29697895050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32678508758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34168863296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33982586860657</t>
   </si>
   <si>
     <t xml:space="preserve">2.36963248252869</t>
@@ -4475,19 +4475,19 @@
     <t xml:space="preserve">2.30443024635315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29325294494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33051156997681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31374502182007</t>
+    <t xml:space="preserve">2.29325270652771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33051133155823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31374478340149</t>
   </si>
   <si>
     <t xml:space="preserve">2.28952693939209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22432494163513</t>
+    <t xml:space="preserve">2.22432470321655</t>
   </si>
   <si>
     <t xml:space="preserve">2.20569562911987</t>
@@ -4496,7 +4496,7 @@
     <t xml:space="preserve">2.16098570823669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14049363136292</t>
+    <t xml:space="preserve">2.14049339294434</t>
   </si>
   <si>
     <t xml:space="preserve">2.1069610118866</t>
@@ -4505,13 +4505,13 @@
     <t xml:space="preserve">2.09950923919678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12559032440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10882377624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09019446372986</t>
+    <t xml:space="preserve">2.12559008598328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1088240146637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09019470214844</t>
   </si>
   <si>
     <t xml:space="preserve">2.0585253238678</t>
@@ -4520,19 +4520,19 @@
     <t xml:space="preserve">2.04362154006958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04921078681946</t>
+    <t xml:space="preserve">2.04921054840088</t>
   </si>
   <si>
     <t xml:space="preserve">2.08460593223572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06411385536194</t>
+    <t xml:space="preserve">2.06411409378052</t>
   </si>
   <si>
     <t xml:space="preserve">2.0510733127594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04175877571106</t>
+    <t xml:space="preserve">2.04175853729248</t>
   </si>
   <si>
     <t xml:space="preserve">2.09205770492554</t>
@@ -4541,13 +4541,13 @@
     <t xml:space="preserve">2.15912270545959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15353417396545</t>
+    <t xml:space="preserve">2.1535336971283</t>
   </si>
   <si>
     <t xml:space="preserve">2.13863062858582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12186431884766</t>
+    <t xml:space="preserve">2.12186455726624</t>
   </si>
   <si>
     <t xml:space="preserve">2.06970238685608</t>
@@ -4568,37 +4568,37 @@
     <t xml:space="preserve">2.0007746219635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99332308769226</t>
+    <t xml:space="preserve">1.99332296848297</t>
   </si>
   <si>
     <t xml:space="preserve">1.97469365596771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95606458187103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9262580871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86478173732758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77349865436554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78095006942749</t>
+    <t xml:space="preserve">1.95606434345245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92625796794891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.864781498909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77349853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78095018863678</t>
   </si>
   <si>
     <t xml:space="preserve">1.78467607498169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80330526828766</t>
+    <t xml:space="preserve">1.80330514907837</t>
   </si>
   <si>
     <t xml:space="preserve">1.83311200141907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80237376689911</t>
+    <t xml:space="preserve">1.80237364768982</t>
   </si>
   <si>
     <t xml:space="preserve">1.75673234462738</t>
@@ -4613,7 +4613,7 @@
     <t xml:space="preserve">1.71947395801544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67196953296661</t>
+    <t xml:space="preserve">1.67196941375732</t>
   </si>
   <si>
     <t xml:space="preserve">1.69991326332092</t>
@@ -4622,16 +4622,16 @@
     <t xml:space="preserve">1.66638076305389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.616082072258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63005375862122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63377964496613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63564252853394</t>
+    <t xml:space="preserve">1.61608195304871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63005387783051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63377952575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63564264774323</t>
   </si>
   <si>
     <t xml:space="preserve">1.64775156974792</t>
@@ -4640,19 +4640,19 @@
     <t xml:space="preserve">1.64682006835938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53131926059723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5499484539032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53877067565918</t>
+    <t xml:space="preserve">1.53131914138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54994833469391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53877079486847</t>
   </si>
   <si>
     <t xml:space="preserve">1.54529106616974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54249656200409</t>
+    <t xml:space="preserve">1.54249668121338</t>
   </si>
   <si>
     <t xml:space="preserve">1.55087971687317</t>
@@ -4700,28 +4700,28 @@
     <t xml:space="preserve">1.65706610679626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68966722488403</t>
+    <t xml:space="preserve">1.68966710567474</t>
   </si>
   <si>
     <t xml:space="preserve">1.69153010845184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66917502880096</t>
+    <t xml:space="preserve">1.66917514801025</t>
   </si>
   <si>
     <t xml:space="preserve">1.6682436466217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67662680149078</t>
+    <t xml:space="preserve">1.67662668228149</t>
   </si>
   <si>
     <t xml:space="preserve">1.69059872627258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72785711288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84242653846741</t>
+    <t xml:space="preserve">1.72785699367523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8424266576767</t>
   </si>
   <si>
     <t xml:space="preserve">1.84801530838013</t>
@@ -4733,7 +4733,7 @@
     <t xml:space="preserve">1.92998361587524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97655653953552</t>
+    <t xml:space="preserve">1.97655665874481</t>
   </si>
   <si>
     <t xml:space="preserve">1.96165335178375</t>
@@ -4757,13 +4757,13 @@
     <t xml:space="preserve">1.99704885482788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09764623641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09392046928406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11068677902222</t>
+    <t xml:space="preserve">2.09764647483826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09392023086548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1106870174408</t>
   </si>
   <si>
     <t xml:space="preserve">2.08646893501282</t>
@@ -4778,13 +4778,13 @@
     <t xml:space="preserve">2.10137224197388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03617000579834</t>
+    <t xml:space="preserve">2.03617024421692</t>
   </si>
   <si>
     <t xml:space="preserve">2.0026376247406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98028254508972</t>
+    <t xml:space="preserve">1.98028242588043</t>
   </si>
   <si>
     <t xml:space="preserve">2.01008915901184</t>
@@ -4793,34 +4793,34 @@
     <t xml:space="preserve">2.01567792892456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98214542865753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90017700195312</t>
+    <t xml:space="preserve">1.98214554786682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90017688274384</t>
   </si>
   <si>
     <t xml:space="preserve">1.91694331169128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8927253484726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92812085151672</t>
+    <t xml:space="preserve">1.89272522926331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92812061309814</t>
   </si>
   <si>
     <t xml:space="preserve">1.95420169830322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06783986091614</t>
+    <t xml:space="preserve">2.06783962249756</t>
   </si>
   <si>
     <t xml:space="preserve">2.03989601135254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07529139518738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09578347206116</t>
+    <t xml:space="preserve">2.0752911567688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09578371047974</t>
   </si>
   <si>
     <t xml:space="preserve">2.11813831329346</t>
@@ -5955,6 +5955,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.30600023269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35400009155273</t>
   </si>
 </sst>
 </file>
@@ -71709,7 +71712,7 @@
     </row>
     <row r="2517">
       <c r="A2517" s="1" t="n">
-        <v>45982.6909722222</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B2517" t="n">
         <v>528908</v>
@@ -71730,6 +71733,32 @@
         <v>1980</v>
       </c>
       <c r="H2517" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" s="1" t="n">
+        <v>45985.6913078704</v>
+      </c>
+      <c r="B2518" t="n">
+        <v>863099</v>
+      </c>
+      <c r="C2518" t="n">
+        <v>4.36999988555908</v>
+      </c>
+      <c r="D2518" t="n">
+        <v>4.31199979782104</v>
+      </c>
+      <c r="E2518" t="n">
+        <v>4.32800006866455</v>
+      </c>
+      <c r="F2518" t="n">
+        <v>4.35400009155273</v>
+      </c>
+      <c r="G2518" t="s">
+        <v>1981</v>
+      </c>
+      <c r="H2518" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/OVS.MI.xlsx
+++ b/data/OVS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1989" uniqueCount="1989">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="1990">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,46 +44,46 @@
     <t xml:space="preserve">OVS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89862394332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76365375518799</t>
+    <t xml:space="preserve">4.89862442016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76365423202515</t>
   </si>
   <si>
     <t xml:space="preserve">4.64456224441528</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71998643875122</t>
+    <t xml:space="preserve">4.71998596191406</t>
   </si>
   <si>
     <t xml:space="preserve">4.65647125244141</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78747224807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94229030609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69219923019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60486507415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63662242889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.616774559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2515606880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22774267196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5334095954895</t>
+    <t xml:space="preserve">4.78747177124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94228982925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69219875335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60486459732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63662338256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61677408218384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25156021118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22774219512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53341007232666</t>
   </si>
   <si>
     <t xml:space="preserve">4.45798540115356</t>
@@ -92,43 +92,43 @@
     <t xml:space="preserve">4.47783422470093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49768257141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51356172561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44607734680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62868356704712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59295558929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51753234863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54531955718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32698535919189</t>
+    <t xml:space="preserve">4.49768304824829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51356220245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4460768699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62868309020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59295654296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51753187179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54531908035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32698583602905</t>
   </si>
   <si>
     <t xml:space="preserve">4.03322601318359</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02925729751587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27934885025024</t>
+    <t xml:space="preserve">4.02925634384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2793493270874</t>
   </si>
   <si>
     <t xml:space="preserve">4.22377252578735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38256120681763</t>
+    <t xml:space="preserve">4.38256072998047</t>
   </si>
   <si>
     <t xml:space="preserve">4.30316734313965</t>
@@ -143,10 +143,10 @@
     <t xml:space="preserve">4.48577356338501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48974323272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27140951156616</t>
+    <t xml:space="preserve">4.48974227905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.271409034729</t>
   </si>
   <si>
     <t xml:space="preserve">4.23965215682983</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">4.56516885757446</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67235088348389</t>
+    <t xml:space="preserve">4.67235040664673</t>
   </si>
   <si>
     <t xml:space="preserve">4.71601676940918</t>
@@ -167,13 +167,13 @@
     <t xml:space="preserve">4.58898687362671</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50562238693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52547168731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38653135299683</t>
+    <t xml:space="preserve">4.50562286376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52547121047974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38653087615967</t>
   </si>
   <si>
     <t xml:space="preserve">4.43019771575928</t>
@@ -182,10 +182,10 @@
     <t xml:space="preserve">4.40241003036499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29125833511353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12056064605713</t>
+    <t xml:space="preserve">4.29125785827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12055969238281</t>
   </si>
   <si>
     <t xml:space="preserve">4.09674215316772</t>
@@ -194,25 +194,25 @@
     <t xml:space="preserve">4.0649847984314</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08880233764648</t>
+    <t xml:space="preserve">4.08880281448364</t>
   </si>
   <si>
     <t xml:space="preserve">4.15628719329834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21186304092407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04910516738892</t>
+    <t xml:space="preserve">4.21186399459839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04910564422607</t>
   </si>
   <si>
     <t xml:space="preserve">4.02131748199463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31110668182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16422700881958</t>
+    <t xml:space="preserve">4.31110620498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16422748565674</t>
   </si>
   <si>
     <t xml:space="preserve">4.23568201065063</t>
@@ -236,40 +236,40 @@
     <t xml:space="preserve">4.48180389404297</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52150106430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55325889587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5413498878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56913805007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5373797416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64853239059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7041072845459</t>
+    <t xml:space="preserve">4.5215015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55325841903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54135036468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56913757324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53737926483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64853143692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70410776138306</t>
   </si>
   <si>
     <t xml:space="preserve">4.84304761886597</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89068412780762</t>
+    <t xml:space="preserve">4.89068460464478</t>
   </si>
   <si>
     <t xml:space="preserve">4.81525993347168</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87877464294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91053295135498</t>
+    <t xml:space="preserve">4.87877607345581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91053247451782</t>
   </si>
   <si>
     <t xml:space="preserve">4.75968408584595</t>
@@ -287,22 +287,22 @@
     <t xml:space="preserve">4.73419427871704</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5671534538269</t>
+    <t xml:space="preserve">4.56715297698975</t>
   </si>
   <si>
     <t xml:space="preserve">4.51826286315918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47344636917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47752094268799</t>
+    <t xml:space="preserve">4.47344732284546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47752046585083</t>
   </si>
   <si>
     <t xml:space="preserve">4.48974418640137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63233947753906</t>
+    <t xml:space="preserve">4.63233995437622</t>
   </si>
   <si>
     <t xml:space="preserve">4.61196851730347</t>
@@ -314,46 +314,46 @@
     <t xml:space="preserve">4.51418924331665</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33085012435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94706296920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13529014587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24529361724854</t>
+    <t xml:space="preserve">4.33085107803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94706344604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13528966903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24529314041138</t>
   </si>
   <si>
     <t xml:space="preserve">4.26566314697266</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30233097076416</t>
+    <t xml:space="preserve">4.30233144760132</t>
   </si>
   <si>
     <t xml:space="preserve">4.2575159072876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1108455657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09047365188599</t>
+    <t xml:space="preserve">4.11084413528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09047412872314</t>
   </si>
   <si>
     <t xml:space="preserve">4.05299139022827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18825340270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16380929946899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15566062927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15973472595215</t>
+    <t xml:space="preserve">4.18825435638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16380882263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15566110610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15973520278931</t>
   </si>
   <si>
     <t xml:space="preserve">4.10677099227905</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">4.11899280548096</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16788244247437</t>
+    <t xml:space="preserve">4.16788339614868</t>
   </si>
   <si>
     <t xml:space="preserve">4.26158905029297</t>
@@ -380,28 +380,28 @@
     <t xml:space="preserve">4.23307037353516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37159299850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36751794815063</t>
+    <t xml:space="preserve">4.37159252166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36751842498779</t>
   </si>
   <si>
     <t xml:space="preserve">4.28603410720825</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27788639068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24121809005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25344181060791</t>
+    <t xml:space="preserve">4.27788686752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24121856689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25344085693359</t>
   </si>
   <si>
     <t xml:space="preserve">4.29825782775879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22899627685547</t>
+    <t xml:space="preserve">4.22899532318115</t>
   </si>
   <si>
     <t xml:space="preserve">4.0725474357605</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">4.19232797622681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10269689559937</t>
+    <t xml:space="preserve">4.10269641876221</t>
   </si>
   <si>
     <t xml:space="preserve">4.04158353805542</t>
@@ -422,22 +422,22 @@
     <t xml:space="preserve">4.13936376571655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09862232208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00084209442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99269366264343</t>
+    <t xml:space="preserve">4.09862327575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00084257125854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99269342422485</t>
   </si>
   <si>
     <t xml:space="preserve">4.03343534469604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19640254974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15158700942993</t>
+    <t xml:space="preserve">4.19640302658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15158653259277</t>
   </si>
   <si>
     <t xml:space="preserve">4.0863995552063</t>
@@ -446,16 +446,16 @@
     <t xml:space="preserve">4.06114053726196</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35937023162842</t>
+    <t xml:space="preserve">4.35936975479126</t>
   </si>
   <si>
     <t xml:space="preserve">4.37566661834717</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44085359573364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41233396530151</t>
+    <t xml:space="preserve">4.4408540725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41233348846436</t>
   </si>
   <si>
     <t xml:space="preserve">4.31862831115723</t>
@@ -473,73 +473,73 @@
     <t xml:space="preserve">4.21677350997925</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18010520935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14343738555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11491870880127</t>
+    <t xml:space="preserve">4.18010663986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14343786239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11491918563843</t>
   </si>
   <si>
     <t xml:space="preserve">4.07417726516724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06928825378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08232545852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06439971923828</t>
+    <t xml:space="preserve">4.06928873062134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08232593536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06439924240112</t>
   </si>
   <si>
     <t xml:space="preserve">4.00573062896729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96010041236877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05462169647217</t>
+    <t xml:space="preserve">3.96009969711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05462074279785</t>
   </si>
   <si>
     <t xml:space="preserve">4.13121604919434</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04647302627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98128485679626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00410127639771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9861752986908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02528762817383</t>
+    <t xml:space="preserve">4.04647254943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98128533363342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00410175323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98617482185364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02528715133667</t>
   </si>
   <si>
     <t xml:space="preserve">3.97476696968079</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02365684509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05951023101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04810285568237</t>
+    <t xml:space="preserve">4.02365779876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05950975418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04810237884521</t>
   </si>
   <si>
     <t xml:space="preserve">4.05136203765869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97965693473816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03017568588257</t>
+    <t xml:space="preserve">3.97965621948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03017616271973</t>
   </si>
   <si>
     <t xml:space="preserve">4.02039813995361</t>
@@ -548,34 +548,34 @@
     <t xml:space="preserve">3.99921202659607</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07825183868408</t>
+    <t xml:space="preserve">4.07825136184692</t>
   </si>
   <si>
     <t xml:space="preserve">4.1475133895874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23714447021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20455121994019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22492218017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01713848114014</t>
+    <t xml:space="preserve">4.23714399337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20455074310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22492170333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01713895797729</t>
   </si>
   <si>
     <t xml:space="preserve">4.02202749252319</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93076610565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91283941268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89491295814514</t>
+    <t xml:space="preserve">3.93076586723328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91283988952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89491367340088</t>
   </si>
   <si>
     <t xml:space="preserve">3.87535738945007</t>
@@ -584,28 +584,28 @@
     <t xml:space="preserve">3.94054460525513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93402576446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89654350280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95521092414856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00247192382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37974071502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38381481170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39196348190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35529518127441</t>
+    <t xml:space="preserve">3.93402600288391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89654326438904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9552116394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00247144699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3797402381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38381433486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39196395874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35529613494873</t>
   </si>
   <si>
     <t xml:space="preserve">4.2901086807251</t>
@@ -614,13 +614,13 @@
     <t xml:space="preserve">4.28196001052856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3267765045166</t>
+    <t xml:space="preserve">4.32677602767944</t>
   </si>
   <si>
     <t xml:space="preserve">4.29418325424194</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33899927139282</t>
+    <t xml:space="preserve">4.33899879455566</t>
   </si>
   <si>
     <t xml:space="preserve">4.33492422103882</t>
@@ -629,31 +629,31 @@
     <t xml:space="preserve">4.34307289123535</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46529817581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48159503936768</t>
+    <t xml:space="preserve">4.46529865264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48159551620483</t>
   </si>
   <si>
     <t xml:space="preserve">4.40825939178467</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53863430023193</t>
+    <t xml:space="preserve">4.53863382339478</t>
   </si>
   <si>
     <t xml:space="preserve">4.55493021011353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52641153335571</t>
+    <t xml:space="preserve">4.52641105651855</t>
   </si>
   <si>
     <t xml:space="preserve">4.50604009628296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43270492553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59567213058472</t>
+    <t xml:space="preserve">4.43270444869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59567165374756</t>
   </si>
   <si>
     <t xml:space="preserve">4.68530464172363</t>
@@ -665,16 +665,16 @@
     <t xml:space="preserve">4.60382032394409</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70160007476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85642004013062</t>
+    <t xml:space="preserve">4.70160055160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85642051696777</t>
   </si>
   <si>
     <t xml:space="preserve">4.8238263130188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77493572235107</t>
+    <t xml:space="preserve">4.77493619918823</t>
   </si>
   <si>
     <t xml:space="preserve">4.7993803024292</t>
@@ -683,10 +683,10 @@
     <t xml:space="preserve">4.74234294891357</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78308486938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72604560852051</t>
+    <t xml:space="preserve">4.78308439254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72604513168335</t>
   </si>
   <si>
     <t xml:space="preserve">4.77900981903076</t>
@@ -695,25 +695,25 @@
     <t xml:space="preserve">4.80752944946289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86456775665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04790544509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01531219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89716100692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91753244400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88901281356812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04383134841919</t>
+    <t xml:space="preserve">4.86456871032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04790592193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01531314849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89716148376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91753196716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88901329040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04383182525635</t>
   </si>
   <si>
     <t xml:space="preserve">4.90531015396118</t>
@@ -722,13 +722,13 @@
     <t xml:space="preserve">4.95012521743774</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05198001861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97864532470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03160858154297</t>
+    <t xml:space="preserve">5.05198049545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97864484786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03160905838013</t>
   </si>
   <si>
     <t xml:space="preserve">5.08457374572754</t>
@@ -737,10 +737,10 @@
     <t xml:space="preserve">5.23939228057861</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19865036010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14568567276001</t>
+    <t xml:space="preserve">5.19864988327026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14568519592285</t>
   </si>
   <si>
     <t xml:space="preserve">5.19457626342773</t>
@@ -749,13 +749,13 @@
     <t xml:space="preserve">5.05605459213257</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06420278549194</t>
+    <t xml:space="preserve">5.0642032623291</t>
   </si>
   <si>
     <t xml:space="preserve">5.13346385955811</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1171669960022</t>
+    <t xml:space="preserve">5.11716651916504</t>
   </si>
   <si>
     <t xml:space="preserve">5.25161504745483</t>
@@ -767,7 +767,7 @@
     <t xml:space="preserve">5.17827987670898</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25568866729736</t>
+    <t xml:space="preserve">5.25568962097168</t>
   </si>
   <si>
     <t xml:space="preserve">5.27198457717896</t>
@@ -776,28 +776,28 @@
     <t xml:space="preserve">5.17420482635498</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16605663299561</t>
+    <t xml:space="preserve">5.16605710983276</t>
   </si>
   <si>
     <t xml:space="preserve">5.1864275932312</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10494470596313</t>
+    <t xml:space="preserve">5.10494518280029</t>
   </si>
   <si>
     <t xml:space="preserve">5.07235050201416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94605159759521</t>
+    <t xml:space="preserve">4.94605112075806</t>
   </si>
   <si>
     <t xml:space="preserve">5.06827640533447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98679304122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03691244125366</t>
+    <t xml:space="preserve">4.98679351806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0369119644165</t>
   </si>
   <si>
     <t xml:space="preserve">5.36268186569214</t>
@@ -806,46 +806,46 @@
     <t xml:space="preserve">5.39191770553589</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31256341934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27915000915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34597587585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35432863235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32091569900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33762311935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27079820632935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27497434616089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18726778030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13297176361084</t>
+    <t xml:space="preserve">5.3125638961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27915048599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34597635269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35432815551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32091617584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33762264251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27079772949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27497386932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1872673034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13297271728516</t>
   </si>
   <si>
     <t xml:space="preserve">5.2039737701416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22903347015381</t>
+    <t xml:space="preserve">5.22903299331665</t>
   </si>
   <si>
     <t xml:space="preserve">5.25409173965454</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2624454498291</t>
+    <t xml:space="preserve">5.26244497299194</t>
   </si>
   <si>
     <t xml:space="preserve">5.18309116363525</t>
@@ -857,13 +857,13 @@
     <t xml:space="preserve">5.17891454696655</t>
   </si>
   <si>
-    <t xml:space="preserve">5.249915599823</t>
+    <t xml:space="preserve">5.24991512298584</t>
   </si>
   <si>
     <t xml:space="preserve">5.24573850631714</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28332805633545</t>
+    <t xml:space="preserve">5.28332710266113</t>
   </si>
   <si>
     <t xml:space="preserve">5.22485589981079</t>
@@ -878,37 +878,37 @@
     <t xml:space="preserve">5.40444660186768</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37521123886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40027093887329</t>
+    <t xml:space="preserve">5.37521171569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40027046203613</t>
   </si>
   <si>
     <t xml:space="preserve">5.38356494903564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37938785552979</t>
+    <t xml:space="preserve">5.37938833236694</t>
   </si>
   <si>
     <t xml:space="preserve">5.23320960998535</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30838680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2582688331604</t>
+    <t xml:space="preserve">5.30838775634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25826930999756</t>
   </si>
   <si>
     <t xml:space="preserve">5.20814990997314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13714838027954</t>
+    <t xml:space="preserve">5.1371488571167</t>
   </si>
   <si>
     <t xml:space="preserve">5.11208963394165</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15385484695435</t>
+    <t xml:space="preserve">5.15385580062866</t>
   </si>
   <si>
     <t xml:space="preserve">5.23738527297974</t>
@@ -917,52 +917,52 @@
     <t xml:space="preserve">5.32509279251099</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30420970916748</t>
+    <t xml:space="preserve">5.30421018600464</t>
   </si>
   <si>
     <t xml:space="preserve">5.29585742950439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32926940917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48797798156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5380973815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59656763076782</t>
+    <t xml:space="preserve">5.32926893234253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4879789352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53809690475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59656810760498</t>
   </si>
   <si>
     <t xml:space="preserve">5.62580394744873</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68845272064209</t>
+    <t xml:space="preserve">5.68845319747925</t>
   </si>
   <si>
     <t xml:space="preserve">5.61327505111694</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57568550109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44203662872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62162828445435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68009853363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64251041412354</t>
+    <t xml:space="preserve">5.57568597793579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44203615188599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62162780761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68009901046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64250993728638</t>
   </si>
   <si>
     <t xml:space="preserve">5.37103509902954</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39609432220459</t>
+    <t xml:space="preserve">5.39609336853027</t>
   </si>
   <si>
     <t xml:space="preserve">5.38774156570435</t>
@@ -977,16 +977,16 @@
     <t xml:space="preserve">5.19561958312988</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08285427093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88655614852905</t>
+    <t xml:space="preserve">5.08285331726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88655567169189</t>
   </si>
   <si>
     <t xml:space="preserve">4.90743923187256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81973075866699</t>
+    <t xml:space="preserve">4.81973171234131</t>
   </si>
   <si>
     <t xml:space="preserve">4.80302572250366</t>
@@ -1001,43 +1001,43 @@
     <t xml:space="preserve">4.94502782821655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90326309204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86567306518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87820291519165</t>
+    <t xml:space="preserve">4.90326261520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86567354202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87820386886597</t>
   </si>
   <si>
     <t xml:space="preserve">4.8531436920166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81137752532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95755767822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92832183837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77796649932861</t>
+    <t xml:space="preserve">4.81137847900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9575572013855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92832136154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77796602249146</t>
   </si>
   <si>
     <t xml:space="preserve">4.861496925354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83226108551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7236704826355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66102266311646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69861078262329</t>
+    <t xml:space="preserve">4.83226156234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72366952896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66102313995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69861173629761</t>
   </si>
   <si>
     <t xml:space="preserve">4.6693754196167</t>
@@ -1055,10 +1055,10 @@
     <t xml:space="preserve">4.64014005661011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71949434280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79049587249756</t>
+    <t xml:space="preserve">4.7194938659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7904953956604</t>
   </si>
   <si>
     <t xml:space="preserve">4.74872970581055</t>
@@ -1073,55 +1073,55 @@
     <t xml:space="preserve">4.67772912979126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91579246520996</t>
+    <t xml:space="preserve">4.9157919883728</t>
   </si>
   <si>
     <t xml:space="preserve">4.92414426803589</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89490938186646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8406138420105</t>
+    <t xml:space="preserve">4.8949089050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84061431884766</t>
   </si>
   <si>
     <t xml:space="preserve">5.16220760345459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99932241439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02020502090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17056035995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09955930709839</t>
+    <t xml:space="preserve">4.99932193756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0202054977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17056083679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09955978393555</t>
   </si>
   <si>
     <t xml:space="preserve">4.95338153839111</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78631925582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68608140945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60672807693481</t>
+    <t xml:space="preserve">4.7863187789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6860818862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60672760009766</t>
   </si>
   <si>
     <t xml:space="preserve">4.59419822692871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61508131027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63178682327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70696449279785</t>
+    <t xml:space="preserve">4.6150803565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63178730010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70696544647217</t>
   </si>
   <si>
     <t xml:space="preserve">4.58584499359131</t>
@@ -1130,10 +1130,10 @@
     <t xml:space="preserve">4.55243301391602</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53990268707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57749223709106</t>
+    <t xml:space="preserve">4.53990316390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57749176025391</t>
   </si>
   <si>
     <t xml:space="preserve">4.48978424072266</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">4.41042995452881</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44384241104126</t>
+    <t xml:space="preserve">4.44384145736694</t>
   </si>
   <si>
     <t xml:space="preserve">4.4939603805542</t>
@@ -1157,22 +1157,22 @@
     <t xml:space="preserve">4.59002113342285</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65684604644775</t>
+    <t xml:space="preserve">4.65684652328491</t>
   </si>
   <si>
     <t xml:space="preserve">4.64849233627319</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59837484359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5607852935791</t>
+    <t xml:space="preserve">4.59837436676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56078577041626</t>
   </si>
   <si>
     <t xml:space="preserve">4.48560810089111</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43966579437256</t>
+    <t xml:space="preserve">4.43966627120972</t>
   </si>
   <si>
     <t xml:space="preserve">4.36031150817871</t>
@@ -1184,13 +1184,13 @@
     <t xml:space="preserve">4.18907308578491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16150760650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15148448944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15649604797363</t>
+    <t xml:space="preserve">4.16150712966919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15148496627808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15649557113647</t>
   </si>
   <si>
     <t xml:space="preserve">4.19324970245361</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">4.09802484512329</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15315437316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10303688049316</t>
+    <t xml:space="preserve">4.15315532684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10303640365601</t>
   </si>
   <si>
     <t xml:space="preserve">4.12642526626587</t>
@@ -1211,28 +1211,28 @@
     <t xml:space="preserve">4.16986131668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17654371261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1431303024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16819047927856</t>
+    <t xml:space="preserve">4.17654323577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14313077926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16819000244141</t>
   </si>
   <si>
     <t xml:space="preserve">2.83002591133118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90687417984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84339046478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87179160118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89350938796997</t>
+    <t xml:space="preserve">2.90687441825867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84339070320129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87179136276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89350914955139</t>
   </si>
   <si>
     <t xml:space="preserve">2.80162501335144</t>
@@ -1250,28 +1250,28 @@
     <t xml:space="preserve">3.08061838150024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17083120346069</t>
+    <t xml:space="preserve">3.17083144187927</t>
   </si>
   <si>
     <t xml:space="preserve">3.14911389350891</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15746641159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14410185813904</t>
+    <t xml:space="preserve">3.15746665000916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14410161972046</t>
   </si>
   <si>
     <t xml:space="preserve">3.17918515205383</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17417335510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10400748252869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01212310791016</t>
+    <t xml:space="preserve">3.17417311668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10400724411011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01212334632874</t>
   </si>
   <si>
     <t xml:space="preserve">3.02882957458496</t>
@@ -1280,13 +1280,13 @@
     <t xml:space="preserve">2.94529819488525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95699238777161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89852142333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84004878997803</t>
+    <t xml:space="preserve">2.95699262619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89852094650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84004902839661</t>
   </si>
   <si>
     <t xml:space="preserve">2.82501363754272</t>
@@ -1298,13 +1298,13 @@
     <t xml:space="preserve">2.74649548530579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55771493911743</t>
+    <t xml:space="preserve">2.55771470069885</t>
   </si>
   <si>
     <t xml:space="preserve">2.54769158363342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51093769073486</t>
+    <t xml:space="preserve">2.51093792915344</t>
   </si>
   <si>
     <t xml:space="preserve">2.58945727348328</t>
@@ -1313,79 +1313,79 @@
     <t xml:space="preserve">2.5009138584137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51594996452332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50592565536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47919607162476</t>
+    <t xml:space="preserve">2.51594972610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50592589378357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47919654846191</t>
   </si>
   <si>
     <t xml:space="preserve">2.41905355453491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39566540718079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36058211326599</t>
+    <t xml:space="preserve">2.39566564559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36058235168457</t>
   </si>
   <si>
     <t xml:space="preserve">2.36726450920105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3772885799408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2753803730011</t>
+    <t xml:space="preserve">2.37728881835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27538061141968</t>
   </si>
   <si>
     <t xml:space="preserve">2.31380534172058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26201558113098</t>
+    <t xml:space="preserve">2.2620153427124</t>
   </si>
   <si>
     <t xml:space="preserve">2.27203965187073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41404247283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38062953948975</t>
+    <t xml:space="preserve">2.41404223442078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38062930107117</t>
   </si>
   <si>
     <t xml:space="preserve">2.30043959617615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30211091041565</t>
+    <t xml:space="preserve">2.30211067199707</t>
   </si>
   <si>
     <t xml:space="preserve">2.29709911346436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32382822036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33552289009094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35389995574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36559438705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35055804252625</t>
+    <t xml:space="preserve">2.32382845878601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33552312850952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35389971733093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36559414863586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35055828094482</t>
   </si>
   <si>
     <t xml:space="preserve">2.35222935676575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35557007789612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25533318519592</t>
+    <t xml:space="preserve">2.3555703163147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25533294677734</t>
   </si>
   <si>
     <t xml:space="preserve">2.22025060653687</t>
@@ -1394,37 +1394,37 @@
     <t xml:space="preserve">2.28039240837097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.225261926651</t>
+    <t xml:space="preserve">2.22526168823242</t>
   </si>
   <si>
     <t xml:space="preserve">2.23027396202087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40067672729492</t>
+    <t xml:space="preserve">2.40067625045776</t>
   </si>
   <si>
     <t xml:space="preserve">2.44912457466125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42406558990479</t>
+    <t xml:space="preserve">2.42406582832336</t>
   </si>
   <si>
     <t xml:space="preserve">2.31881666183472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30879354476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34387588500977</t>
+    <t xml:space="preserve">2.30879330635071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34387564659119</t>
   </si>
   <si>
     <t xml:space="preserve">2.33218121528625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27371001243591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18850898742676</t>
+    <t xml:space="preserve">2.27370953559875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18850874900818</t>
   </si>
   <si>
     <t xml:space="preserve">2.17681455612183</t>
@@ -1436,19 +1436,19 @@
     <t xml:space="preserve">2.21022653579712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21189713478088</t>
+    <t xml:space="preserve">2.2118968963623</t>
   </si>
   <si>
     <t xml:space="preserve">2.05485892295837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01142263412476</t>
+    <t xml:space="preserve">2.01142287254333</t>
   </si>
   <si>
     <t xml:space="preserve">1.97466921806335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00474047660828</t>
+    <t xml:space="preserve">2.0047402381897</t>
   </si>
   <si>
     <t xml:space="preserve">2.03815340995789</t>
@@ -1460,61 +1460,61 @@
     <t xml:space="preserve">2.17180252075195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18182563781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1667902469635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16846084594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15509605407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15676641464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1150016784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07657718658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08994221687317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09829473495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16010808944702</t>
+    <t xml:space="preserve">2.18182587623596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16679072380066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16846060752869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15509581565857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15676665306091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11500144004822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07657766342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08994245529175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09829521179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1601083278656</t>
   </si>
   <si>
     <t xml:space="preserve">2.09662485122681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09161257743835</t>
+    <t xml:space="preserve">2.09161233901978</t>
   </si>
   <si>
     <t xml:space="preserve">2.02478766441345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02645921707153</t>
+    <t xml:space="preserve">2.02645897865295</t>
   </si>
   <si>
     <t xml:space="preserve">2.12502455711365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23695611953735</t>
+    <t xml:space="preserve">2.23695588111877</t>
   </si>
   <si>
     <t xml:space="preserve">2.18683767318726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11834263801575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06989526748657</t>
+    <t xml:space="preserve">2.11834239959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06989502906799</t>
   </si>
   <si>
     <t xml:space="preserve">2.06321263313293</t>
@@ -1526,7 +1526,7 @@
     <t xml:space="preserve">1.99972856044769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98302280902863</t>
+    <t xml:space="preserve">1.98302268981934</t>
   </si>
   <si>
     <t xml:space="preserve">1.94626927375793</t>
@@ -1547,31 +1547,31 @@
     <t xml:space="preserve">1.6288515329361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62968695163727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50439071655273</t>
+    <t xml:space="preserve">1.62968707084656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50439083576202</t>
   </si>
   <si>
     <t xml:space="preserve">1.48601388931274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39663565158844</t>
+    <t xml:space="preserve">1.39663553237915</t>
   </si>
   <si>
     <t xml:space="preserve">1.31728136539459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28553974628448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27133929729462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24962162971497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24460959434509</t>
+    <t xml:space="preserve">1.2855396270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27133941650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24962174892426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24460971355438</t>
   </si>
   <si>
     <t xml:space="preserve">1.2897162437439</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">1.30391645431519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3156111240387</t>
+    <t xml:space="preserve">1.31561100482941</t>
   </si>
   <si>
     <t xml:space="preserve">1.31310510635376</t>
@@ -1601,7 +1601,7 @@
     <t xml:space="preserve">1.35152912139893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29472827911377</t>
+    <t xml:space="preserve">1.29472815990448</t>
   </si>
   <si>
     <t xml:space="preserve">1.29639852046967</t>
@@ -1613,28 +1613,28 @@
     <t xml:space="preserve">1.25212776660919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26799857616425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25296235084534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2337509393692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25630414485931</t>
+    <t xml:space="preserve">1.26799869537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25296247005463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23375082015991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25630402565002</t>
   </si>
   <si>
     <t xml:space="preserve">1.2579745054245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26048040390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36823558807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36990594863892</t>
+    <t xml:space="preserve">1.26048052310944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36823570728302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36990606784821</t>
   </si>
   <si>
     <t xml:space="preserve">1.36405920982361</t>
@@ -1643,10 +1643,10 @@
     <t xml:space="preserve">1.34568238258362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31477546691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34484672546387</t>
+    <t xml:space="preserve">1.31477534770966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34484684467316</t>
   </si>
   <si>
     <t xml:space="preserve">1.25129199028015</t>
@@ -1658,28 +1658,28 @@
     <t xml:space="preserve">1.06835913658142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962275266647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989840626716614</t>
+    <t xml:space="preserve">0.962275147438049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989840567111969</t>
   </si>
   <si>
     <t xml:space="preserve">0.633163154125214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.703329861164093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.705000281333923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862038195133209</t>
+    <t xml:space="preserve">0.703329801559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.705000221729279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.862038254737854</t>
   </si>
   <si>
     <t xml:space="preserve">0.958098888397217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.948074817657471</t>
+    <t xml:space="preserve">0.948074877262115</t>
   </si>
   <si>
     <t xml:space="preserve">0.848673403263092</t>
@@ -1691,22 +1691,22 @@
     <t xml:space="preserve">0.9447340965271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.91883909702301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917168796062469</t>
+    <t xml:space="preserve">0.918839156627655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917168855667114</t>
   </si>
   <si>
     <t xml:space="preserve">1.00487565994263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1477142572403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11430144309998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09926617145538</t>
+    <t xml:space="preserve">1.14771413803101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11430132389069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09926605224609</t>
   </si>
   <si>
     <t xml:space="preserve">1.13184344768524</t>
@@ -1715,25 +1715,25 @@
     <t xml:space="preserve">1.10344254970551</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0357825756073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01155805587769</t>
+    <t xml:space="preserve">1.03578269481659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01155817508698</t>
   </si>
   <si>
     <t xml:space="preserve">1.01824057102203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999029040336609</t>
+    <t xml:space="preserve">0.999028921127319</t>
   </si>
   <si>
     <t xml:space="preserve">1.01573550701141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01322960853577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.082559466362</t>
+    <t xml:space="preserve">1.01322948932648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08255958557129</t>
   </si>
   <si>
     <t xml:space="preserve">1.10177206993103</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">1.1276661157608</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12933743000031</t>
+    <t xml:space="preserve">1.12933731079102</t>
   </si>
   <si>
     <t xml:space="preserve">1.13017213344574</t>
@@ -1754,16 +1754,16 @@
     <t xml:space="preserve">1.11346662044525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10260689258575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06585299968719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03244113922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07086527347565</t>
+    <t xml:space="preserve">1.10260677337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06585311889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0324410200119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07086515426636</t>
   </si>
   <si>
     <t xml:space="preserve">1.06334805488586</t>
@@ -1778,10 +1778,10 @@
     <t xml:space="preserve">1.06501841545105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12850165367126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08506548404694</t>
+    <t xml:space="preserve">1.12850177288055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08506560325623</t>
   </si>
   <si>
     <t xml:space="preserve">1.08673584461212</t>
@@ -1790,40 +1790,40 @@
     <t xml:space="preserve">1.07253646850586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0808892250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1051127910614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07838320732117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10010075569153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1126309633255</t>
+    <t xml:space="preserve">1.08088910579681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10511291027069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07838332653046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10010087490082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11263084411621</t>
   </si>
   <si>
     <t xml:space="preserve">1.11012494564056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2262327671051</t>
+    <t xml:space="preserve">1.22623288631439</t>
   </si>
   <si>
     <t xml:space="preserve">1.46179032325745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41584801673889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.414177775383</t>
+    <t xml:space="preserve">1.4158478975296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41417765617371</t>
   </si>
   <si>
     <t xml:space="preserve">1.36071765422821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33064615726471</t>
+    <t xml:space="preserve">1.330646276474</t>
   </si>
   <si>
     <t xml:space="preserve">1.29806971549988</t>
@@ -1835,31 +1835,31 @@
     <t xml:space="preserve">1.38744723796844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32981157302856</t>
+    <t xml:space="preserve">1.32981145381927</t>
   </si>
   <si>
     <t xml:space="preserve">1.35069346427917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3548709154129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32897579669952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36572968959808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37157642841339</t>
+    <t xml:space="preserve">1.35487079620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32897591590881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36572957038879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37157654762268</t>
   </si>
   <si>
     <t xml:space="preserve">1.40248322486877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41918885707855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4216947555542</t>
+    <t xml:space="preserve">1.41918897628784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42169487476349</t>
   </si>
   <si>
     <t xml:space="preserve">1.42253053188324</t>
@@ -1880,25 +1880,25 @@
     <t xml:space="preserve">1.45343661308289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43589544296265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52861440181732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61131036281586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5971097946167</t>
+    <t xml:space="preserve">1.43589520454407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52861428260803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61131024360657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59710991382599</t>
   </si>
   <si>
     <t xml:space="preserve">1.59376907348633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5745564699173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55283892154694</t>
+    <t xml:space="preserve">1.57455658912659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55283880233765</t>
   </si>
   <si>
     <t xml:space="preserve">1.55116760730743</t>
@@ -1910,13 +1910,13 @@
     <t xml:space="preserve">1.47097861766815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41751849651337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43422508239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38828277587891</t>
+    <t xml:space="preserve">1.41751837730408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43422484397888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3882828950882</t>
   </si>
   <si>
     <t xml:space="preserve">1.38327074050903</t>
@@ -1925,31 +1925,31 @@
     <t xml:space="preserve">1.33231663703918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36740005016327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34985876083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30308103561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32229351997375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31644594669342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2989045381546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30892860889435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31059908866882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31895196437836</t>
+    <t xml:space="preserve">1.36739981174469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34985888004303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3030811548233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32229340076447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31644582748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29890441894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30892848968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31059896945953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31895184516907</t>
   </si>
   <si>
     <t xml:space="preserve">1.29222226142883</t>
@@ -1970,13 +1970,13 @@
     <t xml:space="preserve">1.31978738307953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34902310371399</t>
+    <t xml:space="preserve">1.3490229845047</t>
   </si>
   <si>
     <t xml:space="preserve">1.34651708602905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30725836753845</t>
+    <t xml:space="preserve">1.30725824832916</t>
   </si>
   <si>
     <t xml:space="preserve">1.26215076446533</t>
@@ -1991,7 +1991,7 @@
     <t xml:space="preserve">1.19198513031006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35821163654327</t>
+    <t xml:space="preserve">1.35821151733398</t>
   </si>
   <si>
     <t xml:space="preserve">1.32312905788422</t>
@@ -2000,7 +2000,7 @@
     <t xml:space="preserve">1.28219890594482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24043321609497</t>
+    <t xml:space="preserve">1.24043309688568</t>
   </si>
   <si>
     <t xml:space="preserve">1.27384531497955</t>
@@ -2018,31 +2018,31 @@
     <t xml:space="preserve">1.42503654956818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48183739185333</t>
+    <t xml:space="preserve">1.48183751106262</t>
   </si>
   <si>
     <t xml:space="preserve">1.49603796005249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50272035598755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50355494022369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54448509216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56369757652283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53863823413849</t>
+    <t xml:space="preserve">1.50272023677826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50355505943298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54448533058167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56369769573212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53863847255707</t>
   </si>
   <si>
     <t xml:space="preserve">1.54866254329681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49186086654663</t>
+    <t xml:space="preserve">1.49186062812805</t>
   </si>
   <si>
     <t xml:space="preserve">1.41668295860291</t>
@@ -2051,28 +2051,28 @@
     <t xml:space="preserve">1.39329493045807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39078891277313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42002439498901</t>
+    <t xml:space="preserve">1.39078879356384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4200245141983</t>
   </si>
   <si>
     <t xml:space="preserve">1.37491798400879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34818828105927</t>
+    <t xml:space="preserve">1.34818851947784</t>
   </si>
   <si>
     <t xml:space="preserve">1.33148193359375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32814037799835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29723417758942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29974019527435</t>
+    <t xml:space="preserve">1.32814013957977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29723429679871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29974031448364</t>
   </si>
   <si>
     <t xml:space="preserve">1.30224621295929</t>
@@ -2081,70 +2081,70 @@
     <t xml:space="preserve">1.33315229415894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26549255847931</t>
+    <t xml:space="preserve">1.26549243927002</t>
   </si>
   <si>
     <t xml:space="preserve">1.24210357666016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38995337486267</t>
+    <t xml:space="preserve">1.38995325565338</t>
   </si>
   <si>
     <t xml:space="preserve">1.37074160575867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38494122028351</t>
+    <t xml:space="preserve">1.3849413394928</t>
   </si>
   <si>
     <t xml:space="preserve">1.38911855220795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37992990016937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45260179042816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48852002620697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49687278270721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50104880332947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44758987426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39914166927338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5428147315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46095454692841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39162361621857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41000056266785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40833008289337</t>
+    <t xml:space="preserve">1.37993013858795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45260167121887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48851990699768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49687266349792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50104916095734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.447589635849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39914155006409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54281485080719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4609546661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39162349700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41000044345856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40833020210266</t>
   </si>
   <si>
     <t xml:space="preserve">1.4292129278183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40749454498291</t>
+    <t xml:space="preserve">1.40749430656433</t>
   </si>
   <si>
     <t xml:space="preserve">1.33398795127869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32563424110413</t>
+    <t xml:space="preserve">1.32563412189484</t>
   </si>
   <si>
     <t xml:space="preserve">1.33732867240906</t>
@@ -2153,10 +2153,10 @@
     <t xml:space="preserve">1.36155307292938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36907052993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44508385658264</t>
+    <t xml:space="preserve">1.36907029151917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44508373737335</t>
   </si>
   <si>
     <t xml:space="preserve">1.4350597858429</t>
@@ -2165,7 +2165,7 @@
     <t xml:space="preserve">1.46596658229828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47181344032288</t>
+    <t xml:space="preserve">1.47181332111359</t>
   </si>
   <si>
     <t xml:space="preserve">1.46513092517853</t>
@@ -2183,22 +2183,22 @@
     <t xml:space="preserve">1.4926962852478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52276766300201</t>
+    <t xml:space="preserve">1.52276754379272</t>
   </si>
   <si>
     <t xml:space="preserve">1.54030871391296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53529691696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59794545173645</t>
+    <t xml:space="preserve">1.53529679775238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59794533252716</t>
   </si>
   <si>
     <t xml:space="preserve">1.60629820823669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58625090122223</t>
+    <t xml:space="preserve">1.58625102043152</t>
   </si>
   <si>
     <t xml:space="preserve">1.64555788040161</t>
@@ -2213,13 +2213,13 @@
     <t xml:space="preserve">1.58458054065704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56035614013672</t>
+    <t xml:space="preserve">1.56035602092743</t>
   </si>
   <si>
     <t xml:space="preserve">1.54197907447815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55868554115295</t>
+    <t xml:space="preserve">1.55868566036224</t>
   </si>
   <si>
     <t xml:space="preserve">1.56620371341705</t>
@@ -2228,46 +2228,46 @@
     <t xml:space="preserve">1.56703841686249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58708667755127</t>
+    <t xml:space="preserve">1.58708655834198</t>
   </si>
   <si>
     <t xml:space="preserve">1.64973437786102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74078297615051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70737075805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71906530857086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72908842563629</t>
+    <t xml:space="preserve">1.74078285694122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70737087726593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71906518936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72908854484558</t>
   </si>
   <si>
     <t xml:space="preserve">1.7123829126358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73243033885956</t>
+    <t xml:space="preserve">1.73243021965027</t>
   </si>
   <si>
     <t xml:space="preserve">1.69233477115631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76584208011627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74913585186005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72073566913605</t>
+    <t xml:space="preserve">1.76584231853485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74913573265076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72073554992676</t>
   </si>
   <si>
     <t xml:space="preserve">1.63887548446655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60880422592163</t>
+    <t xml:space="preserve">1.60880410671234</t>
   </si>
   <si>
     <t xml:space="preserve">1.68565237522125</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">1.67061710357666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68732368946075</t>
+    <t xml:space="preserve">1.68732357025146</t>
   </si>
   <si>
     <t xml:space="preserve">1.67562913894653</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">1.61715710163116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61548674106598</t>
+    <t xml:space="preserve">1.61548662185669</t>
   </si>
   <si>
     <t xml:space="preserve">1.62467503547668</t>
@@ -2297,10 +2297,10 @@
     <t xml:space="preserve">1.61047458648682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64054572582245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62383937835693</t>
+    <t xml:space="preserve">1.64054584503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62383949756622</t>
   </si>
   <si>
     <t xml:space="preserve">1.60963988304138</t>
@@ -2309,7 +2309,7 @@
     <t xml:space="preserve">1.57789814472198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59126305580139</t>
+    <t xml:space="preserve">1.59126317501068</t>
   </si>
   <si>
     <t xml:space="preserve">1.56202745437622</t>
@@ -2318,25 +2318,25 @@
     <t xml:space="preserve">1.59209775924683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59543943405151</t>
+    <t xml:space="preserve">1.59543931484222</t>
   </si>
   <si>
     <t xml:space="preserve">1.58290922641754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60379219055176</t>
+    <t xml:space="preserve">1.60379207134247</t>
   </si>
   <si>
     <t xml:space="preserve">1.60045146942139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58541512489319</t>
+    <t xml:space="preserve">1.58541536331177</t>
   </si>
   <si>
     <t xml:space="preserve">1.54532074928284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54699122905731</t>
+    <t xml:space="preserve">1.5469913482666</t>
   </si>
   <si>
     <t xml:space="preserve">1.57706248760223</t>
@@ -2348,22 +2348,22 @@
     <t xml:space="preserve">1.49436676502228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48935556411743</t>
+    <t xml:space="preserve">1.48935544490814</t>
   </si>
   <si>
     <t xml:space="preserve">1.46763694286346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51274359226227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52610838413239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53195607662201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54782676696777</t>
+    <t xml:space="preserve">1.51274347305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52610850334167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53195595741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54782688617706</t>
   </si>
   <si>
     <t xml:space="preserve">1.51691997051239</t>
@@ -2375,13 +2375,13 @@
     <t xml:space="preserve">1.48267221450806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26465678215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23208045959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18029081821442</t>
+    <t xml:space="preserve">1.26465690135956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23208034038544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18029069900513</t>
   </si>
   <si>
     <t xml:space="preserve">1.16692578792572</t>
@@ -2390,19 +2390,19 @@
     <t xml:space="preserve">1.13601982593536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02742898464203</t>
+    <t xml:space="preserve">1.02742910385132</t>
   </si>
   <si>
     <t xml:space="preserve">0.933039724826813</t>
   </si>
   <si>
-    <t xml:space="preserve">0.776836335659027</t>
+    <t xml:space="preserve">0.776836395263672</t>
   </si>
   <si>
     <t xml:space="preserve">0.719200670719147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.695811808109283</t>
+    <t xml:space="preserve">0.695811748504639</t>
   </si>
   <si>
     <t xml:space="preserve">0.546709179878235</t>
@@ -2411,13 +2411,13 @@
     <t xml:space="preserve">0.613534152507782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519561290740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599333763122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.674928963184357</t>
+    <t xml:space="preserve">0.519561350345612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599333703517914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.674928903579712</t>
   </si>
   <si>
     <t xml:space="preserve">0.725047469139099</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">0.701658606529236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.637340545654297</t>
+    <t xml:space="preserve">0.637340426445007</t>
   </si>
   <si>
     <t xml:space="preserve">0.682446956634521</t>
@@ -2441,7 +2441,7 @@
     <t xml:space="preserve">0.659893691539764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643604576587677</t>
+    <t xml:space="preserve">0.643604636192322</t>
   </si>
   <si>
     <t xml:space="preserve">0.659475445747375</t>
@@ -2450,31 +2450,31 @@
     <t xml:space="preserve">0.64318722486496</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627316355705261</t>
+    <t xml:space="preserve">0.627316415309906</t>
   </si>
   <si>
     <t xml:space="preserve">0.576780498027802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618127942085266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.660728514194489</t>
+    <t xml:space="preserve">0.618128001689911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.660728454589844</t>
   </si>
   <si>
     <t xml:space="preserve">0.646528840065002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.650705277919769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.638175249099731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.649869620800018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640263915061951</t>
+    <t xml:space="preserve">0.650705337524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.638175189495087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.649869680404663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640263855457306</t>
   </si>
   <si>
     <t xml:space="preserve">0.612281143665314</t>
@@ -2483,7 +2483,7 @@
     <t xml:space="preserve">0.61562192440033</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610192537307739</t>
+    <t xml:space="preserve">0.610192477703094</t>
   </si>
   <si>
     <t xml:space="preserve">0.605598747730255</t>
@@ -2501,7 +2501,7 @@
     <t xml:space="preserve">0.654881656169891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.642351627349854</t>
+    <t xml:space="preserve">0.642351567745209</t>
   </si>
   <si>
     <t xml:space="preserve">0.641516864299774</t>
@@ -2522,31 +2522,31 @@
     <t xml:space="preserve">0.65028703212738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.6264808177948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609775125980377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.606016099452972</t>
+    <t xml:space="preserve">0.626480877399445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609775185585022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.606016159057617</t>
   </si>
   <si>
     <t xml:space="preserve">0.629822432994843</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596827805042267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.574691832065582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.581792593002319</t>
+    <t xml:space="preserve">0.596827745437622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.574691951274872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.581792533397675</t>
   </si>
   <si>
     <t xml:space="preserve">0.57427453994751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.60183972120285</t>
+    <t xml:space="preserve">0.601839661598206</t>
   </si>
   <si>
     <t xml:space="preserve">0.630658030509949</t>
@@ -2558,13 +2558,13 @@
     <t xml:space="preserve">0.789366483688354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.763054192066193</t>
+    <t xml:space="preserve">0.763054251670837</t>
   </si>
   <si>
     <t xml:space="preserve">0.768483579158783</t>
   </si>
   <si>
-    <t xml:space="preserve">0.82779061794281</t>
+    <t xml:space="preserve">0.827790558338165</t>
   </si>
   <si>
     <t xml:space="preserve">0.83530855178833</t>
@@ -2573,22 +2573,22 @@
     <t xml:space="preserve">0.901297986507416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.910486400127411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00571131706238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01072347164154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968957781791687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877909004688263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924685955047607</t>
+    <t xml:space="preserve">0.910486340522766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00571143627167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01072335243225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968957662582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877909064292908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924686014652252</t>
   </si>
   <si>
     <t xml:space="preserve">0.925521612167358</t>
@@ -2597,16 +2597,16 @@
     <t xml:space="preserve">0.938051700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.922180950641632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892109572887421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.893779993057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895450294017792</t>
+    <t xml:space="preserve">0.922180891036987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892109453678131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.893779933452606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895450353622437</t>
   </si>
   <si>
     <t xml:space="preserve">0.823614180088043</t>
@@ -2618,13 +2618,13 @@
     <t xml:space="preserve">0.824867188930511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.806073009967804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785607516765594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.802313923835754</t>
+    <t xml:space="preserve">0.806072950363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78560745716095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.802313983440399</t>
   </si>
   <si>
     <t xml:space="preserve">0.797719240188599</t>
@@ -2633,13 +2633,13 @@
     <t xml:space="preserve">0.801895618438721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.79855489730835</t>
+    <t xml:space="preserve">0.798554956912994</t>
   </si>
   <si>
     <t xml:space="preserve">0.77641898393631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.782266736030579</t>
+    <t xml:space="preserve">0.782266616821289</t>
   </si>
   <si>
     <t xml:space="preserve">0.766394913196564</t>
@@ -2648,10 +2648,10 @@
     <t xml:space="preserve">0.821525514125824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.795631527900696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863708555698395</t>
+    <t xml:space="preserve">0.795631587505341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86370861530304</t>
   </si>
   <si>
     <t xml:space="preserve">0.855355799198151</t>
@@ -2660,25 +2660,25 @@
     <t xml:space="preserve">0.84449702501297</t>
   </si>
   <si>
-    <t xml:space="preserve">0.857861876487732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.836143374443054</t>
+    <t xml:space="preserve">0.857861816883087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.836143255233765</t>
   </si>
   <si>
     <t xml:space="preserve">0.834890365600586</t>
   </si>
   <si>
-    <t xml:space="preserve">0.838649392127991</t>
+    <t xml:space="preserve">0.838649332523346</t>
   </si>
   <si>
     <t xml:space="preserve">0.800225257873535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.773912906646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789783895015717</t>
+    <t xml:space="preserve">0.773912966251373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789783775806427</t>
   </si>
   <si>
     <t xml:space="preserve">0.77182525396347</t>
@@ -2690,28 +2690,28 @@
     <t xml:space="preserve">0.775583326816559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.786860525608063</t>
+    <t xml:space="preserve">0.786860406398773</t>
   </si>
   <si>
     <t xml:space="preserve">0.792707204818726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.758877754211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.765977621078491</t>
+    <t xml:space="preserve">0.758877813816071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.765977561473846</t>
   </si>
   <si>
     <t xml:space="preserve">0.800642669200897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.809831082820892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799807906150818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.780178070068359</t>
+    <t xml:space="preserve">0.809831023216248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799807965755463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.780178010463715</t>
   </si>
   <si>
     <t xml:space="preserve">0.770989537239075</t>
@@ -2720,25 +2720,25 @@
     <t xml:space="preserve">0.740918278694153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.717947721481323</t>
+    <t xml:space="preserve">0.717947602272034</t>
   </si>
   <si>
     <t xml:space="preserve">0.712100028991699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.684117317199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.690799713134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69288831949234</t>
+    <t xml:space="preserve">0.684117376804352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69079977273941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.692888379096985</t>
   </si>
   <si>
     <t xml:space="preserve">0.685787737369537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674094140529633</t>
+    <t xml:space="preserve">0.674094259738922</t>
   </si>
   <si>
     <t xml:space="preserve">0.666576147079468</t>
@@ -2750,7 +2750,7 @@
     <t xml:space="preserve">0.687458992004395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.68537038564682</t>
+    <t xml:space="preserve">0.685370266437531</t>
   </si>
   <si>
     <t xml:space="preserve">0.67785233259201</t>
@@ -2762,22 +2762,22 @@
     <t xml:space="preserve">0.697482109069824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.703747272491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69831782579422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.721288502216339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.720453679561615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.742588639259338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.767647981643677</t>
+    <t xml:space="preserve">0.703747153282166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.698317766189575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.721288442611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.72045373916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.742588698863983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767647922039032</t>
   </si>
   <si>
     <t xml:space="preserve">0.718365073204041</t>
@@ -2792,73 +2792,73 @@
     <t xml:space="preserve">0.75720739364624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778925061225891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79646623134613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825284600257874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.850343704223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860367834568024</t>
+    <t xml:space="preserve">0.778925001621246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796466290950775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825284540653229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.850343823432922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860367774963379</t>
   </si>
   <si>
     <t xml:space="preserve">0.847003042697906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.858696579933167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843661308288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8720623254776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852014183998108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.854520201683044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812755346298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80774337053299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.813172698020935</t>
+    <t xml:space="preserve">0.858696639537811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843661367893219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872062265872955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852014124393463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.854520082473755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812755405902863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807743310928345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81317275762558</t>
   </si>
   <si>
     <t xml:space="preserve">0.828626155853271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.832802534103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820690751075745</t>
+    <t xml:space="preserve">0.832802593708038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820690810680389</t>
   </si>
   <si>
     <t xml:space="preserve">0.749689340591431</t>
   </si>
   <si>
-    <t xml:space="preserve">0.710846960544586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.654464304447174</t>
+    <t xml:space="preserve">0.710847020149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.654464244842529</t>
   </si>
   <si>
     <t xml:space="preserve">0.633998811244965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.645275831222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.660311102867126</t>
+    <t xml:space="preserve">0.645275890827179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.660311043262482</t>
   </si>
   <si>
     <t xml:space="preserve">0.684534728527069</t>
@@ -2867,31 +2867,31 @@
     <t xml:space="preserve">0.68912935256958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.753030061721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784354448318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787696123123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803148627281189</t>
+    <t xml:space="preserve">0.753030121326447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784354388713837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787696063518524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803148686885834</t>
   </si>
   <si>
     <t xml:space="preserve">0.856191456317902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.845331788063049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877073466777802</t>
+    <t xml:space="preserve">0.845331728458405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877073407173157</t>
   </si>
   <si>
     <t xml:space="preserve">0.900462329387665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.889603555202484</t>
+    <t xml:space="preserve">0.889603495597839</t>
   </si>
   <si>
     <t xml:space="preserve">0.887097477912903</t>
@@ -2906,25 +2906,25 @@
     <t xml:space="preserve">0.904638826847076</t>
   </si>
   <si>
-    <t xml:space="preserve">0.89294421672821</t>
+    <t xml:space="preserve">0.892944276332855</t>
   </si>
   <si>
     <t xml:space="preserve">0.902132749557495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.88208544254303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867885053157806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841155350208282</t>
+    <t xml:space="preserve">0.882085561752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867884933948517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841155409812927</t>
   </si>
   <si>
     <t xml:space="preserve">0.839484930038452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.841990947723389</t>
+    <t xml:space="preserve">0.841991007328033</t>
   </si>
   <si>
     <t xml:space="preserve">0.840320587158203</t>
@@ -2933,31 +2933,31 @@
     <t xml:space="preserve">0.859532177448273</t>
   </si>
   <si>
-    <t xml:space="preserve">0.905474305152893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849508166313171</t>
+    <t xml:space="preserve">0.905474364757538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849508225917816</t>
   </si>
   <si>
     <t xml:space="preserve">0.872897028923035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.906310021877289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943898439407349</t>
+    <t xml:space="preserve">0.906310081481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943898499011993</t>
   </si>
   <si>
     <t xml:space="preserve">0.95392245054245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9572634100914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965616941452026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978146135807037</t>
+    <t xml:space="preserve">0.957263290882111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965616881847382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978146076202393</t>
   </si>
   <si>
     <t xml:space="preserve">0.961439728736877</t>
@@ -2972,10 +2972,10 @@
     <t xml:space="preserve">0.874567449092865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.852849841117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867050290107727</t>
+    <t xml:space="preserve">0.852849781513214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867050230503082</t>
   </si>
   <si>
     <t xml:space="preserve">0.878744661808014</t>
@@ -2984,106 +2984,106 @@
     <t xml:space="preserve">0.907144844532013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.931369364261627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921345114707947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927191972732544</t>
+    <t xml:space="preserve">0.931369304656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921345233917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927191913127899</t>
   </si>
   <si>
     <t xml:space="preserve">0.912992417812347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947239995002747</t>
+    <t xml:space="preserve">0.947240114212036</t>
   </si>
   <si>
     <t xml:space="preserve">0.899626731872559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.929697871208191</t>
+    <t xml:space="preserve">0.929698050022125</t>
   </si>
   <si>
     <t xml:space="preserve">0.938886523246765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.937216103076935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.942228019237518</t>
+    <t xml:space="preserve">0.937215983867645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942228078842163</t>
   </si>
   <si>
     <t xml:space="preserve">0.941392481327057</t>
   </si>
   <si>
-    <t xml:space="preserve">0.94640451669693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.935545742511749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975640118122101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14687860012054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18947911262512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17360818386078</t>
+    <t xml:space="preserve">0.946404576301575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93554562330246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975639998912811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14687871932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18947923183441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17360830307007</t>
   </si>
   <si>
     <t xml:space="preserve">1.16024339199066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15773749351501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17193794250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1385258436203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10928928852081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11096060276031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1067841053009</t>
+    <t xml:space="preserve">1.1577376127243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17193782329559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13852572441101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1092894077301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11096036434174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10678422451019</t>
   </si>
   <si>
     <t xml:space="preserve">1.11179530620575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13100779056549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12098360061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16358518600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14520823955536</t>
+    <t xml:space="preserve">1.1310076713562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12098383903503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16358506679535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14520835876465</t>
   </si>
   <si>
     <t xml:space="preserve">1.11513698101044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10761880874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37742388248444</t>
+    <t xml:space="preserve">1.10761892795563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37742412090302</t>
   </si>
   <si>
     <t xml:space="preserve">1.37241184711456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43923699855804</t>
+    <t xml:space="preserve">1.43923687934875</t>
   </si>
   <si>
     <t xml:space="preserve">1.43673098087311</t>
@@ -3092,13 +3092,13 @@
     <t xml:space="preserve">1.44007170200348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40665972232819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41167175769806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39747142791748</t>
+    <t xml:space="preserve">1.4066596031189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41167187690735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39747130870819</t>
   </si>
   <si>
     <t xml:space="preserve">1.43840134143829</t>
@@ -3107,34 +3107,34 @@
     <t xml:space="preserve">1.47682547569275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45928406715393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44090735912323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43338942527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48100185394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41334211826324</t>
+    <t xml:space="preserve">1.45928430557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44090747833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43338930606842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48100173473358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41334223747253</t>
   </si>
   <si>
     <t xml:space="preserve">1.42587125301361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58792126178741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55033278465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62634539604187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61214601993561</t>
+    <t xml:space="preserve">1.5879213809967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.550332903862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62634551525116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61214590072632</t>
   </si>
   <si>
     <t xml:space="preserve">1.62049877643585</t>
@@ -3143,25 +3143,25 @@
     <t xml:space="preserve">1.61966300010681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62718093395233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6138162612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45677816867828</t>
+    <t xml:space="preserve">1.62718105316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61381614208221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45677828788757</t>
   </si>
   <si>
     <t xml:space="preserve">1.39830696582794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34317636489868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35654127597809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35904705524445</t>
+    <t xml:space="preserve">1.34317624568939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35654103755951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35904717445374</t>
   </si>
   <si>
     <t xml:space="preserve">1.36489391326904</t>
@@ -3170,7 +3170,7 @@
     <t xml:space="preserve">1.4027658700943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43466711044312</t>
+    <t xml:space="preserve">1.4346672296524</t>
   </si>
   <si>
     <t xml:space="preserve">1.41251361370087</t>
@@ -3182,7 +3182,7 @@
     <t xml:space="preserve">1.39213216304779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33364653587341</t>
+    <t xml:space="preserve">1.3336466550827</t>
   </si>
   <si>
     <t xml:space="preserve">1.44795918464661</t>
@@ -3191,10 +3191,10 @@
     <t xml:space="preserve">1.49049437046051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51796472072601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53214299678802</t>
+    <t xml:space="preserve">1.5179648399353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53214287757874</t>
   </si>
   <si>
     <t xml:space="preserve">1.58442544937134</t>
@@ -3206,19 +3206,19 @@
     <t xml:space="preserve">1.54897975921631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54454910755157</t>
+    <t xml:space="preserve">1.54454898834229</t>
   </si>
   <si>
     <t xml:space="preserve">1.53834593296051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5587272644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57645010948181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6145544052124</t>
+    <t xml:space="preserve">1.55872714519501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5764502286911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61455428600311</t>
   </si>
   <si>
     <t xml:space="preserve">1.60657906532288</t>
@@ -3227,22 +3227,22 @@
     <t xml:space="preserve">1.5693610906601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58885610103607</t>
+    <t xml:space="preserve">1.58885622024536</t>
   </si>
   <si>
     <t xml:space="preserve">1.60392069816589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63582193851471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62518799304962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61278212070465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58353936672211</t>
+    <t xml:space="preserve">1.63582181930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62518811225891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61278223991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58353924751282</t>
   </si>
   <si>
     <t xml:space="preserve">1.51885080337524</t>
@@ -3251,16 +3251,16 @@
     <t xml:space="preserve">1.520623087883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4931526184082</t>
+    <t xml:space="preserve">1.49315237998962</t>
   </si>
   <si>
     <t xml:space="preserve">1.49758338928223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52505362033844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50733089447021</t>
+    <t xml:space="preserve">1.52505397796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5073310136795</t>
   </si>
   <si>
     <t xml:space="preserve">1.50112795829773</t>
@@ -3269,10 +3269,10 @@
     <t xml:space="preserve">1.54011833667755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53037071228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55341053009033</t>
+    <t xml:space="preserve">1.53037059307098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55341041088104</t>
   </si>
   <si>
     <t xml:space="preserve">1.6384801864624</t>
@@ -3287,13 +3287,13 @@
     <t xml:space="preserve">1.51707851886749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48872196674347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46568214893341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42403340339661</t>
+    <t xml:space="preserve">1.48872184753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4656822681427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42403328418732</t>
   </si>
   <si>
     <t xml:space="preserve">1.44707310199738</t>
@@ -3302,67 +3302,67 @@
     <t xml:space="preserve">1.46656835079193</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61809885501862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8290011882782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84672427177429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90520966053009</t>
+    <t xml:space="preserve">1.61809897422791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82900106906891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84672403335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9052095413208</t>
   </si>
   <si>
     <t xml:space="preserve">1.89634823799133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98319029808044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03635883331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09129977226257</t>
+    <t xml:space="preserve">1.98319017887115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03635907173157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09129953384399</t>
   </si>
   <si>
     <t xml:space="preserve">2.17105293273926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96015048027039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88925921916962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96192288398743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94597256183624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01863646507263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10902261734009</t>
+    <t xml:space="preserve">1.96015059947968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88925898075104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96192276477814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94597232341766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01863622665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10902309417725</t>
   </si>
   <si>
     <t xml:space="preserve">2.0753493309021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10547828674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13737940788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12674570083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17814207077026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16396379470825</t>
+    <t xml:space="preserve">2.10547804832458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13737964630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12674593925476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17814183235168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16396355628967</t>
   </si>
   <si>
     <t xml:space="preserve">2.17636966705322</t>
@@ -3371,28 +3371,28 @@
     <t xml:space="preserve">2.18168640136719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24371695518494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1799144744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12320137023926</t>
+    <t xml:space="preserve">2.24371671676636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17991423606873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12320113182068</t>
   </si>
   <si>
     <t xml:space="preserve">2.14624071121216</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19763708114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30574679374695</t>
+    <t xml:space="preserve">2.19763684272766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30574655532837</t>
   </si>
   <si>
     <t xml:space="preserve">2.28625154495239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31992483139038</t>
+    <t xml:space="preserve">2.31992506980896</t>
   </si>
   <si>
     <t xml:space="preserve">2.34828162193298</t>
@@ -3401,46 +3401,46 @@
     <t xml:space="preserve">2.417400598526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44575762748718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38372731208801</t>
+    <t xml:space="preserve">2.4457573890686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38372755050659</t>
   </si>
   <si>
     <t xml:space="preserve">2.46348023414612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42449021339417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47411417961121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51310443878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50955986976624</t>
+    <t xml:space="preserve">2.42448997497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47411394119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51310420036316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50956010818481</t>
   </si>
   <si>
     <t xml:space="preserve">2.43157911300659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47056984901428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39613318443298</t>
+    <t xml:space="preserve">2.4705696105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39613342285156</t>
   </si>
   <si>
     <t xml:space="preserve">2.33942031860352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37841033935547</t>
+    <t xml:space="preserve">2.37841057777405</t>
   </si>
   <si>
     <t xml:space="preserve">2.21004319190979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38904452323914</t>
+    <t xml:space="preserve">2.38904428482056</t>
   </si>
   <si>
     <t xml:space="preserve">2.47943115234375</t>
@@ -3452,28 +3452,28 @@
     <t xml:space="preserve">2.56095623970032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6566596031189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64070916175842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63184762001038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65311527252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59640192985535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52373814582825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33233118057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31815266609192</t>
+    <t xml:space="preserve">2.65665984153748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.640709400177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63184785842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65311503410339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59640216827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52373838424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33233094215393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31815242767334</t>
   </si>
   <si>
     <t xml:space="preserve">2.2968852519989</t>
@@ -3482,16 +3482,16 @@
     <t xml:space="preserve">2.28270721435547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2756175994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25966739654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30929136276245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27916240692139</t>
+    <t xml:space="preserve">2.27561807632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25966715812683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30929112434387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27916216850281</t>
   </si>
   <si>
     <t xml:space="preserve">2.28802371025085</t>
@@ -3506,37 +3506,37 @@
     <t xml:space="preserve">2.30751919746399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24017214775085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14978551864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16041922569275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17459726333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13915181159973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15687441825867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05762648582458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16928029060364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1958646774292</t>
+    <t xml:space="preserve">2.24017190933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14978528022766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16041898727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17459750175476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13915157318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15687465667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05762624740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16928052902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19586491584778</t>
   </si>
   <si>
     <t xml:space="preserve">2.13560724258423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39258861541748</t>
+    <t xml:space="preserve">2.39258885383606</t>
   </si>
   <si>
     <t xml:space="preserve">2.39436101913452</t>
@@ -3545,22 +3545,22 @@
     <t xml:space="preserve">2.06648778915405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99382436275482</t>
+    <t xml:space="preserve">1.99382412433624</t>
   </si>
   <si>
     <t xml:space="preserve">2.12142872810364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1196563243866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09484434127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01331901550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08066630363464</t>
+    <t xml:space="preserve">2.11965608596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09484457969666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01331925392151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08066606521606</t>
   </si>
   <si>
     <t xml:space="preserve">1.99205148220062</t>
@@ -3569,52 +3569,52 @@
     <t xml:space="preserve">2.03458690643311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02926969528198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93179392814636</t>
+    <t xml:space="preserve">2.0292694568634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93179404735565</t>
   </si>
   <si>
     <t xml:space="preserve">2.01509141921997</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00445771217346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86799156665802</t>
+    <t xml:space="preserve">2.00445795059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86799168586731</t>
   </si>
   <si>
     <t xml:space="preserve">1.90166509151459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80596172809601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6455694437027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56315815448761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56847488880157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68012917041779</t>
+    <t xml:space="preserve">1.80596148967743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64556956291199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56315803527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56847476959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6801290512085</t>
   </si>
   <si>
     <t xml:space="preserve">1.57999491691589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59505915641785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65974771976471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78646647930145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75545120239258</t>
+    <t xml:space="preserve">1.59505903720856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.659747838974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78646624088287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75545132160187</t>
   </si>
   <si>
     <t xml:space="preserve">1.73684227466583</t>
@@ -3623,10 +3623,10 @@
     <t xml:space="preserve">1.73418390750885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70671343803406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65088629722595</t>
+    <t xml:space="preserve">1.70671331882477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65088617801666</t>
   </si>
   <si>
     <t xml:space="preserve">1.66595065593719</t>
@@ -3635,70 +3635,70 @@
     <t xml:space="preserve">1.67924284934998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72798085212708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86444699764252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83431792259216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74570381641388</t>
+    <t xml:space="preserve">1.72798073291779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8644472360611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83431816101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7457035779953</t>
   </si>
   <si>
     <t xml:space="preserve">1.78469407558441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76254034042358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7288670539856</t>
+    <t xml:space="preserve">1.76254045963287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72886693477631</t>
   </si>
   <si>
     <t xml:space="preserve">1.67038142681122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64113867282867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60126221179962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61987113952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71025788784027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70051038265228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67835664749146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62961864471436</t>
+    <t xml:space="preserve">1.64113879203796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60126233100891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61987125873566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71025800704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70051050186157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67835688591003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62961876392365</t>
   </si>
   <si>
     <t xml:space="preserve">1.63936650753021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63050496578217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60923743247986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62075746059418</t>
+    <t xml:space="preserve">1.63050508499146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60923767089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62075734138489</t>
   </si>
   <si>
     <t xml:space="preserve">1.55075216293335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46302366256714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47897446155548</t>
+    <t xml:space="preserve">1.46302378177643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4789742231369</t>
   </si>
   <si>
     <t xml:space="preserve">1.5418906211853</t>
@@ -3707,67 +3707,67 @@
     <t xml:space="preserve">1.60835146903992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58974242210388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64468336105347</t>
+    <t xml:space="preserve">1.58974254131317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64468324184418</t>
   </si>
   <si>
     <t xml:space="preserve">1.60746514797211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60037612915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52594006061554</t>
+    <t xml:space="preserve">1.6003760099411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52593994140625</t>
   </si>
   <si>
     <t xml:space="preserve">1.52150928974152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63139116764069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64734160900116</t>
+    <t xml:space="preserve">1.6313910484314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64734172821045</t>
   </si>
   <si>
     <t xml:space="preserve">1.72266399860382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69076263904572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71646106243134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78114938735962</t>
+    <t xml:space="preserve">1.690762758255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71646094322205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7811496257782</t>
   </si>
   <si>
     <t xml:space="preserve">1.84495174884796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80773365497589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79887235164642</t>
+    <t xml:space="preserve">1.80773377418518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79887247085571</t>
   </si>
   <si>
     <t xml:space="preserve">1.79532778263092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65797555446625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45593452453613</t>
+    <t xml:space="preserve">1.65797543525696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45593464374542</t>
   </si>
   <si>
     <t xml:space="preserve">1.41871654987335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46506798267365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4768830537796</t>
+    <t xml:space="preserve">1.46506786346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47688293457031</t>
   </si>
   <si>
     <t xml:space="preserve">1.48960697650909</t>
@@ -3776,13 +3776,13 @@
     <t xml:space="preserve">1.45779716968536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47597408294678</t>
+    <t xml:space="preserve">1.47597420215607</t>
   </si>
   <si>
     <t xml:space="preserve">1.43689358234406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.474156498909</t>
+    <t xml:space="preserve">1.47415637969971</t>
   </si>
   <si>
     <t xml:space="preserve">1.48142731189728</t>
@@ -3800,67 +3800,67 @@
     <t xml:space="preserve">1.30147469043732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32783138751984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37418282032013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40781044960022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3859977722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31510746479034</t>
+    <t xml:space="preserve">1.32783150672913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37418270111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40781033039093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38599789142609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31510758399963</t>
   </si>
   <si>
     <t xml:space="preserve">1.28420662879944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27966225147247</t>
+    <t xml:space="preserve">1.27966237068176</t>
   </si>
   <si>
     <t xml:space="preserve">1.30874562263489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32692265510559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39781296253204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37145626544952</t>
+    <t xml:space="preserve">1.3269225358963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39781284332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37145614624023</t>
   </si>
   <si>
     <t xml:space="preserve">1.3578234910965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35691463947296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29693055152893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31328976154327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33328461647034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41962552070618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42689621448517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40144848823547</t>
+    <t xml:space="preserve">1.35691475868225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29693043231964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31328988075256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33328449726105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41962540149689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42689633369446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40144836902618</t>
   </si>
   <si>
     <t xml:space="preserve">1.44416439533234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46961212158203</t>
+    <t xml:space="preserve">1.46961200237274</t>
   </si>
   <si>
     <t xml:space="preserve">1.45961475372314</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">1.48778915405273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49506008625031</t>
+    <t xml:space="preserve">1.49505996704102</t>
   </si>
   <si>
     <t xml:space="preserve">1.48869812488556</t>
@@ -3884,19 +3884,19 @@
     <t xml:space="preserve">1.50051307678223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48051834106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40326607227325</t>
+    <t xml:space="preserve">1.48051846027374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40326619148254</t>
   </si>
   <si>
     <t xml:space="preserve">1.43234932422638</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41144561767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34691739082336</t>
+    <t xml:space="preserve">1.41144573688507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34691727161407</t>
   </si>
   <si>
     <t xml:space="preserve">1.34328186511993</t>
@@ -3905,52 +3905,52 @@
     <t xml:space="preserve">1.37327396869659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37600064277649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36236763000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39235985279083</t>
+    <t xml:space="preserve">1.37600040435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36236774921417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39235973358154</t>
   </si>
   <si>
     <t xml:space="preserve">1.33601105213165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35237038135529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36963868141174</t>
+    <t xml:space="preserve">1.35237050056458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36963856220245</t>
   </si>
   <si>
     <t xml:space="preserve">1.35964131355286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41326344013214</t>
+    <t xml:space="preserve">1.41326332092285</t>
   </si>
   <si>
     <t xml:space="preserve">1.43507587909698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41689884662628</t>
+    <t xml:space="preserve">1.41689896583557</t>
   </si>
   <si>
     <t xml:space="preserve">1.46870338916779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41235458850861</t>
+    <t xml:space="preserve">1.4123547077179</t>
   </si>
   <si>
     <t xml:space="preserve">1.39872181415558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70591342449188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68591868877411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58412754535675</t>
+    <t xml:space="preserve">1.70591354370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6859188079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58412742614746</t>
   </si>
   <si>
     <t xml:space="preserve">1.57867431640625</t>
@@ -3962,10 +3962,10 @@
     <t xml:space="preserve">1.56322383880615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49960434436798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55777060985565</t>
+    <t xml:space="preserve">1.4996041059494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55777084827423</t>
   </si>
   <si>
     <t xml:space="preserve">1.55231761932373</t>
@@ -3977,13 +3977,13 @@
     <t xml:space="preserve">1.58140087127686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53777599334717</t>
+    <t xml:space="preserve">1.53777611255646</t>
   </si>
   <si>
     <t xml:space="preserve">1.52323436737061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56049728393555</t>
+    <t xml:space="preserve">1.56049740314484</t>
   </si>
   <si>
     <t xml:space="preserve">1.53323185443878</t>
@@ -3995,7 +3995,7 @@
     <t xml:space="preserve">1.59412467479706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64047622680664</t>
+    <t xml:space="preserve">1.64047610759735</t>
   </si>
   <si>
     <t xml:space="preserve">1.65774428844452</t>
@@ -4004,10 +4004,10 @@
     <t xml:space="preserve">1.65865325927734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65956199169159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6704683303833</t>
+    <t xml:space="preserve">1.65956211090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67046821117401</t>
   </si>
   <si>
     <t xml:space="preserve">1.76317119598389</t>
@@ -4016,154 +4016,154 @@
     <t xml:space="preserve">1.79225432872772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78861904144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73045241832733</t>
+    <t xml:space="preserve">1.78861892223358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73045253753662</t>
   </si>
   <si>
     <t xml:space="preserve">1.71772849559784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72681701183319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77135062217712</t>
+    <t xml:space="preserve">1.72681713104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77135074138641</t>
   </si>
   <si>
     <t xml:space="preserve">1.73136138916016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75135600566864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78770995140076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84860324859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8667801618576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87223303318024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89949870109558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93403518199921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94494128227234</t>
+    <t xml:space="preserve">1.75135612487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78771007061005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84860301017761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86678004264832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87223315238953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89949882030487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93403506278992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94494140148163</t>
   </si>
   <si>
     <t xml:space="preserve">1.90676963329315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95402991771698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97038924694061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00492548942566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99583733081818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97220706939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97402441501617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99038398265839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04491519927979</t>
+    <t xml:space="preserve">1.95402979850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97038900852203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00492525100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99583697319031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97220695018768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97402453422546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9903838634491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04491496086121</t>
   </si>
   <si>
     <t xml:space="preserve">2.13398241996765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15397715568542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12307620048523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11944055557251</t>
+    <t xml:space="preserve">2.15397691726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12307596206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11944079399109</t>
   </si>
   <si>
     <t xml:space="preserve">2.13761758804321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16851878166199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11035203933716</t>
+    <t xml:space="preserve">2.16851854324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11035227775574</t>
   </si>
   <si>
     <t xml:space="preserve">2.10308122634888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10126352310181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97584235668182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02128481864929</t>
+    <t xml:space="preserve">2.10126376152039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97584247589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02128505706787</t>
   </si>
   <si>
     <t xml:space="preserve">1.85223865509033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89041018486023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91222274303436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92676424980164</t>
+    <t xml:space="preserve">1.89041006565094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91222286224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92676436901093</t>
   </si>
   <si>
     <t xml:space="preserve">1.93585288524628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93948829174042</t>
+    <t xml:space="preserve">1.93948805332184</t>
   </si>
   <si>
     <t xml:space="preserve">1.90131652355194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91404044628143</t>
+    <t xml:space="preserve">1.91404032707214</t>
   </si>
   <si>
     <t xml:space="preserve">1.96311855316162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96857130527496</t>
+    <t xml:space="preserve">1.96857118606567</t>
   </si>
   <si>
     <t xml:space="preserve">2.03219103813171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05945682525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10489916801453</t>
+    <t xml:space="preserve">2.05945658683777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10489892959595</t>
   </si>
   <si>
     <t xml:space="preserve">2.12852907180786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12671160697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09944581985474</t>
+    <t xml:space="preserve">2.12671136856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09944605827332</t>
   </si>
   <si>
     <t xml:space="preserve">2.01946687698364</t>
@@ -4172,22 +4172,22 @@
     <t xml:space="preserve">2.07218050956726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06309175491333</t>
+    <t xml:space="preserve">2.06309199333191</t>
   </si>
   <si>
     <t xml:space="preserve">2.03764414787292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00310778617859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01219630241394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01764941215515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00129008293152</t>
+    <t xml:space="preserve">2.00310754776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01219654083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01764965057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00128984451294</t>
   </si>
   <si>
     <t xml:space="preserve">2.27394556999207</t>
@@ -4196,16 +4196,16 @@
     <t xml:space="preserve">2.2484974861145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31757020950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30848145484924</t>
+    <t xml:space="preserve">2.31757044792175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3084819316864</t>
   </si>
   <si>
     <t xml:space="preserve">2.33211183547974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3721010684967</t>
+    <t xml:space="preserve">2.37210130691528</t>
   </si>
   <si>
     <t xml:space="preserve">2.41572618484497</t>
@@ -4214,7 +4214,7 @@
     <t xml:space="preserve">2.37573671340942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40845537185669</t>
+    <t xml:space="preserve">2.40845561027527</t>
   </si>
   <si>
     <t xml:space="preserve">2.39754915237427</t>
@@ -4223,10 +4223,10 @@
     <t xml:space="preserve">2.38846063613892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39209604263306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35755968093872</t>
+    <t xml:space="preserve">2.39209580421448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3575599193573</t>
   </si>
   <si>
     <t xml:space="preserve">2.34483551979065</t>
@@ -4241,49 +4241,49 @@
     <t xml:space="preserve">2.33574724197388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33938241004944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38118958473206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40663743019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40481996536255</t>
+    <t xml:space="preserve">2.33938264846802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38118982315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40663766860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40481972694397</t>
   </si>
   <si>
     <t xml:space="preserve">2.39027833938599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37937211990356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32302331924438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28666925430298</t>
+    <t xml:space="preserve">2.37937188148499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32302355766296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28666949272156</t>
   </si>
   <si>
     <t xml:space="preserve">2.18487811088562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23213839530945</t>
+    <t xml:space="preserve">2.23213815689087</t>
   </si>
   <si>
     <t xml:space="preserve">2.18306016921997</t>
   </si>
   <si>
-    <t xml:space="preserve">2.143070936203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20487308502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20669031143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17033624649048</t>
+    <t xml:space="preserve">2.14307069778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20487260818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20669007301331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17033648490906</t>
   </si>
   <si>
     <t xml:space="preserve">2.13943552970886</t>
@@ -4298,28 +4298,28 @@
     <t xml:space="preserve">2.19578409194946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19033145904541</t>
+    <t xml:space="preserve">2.19033122062683</t>
   </si>
   <si>
     <t xml:space="preserve">2.26849246025085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24668002128601</t>
+    <t xml:space="preserve">2.24667954444885</t>
   </si>
   <si>
     <t xml:space="preserve">2.24304437637329</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25213289260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30121111869812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28303408622742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34120059013367</t>
+    <t xml:space="preserve">2.25213265419006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30121064186096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28303384780884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34120035171509</t>
   </si>
   <si>
     <t xml:space="preserve">2.47934556007385</t>
@@ -4328,7 +4328,7 @@
     <t xml:space="preserve">2.44844484329224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48843431472778</t>
+    <t xml:space="preserve">2.48843383789062</t>
   </si>
   <si>
     <t xml:space="preserve">2.46843957901001</t>
@@ -4337,13 +4337,13 @@
     <t xml:space="preserve">2.47207498550415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45935106277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45753312110901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43390321731567</t>
+    <t xml:space="preserve">2.45935130119324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45753359794617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43390297889709</t>
   </si>
   <si>
     <t xml:space="preserve">2.51388216018677</t>
@@ -4358,13 +4358,13 @@
     <t xml:space="preserve">2.4702570438385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40118455886841</t>
+    <t xml:space="preserve">2.40118432044983</t>
   </si>
   <si>
     <t xml:space="preserve">2.36664843559265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41754388809204</t>
+    <t xml:space="preserve">2.41754412651062</t>
   </si>
   <si>
     <t xml:space="preserve">2.2793984413147</t>
@@ -4373,49 +4373,49 @@
     <t xml:space="preserve">2.28485155105591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29212260246277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27030968666077</t>
+    <t xml:space="preserve">2.29212236404419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27030992507935</t>
   </si>
   <si>
     <t xml:space="preserve">2.22668528556824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30302834510803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32484126091003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33029413223267</t>
+    <t xml:space="preserve">2.30302858352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32484102249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33029389381409</t>
   </si>
   <si>
     <t xml:space="preserve">2.29939317703247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41936159133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4320855140686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4211790561676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43935632705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25599431991577</t>
+    <t xml:space="preserve">2.41936135292053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43208575248718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42117929458618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43935608863831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25599455833435</t>
   </si>
   <si>
     <t xml:space="preserve">2.28207540512085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27462363243103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24854278564453</t>
+    <t xml:space="preserve">2.27462339401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24854302406311</t>
   </si>
   <si>
     <t xml:space="preserve">2.22991347312927</t>
@@ -4427,28 +4427,28 @@
     <t xml:space="preserve">2.31188225746155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36590647697449</t>
+    <t xml:space="preserve">2.36590671539307</t>
   </si>
   <si>
     <t xml:space="preserve">2.40130209922791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36404371261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29697895050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32678508758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34168863296509</t>
+    <t xml:space="preserve">2.36404395103455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29697871208191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32678556442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34168839454651</t>
   </si>
   <si>
     <t xml:space="preserve">2.33982586860657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36963248252869</t>
+    <t xml:space="preserve">2.36963224411011</t>
   </si>
   <si>
     <t xml:space="preserve">2.36776971817017</t>
@@ -4457,16 +4457,16 @@
     <t xml:space="preserve">2.32864832878113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29884147644043</t>
+    <t xml:space="preserve">2.29884171485901</t>
   </si>
   <si>
     <t xml:space="preserve">2.28580117225647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28021216392517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29511570930481</t>
+    <t xml:space="preserve">2.28021240234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29511594772339</t>
   </si>
   <si>
     <t xml:space="preserve">2.30443024635315</t>
@@ -4475,16 +4475,16 @@
     <t xml:space="preserve">2.29325270652771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33051133155823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31374478340149</t>
+    <t xml:space="preserve">2.33051156997681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31374502182007</t>
   </si>
   <si>
     <t xml:space="preserve">2.28952693939209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22432470321655</t>
+    <t xml:space="preserve">2.22432494163513</t>
   </si>
   <si>
     <t xml:space="preserve">2.20569562911987</t>
@@ -4493,7 +4493,7 @@
     <t xml:space="preserve">2.16098570823669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14049339294434</t>
+    <t xml:space="preserve">2.14049363136292</t>
   </si>
   <si>
     <t xml:space="preserve">2.1069610118866</t>
@@ -4502,10 +4502,10 @@
     <t xml:space="preserve">2.09950923919678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12559008598328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1088240146637</t>
+    <t xml:space="preserve">2.12559032440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10882377624512</t>
   </si>
   <si>
     <t xml:space="preserve">2.09019470214844</t>
@@ -4514,22 +4514,22 @@
     <t xml:space="preserve">2.0585253238678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04362154006958</t>
+    <t xml:space="preserve">2.04362177848816</t>
   </si>
   <si>
     <t xml:space="preserve">2.04921054840088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08460593223572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06411409378052</t>
+    <t xml:space="preserve">2.08460569381714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06411385536194</t>
   </si>
   <si>
     <t xml:space="preserve">2.0510733127594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04175853729248</t>
+    <t xml:space="preserve">2.04175877571106</t>
   </si>
   <si>
     <t xml:space="preserve">2.09205770492554</t>
@@ -4538,7 +4538,7 @@
     <t xml:space="preserve">2.15912270545959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1535336971283</t>
+    <t xml:space="preserve">2.15353417396545</t>
   </si>
   <si>
     <t xml:space="preserve">2.13863062858582</t>
@@ -4550,7 +4550,7 @@
     <t xml:space="preserve">2.06970238685608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0231294631958</t>
+    <t xml:space="preserve">2.02312970161438</t>
   </si>
   <si>
     <t xml:space="preserve">2.01754069328308</t>
@@ -4565,7 +4565,7 @@
     <t xml:space="preserve">2.0007746219635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99332296848297</t>
+    <t xml:space="preserve">1.99332308769226</t>
   </si>
   <si>
     <t xml:space="preserve">1.97469365596771</t>
@@ -4574,22 +4574,22 @@
     <t xml:space="preserve">1.95606434345245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92625796794891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.864781498909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77349853515625</t>
+    <t xml:space="preserve">1.92625784873962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86478161811829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77349865436554</t>
   </si>
   <si>
     <t xml:space="preserve">1.78095018863678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78467607498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80330514907837</t>
+    <t xml:space="preserve">1.7846759557724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80330526828766</t>
   </si>
   <si>
     <t xml:space="preserve">1.83311200141907</t>
@@ -4604,10 +4604,10 @@
     <t xml:space="preserve">1.71109080314636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70829629898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71947395801544</t>
+    <t xml:space="preserve">1.70829641819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71947383880615</t>
   </si>
   <si>
     <t xml:space="preserve">1.67196941375732</t>
@@ -4622,7 +4622,7 @@
     <t xml:space="preserve">1.61608195304871</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63005387783051</t>
+    <t xml:space="preserve">1.63005375862122</t>
   </si>
   <si>
     <t xml:space="preserve">1.63377952575684</t>
@@ -4637,16 +4637,16 @@
     <t xml:space="preserve">1.64682006835938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53131914138794</t>
+    <t xml:space="preserve">1.53131926059723</t>
   </si>
   <si>
     <t xml:space="preserve">1.54994833469391</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53877079486847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54529106616974</t>
+    <t xml:space="preserve">1.53877067565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54529094696045</t>
   </si>
   <si>
     <t xml:space="preserve">1.54249668121338</t>
@@ -4655,19 +4655,19 @@
     <t xml:space="preserve">1.55087971687317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55646848678589</t>
+    <t xml:space="preserve">1.55646860599518</t>
   </si>
   <si>
     <t xml:space="preserve">1.56485164165497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57975494861603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61887633800507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60117852687836</t>
+    <t xml:space="preserve">1.57975506782532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61887621879578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60117840766907</t>
   </si>
   <si>
     <t xml:space="preserve">1.60956168174744</t>
@@ -4682,7 +4682,7 @@
     <t xml:space="preserve">1.59745287895203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61235594749451</t>
+    <t xml:space="preserve">1.6123560667038</t>
   </si>
   <si>
     <t xml:space="preserve">1.62073922157288</t>
@@ -4709,16 +4709,16 @@
     <t xml:space="preserve">1.6682436466217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67662668228149</t>
+    <t xml:space="preserve">1.67662680149078</t>
   </si>
   <si>
     <t xml:space="preserve">1.69059872627258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72785699367523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8424266576767</t>
+    <t xml:space="preserve">1.72785711288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84242653846741</t>
   </si>
   <si>
     <t xml:space="preserve">1.84801530838013</t>
@@ -4727,16 +4727,16 @@
     <t xml:space="preserve">1.90390276908875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92998361587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97655665874481</t>
+    <t xml:space="preserve">1.92998373508453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9765567779541</t>
   </si>
   <si>
     <t xml:space="preserve">1.96165335178375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91508030891418</t>
+    <t xml:space="preserve">1.91508042812347</t>
   </si>
   <si>
     <t xml:space="preserve">1.93557250499725</t>
@@ -4757,10 +4757,10 @@
     <t xml:space="preserve">2.09764647483826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09392023086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1106870174408</t>
+    <t xml:space="preserve">2.09392046928406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11068677902222</t>
   </si>
   <si>
     <t xml:space="preserve">2.08646893501282</t>
@@ -4772,16 +4772,16 @@
     <t xml:space="preserve">2.11441254615784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10137224197388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03617024421692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0026376247406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98028242588043</t>
+    <t xml:space="preserve">2.1013720035553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03617000579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00263738632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98028254508972</t>
   </si>
   <si>
     <t xml:space="preserve">2.01008915901184</t>
@@ -4790,22 +4790,22 @@
     <t xml:space="preserve">2.01567792892456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98214554786682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90017688274384</t>
+    <t xml:space="preserve">1.98214542865753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90017700195312</t>
   </si>
   <si>
     <t xml:space="preserve">1.91694331169128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89272522926331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92812061309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95420169830322</t>
+    <t xml:space="preserve">1.8927253484726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92812085151672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95420157909393</t>
   </si>
   <si>
     <t xml:space="preserve">2.06783962249756</t>
@@ -4814,16 +4814,16 @@
     <t xml:space="preserve">2.03989601135254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0752911567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09578371047974</t>
+    <t xml:space="preserve">2.07529139518738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09578347206116</t>
   </si>
   <si>
     <t xml:space="preserve">2.11813831329346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07715439796448</t>
+    <t xml:space="preserve">2.0771541595459</t>
   </si>
   <si>
     <t xml:space="preserve">2.08281922340393</t>
@@ -4835,7 +4835,7 @@
     <t xml:space="preserve">2.05827116966248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07148909568787</t>
+    <t xml:space="preserve">2.07148933410645</t>
   </si>
   <si>
     <t xml:space="preserve">2.12813878059387</t>
@@ -4856,7 +4856,7 @@
     <t xml:space="preserve">2.08093070983887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14135718345642</t>
+    <t xml:space="preserve">2.14135694503784</t>
   </si>
   <si>
     <t xml:space="preserve">2.10170245170593</t>
@@ -4868,7 +4868,7 @@
     <t xml:space="preserve">2.06771278381348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09981393814087</t>
+    <t xml:space="preserve">2.09981417655945</t>
   </si>
   <si>
     <t xml:space="preserve">2.15835213661194</t>
@@ -4898,13 +4898,13 @@
     <t xml:space="preserve">2.24143815040588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33396601676941</t>
+    <t xml:space="preserve">2.33396577835083</t>
   </si>
   <si>
     <t xml:space="preserve">2.32263612747192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22255492210388</t>
+    <t xml:space="preserve">2.22255516052246</t>
   </si>
   <si>
     <t xml:space="preserve">2.14702200889587</t>
@@ -4919,7 +4919,7 @@
     <t xml:space="preserve">2.09414911270142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04882955551147</t>
+    <t xml:space="preserve">2.0488293170929</t>
   </si>
   <si>
     <t xml:space="preserve">2.19989514350891</t>
@@ -4928,13 +4928,13 @@
     <t xml:space="preserve">2.2471034526825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31130599975586</t>
+    <t xml:space="preserve">2.31130623817444</t>
   </si>
   <si>
     <t xml:space="preserve">2.33207774162292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29431128501892</t>
+    <t xml:space="preserve">2.2943115234375</t>
   </si>
   <si>
     <t xml:space="preserve">2.35662579536438</t>
@@ -4952,13 +4952,13 @@
     <t xml:space="preserve">2.36040258407593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37550902366638</t>
+    <t xml:space="preserve">2.37550926208496</t>
   </si>
   <si>
     <t xml:space="preserve">2.41705203056335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46237182617188</t>
+    <t xml:space="preserve">2.46237206459045</t>
   </si>
   <si>
     <t xml:space="preserve">2.44160032272339</t>
@@ -4967,13 +4967,13 @@
     <t xml:space="preserve">2.46992492675781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48692035675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50202679634094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5265748500824</t>
+    <t xml:space="preserve">2.48692011833191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50202655792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52657508850098</t>
   </si>
   <si>
     <t xml:space="preserve">2.54168128967285</t>
@@ -4988,7 +4988,7 @@
     <t xml:space="preserve">2.50957989692688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5548996925354</t>
+    <t xml:space="preserve">2.55489993095398</t>
   </si>
   <si>
     <t xml:space="preserve">2.56811785697937</t>
@@ -5003,19 +5003,19 @@
     <t xml:space="preserve">2.70407724380493</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66442251205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64553928375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63798594474792</t>
+    <t xml:space="preserve">2.66442227363586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64553904533386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63798570632935</t>
   </si>
   <si>
     <t xml:space="preserve">2.63609766960144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70218873023987</t>
+    <t xml:space="preserve">2.70218896865845</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309238433838</t>
@@ -5036,7 +5036,7 @@
     <t xml:space="preserve">2.60210776329041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55867624282837</t>
+    <t xml:space="preserve">2.55867648124695</t>
   </si>
   <si>
     <t xml:space="preserve">2.60882019996643</t>
@@ -5979,6 +5979,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.40199995040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46000003814697</t>
   </si>
 </sst>
 </file>
@@ -72045,7 +72048,7 @@
     </row>
     <row r="2529">
       <c r="A2529" s="1" t="n">
-        <v>46000.6910416667</v>
+        <v>46000.3333333333</v>
       </c>
       <c r="B2529" t="n">
         <v>380588</v>
@@ -72066,6 +72069,32 @@
         <v>1988</v>
       </c>
       <c r="H2529" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2530">
+      <c r="A2530" s="1" t="n">
+        <v>46001.691087963</v>
+      </c>
+      <c r="B2530" t="n">
+        <v>329519</v>
+      </c>
+      <c r="C2530" t="n">
+        <v>4.46400022506714</v>
+      </c>
+      <c r="D2530" t="n">
+        <v>4.36999988555908</v>
+      </c>
+      <c r="E2530" t="n">
+        <v>4.42000007629395</v>
+      </c>
+      <c r="F2530" t="n">
+        <v>4.46000003814697</v>
+      </c>
+      <c r="G2530" t="s">
+        <v>1989</v>
+      </c>
+      <c r="H2530" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/OVS.MI.xlsx
+++ b/data/OVS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1993" uniqueCount="1993">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1994" uniqueCount="1994">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -50,82 +50,82 @@
     <t xml:space="preserve">4.76365375518799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6445631980896</t>
+    <t xml:space="preserve">4.64456176757812</t>
   </si>
   <si>
     <t xml:space="preserve">4.71998691558838</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65647125244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78747177124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94229030609131</t>
+    <t xml:space="preserve">4.65647077560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78747224807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94228982925415</t>
   </si>
   <si>
     <t xml:space="preserve">4.69219875335693</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6048641204834</t>
+    <t xml:space="preserve">4.60486459732056</t>
   </si>
   <si>
     <t xml:space="preserve">4.6366229057312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61677408218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2515606880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22774267196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53341007232666</t>
+    <t xml:space="preserve">4.616774559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25155973434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22774314880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5334095954895</t>
   </si>
   <si>
     <t xml:space="preserve">4.45798540115356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47783422470093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49768257141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51356172561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4460768699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62868309020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59295558929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51753187179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5453200340271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32698535919189</t>
+    <t xml:space="preserve">4.47783470153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49768304824829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5135612487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44607734680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62868356704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59295701980591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5175313949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54531955718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32698583602905</t>
   </si>
   <si>
     <t xml:space="preserve">4.03322601318359</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02925682067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27934980392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22377300262451</t>
+    <t xml:space="preserve">4.02925729751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2793493270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22377252578735</t>
   </si>
   <si>
     <t xml:space="preserve">4.38256120681763</t>
@@ -140,19 +140,19 @@
     <t xml:space="preserve">4.46592426300049</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48577356338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48974275588989</t>
+    <t xml:space="preserve">4.48577404022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48974323272705</t>
   </si>
   <si>
     <t xml:space="preserve">4.271409034729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23965167999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43813753128052</t>
+    <t xml:space="preserve">4.23965215682983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43813705444336</t>
   </si>
   <si>
     <t xml:space="preserve">4.5651683807373</t>
@@ -167,37 +167,37 @@
     <t xml:space="preserve">4.58898687362671</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50562286376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52547168731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38653135299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43019819259644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40240955352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29125785827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12056064605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09674263000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06498432159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08880233764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15628671646118</t>
+    <t xml:space="preserve">4.50562238693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52547121047974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38653039932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43019771575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40241098403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29125738143921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12056016921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09674215316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06498527526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08880281448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15628719329834</t>
   </si>
   <si>
     <t xml:space="preserve">4.21186399459839</t>
@@ -206,46 +206,46 @@
     <t xml:space="preserve">4.04910516738892</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02131748199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31110620498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16422700881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23568201065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50959205627441</t>
+    <t xml:space="preserve">4.02131795883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31110763549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16422748565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23568248748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50959157943726</t>
   </si>
   <si>
     <t xml:space="preserve">4.7358660697937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54928970336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50165224075317</t>
+    <t xml:space="preserve">4.54928922653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50165319442749</t>
   </si>
   <si>
     <t xml:space="preserve">4.56119775772095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48180437088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5215015411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55325937271118</t>
+    <t xml:space="preserve">4.48180389404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52150201797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55325889587402</t>
   </si>
   <si>
     <t xml:space="preserve">4.5413498878479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56913805007935</t>
+    <t xml:space="preserve">4.56913757324219</t>
   </si>
   <si>
     <t xml:space="preserve">4.5373797416687</t>
@@ -254,19 +254,19 @@
     <t xml:space="preserve">4.64853191375732</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7041072845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84304761886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89068460464478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81525993347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87877511978149</t>
+    <t xml:space="preserve">4.70410823822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84304809570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89068412780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81525945663452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87877607345581</t>
   </si>
   <si>
     <t xml:space="preserve">4.91053295135498</t>
@@ -275,34 +275,34 @@
     <t xml:space="preserve">4.75968408584595</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73826789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76678800582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90123510360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7341947555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56715393066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51826286315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47344636917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47752046585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48974418640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63233995437622</t>
+    <t xml:space="preserve">4.73826837539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7667875289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90123558044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73419427871704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5671534538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51826333999634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4734468460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47752094268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48974370956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63233947753906</t>
   </si>
   <si>
     <t xml:space="preserve">4.61196899414062</t>
@@ -311,82 +311,82 @@
     <t xml:space="preserve">4.55085563659668</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51418876647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33085012435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94706320762634</t>
+    <t xml:space="preserve">4.51418924331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33085060119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94706273078918</t>
   </si>
   <si>
     <t xml:space="preserve">4.13529014587402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24529361724854</t>
+    <t xml:space="preserve">4.24529314041138</t>
   </si>
   <si>
     <t xml:space="preserve">4.26566314697266</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30233192443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2575159072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11084461212158</t>
+    <t xml:space="preserve">4.30233144760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25751543045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11084413528442</t>
   </si>
   <si>
     <t xml:space="preserve">4.09047412872314</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05299139022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18825387954712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16380929946899</t>
+    <t xml:space="preserve">4.05299091339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18825340270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16380882263184</t>
   </si>
   <si>
     <t xml:space="preserve">4.15566062927246</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15973472595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10677099227905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04321336746216</t>
+    <t xml:space="preserve">4.15973520278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10677051544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04321384429932</t>
   </si>
   <si>
     <t xml:space="preserve">4.11899280548096</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16788291931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26158905029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20047760009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20862483978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23307037353516</t>
+    <t xml:space="preserve">4.16788339614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26158952713013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20047664642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20862531661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.233069896698</t>
   </si>
   <si>
     <t xml:space="preserve">4.37159252166748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36751890182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28603410720825</t>
+    <t xml:space="preserve">4.36751842498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28603458404541</t>
   </si>
   <si>
     <t xml:space="preserve">4.27788639068604</t>
@@ -407,31 +407,31 @@
     <t xml:space="preserve">4.0725474357605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17195749282837</t>
+    <t xml:space="preserve">4.17195796966553</t>
   </si>
   <si>
     <t xml:space="preserve">4.19232797622681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10269689559937</t>
+    <t xml:space="preserve">4.10269641876221</t>
   </si>
   <si>
     <t xml:space="preserve">4.04158353805542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13936376571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09862232208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00084257125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99269342422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03343534469604</t>
+    <t xml:space="preserve">4.13936424255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09862327575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00084209442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99269366264343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0334358215332</t>
   </si>
   <si>
     <t xml:space="preserve">4.19640254974365</t>
@@ -440,13 +440,13 @@
     <t xml:space="preserve">4.15158700942993</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08640003204346</t>
+    <t xml:space="preserve">4.0863995552063</t>
   </si>
   <si>
     <t xml:space="preserve">4.0611400604248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35936975479126</t>
+    <t xml:space="preserve">4.3593692779541</t>
   </si>
   <si>
     <t xml:space="preserve">4.37566661834717</t>
@@ -455,76 +455,76 @@
     <t xml:space="preserve">4.44085359573364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41233396530151</t>
+    <t xml:space="preserve">4.41233348846436</t>
   </si>
   <si>
     <t xml:space="preserve">4.31862783432007</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31047916412354</t>
+    <t xml:space="preserve">4.31047868728638</t>
   </si>
   <si>
     <t xml:space="preserve">4.31455326080322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26973819732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21677350997925</t>
+    <t xml:space="preserve">4.2697377204895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21677303314209</t>
   </si>
   <si>
     <t xml:space="preserve">4.1801061630249</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14343786239624</t>
+    <t xml:space="preserve">4.1434383392334</t>
   </si>
   <si>
     <t xml:space="preserve">4.11491870880127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07417774200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06928825378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08232593536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06439971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00573110580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96010041236877</t>
+    <t xml:space="preserve">4.07417821884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06928873062134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08232545852661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06439876556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00573062896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9601001739502</t>
   </si>
   <si>
     <t xml:space="preserve">4.05462121963501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13121557235718</t>
+    <t xml:space="preserve">4.13121604919434</t>
   </si>
   <si>
     <t xml:space="preserve">4.04647254943848</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98128509521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00410175323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9861752986908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02528762817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97476696968079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02365684509277</t>
+    <t xml:space="preserve">3.98128581047058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00410127639771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98617506027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02528667449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97476673126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02365732192993</t>
   </si>
   <si>
     <t xml:space="preserve">4.05950975418091</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">4.04810237884521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05136251449585</t>
+    <t xml:space="preserve">4.05136156082153</t>
   </si>
   <si>
     <t xml:space="preserve">3.97965669631958</t>
@@ -542,10 +542,10 @@
     <t xml:space="preserve">4.03017568588257</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02039813995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99921154975891</t>
+    <t xml:space="preserve">4.02039861679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99921202659607</t>
   </si>
   <si>
     <t xml:space="preserve">4.07825183868408</t>
@@ -554,16 +554,16 @@
     <t xml:space="preserve">4.14751291275024</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23714399337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20455121994019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22492218017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01713848114014</t>
+    <t xml:space="preserve">4.23714447021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20455074310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22492170333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01713800430298</t>
   </si>
   <si>
     <t xml:space="preserve">4.02202749252319</t>
@@ -572,16 +572,16 @@
     <t xml:space="preserve">3.93076610565186</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91283941268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89491295814514</t>
+    <t xml:space="preserve">3.91283965110779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8949134349823</t>
   </si>
   <si>
     <t xml:space="preserve">3.87535738945007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94054460525513</t>
+    <t xml:space="preserve">3.94054484367371</t>
   </si>
   <si>
     <t xml:space="preserve">3.93402552604675</t>
@@ -590,28 +590,28 @@
     <t xml:space="preserve">3.89654350280762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95521068572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00247192382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37974119186401</t>
+    <t xml:space="preserve">3.95521116256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00247240066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37974071502686</t>
   </si>
   <si>
     <t xml:space="preserve">4.38381433486938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39196395874023</t>
+    <t xml:space="preserve">4.39196348190308</t>
   </si>
   <si>
     <t xml:space="preserve">4.35529565811157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2901086807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28196048736572</t>
+    <t xml:space="preserve">4.29010820388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28195953369141</t>
   </si>
   <si>
     <t xml:space="preserve">4.3267765045166</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">4.29418325424194</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33899879455566</t>
+    <t xml:space="preserve">4.33899927139282</t>
   </si>
   <si>
     <t xml:space="preserve">4.33492469787598</t>
@@ -629,22 +629,22 @@
     <t xml:space="preserve">4.34307336807251</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46529817581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48159503936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40825939178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53863334655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55493068695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52641105651855</t>
+    <t xml:space="preserve">4.46529865264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48159456253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40825986862183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53863382339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55493021011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52641153335571</t>
   </si>
   <si>
     <t xml:space="preserve">4.5060396194458</t>
@@ -656,52 +656,52 @@
     <t xml:space="preserve">4.59567213058472</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68530464172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67308139801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60381984710693</t>
+    <t xml:space="preserve">4.68530368804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67308187484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60382032394409</t>
   </si>
   <si>
     <t xml:space="preserve">4.70160102844238</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85642004013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8238263130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77493572235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79938077926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74234247207642</t>
+    <t xml:space="preserve">4.85641956329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82382583618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77493524551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7993803024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74234294891357</t>
   </si>
   <si>
     <t xml:space="preserve">4.78308486938477</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72604465484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77901029586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80752992630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86456823348999</t>
+    <t xml:space="preserve">4.72604560852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7790093421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80752944946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86456775665283</t>
   </si>
   <si>
     <t xml:space="preserve">5.04790544509888</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01531171798706</t>
+    <t xml:space="preserve">5.01531219482422</t>
   </si>
   <si>
     <t xml:space="preserve">4.89716100692749</t>
@@ -713,25 +713,25 @@
     <t xml:space="preserve">4.88901329040527</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04383134841919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90530967712402</t>
+    <t xml:space="preserve">5.04383087158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90531015396118</t>
   </si>
   <si>
     <t xml:space="preserve">4.95012521743774</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05198049545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97864532470703</t>
+    <t xml:space="preserve">5.05198097229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97864437103271</t>
   </si>
   <si>
     <t xml:space="preserve">5.03160905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08457374572754</t>
+    <t xml:space="preserve">5.08457326889038</t>
   </si>
   <si>
     <t xml:space="preserve">5.23939228057861</t>
@@ -743,34 +743,34 @@
     <t xml:space="preserve">5.14568567276001</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19457578659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05605459213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0642032623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13346385955811</t>
+    <t xml:space="preserve">5.19457626342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05605411529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06420230865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13346338272095</t>
   </si>
   <si>
     <t xml:space="preserve">5.11716651916504</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25161552429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18235349655151</t>
+    <t xml:space="preserve">5.25161504745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18235492706299</t>
   </si>
   <si>
     <t xml:space="preserve">5.17827987670898</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25568914413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27198457717896</t>
+    <t xml:space="preserve">5.25568866729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27198505401611</t>
   </si>
   <si>
     <t xml:space="preserve">5.17420530319214</t>
@@ -779,64 +779,64 @@
     <t xml:space="preserve">5.16605663299561</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18642807006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10494470596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07235050201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94605207443237</t>
+    <t xml:space="preserve">5.1864275932312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10494518280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07234954833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94605112075806</t>
   </si>
   <si>
     <t xml:space="preserve">5.06827640533447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98679351806641</t>
+    <t xml:space="preserve">4.98679304122925</t>
   </si>
   <si>
     <t xml:space="preserve">5.0369119644165</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36268186569214</t>
+    <t xml:space="preserve">5.3626823425293</t>
   </si>
   <si>
     <t xml:space="preserve">5.39191770553589</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31256341934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27915000915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34597635269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35432863235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32091617584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33762311935425</t>
+    <t xml:space="preserve">5.3125638961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27915048599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34597587585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35432815551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32091665267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33762264251709</t>
   </si>
   <si>
     <t xml:space="preserve">5.27079820632935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27497434616089</t>
+    <t xml:space="preserve">5.27497386932373</t>
   </si>
   <si>
     <t xml:space="preserve">5.1872673034668</t>
   </si>
   <si>
-    <t xml:space="preserve">5.132972240448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2039737701416</t>
+    <t xml:space="preserve">5.13297271728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20397329330444</t>
   </si>
   <si>
     <t xml:space="preserve">5.22903347015381</t>
@@ -845,10 +845,10 @@
     <t xml:space="preserve">5.25409126281738</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2624454498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18309116363525</t>
+    <t xml:space="preserve">5.26244497299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1830906867981</t>
   </si>
   <si>
     <t xml:space="preserve">5.21232652664185</t>
@@ -872,10 +872,10 @@
     <t xml:space="preserve">5.30003356933594</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33344650268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40444660186768</t>
+    <t xml:space="preserve">5.33344697952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40444707870483</t>
   </si>
   <si>
     <t xml:space="preserve">5.37521123886108</t>
@@ -884,31 +884,31 @@
     <t xml:space="preserve">5.40027093887329</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3835654258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37938785552979</t>
+    <t xml:space="preserve">5.38356494903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37938833236694</t>
   </si>
   <si>
     <t xml:space="preserve">5.23320960998535</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3083872795105</t>
+    <t xml:space="preserve">5.30838775634766</t>
   </si>
   <si>
     <t xml:space="preserve">5.2582688331604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20814990997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1371488571167</t>
+    <t xml:space="preserve">5.2081503868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13714933395386</t>
   </si>
   <si>
     <t xml:space="preserve">5.11208963394165</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15385484695435</t>
+    <t xml:space="preserve">5.1538553237915</t>
   </si>
   <si>
     <t xml:space="preserve">5.23738574981689</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">5.32509279251099</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30421018600464</t>
+    <t xml:space="preserve">5.30420970916748</t>
   </si>
   <si>
     <t xml:space="preserve">5.29585695266724</t>
@@ -926,22 +926,22 @@
     <t xml:space="preserve">5.32926940917969</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48797845840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5380973815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59656810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62580394744873</t>
+    <t xml:space="preserve">5.48797798156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53809690475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5965690612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62580347061157</t>
   </si>
   <si>
     <t xml:space="preserve">5.68845272064209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61327457427979</t>
+    <t xml:space="preserve">5.61327505111694</t>
   </si>
   <si>
     <t xml:space="preserve">5.57568550109863</t>
@@ -950,10 +950,10 @@
     <t xml:space="preserve">5.44203615188599</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62162780761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68009853363037</t>
+    <t xml:space="preserve">5.62162733078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68009901046753</t>
   </si>
   <si>
     <t xml:space="preserve">5.64251089096069</t>
@@ -962,13 +962,13 @@
     <t xml:space="preserve">5.37103509902954</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39609384536743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38774156570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24156188964844</t>
+    <t xml:space="preserve">5.39609336853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38774108886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2415623664856</t>
   </si>
   <si>
     <t xml:space="preserve">5.29168033599854</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">5.0828537940979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88655662536621</t>
+    <t xml:space="preserve">4.88655614852905</t>
   </si>
   <si>
     <t xml:space="preserve">4.90743923187256</t>
@@ -989,16 +989,16 @@
     <t xml:space="preserve">4.81973171234131</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80302572250366</t>
+    <t xml:space="preserve">4.8030252456665</t>
   </si>
   <si>
     <t xml:space="preserve">4.84478950500488</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8364372253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94502782821655</t>
+    <t xml:space="preserve">4.83643770217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94502735137939</t>
   </si>
   <si>
     <t xml:space="preserve">4.90326261520386</t>
@@ -1007,13 +1007,13 @@
     <t xml:space="preserve">4.86567354202271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87820291519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85314416885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81137752532959</t>
+    <t xml:space="preserve">4.87820339202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8531436920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81137800216675</t>
   </si>
   <si>
     <t xml:space="preserve">4.95755767822266</t>
@@ -1028,19 +1028,19 @@
     <t xml:space="preserve">4.861496925354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83226108551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72367000579834</t>
+    <t xml:space="preserve">4.83226156234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7236704826355</t>
   </si>
   <si>
     <t xml:space="preserve">4.66102313995361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69861030578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66937589645386</t>
+    <t xml:space="preserve">4.69861078262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6693754196167</t>
   </si>
   <si>
     <t xml:space="preserve">4.63596391677856</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">4.7904953956604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74873018264771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73202323913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71114110946655</t>
+    <t xml:space="preserve">4.74872970581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7320237159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71114063262939</t>
   </si>
   <si>
     <t xml:space="preserve">4.67772912979126</t>
@@ -1076,10 +1076,10 @@
     <t xml:space="preserve">4.9157919883728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92414426803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8949089050293</t>
+    <t xml:space="preserve">4.92414474487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89490842819214</t>
   </si>
   <si>
     <t xml:space="preserve">4.84061431884766</t>
@@ -1091,10 +1091,10 @@
     <t xml:space="preserve">4.99932241439819</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02020502090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17056083679199</t>
+    <t xml:space="preserve">5.0202054977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17056035995483</t>
   </si>
   <si>
     <t xml:space="preserve">5.09955930709839</t>
@@ -1103,10 +1103,10 @@
     <t xml:space="preserve">4.95338153839111</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78631973266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68608093261719</t>
+    <t xml:space="preserve">4.78631925582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68608140945435</t>
   </si>
   <si>
     <t xml:space="preserve">4.60672760009766</t>
@@ -1115,34 +1115,34 @@
     <t xml:space="preserve">4.59419775009155</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61508131027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63178682327271</t>
+    <t xml:space="preserve">4.6150803565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63178730010986</t>
   </si>
   <si>
     <t xml:space="preserve">4.70696496963501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58584451675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55243253707886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5399022102356</t>
+    <t xml:space="preserve">4.58584499359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55243301391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53990316390991</t>
   </si>
   <si>
     <t xml:space="preserve">4.57749176025391</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48978471755981</t>
+    <t xml:space="preserve">4.48978424072266</t>
   </si>
   <si>
     <t xml:space="preserve">4.41043043136597</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44384241104126</t>
+    <t xml:space="preserve">4.4438419342041</t>
   </si>
   <si>
     <t xml:space="preserve">4.4939603805542</t>
@@ -1157,25 +1157,25 @@
     <t xml:space="preserve">4.5691385269165</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59002113342285</t>
+    <t xml:space="preserve">4.59002161026001</t>
   </si>
   <si>
     <t xml:space="preserve">4.65684604644775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64849281311035</t>
+    <t xml:space="preserve">4.64849233627319</t>
   </si>
   <si>
     <t xml:space="preserve">4.59837436676025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5607852935791</t>
+    <t xml:space="preserve">4.56078577041626</t>
   </si>
   <si>
     <t xml:space="preserve">4.48560810089111</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4396653175354</t>
+    <t xml:space="preserve">4.43966579437256</t>
   </si>
   <si>
     <t xml:space="preserve">4.36031150817871</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">4.16150760650635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15148401260376</t>
+    <t xml:space="preserve">4.15148448944092</t>
   </si>
   <si>
     <t xml:space="preserve">4.15649604797363</t>
@@ -1199,19 +1199,19 @@
     <t xml:space="preserve">4.19324970245361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09802484512329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15315532684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10303640365601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12642526626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16986083984375</t>
+    <t xml:space="preserve">4.09802436828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1531548500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10303688049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12642478942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16986131668091</t>
   </si>
   <si>
     <t xml:space="preserve">4.17654418945312</t>
@@ -1223,13 +1223,13 @@
     <t xml:space="preserve">4.16819047927856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83002591133118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90687417984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84339070320129</t>
+    <t xml:space="preserve">2.8300256729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90687441825867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84339094161987</t>
   </si>
   <si>
     <t xml:space="preserve">2.87179136276245</t>
@@ -1238,10 +1238,10 @@
     <t xml:space="preserve">2.89350914955139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80162477493286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92358040809631</t>
+    <t xml:space="preserve">2.80162501335144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92358064651489</t>
   </si>
   <si>
     <t xml:space="preserve">2.94863986968994</t>
@@ -1250,16 +1250,16 @@
     <t xml:space="preserve">3.01713514328003</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08061861991882</t>
+    <t xml:space="preserve">3.08061838150024</t>
   </si>
   <si>
     <t xml:space="preserve">3.17083144187927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14911365509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15746665000916</t>
+    <t xml:space="preserve">3.14911389350891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15746712684631</t>
   </si>
   <si>
     <t xml:space="preserve">3.14410161972046</t>
@@ -1268,7 +1268,7 @@
     <t xml:space="preserve">3.17918515205383</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17417335510254</t>
+    <t xml:space="preserve">3.17417311668396</t>
   </si>
   <si>
     <t xml:space="preserve">3.10400748252869</t>
@@ -1280,25 +1280,25 @@
     <t xml:space="preserve">3.02882981300354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94529819488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95699262619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89852142333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84004878997803</t>
+    <t xml:space="preserve">2.94529795646667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95699286460876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89852118492126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84004902839661</t>
   </si>
   <si>
     <t xml:space="preserve">2.82501363754272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85007333755493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74649524688721</t>
+    <t xml:space="preserve">2.85007309913635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74649500846863</t>
   </si>
   <si>
     <t xml:space="preserve">2.55771470069885</t>
@@ -1316,13 +1316,13 @@
     <t xml:space="preserve">2.5009138584137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51594996452332</t>
+    <t xml:space="preserve">2.51594972610474</t>
   </si>
   <si>
     <t xml:space="preserve">2.50592589378357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47919583320618</t>
+    <t xml:space="preserve">2.47919607162476</t>
   </si>
   <si>
     <t xml:space="preserve">2.41905355453491</t>
@@ -1331,7 +1331,7 @@
     <t xml:space="preserve">2.39566540718079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36058211326599</t>
+    <t xml:space="preserve">2.36058235168457</t>
   </si>
   <si>
     <t xml:space="preserve">2.36726474761963</t>
@@ -1340,10 +1340,10 @@
     <t xml:space="preserve">2.3772885799408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27538061141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31380534172058</t>
+    <t xml:space="preserve">2.2753803730011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.313805103302</t>
   </si>
   <si>
     <t xml:space="preserve">2.2620153427124</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">2.41404247283936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38062953948975</t>
+    <t xml:space="preserve">2.38062930107117</t>
   </si>
   <si>
     <t xml:space="preserve">2.30043959617615</t>
@@ -1370,13 +1370,13 @@
     <t xml:space="preserve">2.32382845878601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33552289009094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35389995574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36559414863586</t>
+    <t xml:space="preserve">2.33552265167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35389971733093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36559438705444</t>
   </si>
   <si>
     <t xml:space="preserve">2.35055828094482</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">2.35222935676575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35557007789612</t>
+    <t xml:space="preserve">2.35556983947754</t>
   </si>
   <si>
     <t xml:space="preserve">2.25533318519592</t>
@@ -1403,19 +1403,19 @@
     <t xml:space="preserve">2.23027372360229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40067672729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44912481307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42406558990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31881666183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30879354476929</t>
+    <t xml:space="preserve">2.40067648887634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44912457466125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42406535148621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31881642341614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30879330635071</t>
   </si>
   <si>
     <t xml:space="preserve">2.34387588500977</t>
@@ -1427,19 +1427,19 @@
     <t xml:space="preserve">2.27371001243591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18850898742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17681455612183</t>
+    <t xml:space="preserve">2.18850874900818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17681431770325</t>
   </si>
   <si>
     <t xml:space="preserve">2.15342569351196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21022629737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21189713478088</t>
+    <t xml:space="preserve">2.21022653579712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2118968963623</t>
   </si>
   <si>
     <t xml:space="preserve">2.05485892295837</t>
@@ -1448,13 +1448,13 @@
     <t xml:space="preserve">2.01142263412476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97466909885406</t>
+    <t xml:space="preserve">1.97466933727264</t>
   </si>
   <si>
     <t xml:space="preserve">2.00474047660828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03815364837646</t>
+    <t xml:space="preserve">2.03815340995789</t>
   </si>
   <si>
     <t xml:space="preserve">2.1517550945282</t>
@@ -1463,7 +1463,7 @@
     <t xml:space="preserve">2.17180252075195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18182587623596</t>
+    <t xml:space="preserve">2.18182563781738</t>
   </si>
   <si>
     <t xml:space="preserve">2.16679048538208</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">2.16846084594727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15509629249573</t>
+    <t xml:space="preserve">2.15509581565857</t>
   </si>
   <si>
     <t xml:space="preserve">2.15676641464233</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">2.1150016784668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07657766342163</t>
+    <t xml:space="preserve">2.07657742500305</t>
   </si>
   <si>
     <t xml:space="preserve">2.08994221687317</t>
@@ -1502,40 +1502,40 @@
     <t xml:space="preserve">2.02478766441345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02645921707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12502431869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23695611953735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18683767318726</t>
+    <t xml:space="preserve">2.02645874023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12502455711365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23695635795593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18683791160583</t>
   </si>
   <si>
     <t xml:space="preserve">2.11834216117859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06989526748657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06321263313293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00139951705933</t>
+    <t xml:space="preserve">2.06989502906799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06321239471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00139975547791</t>
   </si>
   <si>
     <t xml:space="preserve">1.9997284412384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98302268981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94626927375793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87610352039337</t>
+    <t xml:space="preserve">1.98302292823792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94626903533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8761031627655</t>
   </si>
   <si>
     <t xml:space="preserve">1.75748944282532</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">1.48601388931274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39663577079773</t>
+    <t xml:space="preserve">1.39663565158844</t>
   </si>
   <si>
     <t xml:space="preserve">1.31728148460388</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">1.28553974628448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27133929729462</t>
+    <t xml:space="preserve">1.27133941650391</t>
   </si>
   <si>
     <t xml:space="preserve">1.24962174892426</t>
@@ -1577,22 +1577,22 @@
     <t xml:space="preserve">1.24460971355438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2897162437439</t>
+    <t xml:space="preserve">1.28971612453461</t>
   </si>
   <si>
     <t xml:space="preserve">1.27635133266449</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30391657352448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3156111240387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31310498714447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28386926651001</t>
+    <t xml:space="preserve">1.30391645431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31561100482941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31310486793518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2838693857193</t>
   </si>
   <si>
     <t xml:space="preserve">1.27969288825989</t>
@@ -1604,70 +1604,70 @@
     <t xml:space="preserve">1.35152912139893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29472827911377</t>
+    <t xml:space="preserve">1.29472815990448</t>
   </si>
   <si>
     <t xml:space="preserve">1.29639852046967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24293923377991</t>
+    <t xml:space="preserve">1.2429393529892</t>
   </si>
   <si>
     <t xml:space="preserve">1.25212776660919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26799857616425</t>
+    <t xml:space="preserve">1.26799845695496</t>
   </si>
   <si>
     <t xml:space="preserve">1.25296247005463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23375082015991</t>
+    <t xml:space="preserve">1.23375070095062</t>
   </si>
   <si>
     <t xml:space="preserve">1.25630402565002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2579745054245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26048040390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36823570728302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36990606784821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36405909061432</t>
+    <t xml:space="preserve">1.25797438621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26048052310944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36823558807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36990582942963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36405920982361</t>
   </si>
   <si>
     <t xml:space="preserve">1.34568238258362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31477546691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34484672546387</t>
+    <t xml:space="preserve">1.31477534770966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34484684467316</t>
   </si>
   <si>
     <t xml:space="preserve">1.25129199028015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23876285552979</t>
+    <t xml:space="preserve">1.23876297473907</t>
   </si>
   <si>
     <t xml:space="preserve">1.06835901737213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962275326251984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989840507507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.633163213729858</t>
+    <t xml:space="preserve">0.962275266647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989840626716614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.633163273334503</t>
   </si>
   <si>
     <t xml:space="preserve">0.703329861164093</t>
@@ -1679,7 +1679,7 @@
     <t xml:space="preserve">0.862038254737854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958098828792572</t>
+    <t xml:space="preserve">0.958098888397217</t>
   </si>
   <si>
     <t xml:space="preserve">0.948074817657471</t>
@@ -1688,16 +1688,16 @@
     <t xml:space="preserve">0.848673403263092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.913827180862427</t>
+    <t xml:space="preserve">0.913827061653137</t>
   </si>
   <si>
     <t xml:space="preserve">0.9447340965271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.91883909702301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917168796062469</t>
+    <t xml:space="preserve">0.9188392162323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917168915271759</t>
   </si>
   <si>
     <t xml:space="preserve">1.00487577915192</t>
@@ -1724,7 +1724,7 @@
     <t xml:space="preserve">1.01155817508698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01824057102203</t>
+    <t xml:space="preserve">1.01824069023132</t>
   </si>
   <si>
     <t xml:space="preserve">0.999029040336609</t>
@@ -1733,37 +1733,37 @@
     <t xml:space="preserve">1.01573550701141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01322960853577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08255958557129</t>
+    <t xml:space="preserve">1.01322937011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08255970478058</t>
   </si>
   <si>
     <t xml:space="preserve">1.10177206993103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1276661157608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12933743000031</t>
+    <t xml:space="preserve">1.12766623497009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12933754920959</t>
   </si>
   <si>
     <t xml:space="preserve">1.13017213344574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13685464859009</t>
+    <t xml:space="preserve">1.1368545293808</t>
   </si>
   <si>
     <t xml:space="preserve">1.11346650123596</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10260689258575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06585311889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0324410200119</t>
+    <t xml:space="preserve">1.10260677337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06585323810577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03244113922119</t>
   </si>
   <si>
     <t xml:space="preserve">1.07086515426636</t>
@@ -1775,49 +1775,49 @@
     <t xml:space="preserve">1.01907634735107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03494715690613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06501829624176</t>
+    <t xml:space="preserve">1.03494703769684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06501853466034</t>
   </si>
   <si>
     <t xml:space="preserve">1.12850177288055</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08506560325623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08673584461212</t>
+    <t xml:space="preserve">1.08506572246552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08673596382141</t>
   </si>
   <si>
     <t xml:space="preserve">1.07253646850586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08088934421539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10511267185211</t>
+    <t xml:space="preserve">1.08088910579681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1051127910614</t>
   </si>
   <si>
     <t xml:space="preserve">1.07838320732117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10010075569153</t>
+    <t xml:space="preserve">1.10010087490082</t>
   </si>
   <si>
     <t xml:space="preserve">1.11263084411621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11012482643127</t>
+    <t xml:space="preserve">1.11012506484985</t>
   </si>
   <si>
     <t xml:space="preserve">1.2262327671051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46179020404816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41584813594818</t>
+    <t xml:space="preserve">1.46179032325745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41584801673889</t>
   </si>
   <si>
     <t xml:space="preserve">1.414177775383</t>
@@ -1832,7 +1832,7 @@
     <t xml:space="preserve">1.29806983470917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3732476234436</t>
+    <t xml:space="preserve">1.37324750423431</t>
   </si>
   <si>
     <t xml:space="preserve">1.38744723796844</t>
@@ -1841,10 +1841,10 @@
     <t xml:space="preserve">1.32981145381927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35069346427917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35487067699432</t>
+    <t xml:space="preserve">1.35069358348846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35487079620361</t>
   </si>
   <si>
     <t xml:space="preserve">1.32897591590881</t>
@@ -1853,19 +1853,19 @@
     <t xml:space="preserve">1.36572957038879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37157654762268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40248322486877</t>
+    <t xml:space="preserve">1.37157642841339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40248310565948</t>
   </si>
   <si>
     <t xml:space="preserve">1.41918885707855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42169487476349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42253041267395</t>
+    <t xml:space="preserve">1.42169499397278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42253053188324</t>
   </si>
   <si>
     <t xml:space="preserve">1.42837715148926</t>
@@ -1877,34 +1877,34 @@
     <t xml:space="preserve">1.37575268745422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3941296339035</t>
+    <t xml:space="preserve">1.39412951469421</t>
   </si>
   <si>
     <t xml:space="preserve">1.45343661308289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43589556217194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52861440181732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61131024360657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59710991382599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59376919269562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57455658912659</t>
+    <t xml:space="preserve">1.43589532375336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52861428260803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61131012439728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5971097946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59376907348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5745564699173</t>
   </si>
   <si>
     <t xml:space="preserve">1.55283892154694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55116760730743</t>
+    <t xml:space="preserve">1.55116748809814</t>
   </si>
   <si>
     <t xml:space="preserve">1.51441490650177</t>
@@ -1919,16 +1919,16 @@
     <t xml:space="preserve">1.43422496318817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3882828950882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38327074050903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33231675624847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36739993095398</t>
+    <t xml:space="preserve">1.38828301429749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38327062129974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33231663703918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36740005016327</t>
   </si>
   <si>
     <t xml:space="preserve">1.34985876083374</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">1.30308091640472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32229340076447</t>
+    <t xml:space="preserve">1.32229351997375</t>
   </si>
   <si>
     <t xml:space="preserve">1.31644582748413</t>
@@ -1949,31 +1949,31 @@
     <t xml:space="preserve">1.30892872810364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31059896945953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31895196437836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29222238063812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28721022605896</t>
+    <t xml:space="preserve">1.31059908866882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31895184516907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29222226142883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28721010684967</t>
   </si>
   <si>
     <t xml:space="preserve">1.25045645236969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32730555534363</t>
+    <t xml:space="preserve">1.32730543613434</t>
   </si>
   <si>
     <t xml:space="preserve">1.31143462657928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31978726387024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34902310371399</t>
+    <t xml:space="preserve">1.31978738307953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3490229845047</t>
   </si>
   <si>
     <t xml:space="preserve">1.34651708602905</t>
@@ -1982,28 +1982,28 @@
     <t xml:space="preserve">1.30725836753845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26215064525604</t>
+    <t xml:space="preserve">1.26215088367462</t>
   </si>
   <si>
     <t xml:space="preserve">1.26883316040039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22205626964569</t>
+    <t xml:space="preserve">1.22205638885498</t>
   </si>
   <si>
     <t xml:space="preserve">1.19198513031006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35821163654327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32312917709351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28219890594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24043309688568</t>
+    <t xml:space="preserve">1.35821151733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32312905788422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28219902515411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24043321609497</t>
   </si>
   <si>
     <t xml:space="preserve">1.27384531497955</t>
@@ -2012,16 +2012,16 @@
     <t xml:space="preserve">1.26131618022919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32646989822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33816421031952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42503666877747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48183727264404</t>
+    <t xml:space="preserve">1.32646977901459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33816409111023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42503654956818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48183739185333</t>
   </si>
   <si>
     <t xml:space="preserve">1.49603796005249</t>
@@ -2033,61 +2033,61 @@
     <t xml:space="preserve">1.50355505943298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54448521137238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56369757652283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53863835334778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5486626625061</t>
+    <t xml:space="preserve">1.54448533058167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56369769573212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53863847255707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54866242408752</t>
   </si>
   <si>
     <t xml:space="preserve">1.49186062812805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41668307781219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39329493045807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39078891277313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42002439498901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37491798400879</t>
+    <t xml:space="preserve">1.41668295860291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39329481124878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39078879356384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4200245141983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37491810321808</t>
   </si>
   <si>
     <t xml:space="preserve">1.34818828105927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33148193359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32814025878906</t>
+    <t xml:space="preserve">1.33148205280304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32814037799835</t>
   </si>
   <si>
     <t xml:space="preserve">1.29723429679871</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29974019527435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30224621295929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33315217494965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26549243927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24210357666016</t>
+    <t xml:space="preserve">1.29974031448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30224609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33315229415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26549255847931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24210369586945</t>
   </si>
   <si>
     <t xml:space="preserve">1.38995337486267</t>
@@ -2099,37 +2099,37 @@
     <t xml:space="preserve">1.38494122028351</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38911855220795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37993013858795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45260190963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48851990699768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49687278270721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50104892253876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44758987426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39914166927338</t>
+    <t xml:space="preserve">1.38911867141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37993001937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45260179042816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48852002620697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49687266349792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50104904174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.447589635849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39914178848267</t>
   </si>
   <si>
     <t xml:space="preserve">1.54281485080719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4609546661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39162373542786</t>
+    <t xml:space="preserve">1.46095454692841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39162361621857</t>
   </si>
   <si>
     <t xml:space="preserve">1.41000056266785</t>
@@ -2141,25 +2141,25 @@
     <t xml:space="preserve">1.42921280860901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40749442577362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33398807048798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32563424110413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33732879161835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36155307292938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36907041072845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44508373737335</t>
+    <t xml:space="preserve">1.40749454498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3339878320694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32563412189484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33732867240906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36155319213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36907029151917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44508385658264</t>
   </si>
   <si>
     <t xml:space="preserve">1.4350597858429</t>
@@ -2168,34 +2168,34 @@
     <t xml:space="preserve">1.46596658229828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47181344032288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46513092517853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47264909744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51190876960754</t>
+    <t xml:space="preserve">1.47181332111359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46513104438782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47264897823334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51190888881683</t>
   </si>
   <si>
     <t xml:space="preserve">1.47014307975769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4926962852478</t>
+    <t xml:space="preserve">1.49269616603851</t>
   </si>
   <si>
     <t xml:space="preserve">1.52276766300201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54030883312225</t>
+    <t xml:space="preserve">1.54030871391296</t>
   </si>
   <si>
     <t xml:space="preserve">1.53529691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59794545173645</t>
+    <t xml:space="preserve">1.59794533252716</t>
   </si>
   <si>
     <t xml:space="preserve">1.60629820823669</t>
@@ -2204,10 +2204,10 @@
     <t xml:space="preserve">1.58625102043152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64555776119232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59293341636658</t>
+    <t xml:space="preserve">1.64555788040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59293329715729</t>
   </si>
   <si>
     <t xml:space="preserve">1.63219308853149</t>
@@ -2228,10 +2228,10 @@
     <t xml:space="preserve">1.56620359420776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56703841686249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58708667755127</t>
+    <t xml:space="preserve">1.56703853607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58708655834198</t>
   </si>
   <si>
     <t xml:space="preserve">1.64973437786102</t>
@@ -2249,10 +2249,10 @@
     <t xml:space="preserve">1.72908842563629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71238303184509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73243033885956</t>
+    <t xml:space="preserve">1.7123829126358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73243021965027</t>
   </si>
   <si>
     <t xml:space="preserve">1.69233477115631</t>
@@ -2261,13 +2261,13 @@
     <t xml:space="preserve">1.76584219932556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74913573265076</t>
+    <t xml:space="preserve">1.74913585186005</t>
   </si>
   <si>
     <t xml:space="preserve">1.72073566913605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63887548446655</t>
+    <t xml:space="preserve">1.63887560367584</t>
   </si>
   <si>
     <t xml:space="preserve">1.60880410671234</t>
@@ -2282,19 +2282,19 @@
     <t xml:space="preserve">1.68732368946075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67562925815582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68064117431641</t>
+    <t xml:space="preserve">1.67562913894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68064105510712</t>
   </si>
   <si>
     <t xml:space="preserve">1.61715698242188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61548674106598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62467515468597</t>
+    <t xml:space="preserve">1.61548662185669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62467503547668</t>
   </si>
   <si>
     <t xml:space="preserve">1.61047458648682</t>
@@ -2303,28 +2303,28 @@
     <t xml:space="preserve">1.64054584503174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62383937835693</t>
+    <t xml:space="preserve">1.62383961677551</t>
   </si>
   <si>
     <t xml:space="preserve">1.60963988304138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57789814472198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59126317501068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56202733516693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59209764003754</t>
+    <t xml:space="preserve">1.57789826393127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5912629365921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56202721595764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59209775924683</t>
   </si>
   <si>
     <t xml:space="preserve">1.59543943405151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58290934562683</t>
+    <t xml:space="preserve">1.58290922641754</t>
   </si>
   <si>
     <t xml:space="preserve">1.60379207134247</t>
@@ -2336,34 +2336,34 @@
     <t xml:space="preserve">1.58541524410248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54532074928284</t>
+    <t xml:space="preserve">1.54532086849213</t>
   </si>
   <si>
     <t xml:space="preserve">1.54699122905731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57706248760223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43756568431854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49436664581299</t>
+    <t xml:space="preserve">1.57706260681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43756556510925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4943665266037</t>
   </si>
   <si>
     <t xml:space="preserve">1.48935568332672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46763706207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51274359226227</t>
+    <t xml:space="preserve">1.46763718128204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51274371147156</t>
   </si>
   <si>
     <t xml:space="preserve">1.52610838413239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53195607662201</t>
+    <t xml:space="preserve">1.53195595741272</t>
   </si>
   <si>
     <t xml:space="preserve">1.54782676696777</t>
@@ -2372,7 +2372,7 @@
     <t xml:space="preserve">1.51691997051239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5094028711319</t>
+    <t xml:space="preserve">1.50940263271332</t>
   </si>
   <si>
     <t xml:space="preserve">1.48267209529877</t>
@@ -2387,7 +2387,7 @@
     <t xml:space="preserve">1.18029069900513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16692578792572</t>
+    <t xml:space="preserve">1.16692566871643</t>
   </si>
   <si>
     <t xml:space="preserve">1.13601982593536</t>
@@ -2405,10 +2405,10 @@
     <t xml:space="preserve">0.719200670719147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.695811867713928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.546709179878235</t>
+    <t xml:space="preserve">0.695811808109283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54670923948288</t>
   </si>
   <si>
     <t xml:space="preserve">0.613534212112427</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">0.519561350345612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599333763122559</t>
+    <t xml:space="preserve">0.599333703517914</t>
   </si>
   <si>
     <t xml:space="preserve">0.674928903579712</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">0.725047409534454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.701658606529236</t>
+    <t xml:space="preserve">0.701658487319946</t>
   </si>
   <si>
     <t xml:space="preserve">0.637340486049652</t>
@@ -2435,22 +2435,22 @@
     <t xml:space="preserve">0.682446956634521</t>
   </si>
   <si>
-    <t xml:space="preserve">0.680358350276947</t>
+    <t xml:space="preserve">0.680358290672302</t>
   </si>
   <si>
     <t xml:space="preserve">0.687876343727112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.65989363193512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643604576587677</t>
+    <t xml:space="preserve">0.659893691539764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.643604516983032</t>
   </si>
   <si>
     <t xml:space="preserve">0.659475445747375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643187165260315</t>
+    <t xml:space="preserve">0.64318722486496</t>
   </si>
   <si>
     <t xml:space="preserve">0.627316415309906</t>
@@ -2459,10 +2459,10 @@
     <t xml:space="preserve">0.576780557632446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618128001689911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.660728514194489</t>
+    <t xml:space="preserve">0.618127942085266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.660728454589844</t>
   </si>
   <si>
     <t xml:space="preserve">0.646528840065002</t>
@@ -2474,31 +2474,31 @@
     <t xml:space="preserve">0.638175189495087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649869620800018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640263915061951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612281203269958</t>
+    <t xml:space="preserve">0.649869680404663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640263795852661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612281143665314</t>
   </si>
   <si>
     <t xml:space="preserve">0.61562192440033</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610192537307739</t>
+    <t xml:space="preserve">0.610192596912384</t>
   </si>
   <si>
     <t xml:space="preserve">0.60559868812561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611028134822845</t>
+    <t xml:space="preserve">0.61102819442749</t>
   </si>
   <si>
     <t xml:space="preserve">0.651540040969849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.676599264144897</t>
+    <t xml:space="preserve">0.676599323749542</t>
   </si>
   <si>
     <t xml:space="preserve">0.654881715774536</t>
@@ -2519,10 +2519,10 @@
     <t xml:space="preserve">0.649034917354584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.668246507644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.65028703212738</t>
+    <t xml:space="preserve">0.668246448040009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.650286972522736</t>
   </si>
   <si>
     <t xml:space="preserve">0.6264808177948</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">0.606016159057617</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629822373390198</t>
+    <t xml:space="preserve">0.629822432994843</t>
   </si>
   <si>
     <t xml:space="preserve">0.596827805042267</t>
@@ -2555,19 +2555,19 @@
     <t xml:space="preserve">0.630658090114594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.726300477981567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78936642408371</t>
+    <t xml:space="preserve">0.726300537586212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789366543292999</t>
   </si>
   <si>
     <t xml:space="preserve">0.763054192066193</t>
   </si>
   <si>
-    <t xml:space="preserve">0.768483579158783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.82779061794281</t>
+    <t xml:space="preserve">0.768483519554138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.827790558338165</t>
   </si>
   <si>
     <t xml:space="preserve">0.83530855178833</t>
@@ -2582,28 +2582,28 @@
     <t xml:space="preserve">1.00571131706238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01072347164154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968957781791687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877909004688263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924685955047607</t>
+    <t xml:space="preserve">1.01072359085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968957722187042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877909064292908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924685895442963</t>
   </si>
   <si>
     <t xml:space="preserve">0.925521671772003</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938051760196686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922180950641632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892109513282776</t>
+    <t xml:space="preserve">0.938051581382751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922180891036987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892109572887421</t>
   </si>
   <si>
     <t xml:space="preserve">0.893779993057251</t>
@@ -2612,10 +2612,10 @@
     <t xml:space="preserve">0.895450294017792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.823614180088043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781013667583466</t>
+    <t xml:space="preserve">0.823614120483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781013607978821</t>
   </si>
   <si>
     <t xml:space="preserve">0.824867188930511</t>
@@ -2624,34 +2624,34 @@
     <t xml:space="preserve">0.806072950363159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.785607516765594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.802313983440399</t>
+    <t xml:space="preserve">0.78560745716095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.802313923835754</t>
   </si>
   <si>
     <t xml:space="preserve">0.797719240188599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801895558834076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798554956912994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77641898393631</t>
+    <t xml:space="preserve">0.801895618438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79855489730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776419043540955</t>
   </si>
   <si>
     <t xml:space="preserve">0.782266676425934</t>
   </si>
   <si>
-    <t xml:space="preserve">0.766394972801208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821525454521179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.795631587505341</t>
+    <t xml:space="preserve">0.766394913196564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821525514125824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.795631468296051</t>
   </si>
   <si>
     <t xml:space="preserve">0.863708555698395</t>
@@ -2660,16 +2660,16 @@
     <t xml:space="preserve">0.855355799198151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.84449702501297</t>
+    <t xml:space="preserve">0.844496965408325</t>
   </si>
   <si>
     <t xml:space="preserve">0.857861816883087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.836143374443054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.834890305995941</t>
+    <t xml:space="preserve">0.836143314838409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834890425205231</t>
   </si>
   <si>
     <t xml:space="preserve">0.838649392127991</t>
@@ -2681,19 +2681,19 @@
     <t xml:space="preserve">0.773912906646729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.789783895015717</t>
+    <t xml:space="preserve">0.789783835411072</t>
   </si>
   <si>
     <t xml:space="preserve">0.77182525396347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.767230570316315</t>
+    <t xml:space="preserve">0.767230629920959</t>
   </si>
   <si>
     <t xml:space="preserve">0.775583386421204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.786860466003418</t>
+    <t xml:space="preserve">0.786860406398773</t>
   </si>
   <si>
     <t xml:space="preserve">0.792707145214081</t>
@@ -2705,10 +2705,10 @@
     <t xml:space="preserve">0.765977621078491</t>
   </si>
   <si>
-    <t xml:space="preserve">0.800642609596252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809831082820892</t>
+    <t xml:space="preserve">0.800642669200897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809831023216248</t>
   </si>
   <si>
     <t xml:space="preserve">0.799807906150818</t>
@@ -2720,10 +2720,10 @@
     <t xml:space="preserve">0.770989596843719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.740918397903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.717947781085968</t>
+    <t xml:space="preserve">0.740918278694153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.717947661876678</t>
   </si>
   <si>
     <t xml:space="preserve">0.712100028991699</t>
@@ -2732,10 +2732,10 @@
     <t xml:space="preserve">0.684117317199707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.69079977273941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.692888379096985</t>
+    <t xml:space="preserve">0.690799713134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69288843870163</t>
   </si>
   <si>
     <t xml:space="preserve">0.685787737369537</t>
@@ -2744,37 +2744,37 @@
     <t xml:space="preserve">0.674094140529633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.666576087474823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.682029545307159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.687458992004395</t>
+    <t xml:space="preserve">0.666576147079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.682029604911804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.687459051609039</t>
   </si>
   <si>
     <t xml:space="preserve">0.685370326042175</t>
   </si>
   <si>
-    <t xml:space="preserve">0.677852272987366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69455873966217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.697482109069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.70374721288681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.698317885398865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.721288502216339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.72045373916626</t>
+    <t xml:space="preserve">0.67785233259201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.694558799266815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.697482168674469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.703747272491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69831782579422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.721288442611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.720453679561615</t>
   </si>
   <si>
     <t xml:space="preserve">0.742588698863983</t>
@@ -2783,10 +2783,10 @@
     <t xml:space="preserve">0.767647981643677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.718365132808685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.715024292469025</t>
+    <t xml:space="preserve">0.718365013599396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.71502423286438</t>
   </si>
   <si>
     <t xml:space="preserve">0.781848430633545</t>
@@ -2795,13 +2795,13 @@
     <t xml:space="preserve">0.757207453250885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778925061225891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79646623134613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825284600257874</t>
+    <t xml:space="preserve">0.778925001621246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796466171741486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825284540653229</t>
   </si>
   <si>
     <t xml:space="preserve">0.850343704223633</t>
@@ -2828,10 +2828,10 @@
     <t xml:space="preserve">0.8545201420784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.812755286693573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80774337053299</t>
+    <t xml:space="preserve">0.812755346298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807743310928345</t>
   </si>
   <si>
     <t xml:space="preserve">0.813172698020935</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">0.820690751075745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.749689340591431</t>
+    <t xml:space="preserve">0.74968945980072</t>
   </si>
   <si>
     <t xml:space="preserve">0.710846960544586</t>
@@ -2855,10 +2855,10 @@
     <t xml:space="preserve">0.654464364051819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.63399875164032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.645275890827179</t>
+    <t xml:space="preserve">0.633998811244965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.645275831222534</t>
   </si>
   <si>
     <t xml:space="preserve">0.660311102867126</t>
@@ -2879,22 +2879,22 @@
     <t xml:space="preserve">0.787696063518524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803148686885834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856191515922546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.845331788063049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877073407173157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900462329387665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.889603435993195</t>
+    <t xml:space="preserve">0.803148627281189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856191456317902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.845331847667694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877073347568512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.90046226978302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.889603495597839</t>
   </si>
   <si>
     <t xml:space="preserve">0.887097477912903</t>
@@ -2909,13 +2909,13 @@
     <t xml:space="preserve">0.904638767242432</t>
   </si>
   <si>
-    <t xml:space="preserve">0.892944276332855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902132749557495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882085382938385</t>
+    <t xml:space="preserve">0.89294421672821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.90213268995285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88208544254303</t>
   </si>
   <si>
     <t xml:space="preserve">0.867885053157806</t>
@@ -2930,16 +2930,16 @@
     <t xml:space="preserve">0.841991007328033</t>
   </si>
   <si>
-    <t xml:space="preserve">0.840320587158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.859532117843628</t>
+    <t xml:space="preserve">0.840320527553558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.859532177448273</t>
   </si>
   <si>
     <t xml:space="preserve">0.905474364757538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.849508225917816</t>
+    <t xml:space="preserve">0.849508166313171</t>
   </si>
   <si>
     <t xml:space="preserve">0.87289696931839</t>
@@ -2948,10 +2948,10 @@
     <t xml:space="preserve">0.906310081481934</t>
   </si>
   <si>
-    <t xml:space="preserve">0.943898439407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95392245054245</t>
+    <t xml:space="preserve">0.943898499011993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953922510147095</t>
   </si>
   <si>
     <t xml:space="preserve">0.9572634100914</t>
@@ -2960,10 +2960,10 @@
     <t xml:space="preserve">0.965616941452026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978146016597748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961439669132233</t>
+    <t xml:space="preserve">0.978146135807037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961439788341522</t>
   </si>
   <si>
     <t xml:space="preserve">0.934710025787354</t>
@@ -2972,10 +2972,10 @@
     <t xml:space="preserve">0.902968347072601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.874567449092865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852849781513214</t>
+    <t xml:space="preserve">0.87456738948822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852849841117859</t>
   </si>
   <si>
     <t xml:space="preserve">0.867050230503082</t>
@@ -2984,7 +2984,7 @@
     <t xml:space="preserve">0.878744721412659</t>
   </si>
   <si>
-    <t xml:space="preserve">0.907144904136658</t>
+    <t xml:space="preserve">0.907144784927368</t>
   </si>
   <si>
     <t xml:space="preserve">0.931369304656982</t>
@@ -2993,25 +2993,25 @@
     <t xml:space="preserve">0.921345174312592</t>
   </si>
   <si>
-    <t xml:space="preserve">0.927191972732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912992417812347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947240054607391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899626731872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929697930812836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93888646364212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93721604347229</t>
+    <t xml:space="preserve">0.927192032337189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912992358207703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947240114212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899626672267914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929698050022125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93888658285141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.937215983867645</t>
   </si>
   <si>
     <t xml:space="preserve">0.942228078842163</t>
@@ -3023,7 +3023,7 @@
     <t xml:space="preserve">0.94640451669693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.935545742511749</t>
+    <t xml:space="preserve">0.93554562330246</t>
   </si>
   <si>
     <t xml:space="preserve">0.975640118122101</t>
@@ -3035,10 +3035,10 @@
     <t xml:space="preserve">1.18947899341583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17360830307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16024351119995</t>
+    <t xml:space="preserve">1.17360818386078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16024339199066</t>
   </si>
   <si>
     <t xml:space="preserve">1.15773737430573</t>
@@ -3053,10 +3053,10 @@
     <t xml:space="preserve">1.10928928852081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11096060276031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10678398609161</t>
+    <t xml:space="preserve">1.11096048355103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1067841053009</t>
   </si>
   <si>
     <t xml:space="preserve">1.11179530620575</t>
@@ -3071,7 +3071,7 @@
     <t xml:space="preserve">1.16358518600464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14520823955536</t>
+    <t xml:space="preserve">1.14520812034607</t>
   </si>
   <si>
     <t xml:space="preserve">1.11513686180115</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">1.10761880874634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37742388248444</t>
+    <t xml:space="preserve">1.37742400169373</t>
   </si>
   <si>
     <t xml:space="preserve">1.37241196632385</t>
@@ -3101,28 +3101,28 @@
     <t xml:space="preserve">1.41167175769806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39747130870819</t>
+    <t xml:space="preserve">1.39747142791748</t>
   </si>
   <si>
     <t xml:space="preserve">1.43840134143829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47682535648346</t>
+    <t xml:space="preserve">1.47682547569275</t>
   </si>
   <si>
     <t xml:space="preserve">1.45928418636322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44090747833252</t>
+    <t xml:space="preserve">1.44090735912323</t>
   </si>
   <si>
     <t xml:space="preserve">1.43338942527771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48100185394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41334223747253</t>
+    <t xml:space="preserve">1.48100197315216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41334211826324</t>
   </si>
   <si>
     <t xml:space="preserve">1.42587125301361</t>
@@ -3140,13 +3140,13 @@
     <t xml:space="preserve">1.61214590072632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62049853801727</t>
+    <t xml:space="preserve">1.62049877643585</t>
   </si>
   <si>
     <t xml:space="preserve">1.61966300010681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62718093395233</t>
+    <t xml:space="preserve">1.62718105316162</t>
   </si>
   <si>
     <t xml:space="preserve">1.6138162612915</t>
@@ -3161,7 +3161,7 @@
     <t xml:space="preserve">1.34317636489868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3565411567688</t>
+    <t xml:space="preserve">1.35654103755951</t>
   </si>
   <si>
     <t xml:space="preserve">1.35904705524445</t>
@@ -3170,13 +3170,13 @@
     <t xml:space="preserve">1.36489391326904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40276598930359</t>
+    <t xml:space="preserve">1.4027658700943</t>
   </si>
   <si>
     <t xml:space="preserve">1.43466711044312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41251373291016</t>
+    <t xml:space="preserve">1.41251361370087</t>
   </si>
   <si>
     <t xml:space="preserve">1.39390444755554</t>
@@ -3188,7 +3188,7 @@
     <t xml:space="preserve">1.3336466550827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44795906543732</t>
+    <t xml:space="preserve">1.44795918464661</t>
   </si>
   <si>
     <t xml:space="preserve">1.49049425125122</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">1.58442544937134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52859842777252</t>
+    <t xml:space="preserve">1.52859854698181</t>
   </si>
   <si>
     <t xml:space="preserve">1.54897975921631</t>
@@ -3212,7 +3212,7 @@
     <t xml:space="preserve">1.54454898834229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5383460521698</t>
+    <t xml:space="preserve">1.53834593296051</t>
   </si>
   <si>
     <t xml:space="preserve">1.5587272644043</t>
@@ -3224,19 +3224,19 @@
     <t xml:space="preserve">1.6145544052124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60657894611359</t>
+    <t xml:space="preserve">1.60657906532288</t>
   </si>
   <si>
     <t xml:space="preserve">1.5693610906601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58885622024536</t>
+    <t xml:space="preserve">1.58885633945465</t>
   </si>
   <si>
     <t xml:space="preserve">1.6039205789566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63582181930542</t>
+    <t xml:space="preserve">1.63582193851471</t>
   </si>
   <si>
     <t xml:space="preserve">1.62518811225891</t>
@@ -3245,13 +3245,13 @@
     <t xml:space="preserve">1.61278212070465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58353936672211</t>
+    <t xml:space="preserve">1.58353924751282</t>
   </si>
   <si>
     <t xml:space="preserve">1.51885080337524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.520623087883</t>
+    <t xml:space="preserve">1.52062296867371</t>
   </si>
   <si>
     <t xml:space="preserve">1.4931526184082</t>
@@ -3269,19 +3269,19 @@
     <t xml:space="preserve">1.50112795829773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54011833667755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53037059307098</t>
+    <t xml:space="preserve">1.54011821746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53037083148956</t>
   </si>
   <si>
     <t xml:space="preserve">1.55341053009033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63848030567169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6632924079895</t>
+    <t xml:space="preserve">1.63848042488098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66329228878021</t>
   </si>
   <si>
     <t xml:space="preserve">1.56404423713684</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">1.48872184753418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46568214893341</t>
+    <t xml:space="preserve">1.4656822681427</t>
   </si>
   <si>
     <t xml:space="preserve">1.42403340339661</t>
@@ -3302,7 +3302,7 @@
     <t xml:space="preserve">1.44707322120667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46656835079193</t>
+    <t xml:space="preserve">1.46656823158264</t>
   </si>
   <si>
     <t xml:space="preserve">1.61809897422791</t>
@@ -3311,43 +3311,43 @@
     <t xml:space="preserve">1.8290011882782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84672427177429</t>
+    <t xml:space="preserve">1.84672403335571</t>
   </si>
   <si>
     <t xml:space="preserve">1.90520966053009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89634835720062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98319041728973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03635883331299</t>
+    <t xml:space="preserve">1.89634823799133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98319017887115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03635931015015</t>
   </si>
   <si>
     <t xml:space="preserve">2.09130001068115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17105293273926</t>
+    <t xml:space="preserve">2.17105269432068</t>
   </si>
   <si>
     <t xml:space="preserve">1.96015048027039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88925909996033</t>
+    <t xml:space="preserve">1.88925898075104</t>
   </si>
   <si>
     <t xml:space="preserve">1.96192276477814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94597256183624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01863646507263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10902261734009</t>
+    <t xml:space="preserve">1.94597244262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01863622665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10902309417725</t>
   </si>
   <si>
     <t xml:space="preserve">2.0753493309021</t>
@@ -3356,22 +3356,22 @@
     <t xml:space="preserve">2.10547828674316</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13737916946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1267454624176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17814183235168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16396379470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17636966705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18168616294861</t>
+    <t xml:space="preserve">2.13737940788269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12674593925476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17814207077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16396355628967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1763699054718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18168640136719</t>
   </si>
   <si>
     <t xml:space="preserve">2.24371695518494</t>
@@ -3386,22 +3386,22 @@
     <t xml:space="preserve">2.14624047279358</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19763731956482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30574679374695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28625130653381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31992506980896</t>
+    <t xml:space="preserve">2.19763708114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30574631690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28625154495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31992483139038</t>
   </si>
   <si>
     <t xml:space="preserve">2.34828162193298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.417400598526</t>
+    <t xml:space="preserve">2.41740083694458</t>
   </si>
   <si>
     <t xml:space="preserve">2.4457573890686</t>
@@ -3416,13 +3416,13 @@
     <t xml:space="preserve">2.42448997497559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47411417961121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51310443878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50955986976624</t>
+    <t xml:space="preserve">2.47411394119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51310420036316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50955963134766</t>
   </si>
   <si>
     <t xml:space="preserve">2.43157911300659</t>
@@ -3437,31 +3437,31 @@
     <t xml:space="preserve">2.33942031860352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37841081619263</t>
+    <t xml:space="preserve">2.37841057777405</t>
   </si>
   <si>
     <t xml:space="preserve">2.21004319190979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38904452323914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47943091392517</t>
+    <t xml:space="preserve">2.38904428482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47943115234375</t>
   </si>
   <si>
     <t xml:space="preserve">2.49183702468872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56095623970032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6566596031189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.640709400177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63184762001038</t>
+    <t xml:space="preserve">2.5609564781189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65665984153748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64070916175842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63184785842896</t>
   </si>
   <si>
     <t xml:space="preserve">2.65311503410339</t>
@@ -3473,7 +3473,7 @@
     <t xml:space="preserve">2.52373814582825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33233118057251</t>
+    <t xml:space="preserve">2.33233094215393</t>
   </si>
   <si>
     <t xml:space="preserve">2.31815266609192</t>
@@ -3485,16 +3485,16 @@
     <t xml:space="preserve">2.28270697593689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2756175994873</t>
+    <t xml:space="preserve">2.27561783790588</t>
   </si>
   <si>
     <t xml:space="preserve">2.25966739654541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30929136276245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27916264533997</t>
+    <t xml:space="preserve">2.30929112434387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27916240692139</t>
   </si>
   <si>
     <t xml:space="preserve">2.28802371025085</t>
@@ -3512,10 +3512,10 @@
     <t xml:space="preserve">2.24017214775085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14978575706482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16041946411133</t>
+    <t xml:space="preserve">2.14978551864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16041922569275</t>
   </si>
   <si>
     <t xml:space="preserve">2.17459750175476</t>
@@ -3527,10 +3527,10 @@
     <t xml:space="preserve">2.15687441825867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05762624740601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16928052902222</t>
+    <t xml:space="preserve">2.05762648582458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1692807674408</t>
   </si>
   <si>
     <t xml:space="preserve">2.1958646774292</t>
@@ -3545,55 +3545,55 @@
     <t xml:space="preserve">2.39436101913452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06648802757263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99382424354553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12142848968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1196563243866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09484457969666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01331925392151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08066654205322</t>
+    <t xml:space="preserve">2.06648778915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99382400512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12142872810364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11965656280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09484481811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01331901550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08066630363464</t>
   </si>
   <si>
     <t xml:space="preserve">1.99205148220062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03458666801453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02926993370056</t>
+    <t xml:space="preserve">2.03458642959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02926969528198</t>
   </si>
   <si>
     <t xml:space="preserve">1.93179368972778</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01509141921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00445795059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86799156665802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9016649723053</t>
+    <t xml:space="preserve">2.01509165763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00445771217346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86799144744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90166509151459</t>
   </si>
   <si>
     <t xml:space="preserve">1.80596160888672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64556956291199</t>
+    <t xml:space="preserve">1.6455694437027</t>
   </si>
   <si>
     <t xml:space="preserve">1.56315803527832</t>
@@ -3611,19 +3611,19 @@
     <t xml:space="preserve">1.59505915641785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65974771976471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78646636009216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75545108318329</t>
+    <t xml:space="preserve">1.659747838974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78646624088287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75545120239258</t>
   </si>
   <si>
     <t xml:space="preserve">1.73684227466583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73418402671814</t>
+    <t xml:space="preserve">1.73418378829956</t>
   </si>
   <si>
     <t xml:space="preserve">1.70671331882477</t>
@@ -3632,34 +3632,34 @@
     <t xml:space="preserve">1.65088641643524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66595065593719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67924284934998</t>
+    <t xml:space="preserve">1.66595077514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67924296855927</t>
   </si>
   <si>
     <t xml:space="preserve">1.72798073291779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86444699764252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83431804180145</t>
+    <t xml:space="preserve">1.86444687843323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83431816101074</t>
   </si>
   <si>
     <t xml:space="preserve">1.74570369720459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78469395637512</t>
+    <t xml:space="preserve">1.78469407558441</t>
   </si>
   <si>
     <t xml:space="preserve">1.76254045963287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7288670539856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67038142681122</t>
+    <t xml:space="preserve">1.72886693477631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67038154602051</t>
   </si>
   <si>
     <t xml:space="preserve">1.64113867282867</t>
@@ -3680,22 +3680,22 @@
     <t xml:space="preserve">1.67835676670074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62961876392365</t>
+    <t xml:space="preserve">1.62961888313293</t>
   </si>
   <si>
     <t xml:space="preserve">1.63936650753021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63050508499146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60923755168915</t>
+    <t xml:space="preserve">1.63050496578217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60923743247986</t>
   </si>
   <si>
     <t xml:space="preserve">1.62075746059418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55075216293335</t>
+    <t xml:space="preserve">1.55075204372406</t>
   </si>
   <si>
     <t xml:space="preserve">1.46302366256714</t>
@@ -3710,7 +3710,7 @@
     <t xml:space="preserve">1.60835146903992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58974242210388</t>
+    <t xml:space="preserve">1.58974230289459</t>
   </si>
   <si>
     <t xml:space="preserve">1.64468324184418</t>
@@ -3719,13 +3719,13 @@
     <t xml:space="preserve">1.60746514797211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60037612915039</t>
+    <t xml:space="preserve">1.6003760099411</t>
   </si>
   <si>
     <t xml:space="preserve">1.52594006061554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52150940895081</t>
+    <t xml:space="preserve">1.52150928974152</t>
   </si>
   <si>
     <t xml:space="preserve">1.6313910484314</t>
@@ -3740,13 +3740,13 @@
     <t xml:space="preserve">1.690762758255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71646106243134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78114938735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84495186805725</t>
+    <t xml:space="preserve">1.71646094322205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78114950656891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84495174884796</t>
   </si>
   <si>
     <t xml:space="preserve">1.80773365497589</t>
@@ -3755,22 +3755,22 @@
     <t xml:space="preserve">1.79887235164642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79532766342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65797567367554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45593452453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41871654987335</t>
+    <t xml:space="preserve">1.79532778263092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65797555446625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45593464374542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41871643066406</t>
   </si>
   <si>
     <t xml:space="preserve">1.46506786346436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47688293457031</t>
+    <t xml:space="preserve">1.4768830537796</t>
   </si>
   <si>
     <t xml:space="preserve">1.48960697650909</t>
@@ -3779,13 +3779,13 @@
     <t xml:space="preserve">1.45779705047607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47597408294678</t>
+    <t xml:space="preserve">1.47597420215607</t>
   </si>
   <si>
     <t xml:space="preserve">1.43689346313477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47415637969971</t>
+    <t xml:space="preserve">1.47415626049042</t>
   </si>
   <si>
     <t xml:space="preserve">1.48142719268799</t>
@@ -3800,10 +3800,10 @@
     <t xml:space="preserve">1.37872707843781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30147469043732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32783138751984</t>
+    <t xml:space="preserve">1.30147480964661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32783126831055</t>
   </si>
   <si>
     <t xml:space="preserve">1.37418270111084</t>
@@ -3812,13 +3812,13 @@
     <t xml:space="preserve">1.40781044960022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38599789142609</t>
+    <t xml:space="preserve">1.3859977722168</t>
   </si>
   <si>
     <t xml:space="preserve">1.31510746479034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28420674800873</t>
+    <t xml:space="preserve">1.28420650959015</t>
   </si>
   <si>
     <t xml:space="preserve">1.27966237068176</t>
@@ -3842,10 +3842,10 @@
     <t xml:space="preserve">1.35691475868225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29693055152893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31328976154327</t>
+    <t xml:space="preserve">1.29693043231964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31328988075256</t>
   </si>
   <si>
     <t xml:space="preserve">1.33328461647034</t>
@@ -3884,22 +3884,22 @@
     <t xml:space="preserve">1.50505745410919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50051307678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48051846027374</t>
+    <t xml:space="preserve">1.50051319599152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48051834106445</t>
   </si>
   <si>
     <t xml:space="preserve">1.40326607227325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43234932422638</t>
+    <t xml:space="preserve">1.43234920501709</t>
   </si>
   <si>
     <t xml:space="preserve">1.41144561767578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34691739082336</t>
+    <t xml:space="preserve">1.34691715240479</t>
   </si>
   <si>
     <t xml:space="preserve">1.34328186511993</t>
@@ -3908,7 +3908,7 @@
     <t xml:space="preserve">1.37327408790588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37600064277649</t>
+    <t xml:space="preserve">1.3760005235672</t>
   </si>
   <si>
     <t xml:space="preserve">1.36236763000488</t>
@@ -3926,16 +3926,16 @@
     <t xml:space="preserve">1.36963856220245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35964131355286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41326344013214</t>
+    <t xml:space="preserve">1.35964119434357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41326332092285</t>
   </si>
   <si>
     <t xml:space="preserve">1.43507587909698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41689884662628</t>
+    <t xml:space="preserve">1.41689896583557</t>
   </si>
   <si>
     <t xml:space="preserve">1.46870338916779</t>
@@ -3944,13 +3944,13 @@
     <t xml:space="preserve">1.41235458850861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39872181415558</t>
+    <t xml:space="preserve">1.39872193336487</t>
   </si>
   <si>
     <t xml:space="preserve">1.70591342449188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68591868877411</t>
+    <t xml:space="preserve">1.6859188079834</t>
   </si>
   <si>
     <t xml:space="preserve">1.58412742614746</t>
@@ -3965,16 +3965,16 @@
     <t xml:space="preserve">1.56322383880615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49960434436798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55777072906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55231761932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64956474304199</t>
+    <t xml:space="preserve">1.49960422515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55777084827423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55231750011444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6495646238327</t>
   </si>
   <si>
     <t xml:space="preserve">1.58140087127686</t>
@@ -3992,13 +3992,13 @@
     <t xml:space="preserve">1.53323173522949</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59503352642059</t>
+    <t xml:space="preserve">1.59503376483917</t>
   </si>
   <si>
     <t xml:space="preserve">1.59412467479706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64047610759735</t>
+    <t xml:space="preserve">1.64047598838806</t>
   </si>
   <si>
     <t xml:space="preserve">1.65774440765381</t>
@@ -4010,16 +4010,16 @@
     <t xml:space="preserve">1.65956199169159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6704683303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76317119598389</t>
+    <t xml:space="preserve">1.67046821117401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7631710767746</t>
   </si>
   <si>
     <t xml:space="preserve">1.79225432872772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78861904144287</t>
+    <t xml:space="preserve">1.78861892223358</t>
   </si>
   <si>
     <t xml:space="preserve">1.73045253753662</t>
@@ -4031,7 +4031,7 @@
     <t xml:space="preserve">1.72681701183319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77135062217712</t>
+    <t xml:space="preserve">1.77135074138641</t>
   </si>
   <si>
     <t xml:space="preserve">1.73136126995087</t>
@@ -4043,25 +4043,25 @@
     <t xml:space="preserve">1.78770995140076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8486031293869</t>
+    <t xml:space="preserve">1.84860301017761</t>
   </si>
   <si>
     <t xml:space="preserve">1.86678004264832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87223303318024</t>
+    <t xml:space="preserve">1.87223315238953</t>
   </si>
   <si>
     <t xml:space="preserve">1.89949870109558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9340353012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94494140148163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90676963329315</t>
+    <t xml:space="preserve">1.93403518199921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94494128227234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90676951408386</t>
   </si>
   <si>
     <t xml:space="preserve">1.95402979850769</t>
@@ -4070,7 +4070,7 @@
     <t xml:space="preserve">1.97038924694061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00492548942566</t>
+    <t xml:space="preserve">2.00492525100708</t>
   </si>
   <si>
     <t xml:space="preserve">1.99583721160889</t>
@@ -4085,22 +4085,22 @@
     <t xml:space="preserve">1.99038398265839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04491519927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13398265838623</t>
+    <t xml:space="preserve">2.04491496086121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13398241996765</t>
   </si>
   <si>
     <t xml:space="preserve">2.15397691726685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12307620048523</t>
+    <t xml:space="preserve">2.12307596206665</t>
   </si>
   <si>
     <t xml:space="preserve">2.11944079399109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13761758804321</t>
+    <t xml:space="preserve">2.13761782646179</t>
   </si>
   <si>
     <t xml:space="preserve">2.16851854324341</t>
@@ -4118,46 +4118,46 @@
     <t xml:space="preserve">1.97584235668182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02128505706787</t>
+    <t xml:space="preserve">2.02128481864929</t>
   </si>
   <si>
     <t xml:space="preserve">1.85223865509033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89041006565094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91222274303436</t>
+    <t xml:space="preserve">1.89041018486023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91222262382507</t>
   </si>
   <si>
     <t xml:space="preserve">1.92676424980164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93585288524628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93948829174042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90131664276123</t>
+    <t xml:space="preserve">1.93585312366486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93948817253113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90131652355194</t>
   </si>
   <si>
     <t xml:space="preserve">1.91404032707214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96311855316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96857118606567</t>
+    <t xml:space="preserve">1.96311831474304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96857142448425</t>
   </si>
   <si>
     <t xml:space="preserve">2.03219103813171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05945682525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10489916801453</t>
+    <t xml:space="preserve">2.05945658683777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10489892959595</t>
   </si>
   <si>
     <t xml:space="preserve">2.12852931022644</t>
@@ -4169,22 +4169,22 @@
     <t xml:space="preserve">2.09944581985474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01946687698364</t>
+    <t xml:space="preserve">2.01946711540222</t>
   </si>
   <si>
     <t xml:space="preserve">2.07218050956726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06309175491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03764414787292</t>
+    <t xml:space="preserve">2.06309199333191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0376443862915</t>
   </si>
   <si>
     <t xml:space="preserve">2.00310778617859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01219630241394</t>
+    <t xml:space="preserve">2.01219654083252</t>
   </si>
   <si>
     <t xml:space="preserve">2.01764917373657</t>
@@ -4199,16 +4199,16 @@
     <t xml:space="preserve">2.2484974861145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31757020950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30848145484924</t>
+    <t xml:space="preserve">2.31756997108459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30848169326782</t>
   </si>
   <si>
     <t xml:space="preserve">2.33211183547974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3721010684967</t>
+    <t xml:space="preserve">2.37210130691528</t>
   </si>
   <si>
     <t xml:space="preserve">2.41572594642639</t>
@@ -4217,28 +4217,28 @@
     <t xml:space="preserve">2.375736951828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40845537185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39754915237427</t>
+    <t xml:space="preserve">2.40845561027527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39754891395569</t>
   </si>
   <si>
     <t xml:space="preserve">2.38846063613892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39209604263306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35755968093872</t>
+    <t xml:space="preserve">2.39209580421448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3575599193573</t>
   </si>
   <si>
     <t xml:space="preserve">2.34483575820923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30666422843933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3157525062561</t>
+    <t xml:space="preserve">2.30666446685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31575274467468</t>
   </si>
   <si>
     <t xml:space="preserve">2.3357470035553</t>
@@ -4247,19 +4247,19 @@
     <t xml:space="preserve">2.33938264846802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38118982315063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40663743019104</t>
+    <t xml:space="preserve">2.38118958473206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40663766860962</t>
   </si>
   <si>
     <t xml:space="preserve">2.40481996536255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39027833938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37937211990356</t>
+    <t xml:space="preserve">2.39027857780457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37937188148499</t>
   </si>
   <si>
     <t xml:space="preserve">2.32302331924438</t>
@@ -4268,25 +4268,25 @@
     <t xml:space="preserve">2.28666925430298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18487811088562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23213839530945</t>
+    <t xml:space="preserve">2.18487787246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23213863372803</t>
   </si>
   <si>
     <t xml:space="preserve">2.18306016921997</t>
   </si>
   <si>
-    <t xml:space="preserve">2.143070936203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20487284660339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20669031143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17033624649048</t>
+    <t xml:space="preserve">2.14307069778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20487260818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20669054985046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17033648490906</t>
   </si>
   <si>
     <t xml:space="preserve">2.13943552970886</t>
@@ -4295,22 +4295,22 @@
     <t xml:space="preserve">2.14670634269714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14852380752563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19578385353088</t>
+    <t xml:space="preserve">2.14852404594421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19578409194946</t>
   </si>
   <si>
     <t xml:space="preserve">2.19033145904541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26849246025085</t>
+    <t xml:space="preserve">2.26849222183228</t>
   </si>
   <si>
     <t xml:space="preserve">2.24667978286743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24304437637329</t>
+    <t xml:space="preserve">2.24304413795471</t>
   </si>
   <si>
     <t xml:space="preserve">2.25213289260864</t>
@@ -4319,16 +4319,16 @@
     <t xml:space="preserve">2.30121111869812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28303384780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34120035171509</t>
+    <t xml:space="preserve">2.28303408622742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34120011329651</t>
   </si>
   <si>
     <t xml:space="preserve">2.47934556007385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44844484329224</t>
+    <t xml:space="preserve">2.44844460487366</t>
   </si>
   <si>
     <t xml:space="preserve">2.48843431472778</t>
@@ -4337,7 +4337,7 @@
     <t xml:space="preserve">2.46843957901001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47207498550415</t>
+    <t xml:space="preserve">2.47207474708557</t>
   </si>
   <si>
     <t xml:space="preserve">2.45935106277466</t>
@@ -4346,22 +4346,22 @@
     <t xml:space="preserve">2.45753312110901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43390321731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51388192176819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46480393409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50297570228577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4702570438385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40118432044983</t>
+    <t xml:space="preserve">2.43390297889709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51388216018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46480417251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50297594070435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47025728225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40118455886841</t>
   </si>
   <si>
     <t xml:space="preserve">2.36664843559265</t>
@@ -4379,7 +4379,7 @@
     <t xml:space="preserve">2.29212260246277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27030968666077</t>
+    <t xml:space="preserve">2.27030992507935</t>
   </si>
   <si>
     <t xml:space="preserve">2.22668528556824</t>
@@ -4400,22 +4400,22 @@
     <t xml:space="preserve">2.41936159133911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4320855140686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4211790561676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43935632705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25599431991577</t>
+    <t xml:space="preserve">2.43208575248718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42117929458618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43935608863831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25599455833435</t>
   </si>
   <si>
     <t xml:space="preserve">2.28207540512085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27462363243103</t>
+    <t xml:space="preserve">2.27462387084961</t>
   </si>
   <si>
     <t xml:space="preserve">2.24854278564453</t>
@@ -4430,7 +4430,7 @@
     <t xml:space="preserve">2.31188225746155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36590647697449</t>
+    <t xml:space="preserve">2.36590671539307</t>
   </si>
   <si>
     <t xml:space="preserve">2.40130209922791</t>
@@ -4439,16 +4439,16 @@
     <t xml:space="preserve">2.36404371261597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29697895050049</t>
+    <t xml:space="preserve">2.29697871208191</t>
   </si>
   <si>
     <t xml:space="preserve">2.32678508758545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34168863296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33982586860657</t>
+    <t xml:space="preserve">2.34168839454651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33982610702515</t>
   </si>
   <si>
     <t xml:space="preserve">2.36963248252869</t>
@@ -4463,7 +4463,7 @@
     <t xml:space="preserve">2.29884147644043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28580117225647</t>
+    <t xml:space="preserve">2.28580093383789</t>
   </si>
   <si>
     <t xml:space="preserve">2.28021216392517</t>
@@ -4475,10 +4475,10 @@
     <t xml:space="preserve">2.30443024635315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29325270652771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33051133155823</t>
+    <t xml:space="preserve">2.29325294494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33051156997681</t>
   </si>
   <si>
     <t xml:space="preserve">2.31374478340149</t>
@@ -4496,19 +4496,19 @@
     <t xml:space="preserve">2.16098570823669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14049339294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1069610118866</t>
+    <t xml:space="preserve">2.14049363136292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10696077346802</t>
   </si>
   <si>
     <t xml:space="preserve">2.09950923919678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12559008598328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1088240146637</t>
+    <t xml:space="preserve">2.12559032440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10882377624512</t>
   </si>
   <si>
     <t xml:space="preserve">2.09019470214844</t>
@@ -4517,10 +4517,10 @@
     <t xml:space="preserve">2.0585253238678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04362154006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04921054840088</t>
+    <t xml:space="preserve">2.04362177848816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04921078681946</t>
   </si>
   <si>
     <t xml:space="preserve">2.08460593223572</t>
@@ -4529,7 +4529,7 @@
     <t xml:space="preserve">2.06411409378052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0510733127594</t>
+    <t xml:space="preserve">2.05107307434082</t>
   </si>
   <si>
     <t xml:space="preserve">2.04175853729248</t>
@@ -4541,13 +4541,13 @@
     <t xml:space="preserve">2.15912270545959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1535336971283</t>
+    <t xml:space="preserve">2.15353393554688</t>
   </si>
   <si>
     <t xml:space="preserve">2.13863062858582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12186455726624</t>
+    <t xml:space="preserve">2.12186431884766</t>
   </si>
   <si>
     <t xml:space="preserve">2.06970238685608</t>
@@ -4556,10 +4556,10 @@
     <t xml:space="preserve">2.0231294631958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01754069328308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99891173839569</t>
+    <t xml:space="preserve">2.01754093170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99891149997711</t>
   </si>
   <si>
     <t xml:space="preserve">2.01195240020752</t>
@@ -4574,37 +4574,37 @@
     <t xml:space="preserve">1.97469365596771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95606434345245</t>
+    <t xml:space="preserve">1.95606458187103</t>
   </si>
   <si>
     <t xml:space="preserve">1.92625796794891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.864781498909</t>
+    <t xml:space="preserve">1.86478161811829</t>
   </si>
   <si>
     <t xml:space="preserve">1.77349853515625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78095018863678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78467607498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80330514907837</t>
+    <t xml:space="preserve">1.78095006942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78467619419098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80330526828766</t>
   </si>
   <si>
     <t xml:space="preserve">1.83311200141907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80237364768982</t>
+    <t xml:space="preserve">1.80237376689911</t>
   </si>
   <si>
     <t xml:space="preserve">1.75673234462738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71109080314636</t>
+    <t xml:space="preserve">1.71109068393707</t>
   </si>
   <si>
     <t xml:space="preserve">1.70829629898071</t>
@@ -4613,10 +4613,10 @@
     <t xml:space="preserve">1.71947395801544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67196941375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69991326332092</t>
+    <t xml:space="preserve">1.67196953296661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69991338253021</t>
   </si>
   <si>
     <t xml:space="preserve">1.66638076305389</t>
@@ -4631,7 +4631,7 @@
     <t xml:space="preserve">1.63377952575684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63564264774323</t>
+    <t xml:space="preserve">1.63564252853394</t>
   </si>
   <si>
     <t xml:space="preserve">1.64775156974792</t>
@@ -4640,7 +4640,7 @@
     <t xml:space="preserve">1.64682006835938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53131914138794</t>
+    <t xml:space="preserve">1.53131926059723</t>
   </si>
   <si>
     <t xml:space="preserve">1.54994833469391</t>
@@ -4652,10 +4652,10 @@
     <t xml:space="preserve">1.54529106616974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54249668121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55087971687317</t>
+    <t xml:space="preserve">1.54249656200409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55087983608246</t>
   </si>
   <si>
     <t xml:space="preserve">1.55646848678589</t>
@@ -4673,13 +4673,13 @@
     <t xml:space="preserve">1.60117852687836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60956168174744</t>
+    <t xml:space="preserve">1.60956180095673</t>
   </si>
   <si>
     <t xml:space="preserve">1.61980772018433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62819087505341</t>
+    <t xml:space="preserve">1.6281909942627</t>
   </si>
   <si>
     <t xml:space="preserve">1.59745287895203</t>
@@ -4688,7 +4688,7 @@
     <t xml:space="preserve">1.61235594749451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62073922157288</t>
+    <t xml:space="preserve">1.62073934078217</t>
   </si>
   <si>
     <t xml:space="preserve">1.67755818367004</t>
@@ -4700,7 +4700,7 @@
     <t xml:space="preserve">1.65706610679626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68966710567474</t>
+    <t xml:space="preserve">1.68966722488403</t>
   </si>
   <si>
     <t xml:space="preserve">1.69153010845184</t>
@@ -4709,19 +4709,19 @@
     <t xml:space="preserve">1.66917514801025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6682436466217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67662668228149</t>
+    <t xml:space="preserve">1.66824352741241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67662680149078</t>
   </si>
   <si>
     <t xml:space="preserve">1.69059872627258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72785699367523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8424266576767</t>
+    <t xml:space="preserve">1.72785711288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84242653846741</t>
   </si>
   <si>
     <t xml:space="preserve">1.84801530838013</t>
@@ -4739,10 +4739,10 @@
     <t xml:space="preserve">1.96165335178375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91508030891418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93557250499725</t>
+    <t xml:space="preserve">1.91508042812347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93557262420654</t>
   </si>
   <si>
     <t xml:space="preserve">1.90949153900146</t>
@@ -4757,10 +4757,10 @@
     <t xml:space="preserve">1.99704885482788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09764647483826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09392023086548</t>
+    <t xml:space="preserve">2.09764623641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09392046928406</t>
   </si>
   <si>
     <t xml:space="preserve">2.1106870174408</t>
@@ -4772,7 +4772,7 @@
     <t xml:space="preserve">2.12000155448914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11441254615784</t>
+    <t xml:space="preserve">2.11441278457642</t>
   </si>
   <si>
     <t xml:space="preserve">2.10137224197388</t>
@@ -4781,7 +4781,7 @@
     <t xml:space="preserve">2.03617024421692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0026376247406</t>
+    <t xml:space="preserve">2.00263786315918</t>
   </si>
   <si>
     <t xml:space="preserve">1.98028242588043</t>
@@ -4802,16 +4802,16 @@
     <t xml:space="preserve">1.91694331169128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89272522926331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92812061309814</t>
+    <t xml:space="preserve">1.8927253484726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92812073230743</t>
   </si>
   <si>
     <t xml:space="preserve">1.95420169830322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06783962249756</t>
+    <t xml:space="preserve">2.06783986091614</t>
   </si>
   <si>
     <t xml:space="preserve">2.03989601135254</t>
@@ -4820,7 +4820,7 @@
     <t xml:space="preserve">2.0752911567688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09578371047974</t>
+    <t xml:space="preserve">2.09578347206116</t>
   </si>
   <si>
     <t xml:space="preserve">2.11813831329346</t>
@@ -5991,6 +5991,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.52600002288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51599979400635</t>
   </si>
 </sst>
 </file>
@@ -72187,7 +72190,7 @@
     </row>
     <row r="2534">
       <c r="A2534" s="1" t="n">
-        <v>46007.6913078704</v>
+        <v>46007.3333333333</v>
       </c>
       <c r="B2534" t="n">
         <v>351748</v>
@@ -72196,7 +72199,7 @@
         <v>4.59600019454956</v>
       </c>
       <c r="D2534" t="n">
-        <v>4.53999996185303</v>
+        <v>4.52600002288818</v>
       </c>
       <c r="E2534" t="n">
         <v>4.54199981689453</v>
@@ -72208,6 +72211,32 @@
         <v>1992</v>
       </c>
       <c r="H2534" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2535">
+      <c r="A2535" s="1" t="n">
+        <v>46008.6912847222</v>
+      </c>
+      <c r="B2535" t="n">
+        <v>413988</v>
+      </c>
+      <c r="C2535" t="n">
+        <v>4.55600023269653</v>
+      </c>
+      <c r="D2535" t="n">
+        <v>4.49200010299683</v>
+      </c>
+      <c r="E2535" t="n">
+        <v>4.53000020980835</v>
+      </c>
+      <c r="F2535" t="n">
+        <v>4.51599979400635</v>
+      </c>
+      <c r="G2535" t="s">
+        <v>1993</v>
+      </c>
+      <c r="H2535" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/OVS.MI.xlsx
+++ b/data/OVS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1994" uniqueCount="1994">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1995" uniqueCount="1995">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,19 +44,19 @@
     <t xml:space="preserve">OVS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89862394332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76365375518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64456176757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71998691558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65647077560425</t>
+    <t xml:space="preserve">4.89862442016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76365327835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64456224441528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71998596191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65647125244141</t>
   </si>
   <si>
     <t xml:space="preserve">4.78747224807739</t>
@@ -71,19 +71,19 @@
     <t xml:space="preserve">4.60486459732056</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6366229057312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.616774559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25155973434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22774314880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5334095954895</t>
+    <t xml:space="preserve">4.63662338256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61677408218384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25156021118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22774267196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53341054916382</t>
   </si>
   <si>
     <t xml:space="preserve">4.45798540115356</t>
@@ -95,22 +95,22 @@
     <t xml:space="preserve">4.49768304824829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5135612487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44607734680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62868356704712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59295701980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5175313949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54531955718994</t>
+    <t xml:space="preserve">4.51356077194214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4460768699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62868309020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59295606613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51753187179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5453200340271</t>
   </si>
   <si>
     <t xml:space="preserve">4.32698583602905</t>
@@ -119,43 +119,43 @@
     <t xml:space="preserve">4.03322601318359</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02925729751587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2793493270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22377252578735</t>
+    <t xml:space="preserve">4.02925682067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27934885025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22377300262451</t>
   </si>
   <si>
     <t xml:space="preserve">4.38256120681763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30316781997681</t>
+    <t xml:space="preserve">4.30316734313965</t>
   </si>
   <si>
     <t xml:space="preserve">4.46989488601685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46592426300049</t>
+    <t xml:space="preserve">4.46592473983765</t>
   </si>
   <si>
     <t xml:space="preserve">4.48577404022217</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48974323272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.271409034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23965215682983</t>
+    <t xml:space="preserve">4.48974275588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27140951156616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23965167999268</t>
   </si>
   <si>
     <t xml:space="preserve">4.43813705444336</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5651683807373</t>
+    <t xml:space="preserve">4.56516885757446</t>
   </si>
   <si>
     <t xml:space="preserve">4.67235040664673</t>
@@ -164,58 +164,58 @@
     <t xml:space="preserve">4.71601676940918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58898687362671</t>
+    <t xml:space="preserve">4.58898639678955</t>
   </si>
   <si>
     <t xml:space="preserve">4.50562238693237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52547121047974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38653039932251</t>
+    <t xml:space="preserve">4.52547073364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38652992248535</t>
   </si>
   <si>
     <t xml:space="preserve">4.43019771575928</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40241098403931</t>
+    <t xml:space="preserve">4.40241050720215</t>
   </si>
   <si>
     <t xml:space="preserve">4.29125738143921</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12056016921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09674215316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06498527526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08880281448364</t>
+    <t xml:space="preserve">4.12056064605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09674167633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06498432159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0888032913208</t>
   </si>
   <si>
     <t xml:space="preserve">4.15628719329834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21186399459839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04910516738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02131795883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31110763549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16422748565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23568248748779</t>
+    <t xml:space="preserve">4.21186351776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04910612106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02131700515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31110620498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16422700881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23568201065063</t>
   </si>
   <si>
     <t xml:space="preserve">4.50959157943726</t>
@@ -227,13 +227,13 @@
     <t xml:space="preserve">4.54928922653198</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50165319442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56119775772095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48180389404297</t>
+    <t xml:space="preserve">4.50165224075317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56119823455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48180437088013</t>
   </si>
   <si>
     <t xml:space="preserve">4.52150201797485</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">4.55325889587402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5413498878479</t>
+    <t xml:space="preserve">4.54135036468506</t>
   </si>
   <si>
     <t xml:space="preserve">4.56913757324219</t>
@@ -254,19 +254,19 @@
     <t xml:space="preserve">4.64853191375732</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70410823822021</t>
+    <t xml:space="preserve">4.70410776138306</t>
   </si>
   <si>
     <t xml:space="preserve">4.84304809570312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89068412780762</t>
+    <t xml:space="preserve">4.89068365097046</t>
   </si>
   <si>
     <t xml:space="preserve">4.81525945663452</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87877607345581</t>
+    <t xml:space="preserve">4.87877511978149</t>
   </si>
   <si>
     <t xml:space="preserve">4.91053295135498</t>
@@ -275,19 +275,19 @@
     <t xml:space="preserve">4.75968408584595</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73826837539673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7667875289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90123558044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73419427871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5671534538269</t>
+    <t xml:space="preserve">4.73826789855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76678800582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90123510360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7341947555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56715297698975</t>
   </si>
   <si>
     <t xml:space="preserve">4.51826333999634</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">4.47752094268799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48974370956421</t>
+    <t xml:space="preserve">4.48974418640137</t>
   </si>
   <si>
     <t xml:space="preserve">4.63233947753906</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">4.61196899414062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55085563659668</t>
+    <t xml:space="preserve">4.55085515975952</t>
   </si>
   <si>
     <t xml:space="preserve">4.51418924331665</t>
@@ -320,10 +320,10 @@
     <t xml:space="preserve">3.94706273078918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13529014587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24529314041138</t>
+    <t xml:space="preserve">4.13528966903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24529361724854</t>
   </si>
   <si>
     <t xml:space="preserve">4.26566314697266</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">4.30233144760132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25751543045044</t>
+    <t xml:space="preserve">4.25751447677612</t>
   </si>
   <si>
     <t xml:space="preserve">4.11084413528442</t>
@@ -341,52 +341,52 @@
     <t xml:space="preserve">4.09047412872314</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05299091339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18825340270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16380882263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15566062927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15973520278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10677051544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04321384429932</t>
+    <t xml:space="preserve">4.05299186706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18825387954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16380834579468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15566110610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15973472595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10677099227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04321432113647</t>
   </si>
   <si>
     <t xml:space="preserve">4.11899280548096</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16788339614868</t>
+    <t xml:space="preserve">4.16788291931152</t>
   </si>
   <si>
     <t xml:space="preserve">4.26158952713013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20047664642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20862531661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.233069896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37159252166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36751842498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28603458404541</t>
+    <t xml:space="preserve">4.2004771232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20862483978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23307037353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37159299850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36751890182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28603410720825</t>
   </si>
   <si>
     <t xml:space="preserve">4.27788639068604</t>
@@ -395,13 +395,13 @@
     <t xml:space="preserve">4.24121809005737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25344133377075</t>
+    <t xml:space="preserve">4.25344085693359</t>
   </si>
   <si>
     <t xml:space="preserve">4.29825735092163</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22899627685547</t>
+    <t xml:space="preserve">4.22899580001831</t>
   </si>
   <si>
     <t xml:space="preserve">4.0725474357605</t>
@@ -413,13 +413,13 @@
     <t xml:space="preserve">4.19232797622681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10269641876221</t>
+    <t xml:space="preserve">4.10269737243652</t>
   </si>
   <si>
     <t xml:space="preserve">4.04158353805542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13936424255371</t>
+    <t xml:space="preserve">4.13936376571655</t>
   </si>
   <si>
     <t xml:space="preserve">4.09862327575684</t>
@@ -428,49 +428,49 @@
     <t xml:space="preserve">4.00084209442139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99269366264343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0334358215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19640254974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15158700942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0863995552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0611400604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3593692779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37566661834717</t>
+    <t xml:space="preserve">3.99269318580627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03343534469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19640302658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15158653259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08640003204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06114053726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35936975479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37566614151001</t>
   </si>
   <si>
     <t xml:space="preserve">4.44085359573364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41233348846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31862783432007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31047868728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31455326080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2697377204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21677303314209</t>
+    <t xml:space="preserve">4.41233396530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31862831115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31047916412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31455278396606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26973724365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21677350997925</t>
   </si>
   <si>
     <t xml:space="preserve">4.1801061630249</t>
@@ -494,13 +494,13 @@
     <t xml:space="preserve">4.06439876556396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00573062896729</t>
+    <t xml:space="preserve">4.00573015213013</t>
   </si>
   <si>
     <t xml:space="preserve">3.9601001739502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05462121963501</t>
+    <t xml:space="preserve">4.05462169647217</t>
   </si>
   <si>
     <t xml:space="preserve">4.13121604919434</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">4.04647254943848</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98128581047058</t>
+    <t xml:space="preserve">3.98128533363342</t>
   </si>
   <si>
     <t xml:space="preserve">4.00410127639771</t>
@@ -518,13 +518,13 @@
     <t xml:space="preserve">3.98617506027222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02528667449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97476673126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02365732192993</t>
+    <t xml:space="preserve">4.02528810501099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97476696968079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02365779876709</t>
   </si>
   <si>
     <t xml:space="preserve">4.05950975418091</t>
@@ -536,10 +536,10 @@
     <t xml:space="preserve">4.05136156082153</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97965669631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03017568588257</t>
+    <t xml:space="preserve">3.97965621948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03017520904541</t>
   </si>
   <si>
     <t xml:space="preserve">4.02039861679077</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">3.99921202659607</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07825183868408</t>
+    <t xml:space="preserve">4.07825136184692</t>
   </si>
   <si>
     <t xml:space="preserve">4.14751291275024</t>
@@ -560,10 +560,10 @@
     <t xml:space="preserve">4.20455074310303</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22492170333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01713800430298</t>
+    <t xml:space="preserve">4.22492265701294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01713848114014</t>
   </si>
   <si>
     <t xml:space="preserve">4.02202749252319</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">3.8949134349823</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87535738945007</t>
+    <t xml:space="preserve">3.87535667419434</t>
   </si>
   <si>
     <t xml:space="preserve">3.94054484367371</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93402552604675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89654350280762</t>
+    <t xml:space="preserve">3.93402504920959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89654302597046</t>
   </si>
   <si>
     <t xml:space="preserve">3.95521116256714</t>
@@ -599,7 +599,7 @@
     <t xml:space="preserve">4.37974071502686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38381433486938</t>
+    <t xml:space="preserve">4.38381481170654</t>
   </si>
   <si>
     <t xml:space="preserve">4.39196348190308</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">4.35529565811157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29010820388794</t>
+    <t xml:space="preserve">4.2901086807251</t>
   </si>
   <si>
     <t xml:space="preserve">4.28195953369141</t>
@@ -620,25 +620,25 @@
     <t xml:space="preserve">4.29418325424194</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33899927139282</t>
+    <t xml:space="preserve">4.33899879455566</t>
   </si>
   <si>
     <t xml:space="preserve">4.33492469787598</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34307336807251</t>
+    <t xml:space="preserve">4.34307384490967</t>
   </si>
   <si>
     <t xml:space="preserve">4.46529865264893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48159456253052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40825986862183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53863382339478</t>
+    <t xml:space="preserve">4.48159503936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40825939178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53863334655762</t>
   </si>
   <si>
     <t xml:space="preserve">4.55493021011353</t>
@@ -647,16 +647,16 @@
     <t xml:space="preserve">4.52641153335571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5060396194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43270492553711</t>
+    <t xml:space="preserve">4.50604009628296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43270444869995</t>
   </si>
   <si>
     <t xml:space="preserve">4.59567213058472</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68530368804932</t>
+    <t xml:space="preserve">4.68530416488647</t>
   </si>
   <si>
     <t xml:space="preserve">4.67308187484741</t>
@@ -665,55 +665,55 @@
     <t xml:space="preserve">4.60382032394409</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70160102844238</t>
+    <t xml:space="preserve">4.70160007476807</t>
   </si>
   <si>
     <t xml:space="preserve">4.85641956329346</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82382583618164</t>
+    <t xml:space="preserve">4.82382678985596</t>
   </si>
   <si>
     <t xml:space="preserve">4.77493524551392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7993803024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74234294891357</t>
+    <t xml:space="preserve">4.79938077926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74234247207642</t>
   </si>
   <si>
     <t xml:space="preserve">4.78308486938477</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72604560852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7790093421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80752944946289</t>
+    <t xml:space="preserve">4.72604513168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77900981903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80752992630005</t>
   </si>
   <si>
     <t xml:space="preserve">4.86456775665283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04790544509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01531219482422</t>
+    <t xml:space="preserve">5.04790592193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01531267166138</t>
   </si>
   <si>
     <t xml:space="preserve">4.89716100692749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91753196716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88901329040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04383087158203</t>
+    <t xml:space="preserve">4.91753244400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88901281356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04383134841919</t>
   </si>
   <si>
     <t xml:space="preserve">4.90531015396118</t>
@@ -722,10 +722,10 @@
     <t xml:space="preserve">4.95012521743774</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05198097229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97864437103271</t>
+    <t xml:space="preserve">5.05198049545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97864484786987</t>
   </si>
   <si>
     <t xml:space="preserve">5.03160905838013</t>
@@ -737,43 +737,43 @@
     <t xml:space="preserve">5.23939228057861</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19865036010742</t>
+    <t xml:space="preserve">5.19864988327026</t>
   </si>
   <si>
     <t xml:space="preserve">5.14568567276001</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19457626342773</t>
+    <t xml:space="preserve">5.19457578659058</t>
   </si>
   <si>
     <t xml:space="preserve">5.05605411529541</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06420230865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13346338272095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11716651916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25161504745483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18235492706299</t>
+    <t xml:space="preserve">5.06420278549194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13346385955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1171669960022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25161600112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18235397338867</t>
   </si>
   <si>
     <t xml:space="preserve">5.17827987670898</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25568866729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27198505401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17420530319214</t>
+    <t xml:space="preserve">5.25568914413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27198457717896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17420482635498</t>
   </si>
   <si>
     <t xml:space="preserve">5.16605663299561</t>
@@ -785,13 +785,13 @@
     <t xml:space="preserve">5.10494518280029</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07234954833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94605112075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06827640533447</t>
+    <t xml:space="preserve">5.07235050201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94605159759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06827592849731</t>
   </si>
   <si>
     <t xml:space="preserve">4.98679304122925</t>
@@ -800,7 +800,7 @@
     <t xml:space="preserve">5.0369119644165</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3626823425293</t>
+    <t xml:space="preserve">5.36268186569214</t>
   </si>
   <si>
     <t xml:space="preserve">5.39191770553589</t>
@@ -821,13 +821,13 @@
     <t xml:space="preserve">5.32091665267944</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33762264251709</t>
+    <t xml:space="preserve">5.33762311935425</t>
   </si>
   <si>
     <t xml:space="preserve">5.27079820632935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27497386932373</t>
+    <t xml:space="preserve">5.27497434616089</t>
   </si>
   <si>
     <t xml:space="preserve">5.1872673034668</t>
@@ -836,7 +836,7 @@
     <t xml:space="preserve">5.13297271728516</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20397329330444</t>
+    <t xml:space="preserve">5.2039737701416</t>
   </si>
   <si>
     <t xml:space="preserve">5.22903347015381</t>
@@ -848,16 +848,16 @@
     <t xml:space="preserve">5.26244497299194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1830906867981</t>
+    <t xml:space="preserve">5.18309116363525</t>
   </si>
   <si>
     <t xml:space="preserve">5.21232652664185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17891454696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24991512298584</t>
+    <t xml:space="preserve">5.17891502380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24991464614868</t>
   </si>
   <si>
     <t xml:space="preserve">5.24573850631714</t>
@@ -866,13 +866,13 @@
     <t xml:space="preserve">5.28332757949829</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22485589981079</t>
+    <t xml:space="preserve">5.22485637664795</t>
   </si>
   <si>
     <t xml:space="preserve">5.30003356933594</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33344697952271</t>
+    <t xml:space="preserve">5.33344650268555</t>
   </si>
   <si>
     <t xml:space="preserve">5.40444707870483</t>
@@ -881,28 +881,28 @@
     <t xml:space="preserve">5.37521123886108</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40027093887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38356494903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37938833236694</t>
+    <t xml:space="preserve">5.40027046203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3835654258728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37938785552979</t>
   </si>
   <si>
     <t xml:space="preserve">5.23320960998535</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30838775634766</t>
+    <t xml:space="preserve">5.3083872795105</t>
   </si>
   <si>
     <t xml:space="preserve">5.2582688331604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2081503868103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13714933395386</t>
+    <t xml:space="preserve">5.20814990997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1371488571167</t>
   </si>
   <si>
     <t xml:space="preserve">5.11208963394165</t>
@@ -917,13 +917,13 @@
     <t xml:space="preserve">5.32509279251099</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30420970916748</t>
+    <t xml:space="preserve">5.30421018600464</t>
   </si>
   <si>
     <t xml:space="preserve">5.29585695266724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32926940917969</t>
+    <t xml:space="preserve">5.32926893234253</t>
   </si>
   <si>
     <t xml:space="preserve">5.48797798156738</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.53809690475464</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5965690612793</t>
+    <t xml:space="preserve">5.59656858444214</t>
   </si>
   <si>
     <t xml:space="preserve">5.62580347061157</t>
@@ -941,19 +941,19 @@
     <t xml:space="preserve">5.68845272064209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61327505111694</t>
+    <t xml:space="preserve">5.61327457427979</t>
   </si>
   <si>
     <t xml:space="preserve">5.57568550109863</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44203615188599</t>
+    <t xml:space="preserve">5.44203567504883</t>
   </si>
   <si>
     <t xml:space="preserve">5.62162733078003</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68009901046753</t>
+    <t xml:space="preserve">5.68009853363037</t>
   </si>
   <si>
     <t xml:space="preserve">5.64251089096069</t>
@@ -962,16 +962,16 @@
     <t xml:space="preserve">5.37103509902954</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39609336853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38774108886719</t>
+    <t xml:space="preserve">5.39609384536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38774156570435</t>
   </si>
   <si>
     <t xml:space="preserve">5.2415623664856</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29168033599854</t>
+    <t xml:space="preserve">5.29168081283569</t>
   </si>
   <si>
     <t xml:space="preserve">5.19562005996704</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">4.81973171234131</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8030252456665</t>
+    <t xml:space="preserve">4.80302572250366</t>
   </si>
   <si>
     <t xml:space="preserve">4.84478950500488</t>
@@ -1004,19 +1004,19 @@
     <t xml:space="preserve">4.90326261520386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86567354202271</t>
+    <t xml:space="preserve">4.86567401885986</t>
   </si>
   <si>
     <t xml:space="preserve">4.87820339202881</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8531436920166</t>
+    <t xml:space="preserve">4.85314416885376</t>
   </si>
   <si>
     <t xml:space="preserve">4.81137800216675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95755767822266</t>
+    <t xml:space="preserve">4.95755815505981</t>
   </si>
   <si>
     <t xml:space="preserve">4.92832183837891</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">4.70278835296631</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6735520362854</t>
+    <t xml:space="preserve">4.67355251312256</t>
   </si>
   <si>
     <t xml:space="preserve">4.64014005661011</t>
@@ -1067,25 +1067,25 @@
     <t xml:space="preserve">4.7320237159729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71114063262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67772912979126</t>
+    <t xml:space="preserve">4.71114110946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67772960662842</t>
   </si>
   <si>
     <t xml:space="preserve">4.9157919883728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92414474487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89490842819214</t>
+    <t xml:space="preserve">4.92414426803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8949089050293</t>
   </si>
   <si>
     <t xml:space="preserve">4.84061431884766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16220760345459</t>
+    <t xml:space="preserve">5.16220808029175</t>
   </si>
   <si>
     <t xml:space="preserve">4.99932241439819</t>
@@ -1094,16 +1094,16 @@
     <t xml:space="preserve">5.0202054977417</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17056035995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09955930709839</t>
+    <t xml:space="preserve">5.17056083679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09955978393555</t>
   </si>
   <si>
     <t xml:space="preserve">4.95338153839111</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78631925582886</t>
+    <t xml:space="preserve">4.78631973266602</t>
   </si>
   <si>
     <t xml:space="preserve">4.68608140945435</t>
@@ -1112,10 +1112,10 @@
     <t xml:space="preserve">4.60672760009766</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59419775009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6150803565979</t>
+    <t xml:space="preserve">4.59419822692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61508083343506</t>
   </si>
   <si>
     <t xml:space="preserve">4.63178730010986</t>
@@ -1130,19 +1130,19 @@
     <t xml:space="preserve">4.55243301391602</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53990316390991</t>
+    <t xml:space="preserve">4.53990268707275</t>
   </si>
   <si>
     <t xml:space="preserve">4.57749176025391</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48978424072266</t>
+    <t xml:space="preserve">4.48978471755981</t>
   </si>
   <si>
     <t xml:space="preserve">4.41043043136597</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4438419342041</t>
+    <t xml:space="preserve">4.44384241104126</t>
   </si>
   <si>
     <t xml:space="preserve">4.4939603805542</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">4.47307777404785</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51901960372925</t>
+    <t xml:space="preserve">4.51902008056641</t>
   </si>
   <si>
     <t xml:space="preserve">4.5691385269165</t>
@@ -1160,10 +1160,10 @@
     <t xml:space="preserve">4.59002161026001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65684604644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64849233627319</t>
+    <t xml:space="preserve">4.65684652328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64849281311035</t>
   </si>
   <si>
     <t xml:space="preserve">4.59837436676025</t>
@@ -1178,13 +1178,13 @@
     <t xml:space="preserve">4.43966579437256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36031150817871</t>
+    <t xml:space="preserve">4.36031198501587</t>
   </si>
   <si>
     <t xml:space="preserve">4.38537073135376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18907308578491</t>
+    <t xml:space="preserve">4.18907356262207</t>
   </si>
   <si>
     <t xml:space="preserve">4.16150760650635</t>
@@ -1199,25 +1199,25 @@
     <t xml:space="preserve">4.19324970245361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09802436828613</t>
+    <t xml:space="preserve">4.09802484512329</t>
   </si>
   <si>
     <t xml:space="preserve">4.1531548500061</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10303688049316</t>
+    <t xml:space="preserve">4.10303640365601</t>
   </si>
   <si>
     <t xml:space="preserve">4.12642478942871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16986131668091</t>
+    <t xml:space="preserve">4.16986083984375</t>
   </si>
   <si>
     <t xml:space="preserve">4.17654418945312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14313077926636</t>
+    <t xml:space="preserve">4.14313125610352</t>
   </si>
   <si>
     <t xml:space="preserve">4.16819047927856</t>
@@ -1226,10 +1226,10 @@
     <t xml:space="preserve">2.8300256729126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90687441825867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84339094161987</t>
+    <t xml:space="preserve">2.90687417984009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84339070320129</t>
   </si>
   <si>
     <t xml:space="preserve">2.87179136276245</t>
@@ -1238,34 +1238,34 @@
     <t xml:space="preserve">2.89350914955139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80162501335144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92358064651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94863986968994</t>
+    <t xml:space="preserve">2.80162477493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92358040809631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94863963127136</t>
   </si>
   <si>
     <t xml:space="preserve">3.01713514328003</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08061838150024</t>
+    <t xml:space="preserve">3.08061861991882</t>
   </si>
   <si>
     <t xml:space="preserve">3.17083144187927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14911389350891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15746712684631</t>
+    <t xml:space="preserve">3.14911365509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15746688842773</t>
   </si>
   <si>
     <t xml:space="preserve">3.14410161972046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17918515205383</t>
+    <t xml:space="preserve">3.17918491363525</t>
   </si>
   <si>
     <t xml:space="preserve">3.17417311668396</t>
@@ -1283,19 +1283,19 @@
     <t xml:space="preserve">2.94529795646667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95699286460876</t>
+    <t xml:space="preserve">2.95699262619019</t>
   </si>
   <si>
     <t xml:space="preserve">2.89852118492126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84004902839661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82501363754272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85007309913635</t>
+    <t xml:space="preserve">2.84004878997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8250138759613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85007333755493</t>
   </si>
   <si>
     <t xml:space="preserve">2.74649500846863</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">2.51093792915344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58945727348328</t>
+    <t xml:space="preserve">2.58945751190186</t>
   </si>
   <si>
     <t xml:space="preserve">2.5009138584137</t>
@@ -1322,10 +1322,10 @@
     <t xml:space="preserve">2.50592589378357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47919607162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41905355453491</t>
+    <t xml:space="preserve">2.47919583320618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41905379295349</t>
   </si>
   <si>
     <t xml:space="preserve">2.39566540718079</t>
@@ -1340,10 +1340,10 @@
     <t xml:space="preserve">2.3772885799408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2753803730011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.313805103302</t>
+    <t xml:space="preserve">2.27538061141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31380534172058</t>
   </si>
   <si>
     <t xml:space="preserve">2.2620153427124</t>
@@ -1355,28 +1355,28 @@
     <t xml:space="preserve">2.41404247283936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38062930107117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30043959617615</t>
+    <t xml:space="preserve">2.38062953948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30043935775757</t>
   </si>
   <si>
     <t xml:space="preserve">2.30211091041565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29709887504578</t>
+    <t xml:space="preserve">2.29709911346436</t>
   </si>
   <si>
     <t xml:space="preserve">2.32382845878601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33552265167236</t>
+    <t xml:space="preserve">2.33552289009094</t>
   </si>
   <si>
     <t xml:space="preserve">2.35389971733093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36559438705444</t>
+    <t xml:space="preserve">2.36559414863586</t>
   </si>
   <si>
     <t xml:space="preserve">2.35055828094482</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">2.35222935676575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35556983947754</t>
+    <t xml:space="preserve">2.35557007789612</t>
   </si>
   <si>
     <t xml:space="preserve">2.25533318519592</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">2.42406535148621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31881642341614</t>
+    <t xml:space="preserve">2.31881666183472</t>
   </si>
   <si>
     <t xml:space="preserve">2.30879330635071</t>
@@ -1421,28 +1421,28 @@
     <t xml:space="preserve">2.34387588500977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33218121528625</t>
+    <t xml:space="preserve">2.33218097686768</t>
   </si>
   <si>
     <t xml:space="preserve">2.27371001243591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18850874900818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17681431770325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15342569351196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21022653579712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2118968963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05485892295837</t>
+    <t xml:space="preserve">2.18850898742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17681455612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15342545509338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21022629737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21189713478088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05485916137695</t>
   </si>
   <si>
     <t xml:space="preserve">2.01142263412476</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">2.16846084594727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15509581565857</t>
+    <t xml:space="preserve">2.15509629249573</t>
   </si>
   <si>
     <t xml:space="preserve">2.15676641464233</t>
@@ -1496,25 +1496,25 @@
     <t xml:space="preserve">2.09662485122681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09161257743835</t>
+    <t xml:space="preserve">2.09161281585693</t>
   </si>
   <si>
     <t xml:space="preserve">2.02478766441345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02645874023438</t>
+    <t xml:space="preserve">2.02645897865295</t>
   </si>
   <si>
     <t xml:space="preserve">2.12502455711365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23695635795593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18683791160583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11834216117859</t>
+    <t xml:space="preserve">2.23695611953735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18683767318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11834192276001</t>
   </si>
   <si>
     <t xml:space="preserve">2.06989502906799</t>
@@ -1547,7 +1547,7 @@
     <t xml:space="preserve">1.65391063690186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62885141372681</t>
+    <t xml:space="preserve">1.6288515329361</t>
   </si>
   <si>
     <t xml:space="preserve">1.62968707084656</t>
@@ -1565,13 +1565,13 @@
     <t xml:space="preserve">1.31728148460388</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28553974628448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27133941650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24962174892426</t>
+    <t xml:space="preserve">1.2855396270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27133929729462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24962162971497</t>
   </si>
   <si>
     <t xml:space="preserve">1.24460971355438</t>
@@ -1583,13 +1583,13 @@
     <t xml:space="preserve">1.27635133266449</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30391645431519</t>
+    <t xml:space="preserve">1.30391657352448</t>
   </si>
   <si>
     <t xml:space="preserve">1.31561100482941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31310486793518</t>
+    <t xml:space="preserve">1.31310498714447</t>
   </si>
   <si>
     <t xml:space="preserve">1.2838693857193</t>
@@ -1598,19 +1598,19 @@
     <t xml:space="preserve">1.27969288825989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33899998664856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35152912139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29472815990448</t>
+    <t xml:space="preserve">1.33899986743927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35152924060822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29472827911377</t>
   </si>
   <si>
     <t xml:space="preserve">1.29639852046967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2429393529892</t>
+    <t xml:space="preserve">1.24293923377991</t>
   </si>
   <si>
     <t xml:space="preserve">1.25212776660919</t>
@@ -1622,22 +1622,22 @@
     <t xml:space="preserve">1.25296247005463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23375070095062</t>
+    <t xml:space="preserve">1.23375082015991</t>
   </si>
   <si>
     <t xml:space="preserve">1.25630402565002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25797438621521</t>
+    <t xml:space="preserve">1.2579745054245</t>
   </si>
   <si>
     <t xml:space="preserve">1.26048052310944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36823558807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36990582942963</t>
+    <t xml:space="preserve">1.36823570728302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36990594863892</t>
   </si>
   <si>
     <t xml:space="preserve">1.36405920982361</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">1.31477534770966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34484684467316</t>
+    <t xml:space="preserve">1.34484672546387</t>
   </si>
   <si>
     <t xml:space="preserve">1.25129199028015</t>
@@ -1661,13 +1661,13 @@
     <t xml:space="preserve">1.06835901737213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962275266647339</t>
+    <t xml:space="preserve">0.962275326251984</t>
   </si>
   <si>
     <t xml:space="preserve">0.989840626716614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.633163273334503</t>
+    <t xml:space="preserve">0.633163213729858</t>
   </si>
   <si>
     <t xml:space="preserve">0.703329861164093</t>
@@ -1679,16 +1679,16 @@
     <t xml:space="preserve">0.862038254737854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958098888397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948074817657471</t>
+    <t xml:space="preserve">0.958098948001862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948074877262115</t>
   </si>
   <si>
     <t xml:space="preserve">0.848673403263092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.913827061653137</t>
+    <t xml:space="preserve">0.913827121257782</t>
   </si>
   <si>
     <t xml:space="preserve">0.9447340965271</t>
@@ -1697,7 +1697,7 @@
     <t xml:space="preserve">0.9188392162323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.917168915271759</t>
+    <t xml:space="preserve">0.917168855667114</t>
   </si>
   <si>
     <t xml:space="preserve">1.00487577915192</t>
@@ -1709,7 +1709,7 @@
     <t xml:space="preserve">1.11430132389069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09926617145538</t>
+    <t xml:space="preserve">1.09926605224609</t>
   </si>
   <si>
     <t xml:space="preserve">1.13184344768524</t>
@@ -1718,13 +1718,13 @@
     <t xml:space="preserve">1.10344243049622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03578269481659</t>
+    <t xml:space="preserve">1.03578281402588</t>
   </si>
   <si>
     <t xml:space="preserve">1.01155817508698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01824069023132</t>
+    <t xml:space="preserve">1.01824057102203</t>
   </si>
   <si>
     <t xml:space="preserve">0.999029040336609</t>
@@ -1733,22 +1733,22 @@
     <t xml:space="preserve">1.01573550701141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01322937011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08255970478058</t>
+    <t xml:space="preserve">1.01322948932648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08255958557129</t>
   </si>
   <si>
     <t xml:space="preserve">1.10177206993103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12766623497009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12933754920959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13017213344574</t>
+    <t xml:space="preserve">1.1276661157608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12933743000031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13017225265503</t>
   </si>
   <si>
     <t xml:space="preserve">1.1368545293808</t>
@@ -1757,34 +1757,34 @@
     <t xml:space="preserve">1.11346650123596</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10260677337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06585323810577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03244113922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07086515426636</t>
+    <t xml:space="preserve">1.10260689258575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06585311889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0324410200119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07086503505707</t>
   </si>
   <si>
     <t xml:space="preserve">1.06334805488586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01907634735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03494703769684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06501853466034</t>
+    <t xml:space="preserve">1.01907646656036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03494715690613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06501841545105</t>
   </si>
   <si>
     <t xml:space="preserve">1.12850177288055</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08506572246552</t>
+    <t xml:space="preserve">1.08506560325623</t>
   </si>
   <si>
     <t xml:space="preserve">1.08673596382141</t>
@@ -1793,7 +1793,7 @@
     <t xml:space="preserve">1.07253646850586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08088910579681</t>
+    <t xml:space="preserve">1.0808892250061</t>
   </si>
   <si>
     <t xml:space="preserve">1.1051127910614</t>
@@ -1808,13 +1808,13 @@
     <t xml:space="preserve">1.11263084411621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11012506484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2262327671051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46179032325745</t>
+    <t xml:space="preserve">1.11012494564056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22623288631439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46179020404816</t>
   </si>
   <si>
     <t xml:space="preserve">1.41584801673889</t>
@@ -1823,7 +1823,7 @@
     <t xml:space="preserve">1.414177775383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36071753501892</t>
+    <t xml:space="preserve">1.36071741580963</t>
   </si>
   <si>
     <t xml:space="preserve">1.33064615726471</t>
@@ -1841,28 +1841,28 @@
     <t xml:space="preserve">1.32981145381927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35069358348846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35487079620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32897591590881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36572957038879</t>
+    <t xml:space="preserve">1.35069346427917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35487067699432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3289760351181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36572968959808</t>
   </si>
   <si>
     <t xml:space="preserve">1.37157642841339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40248310565948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41918885707855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42169499397278</t>
+    <t xml:space="preserve">1.40248322486877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41918897628784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42169487476349</t>
   </si>
   <si>
     <t xml:space="preserve">1.42253053188324</t>
@@ -1877,22 +1877,22 @@
     <t xml:space="preserve">1.37575268745422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39412951469421</t>
+    <t xml:space="preserve">1.3941296339035</t>
   </si>
   <si>
     <t xml:space="preserve">1.45343661308289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43589532375336</t>
+    <t xml:space="preserve">1.43589544296265</t>
   </si>
   <si>
     <t xml:space="preserve">1.52861428260803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61131012439728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5971097946167</t>
+    <t xml:space="preserve">1.61131024360657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59710991382599</t>
   </si>
   <si>
     <t xml:space="preserve">1.59376907348633</t>
@@ -1904,7 +1904,7 @@
     <t xml:space="preserve">1.55283892154694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55116748809814</t>
+    <t xml:space="preserve">1.55116760730743</t>
   </si>
   <si>
     <t xml:space="preserve">1.51441490650177</t>
@@ -1913,13 +1913,13 @@
     <t xml:space="preserve">1.47097873687744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41751849651337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43422496318817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38828301429749</t>
+    <t xml:space="preserve">1.41751837730408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43422484397888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3882828950882</t>
   </si>
   <si>
     <t xml:space="preserve">1.38327062129974</t>
@@ -1928,7 +1928,7 @@
     <t xml:space="preserve">1.33231663703918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36740005016327</t>
+    <t xml:space="preserve">1.36739993095398</t>
   </si>
   <si>
     <t xml:space="preserve">1.34985876083374</t>
@@ -1937,28 +1937,28 @@
     <t xml:space="preserve">1.30308091640472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32229351997375</t>
+    <t xml:space="preserve">1.32229340076447</t>
   </si>
   <si>
     <t xml:space="preserve">1.31644582748413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29890465736389</t>
+    <t xml:space="preserve">1.2989045381546</t>
   </si>
   <si>
     <t xml:space="preserve">1.30892872810364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31059908866882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31895184516907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29222226142883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28721010684967</t>
+    <t xml:space="preserve">1.31059896945953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31895196437836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29222214221954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28721022605896</t>
   </si>
   <si>
     <t xml:space="preserve">1.25045645236969</t>
@@ -1997,10 +1997,10 @@
     <t xml:space="preserve">1.35821151733398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32312905788422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28219902515411</t>
+    <t xml:space="preserve">1.32312917709351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28219890594482</t>
   </si>
   <si>
     <t xml:space="preserve">1.24043321609497</t>
@@ -2012,13 +2012,13 @@
     <t xml:space="preserve">1.26131618022919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32646977901459</t>
+    <t xml:space="preserve">1.32646989822388</t>
   </si>
   <si>
     <t xml:space="preserve">1.33816409111023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42503654956818</t>
+    <t xml:space="preserve">1.42503666877747</t>
   </si>
   <si>
     <t xml:space="preserve">1.48183739185333</t>
@@ -2036,13 +2036,13 @@
     <t xml:space="preserve">1.54448533058167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56369769573212</t>
+    <t xml:space="preserve">1.56369757652283</t>
   </si>
   <si>
     <t xml:space="preserve">1.53863847255707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54866242408752</t>
+    <t xml:space="preserve">1.5486626625061</t>
   </si>
   <si>
     <t xml:space="preserve">1.49186062812805</t>
@@ -2054,22 +2054,22 @@
     <t xml:space="preserve">1.39329481124878</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39078879356384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4200245141983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37491810321808</t>
+    <t xml:space="preserve">1.39078891277313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42002439498901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37491798400879</t>
   </si>
   <si>
     <t xml:space="preserve">1.34818828105927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33148205280304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32814037799835</t>
+    <t xml:space="preserve">1.33148193359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32814025878906</t>
   </si>
   <si>
     <t xml:space="preserve">1.29723429679871</t>
@@ -2084,7 +2084,7 @@
     <t xml:space="preserve">1.33315229415894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26549255847931</t>
+    <t xml:space="preserve">1.26549243927002</t>
   </si>
   <si>
     <t xml:space="preserve">1.24210369586945</t>
@@ -2099,16 +2099,16 @@
     <t xml:space="preserve">1.38494122028351</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38911867141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37993001937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45260179042816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48852002620697</t>
+    <t xml:space="preserve">1.38911855220795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37993013858795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45260190963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48851990699768</t>
   </si>
   <si>
     <t xml:space="preserve">1.49687266349792</t>
@@ -2117,49 +2117,49 @@
     <t xml:space="preserve">1.50104904174805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.447589635849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39914178848267</t>
+    <t xml:space="preserve">1.44758975505829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39914166927338</t>
   </si>
   <si>
     <t xml:space="preserve">1.54281485080719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46095454692841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39162361621857</t>
+    <t xml:space="preserve">1.4609546661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39162373542786</t>
   </si>
   <si>
     <t xml:space="preserve">1.41000056266785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40833020210266</t>
+    <t xml:space="preserve">1.40833032131195</t>
   </si>
   <si>
     <t xml:space="preserve">1.42921280860901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40749454498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3339878320694</t>
+    <t xml:space="preserve">1.40749442577362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33398795127869</t>
   </si>
   <si>
     <t xml:space="preserve">1.32563412189484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33732867240906</t>
+    <t xml:space="preserve">1.33732879161835</t>
   </si>
   <si>
     <t xml:space="preserve">1.36155319213867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36907029151917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44508385658264</t>
+    <t xml:space="preserve">1.36907041072845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44508373737335</t>
   </si>
   <si>
     <t xml:space="preserve">1.4350597858429</t>
@@ -2168,7 +2168,7 @@
     <t xml:space="preserve">1.46596658229828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47181332111359</t>
+    <t xml:space="preserve">1.47181344032288</t>
   </si>
   <si>
     <t xml:space="preserve">1.46513104438782</t>
@@ -2183,31 +2183,31 @@
     <t xml:space="preserve">1.47014307975769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49269616603851</t>
+    <t xml:space="preserve">1.4926962852478</t>
   </si>
   <si>
     <t xml:space="preserve">1.52276766300201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54030871391296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53529691696167</t>
+    <t xml:space="preserve">1.54030883312225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53529679775238</t>
   </si>
   <si>
     <t xml:space="preserve">1.59794533252716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60629820823669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58625102043152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64555788040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59293329715729</t>
+    <t xml:space="preserve">1.6062980890274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58625090122223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64555776119232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59293341636658</t>
   </si>
   <si>
     <t xml:space="preserve">1.63219308853149</t>
@@ -2222,22 +2222,22 @@
     <t xml:space="preserve">1.54197919368744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55868554115295</t>
+    <t xml:space="preserve">1.55868566036224</t>
   </si>
   <si>
     <t xml:space="preserve">1.56620359420776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56703853607178</t>
+    <t xml:space="preserve">1.56703841686249</t>
   </si>
   <si>
     <t xml:space="preserve">1.58708655834198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64973437786102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74078297615051</t>
+    <t xml:space="preserve">1.64973449707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7407830953598</t>
   </si>
   <si>
     <t xml:space="preserve">1.70737075805664</t>
@@ -2246,13 +2246,13 @@
     <t xml:space="preserve">1.71906530857086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72908842563629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7123829126358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73243021965027</t>
+    <t xml:space="preserve">1.72908854484558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71238303184509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73243033885956</t>
   </si>
   <si>
     <t xml:space="preserve">1.69233477115631</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">1.74913585186005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72073566913605</t>
+    <t xml:space="preserve">1.72073578834534</t>
   </si>
   <si>
     <t xml:space="preserve">1.63887560367584</t>
@@ -2279,100 +2279,100 @@
     <t xml:space="preserve">1.67061710357666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68732368946075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67562913894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68064105510712</t>
+    <t xml:space="preserve">1.68732357025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67562925815582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68064117431641</t>
   </si>
   <si>
     <t xml:space="preserve">1.61715698242188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61548662185669</t>
+    <t xml:space="preserve">1.61548674106598</t>
   </si>
   <si>
     <t xml:space="preserve">1.62467503547668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61047458648682</t>
+    <t xml:space="preserve">1.61047446727753</t>
   </si>
   <si>
     <t xml:space="preserve">1.64054584503174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62383961677551</t>
+    <t xml:space="preserve">1.62383949756622</t>
   </si>
   <si>
     <t xml:space="preserve">1.60963988304138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57789826393127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5912629365921</t>
+    <t xml:space="preserve">1.57789814472198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59126305580139</t>
   </si>
   <si>
     <t xml:space="preserve">1.56202721595764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59209775924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59543943405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58290922641754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60379207134247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6004513502121</t>
+    <t xml:space="preserve">1.59209764003754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59543931484222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58290934562683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60379219055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60045123100281</t>
   </si>
   <si>
     <t xml:space="preserve">1.58541524410248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54532086849213</t>
+    <t xml:space="preserve">1.54532074928284</t>
   </si>
   <si>
     <t xml:space="preserve">1.54699122905731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57706260681152</t>
+    <t xml:space="preserve">1.57706248760223</t>
   </si>
   <si>
     <t xml:space="preserve">1.43756556510925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4943665266037</t>
+    <t xml:space="preserve">1.49436664581299</t>
   </si>
   <si>
     <t xml:space="preserve">1.48935568332672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46763718128204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51274371147156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52610838413239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53195595741272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54782676696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51691997051239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50940263271332</t>
+    <t xml:space="preserve">1.46763706207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51274359226227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52610850334167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53195607662201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54782688617706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5169198513031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50940275192261</t>
   </si>
   <si>
     <t xml:space="preserve">1.48267209529877</t>
@@ -2387,28 +2387,28 @@
     <t xml:space="preserve">1.18029069900513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16692566871643</t>
+    <t xml:space="preserve">1.16692578792572</t>
   </si>
   <si>
     <t xml:space="preserve">1.13601982593536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02742898464203</t>
+    <t xml:space="preserve">1.02742910385132</t>
   </si>
   <si>
     <t xml:space="preserve">0.933039724826813</t>
   </si>
   <si>
-    <t xml:space="preserve">0.776836395263672</t>
+    <t xml:space="preserve">0.776836454868317</t>
   </si>
   <si>
     <t xml:space="preserve">0.719200670719147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.695811808109283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54670923948288</t>
+    <t xml:space="preserve">0.695811867713928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.546709179878235</t>
   </si>
   <si>
     <t xml:space="preserve">0.613534212112427</t>
@@ -2435,7 +2435,7 @@
     <t xml:space="preserve">0.682446956634521</t>
   </si>
   <si>
-    <t xml:space="preserve">0.680358290672302</t>
+    <t xml:space="preserve">0.680358350276947</t>
   </si>
   <si>
     <t xml:space="preserve">0.687876343727112</t>
@@ -2444,7 +2444,7 @@
     <t xml:space="preserve">0.659893691539764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643604516983032</t>
+    <t xml:space="preserve">0.643604576587677</t>
   </si>
   <si>
     <t xml:space="preserve">0.659475445747375</t>
@@ -2453,16 +2453,16 @@
     <t xml:space="preserve">0.64318722486496</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627316415309906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.576780557632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618127942085266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.660728454589844</t>
+    <t xml:space="preserve">0.627316355705261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.576780498027802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618128001689911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.660728514194489</t>
   </si>
   <si>
     <t xml:space="preserve">0.646528840065002</t>
@@ -2474,10 +2474,10 @@
     <t xml:space="preserve">0.638175189495087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649869680404663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640263795852661</t>
+    <t xml:space="preserve">0.649869620800018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640263855457306</t>
   </si>
   <si>
     <t xml:space="preserve">0.612281143665314</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">0.61562192440033</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610192596912384</t>
+    <t xml:space="preserve">0.610192537307739</t>
   </si>
   <si>
     <t xml:space="preserve">0.60559868812561</t>
@@ -2498,7 +2498,7 @@
     <t xml:space="preserve">0.651540040969849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.676599323749542</t>
+    <t xml:space="preserve">0.676599264144897</t>
   </si>
   <si>
     <t xml:space="preserve">0.654881715774536</t>
@@ -2507,7 +2507,7 @@
     <t xml:space="preserve">0.642351627349854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641516864299774</t>
+    <t xml:space="preserve">0.641516923904419</t>
   </si>
   <si>
     <t xml:space="preserve">0.655717313289642</t>
@@ -2522,10 +2522,10 @@
     <t xml:space="preserve">0.668246448040009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.650286972522736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6264808177948</t>
+    <t xml:space="preserve">0.65028703212738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.626480758190155</t>
   </si>
   <si>
     <t xml:space="preserve">0.609775185585022</t>
@@ -2534,16 +2534,16 @@
     <t xml:space="preserve">0.606016159057617</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629822432994843</t>
+    <t xml:space="preserve">0.629822373390198</t>
   </si>
   <si>
     <t xml:space="preserve">0.596827805042267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.574691891670227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.581792593002319</t>
+    <t xml:space="preserve">0.574691951274872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.581792533397675</t>
   </si>
   <si>
     <t xml:space="preserve">0.57427453994751</t>
@@ -2558,10 +2558,10 @@
     <t xml:space="preserve">0.726300537586212</t>
   </si>
   <si>
-    <t xml:space="preserve">0.789366543292999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.763054192066193</t>
+    <t xml:space="preserve">0.789366483688354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.763054251670837</t>
   </si>
   <si>
     <t xml:space="preserve">0.768483519554138</t>
@@ -2573,7 +2573,7 @@
     <t xml:space="preserve">0.83530855178833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.901298046112061</t>
+    <t xml:space="preserve">0.901297986507416</t>
   </si>
   <si>
     <t xml:space="preserve">0.910486400127411</t>
@@ -2582,13 +2582,13 @@
     <t xml:space="preserve">1.00571131706238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01072359085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968957722187042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877909064292908</t>
+    <t xml:space="preserve">1.01072347164154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968957781791687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877909004688263</t>
   </si>
   <si>
     <t xml:space="preserve">0.924685895442963</t>
@@ -2603,31 +2603,31 @@
     <t xml:space="preserve">0.922180891036987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.892109572887421</t>
+    <t xml:space="preserve">0.892109513282776</t>
   </si>
   <si>
     <t xml:space="preserve">0.893779993057251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.895450294017792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823614120483398</t>
+    <t xml:space="preserve">0.895450234413147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823614239692688</t>
   </si>
   <si>
     <t xml:space="preserve">0.781013607978821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.824867188930511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806072950363159</t>
+    <t xml:space="preserve">0.824867248535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806072890758514</t>
   </si>
   <si>
     <t xml:space="preserve">0.78560745716095</t>
   </si>
   <si>
-    <t xml:space="preserve">0.802313923835754</t>
+    <t xml:space="preserve">0.802313983440399</t>
   </si>
   <si>
     <t xml:space="preserve">0.797719240188599</t>
@@ -2636,28 +2636,28 @@
     <t xml:space="preserve">0.801895618438721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.79855489730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776419043540955</t>
+    <t xml:space="preserve">0.798554956912994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77641898393631</t>
   </si>
   <si>
     <t xml:space="preserve">0.782266676425934</t>
   </si>
   <si>
-    <t xml:space="preserve">0.766394913196564</t>
+    <t xml:space="preserve">0.766394972801208</t>
   </si>
   <si>
     <t xml:space="preserve">0.821525514125824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.795631468296051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863708555698395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855355799198151</t>
+    <t xml:space="preserve">0.795631527900696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86370861530304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855355739593506</t>
   </si>
   <si>
     <t xml:space="preserve">0.844496965408325</t>
@@ -2666,52 +2666,52 @@
     <t xml:space="preserve">0.857861816883087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.836143314838409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.834890425205231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838649392127991</t>
+    <t xml:space="preserve">0.836143374443054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834890365600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838649332523346</t>
   </si>
   <si>
     <t xml:space="preserve">0.800225257873535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.773912906646729</t>
+    <t xml:space="preserve">0.773912966251373</t>
   </si>
   <si>
     <t xml:space="preserve">0.789783835411072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77182525396347</t>
+    <t xml:space="preserve">0.771825194358826</t>
   </si>
   <si>
     <t xml:space="preserve">0.767230629920959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.775583386421204</t>
+    <t xml:space="preserve">0.775583326816559</t>
   </si>
   <si>
     <t xml:space="preserve">0.786860406398773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.792707145214081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.758877754211426</t>
+    <t xml:space="preserve">0.792707204818726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.758877813816071</t>
   </si>
   <si>
     <t xml:space="preserve">0.765977621078491</t>
   </si>
   <si>
-    <t xml:space="preserve">0.800642669200897</t>
+    <t xml:space="preserve">0.800642609596252</t>
   </si>
   <si>
     <t xml:space="preserve">0.809831023216248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.799807906150818</t>
+    <t xml:space="preserve">0.799807846546173</t>
   </si>
   <si>
     <t xml:space="preserve">0.780178070068359</t>
@@ -2720,25 +2720,25 @@
     <t xml:space="preserve">0.770989596843719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.740918278694153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.717947661876678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.712100028991699</t>
+    <t xml:space="preserve">0.740918338298798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.717947721481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.712099969387054</t>
   </si>
   <si>
     <t xml:space="preserve">0.684117317199707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.690799713134766</t>
+    <t xml:space="preserve">0.69079977273941</t>
   </si>
   <si>
     <t xml:space="preserve">0.69288843870163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.685787737369537</t>
+    <t xml:space="preserve">0.685787796974182</t>
   </si>
   <si>
     <t xml:space="preserve">0.674094140529633</t>
@@ -2750,28 +2750,28 @@
     <t xml:space="preserve">0.682029604911804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.687459051609039</t>
+    <t xml:space="preserve">0.687458992004395</t>
   </si>
   <si>
     <t xml:space="preserve">0.685370326042175</t>
   </si>
   <si>
-    <t xml:space="preserve">0.67785233259201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.694558799266815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.697482168674469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.703747272491455</t>
+    <t xml:space="preserve">0.677852272987366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69455873966217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.697482109069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.70374721288681</t>
   </si>
   <si>
     <t xml:space="preserve">0.69831782579422</t>
   </si>
   <si>
-    <t xml:space="preserve">0.721288442611694</t>
+    <t xml:space="preserve">0.721288502216339</t>
   </si>
   <si>
     <t xml:space="preserve">0.720453679561615</t>
@@ -2780,10 +2780,10 @@
     <t xml:space="preserve">0.742588698863983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.767647981643677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.718365013599396</t>
+    <t xml:space="preserve">0.767647922039032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.718365073204041</t>
   </si>
   <si>
     <t xml:space="preserve">0.71502423286438</t>
@@ -2795,10 +2795,10 @@
     <t xml:space="preserve">0.757207453250885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778925001621246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796466171741486</t>
+    <t xml:space="preserve">0.778925061225891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79646623134613</t>
   </si>
   <si>
     <t xml:space="preserve">0.825284540653229</t>
@@ -2807,7 +2807,7 @@
     <t xml:space="preserve">0.850343704223633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.860367834568024</t>
+    <t xml:space="preserve">0.860367894172668</t>
   </si>
   <si>
     <t xml:space="preserve">0.847003042697906</t>
@@ -2819,25 +2819,25 @@
     <t xml:space="preserve">0.843661367893219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.872062265872955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852014183998108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8545201420784</t>
+    <t xml:space="preserve">0.872062206268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852014243602753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.854520082473755</t>
   </si>
   <si>
     <t xml:space="preserve">0.812755346298218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.807743310928345</t>
+    <t xml:space="preserve">0.80774337053299</t>
   </si>
   <si>
     <t xml:space="preserve">0.813172698020935</t>
   </si>
   <si>
-    <t xml:space="preserve">0.828626155853271</t>
+    <t xml:space="preserve">0.828626096248627</t>
   </si>
   <si>
     <t xml:space="preserve">0.832802534103394</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">0.820690751075745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.74968945980072</t>
+    <t xml:space="preserve">0.749689400196075</t>
   </si>
   <si>
     <t xml:space="preserve">0.710846960544586</t>
@@ -2855,19 +2855,19 @@
     <t xml:space="preserve">0.654464364051819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.633998811244965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.645275831222534</t>
+    <t xml:space="preserve">0.63399875164032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.645275890827179</t>
   </si>
   <si>
     <t xml:space="preserve">0.660311102867126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.684534668922424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.689129412174225</t>
+    <t xml:space="preserve">0.684534728527069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.68912935256958</t>
   </si>
   <si>
     <t xml:space="preserve">0.753030061721802</t>
@@ -2879,13 +2879,13 @@
     <t xml:space="preserve">0.787696063518524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803148627281189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856191456317902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.845331847667694</t>
+    <t xml:space="preserve">0.803148686885834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856191515922546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.845331788063049</t>
   </si>
   <si>
     <t xml:space="preserve">0.877073347568512</t>
@@ -2903,19 +2903,19 @@
     <t xml:space="preserve">0.89043915271759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.88125067949295</t>
+    <t xml:space="preserve">0.881250739097595</t>
   </si>
   <si>
     <t xml:space="preserve">0.904638767242432</t>
   </si>
   <si>
-    <t xml:space="preserve">0.89294421672821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.90213268995285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88208544254303</t>
+    <t xml:space="preserve">0.892944276332855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902132749557495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882085382938385</t>
   </si>
   <si>
     <t xml:space="preserve">0.867885053157806</t>
@@ -2930,7 +2930,7 @@
     <t xml:space="preserve">0.841991007328033</t>
   </si>
   <si>
-    <t xml:space="preserve">0.840320527553558</t>
+    <t xml:space="preserve">0.840320587158203</t>
   </si>
   <si>
     <t xml:space="preserve">0.859532177448273</t>
@@ -2948,13 +2948,13 @@
     <t xml:space="preserve">0.906310081481934</t>
   </si>
   <si>
-    <t xml:space="preserve">0.943898499011993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953922510147095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9572634100914</t>
+    <t xml:space="preserve">0.943898439407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95392256975174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957263290882111</t>
   </si>
   <si>
     <t xml:space="preserve">0.965616941452026</t>
@@ -2963,22 +2963,22 @@
     <t xml:space="preserve">0.978146135807037</t>
   </si>
   <si>
-    <t xml:space="preserve">0.961439788341522</t>
+    <t xml:space="preserve">0.961439669132233</t>
   </si>
   <si>
     <t xml:space="preserve">0.934710025787354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.902968347072601</t>
+    <t xml:space="preserve">0.902968406677246</t>
   </si>
   <si>
     <t xml:space="preserve">0.87456738948822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.852849841117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867050230503082</t>
+    <t xml:space="preserve">0.852849781513214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867050170898438</t>
   </si>
   <si>
     <t xml:space="preserve">0.878744721412659</t>
@@ -3008,34 +3008,34 @@
     <t xml:space="preserve">0.929698050022125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.93888658285141</t>
-  </si>
-  <si>
-    <t xml:space="pr